--- a/server_nestjs/src/storage/Kompetenzraster.xlsx
+++ b/server_nestjs/src/storage/Kompetenzraster.xlsx
@@ -62,7 +62,7 @@
     <author> </author>
   </authors>
   <commentList>
-    <comment ref="K5" authorId="0">
+    <comment ref="L5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="337">
   <si>
     <t xml:space="preserve">Voraussetzungen lt. Modulhandbuch</t>
   </si>
@@ -655,6 +655,9 @@
     <t xml:space="preserve">ConceptNodeID</t>
   </si>
   <si>
+    <t xml:space="preserve">ConceptEdge</t>
+  </si>
+  <si>
     <t xml:space="preserve">ContentNodeID</t>
   </si>
   <si>
@@ -673,6 +676,9 @@
     <t xml:space="preserve">1,2</t>
   </si>
   <si>
+    <t xml:space="preserve">Beispielhafte Beschreibung</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pro Zeile eine ContentNode = ContentView</t>
   </si>
   <si>
@@ -724,6 +730,9 @@
     <t xml:space="preserve">1,7,16</t>
   </si>
   <si>
+    <t xml:space="preserve">5,7</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,17</t>
   </si>
   <si>
@@ -746,6 +755,9 @@
   </si>
   <si>
     <t xml:space="preserve">for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,7,17</t>
   </si>
   <si>
     <t xml:space="preserve">1,22</t>
@@ -1237,7 +1249,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1363,6 +1375,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1453,7 +1473,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I245"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.76953125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.18"/>
@@ -4935,39 +4955,39 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:Q124"/>
-  <sheetFormatPr defaultColWidth="10.6875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:R124"/>
+  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="17.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="25" width="16.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="42.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="36.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="31.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="25.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="19.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="17.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="25" width="16.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="42.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="36.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="31.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="25.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="19.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="12.03"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>186</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>78</v>
+      <c r="E1" s="26" t="s">
+        <v>190</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>78</v>
@@ -4975,50 +4995,55 @@
       <c r="G1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="27" t="n">
+      <c r="C2" s="1"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>192</v>
+      </c>
       <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -5026,933 +5051,1043 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="B3" s="28"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="12"/>
       <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>194</v>
+      </c>
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
-      <c r="Q3" s="15" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q3" s="12"/>
+      <c r="R3" s="15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8" t="s">
+      <c r="D4" s="13"/>
+      <c r="E4" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K4" s="12"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="12"/>
+      <c r="K4" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="12"/>
       <c r="P4" s="12"/>
-      <c r="Q4" s="15"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q4" s="12"/>
+      <c r="R4" s="15"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8" t="s">
+      <c r="D5" s="13"/>
+      <c r="E5" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="12"/>
       <c r="K5" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L5" s="14"/>
-      <c r="M5" s="12"/>
+        <v>87</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M5" s="14"/>
       <c r="N5" s="12"/>
-      <c r="O5" s="8"/>
+      <c r="O5" s="12"/>
       <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="D6" s="6"/>
+      <c r="E6" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F6" s="16"/>
       <c r="G6" s="16"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="H6" s="16"/>
+      <c r="I6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="5"/>
       <c r="K6" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L6" s="17"/>
-      <c r="M6" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="M6" s="17"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="6"/>
+      <c r="E7" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="18"/>
+      <c r="K7" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L7" s="17"/>
-      <c r="M7" s="5"/>
+      <c r="M7" s="17"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
-      <c r="Q7" s="15"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q7" s="5"/>
+      <c r="R7" s="15"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="E8" s="8" t="s">
+      <c r="B8" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="F8" s="8"/>
       <c r="G8" s="8"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="12"/>
+      <c r="K8" s="14" t="s">
+        <v>120</v>
+      </c>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
-      <c r="Q8" s="15"/>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q8" s="8"/>
+      <c r="R8" s="15"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="19" t="s">
+      <c r="D9" s="8"/>
+      <c r="E9" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="H9" s="19"/>
+      <c r="I9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="8"/>
       <c r="K9" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L9" s="14"/>
-      <c r="M9" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M9" s="14"/>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
-      <c r="Q9" s="15"/>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q9" s="8"/>
+      <c r="R9" s="15"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="19" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="8"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="8"/>
+      <c r="K10" s="14"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
-      <c r="Q10" s="15"/>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q10" s="8"/>
+      <c r="R10" s="15"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="E11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="F11" s="8"/>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="8"/>
+      <c r="H11" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="I11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="8"/>
       <c r="K11" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L11" s="14"/>
-      <c r="M11" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M11" s="14"/>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
-      <c r="Q11" s="15"/>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q11" s="8"/>
+      <c r="R11" s="15"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="E12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="28" t="s">
+        <v>205</v>
+      </c>
       <c r="F12" s="8"/>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="8"/>
+      <c r="H12" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="I12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="8"/>
       <c r="K12" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L12" s="14"/>
-      <c r="M12" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M12" s="14"/>
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
-      <c r="Q12" s="15"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q12" s="8"/>
+      <c r="R12" s="15"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="8"/>
+      <c r="C13" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="E13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="28" t="s">
+        <v>206</v>
+      </c>
       <c r="F13" s="8"/>
-      <c r="G13" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="8"/>
       <c r="K13" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L13" s="14"/>
-      <c r="M13" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M13" s="14"/>
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
-      <c r="Q13" s="15"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q13" s="8"/>
+      <c r="R13" s="15"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="E14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="28" t="s">
+        <v>208</v>
+      </c>
       <c r="F14" s="8"/>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="8"/>
+      <c r="H14" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="I14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="8"/>
       <c r="K14" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L14" s="14"/>
-      <c r="M14" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M14" s="14"/>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q14" s="8"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8" t="s">
+      <c r="D15" s="8"/>
+      <c r="E15" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="I15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="8"/>
       <c r="K15" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L15" s="14"/>
-      <c r="M15" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M15" s="14"/>
       <c r="N15" s="8"/>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q15" s="8"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8" t="s">
+      <c r="D16" s="8"/>
+      <c r="E16" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="G16" s="8"/>
       <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="I16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="8"/>
       <c r="K16" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L16" s="14"/>
-      <c r="M16" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M16" s="14"/>
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
-      <c r="Q16" s="15"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q16" s="8"/>
+      <c r="R16" s="15"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8" t="s">
+      <c r="D17" s="8"/>
+      <c r="E17" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="G17" s="8"/>
       <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="I17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="8"/>
       <c r="K17" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L17" s="14"/>
-      <c r="M17" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M17" s="14"/>
       <c r="N17" s="8"/>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
-      <c r="Q17" s="15"/>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q17" s="8"/>
+      <c r="R17" s="15"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="C18" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="D18" s="5"/>
+      <c r="E18" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L18" s="5"/>
+      <c r="I18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="5"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5" t="s">
+      <c r="D19" s="5"/>
+      <c r="E19" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="G19" s="5"/>
       <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="N19" s="17"/>
-      <c r="O19" s="5"/>
+      <c r="I19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" s="5"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="O19" s="17"/>
       <c r="P19" s="5"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="31" t="s">
-        <v>213</v>
-      </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5" t="s">
+      <c r="D20" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="5"/>
+      <c r="I20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" s="20"/>
+      <c r="K20" s="17"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="32" t="s">
+        <v>217</v>
+      </c>
       <c r="F21" s="5"/>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="5"/>
+      <c r="H21" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="5"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="N21" s="17"/>
-      <c r="O21" s="5"/>
+      <c r="O21" s="17"/>
       <c r="P21" s="5"/>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q21" s="5"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="E22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="32" t="s">
+        <v>219</v>
+      </c>
       <c r="F22" s="5"/>
-      <c r="G22" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="5"/>
       <c r="K22" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="N22" s="17"/>
-      <c r="O22" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="O22" s="17"/>
       <c r="P22" s="5"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="n">
+      <c r="B23" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="C23" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="E23" s="8" t="s">
+      <c r="D23" s="8"/>
+      <c r="E23" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="F23" s="8"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K23" s="8"/>
+      <c r="I23" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" s="8"/>
+      <c r="K23" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q23" s="8"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8"/>
-      <c r="B24" s="8" t="n">
+      <c r="B24" s="8"/>
+      <c r="C24" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="E24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="28" t="s">
+        <v>222</v>
+      </c>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
+      <c r="I24" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="J24" s="8"/>
-      <c r="K24" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="N24" s="14"/>
-      <c r="O24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="O24" s="14"/>
       <c r="P24" s="8"/>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q24" s="8"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8"/>
-      <c r="B25" s="8" t="n">
+      <c r="B25" s="8"/>
+      <c r="C25" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8" t="s">
+      <c r="D25" s="8"/>
+      <c r="E25" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="G25" s="8"/>
       <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="14" t="s">
-        <v>212</v>
-      </c>
+      <c r="I25" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" s="8"/>
       <c r="K25" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L25" s="14"/>
-      <c r="M25" s="8"/>
+        <v>215</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M25" s="14"/>
       <c r="N25" s="8"/>
       <c r="O25" s="8"/>
       <c r="P25" s="8"/>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q25" s="8"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="8" t="n">
+      <c r="B26" s="8"/>
+      <c r="C26" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8" t="s">
+      <c r="D26" s="8"/>
+      <c r="E26" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="G26" s="8"/>
       <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="I26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" s="8"/>
       <c r="K26" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L26" s="14"/>
-      <c r="M26" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M26" s="14"/>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q26" s="8"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="8" t="n">
+      <c r="B27" s="8"/>
+      <c r="C27" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8" t="s">
+      <c r="D27" s="8"/>
+      <c r="E27" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="G27" s="8"/>
       <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="I27" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" s="8"/>
       <c r="K27" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L27" s="14"/>
-      <c r="M27" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M27" s="14"/>
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q27" s="8"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="8" t="n">
+      <c r="B28" s="8"/>
+      <c r="C28" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10" t="s">
+      <c r="D28" s="8"/>
+      <c r="E28" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="G28" s="10"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="H28" s="10"/>
+      <c r="I28" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" s="8"/>
       <c r="K28" s="14" t="s">
-        <v>196</v>
+        <v>87</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="M28" s="8"/>
+        <v>198</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="N28" s="8"/>
       <c r="O28" s="8"/>
       <c r="P28" s="8"/>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q28" s="8"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8"/>
-      <c r="B29" s="8" t="n">
+      <c r="B29" s="8"/>
+      <c r="C29" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
+      <c r="D29" s="8"/>
+      <c r="E29" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G29" s="8"/>
       <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="K29" s="8"/>
+      <c r="I29" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" s="8"/>
+      <c r="K29" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
       <c r="N29" s="8"/>
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q29" s="8"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="8" t="n">
+      <c r="B30" s="8"/>
+      <c r="C30" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8" t="s">
+      <c r="D30" s="8"/>
+      <c r="E30" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="G30" s="8"/>
       <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="I30" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" s="8"/>
       <c r="K30" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L30" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L30" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q30" s="8"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="8" t="n">
+      <c r="B31" s="8"/>
+      <c r="C31" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8" t="s">
+      <c r="D31" s="8"/>
+      <c r="E31" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="G31" s="8"/>
       <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="I31" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" s="8"/>
       <c r="K31" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L31" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
       <c r="O31" s="8"/>
       <c r="P31" s="8"/>
-    </row>
-    <row r="32" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q31" s="8"/>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
         <v>28</v>
       </c>
       <c r="B32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="E32" s="6" t="s">
+      <c r="D32" s="5"/>
+      <c r="E32" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="F32" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F32" s="6"/>
       <c r="G32" s="6"/>
-      <c r="H32" s="5"/>
+      <c r="H32" s="6"/>
       <c r="I32" s="5"/>
-      <c r="J32" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J32" s="5"/>
       <c r="K32" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L32" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L32" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q32" s="5"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="5"/>
+      <c r="C33" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6" t="s">
+      <c r="D33" s="5"/>
+      <c r="E33" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="G33" s="6"/>
-      <c r="H33" s="5"/>
+      <c r="H33" s="6"/>
       <c r="I33" s="5"/>
-      <c r="J33" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J33" s="5"/>
       <c r="K33" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L33" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L33" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
-    </row>
-    <row r="34" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q33" s="5"/>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="8"/>
+      <c r="B34" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="E34" s="10" t="s">
+      <c r="D34" s="8"/>
+      <c r="E34" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="F34" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F34" s="10"/>
       <c r="G34" s="10"/>
-      <c r="H34" s="8"/>
+      <c r="H34" s="10"/>
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
@@ -5961,194 +6096,203 @@
       <c r="N34" s="8"/>
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
-    </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q34" s="8"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="8" t="n">
+      <c r="B35" s="8"/>
+      <c r="C35" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8" t="s">
+      <c r="D35" s="8"/>
+      <c r="E35" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="G35" s="8"/>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
-      <c r="J35" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J35" s="8"/>
       <c r="K35" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L35" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M35" s="8"/>
       <c r="N35" s="8"/>
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q35" s="8"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8"/>
-      <c r="B36" s="8" t="n">
+      <c r="B36" s="8"/>
+      <c r="C36" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8" t="s">
+      <c r="D36" s="8"/>
+      <c r="E36" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="G36" s="8"/>
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
-      <c r="J36" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J36" s="8"/>
       <c r="K36" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L36" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M36" s="8"/>
       <c r="N36" s="8"/>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q36" s="8"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="B37" s="8" t="n">
+      <c r="B37" s="8"/>
+      <c r="C37" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="28" t="s">
-        <v>228</v>
-      </c>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8" t="s">
+      <c r="D37" s="8"/>
+      <c r="E37" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="G37" s="8"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
-      <c r="J37" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L37" s="8"/>
       <c r="M37" s="8"/>
       <c r="N37" s="8"/>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
-    </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q37" s="8"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="n">
         <v>33</v>
       </c>
       <c r="B38" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C38" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="E38" s="5" t="s">
+      <c r="D38" s="5"/>
+      <c r="E38" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="F38" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F38" s="5"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
-      <c r="J38" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J38" s="5"/>
       <c r="K38" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L38" s="5"/>
-      <c r="M38" s="17" t="s">
-        <v>212</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="L38" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="M38" s="5"/>
       <c r="N38" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="O38" s="5"/>
+        <v>215</v>
+      </c>
+      <c r="O38" s="17" t="s">
+        <v>215</v>
+      </c>
       <c r="P38" s="5"/>
-    </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q38" s="5"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="5"/>
+      <c r="C39" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="E39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="32" t="s">
+        <v>233</v>
+      </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
-      <c r="K39" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L39" s="5"/>
-      <c r="M39" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="N39" s="17"/>
-      <c r="O39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="M39" s="5"/>
+      <c r="N39" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="O39" s="17"/>
       <c r="P39" s="5"/>
-    </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q39" s="5"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="5"/>
+      <c r="C40" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5" t="s">
+      <c r="D40" s="5"/>
+      <c r="E40" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
-      <c r="J40" s="17" t="s">
-        <v>212</v>
-      </c>
+      <c r="J40" s="5"/>
       <c r="K40" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L40" s="5"/>
+        <v>215</v>
+      </c>
+      <c r="L40" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
       <c r="P40" s="5"/>
-    </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q40" s="5"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
         <v>34</v>
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
-      <c r="D41" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="E41" s="8" t="s">
+      <c r="D41" s="8"/>
+      <c r="E41" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="F41" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F41" s="8"/>
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
@@ -6159,184 +6303,193 @@
       <c r="N41" s="8"/>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
-    </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q41" s="8"/>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="B42" s="8" t="n">
+      <c r="B42" s="8"/>
+      <c r="C42" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="28" t="s">
-        <v>231</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8" t="s">
+      <c r="D42" s="8"/>
+      <c r="E42" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="G42" s="8"/>
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
-      <c r="J42" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J42" s="8"/>
       <c r="K42" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L42" s="8"/>
-      <c r="M42" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="N42" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L42" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M42" s="8"/>
+      <c r="N42" s="14" t="s">
+        <v>215</v>
+      </c>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
-    </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q42" s="8"/>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="B43" s="8" t="n">
+      <c r="B43" s="8"/>
+      <c r="C43" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8" t="s">
+      <c r="D43" s="8"/>
+      <c r="E43" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="G43" s="8"/>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
-      <c r="J43" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L43" s="8"/>
       <c r="M43" s="8"/>
       <c r="N43" s="8"/>
       <c r="O43" s="8"/>
       <c r="P43" s="8"/>
-    </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q43" s="8"/>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8"/>
-      <c r="B44" s="8" t="n">
+      <c r="B44" s="8"/>
+      <c r="C44" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="E44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="28" t="s">
+        <v>236</v>
+      </c>
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
-      <c r="J44" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="K44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="14" t="s">
+        <v>215</v>
+      </c>
       <c r="L44" s="8"/>
       <c r="M44" s="8"/>
       <c r="N44" s="8"/>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
-    </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q44" s="8"/>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8"/>
-      <c r="B45" s="8" t="n">
+      <c r="B45" s="8"/>
+      <c r="C45" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="E45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="28" t="s">
+        <v>236</v>
+      </c>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
-      <c r="J45" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="K45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="14" t="s">
+        <v>215</v>
+      </c>
       <c r="L45" s="8"/>
       <c r="M45" s="8"/>
       <c r="N45" s="8"/>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q45" s="8"/>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8"/>
-      <c r="B46" s="8" t="n">
+      <c r="B46" s="8"/>
+      <c r="C46" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="E46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="28" t="s">
+        <v>236</v>
+      </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
-      <c r="J46" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="K46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="L46" s="8"/>
       <c r="M46" s="8"/>
       <c r="N46" s="8"/>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
-    </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q46" s="8"/>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="B47" s="8" t="n">
+      <c r="B47" s="8"/>
+      <c r="C47" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8" t="s">
+      <c r="D47" s="8"/>
+      <c r="E47" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="G47" s="8"/>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
-      <c r="J47" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J47" s="8"/>
       <c r="K47" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L47" s="8"/>
-      <c r="M47" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="N47" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L47" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M47" s="8"/>
+      <c r="N47" s="14" t="s">
+        <v>215</v>
+      </c>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
-    </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q47" s="8"/>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B48" s="5"/>
+      <c r="B48" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="C48" s="5"/>
-      <c r="D48" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="E48" s="5" t="s">
+      <c r="D48" s="5"/>
+      <c r="E48" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F48" s="5"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
@@ -6347,861 +6500,895 @@
       <c r="N48" s="5"/>
       <c r="O48" s="5"/>
       <c r="P48" s="5"/>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q48" s="5"/>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B49" s="5"/>
+      <c r="C49" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="C49" s="5"/>
-      <c r="D49" s="31" t="s">
-        <v>235</v>
-      </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5" t="s">
+      <c r="D49" s="5"/>
+      <c r="E49" s="32" t="s">
+        <v>239</v>
+      </c>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
-      <c r="K49" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L49" s="5"/>
-      <c r="M49" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="N49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="M49" s="5"/>
+      <c r="N49" s="17" t="s">
+        <v>215</v>
+      </c>
       <c r="O49" s="5"/>
       <c r="P49" s="5"/>
-    </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q49" s="5"/>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="5"/>
+      <c r="C50" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="31" t="s">
-        <v>236</v>
-      </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5" t="s">
+      <c r="D50" s="5"/>
+      <c r="E50" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
-      <c r="M50" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="N50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="17" t="s">
+        <v>215</v>
+      </c>
       <c r="O50" s="5"/>
       <c r="P50" s="5"/>
-    </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q50" s="5"/>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="5"/>
+      <c r="C51" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="31" t="s">
-        <v>237</v>
-      </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5" t="s">
+      <c r="D51" s="5"/>
+      <c r="E51" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
-      <c r="M51" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="N51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="17" t="s">
+        <v>215</v>
+      </c>
       <c r="O51" s="5"/>
       <c r="P51" s="5"/>
-    </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q51" s="5"/>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="n">
         <v>42</v>
       </c>
-      <c r="D53" s="25" t="n">
+      <c r="E53" s="25" t="n">
         <v>42</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F53" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="B54" s="8" t="n">
+      <c r="B54" s="8"/>
+      <c r="C54" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="C54" s="8"/>
-      <c r="D54" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="E54" s="21" t="s">
+      <c r="D54" s="8"/>
+      <c r="E54" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="F54" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="F54" s="21"/>
       <c r="G54" s="21"/>
-      <c r="H54" s="8"/>
+      <c r="H54" s="21"/>
       <c r="I54" s="8"/>
-      <c r="J54" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L54" s="8"/>
       <c r="M54" s="8"/>
       <c r="N54" s="8"/>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
-    </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q54" s="8"/>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B55" s="5" t="n">
+      <c r="B55" s="5"/>
+      <c r="C55" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="C55" s="5"/>
-      <c r="D55" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="E55" s="23" t="s">
+      <c r="D55" s="5"/>
+      <c r="E55" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="F55" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="F55" s="23"/>
       <c r="G55" s="23"/>
-      <c r="H55" s="5"/>
+      <c r="H55" s="23"/>
       <c r="I55" s="5"/>
-      <c r="J55" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="K55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="17" t="s">
+        <v>87</v>
+      </c>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
       <c r="O55" s="5"/>
       <c r="P55" s="5"/>
-    </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q55" s="5"/>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="B56" s="8" t="n">
+      <c r="B56" s="8"/>
+      <c r="C56" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="C56" s="8"/>
-      <c r="D56" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="E56" s="8" t="s">
+      <c r="D56" s="8"/>
+      <c r="E56" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="F56" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="F56" s="8"/>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
-      <c r="J56" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K56" s="8"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L56" s="8"/>
       <c r="M56" s="8"/>
       <c r="N56" s="8"/>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
-    </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q56" s="8"/>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="B57" s="8" t="n">
+      <c r="B57" s="8"/>
+      <c r="C57" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="C57" s="8"/>
-      <c r="D57" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8" t="s">
+      <c r="D57" s="8"/>
+      <c r="E57" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G57" s="8"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
-      <c r="J57" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L57" s="8"/>
       <c r="M57" s="8"/>
       <c r="N57" s="8"/>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q57" s="8"/>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="B58" s="8" t="n">
+      <c r="B58" s="8"/>
+      <c r="C58" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="C58" s="8"/>
-      <c r="D58" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8" t="s">
+      <c r="D58" s="8"/>
+      <c r="E58" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="G58" s="8"/>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
-      <c r="J58" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K58" s="8"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L58" s="8"/>
       <c r="M58" s="8"/>
       <c r="N58" s="8"/>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
-    </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q58" s="8"/>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="B59" s="8" t="n">
+      <c r="B59" s="8"/>
+      <c r="C59" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="C59" s="8"/>
-      <c r="D59" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8" t="s">
+      <c r="D59" s="8"/>
+      <c r="E59" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="G59" s="8"/>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
-      <c r="J59" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L59" s="8"/>
       <c r="M59" s="8"/>
       <c r="N59" s="8"/>
       <c r="O59" s="8"/>
       <c r="P59" s="8"/>
-    </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q59" s="8"/>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="B60" s="8" t="n">
+      <c r="B60" s="8"/>
+      <c r="C60" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="C60" s="8"/>
-      <c r="D60" s="28" t="s">
-        <v>245</v>
-      </c>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8" t="s">
+      <c r="D60" s="8"/>
+      <c r="E60" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="G60" s="8"/>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
-      <c r="J60" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L60" s="8"/>
       <c r="M60" s="8"/>
       <c r="N60" s="8"/>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
-    </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q60" s="8"/>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="B61" s="8" t="n">
+      <c r="B61" s="8"/>
+      <c r="C61" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="C61" s="8"/>
-      <c r="D61" s="28" t="s">
-        <v>246</v>
-      </c>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8" t="s">
+      <c r="D61" s="8"/>
+      <c r="E61" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="G61" s="8"/>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
-      <c r="J61" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K61" s="8"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L61" s="8"/>
-      <c r="M61" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="N61" s="8"/>
+      <c r="M61" s="8"/>
+      <c r="N61" s="14" t="s">
+        <v>215</v>
+      </c>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q61" s="8"/>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="B62" s="8" t="n">
+      <c r="B62" s="8"/>
+      <c r="C62" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="C62" s="8"/>
-      <c r="D62" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="E62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="28" t="s">
+        <v>251</v>
+      </c>
       <c r="F62" s="8"/>
-      <c r="G62" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="H62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8" t="s">
+        <v>252</v>
+      </c>
       <c r="I62" s="8"/>
-      <c r="J62" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L62" s="8"/>
       <c r="M62" s="8"/>
       <c r="N62" s="8"/>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
-    </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q62" s="8"/>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="B63" s="8" t="n">
+      <c r="B63" s="8"/>
+      <c r="C63" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="C63" s="8"/>
-      <c r="D63" s="28" t="s">
-        <v>249</v>
-      </c>
-      <c r="E63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="28" t="s">
+        <v>253</v>
+      </c>
       <c r="F63" s="8"/>
-      <c r="G63" s="8" t="s">
+      <c r="G63" s="8"/>
+      <c r="H63" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="H63" s="8"/>
       <c r="I63" s="8"/>
-      <c r="J63" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K63" s="8"/>
+      <c r="J63" s="8"/>
+      <c r="K63" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L63" s="8"/>
       <c r="M63" s="8"/>
       <c r="N63" s="8"/>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
-    </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q63" s="8"/>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="B64" s="8" t="n">
+      <c r="B64" s="8"/>
+      <c r="C64" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="C64" s="8"/>
-      <c r="D64" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8" t="s">
+      <c r="D64" s="8"/>
+      <c r="E64" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="F64" s="8"/>
+      <c r="G64" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="G64" s="8"/>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
-      <c r="J64" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J64" s="8"/>
       <c r="K64" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L64" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L64" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M64" s="8"/>
       <c r="N64" s="8"/>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q64" s="8"/>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="B65" s="8" t="n">
+      <c r="B65" s="8"/>
+      <c r="C65" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="C65" s="8"/>
-      <c r="D65" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8" t="s">
+      <c r="D65" s="8"/>
+      <c r="E65" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="G65" s="8"/>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
-      <c r="J65" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J65" s="8"/>
       <c r="K65" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L65" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L65" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M65" s="8"/>
       <c r="N65" s="8"/>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q65" s="8"/>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="B66" s="5" t="n">
+      <c r="B66" s="5"/>
+      <c r="C66" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="C66" s="5"/>
-      <c r="D66" s="31" t="s">
-        <v>252</v>
-      </c>
-      <c r="E66" s="5" t="s">
+      <c r="D66" s="5"/>
+      <c r="E66" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="F66" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F66" s="17"/>
       <c r="G66" s="17"/>
-      <c r="H66" s="5"/>
+      <c r="H66" s="17"/>
       <c r="I66" s="5"/>
-      <c r="J66" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J66" s="5"/>
       <c r="K66" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L66" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L66" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
       <c r="O66" s="5"/>
       <c r="P66" s="5"/>
-    </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q66" s="5"/>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="n">
         <v>56</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
-      <c r="D67" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="E67" s="8" t="s">
+      <c r="D67" s="8"/>
+      <c r="E67" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="F67" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F67" s="8"/>
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="8"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="14"/>
       <c r="L67" s="8"/>
       <c r="M67" s="8"/>
       <c r="N67" s="8"/>
       <c r="O67" s="8"/>
       <c r="P67" s="8"/>
-    </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q67" s="8"/>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="B68" s="8" t="n">
+      <c r="B68" s="8"/>
+      <c r="C68" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="C68" s="8"/>
-      <c r="D68" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8" t="s">
+      <c r="D68" s="8"/>
+      <c r="E68" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="F68" s="8"/>
+      <c r="G68" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="G68" s="8"/>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
-      <c r="J68" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J68" s="8"/>
       <c r="K68" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L68" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L68" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M68" s="8"/>
       <c r="N68" s="8"/>
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
-    </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q68" s="8"/>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="B69" s="8" t="n">
+      <c r="B69" s="8"/>
+      <c r="C69" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="C69" s="8"/>
-      <c r="D69" s="28" t="s">
-        <v>255</v>
-      </c>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8" t="s">
+      <c r="D69" s="8"/>
+      <c r="E69" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="F69" s="8"/>
+      <c r="G69" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G69" s="8"/>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
-      <c r="J69" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J69" s="8"/>
       <c r="K69" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L69" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L69" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M69" s="8"/>
       <c r="N69" s="8"/>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
-    </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q69" s="8"/>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="B70" s="8" t="n">
+      <c r="B70" s="8"/>
+      <c r="C70" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="C70" s="8"/>
-      <c r="D70" s="28" t="s">
-        <v>256</v>
-      </c>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8" t="s">
+      <c r="D70" s="8"/>
+      <c r="E70" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="G70" s="8"/>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
-      <c r="J70" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J70" s="8"/>
       <c r="K70" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L70" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L70" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M70" s="8"/>
       <c r="N70" s="8"/>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
-    </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q70" s="8"/>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="B71" s="8" t="n">
+      <c r="B71" s="8"/>
+      <c r="C71" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="C71" s="8"/>
-      <c r="D71" s="28" t="s">
-        <v>257</v>
-      </c>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8" t="s">
+      <c r="D71" s="8"/>
+      <c r="E71" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="G71" s="8"/>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
-      <c r="J71" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J71" s="8"/>
       <c r="K71" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L71" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L71" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M71" s="8"/>
       <c r="N71" s="8"/>
       <c r="O71" s="8"/>
       <c r="P71" s="8"/>
-    </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q71" s="8"/>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8"/>
-      <c r="B72" s="8" t="n">
+      <c r="B72" s="8"/>
+      <c r="C72" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="C72" s="8"/>
-      <c r="D72" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8" t="s">
+      <c r="D72" s="8"/>
+      <c r="E72" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="G72" s="8"/>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
-      <c r="J72" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K72" s="8"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L72" s="8"/>
       <c r="M72" s="8"/>
       <c r="N72" s="8"/>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
-    </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q72" s="8"/>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="n">
         <v>61</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
-      <c r="D73" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="E73" s="5" t="s">
+      <c r="D73" s="5"/>
+      <c r="E73" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="F73" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F73" s="5"/>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
-      <c r="J73" s="17"/>
-      <c r="K73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="17"/>
       <c r="L73" s="5"/>
       <c r="M73" s="5"/>
       <c r="N73" s="5"/>
       <c r="O73" s="5"/>
       <c r="P73" s="5"/>
-    </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q73" s="5"/>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="B74" s="5" t="n">
+      <c r="B74" s="5"/>
+      <c r="C74" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="C74" s="5"/>
-      <c r="D74" s="31" t="s">
-        <v>259</v>
-      </c>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5" t="s">
+      <c r="D74" s="5"/>
+      <c r="E74" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="G74" s="5"/>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
-      <c r="J74" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J74" s="5"/>
       <c r="K74" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L74" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L74" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M74" s="5"/>
       <c r="N74" s="5"/>
       <c r="O74" s="5"/>
       <c r="P74" s="5"/>
-    </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q74" s="5"/>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B75" s="5"/>
+      <c r="C75" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="C75" s="5"/>
-      <c r="D75" s="31" t="s">
-        <v>260</v>
-      </c>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5" t="s">
+      <c r="D75" s="5"/>
+      <c r="E75" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
-      <c r="J75" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J75" s="5"/>
       <c r="K75" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L75" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L75" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M75" s="5"/>
       <c r="N75" s="5"/>
       <c r="O75" s="5"/>
       <c r="P75" s="5"/>
-    </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q75" s="5"/>
+    </row>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="n">
         <v>64</v>
       </c>
       <c r="B76" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="C76" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="C76" s="5"/>
-      <c r="D76" s="31" t="s">
-        <v>261</v>
-      </c>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5" t="s">
+      <c r="D76" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="E76" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G76" s="5"/>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
-      <c r="J76" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J76" s="5"/>
       <c r="K76" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L76" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L76" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M76" s="5"/>
       <c r="N76" s="5"/>
       <c r="O76" s="5"/>
       <c r="P76" s="5"/>
-    </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q76" s="5"/>
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="B77" s="5" t="n">
+      <c r="B77" s="5"/>
+      <c r="C77" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="C77" s="5"/>
-      <c r="D77" s="31" t="s">
-        <v>262</v>
-      </c>
-      <c r="E77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="32" t="s">
+        <v>266</v>
+      </c>
       <c r="F77" s="5"/>
-      <c r="G77" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="H77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5" t="s">
+        <v>218</v>
+      </c>
       <c r="I77" s="5"/>
-      <c r="J77" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J77" s="5"/>
       <c r="K77" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L77" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L77" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M77" s="5"/>
       <c r="N77" s="5"/>
       <c r="O77" s="5"/>
       <c r="P77" s="5"/>
-    </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q77" s="5"/>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B78" s="5"/>
+      <c r="C78" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="C78" s="5"/>
-      <c r="D78" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="E78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="32" t="s">
+        <v>267</v>
+      </c>
       <c r="F78" s="5"/>
-      <c r="G78" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="H78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5" t="s">
+        <v>220</v>
+      </c>
       <c r="I78" s="5"/>
-      <c r="J78" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J78" s="5"/>
       <c r="K78" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L78" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L78" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M78" s="5"/>
       <c r="N78" s="5"/>
       <c r="O78" s="5"/>
       <c r="P78" s="5"/>
-    </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q78" s="5"/>
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
-      <c r="B79" s="5" t="n">
+      <c r="B79" s="5"/>
+      <c r="C79" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="C79" s="5"/>
-      <c r="D79" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="E79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="32" t="s">
+        <v>268</v>
+      </c>
       <c r="F79" s="5"/>
-      <c r="G79" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="H79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
-      <c r="K79" s="17" t="s">
-        <v>196</v>
-      </c>
+      <c r="K79" s="5"/>
       <c r="L79" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="M79" s="5"/>
+        <v>198</v>
+      </c>
+      <c r="M79" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="N79" s="5"/>
       <c r="O79" s="5"/>
       <c r="P79" s="5"/>
-    </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q79" s="5"/>
+    </row>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="n">
         <v>67</v>
       </c>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
-      <c r="D80" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="E80" s="19" t="s">
+      <c r="D80" s="8"/>
+      <c r="E80" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="F80" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="F80" s="8"/>
       <c r="G80" s="8"/>
       <c r="H80" s="8"/>
       <c r="I80" s="8"/>
@@ -7212,106 +7399,110 @@
       <c r="N80" s="8"/>
       <c r="O80" s="8"/>
       <c r="P80" s="8"/>
-    </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q80" s="8"/>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="B81" s="8" t="n">
+      <c r="B81" s="8"/>
+      <c r="C81" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="C81" s="8"/>
-      <c r="D81" s="28" t="s">
-        <v>267</v>
-      </c>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8" t="s">
+      <c r="D81" s="8"/>
+      <c r="E81" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="G81" s="8"/>
       <c r="H81" s="8"/>
       <c r="I81" s="8"/>
-      <c r="J81" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K81" s="8"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L81" s="8"/>
       <c r="M81" s="8"/>
       <c r="N81" s="8"/>
       <c r="O81" s="8"/>
       <c r="P81" s="8"/>
-    </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q81" s="8"/>
+    </row>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="B82" s="8" t="n">
+      <c r="B82" s="8"/>
+      <c r="C82" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="C82" s="8"/>
-      <c r="D82" s="28" t="s">
-        <v>268</v>
-      </c>
-      <c r="E82" s="8"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="28" t="s">
+        <v>272</v>
+      </c>
       <c r="F82" s="8"/>
-      <c r="G82" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="H82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8" t="s">
+        <v>273</v>
+      </c>
       <c r="I82" s="8"/>
-      <c r="J82" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K82" s="8"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L82" s="8"/>
       <c r="M82" s="8"/>
       <c r="N82" s="8"/>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
-    </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q82" s="8"/>
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="B83" s="8" t="n">
+      <c r="B83" s="8"/>
+      <c r="C83" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="C83" s="8"/>
-      <c r="D83" s="28" t="s">
-        <v>270</v>
-      </c>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8" t="s">
+      <c r="D83" s="8"/>
+      <c r="E83" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="G83" s="8"/>
       <c r="H83" s="8"/>
       <c r="I83" s="8"/>
-      <c r="J83" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J83" s="8"/>
       <c r="K83" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L83" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L83" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M83" s="8"/>
       <c r="N83" s="8"/>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
-    </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q83" s="8"/>
+    </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="n">
         <v>71</v>
       </c>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
-      <c r="D84" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="E84" s="5" t="s">
+      <c r="D84" s="5"/>
+      <c r="E84" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="F84" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F84" s="5"/>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
@@ -7322,1331 +7513,1380 @@
       <c r="N84" s="5"/>
       <c r="O84" s="5"/>
       <c r="P84" s="5"/>
-    </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q84" s="5"/>
+    </row>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="B85" s="5" t="n">
+      <c r="B85" s="5"/>
+      <c r="C85" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="C85" s="5"/>
-      <c r="D85" s="31" t="s">
-        <v>272</v>
-      </c>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5" t="s">
+      <c r="D85" s="5"/>
+      <c r="E85" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="F85" s="5"/>
+      <c r="G85" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="G85" s="5"/>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
-      <c r="J85" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K85" s="5"/>
+      <c r="J85" s="5"/>
+      <c r="K85" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="L85" s="5"/>
       <c r="M85" s="5"/>
       <c r="N85" s="5"/>
       <c r="O85" s="5"/>
       <c r="P85" s="5"/>
-    </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q85" s="5"/>
+    </row>
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="B86" s="5" t="n">
+      <c r="B86" s="5"/>
+      <c r="C86" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="C86" s="5"/>
-      <c r="D86" s="31"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5" t="s">
+      <c r="D86" s="5"/>
+      <c r="E86" s="32"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="G86" s="5"/>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
-      <c r="J86" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="K86" s="5"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="22" t="s">
+        <v>87</v>
+      </c>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
       <c r="N86" s="5"/>
       <c r="O86" s="5"/>
       <c r="P86" s="5"/>
-    </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q86" s="5"/>
+    </row>
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="B87" s="5" t="n">
+      <c r="B87" s="5"/>
+      <c r="C87" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="C87" s="5"/>
-      <c r="D87" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5" t="s">
+      <c r="D87" s="5"/>
+      <c r="E87" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
-      <c r="J87" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="K87" s="5"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="17" t="s">
+        <v>87</v>
+      </c>
       <c r="L87" s="5"/>
       <c r="M87" s="5"/>
       <c r="N87" s="5"/>
       <c r="O87" s="5"/>
       <c r="P87" s="5"/>
-    </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q87" s="5"/>
+    </row>
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="n">
         <v>75</v>
       </c>
       <c r="B88" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="C88" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="C88" s="5"/>
-      <c r="D88" s="31" t="s">
-        <v>274</v>
-      </c>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5" t="s">
+      <c r="D88" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="E88" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="G88" s="5"/>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
-      <c r="J88" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="K88" s="5"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="17" t="s">
+        <v>87</v>
+      </c>
       <c r="L88" s="5"/>
       <c r="M88" s="5"/>
       <c r="N88" s="5"/>
       <c r="O88" s="5"/>
       <c r="P88" s="5"/>
-    </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q88" s="5"/>
+    </row>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="B89" s="5"/>
+      <c r="B89" s="5" t="n">
+        <v>74</v>
+      </c>
       <c r="C89" s="5"/>
-      <c r="D89" s="31"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="G89" s="5"/>
+      <c r="D89" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="E89" s="32"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="5" t="s">
+        <v>279</v>
+      </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
-      <c r="J89" s="17"/>
-      <c r="K89" s="5"/>
+      <c r="J89" s="5"/>
+      <c r="K89" s="17"/>
       <c r="L89" s="5"/>
       <c r="M89" s="5"/>
       <c r="N89" s="5"/>
       <c r="O89" s="5"/>
       <c r="P89" s="5"/>
-    </row>
-    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q89" s="5"/>
+    </row>
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="B90" s="5" t="n">
+      <c r="B90" s="5"/>
+      <c r="C90" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="C90" s="5"/>
-      <c r="D90" s="31" t="s">
-        <v>276</v>
-      </c>
-      <c r="E90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="32" t="s">
+        <v>280</v>
+      </c>
       <c r="F90" s="5"/>
-      <c r="G90" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="H90" s="5"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5" t="s">
+        <v>281</v>
+      </c>
       <c r="I90" s="5"/>
-      <c r="J90" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="K90" s="5"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="17" t="s">
+        <v>87</v>
+      </c>
       <c r="L90" s="5"/>
       <c r="M90" s="5"/>
       <c r="N90" s="5"/>
       <c r="O90" s="5"/>
       <c r="P90" s="5"/>
-    </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q90" s="5"/>
+    </row>
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B91" s="5" t="n">
+      <c r="B91" s="5"/>
+      <c r="C91" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="C91" s="5"/>
-      <c r="D91" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="E91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="32" t="s">
+        <v>282</v>
+      </c>
       <c r="F91" s="5"/>
-      <c r="G91" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5" t="s">
+        <v>283</v>
+      </c>
       <c r="I91" s="5"/>
-      <c r="J91" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J91" s="5"/>
       <c r="K91" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L91" s="5"/>
-      <c r="M91" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="N91" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L91" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="M91" s="5"/>
+      <c r="N91" s="17" t="s">
+        <v>215</v>
+      </c>
       <c r="O91" s="5"/>
       <c r="P91" s="5"/>
-    </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q91" s="5"/>
+    </row>
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="n">
         <v>79</v>
       </c>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
-      <c r="D92" s="28" t="s">
-        <v>280</v>
-      </c>
-      <c r="E92" s="8" t="s">
+      <c r="D92" s="8"/>
+      <c r="E92" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="F92" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="F92" s="8"/>
       <c r="G92" s="8"/>
       <c r="H92" s="8"/>
       <c r="I92" s="8"/>
-      <c r="J92" s="14"/>
+      <c r="J92" s="8"/>
       <c r="K92" s="14"/>
-      <c r="L92" s="8"/>
-      <c r="M92" s="14"/>
-      <c r="N92" s="8"/>
+      <c r="L92" s="14"/>
+      <c r="M92" s="8"/>
+      <c r="N92" s="14"/>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
-    </row>
-    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q92" s="8"/>
+    </row>
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="B93" s="8" t="n">
+      <c r="B93" s="8"/>
+      <c r="C93" s="8" t="n">
         <v>78</v>
       </c>
-      <c r="C93" s="8"/>
-      <c r="D93" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="E93" s="8"/>
-      <c r="F93" s="24" t="s">
+      <c r="D93" s="8"/>
+      <c r="E93" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="F93" s="8"/>
+      <c r="G93" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="G93" s="24"/>
-      <c r="H93" s="8"/>
+      <c r="H93" s="24"/>
       <c r="I93" s="8"/>
-      <c r="J93" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J93" s="8"/>
       <c r="K93" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L93" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L93" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M93" s="8"/>
       <c r="N93" s="8"/>
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
-    </row>
-    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q93" s="8"/>
+    </row>
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="B94" s="8" t="n">
+      <c r="B94" s="8"/>
+      <c r="C94" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="C94" s="8"/>
-      <c r="D94" s="28" t="s">
-        <v>282</v>
-      </c>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8" t="s">
+      <c r="D94" s="8"/>
+      <c r="E94" s="28" t="s">
+        <v>286</v>
+      </c>
+      <c r="F94" s="8"/>
+      <c r="G94" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="G94" s="8"/>
       <c r="H94" s="8"/>
       <c r="I94" s="8"/>
-      <c r="J94" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J94" s="8"/>
       <c r="K94" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L94" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L94" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M94" s="8"/>
       <c r="N94" s="8"/>
       <c r="O94" s="8"/>
       <c r="P94" s="8"/>
-    </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q94" s="8"/>
+    </row>
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="n">
         <v>82</v>
       </c>
-      <c r="B95" s="8" t="n">
+      <c r="B95" s="8"/>
+      <c r="C95" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="C95" s="8"/>
-      <c r="D95" s="28" t="s">
-        <v>283</v>
-      </c>
-      <c r="E95" s="8"/>
-      <c r="F95" s="8" t="s">
+      <c r="D95" s="8"/>
+      <c r="E95" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="F95" s="8"/>
+      <c r="G95" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G95" s="8"/>
       <c r="H95" s="8"/>
       <c r="I95" s="8"/>
-      <c r="J95" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J95" s="8"/>
       <c r="K95" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L95" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L95" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M95" s="8"/>
       <c r="N95" s="8"/>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
-    </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q95" s="8"/>
+    </row>
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="B96" s="8" t="n">
+      <c r="B96" s="8"/>
+      <c r="C96" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="C96" s="8"/>
-      <c r="D96" s="28" t="s">
-        <v>284</v>
-      </c>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8" t="s">
+      <c r="D96" s="8"/>
+      <c r="E96" s="28" t="s">
+        <v>288</v>
+      </c>
+      <c r="F96" s="8"/>
+      <c r="G96" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="G96" s="8"/>
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
-      <c r="J96" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J96" s="8"/>
       <c r="K96" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L96" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L96" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M96" s="8"/>
       <c r="N96" s="8"/>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
-    </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q96" s="8"/>
+    </row>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="n">
         <v>84</v>
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
-      <c r="D97" s="31"/>
-      <c r="E97" s="5" t="s">
+      <c r="D97" s="5"/>
+      <c r="E97" s="32"/>
+      <c r="F97" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F97" s="5"/>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
-      <c r="J97" s="17"/>
+      <c r="J97" s="5"/>
       <c r="K97" s="17"/>
-      <c r="L97" s="5"/>
+      <c r="L97" s="17"/>
       <c r="M97" s="5"/>
       <c r="N97" s="5"/>
       <c r="O97" s="5"/>
       <c r="P97" s="5"/>
-    </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q97" s="5"/>
+    </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="5"/>
-      <c r="B98" s="5" t="n">
+      <c r="B98" s="5"/>
+      <c r="C98" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="C98" s="5"/>
-      <c r="D98" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5" t="s">
+      <c r="D98" s="5"/>
+      <c r="E98" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="G98" s="5"/>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
-      <c r="J98" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J98" s="5"/>
       <c r="K98" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L98" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L98" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M98" s="5"/>
       <c r="N98" s="5"/>
       <c r="O98" s="5"/>
       <c r="P98" s="5"/>
-    </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q98" s="5"/>
+    </row>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5"/>
-      <c r="B99" s="5" t="n">
+      <c r="B99" s="5"/>
+      <c r="C99" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="C99" s="5"/>
-      <c r="D99" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5" t="s">
+      <c r="D99" s="5"/>
+      <c r="E99" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="F99" s="5"/>
+      <c r="G99" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G99" s="5"/>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
-      <c r="J99" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="K99" s="5"/>
+      <c r="J99" s="5"/>
+      <c r="K99" s="17" t="s">
+        <v>87</v>
+      </c>
       <c r="L99" s="5"/>
       <c r="M99" s="5"/>
       <c r="N99" s="5"/>
       <c r="O99" s="5"/>
       <c r="P99" s="5"/>
-    </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q99" s="5"/>
+    </row>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="B100" s="5" t="n">
+      <c r="B100" s="5"/>
+      <c r="C100" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="C100" s="5"/>
-      <c r="D100" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5" t="s">
+      <c r="D100" s="5"/>
+      <c r="E100" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="G100" s="5"/>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
-      <c r="J100" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J100" s="5"/>
       <c r="K100" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L100" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L100" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M100" s="5"/>
       <c r="N100" s="5"/>
       <c r="O100" s="5"/>
       <c r="P100" s="5"/>
-    </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q100" s="5"/>
+    </row>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="B101" s="5" t="n">
+      <c r="B101" s="5"/>
+      <c r="C101" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="C101" s="5"/>
-      <c r="D101" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5" t="s">
+      <c r="D101" s="5"/>
+      <c r="E101" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="F101" s="5"/>
+      <c r="G101" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="G101" s="5"/>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
-      <c r="J101" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J101" s="5"/>
       <c r="K101" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L101" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L101" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M101" s="5"/>
       <c r="N101" s="5"/>
       <c r="O101" s="5"/>
       <c r="P101" s="5"/>
-    </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q101" s="5"/>
+    </row>
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="B102" s="5" t="n">
+      <c r="B102" s="5"/>
+      <c r="C102" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="C102" s="5"/>
-      <c r="D102" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="E102" s="5"/>
-      <c r="F102" s="5" t="s">
+      <c r="D102" s="5"/>
+      <c r="E102" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="F102" s="5"/>
+      <c r="G102" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="G102" s="5"/>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
-      <c r="J102" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J102" s="5"/>
       <c r="K102" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L102" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L102" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M102" s="5"/>
       <c r="N102" s="5"/>
       <c r="O102" s="5"/>
       <c r="P102" s="5"/>
-    </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q102" s="5"/>
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="B103" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="C103" s="5"/>
-      <c r="D103" s="31" t="s">
-        <v>289</v>
-      </c>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5" t="s">
+      <c r="B103" s="5"/>
+      <c r="C103" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="D103" s="5"/>
+      <c r="E103" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G103" s="5"/>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
-      <c r="J103" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J103" s="5"/>
       <c r="K103" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L103" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L103" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M103" s="5"/>
       <c r="N103" s="5"/>
       <c r="O103" s="5"/>
       <c r="P103" s="5"/>
-    </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q103" s="5"/>
+    </row>
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="B104" s="5" t="n">
+      <c r="B104" s="5"/>
+      <c r="C104" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="C104" s="5"/>
-      <c r="D104" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5" t="s">
+      <c r="D104" s="5"/>
+      <c r="E104" s="32" t="s">
+        <v>294</v>
+      </c>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="G104" s="5"/>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
-      <c r="J104" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J104" s="5"/>
       <c r="K104" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L104" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L104" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M104" s="5"/>
       <c r="N104" s="5"/>
       <c r="O104" s="5"/>
       <c r="P104" s="5"/>
-    </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q104" s="5"/>
+    </row>
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B105" s="5" t="n">
-        <v>89</v>
-      </c>
-      <c r="C105" s="5"/>
-      <c r="D105" s="31" t="s">
-        <v>291</v>
-      </c>
-      <c r="E105" s="5"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="D105" s="5"/>
+      <c r="E105" s="32" t="s">
+        <v>295</v>
+      </c>
       <c r="F105" s="5"/>
-      <c r="G105" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="H105" s="5"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5" t="s">
+        <v>296</v>
+      </c>
       <c r="I105" s="5"/>
-      <c r="J105" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J105" s="5"/>
       <c r="K105" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L105" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L105" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M105" s="5"/>
       <c r="N105" s="5"/>
       <c r="O105" s="5"/>
       <c r="P105" s="5"/>
-    </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q105" s="5"/>
+    </row>
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="B106" s="5" t="n">
+      <c r="B106" s="5"/>
+      <c r="C106" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="C106" s="5"/>
-      <c r="D106" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5" t="s">
+      <c r="D106" s="5"/>
+      <c r="E106" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="G106" s="5"/>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
-      <c r="J106" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J106" s="5"/>
       <c r="K106" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L106" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L106" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M106" s="5"/>
       <c r="N106" s="5"/>
       <c r="O106" s="5"/>
       <c r="P106" s="5"/>
-    </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q106" s="5"/>
+    </row>
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="8" t="n">
         <v>92</v>
       </c>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
-      <c r="D107" s="28"/>
-      <c r="E107" s="8" t="s">
+      <c r="D107" s="8"/>
+      <c r="E107" s="28"/>
+      <c r="F107" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="F107" s="8"/>
       <c r="G107" s="8"/>
       <c r="H107" s="8"/>
       <c r="I107" s="8"/>
-      <c r="J107" s="14"/>
+      <c r="J107" s="8"/>
       <c r="K107" s="14"/>
-      <c r="L107" s="8"/>
+      <c r="L107" s="14"/>
       <c r="M107" s="8"/>
       <c r="N107" s="8"/>
       <c r="O107" s="8"/>
       <c r="P107" s="8"/>
-    </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q107" s="8"/>
+    </row>
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="8" t="n">
         <v>93</v>
       </c>
-      <c r="B108" s="8" t="n">
+      <c r="B108" s="8"/>
+      <c r="C108" s="8" t="n">
         <v>91</v>
       </c>
-      <c r="C108" s="8"/>
-      <c r="D108" s="28" t="s">
-        <v>294</v>
-      </c>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8" t="s">
+      <c r="D108" s="8"/>
+      <c r="E108" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="F108" s="8"/>
+      <c r="G108" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="G108" s="8"/>
       <c r="H108" s="8"/>
       <c r="I108" s="8"/>
-      <c r="J108" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J108" s="8"/>
       <c r="K108" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L108" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L108" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M108" s="8"/>
       <c r="N108" s="8"/>
       <c r="O108" s="8"/>
       <c r="P108" s="8"/>
-    </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q108" s="8"/>
+    </row>
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="8" t="n">
         <v>94</v>
       </c>
-      <c r="B109" s="8" t="n">
+      <c r="B109" s="8"/>
+      <c r="C109" s="8" t="n">
         <v>92</v>
       </c>
-      <c r="C109" s="8"/>
-      <c r="D109" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8" t="s">
+      <c r="D109" s="8"/>
+      <c r="E109" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="F109" s="8"/>
+      <c r="G109" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="G109" s="8"/>
       <c r="H109" s="8"/>
       <c r="I109" s="8"/>
-      <c r="J109" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J109" s="8"/>
       <c r="K109" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L109" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L109" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M109" s="8"/>
       <c r="N109" s="8"/>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
-    </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q109" s="8"/>
+    </row>
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="8" t="n">
         <v>95</v>
       </c>
-      <c r="B110" s="8" t="n">
+      <c r="B110" s="8"/>
+      <c r="C110" s="8" t="n">
         <v>93</v>
       </c>
-      <c r="C110" s="8"/>
-      <c r="D110" s="28" t="s">
-        <v>296</v>
-      </c>
-      <c r="E110" s="8"/>
-      <c r="F110" s="8" t="s">
+      <c r="D110" s="8"/>
+      <c r="E110" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="F110" s="8"/>
+      <c r="G110" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="G110" s="8"/>
       <c r="H110" s="8"/>
       <c r="I110" s="8"/>
-      <c r="J110" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J110" s="8"/>
       <c r="K110" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L110" s="8"/>
-      <c r="M110" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="N110" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L110" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M110" s="8"/>
+      <c r="N110" s="14" t="s">
+        <v>215</v>
+      </c>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
-    </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q110" s="8"/>
+    </row>
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="8" t="n">
         <v>96</v>
       </c>
-      <c r="B111" s="8" t="n">
+      <c r="B111" s="8"/>
+      <c r="C111" s="8" t="n">
         <v>94</v>
       </c>
-      <c r="C111" s="8"/>
-      <c r="D111" s="28" t="s">
-        <v>297</v>
-      </c>
-      <c r="E111" s="8"/>
-      <c r="F111" s="8" t="s">
+      <c r="D111" s="8"/>
+      <c r="E111" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="F111" s="8"/>
+      <c r="G111" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="G111" s="8"/>
       <c r="H111" s="8"/>
       <c r="I111" s="8"/>
-      <c r="J111" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J111" s="8"/>
       <c r="K111" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L111" s="8"/>
-      <c r="M111" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="N111" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L111" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M111" s="8"/>
+      <c r="N111" s="14" t="s">
+        <v>215</v>
+      </c>
       <c r="O111" s="8"/>
       <c r="P111" s="8"/>
-    </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q111" s="8"/>
+    </row>
+    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="B112" s="5" t="n">
+      <c r="B112" s="5"/>
+      <c r="C112" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="C112" s="5"/>
-      <c r="D112" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="E112" s="5" t="s">
+      <c r="D112" s="5"/>
+      <c r="E112" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="F112" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F112" s="5"/>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
-      <c r="J112" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J112" s="5"/>
       <c r="K112" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L112" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L112" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M112" s="5"/>
       <c r="N112" s="5"/>
       <c r="O112" s="5"/>
       <c r="P112" s="5"/>
-    </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q112" s="5"/>
+    </row>
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B113" s="5" t="n">
+      <c r="B113" s="5"/>
+      <c r="C113" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="C113" s="5"/>
-      <c r="D113" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="E113" s="5"/>
-      <c r="F113" s="5" t="s">
+      <c r="D113" s="5"/>
+      <c r="E113" s="32" t="s">
+        <v>303</v>
+      </c>
+      <c r="F113" s="5"/>
+      <c r="G113" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="G113" s="5"/>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
-      <c r="J113" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J113" s="5"/>
       <c r="K113" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L113" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L113" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M113" s="5"/>
       <c r="N113" s="5"/>
       <c r="O113" s="5"/>
       <c r="P113" s="5"/>
-    </row>
-    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q113" s="5"/>
+    </row>
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="8" t="n">
         <v>99</v>
       </c>
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
-      <c r="D114" s="28"/>
-      <c r="E114" s="8" t="s">
+      <c r="D114" s="8"/>
+      <c r="E114" s="28"/>
+      <c r="F114" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="F114" s="8"/>
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
       <c r="I114" s="8"/>
-      <c r="J114" s="14"/>
+      <c r="J114" s="8"/>
       <c r="K114" s="14"/>
-      <c r="L114" s="8"/>
+      <c r="L114" s="14"/>
       <c r="M114" s="8"/>
       <c r="N114" s="8"/>
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
-    </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q114" s="8"/>
+    </row>
+    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="B115" s="8" t="n">
+      <c r="B115" s="8"/>
+      <c r="C115" s="8" t="n">
         <v>97</v>
       </c>
-      <c r="C115" s="8"/>
-      <c r="D115" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="E115" s="8"/>
-      <c r="F115" s="8" t="s">
+      <c r="D115" s="8"/>
+      <c r="E115" s="28" t="s">
+        <v>304</v>
+      </c>
+      <c r="F115" s="8"/>
+      <c r="G115" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="G115" s="8"/>
       <c r="H115" s="8"/>
       <c r="I115" s="8"/>
-      <c r="J115" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J115" s="8"/>
       <c r="K115" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L115" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L115" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M115" s="8"/>
       <c r="N115" s="8"/>
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
-    </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q115" s="8"/>
+    </row>
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="8" t="n">
         <v>101</v>
       </c>
-      <c r="B116" s="8" t="n">
+      <c r="B116" s="8"/>
+      <c r="C116" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="C116" s="8"/>
-      <c r="D116" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="E116" s="8"/>
-      <c r="F116" s="8" t="s">
+      <c r="D116" s="8"/>
+      <c r="E116" s="28" t="s">
+        <v>305</v>
+      </c>
+      <c r="F116" s="8"/>
+      <c r="G116" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="G116" s="8"/>
       <c r="H116" s="8"/>
       <c r="I116" s="8"/>
-      <c r="J116" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="J116" s="8"/>
       <c r="K116" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L116" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L116" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="M116" s="8"/>
       <c r="N116" s="8"/>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
-    </row>
-    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q116" s="8"/>
+    </row>
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="8"/>
-      <c r="B117" s="8" t="n">
+      <c r="B117" s="8"/>
+      <c r="C117" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="C117" s="8"/>
-      <c r="D117" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="E117" s="8"/>
+      <c r="D117" s="8"/>
+      <c r="E117" s="28" t="s">
+        <v>305</v>
+      </c>
       <c r="F117" s="8"/>
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
       <c r="I117" s="8"/>
       <c r="J117" s="8"/>
-      <c r="K117" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L117" s="8"/>
-      <c r="M117" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="N117" s="8"/>
+      <c r="K117" s="8"/>
+      <c r="L117" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M117" s="8"/>
+      <c r="N117" s="14" t="s">
+        <v>215</v>
+      </c>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
-    </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q117" s="8"/>
+    </row>
+    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="n">
         <v>102</v>
       </c>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
-      <c r="D118" s="31" t="n">
+      <c r="D118" s="5"/>
+      <c r="E118" s="32" t="n">
         <v>42</v>
       </c>
-      <c r="E118" s="5" t="s">
+      <c r="F118" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="F118" s="5"/>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
-      <c r="J118" s="17"/>
-      <c r="K118" s="5"/>
+      <c r="J118" s="5"/>
+      <c r="K118" s="17"/>
       <c r="L118" s="5"/>
       <c r="M118" s="5"/>
       <c r="N118" s="5"/>
       <c r="O118" s="5"/>
       <c r="P118" s="5"/>
-    </row>
-    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q118" s="5"/>
+    </row>
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="n">
         <v>103</v>
       </c>
-      <c r="B119" s="5" t="n">
+      <c r="B119" s="5"/>
+      <c r="C119" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="C119" s="5"/>
-      <c r="D119" s="31" t="s">
-        <v>302</v>
-      </c>
-      <c r="E119" s="5"/>
-      <c r="F119" s="5" t="s">
+      <c r="D119" s="5"/>
+      <c r="E119" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="F119" s="5"/>
+      <c r="G119" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="G119" s="5"/>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
-      <c r="J119" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J119" s="5"/>
       <c r="K119" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L119" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L119" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="M119" s="5"/>
       <c r="N119" s="5"/>
       <c r="O119" s="5"/>
       <c r="P119" s="5"/>
-    </row>
-    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q119" s="5"/>
+    </row>
+    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="n">
         <v>104</v>
       </c>
-      <c r="B120" s="5" t="n">
+      <c r="B120" s="5"/>
+      <c r="C120" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="C120" s="5"/>
-      <c r="D120" s="31" t="s">
-        <v>303</v>
-      </c>
-      <c r="E120" s="5"/>
-      <c r="F120" s="5" t="s">
+      <c r="D120" s="5"/>
+      <c r="E120" s="32" t="s">
+        <v>307</v>
+      </c>
+      <c r="F120" s="5"/>
+      <c r="G120" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="G120" s="5"/>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
-      <c r="J120" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J120" s="5"/>
       <c r="K120" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L120" s="5"/>
-      <c r="M120" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="N120" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L120" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="M120" s="5"/>
+      <c r="N120" s="17" t="s">
+        <v>215</v>
+      </c>
       <c r="O120" s="5"/>
       <c r="P120" s="5"/>
-    </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q120" s="5"/>
+    </row>
+    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="n">
         <v>105</v>
       </c>
-      <c r="B121" s="5" t="n">
+      <c r="B121" s="5"/>
+      <c r="C121" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="C121" s="5"/>
-      <c r="D121" s="31" t="s">
-        <v>304</v>
-      </c>
-      <c r="E121" s="5"/>
-      <c r="F121" s="5" t="s">
+      <c r="D121" s="5"/>
+      <c r="E121" s="32" t="s">
+        <v>308</v>
+      </c>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="G121" s="5"/>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
-      <c r="J121" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="J121" s="5"/>
       <c r="K121" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L121" s="5"/>
-      <c r="M121" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="N121" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="L121" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="M121" s="5"/>
+      <c r="N121" s="17" t="s">
+        <v>215</v>
+      </c>
       <c r="O121" s="5"/>
       <c r="P121" s="5"/>
-    </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q121" s="5"/>
+    </row>
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="8" t="n">
         <v>106</v>
       </c>
-      <c r="B122" s="8" t="n">
+      <c r="B122" s="8"/>
+      <c r="C122" s="8" t="n">
         <v>103</v>
       </c>
-      <c r="C122" s="8"/>
-      <c r="D122" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="E122" s="8" t="s">
+      <c r="D122" s="8"/>
+      <c r="E122" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="F122" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F122" s="8"/>
       <c r="G122" s="8"/>
       <c r="H122" s="8"/>
       <c r="I122" s="8"/>
-      <c r="J122" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K122" s="8"/>
+      <c r="J122" s="8"/>
+      <c r="K122" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L122" s="8"/>
       <c r="M122" s="8"/>
       <c r="N122" s="8"/>
       <c r="O122" s="8"/>
       <c r="P122" s="8"/>
-    </row>
-    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q122" s="8"/>
+    </row>
+    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="B123" s="5" t="n">
+      <c r="B123" s="5"/>
+      <c r="C123" s="5" t="n">
         <v>104</v>
       </c>
-      <c r="C123" s="5"/>
-      <c r="D123" s="31" t="s">
-        <v>306</v>
-      </c>
-      <c r="E123" s="5" t="s">
+      <c r="D123" s="5"/>
+      <c r="E123" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="F123" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="F123" s="5"/>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
-      <c r="J123" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="K123" s="5"/>
+      <c r="J123" s="5"/>
+      <c r="K123" s="17" t="s">
+        <v>87</v>
+      </c>
       <c r="L123" s="5"/>
       <c r="M123" s="5"/>
       <c r="N123" s="5"/>
       <c r="O123" s="5"/>
       <c r="P123" s="5"/>
-    </row>
-    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q123" s="5"/>
+    </row>
+    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="5" t="n">
         <v>108</v>
       </c>
-      <c r="B124" s="5" t="n">
+      <c r="B124" s="5"/>
+      <c r="C124" s="5" t="n">
         <v>105</v>
       </c>
-      <c r="C124" s="5"/>
-      <c r="D124" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="E124" s="5"/>
-      <c r="F124" s="5" t="s">
+      <c r="D124" s="5"/>
+      <c r="E124" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="F124" s="5"/>
+      <c r="G124" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="G124" s="5"/>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
-      <c r="J124" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="K124" s="5"/>
+      <c r="J124" s="5"/>
+      <c r="K124" s="17" t="s">
+        <v>87</v>
+      </c>
       <c r="L124" s="5"/>
       <c r="M124" s="5"/>
       <c r="N124" s="5"/>
       <c r="O124" s="5"/>
       <c r="P124" s="5"/>
+      <c r="Q124" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J4" r:id="rId2" display="PDF"/>
-    <hyperlink ref="J5" r:id="rId3" display="PDF"/>
-    <hyperlink ref="K5" r:id="rId4" display="VIDEO"/>
-    <hyperlink ref="J6" r:id="rId5" display="PDF"/>
-    <hyperlink ref="K6" r:id="rId6" display="VIDEO"/>
-    <hyperlink ref="J7" r:id="rId7" display="PDF"/>
-    <hyperlink ref="K7" r:id="rId8" display="VIDEO"/>
-    <hyperlink ref="J9" r:id="rId9" display="PDF"/>
-    <hyperlink ref="K9" r:id="rId10" display="VIDEO"/>
-    <hyperlink ref="J11" r:id="rId11" display="PDF"/>
-    <hyperlink ref="K11" r:id="rId12" display="VIDEO"/>
-    <hyperlink ref="J12" r:id="rId13" display="PDF"/>
-    <hyperlink ref="K12" r:id="rId14" display="VIDEO"/>
-    <hyperlink ref="J13" r:id="rId15" display="PDF"/>
-    <hyperlink ref="K13" r:id="rId16" display="VIDEO"/>
-    <hyperlink ref="J14" r:id="rId17" display="PDF"/>
-    <hyperlink ref="K14" r:id="rId18" display="VIDEO"/>
-    <hyperlink ref="J15" r:id="rId19" display="PDF"/>
-    <hyperlink ref="K15" r:id="rId20" display="VIDEO"/>
-    <hyperlink ref="J16" r:id="rId21" display="PDF"/>
-    <hyperlink ref="K16" r:id="rId22" display="VIDEO"/>
-    <hyperlink ref="J17" r:id="rId23" display="PDF"/>
-    <hyperlink ref="K17" r:id="rId24" display="VIDEO"/>
-    <hyperlink ref="K18" r:id="rId25" display="VIDEO"/>
-    <hyperlink ref="K19" r:id="rId26" display="VIDEO"/>
-    <hyperlink ref="M19" r:id="rId27" display="CODE"/>
-    <hyperlink ref="K21" r:id="rId28" display="VIDEO"/>
-    <hyperlink ref="M21" r:id="rId29" display="CODE"/>
-    <hyperlink ref="J22" r:id="rId30" display="PDF"/>
-    <hyperlink ref="K22" r:id="rId31" display="VIDEO"/>
-    <hyperlink ref="M22" r:id="rId32" display="CODE"/>
-    <hyperlink ref="J23" r:id="rId33" display="PDF"/>
-    <hyperlink ref="K24" r:id="rId34" display="VIDEO"/>
-    <hyperlink ref="M24" r:id="rId35" display="CODE"/>
-    <hyperlink ref="J25" r:id="rId36" display="CODE"/>
-    <hyperlink ref="K25" r:id="rId37" display="VIDEO"/>
-    <hyperlink ref="J26" r:id="rId38" display="PDF"/>
-    <hyperlink ref="K26" r:id="rId39" display="VIDEO"/>
-    <hyperlink ref="J27" r:id="rId40" display="PDF"/>
-    <hyperlink ref="K27" r:id="rId41" display="VIDEO"/>
-    <hyperlink ref="J28" r:id="rId42" display="PDF"/>
-    <hyperlink ref="K28" r:id="rId43" display="VIDEO"/>
-    <hyperlink ref="L28" r:id="rId44" display="VIDEO"/>
-    <hyperlink ref="J29" r:id="rId45" display="VIDEO"/>
-    <hyperlink ref="J30" r:id="rId46" display="PDF"/>
-    <hyperlink ref="K30" r:id="rId47" display="VIDEO"/>
-    <hyperlink ref="J31" r:id="rId48" display="PDF"/>
-    <hyperlink ref="K31" r:id="rId49" display="VIDEO"/>
-    <hyperlink ref="J32" r:id="rId50" display="PDF"/>
-    <hyperlink ref="K32" r:id="rId51" display="VIDEO"/>
-    <hyperlink ref="J33" r:id="rId52" display="PDF"/>
-    <hyperlink ref="K33" r:id="rId53" display="VIDEO"/>
-    <hyperlink ref="J35" r:id="rId54" display="PDF"/>
-    <hyperlink ref="K35" r:id="rId55" display="VIDEO"/>
-    <hyperlink ref="J36" r:id="rId56" display="PDF"/>
-    <hyperlink ref="K36" r:id="rId57" display="VIDEO"/>
-    <hyperlink ref="J37" r:id="rId58" display="PDF"/>
-    <hyperlink ref="J38" r:id="rId59" display="PDF"/>
-    <hyperlink ref="K38" r:id="rId60" display="VIDEO"/>
-    <hyperlink ref="M38" r:id="rId61" display="CODE"/>
-    <hyperlink ref="N38" r:id="rId62" display="CODE"/>
-    <hyperlink ref="K39" r:id="rId63" display="VIDEO"/>
-    <hyperlink ref="M39" r:id="rId64" display="CODE"/>
-    <hyperlink ref="J40" r:id="rId65" display="CODE"/>
-    <hyperlink ref="K40" r:id="rId66" display="VIDEO"/>
-    <hyperlink ref="J42" r:id="rId67" display="PDF"/>
-    <hyperlink ref="K42" r:id="rId68" display="VIDEO"/>
-    <hyperlink ref="M42" r:id="rId69" display="CODE"/>
-    <hyperlink ref="J43" r:id="rId70" display="PDF"/>
-    <hyperlink ref="J44" r:id="rId71" display="CODE"/>
-    <hyperlink ref="J45" r:id="rId72" display="CODE"/>
-    <hyperlink ref="J46" r:id="rId73" display="VIDEO"/>
-    <hyperlink ref="J47" r:id="rId74" display="PDF"/>
-    <hyperlink ref="K47" r:id="rId75" display="VIDEO"/>
-    <hyperlink ref="M47" r:id="rId76" display="CODE"/>
-    <hyperlink ref="K49" r:id="rId77" display="VIDEO"/>
-    <hyperlink ref="M49" r:id="rId78" display="CODE"/>
-    <hyperlink ref="M50" r:id="rId79" display="CODE"/>
-    <hyperlink ref="M51" r:id="rId80" display="CODE"/>
-    <hyperlink ref="J54" r:id="rId81" display="PDF"/>
-    <hyperlink ref="J55" r:id="rId82" display="PDF"/>
-    <hyperlink ref="J56" r:id="rId83" display="PDF"/>
-    <hyperlink ref="J57" r:id="rId84" display="PDF"/>
-    <hyperlink ref="J58" r:id="rId85" display="PDF"/>
-    <hyperlink ref="J59" r:id="rId86" display="PDF"/>
-    <hyperlink ref="J60" r:id="rId87" display="PDF"/>
-    <hyperlink ref="J61" r:id="rId88" display="PDF"/>
-    <hyperlink ref="M61" r:id="rId89" display="CODE"/>
-    <hyperlink ref="J62" r:id="rId90" display="PDF"/>
-    <hyperlink ref="J63" r:id="rId91" display="PDF"/>
-    <hyperlink ref="J64" r:id="rId92" display="PDF"/>
-    <hyperlink ref="K64" r:id="rId93" display="VIDEO"/>
-    <hyperlink ref="J65" r:id="rId94" display="PDF"/>
-    <hyperlink ref="K65" r:id="rId95" display="VIDEO"/>
-    <hyperlink ref="J66" r:id="rId96" display="PDF"/>
-    <hyperlink ref="K66" r:id="rId97" display="VIDEO"/>
-    <hyperlink ref="J68" r:id="rId98" display="PDF"/>
-    <hyperlink ref="K68" r:id="rId99" display="VIDEO"/>
-    <hyperlink ref="J69" r:id="rId100" display="PDF"/>
-    <hyperlink ref="K69" r:id="rId101" display="VIDEO"/>
-    <hyperlink ref="J70" r:id="rId102" display="PDF"/>
-    <hyperlink ref="K70" r:id="rId103" display="VIDEO"/>
-    <hyperlink ref="J71" r:id="rId104" display="PDF"/>
-    <hyperlink ref="K71" r:id="rId105" display="VIDEO"/>
-    <hyperlink ref="J72" r:id="rId106" display="PDF"/>
-    <hyperlink ref="J74" r:id="rId107" display="PDF"/>
-    <hyperlink ref="K74" r:id="rId108" display="VIDEO"/>
-    <hyperlink ref="J75" r:id="rId109" display="PDF"/>
-    <hyperlink ref="K75" r:id="rId110" display="VIDEO"/>
-    <hyperlink ref="J76" r:id="rId111" display="PDF"/>
-    <hyperlink ref="K76" r:id="rId112" display="VIDEO"/>
-    <hyperlink ref="J77" r:id="rId113" display="PDF"/>
-    <hyperlink ref="K77" r:id="rId114" display="VIDEO"/>
-    <hyperlink ref="J78" r:id="rId115" display="PDF"/>
-    <hyperlink ref="K78" r:id="rId116" display="VIDEO"/>
-    <hyperlink ref="K79" r:id="rId117" display="VIDEO"/>
-    <hyperlink ref="L79" r:id="rId118" display="VIDEO"/>
-    <hyperlink ref="J81" r:id="rId119" display="PDF"/>
-    <hyperlink ref="J82" r:id="rId120" display="PDF"/>
-    <hyperlink ref="J83" r:id="rId121" display="PDF"/>
-    <hyperlink ref="K83" r:id="rId122" display="VIDEO"/>
-    <hyperlink ref="J85" r:id="rId123" display="PDF"/>
-    <hyperlink ref="J87" r:id="rId124" display="PDF"/>
-    <hyperlink ref="J88" r:id="rId125" display="PDF"/>
-    <hyperlink ref="J90" r:id="rId126" display="PDF"/>
-    <hyperlink ref="J91" r:id="rId127" display="PDF"/>
-    <hyperlink ref="K91" r:id="rId128" display="VIDEO"/>
-    <hyperlink ref="M91" r:id="rId129" display="CODE"/>
-    <hyperlink ref="J93" r:id="rId130" display="PDF"/>
-    <hyperlink ref="K93" r:id="rId131" display="VIDEO"/>
-    <hyperlink ref="J94" r:id="rId132" display="PDF"/>
-    <hyperlink ref="K94" r:id="rId133" display="VIDEO"/>
-    <hyperlink ref="J95" r:id="rId134" display="PDF"/>
-    <hyperlink ref="K95" r:id="rId135" display="VIDEO"/>
-    <hyperlink ref="J96" r:id="rId136" display="PDF"/>
-    <hyperlink ref="K96" r:id="rId137" display="VIDEO"/>
-    <hyperlink ref="J98" r:id="rId138" display="PDF"/>
-    <hyperlink ref="K98" r:id="rId139" display="VIDEO"/>
-    <hyperlink ref="J99" r:id="rId140" display="PDF"/>
-    <hyperlink ref="J100" r:id="rId141" display="PDF"/>
-    <hyperlink ref="K100" r:id="rId142" display="VIDEO"/>
-    <hyperlink ref="J101" r:id="rId143" display="PDF"/>
-    <hyperlink ref="K101" r:id="rId144" display="VIDEO"/>
-    <hyperlink ref="J102" r:id="rId145" display="PDF"/>
-    <hyperlink ref="K102" r:id="rId146" display="VIDEO"/>
-    <hyperlink ref="J103" r:id="rId147" display="PDF"/>
-    <hyperlink ref="K103" r:id="rId148" display="VIDEO"/>
-    <hyperlink ref="J104" r:id="rId149" display="PDF"/>
-    <hyperlink ref="K104" r:id="rId150" display="VIDEO"/>
-    <hyperlink ref="J105" r:id="rId151" display="PDF"/>
-    <hyperlink ref="K105" r:id="rId152" display="VIDEO"/>
-    <hyperlink ref="J106" r:id="rId153" display="PDF"/>
-    <hyperlink ref="K106" r:id="rId154" display="VIDEO"/>
-    <hyperlink ref="J108" r:id="rId155" display="PDF"/>
-    <hyperlink ref="K108" r:id="rId156" display="VIDEO"/>
-    <hyperlink ref="J109" r:id="rId157" display="PDF"/>
-    <hyperlink ref="K109" r:id="rId158" display="VIDEO"/>
-    <hyperlink ref="J110" r:id="rId159" display="PDF"/>
-    <hyperlink ref="K110" r:id="rId160" display="VIDEO"/>
-    <hyperlink ref="M110" r:id="rId161" display="CODE"/>
-    <hyperlink ref="J111" r:id="rId162" display="PDF"/>
-    <hyperlink ref="K111" r:id="rId163" display="VIDEO"/>
-    <hyperlink ref="M111" r:id="rId164" display="CODE"/>
-    <hyperlink ref="J112" r:id="rId165" display="PDF"/>
-    <hyperlink ref="K112" r:id="rId166" display="VIDEO"/>
-    <hyperlink ref="J113" r:id="rId167" display="PDF"/>
-    <hyperlink ref="K113" r:id="rId168" display="VIDEO"/>
-    <hyperlink ref="J115" r:id="rId169" display="PDF"/>
-    <hyperlink ref="K115" r:id="rId170" display="VIDEO"/>
-    <hyperlink ref="J116" r:id="rId171" display="PDF"/>
-    <hyperlink ref="K116" r:id="rId172" display="VIDEO"/>
-    <hyperlink ref="K117" r:id="rId173" display="VIDEO"/>
-    <hyperlink ref="M117" r:id="rId174" display="CODE"/>
-    <hyperlink ref="J119" r:id="rId175" display="PDF"/>
-    <hyperlink ref="K119" r:id="rId176" display="VIDEO"/>
-    <hyperlink ref="J120" r:id="rId177" display="PDF"/>
-    <hyperlink ref="K120" r:id="rId178" display="VIDEO"/>
-    <hyperlink ref="M120" r:id="rId179" display="CODE"/>
-    <hyperlink ref="J121" r:id="rId180" display="PDF"/>
-    <hyperlink ref="K121" r:id="rId181" display="VIDEO"/>
-    <hyperlink ref="M121" r:id="rId182" display="CODE"/>
-    <hyperlink ref="J122" r:id="rId183" display="PDF"/>
-    <hyperlink ref="J123" r:id="rId184" display="PDF"/>
-    <hyperlink ref="J124" r:id="rId185" display="PDF"/>
+    <hyperlink ref="K4" r:id="rId2" display="PDF"/>
+    <hyperlink ref="K5" r:id="rId3" display="PDF"/>
+    <hyperlink ref="L5" r:id="rId4" display="VIDEO"/>
+    <hyperlink ref="K6" r:id="rId5" display="PDF"/>
+    <hyperlink ref="L6" r:id="rId6" display="VIDEO"/>
+    <hyperlink ref="K7" r:id="rId7" display="PDF"/>
+    <hyperlink ref="L7" r:id="rId8" display="VIDEO"/>
+    <hyperlink ref="K9" r:id="rId9" display="PDF"/>
+    <hyperlink ref="L9" r:id="rId10" display="VIDEO"/>
+    <hyperlink ref="K11" r:id="rId11" display="PDF"/>
+    <hyperlink ref="L11" r:id="rId12" display="VIDEO"/>
+    <hyperlink ref="K12" r:id="rId13" display="PDF"/>
+    <hyperlink ref="L12" r:id="rId14" display="VIDEO"/>
+    <hyperlink ref="K13" r:id="rId15" display="PDF"/>
+    <hyperlink ref="L13" r:id="rId16" display="VIDEO"/>
+    <hyperlink ref="K14" r:id="rId17" display="PDF"/>
+    <hyperlink ref="L14" r:id="rId18" display="VIDEO"/>
+    <hyperlink ref="K15" r:id="rId19" display="PDF"/>
+    <hyperlink ref="L15" r:id="rId20" display="VIDEO"/>
+    <hyperlink ref="K16" r:id="rId21" display="PDF"/>
+    <hyperlink ref="L16" r:id="rId22" display="VIDEO"/>
+    <hyperlink ref="K17" r:id="rId23" display="PDF"/>
+    <hyperlink ref="L17" r:id="rId24" display="VIDEO"/>
+    <hyperlink ref="L18" r:id="rId25" display="VIDEO"/>
+    <hyperlink ref="L19" r:id="rId26" display="VIDEO"/>
+    <hyperlink ref="N19" r:id="rId27" display="CODE"/>
+    <hyperlink ref="L21" r:id="rId28" display="VIDEO"/>
+    <hyperlink ref="N21" r:id="rId29" display="CODE"/>
+    <hyperlink ref="K22" r:id="rId30" display="PDF"/>
+    <hyperlink ref="L22" r:id="rId31" display="VIDEO"/>
+    <hyperlink ref="N22" r:id="rId32" display="CODE"/>
+    <hyperlink ref="K23" r:id="rId33" display="PDF"/>
+    <hyperlink ref="L24" r:id="rId34" display="VIDEO"/>
+    <hyperlink ref="N24" r:id="rId35" display="CODE"/>
+    <hyperlink ref="K25" r:id="rId36" display="CODE"/>
+    <hyperlink ref="L25" r:id="rId37" display="VIDEO"/>
+    <hyperlink ref="K26" r:id="rId38" display="PDF"/>
+    <hyperlink ref="L26" r:id="rId39" display="VIDEO"/>
+    <hyperlink ref="K27" r:id="rId40" display="PDF"/>
+    <hyperlink ref="L27" r:id="rId41" display="VIDEO"/>
+    <hyperlink ref="K28" r:id="rId42" display="PDF"/>
+    <hyperlink ref="L28" r:id="rId43" display="VIDEO"/>
+    <hyperlink ref="M28" r:id="rId44" display="VIDEO"/>
+    <hyperlink ref="K29" r:id="rId45" display="VIDEO"/>
+    <hyperlink ref="K30" r:id="rId46" display="PDF"/>
+    <hyperlink ref="L30" r:id="rId47" display="VIDEO"/>
+    <hyperlink ref="K31" r:id="rId48" display="PDF"/>
+    <hyperlink ref="L31" r:id="rId49" display="VIDEO"/>
+    <hyperlink ref="K32" r:id="rId50" display="PDF"/>
+    <hyperlink ref="L32" r:id="rId51" display="VIDEO"/>
+    <hyperlink ref="K33" r:id="rId52" display="PDF"/>
+    <hyperlink ref="L33" r:id="rId53" display="VIDEO"/>
+    <hyperlink ref="K35" r:id="rId54" display="PDF"/>
+    <hyperlink ref="L35" r:id="rId55" display="VIDEO"/>
+    <hyperlink ref="K36" r:id="rId56" display="PDF"/>
+    <hyperlink ref="L36" r:id="rId57" display="VIDEO"/>
+    <hyperlink ref="K37" r:id="rId58" display="PDF"/>
+    <hyperlink ref="K38" r:id="rId59" display="PDF"/>
+    <hyperlink ref="L38" r:id="rId60" display="VIDEO"/>
+    <hyperlink ref="N38" r:id="rId61" display="CODE"/>
+    <hyperlink ref="O38" r:id="rId62" display="CODE"/>
+    <hyperlink ref="L39" r:id="rId63" display="VIDEO"/>
+    <hyperlink ref="N39" r:id="rId64" display="CODE"/>
+    <hyperlink ref="K40" r:id="rId65" display="CODE"/>
+    <hyperlink ref="L40" r:id="rId66" display="VIDEO"/>
+    <hyperlink ref="K42" r:id="rId67" display="PDF"/>
+    <hyperlink ref="L42" r:id="rId68" display="VIDEO"/>
+    <hyperlink ref="N42" r:id="rId69" display="CODE"/>
+    <hyperlink ref="K43" r:id="rId70" display="PDF"/>
+    <hyperlink ref="K44" r:id="rId71" display="CODE"/>
+    <hyperlink ref="K45" r:id="rId72" display="CODE"/>
+    <hyperlink ref="K46" r:id="rId73" display="VIDEO"/>
+    <hyperlink ref="K47" r:id="rId74" display="PDF"/>
+    <hyperlink ref="L47" r:id="rId75" display="VIDEO"/>
+    <hyperlink ref="N47" r:id="rId76" display="CODE"/>
+    <hyperlink ref="L49" r:id="rId77" display="VIDEO"/>
+    <hyperlink ref="N49" r:id="rId78" display="CODE"/>
+    <hyperlink ref="N50" r:id="rId79" display="CODE"/>
+    <hyperlink ref="N51" r:id="rId80" display="CODE"/>
+    <hyperlink ref="K54" r:id="rId81" display="PDF"/>
+    <hyperlink ref="K55" r:id="rId82" display="PDF"/>
+    <hyperlink ref="K56" r:id="rId83" display="PDF"/>
+    <hyperlink ref="K57" r:id="rId84" display="PDF"/>
+    <hyperlink ref="K58" r:id="rId85" display="PDF"/>
+    <hyperlink ref="K59" r:id="rId86" display="PDF"/>
+    <hyperlink ref="K60" r:id="rId87" display="PDF"/>
+    <hyperlink ref="K61" r:id="rId88" display="PDF"/>
+    <hyperlink ref="N61" r:id="rId89" display="CODE"/>
+    <hyperlink ref="K62" r:id="rId90" display="PDF"/>
+    <hyperlink ref="K63" r:id="rId91" display="PDF"/>
+    <hyperlink ref="K64" r:id="rId92" display="PDF"/>
+    <hyperlink ref="L64" r:id="rId93" display="VIDEO"/>
+    <hyperlink ref="K65" r:id="rId94" display="PDF"/>
+    <hyperlink ref="L65" r:id="rId95" display="VIDEO"/>
+    <hyperlink ref="K66" r:id="rId96" display="PDF"/>
+    <hyperlink ref="L66" r:id="rId97" display="VIDEO"/>
+    <hyperlink ref="K68" r:id="rId98" display="PDF"/>
+    <hyperlink ref="L68" r:id="rId99" display="VIDEO"/>
+    <hyperlink ref="K69" r:id="rId100" display="PDF"/>
+    <hyperlink ref="L69" r:id="rId101" display="VIDEO"/>
+    <hyperlink ref="K70" r:id="rId102" display="PDF"/>
+    <hyperlink ref="L70" r:id="rId103" display="VIDEO"/>
+    <hyperlink ref="K71" r:id="rId104" display="PDF"/>
+    <hyperlink ref="L71" r:id="rId105" display="VIDEO"/>
+    <hyperlink ref="K72" r:id="rId106" display="PDF"/>
+    <hyperlink ref="K74" r:id="rId107" display="PDF"/>
+    <hyperlink ref="L74" r:id="rId108" display="VIDEO"/>
+    <hyperlink ref="K75" r:id="rId109" display="PDF"/>
+    <hyperlink ref="L75" r:id="rId110" display="VIDEO"/>
+    <hyperlink ref="K76" r:id="rId111" display="PDF"/>
+    <hyperlink ref="L76" r:id="rId112" display="VIDEO"/>
+    <hyperlink ref="K77" r:id="rId113" display="PDF"/>
+    <hyperlink ref="L77" r:id="rId114" display="VIDEO"/>
+    <hyperlink ref="K78" r:id="rId115" display="PDF"/>
+    <hyperlink ref="L78" r:id="rId116" display="VIDEO"/>
+    <hyperlink ref="L79" r:id="rId117" display="VIDEO"/>
+    <hyperlink ref="M79" r:id="rId118" display="VIDEO"/>
+    <hyperlink ref="K81" r:id="rId119" display="PDF"/>
+    <hyperlink ref="K82" r:id="rId120" display="PDF"/>
+    <hyperlink ref="K83" r:id="rId121" display="PDF"/>
+    <hyperlink ref="L83" r:id="rId122" display="VIDEO"/>
+    <hyperlink ref="K85" r:id="rId123" display="PDF"/>
+    <hyperlink ref="K87" r:id="rId124" display="PDF"/>
+    <hyperlink ref="K88" r:id="rId125" display="PDF"/>
+    <hyperlink ref="K90" r:id="rId126" display="PDF"/>
+    <hyperlink ref="K91" r:id="rId127" display="PDF"/>
+    <hyperlink ref="L91" r:id="rId128" display="VIDEO"/>
+    <hyperlink ref="N91" r:id="rId129" display="CODE"/>
+    <hyperlink ref="K93" r:id="rId130" display="PDF"/>
+    <hyperlink ref="L93" r:id="rId131" display="VIDEO"/>
+    <hyperlink ref="K94" r:id="rId132" display="PDF"/>
+    <hyperlink ref="L94" r:id="rId133" display="VIDEO"/>
+    <hyperlink ref="K95" r:id="rId134" display="PDF"/>
+    <hyperlink ref="L95" r:id="rId135" display="VIDEO"/>
+    <hyperlink ref="K96" r:id="rId136" display="PDF"/>
+    <hyperlink ref="L96" r:id="rId137" display="VIDEO"/>
+    <hyperlink ref="K98" r:id="rId138" display="PDF"/>
+    <hyperlink ref="L98" r:id="rId139" display="VIDEO"/>
+    <hyperlink ref="K99" r:id="rId140" display="PDF"/>
+    <hyperlink ref="K100" r:id="rId141" display="PDF"/>
+    <hyperlink ref="L100" r:id="rId142" display="VIDEO"/>
+    <hyperlink ref="K101" r:id="rId143" display="PDF"/>
+    <hyperlink ref="L101" r:id="rId144" display="VIDEO"/>
+    <hyperlink ref="K102" r:id="rId145" display="PDF"/>
+    <hyperlink ref="L102" r:id="rId146" display="VIDEO"/>
+    <hyperlink ref="K103" r:id="rId147" display="PDF"/>
+    <hyperlink ref="L103" r:id="rId148" display="VIDEO"/>
+    <hyperlink ref="K104" r:id="rId149" display="PDF"/>
+    <hyperlink ref="L104" r:id="rId150" display="VIDEO"/>
+    <hyperlink ref="K105" r:id="rId151" display="PDF"/>
+    <hyperlink ref="L105" r:id="rId152" display="VIDEO"/>
+    <hyperlink ref="K106" r:id="rId153" display="PDF"/>
+    <hyperlink ref="L106" r:id="rId154" display="VIDEO"/>
+    <hyperlink ref="K108" r:id="rId155" display="PDF"/>
+    <hyperlink ref="L108" r:id="rId156" display="VIDEO"/>
+    <hyperlink ref="K109" r:id="rId157" display="PDF"/>
+    <hyperlink ref="L109" r:id="rId158" display="VIDEO"/>
+    <hyperlink ref="K110" r:id="rId159" display="PDF"/>
+    <hyperlink ref="L110" r:id="rId160" display="VIDEO"/>
+    <hyperlink ref="N110" r:id="rId161" display="CODE"/>
+    <hyperlink ref="K111" r:id="rId162" display="PDF"/>
+    <hyperlink ref="L111" r:id="rId163" display="VIDEO"/>
+    <hyperlink ref="N111" r:id="rId164" display="CODE"/>
+    <hyperlink ref="K112" r:id="rId165" display="PDF"/>
+    <hyperlink ref="L112" r:id="rId166" display="VIDEO"/>
+    <hyperlink ref="K113" r:id="rId167" display="PDF"/>
+    <hyperlink ref="L113" r:id="rId168" display="VIDEO"/>
+    <hyperlink ref="K115" r:id="rId169" display="PDF"/>
+    <hyperlink ref="L115" r:id="rId170" display="VIDEO"/>
+    <hyperlink ref="K116" r:id="rId171" display="PDF"/>
+    <hyperlink ref="L116" r:id="rId172" display="VIDEO"/>
+    <hyperlink ref="L117" r:id="rId173" display="VIDEO"/>
+    <hyperlink ref="N117" r:id="rId174" display="CODE"/>
+    <hyperlink ref="K119" r:id="rId175" display="PDF"/>
+    <hyperlink ref="L119" r:id="rId176" display="VIDEO"/>
+    <hyperlink ref="K120" r:id="rId177" display="PDF"/>
+    <hyperlink ref="L120" r:id="rId178" display="VIDEO"/>
+    <hyperlink ref="N120" r:id="rId179" display="CODE"/>
+    <hyperlink ref="K121" r:id="rId180" display="PDF"/>
+    <hyperlink ref="L121" r:id="rId181" display="VIDEO"/>
+    <hyperlink ref="N121" r:id="rId182" display="CODE"/>
+    <hyperlink ref="K122" r:id="rId183" display="PDF"/>
+    <hyperlink ref="K123" r:id="rId184" display="PDF"/>
+    <hyperlink ref="K124" r:id="rId185" display="PDF"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.700694444444444" right="0.700694444444444" top="0.7875" bottom="0.7875" header="0.511805555555555" footer="0.511805555555555"/>
@@ -8665,7 +8905,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.76953125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.18"/>
@@ -8706,7 +8946,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8716,7 +8956,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -8731,18 +8971,18 @@
       <c r="B6" s="24"/>
       <c r="C6" s="8"/>
       <c r="E6" s="10" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
         <v>27</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8751,10 +8991,10 @@
       <c r="C7" s="8"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
@@ -8768,10 +9008,10 @@
       <c r="C8" s="8"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8" t="s">
@@ -8784,7 +9024,7 @@
       <c r="B9" s="24"/>
       <c r="C9" s="8"/>
       <c r="E9" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="5"/>
@@ -8793,7 +9033,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8802,7 +9042,7 @@
       <c r="C10" s="8"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>39</v>
@@ -8812,7 +9052,7 @@
         <v>45</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8821,17 +9061,17 @@
       <c r="C11" s="8"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>322</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8839,11 +9079,11 @@
       <c r="B12" s="24"/>
       <c r="C12" s="8"/>
       <c r="E12" s="10" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="8" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8" t="s">
@@ -8857,10 +9097,10 @@
       <c r="C13" s="8"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8" t="s">
@@ -8874,10 +9114,10 @@
       <c r="C14" s="8"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8" t="s">
@@ -8891,14 +9131,14 @@
       <c r="C15" s="8"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="J15" s="8"/>
     </row>
@@ -8907,7 +9147,7 @@
       <c r="B16" s="24"/>
       <c r="C16" s="8"/>
       <c r="E16" s="6" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="5"/>
@@ -8920,7 +9160,7 @@
       <c r="B17" s="24"/>
       <c r="C17" s="8"/>
       <c r="E17" s="10" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="8"/>
@@ -8929,8 +9169,8 @@
       <c r="J17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="33"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
@@ -8943,13 +9183,13 @@
         <v>79</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>83</v>

--- a/server_nestjs/src/storage/Kompetenzraster.xlsx
+++ b/server_nestjs/src/storage/Kompetenzraster.xlsx
@@ -62,7 +62,7 @@
     <author> </author>
   </authors>
   <commentList>
-    <comment ref="L7" authorId="0">
+    <comment ref="L6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="410">
   <si>
     <t xml:space="preserve">Voraussetzungen lt. Modulhandbuch</t>
   </si>
@@ -676,10 +676,7 @@
     <t xml:space="preserve">ContentElement</t>
   </si>
   <si>
-    <t xml:space="preserve">BeschreibungVideo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">root</t>
+    <t xml:space="preserve">Content Beschreibung</t>
   </si>
   <si>
     <t xml:space="preserve">Funktionale Programmierung mit Python</t>
@@ -736,13 +733,13 @@
     <t xml:space="preserve">In Python gibt es drei Haupttypen von Zahlen: Integer (ganze Zahlen), Floats (Gleitkommazahlen) und komplexe Zahlen. Während Integer und Floats für alltägliche Berechnungen verwendet werden, wobei Floats aufgrund des IEEE 754 Standards zu Rundungsfehlern führen können, sind komplexe Zahlen mit einem imaginären Teil (in Python mit 'j' gekennzeichnet) für spezielle mathematische Anwendungen gedacht.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,7,9,11</t>
+    <t xml:space="preserve">2,8,10,12</t>
   </si>
   <si>
     <t xml:space="preserve">In Python gibt es drei Arten von Zahlen: Integer (ganze Zahlen), Floats (Gleitkommazahlen) und komplexe Zahlen. Während Integer und Floats für alltägliche Berechnungen genutzt werden, wobei Floats aufgrund des IEEE 754 Standards zu Rundungsfehlern führen können, sind komplexe Zahlen mit einem imaginären Teil (in Python mit 'j' gekennzeichnet) für spezielle mathematische Anwendungen vorgesehen.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,7,9,12</t>
+    <t xml:space="preserve">2,8,10,13</t>
   </si>
   <si>
     <t xml:space="preserve">Complex</t>
@@ -751,25 +748,25 @@
     <t xml:space="preserve">In Python gibt es drei Arten von Zahlen: Integer (ganze Zahlen), Floats (Gleitkommazahlen) und komplexe Zahlen. Während Integer und Floats für alltägliche Berechnungen genutzt werden, wobei Floats aufgrund des IEEE 754 Standards zu Rundungsfehlern führen können, sind komplexe Zahlen mit einem imaginären Teil (in Python mit 'j' gekennzeichnet) ein speziellerer Datentyp, der seltener verwendet wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,7,9,13</t>
+    <t xml:space="preserve">2,8,10,14</t>
   </si>
   <si>
     <t xml:space="preserve">Python bietet verschiedene Operatoren für mathematische Operationen, wie die Standardaddition, -subtraktion, -multiplikation und -division, sowie spezielle Operatoren für ganzzahlige Division (//), Modulus (%) und Exponentiation (**). Bei der Division von Ganzzahlen wird automatisch ein Fließkommawert zurückgegeben, während die ganzzahlige Division immer abrundet; zudem können alle Operatoren in Verbindung mit dem Zuweisungsoperator (z.B. +=, *=) für verkürzte Operationen verwendet werden.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,7,9,10,11,12,14</t>
+    <t xml:space="preserve">2,8,10,11,12,13,15</t>
   </si>
   <si>
     <t xml:space="preserve">In Python können verschiedene Datentypen wie Int, Float und Komplex sowie Strings ineinander umgewandelt werden, indem man den entsprechenden Datentyp als Funktion verwendet (z.B. `int()`, `float()`, `str()`). Bei der Umwandlung von Eingaben ist zu beachten, dass `input()` immer einen String zurückgibt, der erst in einen numerischen Typ umgewandelt werden muss, um mathematische Operationen durchführen zu können.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,7,15</t>
+    <t xml:space="preserve">2,8,16</t>
   </si>
   <si>
     <t xml:space="preserve">In Python repräsentieren Booleans die Wahrheitswerte True und False, während None ein spezieller Datentyp ist, der zur Initialisierung von Variablen verwendet wird und nur den Wert None annehmen kann. Diese Datentypen sind essentiell für Vergleichsoperationen und Kontrollstrukturen, wobei None oft genutzt wird, um den Zustand "kein Wert" oder "nicht initialisiert" darzustellen.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,7,16</t>
+    <t xml:space="preserve">2,8,17</t>
   </si>
   <si>
     <t xml:space="preserve">In Python repräsentieren Booleans die Wahrheitswerte True und False, die häufig in Vergleichsoperationen verwendet werden, um logische Bedingungen zu testen. Der Datentyp None wird oft zur Initialisierung von Variablen verwendet und hat nur einen Wert, nämlich None selbst, was anzeigt, dass eine Variable noch keinen anderen Wert zugewiesen bekommen hat.</t>
@@ -778,13 +775,13 @@
     <t xml:space="preserve">6,8</t>
   </si>
   <si>
-    <t xml:space="preserve">1,17</t>
+    <t xml:space="preserve">2,18</t>
   </si>
   <si>
     <t xml:space="preserve">Python Kontrollstrukturen umfassen If-Statements, die mit Vergleichsoperatoren wie gleich (==), nicht gleich (!=), größer (&gt;), kleiner (&lt;), größer gleich (&gt;=) und kleiner gleich (&lt;=) arbeiten, sowie logische Operatoren wie and, or und not, um boolesche Ausdrücke zu verknüpfen. Wichtig ist dabei die korrekte Einrückung, da sie die Programmlogik bestimmt, und Schleifen wie die while-Schleife, die zur Wiederholung von Code-Blöcken verwendet wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,17,18</t>
+    <t xml:space="preserve">2,18,19</t>
   </si>
   <si>
     <t xml:space="preserve">In Python ermöglichen if-else-Kontrollstrukturen die Ausführung von Codeblöcken basierend auf Bedingungen, die zu wahren (True) oder falschen (False) Werten evaluiert werden. Ein if-Statement führt den nachfolgenden Codeblock aus, wenn die Bedingung wahr ist, während ein else-Statement den Codeblock ausführt, wenn alle vorherigen Bedingungen falsch sind; elif-Statements bieten zusätzliche Bedingungsüberprüfungen.</t>
@@ -793,10 +790,10 @@
     <t xml:space="preserve">CODE</t>
   </si>
   <si>
-    <t xml:space="preserve">1,17,19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,17,19,20</t>
+    <t xml:space="preserve">2,18,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,18,20,21</t>
   </si>
   <si>
     <t xml:space="preserve">while</t>
@@ -805,7 +802,7 @@
     <t xml:space="preserve">In dem Code-Beispiel zur Python-Kontrollstruktur `while` wird eine Schleife verwendet, um ein Kartenspiel zu simulieren, bei dem Karten gezogen werden, bis keine mehr übrig sind. Die `while`-Schleife prüft dabei kontinuierlich, ob die Liste der Preiskarten noch Elemente enthält, und entfernt mit der `pop`-Methode jeweils das letzte Element, bis die Liste leer ist und die Schleife beendet wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,17,19,21</t>
+    <t xml:space="preserve">2,18,20,22</t>
   </si>
   <si>
     <t xml:space="preserve">for</t>
@@ -817,7 +814,7 @@
     <t xml:space="preserve">6,8,18</t>
   </si>
   <si>
-    <t xml:space="preserve">1,22</t>
+    <t xml:space="preserve">2,23</t>
   </si>
   <si>
     <t xml:space="preserve">Python-Funktionen ermöglichen es, Codeblöcke zu isolieren und in sinnvolle Abschnitte aufzuteilen, was die Übersichtlichkeit und Wartbarkeit von Programmen erheblich verbessert, insbesondere bei großen Projekten. Sie werden mit dem Schlüsselwort `def` definiert, können beliebig viele Eingabeargumente enthalten und mit `return` Werte zurückgeben, die dann im Hauptprogramm verwendet werden können.</t>
@@ -826,52 +823,52 @@
     <t xml:space="preserve">In dem Codebeispiel werden Teile eines Kartenspiels in Python-Funktionen ausgelagert, um den Code übersichtlicher und modularer zu gestalten. Die Funktionen `StrategieSpieler1` und `StrategieSpieler2` werden definiert, um die Strategie der Spieler zu kapseln, wobei die Funktionen Eingabeparameter wie den Wert der Preiskarte und die verbleibenden Karten des Spielers erhalten und die ausgewählte Karte zurückgeben.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,22,23</t>
+    <t xml:space="preserve">2,23,24</t>
   </si>
   <si>
     <t xml:space="preserve">Python-Funktionen können mit Docstrings dokumentiert werden, die mit drei Anführungszeichen beginnen und eine systematische Beschreibung der Funktion, ihrer Parameter und Rückgabewerte enthalten. Docstrings sind besonders hilfreich in größeren Projekten, da sie es ermöglichen, die Funktionsweise von Code auch Monate später noch zu verstehen, und können mit der `help()`-Funktion abgerufen werden, um Nutzern und Entwicklern die Verwendung der Funktionen zu erleichtern.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,22,24</t>
+    <t xml:space="preserve">2,23,25</t>
   </si>
   <si>
     <t xml:space="preserve">Python-Funktionen können sowohl Positional Arguments als auch Keyword Arguments akzeptieren, wobei die Reihenfolge bei Positional Arguments wichtig ist und bei Keyword Arguments durch die explizite Benennung irrelevant wird. Zusätzlich können Funktionen in Python mit `*args` und `**kwargs` eine variable Anzahl von Positional bzw. Keyword Arguments empfangen, was die Flexibilität bei der Übergabe von Argumenten erhöht.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,22,25</t>
+    <t xml:space="preserve">2,23,26</t>
   </si>
   <si>
     <t xml:space="preserve">In Python können Funktionen als Variablen gespeichert und verwendet werden, was bedeutet, dass man eine Funktion einer Variablen zuweisen und dann diese Variable wie eine Funktion aufrufen kann. Dies ermöglicht es, Funktionen als Argumente an andere Funktionen zu übergeben und sogenannte Higher-Order Functions zu erstellen, die Funktionen höherer Ordnung sind und von anderen Funktionen abhängen können.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,22,26</t>
+    <t xml:space="preserve">2,23,27</t>
   </si>
   <si>
     <t xml:space="preserve">Python-Funktionen können in ausgelagerten Dateien organisiert und mit dem `import`-Befehl in andere Skripte eingebunden werden, wobei der Namespace des importierten Moduls verwendet wird. Um Funktionen direkt im Namensraum verfügbar zu machen, kann `from Modul import Funktionsname` verwendet werden, während `import Modul as Alias` es ermöglicht, Funktionen mit einem benutzerdefinierten Namespace anzusprechen.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,22,27</t>
+    <t xml:space="preserve">2,23,28</t>
   </si>
   <si>
     <t xml:space="preserve">Python-Funktionen höherer Ordnung sind Funktionen, die andere Funktionen als Argumente entgegennehmen und auf Elemente einer Liste anwenden. Sie ermöglichen es, Operationen wie das Quadrieren von Zahlen oder das Hinzufügen von Absätzen zu Strings in Listen effizient durchzuführen, indem man eine allgemeine Funktion wie "auf jedes Element" definiert und diese dann mit spezifischen Funktionen für unterschiedliche Aufgaben verwendet.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,28</t>
+    <t xml:space="preserve">2,29</t>
   </si>
   <si>
     <t xml:space="preserve">In Python können Variablen entweder global oder lokal sein, wobei globale Variablen überall im Code verwendet werden können und lokale Variablen nur innerhalb der Funktion, in der sie definiert wurden. Änderungen an globalen, veränderbaren (mutable) Variablen innerhalb einer Funktion sind auch außerhalb sichtbar, während Änderungen an lokalen Variablen nach dem Funktionsaufruf nicht bestehen bleiben.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,28,29</t>
+    <t xml:space="preserve">2,29,30</t>
   </si>
   <si>
     <t xml:space="preserve">In Python können Variablen entweder mutable (veränderbar) oder immutable (unveränderbar) sein. Globale Variablen, die außerhalb von Funktionen definiert werden, können innerhalb von Funktionen gelesen und, wenn sie mutable sind, auch verändert werden, wobei die Änderungen dann global sichtbar sind; lokale Variablen hingegen sind nur innerhalb ihrer Funktion sichtbar und existieren außerhalb nicht.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,30,31</t>
+    <t xml:space="preserve">2,31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,31,32</t>
   </si>
   <si>
     <t xml:space="preserve">In Python können Variablen, die außerhalb einer Funktion definiert wurden, innerhalb der Funktion verwendet werden, sofern sie vor der Funktionsdefinition initialisiert wurden; sie gelten dann als globale Variablen. Lokale Variablen hingegen sind nur innerhalb der Funktion bekannt und Änderungen an ihnen sind außerhalb der Funktion nicht sichtbar, es sei denn, sie werden explizit als global innerhalb der Funktion deklariert.</t>
@@ -880,10 +877,10 @@
     <t xml:space="preserve">Das Transkript behandelt die Unterscheidung zwischen lokalen und globalen Variablen in Python und wie sie innerhalb von Funktionen verwendet werden können. Globale Variablen können innerhalb von Funktionen gelesen werden, wenn sie vorher definiert wurden, während lokale Variablen nur innerhalb der Funktion existieren und außerhalb nicht sichtbar sind. Es wird auch erklärt, wie man mit dem Schlüsselwort `global` eine lokale Variable in einer Funktion als global deklarieren kann, sodass Änderungen an ihr auch außerhalb der Funktion sichtbar sind.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,30,32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,33</t>
+    <t xml:space="preserve">2,31,33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,34</t>
   </si>
   <si>
     <t xml:space="preserve">Rekursion in Python bezeichnet das Konzept, bei dem eine Funktion sich selbst aufruft, um ein Problem zu lösen. Es ist wichtig, eine Abbruchbedingung zu definieren, um unendliche Rekursionen und damit Programmabstürze zu vermeiden; rekursive Lösungen können eleganter oder mit weniger Code als iterative Lösungen sein und verhindern die Mutation von Variablen, was sie für funktionale Programmierung attraktiv macht.</t>
@@ -895,151 +892,151 @@
     <t xml:space="preserve">In dem Codebeispiel wird die Rekursion anhand verschiedener mathematischer Probleme in Python demonstriert, wie die Summe aller Zahlen bis N, die Fakultät einer Zahl und die Überprüfung, ob eine Zahl eine Primzahl ist. Die Rekursion wird dabei als Methode zur Problemlösung verwendet, indem ein großes Problem in kleinere Instanzen heruntergebrochen wird, bis eine Instanz erreicht ist, die direkt gelöst werden kann.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,34,35</t>
+    <t xml:space="preserve">2,35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,35,36</t>
   </si>
   <si>
     <t xml:space="preserve">Der Befehl map nimmt eine Funktion und ein iterierbares Objekt (z.B. Liste oder Tupel) entgegen und wendet die Funktion auf jedes Element des iterierbaren Objektes an. Genauer, bekommen wir einen Iterator zurück über welchen wir iterieren können oder Methoden wie __next__() aufrufen.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,34,36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,34,37</t>
+    <t xml:space="preserve">2,35,37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,35,38</t>
   </si>
   <si>
     <t xml:space="preserve">Der Befehl reduce nimmt auch eine Funktion und iterierbares Objekt (z.B. Liste oder Tupel) entgegen. Die Funktion muss zwei Elemente in dem iterierbaren Objekt auf eines abbilden und reduziert nun durch sukzessives Anwenden der Funktion das gesamte iterierbare Objekt auf ein Element.</t>
   </si>
   <si>
-    <t xml:space="preserve">1,38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,38,39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,38,40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,38,41</t>
+    <t xml:space="preserve">2,39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,39,40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,39,41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,39,42</t>
   </si>
   <si>
     <t xml:space="preserve">Objektorientierte Programmierung mit Java</t>
   </si>
   <si>
-    <t xml:space="preserve">42,43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,45,46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,45,47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,45,48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,45,49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,45,50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,45,50,51</t>
+    <t xml:space="preserve">43,44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,46,47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,46,48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,46,49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,46,50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,46,51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,46,51,52</t>
   </si>
   <si>
     <t xml:space="preserve">Operationen auf Strings</t>
   </si>
   <si>
-    <t xml:space="preserve">42,45,50,52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,45,53</t>
+    <t xml:space="preserve">43,46,51,53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,46,54</t>
   </si>
   <si>
     <t xml:space="preserve">In Java müssen Variablen einen spezifischen Typ haben, der ihre Verwendung und die Art der Werte, die sie speichern können, bestimmt. Fehler bei der Zuweisung von Typen oder der Verwendung von Konstanten können zu Fehlermeldungen oder unerwünschtem Verhalten der Anwendung führen.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,45,54</t>
+    <t xml:space="preserve">43,46,55</t>
   </si>
   <si>
     <t xml:space="preserve">In Java können Typkonversionen implizit oder explizit erfolgen, wobei implizite Konversionen meist von einem kleineren zu einem größeren Datentyp ohne Informationsverlust möglich sind. Explizite Konversionen erfordern die Verwendung von Klammern und können zu Informationsverlust führen, wie beim Konvertieren von Fließkommazahlen zu Ganzzahlen, und nicht alle Typen, wie Booleans, können konvertiert werden.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,55</t>
+    <t xml:space="preserve">43,56</t>
   </si>
   <si>
     <t xml:space="preserve">In Java werden Variablen mit einem spezifischen Namen und Typ deklariert, wobei das Schlüsselwort `final` eine Variable als unveränderliche Konstante kennzeichnet. Variablen haben einen definierten Gültigkeitsbereich, der durch Codeblöcke mit geschweiften Klammern festgelegt wird, und innerhalb desselben Gültigkeitsbereichs darf ein Variablenname nicht mehrfach verwendet werden.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,56,57</t>
+    <t xml:space="preserve">43,57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,57,58</t>
   </si>
   <si>
     <t xml:space="preserve">In Java können Variablen als `final` deklariert werden, was bedeutet, dass ihr Wert nach der Initialisierung nicht mehr geändert werden kann, und sie werden somit zu Konstanten. Jede Variable hat einen bestimmten Gültigkeitsbereich, der durch Blöcke mit geschweiften Klammern definiert wird, und innerhalb dessen die Variable aktiv und bekannt ist, außerhalb jedoch nicht mehr gültig ist.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,56,58</t>
+    <t xml:space="preserve">43,57,59</t>
   </si>
   <si>
     <t xml:space="preserve">Java bietet eine Vielzahl von Operatoren, die für verschiedene Arten von Operationen verwendet werden können, darunter arithmetische, unäre, binäre und ternäre Operatoren. Zu den arithmetischen Operatoren gehören Addition, Subtraktion, Multiplikation und Division, während Vergleichsoperatoren und logische Operatoren in bedingten Anweisungen wie if-Tests verwendet werden, um Werte zu vergleichen und Boolesche Ausdrücke zu bilden.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,56,59</t>
+    <t xml:space="preserve">43,57,60</t>
   </si>
   <si>
     <t xml:space="preserve">In Java sind Zuweisungen Anweisungen, bei denen Variablen Werte zugewiesen werden, wie beispielsweise bei der Zuweisung von 7 zu den Variablen x und y. Diese Zuweisungen können auch arithmetische Operationen beinhalten, wie etwa x gleich x minus 5, und werden für verschiedene Datentypen wie Integer, Float oder Double verwendet, wobei der berechnete Wert der Variablen zugewiesen wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,56,60</t>
+    <t xml:space="preserve">43,57,61</t>
   </si>
   <si>
     <t xml:space="preserve">In Java ist ein Block ein Codeabschnitt, der von geschweiften Klammern umgeben ist, innerhalb dessen definierte Variablen nur innerhalb dieses Blocks existieren und nach dessen Ende nicht mehr verfügbar sind. Anweisungen innerhalb eines Blocks werden sequenziell von oben nach unten und von links nach rechts ausgeführt, wobei jede Anweisung durch einen Strichpunkt getrennt wird, außer bei Blöcken selbst, bei denen der abschließende Strichpunkt weggelassen werden kann.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,61,62</t>
+    <t xml:space="preserve">43,62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,62,63</t>
   </si>
   <si>
     <t xml:space="preserve">Java-Kontrollstrukturen wie if-else nutzen Blöcke, die durch geschweifte Klammern definiert sind, um Variablen und Anweisungen zu umschließen, die nur innerhalb dieser Blöcke gültig und lebendig sind. Anweisungen innerhalb eines Blocks werden sequenziell von oben nach unten und von links nach rechts ausgeführt, wobei jede Anweisung durch einen Strichpunkt getrennt wird, außer bei Blöcken selbst, bei denen der abschließende Strichpunkt weggelassen werden kann.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,61,63</t>
+    <t xml:space="preserve">43,62,64</t>
   </si>
   <si>
     <t xml:space="preserve">Die Switch-Anweisung in Java ermöglicht es, einen Wert gegen eine Reihe von Konstanten zu prüfen und entsprechend unterschiedliche Blöcke von Anweisungen auszuführen. Jeder Block wird durch das Schlüsselwort "case" eingeleitet und muss mit einem "break" enden, um die Ausführung der Switch-Anweisung zu beenden; andernfalls wird die Ausführung fortgesetzt, bis ein "break" erreicht wird oder die gesamte Anweisung abgearbeitet ist, wobei "default" für alle nicht explizit aufgeführten Fälle verwendet wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,61,64</t>
+    <t xml:space="preserve">43,62,65</t>
   </si>
   <si>
     <t xml:space="preserve">Java bietet verschiedene Schleifentypen für unterschiedliche Anwendungsfälle: Die for-Schleife eignet sich besonders, wenn die Anzahl der Durchläufe bekannt ist, wie etwa das Durchlaufen von Zahlenbereichen. Die while- und do-while-Schleifen sind hingegen nützlich, wenn die Anzahl der Wiederholungen nicht im Voraus bekannt ist, wobei die do-while-Schleife den Schleifenblock mindestens einmal ausführt, bevor die Bedingung geprüft wird, im Gegensatz zur while-Schleife, die die Bedingung vor dem ersten Durchlauf prüft.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,61,64,65</t>
+    <t xml:space="preserve">43,62,65,66</t>
   </si>
   <si>
     <t xml:space="preserve">Die while-Schleife in Java beginnt mit dem Keyword "while", gefolgt von einer Bedingung in runden Klammern; wenn diese Bedingung wahr ist, werden die in geschweiften Klammern eingeschlossenen Anweisungen ausgeführt. Die do-while-Schleife hingegen führt die Anweisungen mindestens einmal aus, bevor die Bedingung am Ende der Schleife geprüft wird, und wiederholt den Vorgang, solange die Bedingung wahr ist.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,61,64,66</t>
+    <t xml:space="preserve">43,62,65,67</t>
   </si>
   <si>
     <t xml:space="preserve">Java bietet mit der For-Schleife eine Kontrollstruktur, die aus drei Teilen in runden Klammern besteht: Initialisierung (z.B. `int i = 0`), Bedingung (z.B. `i &lt;= 10`) und Inkrementierung (z.B. `i++`), die es ermöglichen, einen Codeblock wiederholt auszuführen, solange die Bedingung wahr ist. Es ist möglich, mehrere Operationen in den einzelnen Teilen der For-Schleife durchzuführen, aber üblicherweise wird sie für einfache Iterationen verwendet, wobei manchmal auch Befehle wie `continue` und `break` genutzt werden können, um die Schleifenausführung zu steuern.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,61,64,65,66</t>
+    <t xml:space="preserve">43,62,65,66,67</t>
   </si>
   <si>
     <t xml:space="preserve">Beispiele</t>
@@ -1048,46 +1045,46 @@
     <t xml:space="preserve">In dem Beispiel BigX wird gezeigt, wie man mit Java Kontrollstrukturen wie for-Schleifen und if-Anweisungen ein großes "X" in der Konsole darstellen kann. Die Größe des "X" wird durch eine Variable bestimmt, und durch geschachtelte for-Schleifen und Bedingungen wird für jede Zeile und Spalte entschieden, ob ein "X" oder ein Leerzeichen ausgegeben wird, um die Form des "X" zu erzeugen.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,67,68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,67,68,69</t>
+    <t xml:space="preserve">43,68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,68,69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,68,69,70</t>
   </si>
   <si>
     <t xml:space="preserve">mehrdimansionales Array</t>
   </si>
   <si>
-    <t xml:space="preserve">42,67,70</t>
+    <t xml:space="preserve">43,68,71</t>
   </si>
   <si>
     <t xml:space="preserve">Java bietet eine Vielzahl von Klassen und Paketen zur Dateiverarbeitung, die man durch Import-Anweisungen in den eigenen Code einbinden kann. Um Dateien zu lesen, zu schreiben und zu bearbeiten, muss man die entsprechenden Klassen und Methoden kennen und nutzen, wie zum Beispiel die File-Klasse für Dateioperationen und verschiedene Methoden für das Öffnen, Schließen, Lesen und Schreiben von Dateien, wobei oft ein Puffer verwendet wird, um die Effizienz zu steigern.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,71,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,71,74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,71,75</t>
+    <t xml:space="preserve">43,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,72,73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,72,75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,72,76</t>
   </si>
   <si>
     <t xml:space="preserve">Objektreferenzen</t>
   </si>
   <si>
-    <t xml:space="preserve">42,71,76,77</t>
+    <t xml:space="preserve">43,72,77,78</t>
   </si>
   <si>
     <t xml:space="preserve">Attribute und Methoden</t>
   </si>
   <si>
-    <t xml:space="preserve">42,71,76,78</t>
+    <t xml:space="preserve">43,72,77,79</t>
   </si>
   <si>
     <t xml:space="preserve">Arrays von Objekten</t>
@@ -1096,70 +1093,70 @@
     <t xml:space="preserve">In Java können Arrays nicht nur primitive Datentypen wie Integers oder Doubles enthalten, sondern auch Objekte, wie zum Beispiel Instanzen der Klasse String oder benutzerdefinierte Klassen wie Enemies in einem Spiel. Um ein Array von Objekten zu verwenden, muss zuerst Speicherplatz für das Array reserviert werden, und anschließend müssen die einzelnen Objekte im Array mit dem Schlüsselwort 'new' tatsächlich erstellt werden, da anfänglich nur Referenzen ohne zugewiesene Objekte existieren.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,79,80</t>
+    <t xml:space="preserve">43,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,80,81</t>
   </si>
   <si>
     <t xml:space="preserve">In Java werden Methoden aufgerufen, indem man ihnen Parameter übergibt, die als Call-by-Value kopiert werden, wodurch die ursprünglichen Variablen unverändert bleiben. Beim Methodenaufruf werden die Parameterwerte auf den Stack kopiert und die Methode ausgeführt, wobei nach Beendigung der Methode die temporären Variablen auf dem Stack gelöscht werden und die ursprünglichen Variablen unverändert bleiben.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,79,81</t>
+    <t xml:space="preserve">43,80,82</t>
   </si>
   <si>
     <t xml:space="preserve">In Java werden Objekte und Arrays als Referenzen an Methoden übergeben (Call-by-Reference), was bedeutet, dass Änderungen an den Objekten innerhalb der Methode auch außerhalb sichtbar sind, da nicht die Werte, sondern die Referenzen auf die Speicherorte der Objekte übergeben werden. Im Gegensatz dazu werden primitive Datentypen wie int als Werte übergeben (Call-by-Value), sodass Änderungen an diesen Parametern innerhalb der Methode nicht außerhalb der Methode sichtbar sind, da Kopien der Werte übergeben werden.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,79,82</t>
+    <t xml:space="preserve">43,80,83</t>
   </si>
   <si>
     <t xml:space="preserve">In Java können Methoden überladen werden, indem man mehrere Methoden mit demselben Namen, aber unterschiedlichen Parametertypen oder -anzahlen definiert, sodass der Compiler anhand der übergebenen Argumente die richtige Methode auswählen kann. Überladene Methoden müssen sich in der Parameterliste unterscheiden, da der Rückgabetyp allein nicht ausreicht, um für den Compiler eine eindeutige Unterscheidung zu ermöglichen, was sonst zu Fehlern führen würde.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,79,83</t>
+    <t xml:space="preserve">43,80,84</t>
   </si>
   <si>
     <t xml:space="preserve">Java-Methoden können rekursiv definiert werden, indem sie sich selbst innerhalb ihrer eigenen Definition aufrufen. Ein klassisches Beispiel für Rekursion in Java ist die Berechnung der Fakultät einer Zahl, bei der die Methode sich mit einem verminderten Wert erneut aufruft, bis der Basisfall erreicht ist, und dann die Ergebnisse auf dem Weg zurück nach oben multipliziert.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,84</t>
+    <t xml:space="preserve">43,85</t>
   </si>
   <si>
     <t xml:space="preserve">Java UML bezieht sich auf die Verwendung von Unified Modeling Language (UML) Diagrammen zur Darstellung und Planung der Struktur von Java-Programmen. UML-Diagramme helfen dabei, einen Überblick über die verschiedenen Klassen und ihre Beziehungen zueinander zu schaffen, was besonders nützlich ist, wenn Projekte komplexer werden und mehrere Klassen und Objekte involviert sind.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,84,85</t>
+    <t xml:space="preserve">43,85,86</t>
   </si>
   <si>
     <t xml:space="preserve">Java UML Klassen dienen als Blaupausen für Objekte und definieren deren Struktur durch Attribute und Methoden. Während Attribute die Eigenschaften einer Klasse festlegen und Initialwerte haben können, ermöglichen Methoden die Manipulation dieser Eigenschaften und das Ausführen von Operationen; Klassen können in UML-Diagrammen unterschiedlich dargestellt werden, je nachdem ob sie Attribute, Methoden oder beides enthalten.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,84,86</t>
+    <t xml:space="preserve">43,85,87</t>
   </si>
   <si>
     <t xml:space="preserve">In UML (Unified Modeling Language) können Objekte als Instanzen von Klassen dargestellt werden, wobei Objekte klein und Klassen groß geschrieben werden, getrennt durch einen Doppelpunkt. Objekte werden mit ihren Attributen und Werten gezeigt, und Beziehungen zwischen Objekten werden durch Linien repräsentiert, wobei die Identität und Gleichheit von Objekten im Speicher durch ihre Darstellung unterschieden werden kann.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,84,87</t>
+    <t xml:space="preserve">43,85,88</t>
   </si>
   <si>
     <t xml:space="preserve">Java UML Attribute repräsentieren die Eigenschaften einer Klasse und können mit einer Multiplizität versehen werden, die angibt, wie viele Instanzen eines Attributs existieren dürfen. Diese Multiplizität wird in eckigen Klammern dargestellt, wobei die Untergrenze und Obergrenze durch zwei Punkte getrennt sind, und ein Stern (*) steht für eine unbestimmte Anzahl von Instanzen.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,84,88</t>
+    <t xml:space="preserve">43,85,89</t>
   </si>
   <si>
     <t xml:space="preserve">In UML werden Operationen (Methoden) einer Klasse durch runde Klammern dargestellt, um sie von Attributen zu unterscheiden, die keine Klammern haben. Die Rückgabetypen und Parameter der Operationen werden in UML spezifiziert, wobei Parameter mit "In" für Eingabeparameter gekennzeichnet werden können und der Typ mit einem Doppelpunkt vom Namen getrennt wird, wobei UML im Gegensatz zu Java nicht sofort Typfehler aufzeigt.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,84,89</t>
+    <t xml:space="preserve">43,85,90</t>
   </si>
   <si>
     <t xml:space="preserve">Java UML Assoziationen beschreiben die Beziehungen zwischen verschiedenen Klassen in einem Klassendiagramm, wobei Assoziationen die Verbindungen zwischen Objekten darstellen und durch Linien repräsentiert werden. Diese Assoziationen können verschiedene Multiplizitäten aufweisen, die angeben, wie viele Instanzen einer Klasse mit Instanzen einer anderen Klasse in Beziehung stehen können, und können auch Rollennamen enthalten, die die Art der Beziehung näher spezifizieren.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,84,89,90</t>
+    <t xml:space="preserve">43,85,90,91</t>
   </si>
   <si>
     <t xml:space="preserve">Navigierbarkeit</t>
@@ -1168,55 +1165,55 @@
     <t xml:space="preserve">In UML-Diagrammen kann die Navigierbarkeit von Assoziationen zwischen Klassen durch Pfeile dargestellt werden, wobei die Richtung des Pfeils die Richtung der Navigierbarkeit angibt. In Java wird diese Navigierbarkeit durch Referenzvariablen als Attribute in den Klassen implementiert, wodurch Objekte einer Klasse auf assoziierte Objekte einer anderen Klasse zugreifen können.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,84,91</t>
+    <t xml:space="preserve">43,85,92</t>
   </si>
   <si>
     <t xml:space="preserve">In Java UML Sichtbarkeit werden Attribute üblicherweise als privat (private) deklariert, um die Prinzipien der Objektorientierung wie Kapselung und klare Schnittstellen zu wahren. UML verwendet spezielle Symbole, um die Sichtbarkeit zu kennzeichnen: ein Plus für öffentlich (public), ein Minus für privat (private) und ein Pfund-Symbol für geschützt (protected), wobei Get- und Set-Methoden definiert werden müssen, um den Zugriff auf private Attribute zu ermöglichen.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,92,93</t>
+    <t xml:space="preserve">43,93,94</t>
   </si>
   <si>
     <t xml:space="preserve">In Java Vererbung und Generalisierung ermöglichen es, Klassen zu schaffen, die gemeinsame Attribute und Methoden von einer Oberklasse erben, um Redundanz zu vermeiden und eine hierarchische Struktur zu schaffen. Durch die Definition einer allgemeinen Klasse wie "Person" mit grundlegenden Eigenschaften und Methoden können spezifischere Klassen wie "Angestellter", "Student" und "Hilfskraft" diese erben und um zusätzliche, spezifische Merkmale erweitern, wodurch eine klare und effiziente Objekthierarchie entsteht.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,92,94</t>
+    <t xml:space="preserve">43,93,95</t>
   </si>
   <si>
     <t xml:space="preserve">In Java können Klassen und Operationen als abstrakt definiert werden, wobei abstrakte Klassen als Vorlage dienen, von denen andere Klassen Attribute und Methoden erben, ohne dass von der abstrakten Klasse selbst Objekte instanziiert werden. UML visualisiert abstrakte Klassen und Operationen durch Kursivschrift oder das Schlüsselwort "abstrakt", und in Java wird das Schlüsselwort `abstract` verwendet, um zu kennzeichnen, dass eine Klasse oder Methode abstrakt ist und von abgeleiteten Klassen implementiert werden muss.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,84,92,95</t>
+    <t xml:space="preserve">43,85,93,96</t>
   </si>
   <si>
     <t xml:space="preserve">Java UML Interfaces repräsentieren abstrakte Klassen mit ausschließlich abstrakten Methoden, die als Schnittstellen dienen und die vollständige Abkapselung von Funktionalitäten ermöglichen. Sie legen fest, welche Methoden von implementierenden Klassen definiert werden müssen, ohne selbst Instanzen zu erzeugen, und dienen als Verträge zwischen verschiedenen Entwicklern, um die Interaktion zwischen verschiedenen Teilen eines Programms zu koordinieren.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,84,92,96</t>
+    <t xml:space="preserve">43,85,93,97</t>
   </si>
   <si>
     <t xml:space="preserve">In Java UML Vererbung übernimmt eine Unterklasse alle Attribute, Methoden und Anfangswerte der Oberklasse, wobei Unterklassen nie etwas von der geerbten Funktionalität löschen können. Zusätzlich können Unterklassen das Verhalten von Methoden neu definieren, indem sie diese überschreiben, wobei die überschriebenen Methoden die gleiche Signatur wie die der Oberklasse haben müssen.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,97</t>
+    <t xml:space="preserve">43,98</t>
   </si>
   <si>
     <t xml:space="preserve">In Java ermöglicht Polymorphie, dass Methoden und Operatoren mehrere Formen annehmen können, indem sie mehrmals definiert und implementiert werden. Die Vererbungshierarchie und die Möglichkeit, Methoden zu überladen und zu überschreiben, erlauben es, dass Objekte einer Oberklasse als Objekte einer Unterklasse interpretiert werden können, wodurch zur Laufzeit die passende Methode dynamisch gebunden und ausgeführt wird, was als Polymorphismus bezeichnet wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,97,98</t>
+    <t xml:space="preserve">43,98,99</t>
   </si>
   <si>
     <t xml:space="preserve">In Java ist jede Klasse, die definiert wird, implizit eine Unterklasse der zentralen Objektklasse, wenn keine explizite Oberklasse angegeben wird. Diese Objektklasse stellt grundlegende Methoden wie toString und equals zur Verfügung, die von allen abgeleiteten Klassen genutzt und überschrieben werden können, um Polymorphie und andere objektorientierte Konzepte zu unterstützen.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,99,100</t>
+    <t xml:space="preserve">43,100,101</t>
   </si>
   <si>
     <t xml:space="preserve">In Java bezeichnet der Begriff "Exceptions" Ausnahmesituationen, die während der Ausführung eines Programms auftreten können, wenn etwas Unerwartetes geschieht, wie beispielsweise eine Division durch Null. Um solche Ausnahmen zu behandeln, bietet Java die Try-Catch-Blöcke an, in denen der Code, der eine Ausnahme auslösen könnte, in einem Try-Block platziert wird und die Behandlung der Ausnahme im zugehörigen Catch-Block erfolgt, wodurch der Code übersichtlicher und robuster gegenüber Fehlern wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,99,100,101</t>
+    <t xml:space="preserve">43,100,101,102</t>
   </si>
   <si>
     <t xml:space="preserve">In Java können Entwickler eigene Ausnahmen definieren und mit dem Schlüsselwort `throw` auslösen, wobei oft ein neues Ausnahmeobjekt mit `new` erstellt wird. Die Ausnahmebehandlung erfolgt durch `try`-Blöcke, die gefolgt von `catch`-Blöcken sind, um spezifische Fehler zu fangen und zu behandeln, und optional einem `finally`-Block für Aufräumarbeiten, der unabhängig vom Erfolg der Fehlerbehandlung ausgeführt wird.</t>
@@ -1225,31 +1222,31 @@
     <t xml:space="preserve">In Java können Ausnahmen mit Try-Catch-Blöcken behandelt werden, um Fehler während der Laufzeit zu handhaben, wie im Beispiel des WURTLE-Spiels gezeigt, bei dem Wörter aus einer Datei geladen werden. Wenn beim Laden der Datei ein Fehler auftritt, fängt der Catch-Block die Ausnahme ab und ermöglicht es dem Programm, mit einem Fallback-Wörterarray fortzufahren, ohne dass der Benutzer einen Fehler bemerkt.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,102,103</t>
+    <t xml:space="preserve">43,103,104</t>
   </si>
   <si>
     <t xml:space="preserve">Java Dateien Streams ermöglichen es, sequenziell Daten zu lesen und zu schreiben, indem sie eine konzeptionelle Darstellung von Datenflüssen als Ströme (Streams) verwenden. In Java gibt es verschiedene Klassen im Paket java.io, wie File-InputStream und File-OutputStream, um Dateien zu lesen bzw. zu schreiben, sowie weitere spezialisierte Streams für bidirektionale Zugriffe oder das Verarbeiten von Objekten und primitiven Datentypen.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,102,104</t>
+    <t xml:space="preserve">43,103,105</t>
   </si>
   <si>
     <t xml:space="preserve">Java-Dateien-Serialisierung ermöglicht es, komplexe Objektstrukturen, die im Speicher eines Programms existieren, in eine sequenzielle Byte-Reihenfolge umzuwandeln und dauerhaft zu speichern, um sie später wiederherstellen zu können. In Java wird dies durch die Implementierung des Serializable-Interfaces erreicht, wobei die Serialisierung und Deserialisierung von Objekten rekursiv erfolgt, um alle verknüpften Objekte und deren Attribute zu erfassen und in einem Stream zu speichern oder aus diesem zu lesen.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,102,105</t>
+    <t xml:space="preserve">43,103,106</t>
   </si>
   <si>
     <t xml:space="preserve">Java bietet mit Reader und Writer Klassen eine Möglichkeit, Text zeichenorientiert statt byte-orientiert zu verarbeiten, was insbesondere für die strukturierte Ausgabe von Daten wie Studenteninformationen in Textdateien nützlich ist. Diese Klassen ermöglichen es, Daten zu lesen und zu schreiben, wobei die Daten als Strings repräsentiert werden, was mehr Speicherplatz beanspruchen kann als die reine Byte-Darstellung.</t>
   </si>
   <si>
-    <t xml:space="preserve">42,106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42,107,108</t>
+    <t xml:space="preserve">43,107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,108,109</t>
   </si>
   <si>
     <t xml:space="preserve">Zusatz ohne Ziel- bzw. Kompetenzfomulierung</t>
@@ -1417,7 +1414,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1433,7 +1430,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E6E6"/>
-        <bgColor rgb="FFEEEEEE"/>
+        <bgColor rgb="FFD0CECE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1445,12 +1442,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFEEEEEE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEEEEE"/>
         <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
@@ -1606,18 +1597,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1655,6 +1634,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1678,6 +1661,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1696,6 +1683,10 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1722,12 +1713,12 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1760,8 +1751,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFEEEEEE"/>
       <rgbColor rgb="FFE7E6E6"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0563C1"/>
@@ -5291,7 +5282,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S128"/>
+  <dimension ref="A1:S1048576"/>
   <sheetFormatPr defaultColWidth="10.72265625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="17.14"/>
@@ -5299,13 +5290,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="25" width="16.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="25.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="42.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="31.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="25.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="31.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="11.99"/>
   </cols>
   <sheetData>
@@ -5356,14 +5347,10 @@
         <v>193</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="R1" s="27" t="s">
         <v>194</v>
       </c>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="27"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="28"/>
@@ -5371,1263 +5358,1330 @@
       <c r="C2" s="28"/>
       <c r="D2" s="29"/>
       <c r="E2" s="29"/>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="29"/>
+      <c r="I2" s="28"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="31"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="I3" s="33"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="S3" s="15" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="33" t="n">
+      <c r="A4" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>196</v>
-      </c>
-      <c r="G4" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="36" t="n">
+      <c r="H4" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="S4" s="15" t="s">
-        <v>197</v>
-      </c>
+      <c r="I4" s="38"/>
+      <c r="J4" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="37" t="n">
+      <c r="A5" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="35"/>
+      <c r="E5" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="F5" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="39" t="s">
-        <v>198</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="K5" s="12"/>
+      <c r="H5" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="12"/>
+      <c r="K5" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
       <c r="Q5" s="12"/>
-      <c r="R5" s="15"/>
+      <c r="R5" s="40"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37" t="n">
-        <v>4</v>
+      <c r="A6" s="34" t="n">
+        <v>5</v>
       </c>
       <c r="B6" s="24"/>
-      <c r="C6" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="38"/>
+      <c r="C6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="35"/>
       <c r="E6" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="F6" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="G6" s="37" t="n">
+      <c r="F6" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="12"/>
+      <c r="H6" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>201</v>
+      </c>
       <c r="K6" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="L6" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="M6" s="14"/>
       <c r="N6" s="12"/>
       <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="42"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="40"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="37" t="n">
+      <c r="A7" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="41" t="s">
-        <v>88</v>
-      </c>
-      <c r="G7" s="37" t="n">
+      <c r="H7" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="12" t="s">
+      <c r="I7" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="K7" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="M7" s="14"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="42"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="40"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="n">
+      <c r="A8" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="42"/>
+      <c r="C8" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="G8" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="44" t="n">
+      <c r="H8" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="F8" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>205</v>
+      <c r="I8" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>206</v>
       </c>
       <c r="K8" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L8" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M8" s="17"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
-      <c r="R8" s="42"/>
+      <c r="R8" s="47"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="43" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45" t="s">
-        <v>206</v>
-      </c>
-      <c r="F9" s="47" t="s">
-        <v>91</v>
-      </c>
-      <c r="G9" s="43" t="n">
+      <c r="A9" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="18" t="s">
+      <c r="C9" s="34"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="K9" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="M9" s="17"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="48"/>
+      <c r="F9" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="48"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="40"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="n">
+      <c r="A10" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="12"/>
+      <c r="H10" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>209</v>
+      </c>
       <c r="K10" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="M10" s="14"/>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
-      <c r="R10" s="42"/>
+      <c r="R10" s="47"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="n">
-        <v>9</v>
+      <c r="A11" s="34" t="n">
+        <v>10</v>
       </c>
       <c r="B11" s="24"/>
-      <c r="C11" s="37" t="n">
-        <v>5</v>
+      <c r="C11" s="34" t="n">
+        <v>6</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="F11" s="50" t="s">
-        <v>93</v>
-      </c>
-      <c r="G11" s="37" t="n">
+        <v>210</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="H11" s="19"/>
-      <c r="I11" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="M11" s="14"/>
+      <c r="H11" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
-      <c r="R11" s="48"/>
+      <c r="R11" s="40"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="n">
-        <v>10</v>
+      <c r="A12" s="34" t="n">
+        <v>11</v>
       </c>
       <c r="B12" s="24"/>
-      <c r="C12" s="37" t="n">
-        <v>6</v>
+      <c r="C12" s="34" t="n">
+        <v>7</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="F12" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="G12" s="37" t="n">
-        <v>8</v>
-      </c>
-      <c r="H12" s="19"/>
-      <c r="I12" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="8"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
+      <c r="F12" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="G12" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="M12" s="14"/>
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
-      <c r="R12" s="42"/>
+      <c r="R12" s="40"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="n">
-        <v>11</v>
+      <c r="A13" s="34" t="n">
+        <v>12</v>
       </c>
       <c r="B13" s="24"/>
-      <c r="C13" s="37" t="n">
-        <v>7</v>
+      <c r="C13" s="34" t="n">
+        <v>8</v>
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="24" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="G13" s="37" t="n">
+        <v>134</v>
+      </c>
+      <c r="G13" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="H13" s="8"/>
-      <c r="I13" s="37" t="n">
+      <c r="H13" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M13" s="14"/>
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
-      <c r="R13" s="42"/>
+      <c r="R13" s="40"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="n">
-        <v>12</v>
+      <c r="A14" s="34" t="n">
+        <v>13</v>
       </c>
       <c r="B14" s="24"/>
-      <c r="C14" s="37" t="n">
-        <v>8</v>
+      <c r="C14" s="34" t="n">
+        <v>9</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="24" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F14" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="G14" s="37" t="n">
+        <v>216</v>
+      </c>
+      <c r="G14" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="37" t="n">
+      <c r="H14" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K14" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M14" s="14"/>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
-      <c r="R14" s="42"/>
+      <c r="R14" s="40"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="n">
-        <v>13</v>
+      <c r="A15" s="34" t="n">
+        <v>14</v>
       </c>
       <c r="B15" s="24"/>
-      <c r="C15" s="37" t="n">
-        <v>9</v>
+      <c r="C15" s="34" t="n">
+        <v>10</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="24" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>217</v>
-      </c>
-      <c r="G15" s="37" t="n">
+        <v>101</v>
+      </c>
+      <c r="G15" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="37" t="n">
+      <c r="H15" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M15" s="14"/>
       <c r="N15" s="8"/>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
-      <c r="R15" s="42"/>
+      <c r="R15" s="40"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37" t="n">
-        <v>14</v>
+      <c r="A16" s="34" t="n">
+        <v>15</v>
       </c>
       <c r="B16" s="24"/>
-      <c r="C16" s="37" t="n">
-        <v>10</v>
+      <c r="C16" s="34" t="n">
+        <v>11</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F16" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="G16" s="37" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" s="48" t="n">
         <v>10</v>
       </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="37" t="n">
+      <c r="H16" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K16" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M16" s="14"/>
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
-      <c r="R16" s="42"/>
+      <c r="R16" s="40"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="37" t="n">
-        <v>15</v>
+      <c r="A17" s="34" t="n">
+        <v>16</v>
       </c>
       <c r="B17" s="24"/>
-      <c r="C17" s="37" t="n">
-        <v>11</v>
+      <c r="C17" s="34" t="n">
+        <v>12</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="F17" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G17" s="49" t="n">
-        <v>10</v>
-      </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="37" t="n">
+        <v>222</v>
+      </c>
+      <c r="F17" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K17" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M17" s="14"/>
       <c r="N17" s="8"/>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
-      <c r="R17" s="42"/>
+      <c r="R17" s="40"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37" t="n">
-        <v>16</v>
+      <c r="A18" s="34" t="n">
+        <v>17</v>
       </c>
       <c r="B18" s="24"/>
-      <c r="C18" s="37" t="n">
-        <v>12</v>
+      <c r="C18" s="34" t="n">
+        <v>13</v>
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="F18" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="G18" s="37" t="n">
+        <v>224</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="37" t="n">
+      <c r="H18" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K18" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M18" s="14"/>
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
-      <c r="R18" s="42"/>
+      <c r="R18" s="40"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="37" t="n">
-        <v>13</v>
-      </c>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="F19" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="37" t="n">
-        <v>8</v>
-      </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="8" t="s">
+      <c r="A19" s="41" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="52" t="s">
         <v>226</v>
       </c>
-      <c r="K19" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L19" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="M19" s="14"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="42"/>
+      <c r="C19" s="41" t="n">
+        <v>14</v>
+      </c>
+      <c r="D19" s="42"/>
+      <c r="E19" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F19" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="G19" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="40"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="43" t="n">
+      <c r="A20" s="41" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="42"/>
+      <c r="C20" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="D20" s="42"/>
+      <c r="E20" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="F20" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" s="41" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="52" t="s">
-        <v>227</v>
-      </c>
-      <c r="C20" s="43" t="n">
-        <v>14</v>
-      </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="F20" s="44" t="s">
-        <v>102</v>
-      </c>
-      <c r="G20" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="43" t="n">
+      <c r="H20" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K20" s="17"/>
       <c r="L20" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
+        <v>202</v>
+      </c>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="O20" s="17"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
-      <c r="R20" s="42"/>
+      <c r="R20" s="47"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="43" t="n">
+      <c r="A21" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="42" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="43" t="n">
-        <v>15</v>
-      </c>
-      <c r="D21" s="44"/>
+      <c r="C21" s="41" t="n">
+        <v>16</v>
+      </c>
+      <c r="D21" s="42" t="n">
+        <v>19</v>
+      </c>
       <c r="E21" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="F21" s="47" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" s="43" t="n">
+        <v>232</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" s="41" t="n">
         <v>18</v>
       </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>231</v>
-      </c>
+      <c r="H21" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="20"/>
       <c r="K21" s="17"/>
-      <c r="L21" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="O21" s="17"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
-      <c r="R21" s="48"/>
+      <c r="R21" s="40"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="44" t="n">
-        <v>19</v>
-      </c>
-      <c r="C22" s="43" t="n">
-        <v>16</v>
-      </c>
-      <c r="D22" s="44" t="n">
-        <v>19</v>
-      </c>
+      <c r="A22" s="41" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="41" t="n">
+        <v>17</v>
+      </c>
+      <c r="D22" s="42"/>
       <c r="E22" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="F22" s="47" t="s">
-        <v>105</v>
-      </c>
-      <c r="G22" s="43" t="n">
-        <v>18</v>
-      </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="20"/>
+      <c r="F22" s="53" t="s">
+        <v>234</v>
+      </c>
+      <c r="G22" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>235</v>
+      </c>
       <c r="K22" s="17"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
+      <c r="L22" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="O22" s="17"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
-      <c r="R22" s="42"/>
+      <c r="R22" s="40"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="43" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="D23" s="44"/>
+      <c r="A23" s="41" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="42"/>
+      <c r="C23" s="41" t="n">
+        <v>18</v>
+      </c>
+      <c r="D23" s="42"/>
       <c r="E23" s="23" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F23" s="53" t="s">
-        <v>235</v>
-      </c>
-      <c r="G23" s="43" t="n">
+        <v>237</v>
+      </c>
+      <c r="G23" s="41" t="n">
         <v>20</v>
       </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="43" t="n">
+      <c r="H23" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="K23" s="17"/>
+        <v>238</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>87</v>
+      </c>
       <c r="L23" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M23" s="17"/>
       <c r="N23" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O23" s="17"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
-      <c r="R23" s="42"/>
+      <c r="R23" s="47"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="43" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="44"/>
-      <c r="C24" s="43" t="n">
-        <v>18</v>
-      </c>
-      <c r="D24" s="44"/>
-      <c r="E24" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="F24" s="53" t="s">
-        <v>238</v>
-      </c>
-      <c r="G24" s="43" t="n">
+      <c r="A24" s="34" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>19</v>
+      </c>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="8"/>
+      <c r="K24" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="40"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="34"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="34" t="n">
         <v>20</v>
-      </c>
-      <c r="H24" s="5"/>
-      <c r="I24" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="K24" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L24" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="O24" s="17"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="48"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="37" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="C25" s="37" t="n">
-        <v>19</v>
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="F25" s="24"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="F25" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="G25" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="8"/>
-      <c r="I25" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="8"/>
-      <c r="K25" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="O25" s="14"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
-      <c r="R25" s="42"/>
+      <c r="R25" s="40"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="37"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="24"/>
-      <c r="C26" s="37" t="n">
-        <v>20</v>
+      <c r="C26" s="34" t="n">
+        <v>21</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="F26" s="24"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="37" t="n">
+        <v>240</v>
+      </c>
+      <c r="F26" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" s="34" t="n">
+        <v>23</v>
+      </c>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="K26" s="8"/>
+      <c r="K26" s="14" t="s">
+        <v>231</v>
+      </c>
       <c r="L26" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M26" s="14"/>
-      <c r="N26" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="O26" s="14"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
-      <c r="R26" s="42"/>
+      <c r="R26" s="40"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="37"/>
+      <c r="A27" s="34" t="n">
+        <v>24</v>
+      </c>
       <c r="B27" s="24"/>
-      <c r="C27" s="37" t="n">
-        <v>21</v>
+      <c r="C27" s="34" t="n">
+        <v>22</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="F27" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G27" s="37" t="n">
+        <v>243</v>
+      </c>
+      <c r="F27" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" s="34" t="n">
         <v>23</v>
       </c>
-      <c r="H27" s="8"/>
-      <c r="I27" s="37" t="n">
+      <c r="H27" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>232</v>
+        <v>87</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M27" s="14"/>
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
-      <c r="R27" s="42"/>
+      <c r="R27" s="40"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="37" t="n">
-        <v>24</v>
+      <c r="A28" s="34" t="n">
+        <v>25</v>
       </c>
       <c r="B28" s="24"/>
-      <c r="C28" s="37" t="n">
-        <v>22</v>
+      <c r="C28" s="34" t="n">
+        <v>23</v>
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="F28" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="G28" s="37" t="n">
+        <v>245</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="G28" s="34" t="n">
         <v>23</v>
       </c>
-      <c r="H28" s="8"/>
-      <c r="I28" s="37" t="n">
+      <c r="H28" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K28" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M28" s="14"/>
       <c r="N28" s="8"/>
       <c r="O28" s="8"/>
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
-      <c r="R28" s="42"/>
+      <c r="R28" s="40"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="37" t="n">
-        <v>25</v>
+      <c r="A29" s="34" t="n">
+        <v>26</v>
       </c>
       <c r="B29" s="24"/>
-      <c r="C29" s="37" t="n">
-        <v>23</v>
+      <c r="C29" s="34" t="n">
+        <v>24</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="F29" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="G29" s="37" t="n">
+        <v>247</v>
+      </c>
+      <c r="F29" s="54" t="s">
+        <v>112</v>
+      </c>
+      <c r="G29" s="48" t="n">
         <v>23</v>
       </c>
-      <c r="H29" s="8"/>
-      <c r="I29" s="37" t="n">
+      <c r="H29" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K29" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L29" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="M29" s="14"/>
+        <v>202</v>
+      </c>
+      <c r="M29" s="14" t="s">
+        <v>202</v>
+      </c>
       <c r="N29" s="8"/>
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="8"/>
-      <c r="R29" s="42"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="37" t="n">
-        <v>26</v>
-      </c>
+      <c r="A30" s="34"/>
       <c r="B30" s="24"/>
-      <c r="C30" s="37" t="n">
-        <v>24</v>
+      <c r="C30" s="34" t="n">
+        <v>25</v>
       </c>
       <c r="D30" s="24"/>
       <c r="E30" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="F30" s="54" t="s">
-        <v>112</v>
-      </c>
-      <c r="G30" s="49" t="n">
+        <v>247</v>
+      </c>
+      <c r="F30" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="G30" s="34" t="n">
         <v>23</v>
       </c>
-      <c r="H30" s="10"/>
-      <c r="I30" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>249</v>
-      </c>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="8"/>
       <c r="K30" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L30" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="M30" s="14" t="s">
-        <v>203</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
       <c r="N30" s="8"/>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
+      <c r="R30" s="40"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="37"/>
+      <c r="A31" s="34" t="n">
+        <v>27</v>
+      </c>
       <c r="B31" s="24"/>
-      <c r="C31" s="37" t="n">
-        <v>25</v>
+      <c r="C31" s="34" t="n">
+        <v>26</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="F31" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="G31" s="37" t="n">
+        <v>249</v>
+      </c>
+      <c r="F31" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="G31" s="34" t="n">
         <v>23</v>
       </c>
-      <c r="H31" s="8"/>
-      <c r="I31" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="8"/>
+      <c r="H31" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>250</v>
+      </c>
       <c r="K31" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="L31" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>202</v>
+      </c>
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
       <c r="O31" s="8"/>
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
-      <c r="R31" s="42"/>
+      <c r="R31" s="40"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="37" t="n">
+      <c r="A32" s="34" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="24"/>
+      <c r="C32" s="34" t="n">
         <v>27</v>
-      </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="37" t="n">
-        <v>26</v>
       </c>
       <c r="D32" s="24"/>
       <c r="E32" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="F32" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="G32" s="37" t="n">
+        <v>251</v>
+      </c>
+      <c r="F32" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="G32" s="34" t="n">
         <v>23</v>
       </c>
-      <c r="H32" s="8"/>
-      <c r="I32" s="37" t="n">
+      <c r="H32" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K32" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L32" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M32" s="8"/>
       <c r="N32" s="8"/>
       <c r="O32" s="8"/>
       <c r="P32" s="8"/>
       <c r="Q32" s="8"/>
-      <c r="R32" s="42"/>
+      <c r="R32" s="40"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="37" t="n">
+      <c r="A33" s="41" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" s="41" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="37" t="n">
-        <v>27</v>
-      </c>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="F33" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="G33" s="37" t="n">
-        <v>23</v>
-      </c>
-      <c r="H33" s="8"/>
-      <c r="I33" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="8" t="s">
+      <c r="D33" s="42"/>
+      <c r="E33" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="K33" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L33" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="42"/>
+      <c r="F33" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="G33" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L33" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="40"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="43" t="n">
+      <c r="A34" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="42"/>
+      <c r="C34" s="41" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="44" t="n">
-        <v>6</v>
-      </c>
-      <c r="C34" s="43" t="n">
-        <v>28</v>
-      </c>
-      <c r="D34" s="44"/>
+      <c r="D34" s="42"/>
       <c r="E34" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="F34" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="G34" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="6"/>
-      <c r="I34" s="43" t="n">
+        <v>255</v>
+      </c>
+      <c r="F34" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="G34" s="45" t="n">
+        <v>29</v>
+      </c>
+      <c r="H34" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K34" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L34" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
-      <c r="R34" s="42"/>
+      <c r="R34" s="47"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="43" t="n">
+      <c r="A35" s="34" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C35" s="34"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="56" t="s">
+        <v>257</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G35" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="34"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
+      <c r="P35" s="8"/>
+      <c r="Q35" s="8"/>
+      <c r="R35" s="40"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="24"/>
+      <c r="C36" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="B35" s="44"/>
-      <c r="C35" s="43" t="n">
-        <v>29</v>
-      </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="F35" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="G35" s="46" t="n">
-        <v>29</v>
-      </c>
-      <c r="H35" s="6"/>
-      <c r="I35" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="K35" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L35" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
-      <c r="R35" s="48"/>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="37" t="n">
+      <c r="D36" s="24"/>
+      <c r="E36" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="F36" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="G36" s="34" t="n">
         <v>31</v>
       </c>
-      <c r="B36" s="24" t="n">
-        <v>23</v>
-      </c>
-      <c r="C36" s="37"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="56" t="s">
-        <v>258</v>
-      </c>
-      <c r="F36" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G36" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="10"/>
-      <c r="I36" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
+      <c r="H36" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>202</v>
+      </c>
       <c r="M36" s="8"/>
       <c r="N36" s="8"/>
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
-      <c r="R36" s="42"/>
+      <c r="R36" s="40"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="37" t="n">
-        <v>32</v>
-      </c>
+      <c r="A37" s="34"/>
       <c r="B37" s="24"/>
-      <c r="C37" s="37" t="n">
-        <v>30</v>
+      <c r="C37" s="34" t="n">
+        <v>31</v>
       </c>
       <c r="D37" s="24"/>
-      <c r="E37" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="F37" s="41" t="s">
-        <v>118</v>
-      </c>
-      <c r="G37" s="37" t="n">
+      <c r="E37" s="56" t="s">
+        <v>257</v>
+      </c>
+      <c r="F37" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="G37" s="34" t="n">
         <v>31</v>
       </c>
-      <c r="H37" s="8"/>
-      <c r="I37" s="37" t="n">
+      <c r="H37" s="34"/>
+      <c r="I37" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="8" t="s">
@@ -6637,292 +6691,292 @@
         <v>87</v>
       </c>
       <c r="L37" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M37" s="8"/>
       <c r="N37" s="8"/>
       <c r="O37" s="8"/>
       <c r="P37" s="8"/>
       <c r="Q37" s="8"/>
-      <c r="R37" s="42"/>
+      <c r="R37" s="47"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="37"/>
+      <c r="A38" s="34" t="n">
+        <v>33</v>
+      </c>
       <c r="B38" s="24"/>
-      <c r="C38" s="37" t="n">
+      <c r="C38" s="34" t="n">
+        <v>32</v>
+      </c>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="F38" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="G38" s="34" t="n">
         <v>31</v>
       </c>
-      <c r="D38" s="24"/>
-      <c r="E38" s="56" t="s">
-        <v>258</v>
-      </c>
-      <c r="F38" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G38" s="37" t="n">
-        <v>31</v>
-      </c>
-      <c r="H38" s="8"/>
-      <c r="I38" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>261</v>
-      </c>
+      <c r="H38" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="8"/>
       <c r="K38" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="L38" s="14" t="s">
-        <v>203</v>
-      </c>
+      <c r="L38" s="8"/>
       <c r="M38" s="8"/>
       <c r="N38" s="8"/>
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
       <c r="Q38" s="8"/>
-      <c r="R38" s="48"/>
+      <c r="R38" s="40"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="37" t="n">
+      <c r="A39" s="41" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="42" t="n">
+        <v>23</v>
+      </c>
+      <c r="C39" s="41" t="n">
         <v>33</v>
       </c>
-      <c r="B39" s="24"/>
-      <c r="C39" s="37" t="n">
-        <v>32</v>
-      </c>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24" t="s">
+      <c r="D39" s="42"/>
+      <c r="E39" s="23" t="s">
         <v>262</v>
       </c>
-      <c r="F39" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="G39" s="37" t="n">
-        <v>31</v>
-      </c>
-      <c r="H39" s="8"/>
-      <c r="I39" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="8"/>
-      <c r="K39" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="8"/>
-      <c r="P39" s="8"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="42"/>
+      <c r="F39" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="G39" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L39" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="M39" s="5"/>
+      <c r="N39" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="O39" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="40"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="43" t="n">
+      <c r="A40" s="41"/>
+      <c r="B40" s="42"/>
+      <c r="C40" s="41" t="n">
         <v>34</v>
       </c>
-      <c r="B40" s="44" t="n">
-        <v>23</v>
-      </c>
-      <c r="C40" s="43" t="n">
-        <v>33</v>
-      </c>
-      <c r="D40" s="44"/>
+      <c r="D40" s="42"/>
       <c r="E40" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="F40" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="G40" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" s="5"/>
-      <c r="I40" s="43" t="n">
+        <v>262</v>
+      </c>
+      <c r="F40" s="42"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="41"/>
+      <c r="I40" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="K40" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="K40" s="5"/>
       <c r="L40" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="O40" s="17" t="s">
-        <v>232</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="O40" s="17"/>
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
-      <c r="R40" s="42"/>
+      <c r="R40" s="40"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="43"/>
-      <c r="B41" s="44"/>
-      <c r="C41" s="43" t="n">
+      <c r="A41" s="41"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="41" t="n">
+        <v>35</v>
+      </c>
+      <c r="D41" s="42"/>
+      <c r="E41" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="F41" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="G41" s="41" t="n">
         <v>34</v>
       </c>
-      <c r="D41" s="44"/>
-      <c r="E41" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="F41" s="44"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="43" t="n">
+      <c r="H41" s="41"/>
+      <c r="I41" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J41" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="K41" s="5"/>
+      <c r="K41" s="17" t="s">
+        <v>231</v>
+      </c>
       <c r="L41" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M41" s="5"/>
-      <c r="N41" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="O41" s="17"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
       <c r="P41" s="5"/>
       <c r="Q41" s="5"/>
-      <c r="R41" s="42"/>
+      <c r="R41" s="47"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="43"/>
-      <c r="B42" s="44"/>
-      <c r="C42" s="43" t="n">
+      <c r="A42" s="34" t="n">
         <v>35</v>
       </c>
-      <c r="D42" s="44"/>
-      <c r="E42" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="F42" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="G42" s="43" t="n">
-        <v>34</v>
-      </c>
-      <c r="H42" s="5"/>
-      <c r="I42" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="5" t="s">
+      <c r="B42" s="24"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24" t="s">
         <v>266</v>
       </c>
-      <c r="K42" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="L42" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="48"/>
+      <c r="F42" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="G42" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" s="34"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
+      <c r="P42" s="8"/>
+      <c r="Q42" s="8"/>
+      <c r="R42" s="40"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="37" t="n">
-        <v>35</v>
+      <c r="A43" s="34" t="n">
+        <v>36</v>
       </c>
       <c r="B43" s="24"/>
-      <c r="C43" s="37"/>
+      <c r="C43" s="34" t="n">
+        <v>36</v>
+      </c>
       <c r="D43" s="24"/>
       <c r="E43" s="24" t="s">
         <v>267</v>
       </c>
-      <c r="F43" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="G43" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" s="8"/>
-      <c r="I43" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
+      <c r="F43" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="G43" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="H43" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L43" s="14" t="s">
+        <v>202</v>
+      </c>
       <c r="M43" s="8"/>
-      <c r="N43" s="8"/>
+      <c r="N43" s="14" t="s">
+        <v>231</v>
+      </c>
       <c r="O43" s="8"/>
       <c r="P43" s="8"/>
       <c r="Q43" s="8"/>
-      <c r="R43" s="42"/>
+      <c r="R43" s="47"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="37" t="n">
-        <v>36</v>
+      <c r="A44" s="34" t="n">
+        <v>37</v>
       </c>
       <c r="B44" s="24"/>
-      <c r="C44" s="37" t="n">
-        <v>36</v>
+      <c r="C44" s="34" t="n">
+        <v>37</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="F44" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="G44" s="37" t="n">
+        <v>267</v>
+      </c>
+      <c r="F44" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="G44" s="34" t="n">
         <v>35</v>
       </c>
-      <c r="H44" s="8"/>
-      <c r="I44" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>269</v>
-      </c>
+      <c r="H44" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="8"/>
       <c r="K44" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="L44" s="14" t="s">
-        <v>203</v>
-      </c>
+      <c r="L44" s="8"/>
       <c r="M44" s="8"/>
-      <c r="N44" s="14" t="s">
-        <v>232</v>
-      </c>
+      <c r="N44" s="8"/>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
       <c r="Q44" s="8"/>
-      <c r="R44" s="48"/>
+      <c r="R44" s="47"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="37" t="n">
-        <v>37</v>
-      </c>
+      <c r="A45" s="34"/>
       <c r="B45" s="24"/>
-      <c r="C45" s="37" t="n">
-        <v>37</v>
+      <c r="C45" s="34" t="n">
+        <v>38</v>
       </c>
       <c r="D45" s="24"/>
       <c r="E45" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="F45" s="41" t="s">
-        <v>124</v>
-      </c>
-      <c r="G45" s="37" t="n">
-        <v>35</v>
-      </c>
-      <c r="H45" s="8"/>
-      <c r="I45" s="37" t="n">
+        <v>269</v>
+      </c>
+      <c r="F45" s="39"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J45" s="8"/>
       <c r="K45" s="14" t="s">
-        <v>87</v>
+        <v>231</v>
       </c>
       <c r="L45" s="8"/>
       <c r="M45" s="8"/>
@@ -6930,27 +6984,27 @@
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
       <c r="Q45" s="8"/>
-      <c r="R45" s="48"/>
+      <c r="R45" s="47"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="37"/>
+      <c r="A46" s="34"/>
       <c r="B46" s="24"/>
-      <c r="C46" s="37" t="n">
-        <v>38</v>
+      <c r="C46" s="34" t="n">
+        <v>39</v>
       </c>
       <c r="D46" s="24"/>
       <c r="E46" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="F46" s="41"/>
-      <c r="G46" s="37"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="37" t="n">
+        <v>269</v>
+      </c>
+      <c r="F46" s="39"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J46" s="8"/>
       <c r="K46" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L46" s="8"/>
       <c r="M46" s="8"/>
@@ -6958,27 +7012,27 @@
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
       <c r="Q46" s="8"/>
-      <c r="R46" s="48"/>
+      <c r="R46" s="47"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="37"/>
+      <c r="A47" s="34"/>
       <c r="B47" s="24"/>
-      <c r="C47" s="37" t="n">
-        <v>39</v>
+      <c r="C47" s="34" t="n">
+        <v>40</v>
       </c>
       <c r="D47" s="24"/>
       <c r="E47" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="F47" s="41"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="37" t="n">
+        <v>269</v>
+      </c>
+      <c r="F47" s="39"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J47" s="8"/>
       <c r="K47" s="14" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="L47" s="8"/>
       <c r="M47" s="8"/>
@@ -6986,164 +7040,178 @@
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
       <c r="Q47" s="8"/>
-      <c r="R47" s="48"/>
+      <c r="R47" s="40"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="37"/>
+      <c r="A48" s="34" t="n">
+        <v>38</v>
+      </c>
       <c r="B48" s="24"/>
-      <c r="C48" s="37" t="n">
-        <v>40</v>
+      <c r="C48" s="34" t="n">
+        <v>41</v>
       </c>
       <c r="D48" s="24"/>
       <c r="E48" s="24" t="s">
         <v>270</v>
       </c>
-      <c r="F48" s="41"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="8"/>
+      <c r="F48" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="G48" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="H48" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>271</v>
+      </c>
       <c r="K48" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="L48" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="L48" s="14" t="s">
+        <v>202</v>
+      </c>
       <c r="M48" s="8"/>
-      <c r="N48" s="8"/>
+      <c r="N48" s="14" t="s">
+        <v>231</v>
+      </c>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
       <c r="Q48" s="8"/>
-      <c r="R48" s="42"/>
+      <c r="R48" s="47"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="37" t="n">
-        <v>38</v>
-      </c>
-      <c r="B49" s="24"/>
-      <c r="C49" s="37" t="n">
-        <v>41</v>
-      </c>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="F49" s="41" t="s">
-        <v>125</v>
-      </c>
-      <c r="G49" s="37" t="n">
-        <v>35</v>
-      </c>
-      <c r="H49" s="8"/>
-      <c r="I49" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="8" t="s">
+      <c r="A49" s="41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B49" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" s="41"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="23" t="s">
         <v>272</v>
       </c>
-      <c r="K49" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L49" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="M49" s="8"/>
-      <c r="N49" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="O49" s="8"/>
-      <c r="P49" s="8"/>
-      <c r="Q49" s="8"/>
-      <c r="R49" s="48"/>
+      <c r="F49" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="G49" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" s="41"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
+      <c r="R49" s="40"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="43" t="n">
-        <v>39</v>
-      </c>
-      <c r="B50" s="44" t="n">
-        <v>8</v>
-      </c>
-      <c r="C50" s="43"/>
-      <c r="D50" s="44"/>
+      <c r="A50" s="41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B50" s="42"/>
+      <c r="C50" s="41" t="n">
+        <v>42</v>
+      </c>
+      <c r="D50" s="42"/>
       <c r="E50" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="F50" s="44" t="s">
-        <v>126</v>
-      </c>
-      <c r="G50" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="H50" s="5"/>
-      <c r="I50" s="43" t="n">
+      <c r="F50" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G50" s="41" t="n">
+        <v>39</v>
+      </c>
+      <c r="H50" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
+      <c r="L50" s="17" t="s">
+        <v>202</v>
+      </c>
       <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
+      <c r="N50" s="17" t="s">
+        <v>231</v>
+      </c>
       <c r="O50" s="5"/>
       <c r="P50" s="5"/>
       <c r="Q50" s="5"/>
-      <c r="R50" s="42"/>
+      <c r="R50" s="47"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B51" s="44"/>
-      <c r="C51" s="43" t="n">
-        <v>42</v>
-      </c>
-      <c r="D51" s="44"/>
+      <c r="A51" s="41" t="n">
+        <v>41</v>
+      </c>
+      <c r="B51" s="42"/>
+      <c r="C51" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="D51" s="42"/>
       <c r="E51" s="23" t="s">
         <v>274</v>
       </c>
-      <c r="F51" s="47" t="s">
-        <v>127</v>
-      </c>
-      <c r="G51" s="43" t="n">
+      <c r="F51" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="G51" s="41" t="n">
         <v>39</v>
       </c>
-      <c r="H51" s="5"/>
-      <c r="I51" s="43" t="n">
+      <c r="H51" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
-      <c r="L51" s="17" t="s">
-        <v>203</v>
-      </c>
+      <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O51" s="5"/>
       <c r="P51" s="5"/>
       <c r="Q51" s="5"/>
-      <c r="R51" s="48"/>
+      <c r="R51" s="47"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="43" t="n">
-        <v>41</v>
-      </c>
-      <c r="B52" s="44"/>
-      <c r="C52" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="D52" s="44"/>
+      <c r="A52" s="41" t="n">
+        <v>42</v>
+      </c>
+      <c r="B52" s="42"/>
+      <c r="C52" s="41" t="n">
+        <v>44</v>
+      </c>
+      <c r="D52" s="42"/>
       <c r="E52" s="23" t="s">
         <v>275</v>
       </c>
-      <c r="F52" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="G52" s="43" t="n">
+      <c r="F52" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="G52" s="41" t="n">
         <v>39</v>
       </c>
-      <c r="H52" s="5"/>
-      <c r="I52" s="43" t="n">
+      <c r="H52" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I52" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J52" s="5"/>
@@ -7151,165 +7219,177 @@
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O52" s="5"/>
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
-      <c r="R52" s="48"/>
+      <c r="R52" s="47"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B53" s="44"/>
-      <c r="C53" s="43" t="n">
+      <c r="A53" s="28"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="28"/>
+      <c r="R53" s="47"/>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="28" t="n">
+        <v>43</v>
+      </c>
+      <c r="B54" s="29"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="29" t="n">
+        <v>43</v>
+      </c>
+      <c r="F54" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="G54" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I54" s="28"/>
+      <c r="R54" s="47"/>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="34" t="n">
         <v>44</v>
       </c>
-      <c r="D53" s="44"/>
-      <c r="E53" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="F53" s="47" t="s">
-        <v>129</v>
-      </c>
-      <c r="G53" s="43" t="n">
-        <v>39</v>
-      </c>
-      <c r="H53" s="5"/>
-      <c r="I53" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
-      <c r="M53" s="5"/>
-      <c r="N53" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="O53" s="5"/>
-      <c r="P53" s="5"/>
-      <c r="Q53" s="5"/>
-      <c r="R53" s="48"/>
-    </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="31"/>
-      <c r="B54" s="32"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="32"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="31"/>
-      <c r="I54" s="31"/>
-      <c r="R54" s="48"/>
-    </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="31" t="n">
+      <c r="B55" s="24"/>
+      <c r="C55" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="G55" s="48" t="n">
         <v>43</v>
       </c>
-      <c r="B55" s="32"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32" t="n">
-        <v>42</v>
-      </c>
-      <c r="F55" s="34" t="s">
-        <v>277</v>
-      </c>
-      <c r="G55" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" s="31"/>
-      <c r="R55" s="48"/>
+      <c r="H55" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="8"/>
+      <c r="K55" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
+      <c r="N55" s="8"/>
+      <c r="O55" s="8"/>
+      <c r="P55" s="8"/>
+      <c r="Q55" s="8"/>
+      <c r="R55" s="47"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="37" t="n">
-        <v>44</v>
-      </c>
-      <c r="B56" s="24"/>
-      <c r="C56" s="37" t="n">
+      <c r="A56" s="41" t="n">
         <v>45</v>
       </c>
-      <c r="D56" s="24"/>
-      <c r="E56" s="24" t="s">
+      <c r="B56" s="42"/>
+      <c r="C56" s="41" t="n">
+        <v>46</v>
+      </c>
+      <c r="D56" s="42"/>
+      <c r="E56" s="23" t="s">
         <v>278</v>
       </c>
-      <c r="F56" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="G56" s="49" t="n">
+      <c r="F56" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="G56" s="41" t="n">
         <v>43</v>
       </c>
-      <c r="H56" s="21"/>
-      <c r="I56" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="8"/>
-      <c r="K56" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L56" s="8"/>
-      <c r="M56" s="8"/>
-      <c r="N56" s="8"/>
-      <c r="O56" s="8"/>
-      <c r="P56" s="8"/>
-      <c r="Q56" s="8"/>
-      <c r="R56" s="48"/>
+      <c r="H56" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="5"/>
+      <c r="K56" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="5"/>
+      <c r="R56" s="47"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="43" t="n">
-        <v>45</v>
-      </c>
-      <c r="B57" s="44"/>
-      <c r="C57" s="43" t="n">
+      <c r="A57" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="D57" s="44"/>
-      <c r="E57" s="23" t="s">
+      <c r="B57" s="24"/>
+      <c r="C57" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24" t="s">
         <v>279</v>
       </c>
-      <c r="F57" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="G57" s="43" t="n">
+      <c r="F57" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="G57" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H57" s="23"/>
-      <c r="I57" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="5"/>
-      <c r="K57" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L57" s="5"/>
-      <c r="M57" s="5"/>
-      <c r="N57" s="5"/>
-      <c r="O57" s="5"/>
-      <c r="P57" s="5"/>
-      <c r="Q57" s="5"/>
-      <c r="R57" s="48"/>
+      <c r="H57" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="8"/>
+      <c r="K57" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L57" s="8"/>
+      <c r="M57" s="8"/>
+      <c r="N57" s="8"/>
+      <c r="O57" s="8"/>
+      <c r="P57" s="8"/>
+      <c r="Q57" s="8"/>
+      <c r="R57" s="47"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="37" t="n">
-        <v>46</v>
+      <c r="A58" s="34" t="n">
+        <v>47</v>
       </c>
       <c r="B58" s="24"/>
-      <c r="C58" s="37" t="n">
-        <v>47</v>
+      <c r="C58" s="34" t="n">
+        <v>48</v>
       </c>
       <c r="D58" s="24"/>
       <c r="E58" s="24" t="s">
         <v>280</v>
       </c>
-      <c r="F58" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="G58" s="37" t="n">
-        <v>43</v>
-      </c>
-      <c r="H58" s="8"/>
-      <c r="I58" s="37" t="n">
+      <c r="F58" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G58" s="34" t="n">
+        <v>46</v>
+      </c>
+      <c r="H58" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J58" s="8"/>
@@ -7322,28 +7402,32 @@
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
       <c r="Q58" s="8"/>
-      <c r="R58" s="48"/>
+      <c r="R58" s="47"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="37" t="n">
+      <c r="A59" s="34" t="n">
+        <v>48</v>
+      </c>
+      <c r="B59" s="24" t="n">
         <v>47</v>
       </c>
-      <c r="B59" s="24"/>
-      <c r="C59" s="37" t="n">
-        <v>48</v>
+      <c r="C59" s="34" t="n">
+        <v>49</v>
       </c>
       <c r="D59" s="24"/>
       <c r="E59" s="24" t="s">
         <v>281</v>
       </c>
-      <c r="F59" s="41" t="s">
-        <v>133</v>
-      </c>
-      <c r="G59" s="37" t="n">
+      <c r="F59" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="G59" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="H59" s="8"/>
-      <c r="I59" s="37" t="n">
+      <c r="H59" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J59" s="8"/>
@@ -7356,30 +7440,30 @@
       <c r="O59" s="8"/>
       <c r="P59" s="8"/>
       <c r="Q59" s="8"/>
-      <c r="R59" s="48"/>
+      <c r="R59" s="47"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="37" t="n">
-        <v>48</v>
-      </c>
-      <c r="B60" s="24" t="n">
-        <v>47</v>
-      </c>
-      <c r="C60" s="37" t="n">
+      <c r="A60" s="34" t="n">
         <v>49</v>
+      </c>
+      <c r="B60" s="24"/>
+      <c r="C60" s="34" t="n">
+        <v>50</v>
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="F60" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="G60" s="37" t="n">
+      <c r="F60" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="G60" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="H60" s="8"/>
-      <c r="I60" s="37" t="n">
+      <c r="H60" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I60" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J60" s="8"/>
@@ -7392,28 +7476,30 @@
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
-      <c r="R60" s="48"/>
+      <c r="R60" s="47"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="37" t="n">
-        <v>49</v>
+      <c r="A61" s="34" t="n">
+        <v>50</v>
       </c>
       <c r="B61" s="24"/>
-      <c r="C61" s="37" t="n">
-        <v>50</v>
+      <c r="C61" s="34" t="n">
+        <v>51</v>
       </c>
       <c r="D61" s="24"/>
       <c r="E61" s="24" t="s">
         <v>283</v>
       </c>
-      <c r="F61" s="41" t="s">
-        <v>135</v>
-      </c>
-      <c r="G61" s="37" t="n">
+      <c r="F61" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="G61" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="H61" s="8"/>
-      <c r="I61" s="37" t="n">
+      <c r="H61" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J61" s="8"/>
@@ -7426,28 +7512,32 @@
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
       <c r="Q61" s="8"/>
-      <c r="R61" s="48"/>
+      <c r="R61" s="47"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="37" t="n">
-        <v>50</v>
-      </c>
-      <c r="B62" s="24"/>
-      <c r="C62" s="37" t="n">
+      <c r="A62" s="34" t="n">
         <v>51</v>
+      </c>
+      <c r="B62" s="24" t="n">
+        <v>49</v>
+      </c>
+      <c r="C62" s="34" t="n">
+        <v>52</v>
       </c>
       <c r="D62" s="24"/>
       <c r="E62" s="24" t="s">
         <v>284</v>
       </c>
-      <c r="F62" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="G62" s="37" t="n">
+      <c r="F62" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="G62" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="H62" s="8"/>
-      <c r="I62" s="37" t="n">
+      <c r="H62" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I62" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J62" s="8"/>
@@ -7456,34 +7546,36 @@
       </c>
       <c r="L62" s="8"/>
       <c r="M62" s="8"/>
-      <c r="N62" s="8"/>
+      <c r="N62" s="14" t="s">
+        <v>231</v>
+      </c>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
       <c r="Q62" s="8"/>
-      <c r="R62" s="48"/>
+      <c r="R62" s="47"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="37" t="n">
-        <v>51</v>
-      </c>
-      <c r="B63" s="24" t="n">
-        <v>49</v>
-      </c>
-      <c r="C63" s="37" t="n">
+      <c r="A63" s="34" t="n">
         <v>52</v>
+      </c>
+      <c r="B63" s="24"/>
+      <c r="C63" s="34" t="n">
+        <v>53</v>
       </c>
       <c r="D63" s="24"/>
       <c r="E63" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="F63" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="G63" s="37" t="n">
-        <v>46</v>
-      </c>
-      <c r="H63" s="8"/>
-      <c r="I63" s="37" t="n">
+      <c r="F63" s="51" t="s">
+        <v>286</v>
+      </c>
+      <c r="G63" s="34" t="n">
+        <v>51</v>
+      </c>
+      <c r="H63" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I63" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J63" s="8"/>
@@ -7492,34 +7584,34 @@
       </c>
       <c r="L63" s="8"/>
       <c r="M63" s="8"/>
-      <c r="N63" s="14" t="s">
-        <v>232</v>
-      </c>
+      <c r="N63" s="8"/>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
       <c r="Q63" s="8"/>
-      <c r="R63" s="48"/>
+      <c r="R63" s="47"/>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="37" t="n">
-        <v>52</v>
+      <c r="A64" s="34" t="n">
+        <v>53</v>
       </c>
       <c r="B64" s="24"/>
-      <c r="C64" s="37" t="n">
-        <v>53</v>
+      <c r="C64" s="34" t="n">
+        <v>54</v>
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F64" s="51" t="s">
-        <v>287</v>
-      </c>
-      <c r="G64" s="37" t="n">
+        <v>160</v>
+      </c>
+      <c r="G64" s="34" t="n">
         <v>51</v>
       </c>
-      <c r="H64" s="8"/>
-      <c r="I64" s="37" t="n">
+      <c r="H64" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J64" s="8"/>
@@ -7532,680 +7624,710 @@
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
       <c r="Q64" s="8"/>
-      <c r="R64" s="48"/>
+      <c r="R64" s="40"/>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="37" t="n">
-        <v>53</v>
+      <c r="A65" s="34" t="n">
+        <v>54</v>
       </c>
       <c r="B65" s="24"/>
-      <c r="C65" s="37" t="n">
-        <v>54</v>
+      <c r="C65" s="34" t="n">
+        <v>55</v>
       </c>
       <c r="D65" s="24"/>
       <c r="E65" s="24" t="s">
         <v>288</v>
       </c>
-      <c r="F65" s="51" t="s">
-        <v>160</v>
-      </c>
-      <c r="G65" s="37" t="n">
-        <v>51</v>
-      </c>
-      <c r="H65" s="8"/>
-      <c r="I65" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="8"/>
+      <c r="F65" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="G65" s="34" t="n">
+        <v>46</v>
+      </c>
+      <c r="H65" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I65" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>289</v>
+      </c>
       <c r="K65" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="L65" s="8"/>
+      <c r="L65" s="14" t="s">
+        <v>202</v>
+      </c>
       <c r="M65" s="8"/>
       <c r="N65" s="8"/>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
       <c r="Q65" s="8"/>
-      <c r="R65" s="42"/>
+      <c r="R65" s="40"/>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="37" t="n">
-        <v>54</v>
+      <c r="A66" s="34" t="n">
+        <v>55</v>
       </c>
       <c r="B66" s="24"/>
-      <c r="C66" s="37" t="n">
-        <v>55</v>
+      <c r="C66" s="34" t="n">
+        <v>56</v>
       </c>
       <c r="D66" s="24"/>
       <c r="E66" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="F66" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="G66" s="37" t="n">
+        <v>290</v>
+      </c>
+      <c r="F66" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="G66" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="H66" s="8"/>
-      <c r="I66" s="37" t="n">
+      <c r="H66" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K66" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L66" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M66" s="8"/>
       <c r="N66" s="8"/>
       <c r="O66" s="8"/>
       <c r="P66" s="8"/>
       <c r="Q66" s="8"/>
-      <c r="R66" s="42"/>
+      <c r="R66" s="40"/>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="37" t="n">
-        <v>55</v>
-      </c>
-      <c r="B67" s="24"/>
-      <c r="C67" s="37" t="n">
+      <c r="A67" s="41" t="n">
         <v>56</v>
       </c>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="F67" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="G67" s="37" t="n">
-        <v>46</v>
-      </c>
-      <c r="H67" s="8"/>
-      <c r="I67" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="8" t="s">
+      <c r="B67" s="42"/>
+      <c r="C67" s="41" t="n">
+        <v>57</v>
+      </c>
+      <c r="D67" s="42"/>
+      <c r="E67" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="K67" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L67" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="M67" s="8"/>
-      <c r="N67" s="8"/>
-      <c r="O67" s="8"/>
-      <c r="P67" s="8"/>
-      <c r="Q67" s="8"/>
-      <c r="R67" s="42"/>
+      <c r="F67" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="G67" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="H67" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="K67" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L67" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+      <c r="Q67" s="5"/>
+      <c r="R67" s="47"/>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="43" t="n">
-        <v>56</v>
-      </c>
-      <c r="B68" s="44"/>
-      <c r="C68" s="43" t="n">
+      <c r="A68" s="34" t="n">
         <v>57</v>
       </c>
-      <c r="D68" s="44"/>
-      <c r="E68" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="F68" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="G68" s="43" t="n">
+      <c r="B68" s="24"/>
+      <c r="C68" s="34"/>
+      <c r="D68" s="24"/>
+      <c r="E68" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="F68" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G68" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H68" s="17"/>
-      <c r="I68" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="K68" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L68" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="M68" s="5"/>
-      <c r="N68" s="5"/>
-      <c r="O68" s="5"/>
-      <c r="P68" s="5"/>
-      <c r="Q68" s="5"/>
-      <c r="R68" s="48"/>
+      <c r="H68" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" s="34"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="14"/>
+      <c r="L68" s="8"/>
+      <c r="M68" s="8"/>
+      <c r="N68" s="8"/>
+      <c r="O68" s="8"/>
+      <c r="P68" s="8"/>
+      <c r="Q68" s="8"/>
+      <c r="R68" s="40"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="37" t="n">
-        <v>57</v>
+      <c r="A69" s="34" t="n">
+        <v>58</v>
       </c>
       <c r="B69" s="24"/>
-      <c r="C69" s="37"/>
+      <c r="C69" s="34" t="n">
+        <v>58</v>
+      </c>
       <c r="D69" s="24"/>
       <c r="E69" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="F69" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="G69" s="37" t="n">
-        <v>43</v>
-      </c>
-      <c r="H69" s="8"/>
-      <c r="I69" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="8"/>
-      <c r="K69" s="14"/>
-      <c r="L69" s="8"/>
+      <c r="F69" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="G69" s="34" t="n">
+        <v>57</v>
+      </c>
+      <c r="H69" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I69" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="K69" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L69" s="14" t="s">
+        <v>202</v>
+      </c>
       <c r="M69" s="8"/>
       <c r="N69" s="8"/>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
       <c r="Q69" s="8"/>
-      <c r="R69" s="42"/>
+      <c r="R69" s="40"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="37" t="n">
-        <v>58</v>
+      <c r="A70" s="34" t="n">
+        <v>59</v>
       </c>
       <c r="B70" s="24"/>
-      <c r="C70" s="37" t="n">
-        <v>58</v>
+      <c r="C70" s="34" t="n">
+        <v>59</v>
       </c>
       <c r="D70" s="24"/>
       <c r="E70" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="F70" s="41" t="s">
-        <v>141</v>
-      </c>
-      <c r="G70" s="37" t="n">
+        <v>297</v>
+      </c>
+      <c r="F70" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="G70" s="34" t="n">
         <v>57</v>
       </c>
-      <c r="H70" s="8"/>
-      <c r="I70" s="37" t="n">
+      <c r="H70" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I70" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K70" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L70" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M70" s="8"/>
       <c r="N70" s="8"/>
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
       <c r="Q70" s="8"/>
-      <c r="R70" s="42"/>
+      <c r="R70" s="40"/>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="37" t="n">
-        <v>59</v>
+      <c r="A71" s="34" t="n">
+        <v>60</v>
       </c>
       <c r="B71" s="24"/>
-      <c r="C71" s="37" t="n">
-        <v>59</v>
+      <c r="C71" s="34" t="n">
+        <v>60</v>
       </c>
       <c r="D71" s="24"/>
       <c r="E71" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="F71" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="G71" s="37" t="n">
+        <v>299</v>
+      </c>
+      <c r="F71" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="G71" s="34" t="n">
         <v>57</v>
       </c>
-      <c r="H71" s="8"/>
-      <c r="I71" s="37" t="n">
+      <c r="H71" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I71" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K71" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L71" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M71" s="8"/>
       <c r="N71" s="8"/>
       <c r="O71" s="8"/>
       <c r="P71" s="8"/>
       <c r="Q71" s="8"/>
-      <c r="R71" s="42"/>
+      <c r="R71" s="40"/>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="37" t="n">
-        <v>60</v>
+      <c r="A72" s="34" t="n">
+        <v>61</v>
       </c>
       <c r="B72" s="24"/>
-      <c r="C72" s="37" t="n">
-        <v>60</v>
+      <c r="C72" s="34" t="n">
+        <v>61</v>
       </c>
       <c r="D72" s="24"/>
       <c r="E72" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="F72" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="G72" s="37" t="n">
+        <v>301</v>
+      </c>
+      <c r="F72" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="G72" s="34" t="n">
         <v>57</v>
       </c>
-      <c r="H72" s="8"/>
-      <c r="I72" s="37" t="n">
+      <c r="H72" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I72" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K72" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L72" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M72" s="8"/>
       <c r="N72" s="8"/>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
       <c r="Q72" s="8"/>
-      <c r="R72" s="42"/>
+      <c r="R72" s="47"/>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="37" t="n">
-        <v>61</v>
-      </c>
+      <c r="A73" s="34"/>
       <c r="B73" s="24"/>
-      <c r="C73" s="37" t="n">
-        <v>61</v>
+      <c r="C73" s="34" t="n">
+        <v>62</v>
       </c>
       <c r="D73" s="24"/>
       <c r="E73" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="F73" s="41" t="s">
-        <v>144</v>
-      </c>
-      <c r="G73" s="37" t="n">
+        <v>294</v>
+      </c>
+      <c r="F73" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="G73" s="34" t="n">
         <v>57</v>
       </c>
-      <c r="H73" s="8"/>
-      <c r="I73" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="8" t="s">
-        <v>303</v>
-      </c>
+      <c r="H73" s="34"/>
+      <c r="I73" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="8"/>
       <c r="K73" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="L73" s="14" t="s">
-        <v>203</v>
-      </c>
+      <c r="L73" s="8"/>
       <c r="M73" s="8"/>
       <c r="N73" s="8"/>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
       <c r="Q73" s="8"/>
-      <c r="R73" s="48"/>
+      <c r="R73" s="47"/>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="37"/>
-      <c r="B74" s="24"/>
-      <c r="C74" s="37" t="n">
+      <c r="A74" s="41" t="n">
         <v>62</v>
       </c>
-      <c r="D74" s="24"/>
-      <c r="E74" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="F74" s="41" t="s">
-        <v>145</v>
-      </c>
-      <c r="G74" s="37" t="n">
-        <v>57</v>
-      </c>
-      <c r="H74" s="8"/>
-      <c r="I74" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="8"/>
-      <c r="K74" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8"/>
-      <c r="N74" s="8"/>
-      <c r="O74" s="8"/>
-      <c r="P74" s="8"/>
-      <c r="Q74" s="8"/>
-      <c r="R74" s="48"/>
+      <c r="B74" s="42"/>
+      <c r="C74" s="41"/>
+      <c r="D74" s="42"/>
+      <c r="E74" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="F74" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="G74" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="H74" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="5"/>
+      <c r="K74" s="17"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5"/>
+      <c r="Q74" s="5"/>
+      <c r="R74" s="40"/>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="43" t="n">
-        <v>62</v>
-      </c>
-      <c r="B75" s="44"/>
-      <c r="C75" s="43"/>
-      <c r="D75" s="44"/>
+      <c r="A75" s="41" t="n">
+        <v>63</v>
+      </c>
+      <c r="B75" s="42"/>
+      <c r="C75" s="41" t="n">
+        <v>63</v>
+      </c>
+      <c r="D75" s="42"/>
       <c r="E75" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="F75" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="G75" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="H75" s="5"/>
-      <c r="I75" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="5"/>
-      <c r="K75" s="17"/>
-      <c r="L75" s="5"/>
+      <c r="F75" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="G75" s="41" t="n">
+        <v>62</v>
+      </c>
+      <c r="H75" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="K75" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L75" s="17" t="s">
+        <v>202</v>
+      </c>
       <c r="M75" s="5"/>
       <c r="N75" s="5"/>
       <c r="O75" s="5"/>
       <c r="P75" s="5"/>
       <c r="Q75" s="5"/>
-      <c r="R75" s="42"/>
+      <c r="R75" s="40"/>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="43" t="n">
-        <v>63</v>
-      </c>
-      <c r="B76" s="44"/>
-      <c r="C76" s="43" t="n">
-        <v>63</v>
-      </c>
-      <c r="D76" s="44"/>
+      <c r="A76" s="41" t="n">
+        <v>64</v>
+      </c>
+      <c r="B76" s="42"/>
+      <c r="C76" s="41" t="n">
+        <v>64</v>
+      </c>
+      <c r="D76" s="42"/>
       <c r="E76" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="F76" s="47" t="s">
-        <v>103</v>
-      </c>
-      <c r="G76" s="43" t="n">
+        <v>306</v>
+      </c>
+      <c r="F76" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="G76" s="41" t="n">
         <v>62</v>
       </c>
-      <c r="H76" s="5"/>
-      <c r="I76" s="43" t="n">
+      <c r="H76" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K76" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L76" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M76" s="5"/>
       <c r="N76" s="5"/>
       <c r="O76" s="5"/>
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
-      <c r="R76" s="42"/>
+      <c r="R76" s="40"/>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="43" t="n">
-        <v>64</v>
-      </c>
-      <c r="B77" s="44"/>
-      <c r="C77" s="43" t="n">
-        <v>64</v>
-      </c>
-      <c r="D77" s="44"/>
+      <c r="A77" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="B77" s="42" t="n">
+        <v>63</v>
+      </c>
+      <c r="C77" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="D77" s="42" t="n">
+        <v>63</v>
+      </c>
       <c r="E77" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="F77" s="47" t="s">
-        <v>147</v>
-      </c>
-      <c r="G77" s="43" t="n">
+        <v>308</v>
+      </c>
+      <c r="F77" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="G77" s="41" t="n">
         <v>62</v>
       </c>
-      <c r="H77" s="5"/>
-      <c r="I77" s="43" t="n">
+      <c r="H77" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I77" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K77" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L77" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M77" s="5"/>
       <c r="N77" s="5"/>
       <c r="O77" s="5"/>
       <c r="P77" s="5"/>
       <c r="Q77" s="5"/>
-      <c r="R77" s="42"/>
+      <c r="R77" s="40"/>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="43" t="n">
+      <c r="A78" s="41" t="n">
+        <v>66</v>
+      </c>
+      <c r="B78" s="42"/>
+      <c r="C78" s="41" t="n">
+        <v>66</v>
+      </c>
+      <c r="D78" s="42"/>
+      <c r="E78" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="F78" s="53" t="s">
+        <v>234</v>
+      </c>
+      <c r="G78" s="41" t="n">
         <v>65</v>
       </c>
-      <c r="B78" s="44" t="n">
-        <v>63</v>
-      </c>
-      <c r="C78" s="43" t="n">
-        <v>65</v>
-      </c>
-      <c r="D78" s="44" t="n">
-        <v>63</v>
-      </c>
-      <c r="E78" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="F78" s="47" t="s">
-        <v>105</v>
-      </c>
-      <c r="G78" s="43" t="n">
-        <v>62</v>
-      </c>
-      <c r="H78" s="5"/>
-      <c r="I78" s="43" t="n">
+      <c r="H78" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I78" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K78" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L78" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M78" s="5"/>
       <c r="N78" s="5"/>
       <c r="O78" s="5"/>
       <c r="P78" s="5"/>
       <c r="Q78" s="5"/>
-      <c r="R78" s="42"/>
+      <c r="R78" s="40"/>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="43" t="n">
-        <v>66</v>
-      </c>
-      <c r="B79" s="44"/>
-      <c r="C79" s="43" t="n">
-        <v>66</v>
-      </c>
-      <c r="D79" s="44"/>
+      <c r="A79" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="B79" s="42"/>
+      <c r="C79" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="D79" s="42"/>
       <c r="E79" s="23" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F79" s="53" t="s">
-        <v>235</v>
-      </c>
-      <c r="G79" s="43" t="n">
+        <v>237</v>
+      </c>
+      <c r="G79" s="41" t="n">
         <v>65</v>
       </c>
-      <c r="H79" s="5"/>
-      <c r="I79" s="43" t="n">
+      <c r="H79" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K79" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L79" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M79" s="5"/>
       <c r="N79" s="5"/>
       <c r="O79" s="5"/>
       <c r="P79" s="5"/>
       <c r="Q79" s="5"/>
-      <c r="R79" s="42"/>
+      <c r="R79" s="40"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="43" t="n">
-        <v>67</v>
-      </c>
-      <c r="B80" s="44"/>
-      <c r="C80" s="43" t="n">
-        <v>67</v>
-      </c>
-      <c r="D80" s="44"/>
+      <c r="A80" s="41"/>
+      <c r="B80" s="42"/>
+      <c r="C80" s="41" t="n">
+        <v>68</v>
+      </c>
+      <c r="D80" s="42"/>
       <c r="E80" s="23" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F80" s="53" t="s">
-        <v>238</v>
-      </c>
-      <c r="G80" s="43" t="n">
+        <v>315</v>
+      </c>
+      <c r="G80" s="41" t="n">
         <v>65</v>
       </c>
-      <c r="H80" s="5"/>
-      <c r="I80" s="43" t="n">
+      <c r="H80" s="41"/>
+      <c r="I80" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="K80" s="17" t="s">
-        <v>87</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="K80" s="5"/>
       <c r="L80" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="M80" s="5"/>
+        <v>202</v>
+      </c>
+      <c r="M80" s="17" t="s">
+        <v>202</v>
+      </c>
       <c r="N80" s="5"/>
       <c r="O80" s="5"/>
       <c r="P80" s="5"/>
       <c r="Q80" s="5"/>
-      <c r="R80" s="42"/>
+      <c r="R80" s="47"/>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="43"/>
-      <c r="B81" s="44"/>
-      <c r="C81" s="43" t="n">
+      <c r="A81" s="34" t="n">
         <v>68</v>
       </c>
-      <c r="D81" s="44"/>
-      <c r="E81" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="F81" s="53" t="s">
-        <v>316</v>
-      </c>
-      <c r="G81" s="43" t="n">
-        <v>65</v>
-      </c>
-      <c r="H81" s="5"/>
-      <c r="I81" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="5" t="s">
+      <c r="B81" s="24"/>
+      <c r="C81" s="34"/>
+      <c r="D81" s="24"/>
+      <c r="E81" s="24" t="s">
         <v>317</v>
       </c>
-      <c r="K81" s="5"/>
-      <c r="L81" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="M81" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="N81" s="5"/>
-      <c r="O81" s="5"/>
-      <c r="P81" s="5"/>
-      <c r="Q81" s="5"/>
-      <c r="R81" s="48"/>
+      <c r="F81" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="G81" s="50" t="n">
+        <v>43</v>
+      </c>
+      <c r="H81" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I81" s="34"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="8"/>
+      <c r="M81" s="8"/>
+      <c r="N81" s="8"/>
+      <c r="O81" s="8"/>
+      <c r="P81" s="8"/>
+      <c r="Q81" s="8"/>
+      <c r="R81" s="47"/>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="37" t="n">
-        <v>68</v>
+      <c r="A82" s="34" t="n">
+        <v>69</v>
       </c>
       <c r="B82" s="24"/>
-      <c r="C82" s="37"/>
+      <c r="C82" s="34" t="n">
+        <v>69</v>
+      </c>
       <c r="D82" s="24"/>
       <c r="E82" s="24" t="s">
         <v>318</v>
       </c>
-      <c r="F82" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="G82" s="58" t="n">
-        <v>43</v>
-      </c>
-      <c r="H82" s="8"/>
-      <c r="I82" s="37" t="n">
+      <c r="F82" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="G82" s="34" t="n">
+        <v>68</v>
+      </c>
+      <c r="H82" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I82" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J82" s="8"/>
-      <c r="K82" s="8"/>
+      <c r="K82" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="L82" s="8"/>
       <c r="M82" s="8"/>
       <c r="N82" s="8"/>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
       <c r="Q82" s="8"/>
-      <c r="R82" s="48"/>
+      <c r="R82" s="47"/>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="37" t="n">
-        <v>69</v>
+      <c r="A83" s="34" t="n">
+        <v>70</v>
       </c>
       <c r="B83" s="24"/>
-      <c r="C83" s="37" t="n">
-        <v>69</v>
+      <c r="C83" s="34" t="n">
+        <v>70</v>
       </c>
       <c r="D83" s="24"/>
       <c r="E83" s="24" t="s">
         <v>319</v>
       </c>
-      <c r="F83" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="G83" s="37" t="n">
-        <v>68</v>
-      </c>
-      <c r="H83" s="8"/>
-      <c r="I83" s="37" t="n">
+      <c r="F83" s="51" t="s">
+        <v>320</v>
+      </c>
+      <c r="G83" s="34" t="n">
+        <v>69</v>
+      </c>
+      <c r="H83" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I83" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J83" s="8"/>
@@ -8218,101 +8340,104 @@
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
       <c r="Q83" s="8"/>
-      <c r="R83" s="48"/>
+      <c r="R83" s="40"/>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="37" t="n">
-        <v>70</v>
+      <c r="A84" s="34" t="n">
+        <v>71</v>
       </c>
       <c r="B84" s="24"/>
-      <c r="C84" s="37" t="n">
-        <v>70</v>
+      <c r="C84" s="34" t="n">
+        <v>71</v>
       </c>
       <c r="D84" s="24"/>
       <c r="E84" s="24" t="s">
-        <v>320</v>
-      </c>
-      <c r="F84" s="51" t="s">
         <v>321</v>
       </c>
-      <c r="G84" s="37" t="n">
-        <v>69</v>
-      </c>
-      <c r="H84" s="8"/>
-      <c r="I84" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="8"/>
+      <c r="F84" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="G84" s="34" t="n">
+        <v>68</v>
+      </c>
+      <c r="H84" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I84" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="8" t="s">
+        <v>322</v>
+      </c>
       <c r="K84" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="L84" s="8"/>
+      <c r="L84" s="14" t="s">
+        <v>202</v>
+      </c>
       <c r="M84" s="8"/>
       <c r="N84" s="8"/>
       <c r="O84" s="8"/>
       <c r="P84" s="8"/>
       <c r="Q84" s="8"/>
-      <c r="R84" s="42"/>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="37" t="n">
-        <v>71</v>
-      </c>
-      <c r="B85" s="24"/>
-      <c r="C85" s="37" t="n">
-        <v>71</v>
-      </c>
-      <c r="D85" s="24"/>
-      <c r="E85" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="F85" s="41" t="s">
-        <v>152</v>
-      </c>
-      <c r="G85" s="37" t="n">
-        <v>68</v>
-      </c>
-      <c r="H85" s="8"/>
-      <c r="I85" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="8" t="s">
+      <c r="A85" s="41" t="n">
+        <v>72</v>
+      </c>
+      <c r="B85" s="42"/>
+      <c r="C85" s="41"/>
+      <c r="D85" s="42"/>
+      <c r="E85" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="K85" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L85" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="M85" s="8"/>
-      <c r="N85" s="8"/>
-      <c r="O85" s="8"/>
-      <c r="P85" s="8"/>
-      <c r="Q85" s="8"/>
+      <c r="F85" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="G85" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="H85" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I85" s="41"/>
+      <c r="J85" s="5"/>
+      <c r="K85" s="5"/>
+      <c r="L85" s="5"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="5"/>
+      <c r="P85" s="5"/>
+      <c r="Q85" s="5"/>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="43" t="n">
+      <c r="A86" s="41" t="n">
+        <v>73</v>
+      </c>
+      <c r="B86" s="42"/>
+      <c r="C86" s="41" t="n">
         <v>72</v>
       </c>
-      <c r="B86" s="44"/>
-      <c r="C86" s="43"/>
-      <c r="D86" s="44"/>
+      <c r="D86" s="42"/>
       <c r="E86" s="23" t="s">
         <v>324</v>
       </c>
-      <c r="F86" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="G86" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="H86" s="5"/>
-      <c r="I86" s="43" t="n">
+      <c r="F86" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="G86" s="41" t="n">
+        <v>72</v>
+      </c>
+      <c r="H86" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I86" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J86" s="5"/>
-      <c r="K86" s="5"/>
+      <c r="K86" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
       <c r="N86" s="5"/>
@@ -8321,29 +8446,29 @@
       <c r="Q86" s="5"/>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="43" t="n">
+      <c r="A87" s="41" t="n">
+        <v>74</v>
+      </c>
+      <c r="B87" s="42"/>
+      <c r="C87" s="41" t="n">
         <v>73</v>
       </c>
-      <c r="B87" s="44"/>
-      <c r="C87" s="43" t="n">
+      <c r="D87" s="42"/>
+      <c r="E87" s="23"/>
+      <c r="F87" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="G87" s="41" t="n">
         <v>72</v>
       </c>
-      <c r="D87" s="44"/>
-      <c r="E87" s="23" t="s">
-        <v>325</v>
-      </c>
-      <c r="F87" s="47" t="s">
-        <v>154</v>
-      </c>
-      <c r="G87" s="43" t="n">
-        <v>72</v>
-      </c>
-      <c r="H87" s="5"/>
-      <c r="I87" s="43" t="n">
+      <c r="H87" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I87" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J87" s="5"/>
-      <c r="K87" s="5" t="s">
+      <c r="K87" s="22" t="s">
         <v>87</v>
       </c>
       <c r="L87" s="5"/>
@@ -8354,27 +8479,31 @@
       <c r="Q87" s="5"/>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="43" t="n">
+      <c r="A88" s="41" t="n">
+        <v>75</v>
+      </c>
+      <c r="B88" s="42"/>
+      <c r="C88" s="41" t="n">
         <v>74</v>
       </c>
-      <c r="B88" s="44"/>
-      <c r="C88" s="43" t="n">
-        <v>73</v>
-      </c>
-      <c r="D88" s="44"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="G88" s="43" t="n">
+      <c r="D88" s="42"/>
+      <c r="E88" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="F88" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="G88" s="41" t="n">
         <v>72</v>
       </c>
-      <c r="H88" s="5"/>
-      <c r="I88" s="43" t="n">
+      <c r="H88" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I88" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J88" s="5"/>
-      <c r="K88" s="22" t="s">
+      <c r="K88" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L88" s="5"/>
@@ -8385,25 +8514,31 @@
       <c r="Q88" s="5"/>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="43" t="n">
+      <c r="A89" s="41" t="n">
+        <v>76</v>
+      </c>
+      <c r="B89" s="42" t="n">
         <v>75</v>
       </c>
-      <c r="B89" s="44"/>
-      <c r="C89" s="43" t="n">
-        <v>74</v>
-      </c>
-      <c r="D89" s="44"/>
+      <c r="C89" s="41" t="n">
+        <v>75</v>
+      </c>
+      <c r="D89" s="42" t="n">
+        <v>75</v>
+      </c>
       <c r="E89" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="F89" s="47" t="s">
-        <v>156</v>
-      </c>
-      <c r="G89" s="43" t="n">
+      <c r="F89" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="G89" s="41" t="n">
         <v>72</v>
       </c>
-      <c r="H89" s="5"/>
-      <c r="I89" s="43" t="n">
+      <c r="H89" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I89" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J89" s="5"/>
@@ -8418,35 +8553,29 @@
       <c r="Q89" s="5"/>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="43" t="n">
-        <v>76</v>
-      </c>
-      <c r="B90" s="44" t="n">
+      <c r="A90" s="41" t="n">
+        <v>77</v>
+      </c>
+      <c r="B90" s="42" t="n">
         <v>75</v>
       </c>
-      <c r="C90" s="43" t="n">
+      <c r="C90" s="41"/>
+      <c r="D90" s="42" t="n">
         <v>75</v>
       </c>
-      <c r="D90" s="44" t="n">
-        <v>75</v>
-      </c>
-      <c r="E90" s="23" t="s">
+      <c r="E90" s="23"/>
+      <c r="F90" s="46" t="s">
         <v>327</v>
       </c>
-      <c r="F90" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="G90" s="43" t="n">
+      <c r="G90" s="41" t="n">
         <v>72</v>
       </c>
-      <c r="H90" s="5"/>
-      <c r="I90" s="43" t="n">
-        <v>1</v>
-      </c>
+      <c r="H90" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I90" s="41"/>
       <c r="J90" s="5"/>
-      <c r="K90" s="17" t="s">
-        <v>87</v>
-      </c>
+      <c r="K90" s="17"/>
       <c r="L90" s="5"/>
       <c r="M90" s="5"/>
       <c r="N90" s="5"/>
@@ -8455,1249 +8584,1305 @@
       <c r="Q90" s="5"/>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="43" t="n">
+      <c r="A91" s="41" t="n">
+        <v>78</v>
+      </c>
+      <c r="B91" s="42"/>
+      <c r="C91" s="41" t="n">
+        <v>76</v>
+      </c>
+      <c r="D91" s="42"/>
+      <c r="E91" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="F91" s="53" t="s">
+        <v>329</v>
+      </c>
+      <c r="G91" s="41" t="n">
         <v>77</v>
       </c>
-      <c r="B91" s="44" t="n">
-        <v>75</v>
-      </c>
-      <c r="C91" s="43"/>
-      <c r="D91" s="44" t="n">
-        <v>75</v>
-      </c>
-      <c r="E91" s="23"/>
-      <c r="F91" s="47" t="s">
-        <v>328</v>
-      </c>
-      <c r="G91" s="43" t="n">
-        <v>72</v>
-      </c>
-      <c r="H91" s="5"/>
-      <c r="I91" s="43" t="n">
+      <c r="H91" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J91" s="5"/>
-      <c r="K91" s="17"/>
+      <c r="K91" s="17" t="s">
+        <v>87</v>
+      </c>
       <c r="L91" s="5"/>
       <c r="M91" s="5"/>
       <c r="N91" s="5"/>
       <c r="O91" s="5"/>
       <c r="P91" s="5"/>
       <c r="Q91" s="5"/>
+      <c r="R91" s="40"/>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="43" t="n">
-        <v>78</v>
-      </c>
-      <c r="B92" s="44"/>
-      <c r="C92" s="43" t="n">
-        <v>76</v>
-      </c>
-      <c r="D92" s="44"/>
+      <c r="A92" s="41" t="n">
+        <v>79</v>
+      </c>
+      <c r="B92" s="42"/>
+      <c r="C92" s="41" t="n">
+        <v>77</v>
+      </c>
+      <c r="D92" s="42"/>
       <c r="E92" s="23" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F92" s="53" t="s">
-        <v>330</v>
-      </c>
-      <c r="G92" s="43" t="n">
+        <v>331</v>
+      </c>
+      <c r="G92" s="41" t="n">
         <v>77</v>
       </c>
-      <c r="H92" s="5"/>
-      <c r="I92" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="5"/>
+      <c r="H92" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I92" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>332</v>
+      </c>
       <c r="K92" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="L92" s="5"/>
+      <c r="L92" s="17" t="s">
+        <v>202</v>
+      </c>
       <c r="M92" s="5"/>
-      <c r="N92" s="5"/>
+      <c r="N92" s="17" t="s">
+        <v>231</v>
+      </c>
       <c r="O92" s="5"/>
       <c r="P92" s="5"/>
       <c r="Q92" s="5"/>
-      <c r="R92" s="42"/>
+      <c r="R92" s="47"/>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="43" t="n">
-        <v>79</v>
-      </c>
-      <c r="B93" s="44"/>
-      <c r="C93" s="43" t="n">
-        <v>77</v>
-      </c>
-      <c r="D93" s="44"/>
-      <c r="E93" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="F93" s="53" t="s">
-        <v>332</v>
-      </c>
-      <c r="G93" s="43" t="n">
-        <v>77</v>
-      </c>
-      <c r="H93" s="5"/>
-      <c r="I93" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="5" t="s">
+      <c r="A93" s="34" t="n">
+        <v>80</v>
+      </c>
+      <c r="B93" s="24"/>
+      <c r="C93" s="34"/>
+      <c r="D93" s="24"/>
+      <c r="E93" s="24" t="s">
         <v>333</v>
       </c>
-      <c r="K93" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L93" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="M93" s="5"/>
-      <c r="N93" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="O93" s="5"/>
-      <c r="P93" s="5"/>
-      <c r="Q93" s="5"/>
-      <c r="R93" s="48"/>
+      <c r="F93" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="G93" s="34" t="n">
+        <v>43</v>
+      </c>
+      <c r="H93" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I93" s="34"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="14"/>
+      <c r="L93" s="14"/>
+      <c r="M93" s="8"/>
+      <c r="N93" s="14"/>
+      <c r="O93" s="8"/>
+      <c r="P93" s="8"/>
+      <c r="Q93" s="8"/>
+      <c r="R93" s="40"/>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="37" t="n">
-        <v>80</v>
+      <c r="A94" s="34" t="n">
+        <v>81</v>
       </c>
       <c r="B94" s="24"/>
-      <c r="C94" s="37"/>
+      <c r="C94" s="34" t="n">
+        <v>78</v>
+      </c>
       <c r="D94" s="24"/>
       <c r="E94" s="24" t="s">
         <v>334</v>
       </c>
-      <c r="F94" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="G94" s="37" t="n">
-        <v>43</v>
-      </c>
-      <c r="H94" s="8"/>
-      <c r="I94" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="8"/>
-      <c r="K94" s="14"/>
-      <c r="L94" s="14"/>
+      <c r="F94" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="G94" s="34" t="n">
+        <v>80</v>
+      </c>
+      <c r="H94" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I94" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="K94" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L94" s="14" t="s">
+        <v>202</v>
+      </c>
       <c r="M94" s="8"/>
-      <c r="N94" s="14"/>
+      <c r="N94" s="8"/>
       <c r="O94" s="8"/>
       <c r="P94" s="8"/>
       <c r="Q94" s="8"/>
-      <c r="R94" s="42"/>
+      <c r="R94" s="40"/>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="37" t="n">
-        <v>81</v>
+      <c r="A95" s="34" t="n">
+        <v>82</v>
       </c>
       <c r="B95" s="24"/>
-      <c r="C95" s="37" t="n">
-        <v>78</v>
+      <c r="C95" s="34" t="n">
+        <v>79</v>
       </c>
       <c r="D95" s="24"/>
       <c r="E95" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="F95" s="41" t="s">
-        <v>161</v>
-      </c>
-      <c r="G95" s="37" t="n">
+        <v>336</v>
+      </c>
+      <c r="F95" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="G95" s="34" t="n">
         <v>80</v>
       </c>
-      <c r="H95" s="24"/>
-      <c r="I95" s="37" t="n">
+      <c r="H95" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I95" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K95" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L95" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M95" s="8"/>
       <c r="N95" s="8"/>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
       <c r="Q95" s="8"/>
-      <c r="R95" s="42"/>
+      <c r="R95" s="40"/>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="37" t="n">
-        <v>82</v>
+      <c r="A96" s="34" t="n">
+        <v>83</v>
       </c>
       <c r="B96" s="24"/>
-      <c r="C96" s="37" t="n">
-        <v>79</v>
+      <c r="C96" s="34" t="n">
+        <v>80</v>
       </c>
       <c r="D96" s="24"/>
       <c r="E96" s="24" t="s">
-        <v>337</v>
-      </c>
-      <c r="F96" s="41" t="s">
-        <v>162</v>
-      </c>
-      <c r="G96" s="37" t="n">
+        <v>338</v>
+      </c>
+      <c r="F96" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="G96" s="34" t="n">
         <v>80</v>
       </c>
-      <c r="H96" s="8"/>
-      <c r="I96" s="37" t="n">
+      <c r="H96" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K96" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L96" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M96" s="8"/>
       <c r="N96" s="8"/>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
       <c r="Q96" s="8"/>
-      <c r="R96" s="42"/>
+      <c r="R96" s="40"/>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="37" t="n">
-        <v>83</v>
+      <c r="A97" s="34" t="n">
+        <v>84</v>
       </c>
       <c r="B97" s="24"/>
-      <c r="C97" s="37" t="n">
-        <v>80</v>
+      <c r="C97" s="34" t="n">
+        <v>81</v>
       </c>
       <c r="D97" s="24"/>
       <c r="E97" s="24" t="s">
-        <v>339</v>
-      </c>
-      <c r="F97" s="41" t="s">
-        <v>163</v>
-      </c>
-      <c r="G97" s="37" t="n">
+        <v>340</v>
+      </c>
+      <c r="F97" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="G97" s="34" t="n">
         <v>80</v>
       </c>
-      <c r="H97" s="8"/>
-      <c r="I97" s="37" t="n">
+      <c r="H97" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I97" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J97" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K97" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L97" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M97" s="8"/>
       <c r="N97" s="8"/>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
       <c r="Q97" s="8"/>
-      <c r="R97" s="42"/>
+      <c r="R97" s="47"/>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="37" t="n">
-        <v>84</v>
-      </c>
-      <c r="B98" s="24"/>
-      <c r="C98" s="37" t="n">
-        <v>81</v>
-      </c>
-      <c r="D98" s="24"/>
-      <c r="E98" s="24" t="s">
-        <v>341</v>
-      </c>
-      <c r="F98" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="G98" s="37" t="n">
-        <v>80</v>
-      </c>
-      <c r="H98" s="8"/>
-      <c r="I98" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="8" t="s">
+      <c r="A98" s="41" t="n">
+        <v>85</v>
+      </c>
+      <c r="B98" s="42"/>
+      <c r="C98" s="41"/>
+      <c r="D98" s="42"/>
+      <c r="E98" s="23"/>
+      <c r="F98" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="G98" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="H98" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I98" s="41"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="17"/>
+      <c r="L98" s="17"/>
+      <c r="M98" s="5"/>
+      <c r="N98" s="5"/>
+      <c r="O98" s="5"/>
+      <c r="P98" s="5"/>
+      <c r="Q98" s="5"/>
+      <c r="R98" s="40"/>
+    </row>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="41"/>
+      <c r="B99" s="42"/>
+      <c r="C99" s="41" t="n">
+        <v>82</v>
+      </c>
+      <c r="D99" s="42"/>
+      <c r="E99" s="23" t="s">
         <v>342</v>
       </c>
-      <c r="K98" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L98" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="M98" s="8"/>
-      <c r="N98" s="8"/>
-      <c r="O98" s="8"/>
-      <c r="P98" s="8"/>
-      <c r="Q98" s="8"/>
-      <c r="R98" s="48"/>
-    </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="43" t="n">
+      <c r="F99" s="46" t="s">
+        <v>67</v>
+      </c>
+      <c r="G99" s="41" t="n">
         <v>85</v>
       </c>
-      <c r="B99" s="44"/>
-      <c r="C99" s="43"/>
-      <c r="D99" s="44"/>
-      <c r="E99" s="23"/>
-      <c r="F99" s="44" t="s">
-        <v>164</v>
-      </c>
-      <c r="G99" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="H99" s="5"/>
-      <c r="I99" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J99" s="5"/>
-      <c r="K99" s="17"/>
-      <c r="L99" s="17"/>
+      <c r="H99" s="41"/>
+      <c r="I99" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="K99" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L99" s="17" t="s">
+        <v>202</v>
+      </c>
       <c r="M99" s="5"/>
       <c r="N99" s="5"/>
       <c r="O99" s="5"/>
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
-      <c r="R99" s="42"/>
+      <c r="R99" s="47"/>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="43"/>
-      <c r="B100" s="44"/>
-      <c r="C100" s="43" t="n">
-        <v>82</v>
-      </c>
-      <c r="D100" s="44"/>
+      <c r="A100" s="41"/>
+      <c r="B100" s="42"/>
+      <c r="C100" s="41" t="n">
+        <v>83</v>
+      </c>
+      <c r="D100" s="42"/>
       <c r="E100" s="23" t="s">
-        <v>343</v>
-      </c>
-      <c r="F100" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="G100" s="43" t="n">
+        <v>342</v>
+      </c>
+      <c r="F100" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="G100" s="41" t="n">
         <v>85</v>
       </c>
-      <c r="H100" s="5"/>
-      <c r="I100" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" s="5" t="s">
-        <v>344</v>
-      </c>
+      <c r="H100" s="41"/>
+      <c r="I100" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" s="5"/>
       <c r="K100" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="L100" s="17" t="s">
-        <v>203</v>
-      </c>
+      <c r="L100" s="5"/>
       <c r="M100" s="5"/>
       <c r="N100" s="5"/>
       <c r="O100" s="5"/>
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
-      <c r="R100" s="48"/>
+      <c r="R100" s="40"/>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="43"/>
-      <c r="B101" s="44"/>
-      <c r="C101" s="43" t="n">
-        <v>83</v>
-      </c>
-      <c r="D101" s="44"/>
+      <c r="A101" s="41" t="n">
+        <v>86</v>
+      </c>
+      <c r="B101" s="42"/>
+      <c r="C101" s="41" t="n">
+        <v>84</v>
+      </c>
+      <c r="D101" s="42"/>
       <c r="E101" s="23" t="s">
-        <v>343</v>
-      </c>
-      <c r="F101" s="47" t="s">
-        <v>165</v>
-      </c>
-      <c r="G101" s="43" t="n">
+        <v>344</v>
+      </c>
+      <c r="F101" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="G101" s="41" t="n">
         <v>85</v>
       </c>
-      <c r="H101" s="5"/>
-      <c r="I101" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J101" s="5"/>
+      <c r="H101" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I101" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" s="5" t="s">
+        <v>345</v>
+      </c>
       <c r="K101" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="L101" s="5"/>
+      <c r="L101" s="17" t="s">
+        <v>202</v>
+      </c>
       <c r="M101" s="5"/>
       <c r="N101" s="5"/>
       <c r="O101" s="5"/>
       <c r="P101" s="5"/>
       <c r="Q101" s="5"/>
-      <c r="R101" s="42"/>
+      <c r="R101" s="40"/>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="43" t="n">
-        <v>86</v>
-      </c>
-      <c r="B102" s="44"/>
-      <c r="C102" s="43" t="n">
-        <v>84</v>
-      </c>
-      <c r="D102" s="44"/>
+      <c r="A102" s="41" t="n">
+        <v>87</v>
+      </c>
+      <c r="B102" s="42"/>
+      <c r="C102" s="41" t="n">
+        <v>85</v>
+      </c>
+      <c r="D102" s="42"/>
       <c r="E102" s="23" t="s">
-        <v>345</v>
-      </c>
-      <c r="F102" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="G102" s="43" t="n">
+        <v>346</v>
+      </c>
+      <c r="F102" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="G102" s="41" t="n">
         <v>85</v>
       </c>
-      <c r="H102" s="5"/>
-      <c r="I102" s="43" t="n">
+      <c r="H102" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I102" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K102" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L102" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M102" s="5"/>
       <c r="N102" s="5"/>
       <c r="O102" s="5"/>
       <c r="P102" s="5"/>
       <c r="Q102" s="5"/>
-      <c r="R102" s="42"/>
+      <c r="R102" s="40"/>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="43" t="n">
-        <v>87</v>
-      </c>
-      <c r="B103" s="44"/>
-      <c r="C103" s="43" t="n">
+      <c r="A103" s="41" t="n">
+        <v>88</v>
+      </c>
+      <c r="B103" s="42"/>
+      <c r="C103" s="41" t="n">
+        <v>86</v>
+      </c>
+      <c r="D103" s="42"/>
+      <c r="E103" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="F103" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="G103" s="41" t="n">
         <v>85</v>
       </c>
-      <c r="D103" s="44"/>
-      <c r="E103" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="F103" s="47" t="s">
-        <v>153</v>
-      </c>
-      <c r="G103" s="43" t="n">
-        <v>85</v>
-      </c>
-      <c r="H103" s="5"/>
-      <c r="I103" s="43" t="n">
+      <c r="H103" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I103" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K103" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L103" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M103" s="5"/>
       <c r="N103" s="5"/>
       <c r="O103" s="5"/>
       <c r="P103" s="5"/>
       <c r="Q103" s="5"/>
-      <c r="R103" s="42"/>
+      <c r="R103" s="40"/>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="43" t="n">
-        <v>88</v>
-      </c>
-      <c r="B104" s="44"/>
-      <c r="C104" s="43" t="n">
-        <v>86</v>
-      </c>
-      <c r="D104" s="44"/>
+      <c r="A104" s="41" t="n">
+        <v>89</v>
+      </c>
+      <c r="B104" s="42"/>
+      <c r="C104" s="41" t="n">
+        <v>87</v>
+      </c>
+      <c r="D104" s="42"/>
       <c r="E104" s="23" t="s">
-        <v>349</v>
-      </c>
-      <c r="F104" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="G104" s="43" t="n">
+        <v>350</v>
+      </c>
+      <c r="F104" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="G104" s="41" t="n">
         <v>85</v>
       </c>
-      <c r="H104" s="5"/>
-      <c r="I104" s="43" t="n">
+      <c r="H104" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K104" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L104" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M104" s="5"/>
       <c r="N104" s="5"/>
       <c r="O104" s="5"/>
       <c r="P104" s="5"/>
       <c r="Q104" s="5"/>
-      <c r="R104" s="42"/>
+      <c r="R104" s="40"/>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="43" t="n">
-        <v>89</v>
-      </c>
-      <c r="B105" s="44"/>
-      <c r="C105" s="43" t="n">
-        <v>87</v>
-      </c>
-      <c r="D105" s="44"/>
+      <c r="A105" s="41" t="n">
+        <v>90</v>
+      </c>
+      <c r="B105" s="42"/>
+      <c r="C105" s="41" t="n">
+        <v>88</v>
+      </c>
+      <c r="D105" s="42"/>
       <c r="E105" s="23" t="s">
-        <v>351</v>
-      </c>
-      <c r="F105" s="47" t="s">
-        <v>167</v>
-      </c>
-      <c r="G105" s="43" t="n">
+        <v>352</v>
+      </c>
+      <c r="F105" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="G105" s="41" t="n">
         <v>85</v>
       </c>
-      <c r="H105" s="5"/>
-      <c r="I105" s="43" t="n">
+      <c r="H105" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I105" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K105" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L105" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M105" s="5"/>
       <c r="N105" s="5"/>
       <c r="O105" s="5"/>
       <c r="P105" s="5"/>
       <c r="Q105" s="5"/>
-      <c r="R105" s="42"/>
+      <c r="R105" s="40"/>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="43" t="n">
+      <c r="A106" s="41" t="n">
+        <v>91</v>
+      </c>
+      <c r="B106" s="42"/>
+      <c r="C106" s="41" t="n">
+        <v>89</v>
+      </c>
+      <c r="D106" s="42"/>
+      <c r="E106" s="23" t="s">
+        <v>354</v>
+      </c>
+      <c r="F106" s="53" t="s">
+        <v>355</v>
+      </c>
+      <c r="G106" s="41" t="n">
         <v>90</v>
       </c>
-      <c r="B106" s="44"/>
-      <c r="C106" s="43" t="n">
-        <v>88</v>
-      </c>
-      <c r="D106" s="44"/>
-      <c r="E106" s="23" t="s">
-        <v>353</v>
-      </c>
-      <c r="F106" s="47" t="s">
-        <v>168</v>
-      </c>
-      <c r="G106" s="43" t="n">
-        <v>85</v>
-      </c>
-      <c r="H106" s="5"/>
-      <c r="I106" s="43" t="n">
+      <c r="H106" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I106" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K106" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L106" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M106" s="5"/>
       <c r="N106" s="5"/>
       <c r="O106" s="5"/>
       <c r="P106" s="5"/>
       <c r="Q106" s="5"/>
-      <c r="R106" s="42"/>
+      <c r="R106" s="40"/>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="43" t="n">
-        <v>91</v>
-      </c>
-      <c r="B107" s="44"/>
-      <c r="C107" s="43" t="n">
-        <v>89</v>
-      </c>
-      <c r="D107" s="44"/>
+      <c r="A107" s="41" t="n">
+        <v>92</v>
+      </c>
+      <c r="B107" s="42"/>
+      <c r="C107" s="41" t="n">
+        <v>90</v>
+      </c>
+      <c r="D107" s="42"/>
       <c r="E107" s="23" t="s">
-        <v>355</v>
-      </c>
-      <c r="F107" s="53" t="s">
-        <v>356</v>
-      </c>
-      <c r="G107" s="43" t="n">
-        <v>90</v>
-      </c>
-      <c r="H107" s="5"/>
-      <c r="I107" s="43" t="n">
+        <v>357</v>
+      </c>
+      <c r="F107" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="G107" s="41" t="n">
+        <v>85</v>
+      </c>
+      <c r="H107" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K107" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L107" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M107" s="5"/>
       <c r="N107" s="5"/>
       <c r="O107" s="5"/>
       <c r="P107" s="5"/>
       <c r="Q107" s="5"/>
-      <c r="R107" s="42"/>
+      <c r="R107" s="47"/>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="43" t="n">
-        <v>92</v>
-      </c>
-      <c r="B108" s="44"/>
-      <c r="C108" s="43" t="n">
-        <v>90</v>
-      </c>
-      <c r="D108" s="44"/>
-      <c r="E108" s="23" t="s">
-        <v>358</v>
-      </c>
-      <c r="F108" s="47" t="s">
-        <v>170</v>
-      </c>
-      <c r="G108" s="43" t="n">
-        <v>85</v>
-      </c>
-      <c r="H108" s="5"/>
-      <c r="I108" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" s="5" t="s">
+      <c r="A108" s="34" t="n">
+        <v>93</v>
+      </c>
+      <c r="B108" s="24"/>
+      <c r="C108" s="34"/>
+      <c r="D108" s="24"/>
+      <c r="E108" s="24"/>
+      <c r="F108" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="G108" s="34" t="n">
+        <v>43</v>
+      </c>
+      <c r="H108" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" s="34"/>
+      <c r="J108" s="8"/>
+      <c r="K108" s="14"/>
+      <c r="L108" s="14"/>
+      <c r="M108" s="8"/>
+      <c r="N108" s="8"/>
+      <c r="O108" s="8"/>
+      <c r="P108" s="8"/>
+      <c r="Q108" s="8"/>
+      <c r="R108" s="40"/>
+    </row>
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="34" t="n">
+        <v>94</v>
+      </c>
+      <c r="B109" s="24"/>
+      <c r="C109" s="34" t="n">
+        <v>91</v>
+      </c>
+      <c r="D109" s="24"/>
+      <c r="E109" s="24" t="s">
         <v>359</v>
       </c>
-      <c r="K108" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L108" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="M108" s="5"/>
-      <c r="N108" s="5"/>
-      <c r="O108" s="5"/>
-      <c r="P108" s="5"/>
-      <c r="Q108" s="5"/>
-      <c r="R108" s="48"/>
-    </row>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="37" t="n">
+      <c r="F109" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="G109" s="34" t="n">
         <v>93</v>
       </c>
-      <c r="B109" s="24"/>
-      <c r="C109" s="37"/>
-      <c r="D109" s="24"/>
-      <c r="E109" s="24"/>
-      <c r="F109" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="G109" s="37" t="n">
-        <v>43</v>
-      </c>
-      <c r="H109" s="8"/>
-      <c r="I109" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="8"/>
-      <c r="K109" s="14"/>
-      <c r="L109" s="14"/>
+      <c r="H109" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I109" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="K109" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L109" s="14" t="s">
+        <v>202</v>
+      </c>
       <c r="M109" s="8"/>
       <c r="N109" s="8"/>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
       <c r="Q109" s="8"/>
-      <c r="R109" s="42"/>
+      <c r="R109" s="40"/>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="37" t="n">
-        <v>94</v>
+      <c r="A110" s="34" t="n">
+        <v>95</v>
       </c>
       <c r="B110" s="24"/>
-      <c r="C110" s="37" t="n">
-        <v>91</v>
+      <c r="C110" s="34" t="n">
+        <v>92</v>
       </c>
       <c r="D110" s="24"/>
       <c r="E110" s="24" t="s">
-        <v>360</v>
-      </c>
-      <c r="F110" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="G110" s="37" t="n">
+        <v>361</v>
+      </c>
+      <c r="F110" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="G110" s="34" t="n">
         <v>93</v>
       </c>
-      <c r="H110" s="8"/>
-      <c r="I110" s="37" t="n">
+      <c r="H110" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I110" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K110" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L110" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M110" s="8"/>
       <c r="N110" s="8"/>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
       <c r="Q110" s="8"/>
-      <c r="R110" s="42"/>
+      <c r="R110" s="40"/>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="37" t="n">
-        <v>95</v>
+      <c r="A111" s="34" t="n">
+        <v>96</v>
       </c>
       <c r="B111" s="24"/>
-      <c r="C111" s="37" t="n">
-        <v>92</v>
+      <c r="C111" s="34" t="n">
+        <v>93</v>
       </c>
       <c r="D111" s="24"/>
       <c r="E111" s="24" t="s">
-        <v>362</v>
-      </c>
-      <c r="F111" s="41" t="s">
-        <v>173</v>
-      </c>
-      <c r="G111" s="37" t="n">
+        <v>363</v>
+      </c>
+      <c r="F111" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="G111" s="34" t="n">
         <v>93</v>
       </c>
-      <c r="H111" s="8"/>
-      <c r="I111" s="37" t="n">
+      <c r="H111" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K111" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L111" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M111" s="8"/>
-      <c r="N111" s="8"/>
+      <c r="N111" s="14" t="s">
+        <v>231</v>
+      </c>
       <c r="O111" s="8"/>
       <c r="P111" s="8"/>
       <c r="Q111" s="8"/>
-      <c r="R111" s="42"/>
+      <c r="R111" s="40"/>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="37" t="n">
-        <v>96</v>
+      <c r="A112" s="34" t="n">
+        <v>97</v>
       </c>
       <c r="B112" s="24"/>
-      <c r="C112" s="37" t="n">
-        <v>93</v>
+      <c r="C112" s="34" t="n">
+        <v>94</v>
       </c>
       <c r="D112" s="24"/>
       <c r="E112" s="24" t="s">
-        <v>364</v>
-      </c>
-      <c r="F112" s="41" t="s">
-        <v>174</v>
-      </c>
-      <c r="G112" s="37" t="n">
+        <v>365</v>
+      </c>
+      <c r="F112" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="G112" s="34" t="n">
         <v>93</v>
       </c>
-      <c r="H112" s="8"/>
-      <c r="I112" s="37" t="n">
+      <c r="H112" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I112" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K112" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L112" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M112" s="8"/>
       <c r="N112" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
       <c r="Q112" s="8"/>
-      <c r="R112" s="42"/>
+      <c r="R112" s="40"/>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="37" t="n">
-        <v>97</v>
-      </c>
-      <c r="B113" s="24"/>
-      <c r="C113" s="37" t="n">
-        <v>94</v>
-      </c>
-      <c r="D113" s="24"/>
-      <c r="E113" s="24" t="s">
-        <v>366</v>
-      </c>
-      <c r="F113" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="G113" s="37" t="n">
-        <v>93</v>
-      </c>
-      <c r="H113" s="8"/>
-      <c r="I113" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="8" t="s">
+      <c r="A113" s="41" t="n">
+        <v>98</v>
+      </c>
+      <c r="B113" s="42"/>
+      <c r="C113" s="41" t="n">
+        <v>95</v>
+      </c>
+      <c r="D113" s="42"/>
+      <c r="E113" s="23" t="s">
         <v>367</v>
       </c>
-      <c r="K113" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L113" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="M113" s="8"/>
-      <c r="N113" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="O113" s="8"/>
-      <c r="P113" s="8"/>
-      <c r="Q113" s="8"/>
-      <c r="R113" s="42"/>
+      <c r="F113" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="G113" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="H113" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I113" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="K113" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L113" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="M113" s="5"/>
+      <c r="N113" s="5"/>
+      <c r="O113" s="5"/>
+      <c r="P113" s="5"/>
+      <c r="Q113" s="5"/>
+      <c r="R113" s="40"/>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="43" t="n">
+      <c r="A114" s="41" t="n">
+        <v>99</v>
+      </c>
+      <c r="B114" s="42"/>
+      <c r="C114" s="41" t="n">
+        <v>96</v>
+      </c>
+      <c r="D114" s="42"/>
+      <c r="E114" s="23" t="s">
+        <v>369</v>
+      </c>
+      <c r="F114" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="G114" s="41" t="n">
         <v>98</v>
       </c>
-      <c r="B114" s="44"/>
-      <c r="C114" s="43" t="n">
-        <v>95</v>
-      </c>
-      <c r="D114" s="44"/>
-      <c r="E114" s="23" t="s">
-        <v>368</v>
-      </c>
-      <c r="F114" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="G114" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="H114" s="5"/>
-      <c r="I114" s="43" t="n">
+      <c r="H114" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I114" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J114" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K114" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L114" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M114" s="5"/>
       <c r="N114" s="5"/>
       <c r="O114" s="5"/>
       <c r="P114" s="5"/>
       <c r="Q114" s="5"/>
-      <c r="R114" s="42"/>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="43" t="n">
-        <v>99</v>
-      </c>
-      <c r="B115" s="44"/>
-      <c r="C115" s="43" t="n">
-        <v>96</v>
-      </c>
-      <c r="D115" s="44"/>
-      <c r="E115" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="F115" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="G115" s="43" t="n">
-        <v>98</v>
-      </c>
-      <c r="H115" s="5"/>
-      <c r="I115" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J115" s="5" t="s">
+      <c r="A115" s="34" t="n">
+        <v>100</v>
+      </c>
+      <c r="B115" s="24"/>
+      <c r="C115" s="34"/>
+      <c r="D115" s="24"/>
+      <c r="E115" s="24"/>
+      <c r="F115" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="G115" s="34" t="n">
+        <v>43</v>
+      </c>
+      <c r="H115" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I115" s="34"/>
+      <c r="J115" s="8"/>
+      <c r="K115" s="14"/>
+      <c r="L115" s="14"/>
+      <c r="M115" s="8"/>
+      <c r="N115" s="8"/>
+      <c r="O115" s="8"/>
+      <c r="P115" s="8"/>
+      <c r="Q115" s="8"/>
+      <c r="R115" s="40"/>
+    </row>
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="34" t="n">
+        <v>101</v>
+      </c>
+      <c r="B116" s="24"/>
+      <c r="C116" s="34" t="n">
+        <v>97</v>
+      </c>
+      <c r="D116" s="24"/>
+      <c r="E116" s="24" t="s">
         <v>371</v>
       </c>
-      <c r="K115" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L115" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="M115" s="5"/>
-      <c r="N115" s="5"/>
-      <c r="O115" s="5"/>
-      <c r="P115" s="5"/>
-      <c r="Q115" s="5"/>
-    </row>
-    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="37" t="n">
+      <c r="F116" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="G116" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="B116" s="24"/>
-      <c r="C116" s="37"/>
-      <c r="D116" s="24"/>
-      <c r="E116" s="24"/>
-      <c r="F116" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="G116" s="37" t="n">
-        <v>43</v>
-      </c>
-      <c r="H116" s="8"/>
-      <c r="I116" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J116" s="8"/>
-      <c r="K116" s="14"/>
-      <c r="L116" s="14"/>
+      <c r="H116" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="K116" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L116" s="14" t="s">
+        <v>202</v>
+      </c>
       <c r="M116" s="8"/>
       <c r="N116" s="8"/>
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
       <c r="Q116" s="8"/>
-      <c r="R116" s="42"/>
+      <c r="R116" s="40"/>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="37" t="n">
-        <v>101</v>
+      <c r="A117" s="34" t="n">
+        <v>102</v>
       </c>
       <c r="B117" s="24"/>
-      <c r="C117" s="37" t="n">
-        <v>97</v>
+      <c r="C117" s="34" t="n">
+        <v>98</v>
       </c>
       <c r="D117" s="24"/>
       <c r="E117" s="24" t="s">
-        <v>372</v>
-      </c>
-      <c r="F117" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="G117" s="37" t="n">
+        <v>373</v>
+      </c>
+      <c r="F117" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="G117" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="H117" s="8"/>
-      <c r="I117" s="37" t="n">
+      <c r="H117" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I117" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J117" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K117" s="14" t="s">
         <v>87</v>
       </c>
       <c r="L117" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M117" s="8"/>
       <c r="N117" s="8"/>
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
       <c r="Q117" s="8"/>
-      <c r="R117" s="42"/>
+      <c r="R117" s="40"/>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="37" t="n">
-        <v>102</v>
-      </c>
+      <c r="A118" s="34"/>
       <c r="B118" s="24"/>
-      <c r="C118" s="37" t="n">
-        <v>98</v>
+      <c r="C118" s="34" t="n">
+        <v>99</v>
       </c>
       <c r="D118" s="24"/>
       <c r="E118" s="24" t="s">
-        <v>374</v>
-      </c>
-      <c r="F118" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="G118" s="37" t="n">
-        <v>100</v>
-      </c>
-      <c r="H118" s="8"/>
-      <c r="I118" s="37" t="n">
+        <v>373</v>
+      </c>
+      <c r="F118" s="24"/>
+      <c r="G118" s="34"/>
+      <c r="H118" s="34"/>
+      <c r="I118" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J118" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="K118" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="K118" s="8"/>
       <c r="L118" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M118" s="8"/>
-      <c r="N118" s="8"/>
+      <c r="N118" s="14" t="s">
+        <v>231</v>
+      </c>
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
       <c r="Q118" s="8"/>
-      <c r="R118" s="42"/>
+      <c r="R118" s="47"/>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="37"/>
-      <c r="B119" s="24"/>
-      <c r="C119" s="37" t="n">
-        <v>99</v>
-      </c>
-      <c r="D119" s="24"/>
-      <c r="E119" s="24" t="s">
-        <v>374</v>
-      </c>
-      <c r="F119" s="24"/>
-      <c r="G119" s="37"/>
-      <c r="H119" s="8"/>
-      <c r="I119" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J119" s="8" t="s">
+      <c r="A119" s="41" t="n">
+        <v>103</v>
+      </c>
+      <c r="B119" s="42"/>
+      <c r="C119" s="41"/>
+      <c r="D119" s="42"/>
+      <c r="E119" s="23" t="n">
+        <v>43</v>
+      </c>
+      <c r="F119" s="42" t="s">
+        <v>180</v>
+      </c>
+      <c r="G119" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="H119" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I119" s="41"/>
+      <c r="J119" s="5"/>
+      <c r="K119" s="17"/>
+      <c r="L119" s="5"/>
+      <c r="M119" s="5"/>
+      <c r="N119" s="5"/>
+      <c r="O119" s="5"/>
+      <c r="P119" s="5"/>
+      <c r="Q119" s="5"/>
+      <c r="R119" s="40"/>
+    </row>
+    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="41" t="n">
+        <v>104</v>
+      </c>
+      <c r="B120" s="42"/>
+      <c r="C120" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="D120" s="42"/>
+      <c r="E120" s="23" t="s">
         <v>376</v>
       </c>
-      <c r="K119" s="8"/>
-      <c r="L119" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="M119" s="8"/>
-      <c r="N119" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="O119" s="8"/>
-      <c r="P119" s="8"/>
-      <c r="Q119" s="8"/>
-      <c r="R119" s="48"/>
-    </row>
-    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="43" t="n">
+      <c r="F120" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="G120" s="41" t="n">
         <v>103</v>
       </c>
-      <c r="B120" s="44"/>
-      <c r="C120" s="43"/>
-      <c r="D120" s="44"/>
-      <c r="E120" s="23" t="n">
-        <v>42</v>
-      </c>
-      <c r="F120" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="G120" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="H120" s="5"/>
-      <c r="I120" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J120" s="5"/>
-      <c r="K120" s="17"/>
-      <c r="L120" s="5"/>
+      <c r="H120" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I120" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="K120" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L120" s="17" t="s">
+        <v>202</v>
+      </c>
       <c r="M120" s="5"/>
       <c r="N120" s="5"/>
       <c r="O120" s="5"/>
       <c r="P120" s="5"/>
       <c r="Q120" s="5"/>
-      <c r="R120" s="42"/>
+      <c r="R120" s="40"/>
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="43" t="n">
-        <v>104</v>
-      </c>
-      <c r="B121" s="44"/>
-      <c r="C121" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="D121" s="44"/>
+      <c r="A121" s="41" t="n">
+        <v>105</v>
+      </c>
+      <c r="B121" s="42"/>
+      <c r="C121" s="41" t="n">
+        <v>101</v>
+      </c>
+      <c r="D121" s="42"/>
       <c r="E121" s="23" t="s">
-        <v>377</v>
-      </c>
-      <c r="F121" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="G121" s="43" t="n">
+        <v>378</v>
+      </c>
+      <c r="F121" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="G121" s="41" t="n">
         <v>103</v>
       </c>
-      <c r="H121" s="5"/>
-      <c r="I121" s="43" t="n">
+      <c r="H121" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I121" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J121" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K121" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L121" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M121" s="5"/>
-      <c r="N121" s="5"/>
+      <c r="N121" s="17" t="s">
+        <v>231</v>
+      </c>
       <c r="O121" s="5"/>
       <c r="P121" s="5"/>
       <c r="Q121" s="5"/>
-      <c r="R121" s="42"/>
+      <c r="R121" s="40"/>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="43" t="n">
-        <v>105</v>
-      </c>
-      <c r="B122" s="44"/>
-      <c r="C122" s="43" t="n">
-        <v>101</v>
-      </c>
-      <c r="D122" s="44"/>
+      <c r="A122" s="41" t="n">
+        <v>106</v>
+      </c>
+      <c r="B122" s="42"/>
+      <c r="C122" s="41" t="n">
+        <v>102</v>
+      </c>
+      <c r="D122" s="42"/>
       <c r="E122" s="23" t="s">
-        <v>379</v>
-      </c>
-      <c r="F122" s="47" t="s">
-        <v>182</v>
-      </c>
-      <c r="G122" s="43" t="n">
+        <v>380</v>
+      </c>
+      <c r="F122" s="46" t="s">
+        <v>183</v>
+      </c>
+      <c r="G122" s="41" t="n">
         <v>103</v>
       </c>
-      <c r="H122" s="5"/>
-      <c r="I122" s="43" t="n">
+      <c r="H122" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I122" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J122" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K122" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L122" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M122" s="5"/>
       <c r="N122" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O122" s="5"/>
       <c r="P122" s="5"/>
       <c r="Q122" s="5"/>
-      <c r="R122" s="42"/>
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="43" t="n">
-        <v>106</v>
-      </c>
-      <c r="B123" s="44"/>
-      <c r="C123" s="43" t="n">
-        <v>102</v>
-      </c>
-      <c r="D123" s="44"/>
-      <c r="E123" s="23" t="s">
-        <v>381</v>
-      </c>
-      <c r="F123" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="G123" s="43" t="n">
+      <c r="A123" s="34" t="n">
+        <v>107</v>
+      </c>
+      <c r="B123" s="24"/>
+      <c r="C123" s="34" t="n">
         <v>103</v>
       </c>
-      <c r="H123" s="5"/>
-      <c r="I123" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J123" s="5" t="s">
+      <c r="D123" s="24"/>
+      <c r="E123" s="24" t="s">
         <v>382</v>
       </c>
-      <c r="K123" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L123" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="M123" s="5"/>
-      <c r="N123" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="O123" s="5"/>
-      <c r="P123" s="5"/>
-      <c r="Q123" s="5"/>
+      <c r="F123" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="G123" s="34" t="n">
+        <v>43</v>
+      </c>
+      <c r="H123" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I123" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" s="8"/>
+      <c r="K123" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L123" s="8"/>
+      <c r="M123" s="8"/>
+      <c r="N123" s="8"/>
+      <c r="O123" s="8"/>
+      <c r="P123" s="8"/>
+      <c r="Q123" s="8"/>
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="37" t="n">
-        <v>107</v>
-      </c>
-      <c r="B124" s="24"/>
-      <c r="C124" s="37" t="n">
-        <v>103</v>
-      </c>
-      <c r="D124" s="24"/>
-      <c r="E124" s="24" t="s">
+      <c r="A124" s="41" t="n">
+        <v>108</v>
+      </c>
+      <c r="B124" s="42"/>
+      <c r="C124" s="41" t="n">
+        <v>104</v>
+      </c>
+      <c r="D124" s="42"/>
+      <c r="E124" s="23" t="s">
         <v>383</v>
       </c>
-      <c r="F124" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="G124" s="37" t="n">
+      <c r="F124" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="G124" s="41" t="n">
         <v>43</v>
       </c>
-      <c r="H124" s="8"/>
-      <c r="I124" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J124" s="8"/>
-      <c r="K124" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L124" s="8"/>
-      <c r="M124" s="8"/>
-      <c r="N124" s="8"/>
-      <c r="O124" s="8"/>
-      <c r="P124" s="8"/>
-      <c r="Q124" s="8"/>
+      <c r="H124" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I124" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" s="5"/>
+      <c r="K124" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L124" s="5"/>
+      <c r="M124" s="5"/>
+      <c r="N124" s="5"/>
+      <c r="O124" s="5"/>
+      <c r="P124" s="5"/>
+      <c r="Q124" s="5"/>
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="43" t="n">
-        <v>108</v>
-      </c>
-      <c r="B125" s="44"/>
-      <c r="C125" s="43" t="n">
-        <v>104</v>
-      </c>
-      <c r="D125" s="44"/>
+      <c r="A125" s="41" t="n">
+        <v>109</v>
+      </c>
+      <c r="B125" s="42"/>
+      <c r="C125" s="41" t="n">
+        <v>105</v>
+      </c>
+      <c r="D125" s="42"/>
       <c r="E125" s="23" t="s">
         <v>384</v>
       </c>
-      <c r="F125" s="44" t="s">
-        <v>184</v>
-      </c>
-      <c r="G125" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="H125" s="5"/>
-      <c r="I125" s="43" t="n">
+      <c r="F125" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="G125" s="41" t="n">
+        <v>108</v>
+      </c>
+      <c r="H125" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I125" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J125" s="5"/>
@@ -9712,232 +9897,200 @@
       <c r="Q125" s="5"/>
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="43" t="n">
-        <v>109</v>
-      </c>
-      <c r="B126" s="44"/>
-      <c r="C126" s="43" t="n">
-        <v>105</v>
-      </c>
-      <c r="D126" s="44"/>
-      <c r="E126" s="23" t="s">
-        <v>385</v>
-      </c>
-      <c r="F126" s="47" t="s">
-        <v>185</v>
-      </c>
-      <c r="G126" s="43" t="n">
-        <v>108</v>
-      </c>
-      <c r="H126" s="5"/>
-      <c r="I126" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J126" s="5"/>
-      <c r="K126" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L126" s="5"/>
-      <c r="M126" s="5"/>
-      <c r="N126" s="5"/>
-      <c r="O126" s="5"/>
-      <c r="P126" s="5"/>
-      <c r="Q126" s="5"/>
+      <c r="A126" s="28"/>
+      <c r="C126" s="28"/>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="31"/>
-      <c r="C127" s="31"/>
-    </row>
-    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="31"/>
-      <c r="C128" s="31"/>
-    </row>
+      <c r="A127" s="28"/>
+      <c r="C127" s="28"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K6" r:id="rId2" display="PDF"/>
-    <hyperlink ref="K7" r:id="rId3" display="PDF"/>
-    <hyperlink ref="L7" r:id="rId4" display="VIDEO"/>
-    <hyperlink ref="K8" r:id="rId5" display="PDF"/>
-    <hyperlink ref="L8" r:id="rId6" display="VIDEO"/>
-    <hyperlink ref="K9" r:id="rId7" display="PDF"/>
-    <hyperlink ref="L9" r:id="rId8" display="VIDEO"/>
-    <hyperlink ref="K11" r:id="rId9" display="PDF"/>
-    <hyperlink ref="L11" r:id="rId10" display="VIDEO"/>
-    <hyperlink ref="K13" r:id="rId11" display="PDF"/>
-    <hyperlink ref="L13" r:id="rId12" display="VIDEO"/>
-    <hyperlink ref="K14" r:id="rId13" display="PDF"/>
-    <hyperlink ref="L14" r:id="rId14" display="VIDEO"/>
-    <hyperlink ref="K15" r:id="rId15" display="PDF"/>
-    <hyperlink ref="L15" r:id="rId16" display="VIDEO"/>
-    <hyperlink ref="K16" r:id="rId17" display="PDF"/>
-    <hyperlink ref="L16" r:id="rId18" display="VIDEO"/>
-    <hyperlink ref="K17" r:id="rId19" display="PDF"/>
-    <hyperlink ref="L17" r:id="rId20" display="VIDEO"/>
-    <hyperlink ref="K18" r:id="rId21" display="PDF"/>
-    <hyperlink ref="L18" r:id="rId22" display="VIDEO"/>
-    <hyperlink ref="K19" r:id="rId23" display="PDF"/>
-    <hyperlink ref="L19" r:id="rId24" display="VIDEO"/>
-    <hyperlink ref="L20" r:id="rId25" display="VIDEO"/>
-    <hyperlink ref="L21" r:id="rId26" display="VIDEO"/>
-    <hyperlink ref="N21" r:id="rId27" display="CODE"/>
-    <hyperlink ref="L23" r:id="rId28" display="VIDEO"/>
-    <hyperlink ref="N23" r:id="rId29" display="CODE"/>
-    <hyperlink ref="K24" r:id="rId30" display="PDF"/>
-    <hyperlink ref="L24" r:id="rId31" display="VIDEO"/>
-    <hyperlink ref="N24" r:id="rId32" display="CODE"/>
-    <hyperlink ref="K25" r:id="rId33" display="PDF"/>
-    <hyperlink ref="L26" r:id="rId34" display="VIDEO"/>
-    <hyperlink ref="N26" r:id="rId35" display="CODE"/>
-    <hyperlink ref="K27" r:id="rId36" display="CODE"/>
-    <hyperlink ref="L27" r:id="rId37" display="VIDEO"/>
-    <hyperlink ref="K28" r:id="rId38" display="PDF"/>
-    <hyperlink ref="L28" r:id="rId39" display="VIDEO"/>
-    <hyperlink ref="K29" r:id="rId40" display="PDF"/>
-    <hyperlink ref="L29" r:id="rId41" display="VIDEO"/>
-    <hyperlink ref="K30" r:id="rId42" display="PDF"/>
-    <hyperlink ref="L30" r:id="rId43" display="VIDEO"/>
-    <hyperlink ref="M30" r:id="rId44" display="VIDEO"/>
-    <hyperlink ref="K31" r:id="rId45" display="VIDEO"/>
-    <hyperlink ref="K32" r:id="rId46" display="PDF"/>
-    <hyperlink ref="L32" r:id="rId47" display="VIDEO"/>
-    <hyperlink ref="K33" r:id="rId48" display="PDF"/>
-    <hyperlink ref="L33" r:id="rId49" display="VIDEO"/>
-    <hyperlink ref="K34" r:id="rId50" display="PDF"/>
-    <hyperlink ref="L34" r:id="rId51" display="VIDEO"/>
-    <hyperlink ref="K35" r:id="rId52" display="PDF"/>
-    <hyperlink ref="L35" r:id="rId53" display="VIDEO"/>
-    <hyperlink ref="K37" r:id="rId54" display="PDF"/>
-    <hyperlink ref="L37" r:id="rId55" display="VIDEO"/>
-    <hyperlink ref="K38" r:id="rId56" display="PDF"/>
-    <hyperlink ref="L38" r:id="rId57" display="VIDEO"/>
-    <hyperlink ref="K39" r:id="rId58" display="PDF"/>
-    <hyperlink ref="K40" r:id="rId59" display="PDF"/>
-    <hyperlink ref="L40" r:id="rId60" display="VIDEO"/>
-    <hyperlink ref="N40" r:id="rId61" display="CODE"/>
-    <hyperlink ref="O40" r:id="rId62" display="CODE"/>
-    <hyperlink ref="L41" r:id="rId63" display="VIDEO"/>
-    <hyperlink ref="N41" r:id="rId64" display="CODE"/>
-    <hyperlink ref="K42" r:id="rId65" display="CODE"/>
-    <hyperlink ref="L42" r:id="rId66" display="VIDEO"/>
-    <hyperlink ref="K44" r:id="rId67" display="PDF"/>
-    <hyperlink ref="L44" r:id="rId68" display="VIDEO"/>
-    <hyperlink ref="N44" r:id="rId69" display="CODE"/>
-    <hyperlink ref="K45" r:id="rId70" display="PDF"/>
-    <hyperlink ref="K46" r:id="rId71" display="CODE"/>
-    <hyperlink ref="K47" r:id="rId72" display="CODE"/>
-    <hyperlink ref="K48" r:id="rId73" display="VIDEO"/>
-    <hyperlink ref="K49" r:id="rId74" display="PDF"/>
-    <hyperlink ref="L49" r:id="rId75" display="VIDEO"/>
-    <hyperlink ref="N49" r:id="rId76" display="CODE"/>
-    <hyperlink ref="L51" r:id="rId77" display="VIDEO"/>
-    <hyperlink ref="N51" r:id="rId78" display="CODE"/>
-    <hyperlink ref="N52" r:id="rId79" display="CODE"/>
-    <hyperlink ref="N53" r:id="rId80" display="CODE"/>
-    <hyperlink ref="K56" r:id="rId81" display="PDF"/>
-    <hyperlink ref="K57" r:id="rId82" display="PDF"/>
-    <hyperlink ref="K58" r:id="rId83" display="PDF"/>
-    <hyperlink ref="K59" r:id="rId84" display="PDF"/>
-    <hyperlink ref="K60" r:id="rId85" display="PDF"/>
-    <hyperlink ref="K61" r:id="rId86" display="PDF"/>
-    <hyperlink ref="K62" r:id="rId87" display="PDF"/>
-    <hyperlink ref="K63" r:id="rId88" display="PDF"/>
-    <hyperlink ref="N63" r:id="rId89" display="CODE"/>
-    <hyperlink ref="K64" r:id="rId90" display="PDF"/>
-    <hyperlink ref="K65" r:id="rId91" display="PDF"/>
-    <hyperlink ref="K66" r:id="rId92" display="PDF"/>
-    <hyperlink ref="L66" r:id="rId93" display="VIDEO"/>
-    <hyperlink ref="K67" r:id="rId94" display="PDF"/>
-    <hyperlink ref="L67" r:id="rId95" display="VIDEO"/>
-    <hyperlink ref="K68" r:id="rId96" display="PDF"/>
-    <hyperlink ref="L68" r:id="rId97" display="VIDEO"/>
-    <hyperlink ref="K70" r:id="rId98" display="PDF"/>
-    <hyperlink ref="L70" r:id="rId99" display="VIDEO"/>
-    <hyperlink ref="K71" r:id="rId100" display="PDF"/>
-    <hyperlink ref="L71" r:id="rId101" display="VIDEO"/>
-    <hyperlink ref="K72" r:id="rId102" display="PDF"/>
-    <hyperlink ref="L72" r:id="rId103" display="VIDEO"/>
-    <hyperlink ref="K73" r:id="rId104" display="PDF"/>
-    <hyperlink ref="L73" r:id="rId105" display="VIDEO"/>
-    <hyperlink ref="K74" r:id="rId106" display="PDF"/>
-    <hyperlink ref="K76" r:id="rId107" display="PDF"/>
-    <hyperlink ref="L76" r:id="rId108" display="VIDEO"/>
-    <hyperlink ref="K77" r:id="rId109" display="PDF"/>
-    <hyperlink ref="L77" r:id="rId110" display="VIDEO"/>
-    <hyperlink ref="K78" r:id="rId111" display="PDF"/>
-    <hyperlink ref="L78" r:id="rId112" display="VIDEO"/>
-    <hyperlink ref="K79" r:id="rId113" display="PDF"/>
-    <hyperlink ref="L79" r:id="rId114" display="VIDEO"/>
-    <hyperlink ref="K80" r:id="rId115" display="PDF"/>
-    <hyperlink ref="L80" r:id="rId116" display="VIDEO"/>
-    <hyperlink ref="L81" r:id="rId117" display="VIDEO"/>
-    <hyperlink ref="M81" r:id="rId118" display="VIDEO"/>
-    <hyperlink ref="K83" r:id="rId119" display="PDF"/>
-    <hyperlink ref="K84" r:id="rId120" display="PDF"/>
-    <hyperlink ref="K85" r:id="rId121" display="PDF"/>
-    <hyperlink ref="L85" r:id="rId122" display="VIDEO"/>
-    <hyperlink ref="K87" r:id="rId123" display="PDF"/>
-    <hyperlink ref="K89" r:id="rId124" display="PDF"/>
-    <hyperlink ref="K90" r:id="rId125" display="PDF"/>
-    <hyperlink ref="K92" r:id="rId126" display="PDF"/>
-    <hyperlink ref="K93" r:id="rId127" display="PDF"/>
-    <hyperlink ref="L93" r:id="rId128" display="VIDEO"/>
-    <hyperlink ref="N93" r:id="rId129" display="CODE"/>
-    <hyperlink ref="K95" r:id="rId130" display="PDF"/>
-    <hyperlink ref="L95" r:id="rId131" display="VIDEO"/>
-    <hyperlink ref="K96" r:id="rId132" display="PDF"/>
-    <hyperlink ref="L96" r:id="rId133" display="VIDEO"/>
-    <hyperlink ref="K97" r:id="rId134" display="PDF"/>
-    <hyperlink ref="L97" r:id="rId135" display="VIDEO"/>
-    <hyperlink ref="K98" r:id="rId136" display="PDF"/>
-    <hyperlink ref="L98" r:id="rId137" display="VIDEO"/>
-    <hyperlink ref="K100" r:id="rId138" display="PDF"/>
-    <hyperlink ref="L100" r:id="rId139" display="VIDEO"/>
-    <hyperlink ref="K101" r:id="rId140" display="PDF"/>
-    <hyperlink ref="K102" r:id="rId141" display="PDF"/>
-    <hyperlink ref="L102" r:id="rId142" display="VIDEO"/>
-    <hyperlink ref="K103" r:id="rId143" display="PDF"/>
-    <hyperlink ref="L103" r:id="rId144" display="VIDEO"/>
-    <hyperlink ref="K104" r:id="rId145" display="PDF"/>
-    <hyperlink ref="L104" r:id="rId146" display="VIDEO"/>
-    <hyperlink ref="K105" r:id="rId147" display="PDF"/>
-    <hyperlink ref="L105" r:id="rId148" display="VIDEO"/>
-    <hyperlink ref="K106" r:id="rId149" display="PDF"/>
-    <hyperlink ref="L106" r:id="rId150" display="VIDEO"/>
-    <hyperlink ref="K107" r:id="rId151" display="PDF"/>
-    <hyperlink ref="L107" r:id="rId152" display="VIDEO"/>
-    <hyperlink ref="K108" r:id="rId153" display="PDF"/>
-    <hyperlink ref="L108" r:id="rId154" display="VIDEO"/>
-    <hyperlink ref="K110" r:id="rId155" display="PDF"/>
-    <hyperlink ref="L110" r:id="rId156" display="VIDEO"/>
-    <hyperlink ref="K111" r:id="rId157" display="PDF"/>
-    <hyperlink ref="L111" r:id="rId158" display="VIDEO"/>
-    <hyperlink ref="K112" r:id="rId159" display="PDF"/>
-    <hyperlink ref="L112" r:id="rId160" display="VIDEO"/>
-    <hyperlink ref="N112" r:id="rId161" display="CODE"/>
-    <hyperlink ref="K113" r:id="rId162" display="PDF"/>
-    <hyperlink ref="L113" r:id="rId163" display="VIDEO"/>
-    <hyperlink ref="N113" r:id="rId164" display="CODE"/>
-    <hyperlink ref="K114" r:id="rId165" display="PDF"/>
-    <hyperlink ref="L114" r:id="rId166" display="VIDEO"/>
-    <hyperlink ref="K115" r:id="rId167" display="PDF"/>
-    <hyperlink ref="L115" r:id="rId168" display="VIDEO"/>
-    <hyperlink ref="K117" r:id="rId169" display="PDF"/>
-    <hyperlink ref="L117" r:id="rId170" display="VIDEO"/>
-    <hyperlink ref="K118" r:id="rId171" display="PDF"/>
-    <hyperlink ref="L118" r:id="rId172" display="VIDEO"/>
-    <hyperlink ref="L119" r:id="rId173" display="VIDEO"/>
-    <hyperlink ref="N119" r:id="rId174" display="CODE"/>
-    <hyperlink ref="K121" r:id="rId175" display="PDF"/>
-    <hyperlink ref="L121" r:id="rId176" display="VIDEO"/>
-    <hyperlink ref="K122" r:id="rId177" display="PDF"/>
-    <hyperlink ref="L122" r:id="rId178" display="VIDEO"/>
-    <hyperlink ref="N122" r:id="rId179" display="CODE"/>
-    <hyperlink ref="K123" r:id="rId180" display="PDF"/>
-    <hyperlink ref="L123" r:id="rId181" display="VIDEO"/>
-    <hyperlink ref="N123" r:id="rId182" display="CODE"/>
-    <hyperlink ref="K124" r:id="rId183" display="PDF"/>
-    <hyperlink ref="K125" r:id="rId184" display="PDF"/>
-    <hyperlink ref="K126" r:id="rId185" display="PDF"/>
+    <hyperlink ref="K5" r:id="rId2" display="PDF"/>
+    <hyperlink ref="K6" r:id="rId3" display="PDF"/>
+    <hyperlink ref="L6" r:id="rId4" display="VIDEO"/>
+    <hyperlink ref="K7" r:id="rId5" display="PDF"/>
+    <hyperlink ref="L7" r:id="rId6" display="VIDEO"/>
+    <hyperlink ref="K8" r:id="rId7" display="PDF"/>
+    <hyperlink ref="L8" r:id="rId8" display="VIDEO"/>
+    <hyperlink ref="K10" r:id="rId9" display="PDF"/>
+    <hyperlink ref="L10" r:id="rId10" display="VIDEO"/>
+    <hyperlink ref="K12" r:id="rId11" display="PDF"/>
+    <hyperlink ref="L12" r:id="rId12" display="VIDEO"/>
+    <hyperlink ref="K13" r:id="rId13" display="PDF"/>
+    <hyperlink ref="L13" r:id="rId14" display="VIDEO"/>
+    <hyperlink ref="K14" r:id="rId15" display="PDF"/>
+    <hyperlink ref="L14" r:id="rId16" display="VIDEO"/>
+    <hyperlink ref="K15" r:id="rId17" display="PDF"/>
+    <hyperlink ref="L15" r:id="rId18" display="VIDEO"/>
+    <hyperlink ref="K16" r:id="rId19" display="PDF"/>
+    <hyperlink ref="L16" r:id="rId20" display="VIDEO"/>
+    <hyperlink ref="K17" r:id="rId21" display="PDF"/>
+    <hyperlink ref="L17" r:id="rId22" display="VIDEO"/>
+    <hyperlink ref="K18" r:id="rId23" display="PDF"/>
+    <hyperlink ref="L18" r:id="rId24" display="VIDEO"/>
+    <hyperlink ref="L19" r:id="rId25" display="VIDEO"/>
+    <hyperlink ref="L20" r:id="rId26" display="VIDEO"/>
+    <hyperlink ref="N20" r:id="rId27" display="CODE"/>
+    <hyperlink ref="L22" r:id="rId28" display="VIDEO"/>
+    <hyperlink ref="N22" r:id="rId29" display="CODE"/>
+    <hyperlink ref="K23" r:id="rId30" display="PDF"/>
+    <hyperlink ref="L23" r:id="rId31" display="VIDEO"/>
+    <hyperlink ref="N23" r:id="rId32" display="CODE"/>
+    <hyperlink ref="K24" r:id="rId33" display="PDF"/>
+    <hyperlink ref="L25" r:id="rId34" display="VIDEO"/>
+    <hyperlink ref="N25" r:id="rId35" display="CODE"/>
+    <hyperlink ref="K26" r:id="rId36" display="CODE"/>
+    <hyperlink ref="L26" r:id="rId37" display="VIDEO"/>
+    <hyperlink ref="K27" r:id="rId38" display="PDF"/>
+    <hyperlink ref="L27" r:id="rId39" display="VIDEO"/>
+    <hyperlink ref="K28" r:id="rId40" display="PDF"/>
+    <hyperlink ref="L28" r:id="rId41" display="VIDEO"/>
+    <hyperlink ref="K29" r:id="rId42" display="PDF"/>
+    <hyperlink ref="L29" r:id="rId43" display="VIDEO"/>
+    <hyperlink ref="M29" r:id="rId44" display="VIDEO"/>
+    <hyperlink ref="K30" r:id="rId45" display="VIDEO"/>
+    <hyperlink ref="K31" r:id="rId46" display="PDF"/>
+    <hyperlink ref="L31" r:id="rId47" display="VIDEO"/>
+    <hyperlink ref="K32" r:id="rId48" display="PDF"/>
+    <hyperlink ref="L32" r:id="rId49" display="VIDEO"/>
+    <hyperlink ref="K33" r:id="rId50" display="PDF"/>
+    <hyperlink ref="L33" r:id="rId51" display="VIDEO"/>
+    <hyperlink ref="K34" r:id="rId52" display="PDF"/>
+    <hyperlink ref="L34" r:id="rId53" display="VIDEO"/>
+    <hyperlink ref="K36" r:id="rId54" display="PDF"/>
+    <hyperlink ref="L36" r:id="rId55" display="VIDEO"/>
+    <hyperlink ref="K37" r:id="rId56" display="PDF"/>
+    <hyperlink ref="L37" r:id="rId57" display="VIDEO"/>
+    <hyperlink ref="K38" r:id="rId58" display="PDF"/>
+    <hyperlink ref="K39" r:id="rId59" display="PDF"/>
+    <hyperlink ref="L39" r:id="rId60" display="VIDEO"/>
+    <hyperlink ref="N39" r:id="rId61" display="CODE"/>
+    <hyperlink ref="O39" r:id="rId62" display="CODE"/>
+    <hyperlink ref="L40" r:id="rId63" display="VIDEO"/>
+    <hyperlink ref="N40" r:id="rId64" display="CODE"/>
+    <hyperlink ref="K41" r:id="rId65" display="CODE"/>
+    <hyperlink ref="L41" r:id="rId66" display="VIDEO"/>
+    <hyperlink ref="K43" r:id="rId67" display="PDF"/>
+    <hyperlink ref="L43" r:id="rId68" display="VIDEO"/>
+    <hyperlink ref="N43" r:id="rId69" display="CODE"/>
+    <hyperlink ref="K44" r:id="rId70" display="PDF"/>
+    <hyperlink ref="K45" r:id="rId71" display="CODE"/>
+    <hyperlink ref="K46" r:id="rId72" display="CODE"/>
+    <hyperlink ref="K47" r:id="rId73" display="VIDEO"/>
+    <hyperlink ref="K48" r:id="rId74" display="PDF"/>
+    <hyperlink ref="L48" r:id="rId75" display="VIDEO"/>
+    <hyperlink ref="N48" r:id="rId76" display="CODE"/>
+    <hyperlink ref="L50" r:id="rId77" display="VIDEO"/>
+    <hyperlink ref="N50" r:id="rId78" display="CODE"/>
+    <hyperlink ref="N51" r:id="rId79" display="CODE"/>
+    <hyperlink ref="N52" r:id="rId80" display="CODE"/>
+    <hyperlink ref="K55" r:id="rId81" display="PDF"/>
+    <hyperlink ref="K56" r:id="rId82" display="PDF"/>
+    <hyperlink ref="K57" r:id="rId83" display="PDF"/>
+    <hyperlink ref="K58" r:id="rId84" display="PDF"/>
+    <hyperlink ref="K59" r:id="rId85" display="PDF"/>
+    <hyperlink ref="K60" r:id="rId86" display="PDF"/>
+    <hyperlink ref="K61" r:id="rId87" display="PDF"/>
+    <hyperlink ref="K62" r:id="rId88" display="PDF"/>
+    <hyperlink ref="N62" r:id="rId89" display="CODE"/>
+    <hyperlink ref="K63" r:id="rId90" display="PDF"/>
+    <hyperlink ref="K64" r:id="rId91" display="PDF"/>
+    <hyperlink ref="K65" r:id="rId92" display="PDF"/>
+    <hyperlink ref="L65" r:id="rId93" display="VIDEO"/>
+    <hyperlink ref="K66" r:id="rId94" display="PDF"/>
+    <hyperlink ref="L66" r:id="rId95" display="VIDEO"/>
+    <hyperlink ref="K67" r:id="rId96" display="PDF"/>
+    <hyperlink ref="L67" r:id="rId97" display="VIDEO"/>
+    <hyperlink ref="K69" r:id="rId98" display="PDF"/>
+    <hyperlink ref="L69" r:id="rId99" display="VIDEO"/>
+    <hyperlink ref="K70" r:id="rId100" display="PDF"/>
+    <hyperlink ref="L70" r:id="rId101" display="VIDEO"/>
+    <hyperlink ref="K71" r:id="rId102" display="PDF"/>
+    <hyperlink ref="L71" r:id="rId103" display="VIDEO"/>
+    <hyperlink ref="K72" r:id="rId104" display="PDF"/>
+    <hyperlink ref="L72" r:id="rId105" display="VIDEO"/>
+    <hyperlink ref="K73" r:id="rId106" display="PDF"/>
+    <hyperlink ref="K75" r:id="rId107" display="PDF"/>
+    <hyperlink ref="L75" r:id="rId108" display="VIDEO"/>
+    <hyperlink ref="K76" r:id="rId109" display="PDF"/>
+    <hyperlink ref="L76" r:id="rId110" display="VIDEO"/>
+    <hyperlink ref="K77" r:id="rId111" display="PDF"/>
+    <hyperlink ref="L77" r:id="rId112" display="VIDEO"/>
+    <hyperlink ref="K78" r:id="rId113" display="PDF"/>
+    <hyperlink ref="L78" r:id="rId114" display="VIDEO"/>
+    <hyperlink ref="K79" r:id="rId115" display="PDF"/>
+    <hyperlink ref="L79" r:id="rId116" display="VIDEO"/>
+    <hyperlink ref="L80" r:id="rId117" display="VIDEO"/>
+    <hyperlink ref="M80" r:id="rId118" display="VIDEO"/>
+    <hyperlink ref="K82" r:id="rId119" display="PDF"/>
+    <hyperlink ref="K83" r:id="rId120" display="PDF"/>
+    <hyperlink ref="K84" r:id="rId121" display="PDF"/>
+    <hyperlink ref="L84" r:id="rId122" display="VIDEO"/>
+    <hyperlink ref="K86" r:id="rId123" display="PDF"/>
+    <hyperlink ref="K88" r:id="rId124" display="PDF"/>
+    <hyperlink ref="K89" r:id="rId125" display="PDF"/>
+    <hyperlink ref="K91" r:id="rId126" display="PDF"/>
+    <hyperlink ref="K92" r:id="rId127" display="PDF"/>
+    <hyperlink ref="L92" r:id="rId128" display="VIDEO"/>
+    <hyperlink ref="N92" r:id="rId129" display="CODE"/>
+    <hyperlink ref="K94" r:id="rId130" display="PDF"/>
+    <hyperlink ref="L94" r:id="rId131" display="VIDEO"/>
+    <hyperlink ref="K95" r:id="rId132" display="PDF"/>
+    <hyperlink ref="L95" r:id="rId133" display="VIDEO"/>
+    <hyperlink ref="K96" r:id="rId134" display="PDF"/>
+    <hyperlink ref="L96" r:id="rId135" display="VIDEO"/>
+    <hyperlink ref="K97" r:id="rId136" display="PDF"/>
+    <hyperlink ref="L97" r:id="rId137" display="VIDEO"/>
+    <hyperlink ref="K99" r:id="rId138" display="PDF"/>
+    <hyperlink ref="L99" r:id="rId139" display="VIDEO"/>
+    <hyperlink ref="K100" r:id="rId140" display="PDF"/>
+    <hyperlink ref="K101" r:id="rId141" display="PDF"/>
+    <hyperlink ref="L101" r:id="rId142" display="VIDEO"/>
+    <hyperlink ref="K102" r:id="rId143" display="PDF"/>
+    <hyperlink ref="L102" r:id="rId144" display="VIDEO"/>
+    <hyperlink ref="K103" r:id="rId145" display="PDF"/>
+    <hyperlink ref="L103" r:id="rId146" display="VIDEO"/>
+    <hyperlink ref="K104" r:id="rId147" display="PDF"/>
+    <hyperlink ref="L104" r:id="rId148" display="VIDEO"/>
+    <hyperlink ref="K105" r:id="rId149" display="PDF"/>
+    <hyperlink ref="L105" r:id="rId150" display="VIDEO"/>
+    <hyperlink ref="K106" r:id="rId151" display="PDF"/>
+    <hyperlink ref="L106" r:id="rId152" display="VIDEO"/>
+    <hyperlink ref="K107" r:id="rId153" display="PDF"/>
+    <hyperlink ref="L107" r:id="rId154" display="VIDEO"/>
+    <hyperlink ref="K109" r:id="rId155" display="PDF"/>
+    <hyperlink ref="L109" r:id="rId156" display="VIDEO"/>
+    <hyperlink ref="K110" r:id="rId157" display="PDF"/>
+    <hyperlink ref="L110" r:id="rId158" display="VIDEO"/>
+    <hyperlink ref="K111" r:id="rId159" display="PDF"/>
+    <hyperlink ref="L111" r:id="rId160" display="VIDEO"/>
+    <hyperlink ref="N111" r:id="rId161" display="CODE"/>
+    <hyperlink ref="K112" r:id="rId162" display="PDF"/>
+    <hyperlink ref="L112" r:id="rId163" display="VIDEO"/>
+    <hyperlink ref="N112" r:id="rId164" display="CODE"/>
+    <hyperlink ref="K113" r:id="rId165" display="PDF"/>
+    <hyperlink ref="L113" r:id="rId166" display="VIDEO"/>
+    <hyperlink ref="K114" r:id="rId167" display="PDF"/>
+    <hyperlink ref="L114" r:id="rId168" display="VIDEO"/>
+    <hyperlink ref="K116" r:id="rId169" display="PDF"/>
+    <hyperlink ref="L116" r:id="rId170" display="VIDEO"/>
+    <hyperlink ref="K117" r:id="rId171" display="PDF"/>
+    <hyperlink ref="L117" r:id="rId172" display="VIDEO"/>
+    <hyperlink ref="L118" r:id="rId173" display="VIDEO"/>
+    <hyperlink ref="N118" r:id="rId174" display="CODE"/>
+    <hyperlink ref="K120" r:id="rId175" display="PDF"/>
+    <hyperlink ref="L120" r:id="rId176" display="VIDEO"/>
+    <hyperlink ref="K121" r:id="rId177" display="PDF"/>
+    <hyperlink ref="L121" r:id="rId178" display="VIDEO"/>
+    <hyperlink ref="N121" r:id="rId179" display="CODE"/>
+    <hyperlink ref="K122" r:id="rId180" display="PDF"/>
+    <hyperlink ref="L122" r:id="rId181" display="VIDEO"/>
+    <hyperlink ref="N122" r:id="rId182" display="CODE"/>
+    <hyperlink ref="K123" r:id="rId183" display="PDF"/>
+    <hyperlink ref="K124" r:id="rId184" display="PDF"/>
+    <hyperlink ref="K125" r:id="rId185" display="PDF"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.700694444444444" right="0.700694444444444" top="0.7875" bottom="0.7875" header="0.511805555555555" footer="0.511805555555555"/>
@@ -9997,7 +10150,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10007,7 +10160,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -10022,18 +10175,18 @@
       <c r="B6" s="24"/>
       <c r="C6" s="8"/>
       <c r="E6" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
         <v>27</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10042,10 +10195,10 @@
       <c r="C7" s="8"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>391</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>392</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
@@ -10059,10 +10212,10 @@
       <c r="C8" s="8"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>393</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>394</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8" t="s">
@@ -10075,7 +10228,7 @@
       <c r="B9" s="24"/>
       <c r="C9" s="8"/>
       <c r="E9" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="5"/>
@@ -10084,7 +10237,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10093,7 +10246,7 @@
       <c r="C10" s="8"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>39</v>
@@ -10103,7 +10256,7 @@
         <v>45</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10112,17 +10265,17 @@
       <c r="C11" s="8"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>398</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>399</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10130,11 +10283,11 @@
       <c r="B12" s="24"/>
       <c r="C12" s="8"/>
       <c r="E12" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="8" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8" t="s">
@@ -10148,10 +10301,10 @@
       <c r="C13" s="8"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8" t="s">
@@ -10165,10 +10318,10 @@
       <c r="C14" s="8"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8" t="s">
@@ -10182,14 +10335,14 @@
       <c r="C15" s="8"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J15" s="8"/>
     </row>
@@ -10198,7 +10351,7 @@
       <c r="B16" s="24"/>
       <c r="C16" s="8"/>
       <c r="E16" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="5"/>
@@ -10211,7 +10364,7 @@
       <c r="B17" s="24"/>
       <c r="C17" s="8"/>
       <c r="E17" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="8"/>
@@ -10220,8 +10373,8 @@
       <c r="J17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="32"/>
-      <c r="B18" s="32"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
@@ -10234,13 +10387,13 @@
         <v>79</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>83</v>

--- a/server_nestjs/src/storage/Kompetenzraster.xlsx
+++ b/server_nestjs/src/storage/Kompetenzraster.xlsx
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="413">
   <si>
     <t xml:space="preserve">Voraussetzungen lt. Modulhandbuch</t>
   </si>
@@ -688,9 +688,6 @@
     <t xml:space="preserve">2,3</t>
   </si>
   <si>
-    <t xml:space="preserve">Beispielhafte Beschreibung</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,3,4</t>
   </si>
   <si>
@@ -901,7 +898,19 @@
     <t xml:space="preserve">Der Befehl map nimmt eine Funktion und ein iterierbares Objekt (z.B. Liste oder Tupel) entgegen und wendet die Funktion auf jedes Element des iterierbaren Objektes an. Genauer, bekommen wir einen Iterator zurück über welchen wir iterieren können oder Methoden wie __next__() aufrufen.</t>
   </si>
   <si>
+    <t xml:space="preserve">Beschreibung PDF</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,35,37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beschreibung CODE 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beschreibung CODE 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beschreibung VIDEO</t>
   </si>
   <si>
     <t xml:space="preserve">2,35,38</t>
@@ -1484,7 +1493,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="65">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1641,8 +1650,16 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1669,6 +1686,14 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1679,6 +1704,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1719,6 +1748,10 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5413,14 +5446,12 @@
         <v>3</v>
       </c>
       <c r="I4" s="38"/>
-      <c r="J4" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
       <c r="P4" s="12"/>
       <c r="Q4" s="12"/>
       <c r="R4" s="15"/>
@@ -5435,9 +5466,9 @@
       </c>
       <c r="D5" s="35"/>
       <c r="E5" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="F5" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" s="40" t="s">
         <v>86</v>
       </c>
       <c r="G5" s="34" t="n">
@@ -5450,16 +5481,16 @@
         <v>1</v>
       </c>
       <c r="J5" s="12"/>
-      <c r="K5" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
+      <c r="K5" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
       <c r="P5" s="12"/>
       <c r="Q5" s="12"/>
-      <c r="R5" s="40"/>
+      <c r="R5" s="42"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="34" t="n">
@@ -5471,9 +5502,9 @@
       </c>
       <c r="D6" s="35"/>
       <c r="E6" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="F6" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" s="40" t="s">
         <v>88</v>
       </c>
       <c r="G6" s="34" t="n">
@@ -5486,102 +5517,102 @@
         <v>1</v>
       </c>
       <c r="J6" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="K6" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="K6" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M6" s="14"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
-      <c r="R6" s="40"/>
+      <c r="R6" s="42"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="41" t="n">
+      <c r="A7" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="42" t="n">
+      <c r="B7" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="41" t="n">
+      <c r="C7" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43" t="s">
+      <c r="D7" s="45"/>
+      <c r="E7" s="45" t="s">
+        <v>202</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="F7" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M7" s="17"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
+      <c r="K7" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M7" s="48"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
-      <c r="R7" s="40"/>
+      <c r="R7" s="42"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="41" t="n">
+      <c r="A8" s="43" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="41" t="n">
+      <c r="B8" s="44"/>
+      <c r="C8" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43" t="s">
+      <c r="D8" s="45"/>
+      <c r="E8" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="G8" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="F8" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="G8" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M8" s="17"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
+      <c r="K8" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L8" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M8" s="48"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
-      <c r="R8" s="47"/>
+      <c r="R8" s="51"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="34" t="n">
@@ -5593,7 +5624,7 @@
       <c r="C9" s="34"/>
       <c r="D9" s="21"/>
       <c r="E9" s="21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F9" s="24" t="s">
         <v>92</v>
@@ -5604,18 +5635,18 @@
       <c r="H9" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="48"/>
+      <c r="I9" s="52"/>
       <c r="J9" s="12"/>
-      <c r="K9" s="14" t="s">
+      <c r="K9" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="53"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="53"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="40"/>
+      <c r="R9" s="42"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="34" t="n">
@@ -5627,35 +5658,35 @@
       </c>
       <c r="D10" s="24"/>
       <c r="E10" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="F10" s="49" t="s">
+        <v>207</v>
+      </c>
+      <c r="F10" s="54" t="s">
         <v>93</v>
       </c>
       <c r="G10" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="H10" s="50" t="n">
+      <c r="H10" s="55" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M10" s="14"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
+        <v>208</v>
+      </c>
+      <c r="K10" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L10" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M10" s="41"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="53"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
-      <c r="R10" s="47"/>
+      <c r="R10" s="51"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="34" t="n">
@@ -5667,29 +5698,29 @@
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="F11" s="49" t="s">
+        <v>209</v>
+      </c>
+      <c r="F11" s="54" t="s">
         <v>94</v>
       </c>
       <c r="G11" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="H11" s="50" t="n">
+      <c r="H11" s="55" t="n">
         <v>3</v>
       </c>
       <c r="I11" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="8"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="53"/>
+      <c r="O11" s="53"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
-      <c r="R11" s="40"/>
+      <c r="R11" s="42"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="34" t="n">
@@ -5701,9 +5732,9 @@
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="F12" s="51" t="s">
+        <v>210</v>
+      </c>
+      <c r="F12" s="56" t="s">
         <v>133</v>
       </c>
       <c r="G12" s="34" t="n">
@@ -5716,20 +5747,20 @@
         <v>1</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="K12" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M12" s="14"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
+        <v>211</v>
+      </c>
+      <c r="K12" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M12" s="41"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
-      <c r="R12" s="40"/>
+      <c r="R12" s="42"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="n">
@@ -5741,9 +5772,9 @@
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="F13" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="F13" s="56" t="s">
         <v>134</v>
       </c>
       <c r="G13" s="34" t="n">
@@ -5756,20 +5787,20 @@
         <v>1</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M13" s="14"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
+        <v>213</v>
+      </c>
+      <c r="K13" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M13" s="41"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="53"/>
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
-      <c r="R13" s="40"/>
+      <c r="R13" s="42"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="34" t="n">
@@ -5781,10 +5812,10 @@
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="F14" s="56" t="s">
         <v>215</v>
-      </c>
-      <c r="F14" s="51" t="s">
-        <v>216</v>
       </c>
       <c r="G14" s="34" t="n">
         <v>10</v>
@@ -5796,20 +5827,20 @@
         <v>1</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M14" s="14"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
+        <v>216</v>
+      </c>
+      <c r="K14" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M14" s="41"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="53"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
-      <c r="R14" s="40"/>
+      <c r="R14" s="42"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="34" t="n">
@@ -5821,9 +5852,9 @@
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="F15" s="51" t="s">
+        <v>217</v>
+      </c>
+      <c r="F15" s="56" t="s">
         <v>101</v>
       </c>
       <c r="G15" s="34" t="n">
@@ -5836,20 +5867,20 @@
         <v>1</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M15" s="14"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
+        <v>218</v>
+      </c>
+      <c r="K15" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L15" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M15" s="41"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="53"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
-      <c r="R15" s="40"/>
+      <c r="R15" s="42"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="34" t="n">
@@ -5861,12 +5892,12 @@
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="F16" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="F16" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="48" t="n">
+      <c r="G16" s="52" t="n">
         <v>10</v>
       </c>
       <c r="H16" s="34" t="n">
@@ -5876,20 +5907,20 @@
         <v>1</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L16" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M16" s="14"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
+        <v>220</v>
+      </c>
+      <c r="K16" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L16" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M16" s="41"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="53"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
-      <c r="R16" s="40"/>
+      <c r="R16" s="42"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="34" t="n">
@@ -5901,9 +5932,9 @@
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="F17" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="F17" s="40" t="s">
         <v>97</v>
       </c>
       <c r="G17" s="34" t="n">
@@ -5916,20 +5947,20 @@
         <v>1</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L17" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M17" s="14"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
+        <v>222</v>
+      </c>
+      <c r="K17" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L17" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M17" s="41"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="53"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
-      <c r="R17" s="40"/>
+      <c r="R17" s="42"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="34" t="n">
@@ -5941,9 +5972,9 @@
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="24" t="s">
-        <v>224</v>
-      </c>
-      <c r="F18" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="F18" s="40" t="s">
         <v>98</v>
       </c>
       <c r="G18" s="34" t="n">
@@ -5956,234 +5987,234 @@
         <v>1</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L18" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M18" s="14"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
+        <v>224</v>
+      </c>
+      <c r="K18" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L18" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M18" s="41"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="53"/>
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
-      <c r="R18" s="40"/>
+      <c r="R18" s="42"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="41" t="n">
+      <c r="A19" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="C19" s="43" t="n">
+        <v>14</v>
+      </c>
+      <c r="D19" s="44"/>
+      <c r="E19" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="C19" s="41" t="n">
-        <v>14</v>
-      </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="23" t="s">
+      <c r="F19" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="G19" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="F19" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="G19" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M19" s="49"/>
+      <c r="N19" s="49"/>
+      <c r="O19" s="49"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
-      <c r="R19" s="40"/>
+      <c r="R19" s="42"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="41" t="n">
+      <c r="A20" s="43" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="41" t="n">
+      <c r="B20" s="44"/>
+      <c r="C20" s="43" t="n">
         <v>15</v>
       </c>
-      <c r="D20" s="42"/>
+      <c r="D20" s="44"/>
       <c r="E20" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="F20" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="H20" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="F20" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="G20" s="41" t="n">
-        <v>18</v>
-      </c>
-      <c r="H20" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="5" t="s">
+      <c r="K20" s="48"/>
+      <c r="L20" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M20" s="48"/>
+      <c r="N20" s="48" t="s">
         <v>230</v>
       </c>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="O20" s="17"/>
+      <c r="O20" s="48"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
-      <c r="R20" s="47"/>
+      <c r="R20" s="51"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="41" t="n">
+      <c r="A21" s="43" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="42" t="n">
+      <c r="B21" s="44" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="41" t="n">
+      <c r="C21" s="43" t="n">
         <v>16</v>
       </c>
-      <c r="D21" s="42" t="n">
+      <c r="D21" s="44" t="n">
         <v>19</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="F21" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="F21" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="41" t="n">
+      <c r="G21" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="H21" s="41" t="n">
+      <c r="H21" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="I21" s="41" t="n">
+      <c r="I21" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="20"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="49"/>
+      <c r="O21" s="49"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
-      <c r="R21" s="40"/>
+      <c r="R21" s="42"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="41" t="n">
+      <c r="A22" s="43" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="41" t="n">
+      <c r="B22" s="44"/>
+      <c r="C22" s="43" t="n">
         <v>17</v>
       </c>
-      <c r="D22" s="42"/>
+      <c r="D22" s="44"/>
       <c r="E22" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="F22" s="58" t="s">
         <v>233</v>
       </c>
-      <c r="F22" s="53" t="s">
+      <c r="G22" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="G22" s="41" t="n">
-        <v>20</v>
-      </c>
-      <c r="H22" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="O22" s="17"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M22" s="48"/>
+      <c r="N22" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="O22" s="48"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
-      <c r="R22" s="40"/>
+      <c r="R22" s="42"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="41" t="n">
+      <c r="A23" s="43" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="41" t="n">
+      <c r="B23" s="44"/>
+      <c r="C23" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="D23" s="42"/>
+      <c r="D23" s="44"/>
       <c r="E23" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="F23" s="58" t="s">
         <v>236</v>
       </c>
-      <c r="F23" s="53" t="s">
+      <c r="G23" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="G23" s="41" t="n">
-        <v>20</v>
-      </c>
-      <c r="H23" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="I23" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="K23" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L23" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="O23" s="17"/>
+      <c r="K23" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L23" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M23" s="48"/>
+      <c r="N23" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="O23" s="48"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
-      <c r="R23" s="47"/>
+      <c r="R23" s="51"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="34" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C24" s="34" t="n">
         <v>19</v>
       </c>
       <c r="D24" s="24"/>
       <c r="E24" s="24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F24" s="24" t="s">
         <v>108</v>
@@ -6198,16 +6229,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="8"/>
-      <c r="K24" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
+      <c r="K24" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="53"/>
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
-      <c r="R24" s="40"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="34"/>
@@ -6217,7 +6248,7 @@
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F25" s="24"/>
       <c r="G25" s="34"/>
@@ -6226,20 +6257,20 @@
         <v>1</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="K25" s="8"/>
-      <c r="L25" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="O25" s="14"/>
+        <v>240</v>
+      </c>
+      <c r="K25" s="53"/>
+      <c r="L25" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="O25" s="41"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
-      <c r="R25" s="40"/>
+      <c r="R25" s="42"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="34"/>
@@ -6249,9 +6280,9 @@
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="F26" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="F26" s="40" t="s">
         <v>109</v>
       </c>
       <c r="G26" s="34" t="n">
@@ -6262,20 +6293,20 @@
         <v>1</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="K26" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="L26" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M26" s="14"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
+        <v>241</v>
+      </c>
+      <c r="K26" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="L26" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M26" s="41"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="53"/>
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
-      <c r="R26" s="40"/>
+      <c r="R26" s="42"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="34" t="n">
@@ -6287,9 +6318,9 @@
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="F27" s="39" t="s">
+        <v>242</v>
+      </c>
+      <c r="F27" s="40" t="s">
         <v>110</v>
       </c>
       <c r="G27" s="34" t="n">
@@ -6302,20 +6333,20 @@
         <v>1</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="K27" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L27" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M27" s="14"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
+        <v>243</v>
+      </c>
+      <c r="K27" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L27" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M27" s="41"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53"/>
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
-      <c r="R27" s="40"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="34" t="n">
@@ -6327,9 +6358,9 @@
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="F28" s="39" t="s">
+        <v>244</v>
+      </c>
+      <c r="F28" s="40" t="s">
         <v>111</v>
       </c>
       <c r="G28" s="34" t="n">
@@ -6342,20 +6373,20 @@
         <v>1</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="K28" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M28" s="14"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
+        <v>245</v>
+      </c>
+      <c r="K28" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L28" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M28" s="41"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
-      <c r="R28" s="40"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="34" t="n">
@@ -6367,34 +6398,34 @@
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="F29" s="59" t="s">
+        <v>112</v>
+      </c>
+      <c r="G29" s="52" t="n">
+        <v>23</v>
+      </c>
+      <c r="H29" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="F29" s="54" t="s">
-        <v>112</v>
-      </c>
-      <c r="G29" s="48" t="n">
-        <v>23</v>
-      </c>
-      <c r="H29" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="I29" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="K29" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L29" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M29" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
+      <c r="K29" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L29" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M29" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="N29" s="53"/>
+      <c r="O29" s="53"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="8"/>
     </row>
@@ -6406,9 +6437,9 @@
       </c>
       <c r="D30" s="24"/>
       <c r="E30" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="F30" s="39" t="s">
+        <v>246</v>
+      </c>
+      <c r="F30" s="40" t="s">
         <v>113</v>
       </c>
       <c r="G30" s="34" t="n">
@@ -6419,16 +6450,16 @@
         <v>1</v>
       </c>
       <c r="J30" s="8"/>
-      <c r="K30" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
+      <c r="K30" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="L30" s="53"/>
+      <c r="M30" s="53"/>
+      <c r="N30" s="53"/>
+      <c r="O30" s="53"/>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
-      <c r="R30" s="40"/>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="34" t="n">
@@ -6440,9 +6471,9 @@
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="F31" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="F31" s="40" t="s">
         <v>114</v>
       </c>
       <c r="G31" s="34" t="n">
@@ -6455,20 +6486,20 @@
         <v>1</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L31" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
+        <v>249</v>
+      </c>
+      <c r="K31" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L31" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M31" s="53"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="53"/>
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
-      <c r="R31" s="40"/>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="34" t="n">
@@ -6480,9 +6511,9 @@
       </c>
       <c r="D32" s="24"/>
       <c r="E32" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="F32" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="F32" s="40" t="s">
         <v>73</v>
       </c>
       <c r="G32" s="34" t="n">
@@ -6495,102 +6526,102 @@
         <v>1</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L32" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
+        <v>251</v>
+      </c>
+      <c r="K32" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L32" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M32" s="53"/>
+      <c r="N32" s="53"/>
+      <c r="O32" s="53"/>
       <c r="P32" s="8"/>
       <c r="Q32" s="8"/>
-      <c r="R32" s="40"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="41" t="n">
+      <c r="A33" s="43" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="42" t="n">
+      <c r="B33" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="C33" s="41" t="n">
+      <c r="C33" s="43" t="n">
         <v>28</v>
       </c>
-      <c r="D33" s="42"/>
+      <c r="D33" s="44"/>
       <c r="E33" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="F33" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="G33" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="F33" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="G33" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="I33" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="K33" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L33" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
+      <c r="K33" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L33" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M33" s="49"/>
+      <c r="N33" s="49"/>
+      <c r="O33" s="49"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
-      <c r="R33" s="40"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="41" t="n">
+      <c r="A34" s="43" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="41" t="n">
+      <c r="B34" s="44"/>
+      <c r="C34" s="43" t="n">
         <v>29</v>
       </c>
-      <c r="D34" s="42"/>
+      <c r="D34" s="44"/>
       <c r="E34" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="F34" s="60" t="s">
+        <v>117</v>
+      </c>
+      <c r="G34" s="47" t="n">
+        <v>29</v>
+      </c>
+      <c r="H34" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="F34" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="G34" s="45" t="n">
-        <v>29</v>
-      </c>
-      <c r="H34" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="I34" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="K34" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L34" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
+      <c r="K34" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L34" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M34" s="49"/>
+      <c r="N34" s="49"/>
+      <c r="O34" s="49"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
-      <c r="R34" s="47"/>
+      <c r="R34" s="51"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="34" t="n">
@@ -6601,28 +6632,28 @@
       </c>
       <c r="C35" s="34"/>
       <c r="D35" s="24"/>
-      <c r="E35" s="56" t="s">
-        <v>257</v>
+      <c r="E35" s="61" t="s">
+        <v>256</v>
       </c>
       <c r="F35" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="48" t="n">
+      <c r="G35" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="48" t="n">
+      <c r="H35" s="52" t="n">
         <v>3</v>
       </c>
       <c r="I35" s="34"/>
       <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="8"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="53"/>
+      <c r="N35" s="53"/>
+      <c r="O35" s="53"/>
       <c r="P35" s="8"/>
       <c r="Q35" s="8"/>
-      <c r="R35" s="40"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="34" t="n">
@@ -6634,9 +6665,9 @@
       </c>
       <c r="D36" s="24"/>
       <c r="E36" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="F36" s="39" t="s">
+        <v>257</v>
+      </c>
+      <c r="F36" s="40" t="s">
         <v>118</v>
       </c>
       <c r="G36" s="34" t="n">
@@ -6649,20 +6680,20 @@
         <v>1</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="K36" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L36" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="8"/>
+        <v>258</v>
+      </c>
+      <c r="K36" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L36" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M36" s="53"/>
+      <c r="N36" s="53"/>
+      <c r="O36" s="53"/>
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
-      <c r="R36" s="40"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="34"/>
@@ -6671,10 +6702,10 @@
         <v>31</v>
       </c>
       <c r="D37" s="24"/>
-      <c r="E37" s="56" t="s">
-        <v>257</v>
-      </c>
-      <c r="F37" s="39" t="s">
+      <c r="E37" s="61" t="s">
+        <v>256</v>
+      </c>
+      <c r="F37" s="40" t="s">
         <v>109</v>
       </c>
       <c r="G37" s="34" t="n">
@@ -6685,20 +6716,20 @@
         <v>1</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L37" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
+        <v>259</v>
+      </c>
+      <c r="K37" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L37" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M37" s="53"/>
+      <c r="N37" s="53"/>
+      <c r="O37" s="53"/>
       <c r="P37" s="8"/>
       <c r="Q37" s="8"/>
-      <c r="R37" s="47"/>
+      <c r="R37" s="51"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="34" t="n">
@@ -6710,9 +6741,9 @@
       </c>
       <c r="D38" s="24"/>
       <c r="E38" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="F38" s="39" t="s">
+        <v>260</v>
+      </c>
+      <c r="F38" s="40" t="s">
         <v>119</v>
       </c>
       <c r="G38" s="34" t="n">
@@ -6725,130 +6756,130 @@
         <v>1</v>
       </c>
       <c r="J38" s="8"/>
-      <c r="K38" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L38" s="8"/>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8"/>
-      <c r="O38" s="8"/>
+      <c r="K38" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L38" s="53"/>
+      <c r="M38" s="53"/>
+      <c r="N38" s="53"/>
+      <c r="O38" s="53"/>
       <c r="P38" s="8"/>
       <c r="Q38" s="8"/>
-      <c r="R38" s="40"/>
+      <c r="R38" s="42"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="41" t="n">
+      <c r="A39" s="43" t="n">
         <v>34</v>
       </c>
-      <c r="B39" s="42" t="n">
+      <c r="B39" s="44" t="n">
         <v>23</v>
       </c>
-      <c r="C39" s="41" t="n">
+      <c r="C39" s="43" t="n">
         <v>33</v>
       </c>
-      <c r="D39" s="42"/>
+      <c r="D39" s="44"/>
       <c r="E39" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="F39" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="G39" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="F39" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G39" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="K39" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L39" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M39" s="5"/>
-      <c r="N39" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="O39" s="17" t="s">
-        <v>231</v>
+      <c r="K39" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L39" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M39" s="49"/>
+      <c r="N39" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="O39" s="48" t="s">
+        <v>230</v>
       </c>
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
-      <c r="R39" s="40"/>
+      <c r="R39" s="42"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="41"/>
-      <c r="B40" s="42"/>
-      <c r="C40" s="41" t="n">
+      <c r="A40" s="43"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="43" t="n">
         <v>34</v>
       </c>
-      <c r="D40" s="42"/>
+      <c r="D40" s="44"/>
       <c r="E40" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="F40" s="42"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="41"/>
-      <c r="I40" s="41" t="n">
+        <v>261</v>
+      </c>
+      <c r="F40" s="44"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="K40" s="5"/>
-      <c r="L40" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M40" s="5"/>
-      <c r="N40" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="O40" s="17"/>
+        <v>263</v>
+      </c>
+      <c r="K40" s="49"/>
+      <c r="L40" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M40" s="49"/>
+      <c r="N40" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="O40" s="48"/>
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
-      <c r="R40" s="40"/>
+      <c r="R40" s="42"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="41"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="41" t="n">
+      <c r="A41" s="43"/>
+      <c r="B41" s="44"/>
+      <c r="C41" s="43" t="n">
         <v>35</v>
       </c>
-      <c r="D41" s="42"/>
+      <c r="D41" s="44"/>
       <c r="E41" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="F41" s="46" t="s">
+        <v>261</v>
+      </c>
+      <c r="F41" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="G41" s="41" t="n">
+      <c r="G41" s="43" t="n">
         <v>34</v>
       </c>
-      <c r="H41" s="41"/>
-      <c r="I41" s="41" t="n">
+      <c r="H41" s="43"/>
+      <c r="I41" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="K41" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="L41" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
+        <v>264</v>
+      </c>
+      <c r="K41" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="L41" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M41" s="49"/>
+      <c r="N41" s="49"/>
+      <c r="O41" s="49"/>
       <c r="P41" s="5"/>
       <c r="Q41" s="5"/>
-      <c r="R41" s="47"/>
+      <c r="R41" s="51"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="34" t="n">
@@ -6858,7 +6889,7 @@
       <c r="C42" s="34"/>
       <c r="D42" s="24"/>
       <c r="E42" s="24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F42" s="24" t="s">
         <v>122</v>
@@ -6871,14 +6902,14 @@
       </c>
       <c r="I42" s="34"/>
       <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8"/>
-      <c r="O42" s="8"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="53"/>
+      <c r="M42" s="53"/>
+      <c r="N42" s="53"/>
+      <c r="O42" s="53"/>
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
-      <c r="R42" s="40"/>
+      <c r="R42" s="42"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="34" t="n">
@@ -6890,9 +6921,9 @@
       </c>
       <c r="D43" s="24"/>
       <c r="E43" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="F43" s="39" t="s">
+        <v>266</v>
+      </c>
+      <c r="F43" s="40" t="s">
         <v>123</v>
       </c>
       <c r="G43" s="34" t="n">
@@ -6905,22 +6936,22 @@
         <v>1</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="K43" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L43" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M43" s="8"/>
-      <c r="N43" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="O43" s="8"/>
+        <v>267</v>
+      </c>
+      <c r="K43" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L43" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M43" s="53"/>
+      <c r="N43" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="O43" s="53"/>
       <c r="P43" s="8"/>
       <c r="Q43" s="8"/>
-      <c r="R43" s="47"/>
+      <c r="R43" s="51"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="34" t="n">
@@ -6932,9 +6963,9 @@
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="F44" s="39" t="s">
+        <v>266</v>
+      </c>
+      <c r="F44" s="40" t="s">
         <v>124</v>
       </c>
       <c r="G44" s="34" t="n">
@@ -6947,16 +6978,18 @@
         <v>1</v>
       </c>
       <c r="J44" s="8"/>
-      <c r="K44" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L44" s="8"/>
-      <c r="M44" s="8"/>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
-      <c r="P44" s="8"/>
+      <c r="K44" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L44" s="53"/>
+      <c r="M44" s="53"/>
+      <c r="N44" s="53"/>
+      <c r="O44" s="53"/>
+      <c r="P44" s="8" t="s">
+        <v>268</v>
+      </c>
       <c r="Q44" s="8"/>
-      <c r="R44" s="47"/>
+      <c r="R44" s="51"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="34"/>
@@ -6968,23 +7001,25 @@
       <c r="E45" s="24" t="s">
         <v>269</v>
       </c>
-      <c r="F45" s="39"/>
+      <c r="F45" s="40"/>
       <c r="G45" s="34"/>
       <c r="H45" s="34"/>
       <c r="I45" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J45" s="8"/>
-      <c r="K45" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="L45" s="8"/>
-      <c r="M45" s="8"/>
-      <c r="N45" s="8"/>
-      <c r="O45" s="8"/>
-      <c r="P45" s="8"/>
+      <c r="K45" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="L45" s="53"/>
+      <c r="M45" s="53"/>
+      <c r="N45" s="53"/>
+      <c r="O45" s="53"/>
+      <c r="P45" s="8" t="s">
+        <v>270</v>
+      </c>
       <c r="Q45" s="8"/>
-      <c r="R45" s="47"/>
+      <c r="R45" s="51"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="34"/>
@@ -6996,23 +7031,25 @@
       <c r="E46" s="24" t="s">
         <v>269</v>
       </c>
-      <c r="F46" s="39"/>
+      <c r="F46" s="40"/>
       <c r="G46" s="34"/>
       <c r="H46" s="34"/>
       <c r="I46" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J46" s="8"/>
-      <c r="K46" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="L46" s="8"/>
-      <c r="M46" s="8"/>
-      <c r="N46" s="8"/>
-      <c r="O46" s="8"/>
-      <c r="P46" s="8"/>
+      <c r="K46" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="L46" s="53"/>
+      <c r="M46" s="53"/>
+      <c r="N46" s="53"/>
+      <c r="O46" s="53"/>
+      <c r="P46" s="8" t="s">
+        <v>271</v>
+      </c>
       <c r="Q46" s="8"/>
-      <c r="R46" s="47"/>
+      <c r="R46" s="51"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="34"/>
@@ -7024,23 +7061,25 @@
       <c r="E47" s="24" t="s">
         <v>269</v>
       </c>
-      <c r="F47" s="39"/>
+      <c r="F47" s="40"/>
       <c r="G47" s="34"/>
       <c r="H47" s="34"/>
       <c r="I47" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J47" s="8"/>
-      <c r="K47" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="L47" s="8"/>
-      <c r="M47" s="8"/>
-      <c r="N47" s="8"/>
-      <c r="O47" s="8"/>
-      <c r="P47" s="8"/>
+      <c r="K47" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="L47" s="53"/>
+      <c r="M47" s="53"/>
+      <c r="N47" s="53"/>
+      <c r="O47" s="53"/>
+      <c r="P47" s="8" t="s">
+        <v>272</v>
+      </c>
       <c r="Q47" s="8"/>
-      <c r="R47" s="40"/>
+      <c r="R47" s="42"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="34" t="n">
@@ -7052,9 +7091,9 @@
       </c>
       <c r="D48" s="24"/>
       <c r="E48" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="F48" s="39" t="s">
+        <v>273</v>
+      </c>
+      <c r="F48" s="40" t="s">
         <v>125</v>
       </c>
       <c r="G48" s="34" t="n">
@@ -7067,164 +7106,164 @@
         <v>1</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="K48" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L48" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M48" s="8"/>
-      <c r="N48" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="O48" s="8"/>
+        <v>274</v>
+      </c>
+      <c r="K48" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L48" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M48" s="53"/>
+      <c r="N48" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="O48" s="53"/>
       <c r="P48" s="8"/>
       <c r="Q48" s="8"/>
-      <c r="R48" s="47"/>
+      <c r="R48" s="51"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="41" t="n">
+      <c r="A49" s="43" t="n">
         <v>39</v>
       </c>
-      <c r="B49" s="42" t="n">
+      <c r="B49" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="C49" s="41"/>
-      <c r="D49" s="42"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="44"/>
       <c r="E49" s="23" t="s">
-        <v>272</v>
-      </c>
-      <c r="F49" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="F49" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="G49" s="41" t="n">
+      <c r="G49" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="41" t="n">
+      <c r="H49" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="I49" s="41"/>
+      <c r="I49" s="43"/>
       <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5"/>
-      <c r="M49" s="5"/>
-      <c r="N49" s="5"/>
-      <c r="O49" s="5"/>
+      <c r="K49" s="49"/>
+      <c r="L49" s="49"/>
+      <c r="M49" s="49"/>
+      <c r="N49" s="49"/>
+      <c r="O49" s="49"/>
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
-      <c r="R49" s="40"/>
+      <c r="R49" s="42"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="41" t="n">
+      <c r="A50" s="43" t="n">
         <v>40</v>
       </c>
-      <c r="B50" s="42"/>
-      <c r="C50" s="41" t="n">
+      <c r="B50" s="44"/>
+      <c r="C50" s="43" t="n">
         <v>42</v>
       </c>
-      <c r="D50" s="42"/>
+      <c r="D50" s="44"/>
       <c r="E50" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="F50" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="F50" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="G50" s="41" t="n">
+      <c r="G50" s="43" t="n">
         <v>39</v>
       </c>
-      <c r="H50" s="41" t="n">
+      <c r="H50" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="I50" s="41" t="n">
+      <c r="I50" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M50" s="5"/>
-      <c r="N50" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="O50" s="5"/>
+      <c r="K50" s="49"/>
+      <c r="L50" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M50" s="49"/>
+      <c r="N50" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="O50" s="49"/>
       <c r="P50" s="5"/>
       <c r="Q50" s="5"/>
-      <c r="R50" s="47"/>
+      <c r="R50" s="51"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="41" t="n">
+      <c r="A51" s="43" t="n">
         <v>41</v>
       </c>
-      <c r="B51" s="42"/>
-      <c r="C51" s="41" t="n">
+      <c r="B51" s="44"/>
+      <c r="C51" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="D51" s="42"/>
+      <c r="D51" s="44"/>
       <c r="E51" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="F51" s="46" t="s">
+        <v>277</v>
+      </c>
+      <c r="F51" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="G51" s="41" t="n">
+      <c r="G51" s="43" t="n">
         <v>39</v>
       </c>
-      <c r="H51" s="41" t="n">
+      <c r="H51" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="I51" s="41" t="n">
+      <c r="I51" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="O51" s="5"/>
+      <c r="K51" s="49"/>
+      <c r="L51" s="49"/>
+      <c r="M51" s="49"/>
+      <c r="N51" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="O51" s="49"/>
       <c r="P51" s="5"/>
       <c r="Q51" s="5"/>
-      <c r="R51" s="47"/>
+      <c r="R51" s="51"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="41" t="n">
+      <c r="A52" s="43" t="n">
         <v>42</v>
       </c>
-      <c r="B52" s="42"/>
-      <c r="C52" s="41" t="n">
+      <c r="B52" s="44"/>
+      <c r="C52" s="43" t="n">
         <v>44</v>
       </c>
-      <c r="D52" s="42"/>
+      <c r="D52" s="44"/>
       <c r="E52" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="F52" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="F52" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="G52" s="41" t="n">
+      <c r="G52" s="43" t="n">
         <v>39</v>
       </c>
-      <c r="H52" s="41" t="n">
+      <c r="H52" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="I52" s="41" t="n">
+      <c r="I52" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="O52" s="5"/>
+      <c r="K52" s="49"/>
+      <c r="L52" s="49"/>
+      <c r="M52" s="49"/>
+      <c r="N52" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="O52" s="49"/>
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
-      <c r="R52" s="47"/>
+      <c r="R52" s="51"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="28"/>
@@ -7236,7 +7275,12 @@
       <c r="G53" s="28"/>
       <c r="H53" s="28"/>
       <c r="I53" s="28"/>
-      <c r="R53" s="47"/>
+      <c r="K53" s="25"/>
+      <c r="L53" s="25"/>
+      <c r="M53" s="25"/>
+      <c r="N53" s="25"/>
+      <c r="O53" s="25"/>
+      <c r="R53" s="51"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="28" t="n">
@@ -7249,7 +7293,7 @@
         <v>43</v>
       </c>
       <c r="F54" s="31" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G54" s="30" t="n">
         <v>1</v>
@@ -7258,7 +7302,12 @@
         <v>5</v>
       </c>
       <c r="I54" s="28"/>
-      <c r="R54" s="47"/>
+      <c r="K54" s="25"/>
+      <c r="L54" s="25"/>
+      <c r="M54" s="25"/>
+      <c r="N54" s="25"/>
+      <c r="O54" s="25"/>
+      <c r="R54" s="51"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="34" t="n">
@@ -7270,67 +7319,67 @@
       </c>
       <c r="D55" s="24"/>
       <c r="E55" s="24" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F55" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="G55" s="48" t="n">
+      <c r="G55" s="52" t="n">
         <v>43</v>
       </c>
-      <c r="H55" s="48" t="n">
+      <c r="H55" s="52" t="n">
         <v>2</v>
       </c>
       <c r="I55" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J55" s="8"/>
-      <c r="K55" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L55" s="8"/>
-      <c r="M55" s="8"/>
-      <c r="N55" s="8"/>
-      <c r="O55" s="8"/>
+      <c r="K55" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L55" s="53"/>
+      <c r="M55" s="53"/>
+      <c r="N55" s="53"/>
+      <c r="O55" s="53"/>
       <c r="P55" s="8"/>
       <c r="Q55" s="8"/>
-      <c r="R55" s="47"/>
+      <c r="R55" s="51"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="41" t="n">
+      <c r="A56" s="43" t="n">
         <v>45</v>
       </c>
-      <c r="B56" s="42"/>
-      <c r="C56" s="41" t="n">
+      <c r="B56" s="44"/>
+      <c r="C56" s="43" t="n">
         <v>46</v>
       </c>
-      <c r="D56" s="42"/>
+      <c r="D56" s="44"/>
       <c r="E56" s="23" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F56" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="G56" s="41" t="n">
+      <c r="G56" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H56" s="41" t="n">
+      <c r="H56" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="41" t="n">
+      <c r="I56" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J56" s="5"/>
-      <c r="K56" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L56" s="5"/>
-      <c r="M56" s="5"/>
-      <c r="N56" s="5"/>
-      <c r="O56" s="5"/>
+      <c r="K56" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L56" s="49"/>
+      <c r="M56" s="49"/>
+      <c r="N56" s="49"/>
+      <c r="O56" s="49"/>
       <c r="P56" s="5"/>
       <c r="Q56" s="5"/>
-      <c r="R56" s="47"/>
+      <c r="R56" s="51"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="34" t="n">
@@ -7342,7 +7391,7 @@
       </c>
       <c r="D57" s="24"/>
       <c r="E57" s="24" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F57" s="24" t="s">
         <v>92</v>
@@ -7357,16 +7406,16 @@
         <v>1</v>
       </c>
       <c r="J57" s="8"/>
-      <c r="K57" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L57" s="8"/>
-      <c r="M57" s="8"/>
-      <c r="N57" s="8"/>
-      <c r="O57" s="8"/>
+      <c r="K57" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L57" s="53"/>
+      <c r="M57" s="53"/>
+      <c r="N57" s="53"/>
+      <c r="O57" s="53"/>
       <c r="P57" s="8"/>
       <c r="Q57" s="8"/>
-      <c r="R57" s="47"/>
+      <c r="R57" s="51"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="34" t="n">
@@ -7378,9 +7427,9 @@
       </c>
       <c r="D58" s="24"/>
       <c r="E58" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="F58" s="39" t="s">
+        <v>283</v>
+      </c>
+      <c r="F58" s="40" t="s">
         <v>133</v>
       </c>
       <c r="G58" s="34" t="n">
@@ -7393,16 +7442,16 @@
         <v>1</v>
       </c>
       <c r="J58" s="8"/>
-      <c r="K58" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L58" s="8"/>
-      <c r="M58" s="8"/>
-      <c r="N58" s="8"/>
-      <c r="O58" s="8"/>
+      <c r="K58" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L58" s="53"/>
+      <c r="M58" s="53"/>
+      <c r="N58" s="53"/>
+      <c r="O58" s="53"/>
       <c r="P58" s="8"/>
       <c r="Q58" s="8"/>
-      <c r="R58" s="47"/>
+      <c r="R58" s="51"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="34" t="n">
@@ -7416,9 +7465,9 @@
       </c>
       <c r="D59" s="24"/>
       <c r="E59" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="F59" s="39" t="s">
+        <v>284</v>
+      </c>
+      <c r="F59" s="40" t="s">
         <v>134</v>
       </c>
       <c r="G59" s="34" t="n">
@@ -7431,16 +7480,16 @@
         <v>1</v>
       </c>
       <c r="J59" s="8"/>
-      <c r="K59" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L59" s="8"/>
-      <c r="M59" s="8"/>
-      <c r="N59" s="8"/>
-      <c r="O59" s="8"/>
+      <c r="K59" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L59" s="53"/>
+      <c r="M59" s="53"/>
+      <c r="N59" s="53"/>
+      <c r="O59" s="53"/>
       <c r="P59" s="8"/>
       <c r="Q59" s="8"/>
-      <c r="R59" s="47"/>
+      <c r="R59" s="51"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="34" t="n">
@@ -7452,9 +7501,9 @@
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="F60" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="F60" s="40" t="s">
         <v>135</v>
       </c>
       <c r="G60" s="34" t="n">
@@ -7467,16 +7516,16 @@
         <v>1</v>
       </c>
       <c r="J60" s="8"/>
-      <c r="K60" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L60" s="8"/>
-      <c r="M60" s="8"/>
-      <c r="N60" s="8"/>
-      <c r="O60" s="8"/>
+      <c r="K60" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L60" s="53"/>
+      <c r="M60" s="53"/>
+      <c r="N60" s="53"/>
+      <c r="O60" s="53"/>
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
-      <c r="R60" s="47"/>
+      <c r="R60" s="51"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="34" t="n">
@@ -7488,9 +7537,9 @@
       </c>
       <c r="D61" s="24"/>
       <c r="E61" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="F61" s="39" t="s">
+        <v>286</v>
+      </c>
+      <c r="F61" s="40" t="s">
         <v>97</v>
       </c>
       <c r="G61" s="34" t="n">
@@ -7503,16 +7552,16 @@
         <v>1</v>
       </c>
       <c r="J61" s="8"/>
-      <c r="K61" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L61" s="8"/>
-      <c r="M61" s="8"/>
-      <c r="N61" s="8"/>
-      <c r="O61" s="8"/>
+      <c r="K61" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L61" s="53"/>
+      <c r="M61" s="53"/>
+      <c r="N61" s="53"/>
+      <c r="O61" s="53"/>
       <c r="P61" s="8"/>
       <c r="Q61" s="8"/>
-      <c r="R61" s="47"/>
+      <c r="R61" s="51"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="34" t="n">
@@ -7526,9 +7575,9 @@
       </c>
       <c r="D62" s="24"/>
       <c r="E62" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="F62" s="39" t="s">
+        <v>287</v>
+      </c>
+      <c r="F62" s="40" t="s">
         <v>93</v>
       </c>
       <c r="G62" s="34" t="n">
@@ -7541,18 +7590,18 @@
         <v>1</v>
       </c>
       <c r="J62" s="8"/>
-      <c r="K62" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L62" s="8"/>
-      <c r="M62" s="8"/>
-      <c r="N62" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="O62" s="8"/>
+      <c r="K62" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L62" s="53"/>
+      <c r="M62" s="53"/>
+      <c r="N62" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="O62" s="53"/>
       <c r="P62" s="8"/>
       <c r="Q62" s="8"/>
-      <c r="R62" s="47"/>
+      <c r="R62" s="51"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="34" t="n">
@@ -7564,10 +7613,10 @@
       </c>
       <c r="D63" s="24"/>
       <c r="E63" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="F63" s="51" t="s">
-        <v>286</v>
+        <v>288</v>
+      </c>
+      <c r="F63" s="56" t="s">
+        <v>289</v>
       </c>
       <c r="G63" s="34" t="n">
         <v>51</v>
@@ -7579,16 +7628,16 @@
         <v>1</v>
       </c>
       <c r="J63" s="8"/>
-      <c r="K63" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L63" s="8"/>
-      <c r="M63" s="8"/>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
+      <c r="K63" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L63" s="53"/>
+      <c r="M63" s="53"/>
+      <c r="N63" s="53"/>
+      <c r="O63" s="53"/>
       <c r="P63" s="8"/>
       <c r="Q63" s="8"/>
-      <c r="R63" s="47"/>
+      <c r="R63" s="51"/>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="34" t="n">
@@ -7600,9 +7649,9 @@
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="F64" s="51" t="s">
+        <v>290</v>
+      </c>
+      <c r="F64" s="56" t="s">
         <v>160</v>
       </c>
       <c r="G64" s="34" t="n">
@@ -7615,16 +7664,16 @@
         <v>1</v>
       </c>
       <c r="J64" s="8"/>
-      <c r="K64" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L64" s="8"/>
-      <c r="M64" s="8"/>
-      <c r="N64" s="8"/>
-      <c r="O64" s="8"/>
+      <c r="K64" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L64" s="53"/>
+      <c r="M64" s="53"/>
+      <c r="N64" s="53"/>
+      <c r="O64" s="53"/>
       <c r="P64" s="8"/>
       <c r="Q64" s="8"/>
-      <c r="R64" s="40"/>
+      <c r="R64" s="42"/>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="34" t="n">
@@ -7636,9 +7685,9 @@
       </c>
       <c r="D65" s="24"/>
       <c r="E65" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="F65" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="F65" s="40" t="s">
         <v>138</v>
       </c>
       <c r="G65" s="34" t="n">
@@ -7651,20 +7700,20 @@
         <v>1</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="K65" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L65" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M65" s="8"/>
-      <c r="N65" s="8"/>
-      <c r="O65" s="8"/>
+        <v>292</v>
+      </c>
+      <c r="K65" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L65" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M65" s="53"/>
+      <c r="N65" s="53"/>
+      <c r="O65" s="53"/>
       <c r="P65" s="8"/>
       <c r="Q65" s="8"/>
-      <c r="R65" s="40"/>
+      <c r="R65" s="42"/>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="34" t="n">
@@ -7676,9 +7725,9 @@
       </c>
       <c r="D66" s="24"/>
       <c r="E66" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="F66" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="F66" s="40" t="s">
         <v>139</v>
       </c>
       <c r="G66" s="34" t="n">
@@ -7691,60 +7740,60 @@
         <v>1</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="K66" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L66" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M66" s="8"/>
-      <c r="N66" s="8"/>
-      <c r="O66" s="8"/>
+        <v>294</v>
+      </c>
+      <c r="K66" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L66" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M66" s="53"/>
+      <c r="N66" s="53"/>
+      <c r="O66" s="53"/>
       <c r="P66" s="8"/>
       <c r="Q66" s="8"/>
-      <c r="R66" s="40"/>
+      <c r="R66" s="42"/>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="41" t="n">
+      <c r="A67" s="43" t="n">
         <v>56</v>
       </c>
-      <c r="B67" s="42"/>
-      <c r="C67" s="41" t="n">
+      <c r="B67" s="44"/>
+      <c r="C67" s="43" t="n">
         <v>57</v>
       </c>
-      <c r="D67" s="42"/>
+      <c r="D67" s="44"/>
       <c r="E67" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="F67" s="42" t="s">
+        <v>295</v>
+      </c>
+      <c r="F67" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="G67" s="41" t="n">
+      <c r="G67" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H67" s="57" t="n">
+      <c r="H67" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="I67" s="41" t="n">
+      <c r="I67" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="K67" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L67" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M67" s="5"/>
-      <c r="N67" s="5"/>
-      <c r="O67" s="5"/>
+        <v>296</v>
+      </c>
+      <c r="K67" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L67" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M67" s="49"/>
+      <c r="N67" s="49"/>
+      <c r="O67" s="49"/>
       <c r="P67" s="5"/>
       <c r="Q67" s="5"/>
-      <c r="R67" s="47"/>
+      <c r="R67" s="51"/>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="34" t="n">
@@ -7754,7 +7803,7 @@
       <c r="C68" s="34"/>
       <c r="D68" s="24"/>
       <c r="E68" s="24" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F68" s="24" t="s">
         <v>140</v>
@@ -7767,14 +7816,14 @@
       </c>
       <c r="I68" s="34"/>
       <c r="J68" s="8"/>
-      <c r="K68" s="14"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="8"/>
-      <c r="N68" s="8"/>
-      <c r="O68" s="8"/>
+      <c r="K68" s="41"/>
+      <c r="L68" s="53"/>
+      <c r="M68" s="53"/>
+      <c r="N68" s="53"/>
+      <c r="O68" s="53"/>
       <c r="P68" s="8"/>
       <c r="Q68" s="8"/>
-      <c r="R68" s="40"/>
+      <c r="R68" s="42"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="34" t="n">
@@ -7786,9 +7835,9 @@
       </c>
       <c r="D69" s="24"/>
       <c r="E69" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="F69" s="39" t="s">
+        <v>298</v>
+      </c>
+      <c r="F69" s="40" t="s">
         <v>141</v>
       </c>
       <c r="G69" s="34" t="n">
@@ -7801,20 +7850,20 @@
         <v>1</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K69" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L69" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M69" s="8"/>
-      <c r="N69" s="8"/>
-      <c r="O69" s="8"/>
+        <v>299</v>
+      </c>
+      <c r="K69" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L69" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M69" s="53"/>
+      <c r="N69" s="53"/>
+      <c r="O69" s="53"/>
       <c r="P69" s="8"/>
       <c r="Q69" s="8"/>
-      <c r="R69" s="40"/>
+      <c r="R69" s="42"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="34" t="n">
@@ -7826,9 +7875,9 @@
       </c>
       <c r="D70" s="24"/>
       <c r="E70" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="F70" s="39" t="s">
+        <v>300</v>
+      </c>
+      <c r="F70" s="40" t="s">
         <v>5</v>
       </c>
       <c r="G70" s="34" t="n">
@@ -7841,20 +7890,20 @@
         <v>1</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="K70" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L70" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M70" s="8"/>
-      <c r="N70" s="8"/>
-      <c r="O70" s="8"/>
+        <v>301</v>
+      </c>
+      <c r="K70" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L70" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M70" s="53"/>
+      <c r="N70" s="53"/>
+      <c r="O70" s="53"/>
       <c r="P70" s="8"/>
       <c r="Q70" s="8"/>
-      <c r="R70" s="40"/>
+      <c r="R70" s="42"/>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="34" t="n">
@@ -7866,9 +7915,9 @@
       </c>
       <c r="D71" s="24"/>
       <c r="E71" s="24" t="s">
-        <v>299</v>
-      </c>
-      <c r="F71" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="F71" s="40" t="s">
         <v>143</v>
       </c>
       <c r="G71" s="34" t="n">
@@ -7881,20 +7930,20 @@
         <v>1</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="K71" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L71" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M71" s="8"/>
-      <c r="N71" s="8"/>
-      <c r="O71" s="8"/>
+        <v>303</v>
+      </c>
+      <c r="K71" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L71" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M71" s="53"/>
+      <c r="N71" s="53"/>
+      <c r="O71" s="53"/>
       <c r="P71" s="8"/>
       <c r="Q71" s="8"/>
-      <c r="R71" s="40"/>
+      <c r="R71" s="42"/>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="34" t="n">
@@ -7906,9 +7955,9 @@
       </c>
       <c r="D72" s="24"/>
       <c r="E72" s="24" t="s">
-        <v>301</v>
-      </c>
-      <c r="F72" s="39" t="s">
+        <v>304</v>
+      </c>
+      <c r="F72" s="40" t="s">
         <v>144</v>
       </c>
       <c r="G72" s="34" t="n">
@@ -7921,20 +7970,20 @@
         <v>1</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="K72" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L72" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M72" s="8"/>
-      <c r="N72" s="8"/>
-      <c r="O72" s="8"/>
+        <v>305</v>
+      </c>
+      <c r="K72" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L72" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M72" s="53"/>
+      <c r="N72" s="53"/>
+      <c r="O72" s="53"/>
       <c r="P72" s="8"/>
       <c r="Q72" s="8"/>
-      <c r="R72" s="47"/>
+      <c r="R72" s="51"/>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="34"/>
@@ -7944,9 +7993,9 @@
       </c>
       <c r="D73" s="24"/>
       <c r="E73" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="F73" s="39" t="s">
+        <v>297</v>
+      </c>
+      <c r="F73" s="40" t="s">
         <v>145</v>
       </c>
       <c r="G73" s="34" t="n">
@@ -7957,288 +8006,288 @@
         <v>1</v>
       </c>
       <c r="J73" s="8"/>
-      <c r="K73" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8"/>
-      <c r="N73" s="8"/>
-      <c r="O73" s="8"/>
+      <c r="K73" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L73" s="53"/>
+      <c r="M73" s="53"/>
+      <c r="N73" s="53"/>
+      <c r="O73" s="53"/>
       <c r="P73" s="8"/>
       <c r="Q73" s="8"/>
-      <c r="R73" s="47"/>
+      <c r="R73" s="51"/>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="41" t="n">
+      <c r="A74" s="43" t="n">
         <v>62</v>
       </c>
-      <c r="B74" s="42"/>
-      <c r="C74" s="41"/>
-      <c r="D74" s="42"/>
+      <c r="B74" s="44"/>
+      <c r="C74" s="43"/>
+      <c r="D74" s="44"/>
       <c r="E74" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="F74" s="42" t="s">
+        <v>306</v>
+      </c>
+      <c r="F74" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="G74" s="41" t="n">
+      <c r="G74" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H74" s="41" t="n">
+      <c r="H74" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I74" s="41" t="n">
+      <c r="I74" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J74" s="5"/>
-      <c r="K74" s="17"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
-      <c r="N74" s="5"/>
-      <c r="O74" s="5"/>
+      <c r="K74" s="48"/>
+      <c r="L74" s="49"/>
+      <c r="M74" s="49"/>
+      <c r="N74" s="49"/>
+      <c r="O74" s="49"/>
       <c r="P74" s="5"/>
       <c r="Q74" s="5"/>
-      <c r="R74" s="40"/>
+      <c r="R74" s="42"/>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="41" t="n">
+      <c r="A75" s="43" t="n">
         <v>63</v>
       </c>
-      <c r="B75" s="42"/>
-      <c r="C75" s="41" t="n">
+      <c r="B75" s="44"/>
+      <c r="C75" s="43" t="n">
         <v>63</v>
       </c>
-      <c r="D75" s="42"/>
+      <c r="D75" s="44"/>
       <c r="E75" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="F75" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="F75" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="G75" s="41" t="n">
+      <c r="G75" s="43" t="n">
         <v>62</v>
       </c>
-      <c r="H75" s="41" t="n">
+      <c r="H75" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I75" s="41" t="n">
+      <c r="I75" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="K75" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L75" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M75" s="5"/>
-      <c r="N75" s="5"/>
-      <c r="O75" s="5"/>
+        <v>308</v>
+      </c>
+      <c r="K75" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L75" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M75" s="49"/>
+      <c r="N75" s="49"/>
+      <c r="O75" s="49"/>
       <c r="P75" s="5"/>
       <c r="Q75" s="5"/>
-      <c r="R75" s="40"/>
+      <c r="R75" s="42"/>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="41" t="n">
+      <c r="A76" s="43" t="n">
         <v>64</v>
       </c>
-      <c r="B76" s="42"/>
-      <c r="C76" s="41" t="n">
+      <c r="B76" s="44"/>
+      <c r="C76" s="43" t="n">
         <v>64</v>
       </c>
-      <c r="D76" s="42"/>
+      <c r="D76" s="44"/>
       <c r="E76" s="23" t="s">
-        <v>306</v>
-      </c>
-      <c r="F76" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="F76" s="50" t="s">
         <v>147</v>
       </c>
-      <c r="G76" s="41" t="n">
+      <c r="G76" s="43" t="n">
         <v>62</v>
       </c>
-      <c r="H76" s="41" t="n">
+      <c r="H76" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I76" s="41" t="n">
+      <c r="I76" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="K76" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L76" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M76" s="5"/>
-      <c r="N76" s="5"/>
-      <c r="O76" s="5"/>
+        <v>310</v>
+      </c>
+      <c r="K76" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L76" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M76" s="49"/>
+      <c r="N76" s="49"/>
+      <c r="O76" s="49"/>
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
-      <c r="R76" s="40"/>
+      <c r="R76" s="42"/>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="41" t="n">
+      <c r="A77" s="43" t="n">
         <v>65</v>
       </c>
-      <c r="B77" s="42" t="n">
+      <c r="B77" s="44" t="n">
         <v>63</v>
       </c>
-      <c r="C77" s="41" t="n">
+      <c r="C77" s="43" t="n">
         <v>65</v>
       </c>
-      <c r="D77" s="42" t="n">
+      <c r="D77" s="44" t="n">
         <v>63</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="F77" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="F77" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="G77" s="41" t="n">
+      <c r="G77" s="43" t="n">
         <v>62</v>
       </c>
-      <c r="H77" s="41" t="n">
+      <c r="H77" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I77" s="41" t="n">
+      <c r="I77" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="K77" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L77" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M77" s="5"/>
-      <c r="N77" s="5"/>
-      <c r="O77" s="5"/>
+        <v>312</v>
+      </c>
+      <c r="K77" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L77" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M77" s="49"/>
+      <c r="N77" s="49"/>
+      <c r="O77" s="49"/>
       <c r="P77" s="5"/>
       <c r="Q77" s="5"/>
-      <c r="R77" s="40"/>
+      <c r="R77" s="42"/>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="41" t="n">
+      <c r="A78" s="43" t="n">
         <v>66</v>
       </c>
-      <c r="B78" s="42"/>
-      <c r="C78" s="41" t="n">
+      <c r="B78" s="44"/>
+      <c r="C78" s="43" t="n">
         <v>66</v>
       </c>
-      <c r="D78" s="42"/>
+      <c r="D78" s="44"/>
       <c r="E78" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="F78" s="53" t="s">
-        <v>234</v>
-      </c>
-      <c r="G78" s="41" t="n">
+        <v>313</v>
+      </c>
+      <c r="F78" s="58" t="s">
+        <v>233</v>
+      </c>
+      <c r="G78" s="43" t="n">
         <v>65</v>
       </c>
-      <c r="H78" s="41" t="n">
+      <c r="H78" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I78" s="41" t="n">
+      <c r="I78" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="K78" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L78" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M78" s="5"/>
-      <c r="N78" s="5"/>
-      <c r="O78" s="5"/>
+        <v>314</v>
+      </c>
+      <c r="K78" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L78" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M78" s="49"/>
+      <c r="N78" s="49"/>
+      <c r="O78" s="49"/>
       <c r="P78" s="5"/>
       <c r="Q78" s="5"/>
-      <c r="R78" s="40"/>
+      <c r="R78" s="42"/>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="41" t="n">
+      <c r="A79" s="43" t="n">
         <v>67</v>
       </c>
-      <c r="B79" s="42"/>
-      <c r="C79" s="41" t="n">
+      <c r="B79" s="44"/>
+      <c r="C79" s="43" t="n">
         <v>67</v>
       </c>
-      <c r="D79" s="42"/>
+      <c r="D79" s="44"/>
       <c r="E79" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="F79" s="53" t="s">
-        <v>237</v>
-      </c>
-      <c r="G79" s="41" t="n">
+        <v>315</v>
+      </c>
+      <c r="F79" s="58" t="s">
+        <v>236</v>
+      </c>
+      <c r="G79" s="43" t="n">
         <v>65</v>
       </c>
-      <c r="H79" s="41" t="n">
+      <c r="H79" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I79" s="41" t="n">
+      <c r="I79" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="K79" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L79" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M79" s="5"/>
-      <c r="N79" s="5"/>
-      <c r="O79" s="5"/>
+        <v>316</v>
+      </c>
+      <c r="K79" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L79" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M79" s="49"/>
+      <c r="N79" s="49"/>
+      <c r="O79" s="49"/>
       <c r="P79" s="5"/>
       <c r="Q79" s="5"/>
-      <c r="R79" s="40"/>
+      <c r="R79" s="42"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="41"/>
-      <c r="B80" s="42"/>
-      <c r="C80" s="41" t="n">
+      <c r="A80" s="43"/>
+      <c r="B80" s="44"/>
+      <c r="C80" s="43" t="n">
         <v>68</v>
       </c>
-      <c r="D80" s="42"/>
+      <c r="D80" s="44"/>
       <c r="E80" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="F80" s="53" t="s">
-        <v>315</v>
-      </c>
-      <c r="G80" s="41" t="n">
+        <v>317</v>
+      </c>
+      <c r="F80" s="58" t="s">
+        <v>318</v>
+      </c>
+      <c r="G80" s="43" t="n">
         <v>65</v>
       </c>
-      <c r="H80" s="41"/>
-      <c r="I80" s="41" t="n">
+      <c r="H80" s="43"/>
+      <c r="I80" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="K80" s="5"/>
-      <c r="L80" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M80" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="N80" s="5"/>
-      <c r="O80" s="5"/>
+        <v>319</v>
+      </c>
+      <c r="K80" s="49"/>
+      <c r="L80" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M80" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="N80" s="49"/>
+      <c r="O80" s="49"/>
       <c r="P80" s="5"/>
       <c r="Q80" s="5"/>
-      <c r="R80" s="47"/>
+      <c r="R80" s="51"/>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="34" t="n">
@@ -8248,12 +8297,12 @@
       <c r="C81" s="34"/>
       <c r="D81" s="24"/>
       <c r="E81" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="F81" s="58" t="s">
+        <v>320</v>
+      </c>
+      <c r="F81" s="63" t="s">
         <v>126</v>
       </c>
-      <c r="G81" s="50" t="n">
+      <c r="G81" s="55" t="n">
         <v>43</v>
       </c>
       <c r="H81" s="34" t="n">
@@ -8261,14 +8310,14 @@
       </c>
       <c r="I81" s="34"/>
       <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="8"/>
-      <c r="N81" s="8"/>
-      <c r="O81" s="8"/>
+      <c r="K81" s="53"/>
+      <c r="L81" s="53"/>
+      <c r="M81" s="53"/>
+      <c r="N81" s="53"/>
+      <c r="O81" s="53"/>
       <c r="P81" s="8"/>
       <c r="Q81" s="8"/>
-      <c r="R81" s="47"/>
+      <c r="R81" s="51"/>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="34" t="n">
@@ -8280,9 +8329,9 @@
       </c>
       <c r="D82" s="24"/>
       <c r="E82" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="F82" s="39" t="s">
+        <v>321</v>
+      </c>
+      <c r="F82" s="40" t="s">
         <v>150</v>
       </c>
       <c r="G82" s="34" t="n">
@@ -8295,16 +8344,16 @@
         <v>1</v>
       </c>
       <c r="J82" s="8"/>
-      <c r="K82" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L82" s="8"/>
-      <c r="M82" s="8"/>
-      <c r="N82" s="8"/>
-      <c r="O82" s="8"/>
+      <c r="K82" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L82" s="53"/>
+      <c r="M82" s="53"/>
+      <c r="N82" s="53"/>
+      <c r="O82" s="53"/>
       <c r="P82" s="8"/>
       <c r="Q82" s="8"/>
-      <c r="R82" s="47"/>
+      <c r="R82" s="51"/>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="34" t="n">
@@ -8316,10 +8365,10 @@
       </c>
       <c r="D83" s="24"/>
       <c r="E83" s="24" t="s">
-        <v>319</v>
-      </c>
-      <c r="F83" s="51" t="s">
-        <v>320</v>
+        <v>322</v>
+      </c>
+      <c r="F83" s="56" t="s">
+        <v>323</v>
       </c>
       <c r="G83" s="34" t="n">
         <v>69</v>
@@ -8331,16 +8380,16 @@
         <v>1</v>
       </c>
       <c r="J83" s="8"/>
-      <c r="K83" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L83" s="8"/>
-      <c r="M83" s="8"/>
-      <c r="N83" s="8"/>
-      <c r="O83" s="8"/>
+      <c r="K83" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L83" s="53"/>
+      <c r="M83" s="53"/>
+      <c r="N83" s="53"/>
+      <c r="O83" s="53"/>
       <c r="P83" s="8"/>
       <c r="Q83" s="8"/>
-      <c r="R83" s="40"/>
+      <c r="R83" s="42"/>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="34" t="n">
@@ -8352,9 +8401,9 @@
       </c>
       <c r="D84" s="24"/>
       <c r="E84" s="24" t="s">
-        <v>321</v>
-      </c>
-      <c r="F84" s="39" t="s">
+        <v>324</v>
+      </c>
+      <c r="F84" s="40" t="s">
         <v>152</v>
       </c>
       <c r="G84" s="34" t="n">
@@ -8367,299 +8416,299 @@
         <v>1</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="K84" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L84" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M84" s="8"/>
-      <c r="N84" s="8"/>
-      <c r="O84" s="8"/>
+        <v>325</v>
+      </c>
+      <c r="K84" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L84" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M84" s="53"/>
+      <c r="N84" s="53"/>
+      <c r="O84" s="53"/>
       <c r="P84" s="8"/>
       <c r="Q84" s="8"/>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="41" t="n">
+      <c r="A85" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="B85" s="42"/>
-      <c r="C85" s="41"/>
-      <c r="D85" s="42"/>
+      <c r="B85" s="44"/>
+      <c r="C85" s="43"/>
+      <c r="D85" s="44"/>
       <c r="E85" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="F85" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="F85" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="G85" s="41" t="n">
+      <c r="G85" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H85" s="41" t="n">
+      <c r="H85" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I85" s="41"/>
+      <c r="I85" s="43"/>
       <c r="J85" s="5"/>
-      <c r="K85" s="5"/>
-      <c r="L85" s="5"/>
-      <c r="M85" s="5"/>
-      <c r="N85" s="5"/>
-      <c r="O85" s="5"/>
+      <c r="K85" s="49"/>
+      <c r="L85" s="49"/>
+      <c r="M85" s="49"/>
+      <c r="N85" s="49"/>
+      <c r="O85" s="49"/>
       <c r="P85" s="5"/>
       <c r="Q85" s="5"/>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="41" t="n">
+      <c r="A86" s="43" t="n">
         <v>73</v>
       </c>
-      <c r="B86" s="42"/>
-      <c r="C86" s="41" t="n">
+      <c r="B86" s="44"/>
+      <c r="C86" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="D86" s="42"/>
+      <c r="D86" s="44"/>
       <c r="E86" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="F86" s="46" t="s">
+        <v>327</v>
+      </c>
+      <c r="F86" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="G86" s="41" t="n">
+      <c r="G86" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H86" s="41" t="n">
+      <c r="H86" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I86" s="41" t="n">
+      <c r="I86" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J86" s="5"/>
-      <c r="K86" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="L86" s="5"/>
-      <c r="M86" s="5"/>
-      <c r="N86" s="5"/>
-      <c r="O86" s="5"/>
+      <c r="K86" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="L86" s="49"/>
+      <c r="M86" s="49"/>
+      <c r="N86" s="49"/>
+      <c r="O86" s="49"/>
       <c r="P86" s="5"/>
       <c r="Q86" s="5"/>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="41" t="n">
+      <c r="A87" s="43" t="n">
         <v>74</v>
       </c>
-      <c r="B87" s="42"/>
-      <c r="C87" s="41" t="n">
+      <c r="B87" s="44"/>
+      <c r="C87" s="43" t="n">
         <v>73</v>
       </c>
-      <c r="D87" s="42"/>
+      <c r="D87" s="44"/>
       <c r="E87" s="23"/>
-      <c r="F87" s="46" t="s">
+      <c r="F87" s="50" t="s">
         <v>155</v>
       </c>
-      <c r="G87" s="41" t="n">
+      <c r="G87" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H87" s="41" t="n">
+      <c r="H87" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I87" s="41" t="n">
+      <c r="I87" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J87" s="5"/>
-      <c r="K87" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="L87" s="5"/>
-      <c r="M87" s="5"/>
-      <c r="N87" s="5"/>
-      <c r="O87" s="5"/>
+      <c r="K87" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="L87" s="49"/>
+      <c r="M87" s="49"/>
+      <c r="N87" s="49"/>
+      <c r="O87" s="49"/>
       <c r="P87" s="5"/>
       <c r="Q87" s="5"/>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="41" t="n">
+      <c r="A88" s="43" t="n">
         <v>75</v>
       </c>
-      <c r="B88" s="42"/>
-      <c r="C88" s="41" t="n">
+      <c r="B88" s="44"/>
+      <c r="C88" s="43" t="n">
         <v>74</v>
       </c>
-      <c r="D88" s="42"/>
+      <c r="D88" s="44"/>
       <c r="E88" s="23" t="s">
-        <v>325</v>
-      </c>
-      <c r="F88" s="46" t="s">
+        <v>328</v>
+      </c>
+      <c r="F88" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="G88" s="41" t="n">
+      <c r="G88" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H88" s="41" t="n">
+      <c r="H88" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I88" s="41" t="n">
+      <c r="I88" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J88" s="5"/>
-      <c r="K88" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L88" s="5"/>
-      <c r="M88" s="5"/>
-      <c r="N88" s="5"/>
-      <c r="O88" s="5"/>
+      <c r="K88" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L88" s="49"/>
+      <c r="M88" s="49"/>
+      <c r="N88" s="49"/>
+      <c r="O88" s="49"/>
       <c r="P88" s="5"/>
       <c r="Q88" s="5"/>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="41" t="n">
+      <c r="A89" s="43" t="n">
         <v>76</v>
       </c>
-      <c r="B89" s="42" t="n">
+      <c r="B89" s="44" t="n">
         <v>75</v>
       </c>
-      <c r="C89" s="41" t="n">
+      <c r="C89" s="43" t="n">
         <v>75</v>
       </c>
-      <c r="D89" s="42" t="n">
+      <c r="D89" s="44" t="n">
         <v>75</v>
       </c>
       <c r="E89" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="F89" s="46" t="s">
+        <v>329</v>
+      </c>
+      <c r="F89" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="G89" s="41" t="n">
+      <c r="G89" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H89" s="41" t="n">
+      <c r="H89" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I89" s="41" t="n">
+      <c r="I89" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J89" s="5"/>
-      <c r="K89" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L89" s="5"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="5"/>
-      <c r="O89" s="5"/>
+      <c r="K89" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L89" s="49"/>
+      <c r="M89" s="49"/>
+      <c r="N89" s="49"/>
+      <c r="O89" s="49"/>
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="41" t="n">
+      <c r="A90" s="43" t="n">
         <v>77</v>
       </c>
-      <c r="B90" s="42" t="n">
+      <c r="B90" s="44" t="n">
         <v>75</v>
       </c>
-      <c r="C90" s="41"/>
-      <c r="D90" s="42" t="n">
+      <c r="C90" s="43"/>
+      <c r="D90" s="44" t="n">
         <v>75</v>
       </c>
       <c r="E90" s="23"/>
-      <c r="F90" s="46" t="s">
-        <v>327</v>
-      </c>
-      <c r="G90" s="41" t="n">
+      <c r="F90" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="G90" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H90" s="41" t="n">
+      <c r="H90" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I90" s="41"/>
+      <c r="I90" s="43"/>
       <c r="J90" s="5"/>
-      <c r="K90" s="17"/>
-      <c r="L90" s="5"/>
-      <c r="M90" s="5"/>
-      <c r="N90" s="5"/>
-      <c r="O90" s="5"/>
+      <c r="K90" s="48"/>
+      <c r="L90" s="49"/>
+      <c r="M90" s="49"/>
+      <c r="N90" s="49"/>
+      <c r="O90" s="49"/>
       <c r="P90" s="5"/>
       <c r="Q90" s="5"/>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="41" t="n">
+      <c r="A91" s="43" t="n">
         <v>78</v>
       </c>
-      <c r="B91" s="42"/>
-      <c r="C91" s="41" t="n">
+      <c r="B91" s="44"/>
+      <c r="C91" s="43" t="n">
         <v>76</v>
       </c>
-      <c r="D91" s="42"/>
+      <c r="D91" s="44"/>
       <c r="E91" s="23" t="s">
-        <v>328</v>
-      </c>
-      <c r="F91" s="53" t="s">
-        <v>329</v>
-      </c>
-      <c r="G91" s="41" t="n">
+        <v>331</v>
+      </c>
+      <c r="F91" s="58" t="s">
+        <v>332</v>
+      </c>
+      <c r="G91" s="43" t="n">
         <v>77</v>
       </c>
-      <c r="H91" s="41" t="n">
+      <c r="H91" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I91" s="41" t="n">
+      <c r="I91" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J91" s="5"/>
-      <c r="K91" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L91" s="5"/>
-      <c r="M91" s="5"/>
-      <c r="N91" s="5"/>
-      <c r="O91" s="5"/>
+      <c r="K91" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L91" s="49"/>
+      <c r="M91" s="49"/>
+      <c r="N91" s="49"/>
+      <c r="O91" s="49"/>
       <c r="P91" s="5"/>
       <c r="Q91" s="5"/>
-      <c r="R91" s="40"/>
+      <c r="R91" s="42"/>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="41" t="n">
+      <c r="A92" s="43" t="n">
         <v>79</v>
       </c>
-      <c r="B92" s="42"/>
-      <c r="C92" s="41" t="n">
+      <c r="B92" s="44"/>
+      <c r="C92" s="43" t="n">
         <v>77</v>
       </c>
-      <c r="D92" s="42"/>
+      <c r="D92" s="44"/>
       <c r="E92" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="F92" s="53" t="s">
-        <v>331</v>
-      </c>
-      <c r="G92" s="41" t="n">
+        <v>333</v>
+      </c>
+      <c r="F92" s="58" t="s">
+        <v>334</v>
+      </c>
+      <c r="G92" s="43" t="n">
         <v>77</v>
       </c>
-      <c r="H92" s="41" t="n">
+      <c r="H92" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I92" s="41" t="n">
+      <c r="I92" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="K92" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L92" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M92" s="5"/>
-      <c r="N92" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="O92" s="5"/>
+        <v>335</v>
+      </c>
+      <c r="K92" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L92" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M92" s="49"/>
+      <c r="N92" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="O92" s="49"/>
       <c r="P92" s="5"/>
       <c r="Q92" s="5"/>
-      <c r="R92" s="47"/>
+      <c r="R92" s="51"/>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="34" t="n">
@@ -8669,7 +8718,7 @@
       <c r="C93" s="34"/>
       <c r="D93" s="24"/>
       <c r="E93" s="24" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F93" s="24" t="s">
         <v>160</v>
@@ -8682,14 +8731,14 @@
       </c>
       <c r="I93" s="34"/>
       <c r="J93" s="8"/>
-      <c r="K93" s="14"/>
-      <c r="L93" s="14"/>
-      <c r="M93" s="8"/>
-      <c r="N93" s="14"/>
-      <c r="O93" s="8"/>
+      <c r="K93" s="41"/>
+      <c r="L93" s="41"/>
+      <c r="M93" s="53"/>
+      <c r="N93" s="41"/>
+      <c r="O93" s="53"/>
       <c r="P93" s="8"/>
       <c r="Q93" s="8"/>
-      <c r="R93" s="40"/>
+      <c r="R93" s="42"/>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="34" t="n">
@@ -8701,9 +8750,9 @@
       </c>
       <c r="D94" s="24"/>
       <c r="E94" s="24" t="s">
-        <v>334</v>
-      </c>
-      <c r="F94" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="F94" s="40" t="s">
         <v>161</v>
       </c>
       <c r="G94" s="34" t="n">
@@ -8716,20 +8765,20 @@
         <v>1</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="K94" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L94" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M94" s="8"/>
-      <c r="N94" s="8"/>
-      <c r="O94" s="8"/>
+        <v>338</v>
+      </c>
+      <c r="K94" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L94" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M94" s="53"/>
+      <c r="N94" s="53"/>
+      <c r="O94" s="53"/>
       <c r="P94" s="8"/>
       <c r="Q94" s="8"/>
-      <c r="R94" s="40"/>
+      <c r="R94" s="42"/>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="34" t="n">
@@ -8741,9 +8790,9 @@
       </c>
       <c r="D95" s="24"/>
       <c r="E95" s="24" t="s">
-        <v>336</v>
-      </c>
-      <c r="F95" s="39" t="s">
+        <v>339</v>
+      </c>
+      <c r="F95" s="40" t="s">
         <v>162</v>
       </c>
       <c r="G95" s="34" t="n">
@@ -8756,20 +8805,20 @@
         <v>1</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="K95" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L95" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M95" s="8"/>
-      <c r="N95" s="8"/>
-      <c r="O95" s="8"/>
+        <v>340</v>
+      </c>
+      <c r="K95" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L95" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M95" s="53"/>
+      <c r="N95" s="53"/>
+      <c r="O95" s="53"/>
       <c r="P95" s="8"/>
       <c r="Q95" s="8"/>
-      <c r="R95" s="40"/>
+      <c r="R95" s="42"/>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="34" t="n">
@@ -8781,9 +8830,9 @@
       </c>
       <c r="D96" s="24"/>
       <c r="E96" s="24" t="s">
-        <v>338</v>
-      </c>
-      <c r="F96" s="39" t="s">
+        <v>341</v>
+      </c>
+      <c r="F96" s="40" t="s">
         <v>163</v>
       </c>
       <c r="G96" s="34" t="n">
@@ -8796,20 +8845,20 @@
         <v>1</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="K96" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L96" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M96" s="8"/>
-      <c r="N96" s="8"/>
-      <c r="O96" s="8"/>
+        <v>342</v>
+      </c>
+      <c r="K96" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L96" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M96" s="53"/>
+      <c r="N96" s="53"/>
+      <c r="O96" s="53"/>
       <c r="P96" s="8"/>
       <c r="Q96" s="8"/>
-      <c r="R96" s="40"/>
+      <c r="R96" s="42"/>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="34" t="n">
@@ -8821,9 +8870,9 @@
       </c>
       <c r="D97" s="24"/>
       <c r="E97" s="24" t="s">
-        <v>340</v>
-      </c>
-      <c r="F97" s="39" t="s">
+        <v>343</v>
+      </c>
+      <c r="F97" s="40" t="s">
         <v>121</v>
       </c>
       <c r="G97" s="34" t="n">
@@ -8836,396 +8885,396 @@
         <v>1</v>
       </c>
       <c r="J97" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="K97" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L97" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M97" s="8"/>
-      <c r="N97" s="8"/>
-      <c r="O97" s="8"/>
+        <v>344</v>
+      </c>
+      <c r="K97" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L97" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M97" s="53"/>
+      <c r="N97" s="53"/>
+      <c r="O97" s="53"/>
       <c r="P97" s="8"/>
       <c r="Q97" s="8"/>
-      <c r="R97" s="47"/>
+      <c r="R97" s="51"/>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="41" t="n">
+      <c r="A98" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="B98" s="42"/>
-      <c r="C98" s="41"/>
-      <c r="D98" s="42"/>
+      <c r="B98" s="44"/>
+      <c r="C98" s="43"/>
+      <c r="D98" s="44"/>
       <c r="E98" s="23"/>
-      <c r="F98" s="42" t="s">
+      <c r="F98" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="G98" s="41" t="n">
+      <c r="G98" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H98" s="41" t="n">
+      <c r="H98" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I98" s="41"/>
+      <c r="I98" s="43"/>
       <c r="J98" s="5"/>
-      <c r="K98" s="17"/>
-      <c r="L98" s="17"/>
-      <c r="M98" s="5"/>
-      <c r="N98" s="5"/>
-      <c r="O98" s="5"/>
+      <c r="K98" s="48"/>
+      <c r="L98" s="48"/>
+      <c r="M98" s="49"/>
+      <c r="N98" s="49"/>
+      <c r="O98" s="49"/>
       <c r="P98" s="5"/>
       <c r="Q98" s="5"/>
-      <c r="R98" s="40"/>
+      <c r="R98" s="42"/>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="41"/>
-      <c r="B99" s="42"/>
-      <c r="C99" s="41" t="n">
+      <c r="A99" s="43"/>
+      <c r="B99" s="44"/>
+      <c r="C99" s="43" t="n">
         <v>82</v>
       </c>
-      <c r="D99" s="42"/>
+      <c r="D99" s="44"/>
       <c r="E99" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="F99" s="46" t="s">
+        <v>345</v>
+      </c>
+      <c r="F99" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="G99" s="41" t="n">
+      <c r="G99" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H99" s="41"/>
-      <c r="I99" s="41" t="n">
+      <c r="H99" s="43"/>
+      <c r="I99" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="K99" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L99" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M99" s="5"/>
-      <c r="N99" s="5"/>
-      <c r="O99" s="5"/>
+        <v>346</v>
+      </c>
+      <c r="K99" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L99" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M99" s="49"/>
+      <c r="N99" s="49"/>
+      <c r="O99" s="49"/>
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
-      <c r="R99" s="47"/>
+      <c r="R99" s="51"/>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="41"/>
-      <c r="B100" s="42"/>
-      <c r="C100" s="41" t="n">
+      <c r="A100" s="43"/>
+      <c r="B100" s="44"/>
+      <c r="C100" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="D100" s="42"/>
+      <c r="D100" s="44"/>
       <c r="E100" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="F100" s="46" t="s">
+        <v>345</v>
+      </c>
+      <c r="F100" s="50" t="s">
         <v>165</v>
       </c>
-      <c r="G100" s="41" t="n">
+      <c r="G100" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H100" s="41"/>
-      <c r="I100" s="41" t="n">
+      <c r="H100" s="43"/>
+      <c r="I100" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J100" s="5"/>
-      <c r="K100" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L100" s="5"/>
-      <c r="M100" s="5"/>
-      <c r="N100" s="5"/>
-      <c r="O100" s="5"/>
+      <c r="K100" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L100" s="49"/>
+      <c r="M100" s="49"/>
+      <c r="N100" s="49"/>
+      <c r="O100" s="49"/>
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
-      <c r="R100" s="40"/>
+      <c r="R100" s="42"/>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="41" t="n">
+      <c r="A101" s="43" t="n">
         <v>86</v>
       </c>
-      <c r="B101" s="42"/>
-      <c r="C101" s="41" t="n">
+      <c r="B101" s="44"/>
+      <c r="C101" s="43" t="n">
         <v>84</v>
       </c>
-      <c r="D101" s="42"/>
+      <c r="D101" s="44"/>
       <c r="E101" s="23" t="s">
-        <v>344</v>
-      </c>
-      <c r="F101" s="46" t="s">
+        <v>347</v>
+      </c>
+      <c r="F101" s="50" t="s">
         <v>155</v>
       </c>
-      <c r="G101" s="41" t="n">
+      <c r="G101" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H101" s="41" t="n">
+      <c r="H101" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I101" s="41" t="n">
+      <c r="I101" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="K101" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L101" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M101" s="5"/>
-      <c r="N101" s="5"/>
-      <c r="O101" s="5"/>
+        <v>348</v>
+      </c>
+      <c r="K101" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L101" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M101" s="49"/>
+      <c r="N101" s="49"/>
+      <c r="O101" s="49"/>
       <c r="P101" s="5"/>
       <c r="Q101" s="5"/>
-      <c r="R101" s="40"/>
+      <c r="R101" s="42"/>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="41" t="n">
-        <v>87</v>
-      </c>
-      <c r="B102" s="42"/>
-      <c r="C102" s="41" t="n">
+      <c r="A102" s="43" t="n">
+        <v>87</v>
+      </c>
+      <c r="B102" s="44"/>
+      <c r="C102" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="D102" s="42"/>
+      <c r="D102" s="44"/>
       <c r="E102" s="23" t="s">
-        <v>346</v>
-      </c>
-      <c r="F102" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="F102" s="50" t="s">
         <v>153</v>
       </c>
-      <c r="G102" s="41" t="n">
+      <c r="G102" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H102" s="41" t="n">
+      <c r="H102" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I102" s="41" t="n">
+      <c r="I102" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="K102" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L102" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M102" s="5"/>
-      <c r="N102" s="5"/>
-      <c r="O102" s="5"/>
+        <v>350</v>
+      </c>
+      <c r="K102" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L102" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M102" s="49"/>
+      <c r="N102" s="49"/>
+      <c r="O102" s="49"/>
       <c r="P102" s="5"/>
       <c r="Q102" s="5"/>
-      <c r="R102" s="40"/>
+      <c r="R102" s="42"/>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="41" t="n">
+      <c r="A103" s="43" t="n">
         <v>88</v>
       </c>
-      <c r="B103" s="42"/>
-      <c r="C103" s="41" t="n">
+      <c r="B103" s="44"/>
+      <c r="C103" s="43" t="n">
         <v>86</v>
       </c>
-      <c r="D103" s="42"/>
+      <c r="D103" s="44"/>
       <c r="E103" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="F103" s="46" t="s">
+        <v>351</v>
+      </c>
+      <c r="F103" s="50" t="s">
         <v>166</v>
       </c>
-      <c r="G103" s="41" t="n">
+      <c r="G103" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H103" s="41" t="n">
+      <c r="H103" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I103" s="41" t="n">
+      <c r="I103" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="K103" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L103" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M103" s="5"/>
-      <c r="N103" s="5"/>
-      <c r="O103" s="5"/>
+        <v>352</v>
+      </c>
+      <c r="K103" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L103" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M103" s="49"/>
+      <c r="N103" s="49"/>
+      <c r="O103" s="49"/>
       <c r="P103" s="5"/>
       <c r="Q103" s="5"/>
-      <c r="R103" s="40"/>
+      <c r="R103" s="42"/>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="41" t="n">
+      <c r="A104" s="43" t="n">
         <v>89</v>
       </c>
-      <c r="B104" s="42"/>
-      <c r="C104" s="41" t="n">
-        <v>87</v>
-      </c>
-      <c r="D104" s="42"/>
+      <c r="B104" s="44"/>
+      <c r="C104" s="43" t="n">
+        <v>87</v>
+      </c>
+      <c r="D104" s="44"/>
       <c r="E104" s="23" t="s">
-        <v>350</v>
-      </c>
-      <c r="F104" s="46" t="s">
+        <v>353</v>
+      </c>
+      <c r="F104" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="G104" s="41" t="n">
+      <c r="G104" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H104" s="41" t="n">
+      <c r="H104" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I104" s="41" t="n">
+      <c r="I104" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="K104" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L104" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M104" s="5"/>
-      <c r="N104" s="5"/>
-      <c r="O104" s="5"/>
+        <v>354</v>
+      </c>
+      <c r="K104" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L104" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M104" s="49"/>
+      <c r="N104" s="49"/>
+      <c r="O104" s="49"/>
       <c r="P104" s="5"/>
       <c r="Q104" s="5"/>
-      <c r="R104" s="40"/>
+      <c r="R104" s="42"/>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="41" t="n">
+      <c r="A105" s="43" t="n">
         <v>90</v>
       </c>
-      <c r="B105" s="42"/>
-      <c r="C105" s="41" t="n">
+      <c r="B105" s="44"/>
+      <c r="C105" s="43" t="n">
         <v>88</v>
       </c>
-      <c r="D105" s="42"/>
+      <c r="D105" s="44"/>
       <c r="E105" s="23" t="s">
-        <v>352</v>
-      </c>
-      <c r="F105" s="46" t="s">
+        <v>355</v>
+      </c>
+      <c r="F105" s="50" t="s">
         <v>168</v>
       </c>
-      <c r="G105" s="41" t="n">
+      <c r="G105" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H105" s="41" t="n">
+      <c r="H105" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I105" s="41" t="n">
+      <c r="I105" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="K105" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L105" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M105" s="5"/>
-      <c r="N105" s="5"/>
-      <c r="O105" s="5"/>
+        <v>356</v>
+      </c>
+      <c r="K105" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L105" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M105" s="49"/>
+      <c r="N105" s="49"/>
+      <c r="O105" s="49"/>
       <c r="P105" s="5"/>
       <c r="Q105" s="5"/>
-      <c r="R105" s="40"/>
+      <c r="R105" s="42"/>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="41" t="n">
+      <c r="A106" s="43" t="n">
         <v>91</v>
       </c>
-      <c r="B106" s="42"/>
-      <c r="C106" s="41" t="n">
+      <c r="B106" s="44"/>
+      <c r="C106" s="43" t="n">
         <v>89</v>
       </c>
-      <c r="D106" s="42"/>
+      <c r="D106" s="44"/>
       <c r="E106" s="23" t="s">
-        <v>354</v>
-      </c>
-      <c r="F106" s="53" t="s">
-        <v>355</v>
-      </c>
-      <c r="G106" s="41" t="n">
+        <v>357</v>
+      </c>
+      <c r="F106" s="58" t="s">
+        <v>358</v>
+      </c>
+      <c r="G106" s="43" t="n">
         <v>90</v>
       </c>
-      <c r="H106" s="41" t="n">
+      <c r="H106" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I106" s="41" t="n">
+      <c r="I106" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="K106" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L106" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M106" s="5"/>
-      <c r="N106" s="5"/>
-      <c r="O106" s="5"/>
+        <v>359</v>
+      </c>
+      <c r="K106" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L106" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M106" s="49"/>
+      <c r="N106" s="49"/>
+      <c r="O106" s="49"/>
       <c r="P106" s="5"/>
       <c r="Q106" s="5"/>
-      <c r="R106" s="40"/>
+      <c r="R106" s="42"/>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="41" t="n">
+      <c r="A107" s="43" t="n">
         <v>92</v>
       </c>
-      <c r="B107" s="42"/>
-      <c r="C107" s="41" t="n">
+      <c r="B107" s="44"/>
+      <c r="C107" s="43" t="n">
         <v>90</v>
       </c>
-      <c r="D107" s="42"/>
+      <c r="D107" s="44"/>
       <c r="E107" s="23" t="s">
-        <v>357</v>
-      </c>
-      <c r="F107" s="46" t="s">
+        <v>360</v>
+      </c>
+      <c r="F107" s="50" t="s">
         <v>170</v>
       </c>
-      <c r="G107" s="41" t="n">
+      <c r="G107" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H107" s="41" t="n">
+      <c r="H107" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I107" s="41" t="n">
+      <c r="I107" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="K107" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L107" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M107" s="5"/>
-      <c r="N107" s="5"/>
-      <c r="O107" s="5"/>
+        <v>361</v>
+      </c>
+      <c r="K107" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L107" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M107" s="49"/>
+      <c r="N107" s="49"/>
+      <c r="O107" s="49"/>
       <c r="P107" s="5"/>
       <c r="Q107" s="5"/>
-      <c r="R107" s="47"/>
+      <c r="R107" s="51"/>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="34" t="n">
@@ -9246,14 +9295,14 @@
       </c>
       <c r="I108" s="34"/>
       <c r="J108" s="8"/>
-      <c r="K108" s="14"/>
-      <c r="L108" s="14"/>
-      <c r="M108" s="8"/>
-      <c r="N108" s="8"/>
-      <c r="O108" s="8"/>
+      <c r="K108" s="41"/>
+      <c r="L108" s="41"/>
+      <c r="M108" s="53"/>
+      <c r="N108" s="53"/>
+      <c r="O108" s="53"/>
       <c r="P108" s="8"/>
       <c r="Q108" s="8"/>
-      <c r="R108" s="40"/>
+      <c r="R108" s="42"/>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="34" t="n">
@@ -9265,9 +9314,9 @@
       </c>
       <c r="D109" s="24"/>
       <c r="E109" s="24" t="s">
-        <v>359</v>
-      </c>
-      <c r="F109" s="39" t="s">
+        <v>362</v>
+      </c>
+      <c r="F109" s="40" t="s">
         <v>172</v>
       </c>
       <c r="G109" s="34" t="n">
@@ -9280,20 +9329,20 @@
         <v>1</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="K109" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L109" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M109" s="8"/>
-      <c r="N109" s="8"/>
-      <c r="O109" s="8"/>
+        <v>363</v>
+      </c>
+      <c r="K109" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L109" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M109" s="53"/>
+      <c r="N109" s="53"/>
+      <c r="O109" s="53"/>
       <c r="P109" s="8"/>
       <c r="Q109" s="8"/>
-      <c r="R109" s="40"/>
+      <c r="R109" s="42"/>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="34" t="n">
@@ -9305,9 +9354,9 @@
       </c>
       <c r="D110" s="24"/>
       <c r="E110" s="24" t="s">
-        <v>361</v>
-      </c>
-      <c r="F110" s="39" t="s">
+        <v>364</v>
+      </c>
+      <c r="F110" s="40" t="s">
         <v>173</v>
       </c>
       <c r="G110" s="34" t="n">
@@ -9320,20 +9369,20 @@
         <v>1</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="K110" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L110" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M110" s="8"/>
-      <c r="N110" s="8"/>
-      <c r="O110" s="8"/>
+        <v>365</v>
+      </c>
+      <c r="K110" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L110" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M110" s="53"/>
+      <c r="N110" s="53"/>
+      <c r="O110" s="53"/>
       <c r="P110" s="8"/>
       <c r="Q110" s="8"/>
-      <c r="R110" s="40"/>
+      <c r="R110" s="42"/>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="34" t="n">
@@ -9345,9 +9394,9 @@
       </c>
       <c r="D111" s="24"/>
       <c r="E111" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="F111" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="F111" s="40" t="s">
         <v>174</v>
       </c>
       <c r="G111" s="34" t="n">
@@ -9360,22 +9409,22 @@
         <v>1</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="K111" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L111" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M111" s="8"/>
-      <c r="N111" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="O111" s="8"/>
+        <v>367</v>
+      </c>
+      <c r="K111" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L111" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M111" s="53"/>
+      <c r="N111" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="O111" s="53"/>
       <c r="P111" s="8"/>
       <c r="Q111" s="8"/>
-      <c r="R111" s="40"/>
+      <c r="R111" s="42"/>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="34" t="n">
@@ -9387,9 +9436,9 @@
       </c>
       <c r="D112" s="24"/>
       <c r="E112" s="24" t="s">
-        <v>365</v>
-      </c>
-      <c r="F112" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="F112" s="40" t="s">
         <v>171</v>
       </c>
       <c r="G112" s="34" t="n">
@@ -9402,99 +9451,99 @@
         <v>1</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="K112" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L112" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M112" s="8"/>
-      <c r="N112" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="O112" s="8"/>
+        <v>369</v>
+      </c>
+      <c r="K112" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L112" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M112" s="53"/>
+      <c r="N112" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="O112" s="53"/>
       <c r="P112" s="8"/>
       <c r="Q112" s="8"/>
-      <c r="R112" s="40"/>
+      <c r="R112" s="42"/>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="41" t="n">
+      <c r="A113" s="43" t="n">
         <v>98</v>
       </c>
-      <c r="B113" s="42"/>
-      <c r="C113" s="41" t="n">
+      <c r="B113" s="44"/>
+      <c r="C113" s="43" t="n">
         <v>95</v>
       </c>
-      <c r="D113" s="42"/>
+      <c r="D113" s="44"/>
       <c r="E113" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="F113" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="F113" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="G113" s="41" t="n">
+      <c r="G113" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H113" s="41" t="n">
+      <c r="H113" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I113" s="41" t="n">
+      <c r="I113" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J113" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="K113" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L113" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M113" s="5"/>
-      <c r="N113" s="5"/>
-      <c r="O113" s="5"/>
+        <v>371</v>
+      </c>
+      <c r="K113" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L113" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M113" s="49"/>
+      <c r="N113" s="49"/>
+      <c r="O113" s="49"/>
       <c r="P113" s="5"/>
       <c r="Q113" s="5"/>
-      <c r="R113" s="40"/>
+      <c r="R113" s="42"/>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="41" t="n">
+      <c r="A114" s="43" t="n">
         <v>99</v>
       </c>
-      <c r="B114" s="42"/>
-      <c r="C114" s="41" t="n">
+      <c r="B114" s="44"/>
+      <c r="C114" s="43" t="n">
         <v>96</v>
       </c>
-      <c r="D114" s="42"/>
+      <c r="D114" s="44"/>
       <c r="E114" s="23" t="s">
-        <v>369</v>
-      </c>
-      <c r="F114" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="F114" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="G114" s="41" t="n">
+      <c r="G114" s="43" t="n">
         <v>98</v>
       </c>
-      <c r="H114" s="41" t="n">
+      <c r="H114" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I114" s="41" t="n">
+      <c r="I114" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J114" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="K114" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L114" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M114" s="5"/>
-      <c r="N114" s="5"/>
-      <c r="O114" s="5"/>
+        <v>373</v>
+      </c>
+      <c r="K114" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L114" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M114" s="49"/>
+      <c r="N114" s="49"/>
+      <c r="O114" s="49"/>
       <c r="P114" s="5"/>
       <c r="Q114" s="5"/>
     </row>
@@ -9517,14 +9566,14 @@
       </c>
       <c r="I115" s="34"/>
       <c r="J115" s="8"/>
-      <c r="K115" s="14"/>
-      <c r="L115" s="14"/>
-      <c r="M115" s="8"/>
-      <c r="N115" s="8"/>
-      <c r="O115" s="8"/>
+      <c r="K115" s="41"/>
+      <c r="L115" s="41"/>
+      <c r="M115" s="53"/>
+      <c r="N115" s="53"/>
+      <c r="O115" s="53"/>
       <c r="P115" s="8"/>
       <c r="Q115" s="8"/>
-      <c r="R115" s="40"/>
+      <c r="R115" s="42"/>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="34" t="n">
@@ -9536,9 +9585,9 @@
       </c>
       <c r="D116" s="24"/>
       <c r="E116" s="24" t="s">
-        <v>371</v>
-      </c>
-      <c r="F116" s="39" t="s">
+        <v>374</v>
+      </c>
+      <c r="F116" s="40" t="s">
         <v>178</v>
       </c>
       <c r="G116" s="34" t="n">
@@ -9551,20 +9600,20 @@
         <v>1</v>
       </c>
       <c r="J116" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="K116" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L116" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M116" s="8"/>
-      <c r="N116" s="8"/>
-      <c r="O116" s="8"/>
+        <v>375</v>
+      </c>
+      <c r="K116" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L116" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M116" s="53"/>
+      <c r="N116" s="53"/>
+      <c r="O116" s="53"/>
       <c r="P116" s="8"/>
       <c r="Q116" s="8"/>
-      <c r="R116" s="40"/>
+      <c r="R116" s="42"/>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="34" t="n">
@@ -9576,9 +9625,9 @@
       </c>
       <c r="D117" s="24"/>
       <c r="E117" s="24" t="s">
-        <v>373</v>
-      </c>
-      <c r="F117" s="39" t="s">
+        <v>376</v>
+      </c>
+      <c r="F117" s="40" t="s">
         <v>179</v>
       </c>
       <c r="G117" s="34" t="n">
@@ -9591,20 +9640,20 @@
         <v>1</v>
       </c>
       <c r="J117" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="K117" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L117" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M117" s="8"/>
-      <c r="N117" s="8"/>
-      <c r="O117" s="8"/>
+        <v>377</v>
+      </c>
+      <c r="K117" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L117" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M117" s="53"/>
+      <c r="N117" s="53"/>
+      <c r="O117" s="53"/>
       <c r="P117" s="8"/>
       <c r="Q117" s="8"/>
-      <c r="R117" s="40"/>
+      <c r="R117" s="42"/>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="34"/>
@@ -9614,7 +9663,7 @@
       </c>
       <c r="D118" s="24"/>
       <c r="E118" s="24" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F118" s="24"/>
       <c r="G118" s="34"/>
@@ -9623,171 +9672,171 @@
         <v>1</v>
       </c>
       <c r="J118" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="K118" s="8"/>
-      <c r="L118" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="M118" s="8"/>
-      <c r="N118" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="O118" s="8"/>
+        <v>378</v>
+      </c>
+      <c r="K118" s="53"/>
+      <c r="L118" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="M118" s="53"/>
+      <c r="N118" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="O118" s="53"/>
       <c r="P118" s="8"/>
       <c r="Q118" s="8"/>
-      <c r="R118" s="47"/>
+      <c r="R118" s="51"/>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="41" t="n">
+      <c r="A119" s="43" t="n">
         <v>103</v>
       </c>
-      <c r="B119" s="42"/>
-      <c r="C119" s="41"/>
-      <c r="D119" s="42"/>
+      <c r="B119" s="44"/>
+      <c r="C119" s="43"/>
+      <c r="D119" s="44"/>
       <c r="E119" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="F119" s="42" t="s">
+      <c r="F119" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="G119" s="41" t="n">
+      <c r="G119" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H119" s="41" t="n">
+      <c r="H119" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I119" s="41"/>
+      <c r="I119" s="43"/>
       <c r="J119" s="5"/>
-      <c r="K119" s="17"/>
-      <c r="L119" s="5"/>
-      <c r="M119" s="5"/>
-      <c r="N119" s="5"/>
-      <c r="O119" s="5"/>
+      <c r="K119" s="48"/>
+      <c r="L119" s="49"/>
+      <c r="M119" s="49"/>
+      <c r="N119" s="49"/>
+      <c r="O119" s="49"/>
       <c r="P119" s="5"/>
       <c r="Q119" s="5"/>
-      <c r="R119" s="40"/>
+      <c r="R119" s="42"/>
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="41" t="n">
+      <c r="A120" s="43" t="n">
         <v>104</v>
       </c>
-      <c r="B120" s="42"/>
-      <c r="C120" s="41" t="n">
+      <c r="B120" s="44"/>
+      <c r="C120" s="43" t="n">
         <v>100</v>
       </c>
-      <c r="D120" s="42"/>
+      <c r="D120" s="44"/>
       <c r="E120" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="F120" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="F120" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="G120" s="41" t="n">
+      <c r="G120" s="43" t="n">
         <v>103</v>
       </c>
-      <c r="H120" s="41" t="n">
+      <c r="H120" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I120" s="41" t="n">
+      <c r="I120" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J120" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="K120" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L120" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M120" s="5"/>
-      <c r="N120" s="5"/>
-      <c r="O120" s="5"/>
+        <v>380</v>
+      </c>
+      <c r="K120" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L120" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M120" s="49"/>
+      <c r="N120" s="49"/>
+      <c r="O120" s="49"/>
       <c r="P120" s="5"/>
       <c r="Q120" s="5"/>
-      <c r="R120" s="40"/>
+      <c r="R120" s="42"/>
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="41" t="n">
+      <c r="A121" s="43" t="n">
         <v>105</v>
       </c>
-      <c r="B121" s="42"/>
-      <c r="C121" s="41" t="n">
+      <c r="B121" s="44"/>
+      <c r="C121" s="43" t="n">
         <v>101</v>
       </c>
-      <c r="D121" s="42"/>
+      <c r="D121" s="44"/>
       <c r="E121" s="23" t="s">
-        <v>378</v>
-      </c>
-      <c r="F121" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="F121" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="G121" s="41" t="n">
+      <c r="G121" s="43" t="n">
         <v>103</v>
       </c>
-      <c r="H121" s="41" t="n">
+      <c r="H121" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I121" s="41" t="n">
+      <c r="I121" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J121" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="K121" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L121" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M121" s="5"/>
-      <c r="N121" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="O121" s="5"/>
+        <v>382</v>
+      </c>
+      <c r="K121" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L121" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M121" s="49"/>
+      <c r="N121" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="O121" s="49"/>
       <c r="P121" s="5"/>
       <c r="Q121" s="5"/>
-      <c r="R121" s="40"/>
+      <c r="R121" s="42"/>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="41" t="n">
+      <c r="A122" s="43" t="n">
         <v>106</v>
       </c>
-      <c r="B122" s="42"/>
-      <c r="C122" s="41" t="n">
+      <c r="B122" s="44"/>
+      <c r="C122" s="43" t="n">
         <v>102</v>
       </c>
-      <c r="D122" s="42"/>
+      <c r="D122" s="44"/>
       <c r="E122" s="23" t="s">
-        <v>380</v>
-      </c>
-      <c r="F122" s="46" t="s">
+        <v>383</v>
+      </c>
+      <c r="F122" s="50" t="s">
         <v>183</v>
       </c>
-      <c r="G122" s="41" t="n">
+      <c r="G122" s="43" t="n">
         <v>103</v>
       </c>
-      <c r="H122" s="41" t="n">
+      <c r="H122" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I122" s="41" t="n">
+      <c r="I122" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J122" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="K122" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L122" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="M122" s="5"/>
-      <c r="N122" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="O122" s="5"/>
+        <v>384</v>
+      </c>
+      <c r="K122" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L122" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M122" s="49"/>
+      <c r="N122" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="O122" s="49"/>
       <c r="P122" s="5"/>
       <c r="Q122" s="5"/>
     </row>
@@ -9801,7 +9850,7 @@
       </c>
       <c r="D123" s="24"/>
       <c r="E123" s="24" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F123" s="24" t="s">
         <v>36</v>
@@ -9816,83 +9865,83 @@
         <v>1</v>
       </c>
       <c r="J123" s="8"/>
-      <c r="K123" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L123" s="8"/>
-      <c r="M123" s="8"/>
-      <c r="N123" s="8"/>
-      <c r="O123" s="8"/>
+      <c r="K123" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L123" s="53"/>
+      <c r="M123" s="53"/>
+      <c r="N123" s="53"/>
+      <c r="O123" s="53"/>
       <c r="P123" s="8"/>
       <c r="Q123" s="8"/>
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="41" t="n">
+      <c r="A124" s="43" t="n">
         <v>108</v>
       </c>
-      <c r="B124" s="42"/>
-      <c r="C124" s="41" t="n">
+      <c r="B124" s="44"/>
+      <c r="C124" s="43" t="n">
         <v>104</v>
       </c>
-      <c r="D124" s="42"/>
+      <c r="D124" s="44"/>
       <c r="E124" s="23" t="s">
-        <v>383</v>
-      </c>
-      <c r="F124" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="F124" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="G124" s="41" t="n">
+      <c r="G124" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H124" s="41" t="n">
+      <c r="H124" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I124" s="41" t="n">
+      <c r="I124" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J124" s="5"/>
-      <c r="K124" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L124" s="5"/>
-      <c r="M124" s="5"/>
-      <c r="N124" s="5"/>
-      <c r="O124" s="5"/>
+      <c r="K124" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L124" s="49"/>
+      <c r="M124" s="49"/>
+      <c r="N124" s="49"/>
+      <c r="O124" s="49"/>
       <c r="P124" s="5"/>
       <c r="Q124" s="5"/>
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="41" t="n">
+      <c r="A125" s="43" t="n">
         <v>109</v>
       </c>
-      <c r="B125" s="42"/>
-      <c r="C125" s="41" t="n">
+      <c r="B125" s="44"/>
+      <c r="C125" s="43" t="n">
         <v>105</v>
       </c>
-      <c r="D125" s="42"/>
+      <c r="D125" s="44"/>
       <c r="E125" s="23" t="s">
-        <v>384</v>
-      </c>
-      <c r="F125" s="46" t="s">
+        <v>387</v>
+      </c>
+      <c r="F125" s="50" t="s">
         <v>185</v>
       </c>
-      <c r="G125" s="41" t="n">
+      <c r="G125" s="43" t="n">
         <v>108</v>
       </c>
-      <c r="H125" s="41" t="n">
+      <c r="H125" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I125" s="41" t="n">
+      <c r="I125" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J125" s="5"/>
-      <c r="K125" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L125" s="5"/>
-      <c r="M125" s="5"/>
-      <c r="N125" s="5"/>
-      <c r="O125" s="5"/>
+      <c r="K125" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L125" s="49"/>
+      <c r="M125" s="49"/>
+      <c r="N125" s="49"/>
+      <c r="O125" s="49"/>
       <c r="P125" s="5"/>
       <c r="Q125" s="5"/>
     </row>
@@ -10150,7 +10199,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10160,7 +10209,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -10175,18 +10224,18 @@
       <c r="B6" s="24"/>
       <c r="C6" s="8"/>
       <c r="E6" s="10" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
         <v>27</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10195,10 +10244,10 @@
       <c r="C7" s="8"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
@@ -10212,10 +10261,10 @@
       <c r="C8" s="8"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8" t="s">
@@ -10228,7 +10277,7 @@
       <c r="B9" s="24"/>
       <c r="C9" s="8"/>
       <c r="E9" s="6" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="5"/>
@@ -10237,7 +10286,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10246,7 +10295,7 @@
       <c r="C10" s="8"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>39</v>
@@ -10256,7 +10305,7 @@
         <v>45</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10265,17 +10314,17 @@
       <c r="C11" s="8"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10283,11 +10332,11 @@
       <c r="B12" s="24"/>
       <c r="C12" s="8"/>
       <c r="E12" s="10" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="8" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8" t="s">
@@ -10301,10 +10350,10 @@
       <c r="C13" s="8"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8" t="s">
@@ -10318,10 +10367,10 @@
       <c r="C14" s="8"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8" t="s">
@@ -10335,14 +10384,14 @@
       <c r="C15" s="8"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="G15" s="8" t="s">
         <v>404</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>401</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="J15" s="8"/>
     </row>
@@ -10351,7 +10400,7 @@
       <c r="B16" s="24"/>
       <c r="C16" s="8"/>
       <c r="E16" s="6" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="5"/>
@@ -10364,7 +10413,7 @@
       <c r="B17" s="24"/>
       <c r="C17" s="8"/>
       <c r="E17" s="10" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="8"/>
@@ -10387,13 +10436,13 @@
         <v>79</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>83</v>

--- a/server_nestjs/src/storage/Kompetenzraster.xlsx
+++ b/server_nestjs/src/storage/Kompetenzraster.xlsx
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="418">
   <si>
     <t xml:space="preserve">Voraussetzungen lt. Modulhandbuch</t>
   </si>
@@ -694,6 +694,9 @@
     <t xml:space="preserve">2,3,5</t>
   </si>
   <si>
+    <t xml:space="preserve">Installation von python</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python ist eine vielseitige und populäre Programmiersprache, die sich besonders für Data Science und Machine Learning eignet und durch ihre Einfachheit und die Verfügbarkeit vieler Bibliotheken auszeichnet. Für die Installation von Python wird häufig die Anaconda-Distribution empfohlen, die neben Python auch viele nützliche Bibliotheken und Entwicklungsumgebungen wie Spyder und Jupyter-Notebooks enthält, wobei Miniconda eine schlankere Alternative darstellt.</t>
   </si>
   <si>
@@ -745,12 +748,18 @@
     <t xml:space="preserve">In Python gibt es drei Arten von Zahlen: Integer (ganze Zahlen), Floats (Gleitkommazahlen) und komplexe Zahlen. Während Integer und Floats für alltägliche Berechnungen genutzt werden, wobei Floats aufgrund des IEEE 754 Standards zu Rundungsfehlern führen können, sind komplexe Zahlen mit einem imaginären Teil (in Python mit 'j' gekennzeichnet) ein speziellerer Datentyp, der seltener verwendet wird.</t>
   </si>
   <si>
+    <t xml:space="preserve">11,12,13</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,8,10,14</t>
   </si>
   <si>
     <t xml:space="preserve">Python bietet verschiedene Operatoren für mathematische Operationen, wie die Standardaddition, -subtraktion, -multiplikation und -division, sowie spezielle Operatoren für ganzzahlige Division (//), Modulus (%) und Exponentiation (**). Bei der Division von Ganzzahlen wird automatisch ein Fließkommawert zurückgegeben, während die ganzzahlige Division immer abrundet; zudem können alle Operatoren in Verbindung mit dem Zuweisungsoperator (z.B. +=, *=) für verkürzte Operationen verwendet werden.</t>
   </si>
   <si>
+    <t xml:space="preserve">9,10</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,8,10,11,12,13,15</t>
   </si>
   <si>
@@ -769,9 +778,6 @@
     <t xml:space="preserve">In Python repräsentieren Booleans die Wahrheitswerte True und False, die häufig in Vergleichsoperationen verwendet werden, um logische Bedingungen zu testen. Der Datentyp None wird oft zur Initialisierung von Variablen verwendet und hat nur einen Wert, nämlich None selbst, was anzeigt, dass eine Variable noch keinen anderen Wert zugewiesen bekommen hat.</t>
   </si>
   <si>
-    <t xml:space="preserve">6,8</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,18</t>
   </si>
   <si>
@@ -808,9 +814,6 @@
     <t xml:space="preserve">In Python ermöglichen for-Schleifen das Durchlaufen von iterierbaren Objekten wie Listen, indem man eine Variable über die Elemente iterieren lässt, beispielsweise mit `for element in my_list`. Die `range`-Funktion wird oft in for-Schleifen verwendet, um über eine Sequenz von Zahlen zu iterieren, wobei man Start-, Stopp- und Schrittweite angeben kann, um beispielsweise mit `for i in range(1, 10, 3)` die Zahlen 1, 4 und 7 zu durchlaufen.</t>
   </si>
   <si>
-    <t xml:space="preserve">6,8,18</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,23</t>
   </si>
   <si>
@@ -838,6 +841,9 @@
     <t xml:space="preserve">In Python können Funktionen als Variablen gespeichert und verwendet werden, was bedeutet, dass man eine Funktion einer Variablen zuweisen und dann diese Variable wie eine Funktion aufrufen kann. Dies ermöglicht es, Funktionen als Argumente an andere Funktionen zu übergeben und sogenannte Higher-Order Functions zu erstellen, die Funktionen höherer Ordnung sind und von anderen Funktionen abhängen können.</t>
   </si>
   <si>
+    <t xml:space="preserve">5, 23</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,23,27</t>
   </si>
   <si>
@@ -862,6 +868,9 @@
     <t xml:space="preserve">In Python können Variablen entweder mutable (veränderbar) oder immutable (unveränderbar) sein. Globale Variablen, die außerhalb von Funktionen definiert werden, können innerhalb von Funktionen gelesen und, wenn sie mutable sind, auch verändert werden, wobei die Änderungen dann global sichtbar sind; lokale Variablen hingegen sind nur innerhalb ihrer Funktion sichtbar und existieren außerhalb nicht.</t>
   </si>
   <si>
+    <t xml:space="preserve">23,29</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,31</t>
   </si>
   <si>
@@ -877,6 +886,9 @@
     <t xml:space="preserve">2,31,33</t>
   </si>
   <si>
+    <t xml:space="preserve">23,31</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,34</t>
   </si>
   <si>
@@ -917,6 +929,9 @@
   </si>
   <si>
     <t xml:space="preserve">Der Befehl reduce nimmt auch eine Funktion und iterierbares Objekt (z.B. Liste oder Tupel) entgegen. Die Funktion muss zwei Elemente in dem iterierbaren Objekt auf eines abbilden und reduziert nun durch sukzessives Anwenden der Funktion das gesamte iterierbare Objekt auf ein Element.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,23</t>
   </si>
   <si>
     <t xml:space="preserve">2,39</t>
@@ -1493,7 +1508,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1630,6 +1645,30 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1638,27 +1677,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1666,40 +1693,16 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1710,24 +1713,40 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1833,7 +1852,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I245"/>
-  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.15"/>
@@ -5315,25 +5334,25 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S1048576"/>
-  <sheetFormatPr defaultColWidth="10.72265625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:S127"/>
+  <sheetFormatPr defaultColWidth="10.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="17.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="17.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="25" width="16.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="25.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="25" width="22.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="31.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="25.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="31.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="11.99"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>186</v>
       </c>
@@ -5385,7 +5404,7 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="27"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="28"/>
       <c r="B2" s="29"/>
       <c r="C2" s="28"/>
@@ -5394,7 +5413,7 @@
       <c r="F2" s="29"/>
       <c r="I2" s="28"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="n">
         <v>2</v>
       </c>
@@ -5411,7 +5430,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="30" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I3" s="33"/>
       <c r="J3" s="1"/>
@@ -5426,17 +5445,17 @@
         <v>196</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="24"/>
+      <c r="B4" s="23"/>
       <c r="C4" s="34"/>
       <c r="D4" s="35"/>
       <c r="E4" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="23" t="s">
         <v>67</v>
       </c>
       <c r="G4" s="34" t="n">
@@ -5446,1826 +5465,1846 @@
         <v>3</v>
       </c>
       <c r="I4" s="38"/>
-      <c r="J4" s="12"/>
+      <c r="J4" s="18"/>
       <c r="K4" s="39"/>
       <c r="L4" s="39"/>
       <c r="M4" s="39"/>
       <c r="N4" s="39"/>
       <c r="O4" s="39"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
       <c r="R4" s="15"/>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="40" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="24"/>
-      <c r="C5" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="35"/>
+      <c r="C5" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="41"/>
       <c r="E5" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F5" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="G5" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" s="38" t="n">
+      <c r="G5" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="12"/>
-      <c r="K5" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
+      <c r="K5" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
       <c r="P5" s="12"/>
       <c r="Q5" s="12"/>
-      <c r="R5" s="42"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R5" s="45"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="23"/>
       <c r="C6" s="34" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="35"/>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="46" t="s">
         <v>199</v>
       </c>
-      <c r="F6" s="40" t="s">
-        <v>88</v>
+      <c r="F6" s="23" t="s">
+        <v>200</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="K6" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L6" s="41" t="s">
+      <c r="J6" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="M6" s="41"/>
+      <c r="K6" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M6" s="47"/>
       <c r="N6" s="39"/>
       <c r="O6" s="39"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="42"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="45"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="n">
+      <c r="A7" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="44" t="n">
+      <c r="B7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="43" t="n">
+      <c r="D7" s="21"/>
+      <c r="E7" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45" t="s">
+      <c r="I7" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="K7" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="F7" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="43" t="n">
+      <c r="M7" s="43"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="45"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46" t="s">
+        <v>205</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="G8" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="46" t="n">
+      <c r="H8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="K7" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L7" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M7" s="48"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="42"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="43" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="F8" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="G8" s="43" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="47" t="n">
+      <c r="I8" s="51" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="K8" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L8" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M8" s="48"/>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49"/>
+        <v>206</v>
+      </c>
+      <c r="K8" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L8" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M8" s="47"/>
+      <c r="N8" s="52"/>
+      <c r="O8" s="52"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
-      <c r="R8" s="51"/>
+      <c r="R8" s="53"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34" t="n">
+      <c r="A9" s="40" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" s="34"/>
+        <v>7</v>
+      </c>
+      <c r="C9" s="40"/>
       <c r="D9" s="21"/>
       <c r="E9" s="21" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F9" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="G9" s="34" t="n">
+      <c r="G9" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="34" t="n">
+      <c r="H9" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="52"/>
+      <c r="I9" s="49"/>
       <c r="J9" s="12"/>
-      <c r="K9" s="41" t="s">
+      <c r="K9" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="53"/>
+      <c r="L9" s="50"/>
+      <c r="M9" s="50"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="50"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="42"/>
+      <c r="R9" s="45"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="34" t="n">
+      <c r="A10" s="40" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="24"/>
-      <c r="C10" s="34" t="n">
+      <c r="C10" s="40" t="n">
         <v>5</v>
       </c>
       <c r="D10" s="24"/>
       <c r="E10" s="24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F10" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="34" t="n">
+      <c r="G10" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="H10" s="55" t="n">
+      <c r="H10" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="34" t="n">
+      <c r="I10" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="K10" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L10" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M10" s="41"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
+        <v>209</v>
+      </c>
+      <c r="K10" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L10" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M10" s="43"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="50"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
-      <c r="R10" s="51"/>
+      <c r="R10" s="53"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="34" t="n">
+      <c r="A11" s="40" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="24"/>
-      <c r="C11" s="34" t="n">
+      <c r="C11" s="40" t="n">
         <v>6</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="24" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F11" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="34" t="n">
+      <c r="G11" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="H11" s="55" t="n">
+      <c r="H11" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="34" t="n">
+      <c r="I11" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="8"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="53"/>
-      <c r="N11" s="53"/>
-      <c r="O11" s="53"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="50"/>
+      <c r="M11" s="50"/>
+      <c r="N11" s="50"/>
+      <c r="O11" s="50"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
-      <c r="R11" s="42"/>
+      <c r="R11" s="45"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="34" t="n">
+      <c r="A12" s="40" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="24"/>
-      <c r="C12" s="34" t="n">
+      <c r="C12" s="40" t="n">
         <v>7</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="F12" s="56" t="s">
+        <v>211</v>
+      </c>
+      <c r="F12" s="55" t="s">
         <v>133</v>
       </c>
-      <c r="G12" s="34" t="n">
+      <c r="G12" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="H12" s="34" t="n">
+      <c r="H12" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="I12" s="34" t="n">
+      <c r="I12" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="K12" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L12" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M12" s="41"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="53"/>
+        <v>212</v>
+      </c>
+      <c r="K12" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M12" s="43"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
-      <c r="R12" s="42"/>
+      <c r="R12" s="45"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34" t="n">
+      <c r="A13" s="40" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="24"/>
-      <c r="C13" s="34" t="n">
+      <c r="C13" s="40" t="n">
         <v>8</v>
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="F13" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="F13" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="G13" s="34" t="n">
+      <c r="G13" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="H13" s="34" t="n">
+      <c r="H13" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="34" t="n">
+      <c r="I13" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="K13" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L13" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M13" s="41"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="53"/>
+        <v>214</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M13" s="43"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="50"/>
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
-      <c r="R13" s="42"/>
+      <c r="R13" s="45"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="34" t="n">
+      <c r="A14" s="40" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="24"/>
-      <c r="C14" s="34" t="n">
+      <c r="C14" s="40" t="n">
         <v>9</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="F14" s="56" t="s">
         <v>215</v>
       </c>
-      <c r="G14" s="34" t="n">
+      <c r="F14" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="G14" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="H14" s="34" t="n">
+      <c r="H14" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="34" t="n">
+      <c r="I14" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="K14" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L14" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M14" s="41"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="53"/>
+        <v>217</v>
+      </c>
+      <c r="K14" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M14" s="43"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="50"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
-      <c r="R14" s="42"/>
+      <c r="R14" s="45"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34" t="n">
+      <c r="A15" s="40" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="34" t="n">
+      <c r="B15" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="C15" s="40" t="n">
         <v>10</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="F15" s="56" t="s">
+        <v>219</v>
+      </c>
+      <c r="F15" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="34" t="n">
+      <c r="G15" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="34" t="n">
+      <c r="H15" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="34" t="n">
+      <c r="I15" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="K15" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L15" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M15" s="41"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="53"/>
+        <v>220</v>
+      </c>
+      <c r="K15" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L15" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M15" s="43"/>
+      <c r="N15" s="50"/>
+      <c r="O15" s="50"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
-      <c r="R15" s="42"/>
+      <c r="R15" s="45"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34" t="n">
+      <c r="A16" s="40" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="34" t="n">
+      <c r="B16" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="C16" s="40" t="n">
         <v>11</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="F16" s="56" t="s">
+        <v>222</v>
+      </c>
+      <c r="F16" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="52" t="n">
-        <v>10</v>
-      </c>
-      <c r="H16" s="34" t="n">
+      <c r="G16" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="34" t="n">
+      <c r="I16" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="K16" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L16" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M16" s="41"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="53"/>
+        <v>223</v>
+      </c>
+      <c r="K16" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L16" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M16" s="43"/>
+      <c r="N16" s="50"/>
+      <c r="O16" s="50"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
-      <c r="R16" s="42"/>
+      <c r="R16" s="45"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="34" t="n">
+      <c r="A17" s="40" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="34" t="n">
+      <c r="B17" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="40" t="n">
         <v>12</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="F17" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="F17" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="G17" s="34" t="n">
+      <c r="G17" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="H17" s="34" t="n">
+      <c r="H17" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="I17" s="34" t="n">
+      <c r="I17" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="K17" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L17" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M17" s="41"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="53"/>
+        <v>225</v>
+      </c>
+      <c r="K17" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L17" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M17" s="43"/>
+      <c r="N17" s="50"/>
+      <c r="O17" s="50"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
-      <c r="R17" s="42"/>
+      <c r="R17" s="45"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="34" t="n">
+      <c r="A18" s="40" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="34" t="n">
+      <c r="B18" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" s="40" t="n">
         <v>13</v>
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="F18" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="F18" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="34" t="n">
+      <c r="G18" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="H18" s="34" t="n">
+      <c r="H18" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="34" t="n">
+      <c r="I18" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="K18" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L18" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M18" s="41"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="53"/>
+        <v>227</v>
+      </c>
+      <c r="K18" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L18" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M18" s="43"/>
+      <c r="N18" s="50"/>
+      <c r="O18" s="50"/>
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
-      <c r="R18" s="42"/>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="43" t="n">
+      <c r="R18" s="45"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="57" t="s">
-        <v>225</v>
-      </c>
-      <c r="C19" s="43" t="n">
+      <c r="B19" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="D19" s="44"/>
+      <c r="D19" s="23"/>
       <c r="E19" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="F19" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="F19" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="G19" s="43" t="n">
+      <c r="G19" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="43" t="n">
+      <c r="H19" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="43" t="n">
+      <c r="I19" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M19" s="49"/>
-      <c r="N19" s="49"/>
-      <c r="O19" s="49"/>
+        <v>229</v>
+      </c>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M19" s="52"/>
+      <c r="N19" s="52"/>
+      <c r="O19" s="52"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
-      <c r="R19" s="42"/>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="43" t="n">
+      <c r="R19" s="45"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="34" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="43" t="n">
+      <c r="B20" s="23"/>
+      <c r="C20" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="D20" s="44"/>
+      <c r="D20" s="23"/>
       <c r="E20" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="F20" s="50" t="s">
+        <v>230</v>
+      </c>
+      <c r="F20" s="58" t="s">
         <v>103</v>
       </c>
-      <c r="G20" s="43" t="n">
+      <c r="G20" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="H20" s="43" t="n">
+      <c r="H20" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="I20" s="43" t="n">
+      <c r="I20" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="K20" s="48"/>
-      <c r="L20" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M20" s="48"/>
-      <c r="N20" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="O20" s="48"/>
+        <v>231</v>
+      </c>
+      <c r="K20" s="47"/>
+      <c r="L20" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M20" s="47"/>
+      <c r="N20" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="O20" s="47"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
-      <c r="R20" s="51"/>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="43" t="n">
+      <c r="R20" s="53"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="44" t="n">
+      <c r="B21" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="43" t="n">
+      <c r="C21" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="D21" s="44" t="n">
+      <c r="D21" s="23" t="n">
         <v>19</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="F21" s="50" t="s">
+        <v>233</v>
+      </c>
+      <c r="F21" s="58" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="43" t="n">
+      <c r="G21" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="H21" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" s="43" t="n">
+      <c r="H21" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="20"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="49"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="49"/>
-      <c r="O21" s="49"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="52"/>
+      <c r="O21" s="52"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
-      <c r="R21" s="42"/>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="43" t="n">
+      <c r="R21" s="45"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="34" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="44"/>
-      <c r="C22" s="43" t="n">
+      <c r="B22" s="23"/>
+      <c r="C22" s="34" t="n">
         <v>17</v>
       </c>
-      <c r="D22" s="44"/>
+      <c r="D22" s="23"/>
       <c r="E22" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="F22" s="59" t="s">
+        <v>235</v>
+      </c>
+      <c r="G22" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="K22" s="47"/>
+      <c r="L22" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M22" s="47"/>
+      <c r="N22" s="47" t="s">
         <v>232</v>
       </c>
-      <c r="F22" s="58" t="s">
-        <v>233</v>
-      </c>
-      <c r="G22" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="H22" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="K22" s="48"/>
-      <c r="L22" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M22" s="48"/>
-      <c r="N22" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="O22" s="48"/>
+      <c r="O22" s="47"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
-      <c r="R22" s="42"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="43" t="n">
+      <c r="R22" s="45"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="34" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="43" t="n">
+      <c r="B23" s="23"/>
+      <c r="C23" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="D23" s="44"/>
+      <c r="D23" s="23"/>
       <c r="E23" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="F23" s="58" t="s">
-        <v>236</v>
-      </c>
-      <c r="G23" s="43" t="n">
+        <v>237</v>
+      </c>
+      <c r="F23" s="59" t="s">
+        <v>238</v>
+      </c>
+      <c r="G23" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="H23" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I23" s="43" t="n">
+      <c r="H23" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="K23" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L23" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M23" s="48"/>
-      <c r="N23" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="O23" s="48"/>
+        <v>239</v>
+      </c>
+      <c r="K23" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L23" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M23" s="47"/>
+      <c r="N23" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="O23" s="47"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
-      <c r="R23" s="51"/>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="34" t="n">
+      <c r="R23" s="53"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="40" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="C24" s="34" t="n">
+      <c r="B24" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" s="40" t="n">
         <v>19</v>
       </c>
       <c r="D24" s="24"/>
       <c r="E24" s="24" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F24" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="G24" s="34" t="n">
+      <c r="G24" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" s="34" t="n">
+      <c r="H24" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J24" s="8"/>
-      <c r="K24" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="53"/>
+      <c r="K24" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L24" s="50"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="50"/>
+      <c r="O24" s="50"/>
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
-      <c r="R24" s="42"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="34"/>
+      <c r="R24" s="45"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="40"/>
       <c r="B25" s="24"/>
-      <c r="C25" s="34" t="n">
+      <c r="C25" s="40" t="n">
         <v>20</v>
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="24" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F25" s="24"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34" t="n">
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="K25" s="53"/>
-      <c r="L25" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M25" s="41"/>
-      <c r="N25" s="41" t="s">
-        <v>230</v>
-      </c>
-      <c r="O25" s="41"/>
+        <v>241</v>
+      </c>
+      <c r="K25" s="50"/>
+      <c r="L25" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="O25" s="43"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
-      <c r="R25" s="42"/>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="34"/>
+      <c r="R25" s="45"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="40"/>
       <c r="B26" s="24"/>
-      <c r="C26" s="34" t="n">
+      <c r="C26" s="40" t="n">
         <v>21</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="F26" s="40" t="s">
+        <v>240</v>
+      </c>
+      <c r="F26" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="G26" s="34" t="n">
+      <c r="G26" s="40" t="n">
         <v>23</v>
       </c>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34" t="n">
+      <c r="H26" s="40"/>
+      <c r="I26" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="K26" s="41" t="s">
-        <v>230</v>
-      </c>
-      <c r="L26" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M26" s="41"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="53"/>
+        <v>242</v>
+      </c>
+      <c r="K26" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="L26" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M26" s="43"/>
+      <c r="N26" s="50"/>
+      <c r="O26" s="50"/>
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
-      <c r="R26" s="42"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="34" t="n">
+      <c r="R26" s="45"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="40" t="n">
         <v>24</v>
       </c>
       <c r="B27" s="24"/>
-      <c r="C27" s="34" t="n">
+      <c r="C27" s="40" t="n">
         <v>22</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="F27" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="F27" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="G27" s="34" t="n">
+      <c r="G27" s="40" t="n">
         <v>23</v>
       </c>
-      <c r="H27" s="34" t="n">
+      <c r="H27" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="I27" s="34" t="n">
+      <c r="I27" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="K27" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L27" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M27" s="41"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
+        <v>244</v>
+      </c>
+      <c r="K27" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L27" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M27" s="43"/>
+      <c r="N27" s="50"/>
+      <c r="O27" s="50"/>
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
-      <c r="R27" s="42"/>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34" t="n">
+      <c r="R27" s="45"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="40" t="n">
         <v>25</v>
       </c>
       <c r="B28" s="24"/>
-      <c r="C28" s="34" t="n">
+      <c r="C28" s="40" t="n">
         <v>23</v>
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="F28" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="F28" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="G28" s="34" t="n">
+      <c r="G28" s="40" t="n">
         <v>23</v>
       </c>
-      <c r="H28" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" s="34" t="n">
+      <c r="H28" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K28" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L28" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M28" s="41"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
+        <v>246</v>
+      </c>
+      <c r="K28" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L28" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M28" s="43"/>
+      <c r="N28" s="50"/>
+      <c r="O28" s="50"/>
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
-      <c r="R28" s="42"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="34" t="n">
+      <c r="R28" s="45"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="40" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="34" t="n">
+      <c r="B29" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="C29" s="40" t="n">
         <v>24</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="F29" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="F29" s="60" t="s">
         <v>112</v>
       </c>
-      <c r="G29" s="52" t="n">
+      <c r="G29" s="49" t="n">
         <v>23</v>
       </c>
-      <c r="H29" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="I29" s="34" t="n">
+      <c r="H29" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="K29" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L29" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M29" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="N29" s="53"/>
-      <c r="O29" s="53"/>
+        <v>248</v>
+      </c>
+      <c r="K29" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L29" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M29" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="N29" s="50"/>
+      <c r="O29" s="50"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="8"/>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="34"/>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="40"/>
       <c r="B30" s="24"/>
-      <c r="C30" s="34" t="n">
+      <c r="C30" s="40" t="n">
         <v>25</v>
       </c>
       <c r="D30" s="24"/>
       <c r="E30" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="F30" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="F30" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="G30" s="34" t="n">
+      <c r="G30" s="40" t="n">
         <v>23</v>
       </c>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34" t="n">
+      <c r="H30" s="40"/>
+      <c r="I30" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="8"/>
-      <c r="K30" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="L30" s="53"/>
-      <c r="M30" s="53"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="53"/>
+      <c r="K30" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="L30" s="50"/>
+      <c r="M30" s="50"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="50"/>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
-      <c r="R30" s="42"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="34" t="n">
+      <c r="R30" s="45"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="40" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="34" t="n">
+      <c r="B31" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="C31" s="40" t="n">
         <v>26</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="F31" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="F31" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="G31" s="34" t="n">
-        <v>23</v>
-      </c>
-      <c r="H31" s="34" t="n">
+      <c r="G31" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="I31" s="34" t="n">
+      <c r="I31" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="K31" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L31" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M31" s="53"/>
-      <c r="N31" s="53"/>
-      <c r="O31" s="53"/>
+        <v>251</v>
+      </c>
+      <c r="K31" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L31" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M31" s="50"/>
+      <c r="N31" s="50"/>
+      <c r="O31" s="50"/>
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
-      <c r="R31" s="42"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="34" t="n">
+      <c r="R31" s="45"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="40" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="34" t="n">
+      <c r="B32" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="C32" s="40" t="n">
         <v>27</v>
       </c>
       <c r="D32" s="24"/>
       <c r="E32" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="F32" s="40" t="s">
+        <v>252</v>
+      </c>
+      <c r="F32" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="G32" s="34" t="n">
+      <c r="G32" s="40" t="n">
         <v>23</v>
       </c>
-      <c r="H32" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I32" s="34" t="n">
+      <c r="H32" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I32" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="K32" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L32" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M32" s="53"/>
-      <c r="N32" s="53"/>
-      <c r="O32" s="53"/>
+        <v>253</v>
+      </c>
+      <c r="K32" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L32" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M32" s="50"/>
+      <c r="N32" s="50"/>
+      <c r="O32" s="50"/>
       <c r="P32" s="8"/>
       <c r="Q32" s="8"/>
-      <c r="R32" s="42"/>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="43" t="n">
+      <c r="R32" s="45"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="34" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="44" t="n">
+      <c r="B33" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="C33" s="34" t="n">
+        <v>28</v>
+      </c>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="F33" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="G33" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="C33" s="43" t="n">
-        <v>28</v>
-      </c>
-      <c r="D33" s="44"/>
-      <c r="E33" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="F33" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="G33" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="I33" s="43" t="n">
+      <c r="I33" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="K33" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L33" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M33" s="49"/>
-      <c r="N33" s="49"/>
-      <c r="O33" s="49"/>
+        <v>255</v>
+      </c>
+      <c r="K33" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L33" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M33" s="52"/>
+      <c r="N33" s="52"/>
+      <c r="O33" s="52"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
-      <c r="R33" s="42"/>
-    </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="43" t="n">
+      <c r="R33" s="45"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="44"/>
-      <c r="C34" s="43" t="n">
+      <c r="B34" s="23"/>
+      <c r="C34" s="34" t="n">
         <v>29</v>
       </c>
-      <c r="D34" s="44"/>
+      <c r="D34" s="23"/>
       <c r="E34" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="F34" s="60" t="s">
+        <v>256</v>
+      </c>
+      <c r="F34" s="61" t="s">
         <v>117</v>
       </c>
-      <c r="G34" s="47" t="n">
+      <c r="G34" s="51" t="n">
         <v>29</v>
       </c>
-      <c r="H34" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="I34" s="43" t="n">
+      <c r="H34" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="I34" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="K34" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L34" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M34" s="49"/>
-      <c r="N34" s="49"/>
-      <c r="O34" s="49"/>
+        <v>257</v>
+      </c>
+      <c r="K34" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L34" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M34" s="52"/>
+      <c r="N34" s="52"/>
+      <c r="O34" s="52"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
-      <c r="R34" s="51"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="34" t="n">
+      <c r="R34" s="53"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="40" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="24" t="n">
-        <v>23</v>
-      </c>
-      <c r="C35" s="34"/>
+      <c r="B35" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="C35" s="40"/>
       <c r="D35" s="24"/>
-      <c r="E35" s="61" t="s">
-        <v>256</v>
+      <c r="E35" s="62" t="s">
+        <v>259</v>
       </c>
       <c r="F35" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="52" t="n">
+      <c r="G35" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="I35" s="34"/>
+      <c r="H35" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I35" s="40"/>
       <c r="J35" s="8"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="53"/>
-      <c r="N35" s="53"/>
-      <c r="O35" s="53"/>
+      <c r="K35" s="50"/>
+      <c r="L35" s="50"/>
+      <c r="M35" s="50"/>
+      <c r="N35" s="50"/>
+      <c r="O35" s="50"/>
       <c r="P35" s="8"/>
       <c r="Q35" s="8"/>
-      <c r="R35" s="42"/>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="34" t="n">
+      <c r="R35" s="45"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="40" t="n">
         <v>32</v>
       </c>
       <c r="B36" s="24"/>
-      <c r="C36" s="34" t="n">
+      <c r="C36" s="40" t="n">
         <v>30</v>
       </c>
       <c r="D36" s="24"/>
       <c r="E36" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="F36" s="40" t="s">
+        <v>260</v>
+      </c>
+      <c r="F36" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="G36" s="34" t="n">
+      <c r="G36" s="40" t="n">
         <v>31</v>
       </c>
-      <c r="H36" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I36" s="34" t="n">
+      <c r="H36" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I36" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="K36" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L36" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M36" s="53"/>
-      <c r="N36" s="53"/>
-      <c r="O36" s="53"/>
+        <v>261</v>
+      </c>
+      <c r="K36" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L36" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
+      <c r="O36" s="50"/>
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
-      <c r="R36" s="42"/>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="34"/>
+      <c r="R36" s="45"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="40"/>
       <c r="B37" s="24"/>
-      <c r="C37" s="34" t="n">
+      <c r="C37" s="40" t="n">
         <v>31</v>
       </c>
       <c r="D37" s="24"/>
-      <c r="E37" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="F37" s="40" t="s">
+      <c r="E37" s="62" t="s">
+        <v>259</v>
+      </c>
+      <c r="F37" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="G37" s="34" t="n">
+      <c r="G37" s="40" t="n">
         <v>31</v>
       </c>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34" t="n">
+      <c r="H37" s="40"/>
+      <c r="I37" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="K37" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L37" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M37" s="53"/>
-      <c r="N37" s="53"/>
-      <c r="O37" s="53"/>
+        <v>262</v>
+      </c>
+      <c r="K37" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L37" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M37" s="50"/>
+      <c r="N37" s="50"/>
+      <c r="O37" s="50"/>
       <c r="P37" s="8"/>
       <c r="Q37" s="8"/>
-      <c r="R37" s="51"/>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="34" t="n">
+      <c r="R37" s="53"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="40" t="n">
         <v>33</v>
       </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="34" t="n">
+      <c r="B38" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="C38" s="40" t="n">
         <v>32</v>
       </c>
       <c r="D38" s="24"/>
       <c r="E38" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="F38" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="F38" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="G38" s="34" t="n">
+      <c r="G38" s="40" t="n">
         <v>31</v>
       </c>
-      <c r="H38" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I38" s="34" t="n">
+      <c r="H38" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I38" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J38" s="8"/>
-      <c r="K38" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L38" s="53"/>
-      <c r="M38" s="53"/>
-      <c r="N38" s="53"/>
-      <c r="O38" s="53"/>
+      <c r="K38" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L38" s="50"/>
+      <c r="M38" s="50"/>
+      <c r="N38" s="50"/>
+      <c r="O38" s="50"/>
       <c r="P38" s="8"/>
       <c r="Q38" s="8"/>
-      <c r="R38" s="42"/>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="43" t="n">
+      <c r="R38" s="45"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="34" t="n">
         <v>34</v>
       </c>
-      <c r="B39" s="44" t="n">
-        <v>23</v>
-      </c>
-      <c r="C39" s="43" t="n">
+      <c r="B39" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="C39" s="34" t="n">
         <v>33</v>
       </c>
-      <c r="D39" s="44"/>
+      <c r="D39" s="23"/>
       <c r="E39" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="F39" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="F39" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="G39" s="43" t="n">
+      <c r="G39" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H39" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" s="43" t="n">
+      <c r="H39" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I39" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="K39" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L39" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M39" s="49"/>
-      <c r="N39" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="O39" s="48" t="s">
-        <v>230</v>
+        <v>266</v>
+      </c>
+      <c r="K39" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L39" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M39" s="52"/>
+      <c r="N39" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="O39" s="47" t="s">
+        <v>232</v>
       </c>
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
-      <c r="R39" s="42"/>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="43"/>
-      <c r="B40" s="44"/>
-      <c r="C40" s="43" t="n">
+      <c r="R39" s="45"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="34"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="34" t="n">
         <v>34</v>
       </c>
-      <c r="D40" s="44"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="F40" s="44"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="43"/>
-      <c r="I40" s="43" t="n">
+        <v>265</v>
+      </c>
+      <c r="F40" s="23"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="K40" s="49"/>
-      <c r="L40" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M40" s="49"/>
-      <c r="N40" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="O40" s="48"/>
+        <v>267</v>
+      </c>
+      <c r="K40" s="52"/>
+      <c r="L40" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M40" s="52"/>
+      <c r="N40" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="O40" s="47"/>
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
-      <c r="R40" s="42"/>
-    </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="43"/>
-      <c r="B41" s="44"/>
-      <c r="C41" s="43" t="n">
+      <c r="R40" s="45"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="34"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="34" t="n">
         <v>35</v>
       </c>
-      <c r="D41" s="44"/>
+      <c r="D41" s="23"/>
       <c r="E41" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="F41" s="50" t="s">
+        <v>265</v>
+      </c>
+      <c r="F41" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="G41" s="43" t="n">
+      <c r="G41" s="34" t="n">
         <v>34</v>
       </c>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43" t="n">
+      <c r="H41" s="34"/>
+      <c r="I41" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="K41" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="L41" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M41" s="49"/>
-      <c r="N41" s="49"/>
-      <c r="O41" s="49"/>
+        <v>268</v>
+      </c>
+      <c r="K41" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="L41" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M41" s="52"/>
+      <c r="N41" s="52"/>
+      <c r="O41" s="52"/>
       <c r="P41" s="5"/>
       <c r="Q41" s="5"/>
-      <c r="R41" s="51"/>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="34" t="n">
+      <c r="R41" s="53"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="40" t="n">
         <v>35</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="34"/>
+      <c r="B42" s="24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C42" s="40"/>
       <c r="D42" s="24"/>
       <c r="E42" s="24" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F42" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="G42" s="34" t="n">
+      <c r="G42" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I42" s="34"/>
+      <c r="H42" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I42" s="40"/>
       <c r="J42" s="8"/>
-      <c r="K42" s="53"/>
-      <c r="L42" s="53"/>
-      <c r="M42" s="53"/>
-      <c r="N42" s="53"/>
-      <c r="O42" s="53"/>
+      <c r="K42" s="50"/>
+      <c r="L42" s="50"/>
+      <c r="M42" s="50"/>
+      <c r="N42" s="50"/>
+      <c r="O42" s="50"/>
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
-      <c r="R42" s="42"/>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="34" t="n">
+      <c r="R42" s="45"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="40" t="n">
         <v>36</v>
       </c>
       <c r="B43" s="24"/>
-      <c r="C43" s="34" t="n">
+      <c r="C43" s="40" t="n">
         <v>36</v>
       </c>
       <c r="D43" s="24"/>
       <c r="E43" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="F43" s="40" t="s">
+        <v>270</v>
+      </c>
+      <c r="F43" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="G43" s="34" t="n">
+      <c r="G43" s="40" t="n">
         <v>35</v>
       </c>
-      <c r="H43" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I43" s="34" t="n">
+      <c r="H43" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I43" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="K43" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L43" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M43" s="53"/>
-      <c r="N43" s="41" t="s">
-        <v>230</v>
-      </c>
-      <c r="O43" s="53"/>
+        <v>271</v>
+      </c>
+      <c r="K43" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L43" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M43" s="50"/>
+      <c r="N43" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="O43" s="50"/>
       <c r="P43" s="8"/>
       <c r="Q43" s="8"/>
-      <c r="R43" s="51"/>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="34" t="n">
+      <c r="R43" s="53"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="40" t="n">
         <v>37</v>
       </c>
       <c r="B44" s="24"/>
-      <c r="C44" s="34" t="n">
+      <c r="C44" s="40" t="n">
         <v>37</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="F44" s="40" t="s">
+        <v>270</v>
+      </c>
+      <c r="F44" s="56" t="s">
         <v>124</v>
       </c>
-      <c r="G44" s="34" t="n">
+      <c r="G44" s="40" t="n">
         <v>35</v>
       </c>
-      <c r="H44" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I44" s="34" t="n">
+      <c r="H44" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I44" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J44" s="8"/>
-      <c r="K44" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L44" s="53"/>
-      <c r="M44" s="53"/>
-      <c r="N44" s="53"/>
-      <c r="O44" s="53"/>
+      <c r="K44" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L44" s="50"/>
+      <c r="M44" s="50"/>
+      <c r="N44" s="50"/>
+      <c r="O44" s="50"/>
       <c r="P44" s="8" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q44" s="8"/>
-      <c r="R44" s="51"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="34"/>
+      <c r="R44" s="53"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="40"/>
       <c r="B45" s="24"/>
-      <c r="C45" s="34" t="n">
+      <c r="C45" s="40" t="n">
         <v>38</v>
       </c>
       <c r="D45" s="24"/>
       <c r="E45" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="F45" s="40"/>
-      <c r="G45" s="34"/>
-      <c r="H45" s="34"/>
-      <c r="I45" s="34" t="n">
+        <v>273</v>
+      </c>
+      <c r="F45" s="56"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J45" s="8"/>
-      <c r="K45" s="41" t="s">
-        <v>230</v>
-      </c>
-      <c r="L45" s="53"/>
-      <c r="M45" s="53"/>
-      <c r="N45" s="53"/>
-      <c r="O45" s="53"/>
+      <c r="K45" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="L45" s="50"/>
+      <c r="M45" s="50"/>
+      <c r="N45" s="50"/>
+      <c r="O45" s="50"/>
       <c r="P45" s="8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q45" s="8"/>
-      <c r="R45" s="51"/>
-    </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="34"/>
+      <c r="R45" s="53"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="40"/>
       <c r="B46" s="24"/>
-      <c r="C46" s="34" t="n">
+      <c r="C46" s="40" t="n">
         <v>39</v>
       </c>
       <c r="D46" s="24"/>
       <c r="E46" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="F46" s="40"/>
-      <c r="G46" s="34"/>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34" t="n">
+        <v>273</v>
+      </c>
+      <c r="F46" s="56"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="40"/>
+      <c r="I46" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J46" s="8"/>
-      <c r="K46" s="41" t="s">
-        <v>230</v>
-      </c>
-      <c r="L46" s="53"/>
-      <c r="M46" s="53"/>
-      <c r="N46" s="53"/>
-      <c r="O46" s="53"/>
+      <c r="K46" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="L46" s="50"/>
+      <c r="M46" s="50"/>
+      <c r="N46" s="50"/>
+      <c r="O46" s="50"/>
       <c r="P46" s="8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q46" s="8"/>
-      <c r="R46" s="51"/>
-    </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="34"/>
+      <c r="R46" s="53"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="40"/>
       <c r="B47" s="24"/>
-      <c r="C47" s="34" t="n">
+      <c r="C47" s="40" t="n">
         <v>40</v>
       </c>
       <c r="D47" s="24"/>
       <c r="E47" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="F47" s="40"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="34"/>
-      <c r="I47" s="34" t="n">
+        <v>273</v>
+      </c>
+      <c r="F47" s="56"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="40"/>
+      <c r="I47" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J47" s="8"/>
-      <c r="K47" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="L47" s="53"/>
-      <c r="M47" s="53"/>
-      <c r="N47" s="53"/>
-      <c r="O47" s="53"/>
+      <c r="K47" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="L47" s="50"/>
+      <c r="M47" s="50"/>
+      <c r="N47" s="50"/>
+      <c r="O47" s="50"/>
       <c r="P47" s="8" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q47" s="8"/>
-      <c r="R47" s="42"/>
-    </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="34" t="n">
+      <c r="R47" s="45"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="40" t="n">
         <v>38</v>
       </c>
       <c r="B48" s="24"/>
-      <c r="C48" s="34" t="n">
+      <c r="C48" s="40" t="n">
         <v>41</v>
       </c>
       <c r="D48" s="24"/>
       <c r="E48" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="F48" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="F48" s="56" t="s">
         <v>125</v>
       </c>
-      <c r="G48" s="34" t="n">
+      <c r="G48" s="40" t="n">
         <v>35</v>
       </c>
-      <c r="H48" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I48" s="34" t="n">
+      <c r="H48" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I48" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="K48" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L48" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M48" s="53"/>
-      <c r="N48" s="41" t="s">
-        <v>230</v>
-      </c>
-      <c r="O48" s="53"/>
+        <v>278</v>
+      </c>
+      <c r="K48" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L48" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M48" s="50"/>
+      <c r="N48" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="O48" s="50"/>
       <c r="P48" s="8"/>
       <c r="Q48" s="8"/>
-      <c r="R48" s="51"/>
-    </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="43" t="n">
+      <c r="R48" s="53"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="34" t="n">
         <v>39</v>
       </c>
-      <c r="B49" s="44" t="n">
-        <v>8</v>
-      </c>
-      <c r="C49" s="43"/>
-      <c r="D49" s="44"/>
+      <c r="B49" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="C49" s="34"/>
+      <c r="D49" s="23"/>
       <c r="E49" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="F49" s="44" t="s">
+        <v>280</v>
+      </c>
+      <c r="F49" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="G49" s="43" t="n">
+      <c r="G49" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I49" s="43"/>
+      <c r="H49" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I49" s="34"/>
       <c r="J49" s="5"/>
-      <c r="K49" s="49"/>
-      <c r="L49" s="49"/>
-      <c r="M49" s="49"/>
-      <c r="N49" s="49"/>
-      <c r="O49" s="49"/>
+      <c r="K49" s="52"/>
+      <c r="L49" s="52"/>
+      <c r="M49" s="52"/>
+      <c r="N49" s="52"/>
+      <c r="O49" s="52"/>
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
-      <c r="R49" s="42"/>
-    </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="43" t="n">
+      <c r="R49" s="45"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="34" t="n">
         <v>40</v>
       </c>
-      <c r="B50" s="44"/>
-      <c r="C50" s="43" t="n">
+      <c r="B50" s="23"/>
+      <c r="C50" s="34" t="n">
         <v>42</v>
       </c>
-      <c r="D50" s="44"/>
+      <c r="D50" s="23"/>
       <c r="E50" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="F50" s="50" t="s">
+        <v>281</v>
+      </c>
+      <c r="F50" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="G50" s="43" t="n">
+      <c r="G50" s="34" t="n">
         <v>39</v>
       </c>
-      <c r="H50" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I50" s="43" t="n">
+      <c r="H50" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I50" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J50" s="5"/>
-      <c r="K50" s="49"/>
-      <c r="L50" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M50" s="49"/>
-      <c r="N50" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="O50" s="49"/>
+      <c r="K50" s="52"/>
+      <c r="L50" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M50" s="52"/>
+      <c r="N50" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="O50" s="52"/>
       <c r="P50" s="5"/>
       <c r="Q50" s="5"/>
-      <c r="R50" s="51"/>
-    </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="43" t="n">
+      <c r="R50" s="53"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="34" t="n">
         <v>41</v>
       </c>
-      <c r="B51" s="44"/>
-      <c r="C51" s="43" t="n">
+      <c r="B51" s="23"/>
+      <c r="C51" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="D51" s="44"/>
+      <c r="D51" s="23"/>
       <c r="E51" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="F51" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="F51" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="G51" s="43" t="n">
+      <c r="G51" s="34" t="n">
         <v>39</v>
       </c>
-      <c r="H51" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I51" s="43" t="n">
+      <c r="H51" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I51" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="5"/>
-      <c r="K51" s="49"/>
-      <c r="L51" s="49"/>
-      <c r="M51" s="49"/>
-      <c r="N51" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="O51" s="49"/>
+      <c r="K51" s="52"/>
+      <c r="L51" s="52"/>
+      <c r="M51" s="52"/>
+      <c r="N51" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="O51" s="52"/>
       <c r="P51" s="5"/>
       <c r="Q51" s="5"/>
-      <c r="R51" s="51"/>
-    </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="43" t="n">
+      <c r="R51" s="53"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="34" t="n">
         <v>42</v>
       </c>
-      <c r="B52" s="44"/>
-      <c r="C52" s="43" t="n">
+      <c r="B52" s="23"/>
+      <c r="C52" s="34" t="n">
         <v>44</v>
       </c>
-      <c r="D52" s="44"/>
+      <c r="D52" s="23"/>
       <c r="E52" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="F52" s="50" t="s">
+        <v>283</v>
+      </c>
+      <c r="F52" s="58" t="s">
         <v>129</v>
       </c>
-      <c r="G52" s="43" t="n">
+      <c r="G52" s="34" t="n">
         <v>39</v>
       </c>
-      <c r="H52" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I52" s="43" t="n">
+      <c r="H52" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I52" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J52" s="5"/>
-      <c r="K52" s="49"/>
-      <c r="L52" s="49"/>
-      <c r="M52" s="49"/>
-      <c r="N52" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="O52" s="49"/>
+      <c r="K52" s="52"/>
+      <c r="L52" s="52"/>
+      <c r="M52" s="52"/>
+      <c r="N52" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="O52" s="52"/>
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
-      <c r="R52" s="51"/>
-    </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R52" s="53"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="28"/>
       <c r="B53" s="29"/>
       <c r="C53" s="28"/>
@@ -7280,20 +7319,22 @@
       <c r="M53" s="25"/>
       <c r="N53" s="25"/>
       <c r="O53" s="25"/>
-      <c r="R53" s="51"/>
-    </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R53" s="53"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="28" t="n">
         <v>43</v>
       </c>
-      <c r="B54" s="29"/>
+      <c r="B54" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="C54" s="28"/>
       <c r="D54" s="29"/>
       <c r="E54" s="29" t="n">
         <v>43</v>
       </c>
       <c r="F54" s="31" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G54" s="30" t="n">
         <v>1</v>
@@ -7307,2653 +7348,2652 @@
       <c r="M54" s="25"/>
       <c r="N54" s="25"/>
       <c r="O54" s="25"/>
-      <c r="R54" s="51"/>
-    </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="34" t="n">
+      <c r="R54" s="53"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="40" t="n">
         <v>44</v>
       </c>
       <c r="B55" s="24"/>
-      <c r="C55" s="34" t="n">
+      <c r="C55" s="40" t="n">
         <v>45</v>
       </c>
       <c r="D55" s="24"/>
       <c r="E55" s="24" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F55" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="G55" s="52" t="n">
+      <c r="G55" s="49" t="n">
         <v>43</v>
       </c>
-      <c r="H55" s="52" t="n">
+      <c r="H55" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="I55" s="34" t="n">
+      <c r="I55" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J55" s="8"/>
-      <c r="K55" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L55" s="53"/>
-      <c r="M55" s="53"/>
-      <c r="N55" s="53"/>
-      <c r="O55" s="53"/>
+      <c r="K55" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L55" s="50"/>
+      <c r="M55" s="50"/>
+      <c r="N55" s="50"/>
+      <c r="O55" s="50"/>
       <c r="P55" s="8"/>
       <c r="Q55" s="8"/>
-      <c r="R55" s="51"/>
-    </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="43" t="n">
+      <c r="R55" s="53"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="B56" s="44"/>
-      <c r="C56" s="43" t="n">
+      <c r="B56" s="23"/>
+      <c r="C56" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="D56" s="44"/>
+      <c r="D56" s="23"/>
       <c r="E56" s="23" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="F56" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="G56" s="43" t="n">
+      <c r="G56" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H56" s="43" t="n">
+      <c r="H56" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="43" t="n">
+      <c r="I56" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J56" s="5"/>
-      <c r="K56" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L56" s="49"/>
-      <c r="M56" s="49"/>
-      <c r="N56" s="49"/>
-      <c r="O56" s="49"/>
+      <c r="K56" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L56" s="52"/>
+      <c r="M56" s="52"/>
+      <c r="N56" s="52"/>
+      <c r="O56" s="52"/>
       <c r="P56" s="5"/>
       <c r="Q56" s="5"/>
-      <c r="R56" s="51"/>
-    </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="34" t="n">
+      <c r="R56" s="53"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="40" t="n">
         <v>46</v>
       </c>
       <c r="B57" s="24"/>
-      <c r="C57" s="34" t="n">
+      <c r="C57" s="40" t="n">
         <v>47</v>
       </c>
       <c r="D57" s="24"/>
       <c r="E57" s="24" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F57" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="G57" s="34" t="n">
+      <c r="G57" s="40" t="n">
         <v>43</v>
       </c>
-      <c r="H57" s="34" t="n">
+      <c r="H57" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I57" s="34" t="n">
+      <c r="I57" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J57" s="8"/>
-      <c r="K57" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L57" s="53"/>
-      <c r="M57" s="53"/>
-      <c r="N57" s="53"/>
-      <c r="O57" s="53"/>
+      <c r="K57" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L57" s="50"/>
+      <c r="M57" s="50"/>
+      <c r="N57" s="50"/>
+      <c r="O57" s="50"/>
       <c r="P57" s="8"/>
       <c r="Q57" s="8"/>
-      <c r="R57" s="51"/>
-    </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="34" t="n">
+      <c r="R57" s="53"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="40" t="n">
         <v>47</v>
       </c>
       <c r="B58" s="24"/>
-      <c r="C58" s="34" t="n">
+      <c r="C58" s="40" t="n">
         <v>48</v>
       </c>
       <c r="D58" s="24"/>
       <c r="E58" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="F58" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="F58" s="56" t="s">
         <v>133</v>
       </c>
-      <c r="G58" s="34" t="n">
+      <c r="G58" s="40" t="n">
         <v>46</v>
       </c>
-      <c r="H58" s="34" t="n">
+      <c r="H58" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="34" t="n">
+      <c r="I58" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J58" s="8"/>
-      <c r="K58" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L58" s="53"/>
-      <c r="M58" s="53"/>
-      <c r="N58" s="53"/>
-      <c r="O58" s="53"/>
+      <c r="K58" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L58" s="50"/>
+      <c r="M58" s="50"/>
+      <c r="N58" s="50"/>
+      <c r="O58" s="50"/>
       <c r="P58" s="8"/>
       <c r="Q58" s="8"/>
-      <c r="R58" s="51"/>
-    </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="34" t="n">
+      <c r="R58" s="53"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="40" t="n">
         <v>48</v>
       </c>
       <c r="B59" s="24" t="n">
         <v>47</v>
       </c>
-      <c r="C59" s="34" t="n">
+      <c r="C59" s="40" t="n">
         <v>49</v>
       </c>
       <c r="D59" s="24"/>
       <c r="E59" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="F59" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="F59" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="G59" s="34" t="n">
+      <c r="G59" s="40" t="n">
         <v>46</v>
       </c>
-      <c r="H59" s="34" t="n">
+      <c r="H59" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I59" s="34" t="n">
+      <c r="I59" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J59" s="8"/>
-      <c r="K59" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L59" s="53"/>
-      <c r="M59" s="53"/>
-      <c r="N59" s="53"/>
-      <c r="O59" s="53"/>
+      <c r="K59" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L59" s="50"/>
+      <c r="M59" s="50"/>
+      <c r="N59" s="50"/>
+      <c r="O59" s="50"/>
       <c r="P59" s="8"/>
       <c r="Q59" s="8"/>
-      <c r="R59" s="51"/>
-    </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="34" t="n">
+      <c r="R59" s="53"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="40" t="n">
         <v>49</v>
       </c>
       <c r="B60" s="24"/>
-      <c r="C60" s="34" t="n">
+      <c r="C60" s="40" t="n">
         <v>50</v>
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="F60" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="F60" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="G60" s="34" t="n">
+      <c r="G60" s="40" t="n">
         <v>46</v>
       </c>
-      <c r="H60" s="34" t="n">
+      <c r="H60" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I60" s="34" t="n">
+      <c r="I60" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J60" s="8"/>
-      <c r="K60" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L60" s="53"/>
-      <c r="M60" s="53"/>
-      <c r="N60" s="53"/>
-      <c r="O60" s="53"/>
+      <c r="K60" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L60" s="50"/>
+      <c r="M60" s="50"/>
+      <c r="N60" s="50"/>
+      <c r="O60" s="50"/>
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
-      <c r="R60" s="51"/>
-    </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="34" t="n">
+      <c r="R60" s="53"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="40" t="n">
         <v>50</v>
       </c>
       <c r="B61" s="24"/>
-      <c r="C61" s="34" t="n">
+      <c r="C61" s="40" t="n">
         <v>51</v>
       </c>
       <c r="D61" s="24"/>
       <c r="E61" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="F61" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="F61" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="G61" s="34" t="n">
+      <c r="G61" s="40" t="n">
         <v>46</v>
       </c>
-      <c r="H61" s="34" t="n">
+      <c r="H61" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I61" s="34" t="n">
+      <c r="I61" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J61" s="8"/>
-      <c r="K61" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L61" s="53"/>
-      <c r="M61" s="53"/>
-      <c r="N61" s="53"/>
-      <c r="O61" s="53"/>
+      <c r="K61" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L61" s="50"/>
+      <c r="M61" s="50"/>
+      <c r="N61" s="50"/>
+      <c r="O61" s="50"/>
       <c r="P61" s="8"/>
       <c r="Q61" s="8"/>
-      <c r="R61" s="51"/>
-    </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="34" t="n">
+      <c r="R61" s="53"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="40" t="n">
         <v>51</v>
       </c>
       <c r="B62" s="24" t="n">
         <v>49</v>
       </c>
-      <c r="C62" s="34" t="n">
+      <c r="C62" s="40" t="n">
         <v>52</v>
       </c>
       <c r="D62" s="24"/>
       <c r="E62" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="F62" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="F62" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="G62" s="34" t="n">
+      <c r="G62" s="40" t="n">
         <v>46</v>
       </c>
-      <c r="H62" s="34" t="n">
+      <c r="H62" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I62" s="34" t="n">
+      <c r="I62" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J62" s="8"/>
-      <c r="K62" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L62" s="53"/>
-      <c r="M62" s="53"/>
-      <c r="N62" s="41" t="s">
-        <v>230</v>
-      </c>
-      <c r="O62" s="53"/>
+      <c r="K62" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L62" s="50"/>
+      <c r="M62" s="50"/>
+      <c r="N62" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="O62" s="50"/>
       <c r="P62" s="8"/>
       <c r="Q62" s="8"/>
-      <c r="R62" s="51"/>
-    </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="34" t="n">
+      <c r="R62" s="53"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="40" t="n">
         <v>52</v>
       </c>
       <c r="B63" s="24"/>
-      <c r="C63" s="34" t="n">
+      <c r="C63" s="40" t="n">
         <v>53</v>
       </c>
       <c r="D63" s="24"/>
       <c r="E63" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="F63" s="56" t="s">
-        <v>289</v>
-      </c>
-      <c r="G63" s="34" t="n">
+        <v>293</v>
+      </c>
+      <c r="F63" s="55" t="s">
+        <v>294</v>
+      </c>
+      <c r="G63" s="40" t="n">
         <v>51</v>
       </c>
-      <c r="H63" s="34" t="n">
+      <c r="H63" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I63" s="34" t="n">
+      <c r="I63" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J63" s="8"/>
-      <c r="K63" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L63" s="53"/>
-      <c r="M63" s="53"/>
-      <c r="N63" s="53"/>
-      <c r="O63" s="53"/>
+      <c r="K63" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L63" s="50"/>
+      <c r="M63" s="50"/>
+      <c r="N63" s="50"/>
+      <c r="O63" s="50"/>
       <c r="P63" s="8"/>
       <c r="Q63" s="8"/>
-      <c r="R63" s="51"/>
-    </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="34" t="n">
+      <c r="R63" s="53"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="40" t="n">
         <v>53</v>
       </c>
       <c r="B64" s="24"/>
-      <c r="C64" s="34" t="n">
+      <c r="C64" s="40" t="n">
         <v>54</v>
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="F64" s="56" t="s">
+        <v>295</v>
+      </c>
+      <c r="F64" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="G64" s="34" t="n">
+      <c r="G64" s="40" t="n">
         <v>51</v>
       </c>
-      <c r="H64" s="34" t="n">
+      <c r="H64" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I64" s="34" t="n">
+      <c r="I64" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J64" s="8"/>
-      <c r="K64" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L64" s="53"/>
-      <c r="M64" s="53"/>
-      <c r="N64" s="53"/>
-      <c r="O64" s="53"/>
+      <c r="K64" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L64" s="50"/>
+      <c r="M64" s="50"/>
+      <c r="N64" s="50"/>
+      <c r="O64" s="50"/>
       <c r="P64" s="8"/>
       <c r="Q64" s="8"/>
-      <c r="R64" s="42"/>
-    </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="34" t="n">
+      <c r="R64" s="45"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="40" t="n">
         <v>54</v>
       </c>
       <c r="B65" s="24"/>
-      <c r="C65" s="34" t="n">
+      <c r="C65" s="40" t="n">
         <v>55</v>
       </c>
       <c r="D65" s="24"/>
       <c r="E65" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="F65" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="F65" s="56" t="s">
         <v>138</v>
       </c>
-      <c r="G65" s="34" t="n">
+      <c r="G65" s="40" t="n">
         <v>46</v>
       </c>
-      <c r="H65" s="34" t="n">
+      <c r="H65" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I65" s="34" t="n">
+      <c r="I65" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="K65" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L65" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M65" s="53"/>
-      <c r="N65" s="53"/>
-      <c r="O65" s="53"/>
+        <v>297</v>
+      </c>
+      <c r="K65" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L65" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M65" s="50"/>
+      <c r="N65" s="50"/>
+      <c r="O65" s="50"/>
       <c r="P65" s="8"/>
       <c r="Q65" s="8"/>
-      <c r="R65" s="42"/>
-    </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="34" t="n">
+      <c r="R65" s="45"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="40" t="n">
         <v>55</v>
       </c>
       <c r="B66" s="24"/>
-      <c r="C66" s="34" t="n">
+      <c r="C66" s="40" t="n">
         <v>56</v>
       </c>
       <c r="D66" s="24"/>
       <c r="E66" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="F66" s="40" t="s">
+        <v>298</v>
+      </c>
+      <c r="F66" s="56" t="s">
         <v>139</v>
       </c>
-      <c r="G66" s="34" t="n">
+      <c r="G66" s="40" t="n">
         <v>46</v>
       </c>
-      <c r="H66" s="34" t="n">
+      <c r="H66" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I66" s="34" t="n">
+      <c r="I66" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="K66" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L66" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M66" s="53"/>
-      <c r="N66" s="53"/>
-      <c r="O66" s="53"/>
+        <v>299</v>
+      </c>
+      <c r="K66" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L66" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M66" s="50"/>
+      <c r="N66" s="50"/>
+      <c r="O66" s="50"/>
       <c r="P66" s="8"/>
       <c r="Q66" s="8"/>
-      <c r="R66" s="42"/>
-    </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="43" t="n">
+      <c r="R66" s="45"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="34" t="n">
         <v>56</v>
       </c>
-      <c r="B67" s="44"/>
-      <c r="C67" s="43" t="n">
+      <c r="B67" s="23"/>
+      <c r="C67" s="34" t="n">
         <v>57</v>
       </c>
-      <c r="D67" s="44"/>
+      <c r="D67" s="23"/>
       <c r="E67" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="F67" s="44" t="s">
+        <v>300</v>
+      </c>
+      <c r="F67" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G67" s="43" t="n">
+      <c r="G67" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H67" s="62" t="n">
+      <c r="H67" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I67" s="43" t="n">
+      <c r="I67" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="K67" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L67" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M67" s="49"/>
-      <c r="N67" s="49"/>
-      <c r="O67" s="49"/>
+        <v>301</v>
+      </c>
+      <c r="K67" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L67" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M67" s="52"/>
+      <c r="N67" s="52"/>
+      <c r="O67" s="52"/>
       <c r="P67" s="5"/>
       <c r="Q67" s="5"/>
-      <c r="R67" s="51"/>
-    </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="34" t="n">
+      <c r="R67" s="53"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="40" t="n">
         <v>57</v>
       </c>
       <c r="B68" s="24"/>
-      <c r="C68" s="34"/>
+      <c r="C68" s="40"/>
       <c r="D68" s="24"/>
       <c r="E68" s="24" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F68" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G68" s="34" t="n">
+      <c r="G68" s="40" t="n">
         <v>43</v>
       </c>
-      <c r="H68" s="34" t="n">
+      <c r="H68" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I68" s="34"/>
+      <c r="I68" s="40"/>
       <c r="J68" s="8"/>
-      <c r="K68" s="41"/>
-      <c r="L68" s="53"/>
-      <c r="M68" s="53"/>
-      <c r="N68" s="53"/>
-      <c r="O68" s="53"/>
+      <c r="K68" s="43"/>
+      <c r="L68" s="50"/>
+      <c r="M68" s="50"/>
+      <c r="N68" s="50"/>
+      <c r="O68" s="50"/>
       <c r="P68" s="8"/>
       <c r="Q68" s="8"/>
-      <c r="R68" s="42"/>
-    </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="34" t="n">
+      <c r="R68" s="45"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="40" t="n">
         <v>58</v>
       </c>
       <c r="B69" s="24"/>
-      <c r="C69" s="34" t="n">
+      <c r="C69" s="40" t="n">
         <v>58</v>
       </c>
       <c r="D69" s="24"/>
       <c r="E69" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="F69" s="40" t="s">
+        <v>303</v>
+      </c>
+      <c r="F69" s="56" t="s">
         <v>141</v>
       </c>
-      <c r="G69" s="34" t="n">
+      <c r="G69" s="40" t="n">
         <v>57</v>
       </c>
-      <c r="H69" s="34" t="n">
+      <c r="H69" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I69" s="34" t="n">
+      <c r="I69" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="K69" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L69" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M69" s="53"/>
-      <c r="N69" s="53"/>
-      <c r="O69" s="53"/>
+        <v>304</v>
+      </c>
+      <c r="K69" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L69" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M69" s="50"/>
+      <c r="N69" s="50"/>
+      <c r="O69" s="50"/>
       <c r="P69" s="8"/>
       <c r="Q69" s="8"/>
-      <c r="R69" s="42"/>
-    </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="34" t="n">
+      <c r="R69" s="45"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="40" t="n">
         <v>59</v>
       </c>
       <c r="B70" s="24"/>
-      <c r="C70" s="34" t="n">
+      <c r="C70" s="40" t="n">
         <v>59</v>
       </c>
       <c r="D70" s="24"/>
       <c r="E70" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="F70" s="40" t="s">
+        <v>305</v>
+      </c>
+      <c r="F70" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="G70" s="34" t="n">
+      <c r="G70" s="40" t="n">
         <v>57</v>
       </c>
-      <c r="H70" s="34" t="n">
+      <c r="H70" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I70" s="34" t="n">
+      <c r="I70" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="K70" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L70" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M70" s="53"/>
-      <c r="N70" s="53"/>
-      <c r="O70" s="53"/>
+        <v>306</v>
+      </c>
+      <c r="K70" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L70" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M70" s="50"/>
+      <c r="N70" s="50"/>
+      <c r="O70" s="50"/>
       <c r="P70" s="8"/>
       <c r="Q70" s="8"/>
-      <c r="R70" s="42"/>
-    </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="34" t="n">
+      <c r="R70" s="45"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="40" t="n">
         <v>60</v>
       </c>
       <c r="B71" s="24"/>
-      <c r="C71" s="34" t="n">
+      <c r="C71" s="40" t="n">
         <v>60</v>
       </c>
       <c r="D71" s="24"/>
       <c r="E71" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="F71" s="40" t="s">
+        <v>307</v>
+      </c>
+      <c r="F71" s="56" t="s">
         <v>143</v>
       </c>
-      <c r="G71" s="34" t="n">
+      <c r="G71" s="40" t="n">
         <v>57</v>
       </c>
-      <c r="H71" s="34" t="n">
+      <c r="H71" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I71" s="34" t="n">
+      <c r="I71" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="K71" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L71" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M71" s="53"/>
-      <c r="N71" s="53"/>
-      <c r="O71" s="53"/>
+        <v>308</v>
+      </c>
+      <c r="K71" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L71" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M71" s="50"/>
+      <c r="N71" s="50"/>
+      <c r="O71" s="50"/>
       <c r="P71" s="8"/>
       <c r="Q71" s="8"/>
-      <c r="R71" s="42"/>
-    </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="34" t="n">
+      <c r="R71" s="45"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="40" t="n">
         <v>61</v>
       </c>
       <c r="B72" s="24"/>
-      <c r="C72" s="34" t="n">
+      <c r="C72" s="40" t="n">
         <v>61</v>
       </c>
       <c r="D72" s="24"/>
       <c r="E72" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="F72" s="40" t="s">
+        <v>309</v>
+      </c>
+      <c r="F72" s="56" t="s">
         <v>144</v>
       </c>
-      <c r="G72" s="34" t="n">
+      <c r="G72" s="40" t="n">
         <v>57</v>
       </c>
-      <c r="H72" s="34" t="n">
+      <c r="H72" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I72" s="34" t="n">
+      <c r="I72" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="K72" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L72" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M72" s="53"/>
-      <c r="N72" s="53"/>
-      <c r="O72" s="53"/>
+        <v>310</v>
+      </c>
+      <c r="K72" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L72" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M72" s="50"/>
+      <c r="N72" s="50"/>
+      <c r="O72" s="50"/>
       <c r="P72" s="8"/>
       <c r="Q72" s="8"/>
-      <c r="R72" s="51"/>
-    </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="34"/>
+      <c r="R72" s="53"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="40"/>
       <c r="B73" s="24"/>
-      <c r="C73" s="34" t="n">
+      <c r="C73" s="40" t="n">
         <v>62</v>
       </c>
       <c r="D73" s="24"/>
       <c r="E73" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="F73" s="40" t="s">
+        <v>302</v>
+      </c>
+      <c r="F73" s="56" t="s">
         <v>145</v>
       </c>
-      <c r="G73" s="34" t="n">
+      <c r="G73" s="40" t="n">
         <v>57</v>
       </c>
-      <c r="H73" s="34"/>
-      <c r="I73" s="34" t="n">
+      <c r="H73" s="40"/>
+      <c r="I73" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J73" s="8"/>
-      <c r="K73" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L73" s="53"/>
-      <c r="M73" s="53"/>
-      <c r="N73" s="53"/>
-      <c r="O73" s="53"/>
+      <c r="K73" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L73" s="50"/>
+      <c r="M73" s="50"/>
+      <c r="N73" s="50"/>
+      <c r="O73" s="50"/>
       <c r="P73" s="8"/>
       <c r="Q73" s="8"/>
-      <c r="R73" s="51"/>
-    </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="43" t="n">
+      <c r="R73" s="53"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="34" t="n">
         <v>62</v>
       </c>
-      <c r="B74" s="44"/>
-      <c r="C74" s="43"/>
-      <c r="D74" s="44"/>
+      <c r="B74" s="23"/>
+      <c r="C74" s="34"/>
+      <c r="D74" s="23"/>
       <c r="E74" s="23" t="s">
-        <v>306</v>
-      </c>
-      <c r="F74" s="44" t="s">
+        <v>311</v>
+      </c>
+      <c r="F74" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="G74" s="43" t="n">
+      <c r="G74" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H74" s="43" t="n">
+      <c r="H74" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I74" s="43" t="n">
+      <c r="I74" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J74" s="5"/>
-      <c r="K74" s="48"/>
-      <c r="L74" s="49"/>
-      <c r="M74" s="49"/>
-      <c r="N74" s="49"/>
-      <c r="O74" s="49"/>
+      <c r="K74" s="47"/>
+      <c r="L74" s="52"/>
+      <c r="M74" s="52"/>
+      <c r="N74" s="52"/>
+      <c r="O74" s="52"/>
       <c r="P74" s="5"/>
       <c r="Q74" s="5"/>
-      <c r="R74" s="42"/>
-    </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="43" t="n">
+      <c r="R74" s="45"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="34" t="n">
         <v>63</v>
       </c>
-      <c r="B75" s="44"/>
-      <c r="C75" s="43" t="n">
+      <c r="B75" s="23"/>
+      <c r="C75" s="34" t="n">
         <v>63</v>
       </c>
-      <c r="D75" s="44"/>
+      <c r="D75" s="23"/>
       <c r="E75" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="F75" s="50" t="s">
+        <v>312</v>
+      </c>
+      <c r="F75" s="58" t="s">
         <v>103</v>
       </c>
-      <c r="G75" s="43" t="n">
+      <c r="G75" s="34" t="n">
         <v>62</v>
       </c>
-      <c r="H75" s="43" t="n">
+      <c r="H75" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I75" s="43" t="n">
+      <c r="I75" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="K75" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L75" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M75" s="49"/>
-      <c r="N75" s="49"/>
-      <c r="O75" s="49"/>
+        <v>313</v>
+      </c>
+      <c r="K75" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L75" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M75" s="52"/>
+      <c r="N75" s="52"/>
+      <c r="O75" s="52"/>
       <c r="P75" s="5"/>
       <c r="Q75" s="5"/>
-      <c r="R75" s="42"/>
-    </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="43" t="n">
+      <c r="R75" s="45"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="34" t="n">
         <v>64</v>
       </c>
-      <c r="B76" s="44"/>
-      <c r="C76" s="43" t="n">
+      <c r="B76" s="23"/>
+      <c r="C76" s="34" t="n">
         <v>64</v>
       </c>
-      <c r="D76" s="44"/>
+      <c r="D76" s="23"/>
       <c r="E76" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="F76" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="F76" s="58" t="s">
         <v>147</v>
       </c>
-      <c r="G76" s="43" t="n">
+      <c r="G76" s="34" t="n">
         <v>62</v>
       </c>
-      <c r="H76" s="43" t="n">
+      <c r="H76" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I76" s="43" t="n">
+      <c r="I76" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="K76" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L76" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M76" s="49"/>
-      <c r="N76" s="49"/>
-      <c r="O76" s="49"/>
+        <v>315</v>
+      </c>
+      <c r="K76" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L76" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M76" s="52"/>
+      <c r="N76" s="52"/>
+      <c r="O76" s="52"/>
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
-      <c r="R76" s="42"/>
-    </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="43" t="n">
+      <c r="R76" s="45"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="34" t="n">
         <v>65</v>
       </c>
-      <c r="B77" s="44" t="n">
+      <c r="B77" s="23" t="n">
         <v>63</v>
       </c>
-      <c r="C77" s="43" t="n">
+      <c r="C77" s="34" t="n">
         <v>65</v>
       </c>
-      <c r="D77" s="44" t="n">
+      <c r="D77" s="23" t="n">
         <v>63</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="F77" s="50" t="s">
+        <v>316</v>
+      </c>
+      <c r="F77" s="58" t="s">
         <v>105</v>
       </c>
-      <c r="G77" s="43" t="n">
+      <c r="G77" s="34" t="n">
         <v>62</v>
       </c>
-      <c r="H77" s="43" t="n">
+      <c r="H77" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I77" s="43" t="n">
+      <c r="I77" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="K77" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L77" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M77" s="49"/>
-      <c r="N77" s="49"/>
-      <c r="O77" s="49"/>
+        <v>317</v>
+      </c>
+      <c r="K77" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L77" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M77" s="52"/>
+      <c r="N77" s="52"/>
+      <c r="O77" s="52"/>
       <c r="P77" s="5"/>
       <c r="Q77" s="5"/>
-      <c r="R77" s="42"/>
-    </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="43" t="n">
+      <c r="R77" s="45"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="34" t="n">
         <v>66</v>
       </c>
-      <c r="B78" s="44"/>
-      <c r="C78" s="43" t="n">
+      <c r="B78" s="23"/>
+      <c r="C78" s="34" t="n">
         <v>66</v>
       </c>
-      <c r="D78" s="44"/>
+      <c r="D78" s="23"/>
       <c r="E78" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="F78" s="58" t="s">
-        <v>233</v>
-      </c>
-      <c r="G78" s="43" t="n">
+        <v>318</v>
+      </c>
+      <c r="F78" s="59" t="s">
+        <v>235</v>
+      </c>
+      <c r="G78" s="34" t="n">
         <v>65</v>
       </c>
-      <c r="H78" s="43" t="n">
+      <c r="H78" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I78" s="43" t="n">
+      <c r="I78" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="K78" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L78" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M78" s="49"/>
-      <c r="N78" s="49"/>
-      <c r="O78" s="49"/>
+        <v>319</v>
+      </c>
+      <c r="K78" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L78" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M78" s="52"/>
+      <c r="N78" s="52"/>
+      <c r="O78" s="52"/>
       <c r="P78" s="5"/>
       <c r="Q78" s="5"/>
-      <c r="R78" s="42"/>
-    </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="43" t="n">
+      <c r="R78" s="45"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="34" t="n">
         <v>67</v>
       </c>
-      <c r="B79" s="44"/>
-      <c r="C79" s="43" t="n">
+      <c r="B79" s="23"/>
+      <c r="C79" s="34" t="n">
         <v>67</v>
       </c>
-      <c r="D79" s="44"/>
+      <c r="D79" s="23"/>
       <c r="E79" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="F79" s="58" t="s">
-        <v>236</v>
-      </c>
-      <c r="G79" s="43" t="n">
+        <v>320</v>
+      </c>
+      <c r="F79" s="59" t="s">
+        <v>238</v>
+      </c>
+      <c r="G79" s="34" t="n">
         <v>65</v>
       </c>
-      <c r="H79" s="43" t="n">
+      <c r="H79" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I79" s="43" t="n">
+      <c r="I79" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="K79" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L79" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M79" s="49"/>
-      <c r="N79" s="49"/>
-      <c r="O79" s="49"/>
+        <v>321</v>
+      </c>
+      <c r="K79" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L79" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M79" s="52"/>
+      <c r="N79" s="52"/>
+      <c r="O79" s="52"/>
       <c r="P79" s="5"/>
       <c r="Q79" s="5"/>
-      <c r="R79" s="42"/>
-    </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="43"/>
-      <c r="B80" s="44"/>
-      <c r="C80" s="43" t="n">
+      <c r="R79" s="45"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="34"/>
+      <c r="B80" s="23"/>
+      <c r="C80" s="34" t="n">
         <v>68</v>
       </c>
-      <c r="D80" s="44"/>
+      <c r="D80" s="23"/>
       <c r="E80" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="F80" s="58" t="s">
-        <v>318</v>
-      </c>
-      <c r="G80" s="43" t="n">
+        <v>322</v>
+      </c>
+      <c r="F80" s="59" t="s">
+        <v>323</v>
+      </c>
+      <c r="G80" s="34" t="n">
         <v>65</v>
       </c>
-      <c r="H80" s="43"/>
-      <c r="I80" s="43" t="n">
+      <c r="H80" s="34"/>
+      <c r="I80" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="K80" s="49"/>
-      <c r="L80" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M80" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="N80" s="49"/>
-      <c r="O80" s="49"/>
+        <v>324</v>
+      </c>
+      <c r="K80" s="52"/>
+      <c r="L80" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M80" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="N80" s="52"/>
+      <c r="O80" s="52"/>
       <c r="P80" s="5"/>
       <c r="Q80" s="5"/>
-      <c r="R80" s="51"/>
-    </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="34" t="n">
+      <c r="R80" s="53"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="40" t="n">
         <v>68</v>
       </c>
       <c r="B81" s="24"/>
-      <c r="C81" s="34"/>
+      <c r="C81" s="40"/>
       <c r="D81" s="24"/>
       <c r="E81" s="24" t="s">
-        <v>320</v>
-      </c>
-      <c r="F81" s="63" t="s">
+        <v>325</v>
+      </c>
+      <c r="F81" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="G81" s="55" t="n">
+      <c r="G81" s="48" t="n">
         <v>43</v>
       </c>
-      <c r="H81" s="34" t="n">
+      <c r="H81" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I81" s="34"/>
+      <c r="I81" s="40"/>
       <c r="J81" s="8"/>
-      <c r="K81" s="53"/>
-      <c r="L81" s="53"/>
-      <c r="M81" s="53"/>
-      <c r="N81" s="53"/>
-      <c r="O81" s="53"/>
+      <c r="K81" s="50"/>
+      <c r="L81" s="50"/>
+      <c r="M81" s="50"/>
+      <c r="N81" s="50"/>
+      <c r="O81" s="50"/>
       <c r="P81" s="8"/>
       <c r="Q81" s="8"/>
-      <c r="R81" s="51"/>
-    </row>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="34" t="n">
+      <c r="R81" s="53"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="40" t="n">
         <v>69</v>
       </c>
       <c r="B82" s="24"/>
-      <c r="C82" s="34" t="n">
+      <c r="C82" s="40" t="n">
         <v>69</v>
       </c>
       <c r="D82" s="24"/>
       <c r="E82" s="24" t="s">
-        <v>321</v>
-      </c>
-      <c r="F82" s="40" t="s">
+        <v>326</v>
+      </c>
+      <c r="F82" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="G82" s="34" t="n">
+      <c r="G82" s="40" t="n">
         <v>68</v>
       </c>
-      <c r="H82" s="34" t="n">
+      <c r="H82" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I82" s="34" t="n">
+      <c r="I82" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J82" s="8"/>
-      <c r="K82" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L82" s="53"/>
-      <c r="M82" s="53"/>
-      <c r="N82" s="53"/>
-      <c r="O82" s="53"/>
+      <c r="K82" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L82" s="50"/>
+      <c r="M82" s="50"/>
+      <c r="N82" s="50"/>
+      <c r="O82" s="50"/>
       <c r="P82" s="8"/>
       <c r="Q82" s="8"/>
-      <c r="R82" s="51"/>
-    </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="34" t="n">
+      <c r="R82" s="53"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="40" t="n">
         <v>70</v>
       </c>
       <c r="B83" s="24"/>
-      <c r="C83" s="34" t="n">
+      <c r="C83" s="40" t="n">
         <v>70</v>
       </c>
       <c r="D83" s="24"/>
       <c r="E83" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="F83" s="56" t="s">
-        <v>323</v>
-      </c>
-      <c r="G83" s="34" t="n">
+        <v>327</v>
+      </c>
+      <c r="F83" s="55" t="s">
+        <v>328</v>
+      </c>
+      <c r="G83" s="40" t="n">
         <v>69</v>
       </c>
-      <c r="H83" s="34" t="n">
+      <c r="H83" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I83" s="34" t="n">
+      <c r="I83" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J83" s="8"/>
-      <c r="K83" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L83" s="53"/>
-      <c r="M83" s="53"/>
-      <c r="N83" s="53"/>
-      <c r="O83" s="53"/>
+      <c r="K83" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L83" s="50"/>
+      <c r="M83" s="50"/>
+      <c r="N83" s="50"/>
+      <c r="O83" s="50"/>
       <c r="P83" s="8"/>
       <c r="Q83" s="8"/>
-      <c r="R83" s="42"/>
-    </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="34" t="n">
+      <c r="R83" s="45"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="40" t="n">
         <v>71</v>
       </c>
       <c r="B84" s="24"/>
-      <c r="C84" s="34" t="n">
+      <c r="C84" s="40" t="n">
         <v>71</v>
       </c>
       <c r="D84" s="24"/>
       <c r="E84" s="24" t="s">
-        <v>324</v>
-      </c>
-      <c r="F84" s="40" t="s">
+        <v>329</v>
+      </c>
+      <c r="F84" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="G84" s="34" t="n">
+      <c r="G84" s="40" t="n">
         <v>68</v>
       </c>
-      <c r="H84" s="34" t="n">
+      <c r="H84" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I84" s="34" t="n">
+      <c r="I84" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="K84" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L84" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M84" s="53"/>
-      <c r="N84" s="53"/>
-      <c r="O84" s="53"/>
+        <v>330</v>
+      </c>
+      <c r="K84" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L84" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M84" s="50"/>
+      <c r="N84" s="50"/>
+      <c r="O84" s="50"/>
       <c r="P84" s="8"/>
       <c r="Q84" s="8"/>
     </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="43" t="n">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="34" t="n">
         <v>72</v>
       </c>
-      <c r="B85" s="44"/>
-      <c r="C85" s="43"/>
-      <c r="D85" s="44"/>
+      <c r="B85" s="23"/>
+      <c r="C85" s="34"/>
+      <c r="D85" s="23"/>
       <c r="E85" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="F85" s="44" t="s">
+        <v>331</v>
+      </c>
+      <c r="F85" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="G85" s="43" t="n">
+      <c r="G85" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H85" s="43" t="n">
+      <c r="H85" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I85" s="43"/>
+      <c r="I85" s="34"/>
       <c r="J85" s="5"/>
-      <c r="K85" s="49"/>
-      <c r="L85" s="49"/>
-      <c r="M85" s="49"/>
-      <c r="N85" s="49"/>
-      <c r="O85" s="49"/>
+      <c r="K85" s="52"/>
+      <c r="L85" s="52"/>
+      <c r="M85" s="52"/>
+      <c r="N85" s="52"/>
+      <c r="O85" s="52"/>
       <c r="P85" s="5"/>
       <c r="Q85" s="5"/>
     </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="43" t="n">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="34" t="n">
         <v>73</v>
       </c>
-      <c r="B86" s="44"/>
-      <c r="C86" s="43" t="n">
+      <c r="B86" s="23"/>
+      <c r="C86" s="34" t="n">
         <v>72</v>
       </c>
-      <c r="D86" s="44"/>
+      <c r="D86" s="23"/>
       <c r="E86" s="23" t="s">
-        <v>327</v>
-      </c>
-      <c r="F86" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="F86" s="58" t="s">
         <v>154</v>
       </c>
-      <c r="G86" s="43" t="n">
+      <c r="G86" s="34" t="n">
         <v>72</v>
       </c>
-      <c r="H86" s="43" t="n">
+      <c r="H86" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I86" s="43" t="n">
+      <c r="I86" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J86" s="5"/>
-      <c r="K86" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="L86" s="49"/>
-      <c r="M86" s="49"/>
-      <c r="N86" s="49"/>
-      <c r="O86" s="49"/>
+      <c r="K86" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="L86" s="52"/>
+      <c r="M86" s="52"/>
+      <c r="N86" s="52"/>
+      <c r="O86" s="52"/>
       <c r="P86" s="5"/>
       <c r="Q86" s="5"/>
     </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="43" t="n">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="34" t="n">
         <v>74</v>
       </c>
-      <c r="B87" s="44"/>
-      <c r="C87" s="43" t="n">
+      <c r="B87" s="23"/>
+      <c r="C87" s="34" t="n">
         <v>73</v>
       </c>
-      <c r="D87" s="44"/>
+      <c r="D87" s="23"/>
       <c r="E87" s="23"/>
-      <c r="F87" s="50" t="s">
+      <c r="F87" s="58" t="s">
         <v>155</v>
       </c>
-      <c r="G87" s="43" t="n">
+      <c r="G87" s="34" t="n">
         <v>72</v>
       </c>
-      <c r="H87" s="43" t="n">
+      <c r="H87" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I87" s="43" t="n">
+      <c r="I87" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J87" s="5"/>
-      <c r="K87" s="64" t="s">
-        <v>87</v>
-      </c>
-      <c r="L87" s="49"/>
-      <c r="M87" s="49"/>
-      <c r="N87" s="49"/>
-      <c r="O87" s="49"/>
+      <c r="K87" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="L87" s="52"/>
+      <c r="M87" s="52"/>
+      <c r="N87" s="52"/>
+      <c r="O87" s="52"/>
       <c r="P87" s="5"/>
       <c r="Q87" s="5"/>
     </row>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="43" t="n">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="34" t="n">
         <v>75</v>
       </c>
-      <c r="B88" s="44"/>
-      <c r="C88" s="43" t="n">
+      <c r="B88" s="23"/>
+      <c r="C88" s="34" t="n">
         <v>74</v>
       </c>
-      <c r="D88" s="44"/>
+      <c r="D88" s="23"/>
       <c r="E88" s="23" t="s">
-        <v>328</v>
-      </c>
-      <c r="F88" s="50" t="s">
+        <v>333</v>
+      </c>
+      <c r="F88" s="58" t="s">
         <v>156</v>
       </c>
-      <c r="G88" s="43" t="n">
+      <c r="G88" s="34" t="n">
         <v>72</v>
       </c>
-      <c r="H88" s="43" t="n">
+      <c r="H88" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I88" s="43" t="n">
+      <c r="I88" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J88" s="5"/>
-      <c r="K88" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L88" s="49"/>
-      <c r="M88" s="49"/>
-      <c r="N88" s="49"/>
-      <c r="O88" s="49"/>
+      <c r="K88" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L88" s="52"/>
+      <c r="M88" s="52"/>
+      <c r="N88" s="52"/>
+      <c r="O88" s="52"/>
       <c r="P88" s="5"/>
       <c r="Q88" s="5"/>
     </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="43" t="n">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="34" t="n">
         <v>76</v>
       </c>
-      <c r="B89" s="44" t="n">
+      <c r="B89" s="23" t="n">
         <v>75</v>
       </c>
-      <c r="C89" s="43" t="n">
+      <c r="C89" s="34" t="n">
         <v>75</v>
       </c>
-      <c r="D89" s="44" t="n">
+      <c r="D89" s="23" t="n">
         <v>75</v>
       </c>
       <c r="E89" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="F89" s="50" t="s">
+        <v>334</v>
+      </c>
+      <c r="F89" s="58" t="s">
         <v>157</v>
       </c>
-      <c r="G89" s="43" t="n">
+      <c r="G89" s="34" t="n">
         <v>72</v>
       </c>
-      <c r="H89" s="43" t="n">
+      <c r="H89" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I89" s="43" t="n">
+      <c r="I89" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J89" s="5"/>
-      <c r="K89" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L89" s="49"/>
-      <c r="M89" s="49"/>
-      <c r="N89" s="49"/>
-      <c r="O89" s="49"/>
+      <c r="K89" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L89" s="52"/>
+      <c r="M89" s="52"/>
+      <c r="N89" s="52"/>
+      <c r="O89" s="52"/>
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
     </row>
-    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="43" t="n">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="34" t="n">
         <v>77</v>
       </c>
-      <c r="B90" s="44" t="n">
+      <c r="B90" s="23" t="n">
         <v>75</v>
       </c>
-      <c r="C90" s="43"/>
-      <c r="D90" s="44" t="n">
+      <c r="C90" s="34"/>
+      <c r="D90" s="23" t="n">
         <v>75</v>
       </c>
       <c r="E90" s="23"/>
-      <c r="F90" s="50" t="s">
-        <v>330</v>
-      </c>
-      <c r="G90" s="43" t="n">
+      <c r="F90" s="58" t="s">
+        <v>335</v>
+      </c>
+      <c r="G90" s="34" t="n">
         <v>72</v>
       </c>
-      <c r="H90" s="43" t="n">
+      <c r="H90" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I90" s="43"/>
+      <c r="I90" s="34"/>
       <c r="J90" s="5"/>
-      <c r="K90" s="48"/>
-      <c r="L90" s="49"/>
-      <c r="M90" s="49"/>
-      <c r="N90" s="49"/>
-      <c r="O90" s="49"/>
+      <c r="K90" s="47"/>
+      <c r="L90" s="52"/>
+      <c r="M90" s="52"/>
+      <c r="N90" s="52"/>
+      <c r="O90" s="52"/>
       <c r="P90" s="5"/>
       <c r="Q90" s="5"/>
     </row>
-    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="43" t="n">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="34" t="n">
         <v>78</v>
       </c>
-      <c r="B91" s="44"/>
-      <c r="C91" s="43" t="n">
+      <c r="B91" s="23"/>
+      <c r="C91" s="34" t="n">
         <v>76</v>
       </c>
-      <c r="D91" s="44"/>
+      <c r="D91" s="23"/>
       <c r="E91" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="F91" s="58" t="s">
-        <v>332</v>
-      </c>
-      <c r="G91" s="43" t="n">
+        <v>336</v>
+      </c>
+      <c r="F91" s="59" t="s">
+        <v>337</v>
+      </c>
+      <c r="G91" s="34" t="n">
         <v>77</v>
       </c>
-      <c r="H91" s="43" t="n">
+      <c r="H91" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I91" s="43" t="n">
+      <c r="I91" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J91" s="5"/>
-      <c r="K91" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L91" s="49"/>
-      <c r="M91" s="49"/>
-      <c r="N91" s="49"/>
-      <c r="O91" s="49"/>
+      <c r="K91" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L91" s="52"/>
+      <c r="M91" s="52"/>
+      <c r="N91" s="52"/>
+      <c r="O91" s="52"/>
       <c r="P91" s="5"/>
       <c r="Q91" s="5"/>
-      <c r="R91" s="42"/>
-    </row>
-    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="43" t="n">
+      <c r="R91" s="45"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="34" t="n">
         <v>79</v>
       </c>
-      <c r="B92" s="44"/>
-      <c r="C92" s="43" t="n">
+      <c r="B92" s="23"/>
+      <c r="C92" s="34" t="n">
         <v>77</v>
       </c>
-      <c r="D92" s="44"/>
+      <c r="D92" s="23"/>
       <c r="E92" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="F92" s="58" t="s">
-        <v>334</v>
-      </c>
-      <c r="G92" s="43" t="n">
+        <v>338</v>
+      </c>
+      <c r="F92" s="59" t="s">
+        <v>339</v>
+      </c>
+      <c r="G92" s="34" t="n">
         <v>77</v>
       </c>
-      <c r="H92" s="43" t="n">
+      <c r="H92" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I92" s="43" t="n">
+      <c r="I92" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="K92" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L92" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M92" s="49"/>
-      <c r="N92" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="O92" s="49"/>
+        <v>340</v>
+      </c>
+      <c r="K92" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L92" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M92" s="52"/>
+      <c r="N92" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="O92" s="52"/>
       <c r="P92" s="5"/>
       <c r="Q92" s="5"/>
-      <c r="R92" s="51"/>
-    </row>
-    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="34" t="n">
+      <c r="R92" s="53"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="40" t="n">
         <v>80</v>
       </c>
       <c r="B93" s="24"/>
-      <c r="C93" s="34"/>
+      <c r="C93" s="40"/>
       <c r="D93" s="24"/>
       <c r="E93" s="24" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F93" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="G93" s="34" t="n">
+      <c r="G93" s="40" t="n">
         <v>43</v>
       </c>
-      <c r="H93" s="34" t="n">
+      <c r="H93" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I93" s="34"/>
+      <c r="I93" s="40"/>
       <c r="J93" s="8"/>
-      <c r="K93" s="41"/>
-      <c r="L93" s="41"/>
-      <c r="M93" s="53"/>
-      <c r="N93" s="41"/>
-      <c r="O93" s="53"/>
+      <c r="K93" s="43"/>
+      <c r="L93" s="43"/>
+      <c r="M93" s="50"/>
+      <c r="N93" s="43"/>
+      <c r="O93" s="50"/>
       <c r="P93" s="8"/>
       <c r="Q93" s="8"/>
-      <c r="R93" s="42"/>
-    </row>
-    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="34" t="n">
+      <c r="R93" s="45"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="40" t="n">
         <v>81</v>
       </c>
       <c r="B94" s="24"/>
-      <c r="C94" s="34" t="n">
+      <c r="C94" s="40" t="n">
         <v>78</v>
       </c>
       <c r="D94" s="24"/>
       <c r="E94" s="24" t="s">
-        <v>337</v>
-      </c>
-      <c r="F94" s="40" t="s">
+        <v>342</v>
+      </c>
+      <c r="F94" s="56" t="s">
         <v>161</v>
       </c>
-      <c r="G94" s="34" t="n">
+      <c r="G94" s="40" t="n">
         <v>80</v>
       </c>
-      <c r="H94" s="34" t="n">
+      <c r="H94" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I94" s="34" t="n">
+      <c r="I94" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="K94" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L94" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M94" s="53"/>
-      <c r="N94" s="53"/>
-      <c r="O94" s="53"/>
+        <v>343</v>
+      </c>
+      <c r="K94" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L94" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M94" s="50"/>
+      <c r="N94" s="50"/>
+      <c r="O94" s="50"/>
       <c r="P94" s="8"/>
       <c r="Q94" s="8"/>
-      <c r="R94" s="42"/>
-    </row>
-    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="34" t="n">
+      <c r="R94" s="45"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="40" t="n">
         <v>82</v>
       </c>
       <c r="B95" s="24"/>
-      <c r="C95" s="34" t="n">
+      <c r="C95" s="40" t="n">
         <v>79</v>
       </c>
       <c r="D95" s="24"/>
       <c r="E95" s="24" t="s">
-        <v>339</v>
-      </c>
-      <c r="F95" s="40" t="s">
+        <v>344</v>
+      </c>
+      <c r="F95" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="G95" s="34" t="n">
+      <c r="G95" s="40" t="n">
         <v>80</v>
       </c>
-      <c r="H95" s="34" t="n">
+      <c r="H95" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I95" s="34" t="n">
+      <c r="I95" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="K95" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L95" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M95" s="53"/>
-      <c r="N95" s="53"/>
-      <c r="O95" s="53"/>
+        <v>345</v>
+      </c>
+      <c r="K95" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L95" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M95" s="50"/>
+      <c r="N95" s="50"/>
+      <c r="O95" s="50"/>
       <c r="P95" s="8"/>
       <c r="Q95" s="8"/>
-      <c r="R95" s="42"/>
-    </row>
-    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="34" t="n">
+      <c r="R95" s="45"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="40" t="n">
         <v>83</v>
       </c>
       <c r="B96" s="24"/>
-      <c r="C96" s="34" t="n">
+      <c r="C96" s="40" t="n">
         <v>80</v>
       </c>
       <c r="D96" s="24"/>
       <c r="E96" s="24" t="s">
-        <v>341</v>
-      </c>
-      <c r="F96" s="40" t="s">
+        <v>346</v>
+      </c>
+      <c r="F96" s="56" t="s">
         <v>163</v>
       </c>
-      <c r="G96" s="34" t="n">
+      <c r="G96" s="40" t="n">
         <v>80</v>
       </c>
-      <c r="H96" s="34" t="n">
+      <c r="H96" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I96" s="34" t="n">
+      <c r="I96" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="K96" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L96" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M96" s="53"/>
-      <c r="N96" s="53"/>
-      <c r="O96" s="53"/>
+        <v>347</v>
+      </c>
+      <c r="K96" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L96" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M96" s="50"/>
+      <c r="N96" s="50"/>
+      <c r="O96" s="50"/>
       <c r="P96" s="8"/>
       <c r="Q96" s="8"/>
-      <c r="R96" s="42"/>
-    </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="34" t="n">
+      <c r="R96" s="45"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="40" t="n">
         <v>84</v>
       </c>
       <c r="B97" s="24"/>
-      <c r="C97" s="34" t="n">
+      <c r="C97" s="40" t="n">
         <v>81</v>
       </c>
       <c r="D97" s="24"/>
       <c r="E97" s="24" t="s">
-        <v>343</v>
-      </c>
-      <c r="F97" s="40" t="s">
+        <v>348</v>
+      </c>
+      <c r="F97" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="G97" s="34" t="n">
+      <c r="G97" s="40" t="n">
         <v>80</v>
       </c>
-      <c r="H97" s="34" t="n">
+      <c r="H97" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I97" s="34" t="n">
+      <c r="I97" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J97" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="K97" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L97" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M97" s="53"/>
-      <c r="N97" s="53"/>
-      <c r="O97" s="53"/>
+        <v>349</v>
+      </c>
+      <c r="K97" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L97" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M97" s="50"/>
+      <c r="N97" s="50"/>
+      <c r="O97" s="50"/>
       <c r="P97" s="8"/>
       <c r="Q97" s="8"/>
-      <c r="R97" s="51"/>
-    </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="43" t="n">
+      <c r="R97" s="53"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="34" t="n">
         <v>85</v>
       </c>
-      <c r="B98" s="44"/>
-      <c r="C98" s="43"/>
-      <c r="D98" s="44"/>
+      <c r="B98" s="23"/>
+      <c r="C98" s="34"/>
+      <c r="D98" s="23"/>
       <c r="E98" s="23"/>
-      <c r="F98" s="44" t="s">
+      <c r="F98" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="G98" s="43" t="n">
+      <c r="G98" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H98" s="43" t="n">
+      <c r="H98" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I98" s="43"/>
+      <c r="I98" s="34"/>
       <c r="J98" s="5"/>
-      <c r="K98" s="48"/>
-      <c r="L98" s="48"/>
-      <c r="M98" s="49"/>
-      <c r="N98" s="49"/>
-      <c r="O98" s="49"/>
+      <c r="K98" s="47"/>
+      <c r="L98" s="47"/>
+      <c r="M98" s="52"/>
+      <c r="N98" s="52"/>
+      <c r="O98" s="52"/>
       <c r="P98" s="5"/>
       <c r="Q98" s="5"/>
-      <c r="R98" s="42"/>
-    </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="43"/>
-      <c r="B99" s="44"/>
-      <c r="C99" s="43" t="n">
+      <c r="R98" s="45"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="34"/>
+      <c r="B99" s="23"/>
+      <c r="C99" s="34" t="n">
         <v>82</v>
       </c>
-      <c r="D99" s="44"/>
+      <c r="D99" s="23"/>
       <c r="E99" s="23" t="s">
-        <v>345</v>
-      </c>
-      <c r="F99" s="50" t="s">
+        <v>350</v>
+      </c>
+      <c r="F99" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="G99" s="43" t="n">
+      <c r="G99" s="34" t="n">
         <v>85</v>
       </c>
-      <c r="H99" s="43"/>
-      <c r="I99" s="43" t="n">
+      <c r="H99" s="34"/>
+      <c r="I99" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="K99" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L99" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M99" s="49"/>
-      <c r="N99" s="49"/>
-      <c r="O99" s="49"/>
+        <v>351</v>
+      </c>
+      <c r="K99" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L99" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M99" s="52"/>
+      <c r="N99" s="52"/>
+      <c r="O99" s="52"/>
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
-      <c r="R99" s="51"/>
-    </row>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="43"/>
-      <c r="B100" s="44"/>
-      <c r="C100" s="43" t="n">
+      <c r="R99" s="53"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="34"/>
+      <c r="B100" s="23"/>
+      <c r="C100" s="34" t="n">
         <v>83</v>
       </c>
-      <c r="D100" s="44"/>
+      <c r="D100" s="23"/>
       <c r="E100" s="23" t="s">
-        <v>345</v>
-      </c>
-      <c r="F100" s="50" t="s">
+        <v>350</v>
+      </c>
+      <c r="F100" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="G100" s="43" t="n">
+      <c r="G100" s="34" t="n">
         <v>85</v>
       </c>
-      <c r="H100" s="43"/>
-      <c r="I100" s="43" t="n">
+      <c r="H100" s="34"/>
+      <c r="I100" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J100" s="5"/>
-      <c r="K100" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L100" s="49"/>
-      <c r="M100" s="49"/>
-      <c r="N100" s="49"/>
-      <c r="O100" s="49"/>
+      <c r="K100" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L100" s="52"/>
+      <c r="M100" s="52"/>
+      <c r="N100" s="52"/>
+      <c r="O100" s="52"/>
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
-      <c r="R100" s="42"/>
-    </row>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="43" t="n">
+      <c r="R100" s="45"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="34" t="n">
         <v>86</v>
       </c>
-      <c r="B101" s="44"/>
-      <c r="C101" s="43" t="n">
+      <c r="B101" s="23"/>
+      <c r="C101" s="34" t="n">
         <v>84</v>
       </c>
-      <c r="D101" s="44"/>
+      <c r="D101" s="23"/>
       <c r="E101" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="F101" s="50" t="s">
+        <v>352</v>
+      </c>
+      <c r="F101" s="58" t="s">
         <v>155</v>
       </c>
-      <c r="G101" s="43" t="n">
+      <c r="G101" s="34" t="n">
         <v>85</v>
       </c>
-      <c r="H101" s="43" t="n">
+      <c r="H101" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I101" s="43" t="n">
+      <c r="I101" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="K101" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L101" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M101" s="49"/>
-      <c r="N101" s="49"/>
-      <c r="O101" s="49"/>
+        <v>353</v>
+      </c>
+      <c r="K101" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L101" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M101" s="52"/>
+      <c r="N101" s="52"/>
+      <c r="O101" s="52"/>
       <c r="P101" s="5"/>
       <c r="Q101" s="5"/>
-      <c r="R101" s="42"/>
-    </row>
-    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="43" t="n">
-        <v>87</v>
-      </c>
-      <c r="B102" s="44"/>
-      <c r="C102" s="43" t="n">
+      <c r="R101" s="45"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="34" t="n">
+        <v>87</v>
+      </c>
+      <c r="B102" s="23"/>
+      <c r="C102" s="34" t="n">
         <v>85</v>
       </c>
-      <c r="D102" s="44"/>
+      <c r="D102" s="23"/>
       <c r="E102" s="23" t="s">
-        <v>349</v>
-      </c>
-      <c r="F102" s="50" t="s">
+        <v>354</v>
+      </c>
+      <c r="F102" s="58" t="s">
         <v>153</v>
       </c>
-      <c r="G102" s="43" t="n">
+      <c r="G102" s="34" t="n">
         <v>85</v>
       </c>
-      <c r="H102" s="43" t="n">
+      <c r="H102" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I102" s="43" t="n">
+      <c r="I102" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="K102" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L102" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M102" s="49"/>
-      <c r="N102" s="49"/>
-      <c r="O102" s="49"/>
+        <v>355</v>
+      </c>
+      <c r="K102" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L102" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M102" s="52"/>
+      <c r="N102" s="52"/>
+      <c r="O102" s="52"/>
       <c r="P102" s="5"/>
       <c r="Q102" s="5"/>
-      <c r="R102" s="42"/>
-    </row>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="43" t="n">
+      <c r="R102" s="45"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="34" t="n">
         <v>88</v>
       </c>
-      <c r="B103" s="44"/>
-      <c r="C103" s="43" t="n">
+      <c r="B103" s="23"/>
+      <c r="C103" s="34" t="n">
         <v>86</v>
       </c>
-      <c r="D103" s="44"/>
+      <c r="D103" s="23"/>
       <c r="E103" s="23" t="s">
-        <v>351</v>
-      </c>
-      <c r="F103" s="50" t="s">
+        <v>356</v>
+      </c>
+      <c r="F103" s="58" t="s">
         <v>166</v>
       </c>
-      <c r="G103" s="43" t="n">
+      <c r="G103" s="34" t="n">
         <v>85</v>
       </c>
-      <c r="H103" s="43" t="n">
+      <c r="H103" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I103" s="43" t="n">
+      <c r="I103" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="K103" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L103" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M103" s="49"/>
-      <c r="N103" s="49"/>
-      <c r="O103" s="49"/>
+        <v>357</v>
+      </c>
+      <c r="K103" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L103" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M103" s="52"/>
+      <c r="N103" s="52"/>
+      <c r="O103" s="52"/>
       <c r="P103" s="5"/>
       <c r="Q103" s="5"/>
-      <c r="R103" s="42"/>
-    </row>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="43" t="n">
+      <c r="R103" s="45"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="34" t="n">
         <v>89</v>
       </c>
-      <c r="B104" s="44"/>
-      <c r="C104" s="43" t="n">
-        <v>87</v>
-      </c>
-      <c r="D104" s="44"/>
+      <c r="B104" s="23"/>
+      <c r="C104" s="34" t="n">
+        <v>87</v>
+      </c>
+      <c r="D104" s="23"/>
       <c r="E104" s="23" t="s">
-        <v>353</v>
-      </c>
-      <c r="F104" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="F104" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="G104" s="43" t="n">
+      <c r="G104" s="34" t="n">
         <v>85</v>
       </c>
-      <c r="H104" s="43" t="n">
+      <c r="H104" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I104" s="43" t="n">
+      <c r="I104" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="K104" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L104" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M104" s="49"/>
-      <c r="N104" s="49"/>
-      <c r="O104" s="49"/>
+        <v>359</v>
+      </c>
+      <c r="K104" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L104" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M104" s="52"/>
+      <c r="N104" s="52"/>
+      <c r="O104" s="52"/>
       <c r="P104" s="5"/>
       <c r="Q104" s="5"/>
-      <c r="R104" s="42"/>
-    </row>
-    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="43" t="n">
+      <c r="R104" s="45"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="34" t="n">
         <v>90</v>
       </c>
-      <c r="B105" s="44"/>
-      <c r="C105" s="43" t="n">
+      <c r="B105" s="23"/>
+      <c r="C105" s="34" t="n">
         <v>88</v>
       </c>
-      <c r="D105" s="44"/>
+      <c r="D105" s="23"/>
       <c r="E105" s="23" t="s">
-        <v>355</v>
-      </c>
-      <c r="F105" s="50" t="s">
+        <v>360</v>
+      </c>
+      <c r="F105" s="58" t="s">
         <v>168</v>
       </c>
-      <c r="G105" s="43" t="n">
+      <c r="G105" s="34" t="n">
         <v>85</v>
       </c>
-      <c r="H105" s="43" t="n">
+      <c r="H105" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I105" s="43" t="n">
+      <c r="I105" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="K105" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L105" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M105" s="49"/>
-      <c r="N105" s="49"/>
-      <c r="O105" s="49"/>
+        <v>361</v>
+      </c>
+      <c r="K105" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L105" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M105" s="52"/>
+      <c r="N105" s="52"/>
+      <c r="O105" s="52"/>
       <c r="P105" s="5"/>
       <c r="Q105" s="5"/>
-      <c r="R105" s="42"/>
-    </row>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="43" t="n">
+      <c r="R105" s="45"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="34" t="n">
         <v>91</v>
       </c>
-      <c r="B106" s="44"/>
-      <c r="C106" s="43" t="n">
+      <c r="B106" s="23"/>
+      <c r="C106" s="34" t="n">
         <v>89</v>
       </c>
-      <c r="D106" s="44"/>
+      <c r="D106" s="23"/>
       <c r="E106" s="23" t="s">
-        <v>357</v>
-      </c>
-      <c r="F106" s="58" t="s">
-        <v>358</v>
-      </c>
-      <c r="G106" s="43" t="n">
+        <v>362</v>
+      </c>
+      <c r="F106" s="59" t="s">
+        <v>363</v>
+      </c>
+      <c r="G106" s="34" t="n">
         <v>90</v>
       </c>
-      <c r="H106" s="43" t="n">
+      <c r="H106" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I106" s="43" t="n">
+      <c r="I106" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="K106" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L106" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M106" s="49"/>
-      <c r="N106" s="49"/>
-      <c r="O106" s="49"/>
+        <v>364</v>
+      </c>
+      <c r="K106" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L106" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M106" s="52"/>
+      <c r="N106" s="52"/>
+      <c r="O106" s="52"/>
       <c r="P106" s="5"/>
       <c r="Q106" s="5"/>
-      <c r="R106" s="42"/>
-    </row>
-    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="43" t="n">
+      <c r="R106" s="45"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="34" t="n">
         <v>92</v>
       </c>
-      <c r="B107" s="44"/>
-      <c r="C107" s="43" t="n">
+      <c r="B107" s="23"/>
+      <c r="C107" s="34" t="n">
         <v>90</v>
       </c>
-      <c r="D107" s="44"/>
+      <c r="D107" s="23"/>
       <c r="E107" s="23" t="s">
-        <v>360</v>
-      </c>
-      <c r="F107" s="50" t="s">
+        <v>365</v>
+      </c>
+      <c r="F107" s="58" t="s">
         <v>170</v>
       </c>
-      <c r="G107" s="43" t="n">
+      <c r="G107" s="34" t="n">
         <v>85</v>
       </c>
-      <c r="H107" s="43" t="n">
+      <c r="H107" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I107" s="43" t="n">
+      <c r="I107" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="K107" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L107" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M107" s="49"/>
-      <c r="N107" s="49"/>
-      <c r="O107" s="49"/>
+        <v>366</v>
+      </c>
+      <c r="K107" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L107" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M107" s="52"/>
+      <c r="N107" s="52"/>
+      <c r="O107" s="52"/>
       <c r="P107" s="5"/>
       <c r="Q107" s="5"/>
-      <c r="R107" s="51"/>
-    </row>
-    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="34" t="n">
+      <c r="R107" s="53"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="40" t="n">
         <v>93</v>
       </c>
       <c r="B108" s="24"/>
-      <c r="C108" s="34"/>
+      <c r="C108" s="40"/>
       <c r="D108" s="24"/>
       <c r="E108" s="24"/>
       <c r="F108" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="G108" s="34" t="n">
+      <c r="G108" s="40" t="n">
         <v>43</v>
       </c>
-      <c r="H108" s="34" t="n">
+      <c r="H108" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I108" s="34"/>
+      <c r="I108" s="40"/>
       <c r="J108" s="8"/>
-      <c r="K108" s="41"/>
-      <c r="L108" s="41"/>
-      <c r="M108" s="53"/>
-      <c r="N108" s="53"/>
-      <c r="O108" s="53"/>
+      <c r="K108" s="43"/>
+      <c r="L108" s="43"/>
+      <c r="M108" s="50"/>
+      <c r="N108" s="50"/>
+      <c r="O108" s="50"/>
       <c r="P108" s="8"/>
       <c r="Q108" s="8"/>
-      <c r="R108" s="42"/>
-    </row>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="34" t="n">
+      <c r="R108" s="45"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="40" t="n">
         <v>94</v>
       </c>
       <c r="B109" s="24"/>
-      <c r="C109" s="34" t="n">
+      <c r="C109" s="40" t="n">
         <v>91</v>
       </c>
       <c r="D109" s="24"/>
       <c r="E109" s="24" t="s">
-        <v>362</v>
-      </c>
-      <c r="F109" s="40" t="s">
+        <v>367</v>
+      </c>
+      <c r="F109" s="56" t="s">
         <v>172</v>
       </c>
-      <c r="G109" s="34" t="n">
+      <c r="G109" s="40" t="n">
         <v>93</v>
       </c>
-      <c r="H109" s="34" t="n">
+      <c r="H109" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I109" s="34" t="n">
+      <c r="I109" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="K109" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L109" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M109" s="53"/>
-      <c r="N109" s="53"/>
-      <c r="O109" s="53"/>
+        <v>368</v>
+      </c>
+      <c r="K109" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L109" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M109" s="50"/>
+      <c r="N109" s="50"/>
+      <c r="O109" s="50"/>
       <c r="P109" s="8"/>
       <c r="Q109" s="8"/>
-      <c r="R109" s="42"/>
-    </row>
-    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="34" t="n">
+      <c r="R109" s="45"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="40" t="n">
         <v>95</v>
       </c>
       <c r="B110" s="24"/>
-      <c r="C110" s="34" t="n">
+      <c r="C110" s="40" t="n">
         <v>92</v>
       </c>
       <c r="D110" s="24"/>
       <c r="E110" s="24" t="s">
-        <v>364</v>
-      </c>
-      <c r="F110" s="40" t="s">
+        <v>369</v>
+      </c>
+      <c r="F110" s="56" t="s">
         <v>173</v>
       </c>
-      <c r="G110" s="34" t="n">
+      <c r="G110" s="40" t="n">
         <v>93</v>
       </c>
-      <c r="H110" s="34" t="n">
+      <c r="H110" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I110" s="34" t="n">
+      <c r="I110" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="K110" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L110" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M110" s="53"/>
-      <c r="N110" s="53"/>
-      <c r="O110" s="53"/>
+        <v>370</v>
+      </c>
+      <c r="K110" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L110" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M110" s="50"/>
+      <c r="N110" s="50"/>
+      <c r="O110" s="50"/>
       <c r="P110" s="8"/>
       <c r="Q110" s="8"/>
-      <c r="R110" s="42"/>
-    </row>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="34" t="n">
+      <c r="R110" s="45"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="40" t="n">
         <v>96</v>
       </c>
       <c r="B111" s="24"/>
-      <c r="C111" s="34" t="n">
+      <c r="C111" s="40" t="n">
         <v>93</v>
       </c>
       <c r="D111" s="24"/>
       <c r="E111" s="24" t="s">
-        <v>366</v>
-      </c>
-      <c r="F111" s="40" t="s">
+        <v>371</v>
+      </c>
+      <c r="F111" s="56" t="s">
         <v>174</v>
       </c>
-      <c r="G111" s="34" t="n">
+      <c r="G111" s="40" t="n">
         <v>93</v>
       </c>
-      <c r="H111" s="34" t="n">
+      <c r="H111" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I111" s="34" t="n">
+      <c r="I111" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="K111" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L111" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M111" s="53"/>
-      <c r="N111" s="41" t="s">
-        <v>230</v>
-      </c>
-      <c r="O111" s="53"/>
+        <v>372</v>
+      </c>
+      <c r="K111" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L111" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M111" s="50"/>
+      <c r="N111" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="O111" s="50"/>
       <c r="P111" s="8"/>
       <c r="Q111" s="8"/>
-      <c r="R111" s="42"/>
-    </row>
-    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="34" t="n">
+      <c r="R111" s="45"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="40" t="n">
         <v>97</v>
       </c>
       <c r="B112" s="24"/>
-      <c r="C112" s="34" t="n">
+      <c r="C112" s="40" t="n">
         <v>94</v>
       </c>
       <c r="D112" s="24"/>
       <c r="E112" s="24" t="s">
-        <v>368</v>
-      </c>
-      <c r="F112" s="40" t="s">
+        <v>373</v>
+      </c>
+      <c r="F112" s="56" t="s">
         <v>171</v>
       </c>
-      <c r="G112" s="34" t="n">
+      <c r="G112" s="40" t="n">
         <v>93</v>
       </c>
-      <c r="H112" s="34" t="n">
+      <c r="H112" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I112" s="34" t="n">
+      <c r="I112" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="K112" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L112" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M112" s="53"/>
-      <c r="N112" s="41" t="s">
-        <v>230</v>
-      </c>
-      <c r="O112" s="53"/>
+        <v>374</v>
+      </c>
+      <c r="K112" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L112" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M112" s="50"/>
+      <c r="N112" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="O112" s="50"/>
       <c r="P112" s="8"/>
       <c r="Q112" s="8"/>
-      <c r="R112" s="42"/>
-    </row>
-    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="43" t="n">
+      <c r="R112" s="45"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="34" t="n">
         <v>98</v>
       </c>
-      <c r="B113" s="44"/>
-      <c r="C113" s="43" t="n">
+      <c r="B113" s="23"/>
+      <c r="C113" s="34" t="n">
         <v>95</v>
       </c>
-      <c r="D113" s="44"/>
+      <c r="D113" s="23"/>
       <c r="E113" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="F113" s="44" t="s">
+        <v>375</v>
+      </c>
+      <c r="F113" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="G113" s="43" t="n">
+      <c r="G113" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H113" s="43" t="n">
+      <c r="H113" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I113" s="43" t="n">
+      <c r="I113" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J113" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="K113" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L113" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M113" s="49"/>
-      <c r="N113" s="49"/>
-      <c r="O113" s="49"/>
+        <v>376</v>
+      </c>
+      <c r="K113" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L113" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M113" s="52"/>
+      <c r="N113" s="52"/>
+      <c r="O113" s="52"/>
       <c r="P113" s="5"/>
       <c r="Q113" s="5"/>
-      <c r="R113" s="42"/>
-    </row>
-    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="43" t="n">
+      <c r="R113" s="45"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="34" t="n">
         <v>99</v>
       </c>
-      <c r="B114" s="44"/>
-      <c r="C114" s="43" t="n">
+      <c r="B114" s="23"/>
+      <c r="C114" s="34" t="n">
         <v>96</v>
       </c>
-      <c r="D114" s="44"/>
+      <c r="D114" s="23"/>
       <c r="E114" s="23" t="s">
-        <v>372</v>
-      </c>
-      <c r="F114" s="50" t="s">
+        <v>377</v>
+      </c>
+      <c r="F114" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="G114" s="43" t="n">
+      <c r="G114" s="34" t="n">
         <v>98</v>
       </c>
-      <c r="H114" s="43" t="n">
+      <c r="H114" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I114" s="43" t="n">
+      <c r="I114" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J114" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="K114" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L114" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M114" s="49"/>
-      <c r="N114" s="49"/>
-      <c r="O114" s="49"/>
+        <v>378</v>
+      </c>
+      <c r="K114" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L114" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M114" s="52"/>
+      <c r="N114" s="52"/>
+      <c r="O114" s="52"/>
       <c r="P114" s="5"/>
       <c r="Q114" s="5"/>
     </row>
-    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="34" t="n">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="40" t="n">
         <v>100</v>
       </c>
       <c r="B115" s="24"/>
-      <c r="C115" s="34"/>
+      <c r="C115" s="40"/>
       <c r="D115" s="24"/>
       <c r="E115" s="24"/>
       <c r="F115" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="G115" s="34" t="n">
+      <c r="G115" s="40" t="n">
         <v>43</v>
       </c>
-      <c r="H115" s="34" t="n">
+      <c r="H115" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I115" s="34"/>
+      <c r="I115" s="40"/>
       <c r="J115" s="8"/>
-      <c r="K115" s="41"/>
-      <c r="L115" s="41"/>
-      <c r="M115" s="53"/>
-      <c r="N115" s="53"/>
-      <c r="O115" s="53"/>
+      <c r="K115" s="43"/>
+      <c r="L115" s="43"/>
+      <c r="M115" s="50"/>
+      <c r="N115" s="50"/>
+      <c r="O115" s="50"/>
       <c r="P115" s="8"/>
       <c r="Q115" s="8"/>
-      <c r="R115" s="42"/>
-    </row>
-    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="34" t="n">
+      <c r="R115" s="45"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="40" t="n">
         <v>101</v>
       </c>
       <c r="B116" s="24"/>
-      <c r="C116" s="34" t="n">
+      <c r="C116" s="40" t="n">
         <v>97</v>
       </c>
       <c r="D116" s="24"/>
       <c r="E116" s="24" t="s">
-        <v>374</v>
-      </c>
-      <c r="F116" s="40" t="s">
+        <v>379</v>
+      </c>
+      <c r="F116" s="56" t="s">
         <v>178</v>
       </c>
-      <c r="G116" s="34" t="n">
+      <c r="G116" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="H116" s="34" t="n">
+      <c r="H116" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I116" s="34" t="n">
+      <c r="I116" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J116" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="K116" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L116" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M116" s="53"/>
-      <c r="N116" s="53"/>
-      <c r="O116" s="53"/>
+        <v>380</v>
+      </c>
+      <c r="K116" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L116" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M116" s="50"/>
+      <c r="N116" s="50"/>
+      <c r="O116" s="50"/>
       <c r="P116" s="8"/>
       <c r="Q116" s="8"/>
-      <c r="R116" s="42"/>
-    </row>
-    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="34" t="n">
+      <c r="R116" s="45"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="40" t="n">
         <v>102</v>
       </c>
       <c r="B117" s="24"/>
-      <c r="C117" s="34" t="n">
+      <c r="C117" s="40" t="n">
         <v>98</v>
       </c>
       <c r="D117" s="24"/>
       <c r="E117" s="24" t="s">
-        <v>376</v>
-      </c>
-      <c r="F117" s="40" t="s">
+        <v>381</v>
+      </c>
+      <c r="F117" s="56" t="s">
         <v>179</v>
       </c>
-      <c r="G117" s="34" t="n">
+      <c r="G117" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="H117" s="34" t="n">
+      <c r="H117" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I117" s="34" t="n">
+      <c r="I117" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J117" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="K117" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L117" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M117" s="53"/>
-      <c r="N117" s="53"/>
-      <c r="O117" s="53"/>
+        <v>382</v>
+      </c>
+      <c r="K117" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L117" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M117" s="50"/>
+      <c r="N117" s="50"/>
+      <c r="O117" s="50"/>
       <c r="P117" s="8"/>
       <c r="Q117" s="8"/>
-      <c r="R117" s="42"/>
-    </row>
-    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="34"/>
+      <c r="R117" s="45"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="40"/>
       <c r="B118" s="24"/>
-      <c r="C118" s="34" t="n">
+      <c r="C118" s="40" t="n">
         <v>99</v>
       </c>
       <c r="D118" s="24"/>
       <c r="E118" s="24" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F118" s="24"/>
-      <c r="G118" s="34"/>
-      <c r="H118" s="34"/>
-      <c r="I118" s="34" t="n">
+      <c r="G118" s="40"/>
+      <c r="H118" s="40"/>
+      <c r="I118" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J118" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="K118" s="53"/>
-      <c r="L118" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="M118" s="53"/>
-      <c r="N118" s="41" t="s">
-        <v>230</v>
-      </c>
-      <c r="O118" s="53"/>
+        <v>383</v>
+      </c>
+      <c r="K118" s="50"/>
+      <c r="L118" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="M118" s="50"/>
+      <c r="N118" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="O118" s="50"/>
       <c r="P118" s="8"/>
       <c r="Q118" s="8"/>
-      <c r="R118" s="51"/>
-    </row>
-    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="43" t="n">
+      <c r="R118" s="53"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="34" t="n">
         <v>103</v>
       </c>
-      <c r="B119" s="44"/>
-      <c r="C119" s="43"/>
-      <c r="D119" s="44"/>
+      <c r="B119" s="23"/>
+      <c r="C119" s="34"/>
+      <c r="D119" s="23"/>
       <c r="E119" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="F119" s="44" t="s">
+      <c r="F119" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="G119" s="43" t="n">
+      <c r="G119" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H119" s="43" t="n">
+      <c r="H119" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I119" s="43"/>
+      <c r="I119" s="34"/>
       <c r="J119" s="5"/>
-      <c r="K119" s="48"/>
-      <c r="L119" s="49"/>
-      <c r="M119" s="49"/>
-      <c r="N119" s="49"/>
-      <c r="O119" s="49"/>
+      <c r="K119" s="47"/>
+      <c r="L119" s="52"/>
+      <c r="M119" s="52"/>
+      <c r="N119" s="52"/>
+      <c r="O119" s="52"/>
       <c r="P119" s="5"/>
       <c r="Q119" s="5"/>
-      <c r="R119" s="42"/>
-    </row>
-    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="43" t="n">
+      <c r="R119" s="45"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="34" t="n">
         <v>104</v>
       </c>
-      <c r="B120" s="44"/>
-      <c r="C120" s="43" t="n">
+      <c r="B120" s="23"/>
+      <c r="C120" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="D120" s="44"/>
+      <c r="D120" s="23"/>
       <c r="E120" s="23" t="s">
-        <v>379</v>
-      </c>
-      <c r="F120" s="50" t="s">
+        <v>384</v>
+      </c>
+      <c r="F120" s="58" t="s">
         <v>181</v>
       </c>
-      <c r="G120" s="43" t="n">
+      <c r="G120" s="34" t="n">
         <v>103</v>
       </c>
-      <c r="H120" s="43" t="n">
+      <c r="H120" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I120" s="43" t="n">
+      <c r="I120" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J120" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="K120" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L120" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M120" s="49"/>
-      <c r="N120" s="49"/>
-      <c r="O120" s="49"/>
+        <v>385</v>
+      </c>
+      <c r="K120" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L120" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M120" s="52"/>
+      <c r="N120" s="52"/>
+      <c r="O120" s="52"/>
       <c r="P120" s="5"/>
       <c r="Q120" s="5"/>
-      <c r="R120" s="42"/>
-    </row>
-    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="43" t="n">
+      <c r="R120" s="45"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="34" t="n">
         <v>105</v>
       </c>
-      <c r="B121" s="44"/>
-      <c r="C121" s="43" t="n">
+      <c r="B121" s="23"/>
+      <c r="C121" s="34" t="n">
         <v>101</v>
       </c>
-      <c r="D121" s="44"/>
+      <c r="D121" s="23"/>
       <c r="E121" s="23" t="s">
-        <v>381</v>
-      </c>
-      <c r="F121" s="50" t="s">
+        <v>386</v>
+      </c>
+      <c r="F121" s="58" t="s">
         <v>182</v>
       </c>
-      <c r="G121" s="43" t="n">
+      <c r="G121" s="34" t="n">
         <v>103</v>
       </c>
-      <c r="H121" s="43" t="n">
+      <c r="H121" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I121" s="43" t="n">
+      <c r="I121" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J121" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="K121" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L121" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M121" s="49"/>
-      <c r="N121" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="O121" s="49"/>
+        <v>387</v>
+      </c>
+      <c r="K121" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L121" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M121" s="52"/>
+      <c r="N121" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="O121" s="52"/>
       <c r="P121" s="5"/>
       <c r="Q121" s="5"/>
-      <c r="R121" s="42"/>
-    </row>
-    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="43" t="n">
+      <c r="R121" s="45"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="34" t="n">
         <v>106</v>
       </c>
-      <c r="B122" s="44"/>
-      <c r="C122" s="43" t="n">
+      <c r="B122" s="23"/>
+      <c r="C122" s="34" t="n">
         <v>102</v>
       </c>
-      <c r="D122" s="44"/>
+      <c r="D122" s="23"/>
       <c r="E122" s="23" t="s">
-        <v>383</v>
-      </c>
-      <c r="F122" s="50" t="s">
+        <v>388</v>
+      </c>
+      <c r="F122" s="58" t="s">
         <v>183</v>
       </c>
-      <c r="G122" s="43" t="n">
+      <c r="G122" s="34" t="n">
         <v>103</v>
       </c>
-      <c r="H122" s="43" t="n">
+      <c r="H122" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I122" s="43" t="n">
+      <c r="I122" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J122" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="K122" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L122" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="M122" s="49"/>
-      <c r="N122" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="O122" s="49"/>
+        <v>389</v>
+      </c>
+      <c r="K122" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L122" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M122" s="52"/>
+      <c r="N122" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="O122" s="52"/>
       <c r="P122" s="5"/>
       <c r="Q122" s="5"/>
     </row>
-    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="34" t="n">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="40" t="n">
         <v>107</v>
       </c>
       <c r="B123" s="24"/>
-      <c r="C123" s="34" t="n">
+      <c r="C123" s="40" t="n">
         <v>103</v>
       </c>
       <c r="D123" s="24"/>
       <c r="E123" s="24" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F123" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G123" s="34" t="n">
+      <c r="G123" s="40" t="n">
         <v>43</v>
       </c>
-      <c r="H123" s="34" t="n">
+      <c r="H123" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="I123" s="34" t="n">
+      <c r="I123" s="40" t="n">
         <v>1</v>
       </c>
       <c r="J123" s="8"/>
-      <c r="K123" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L123" s="53"/>
-      <c r="M123" s="53"/>
-      <c r="N123" s="53"/>
-      <c r="O123" s="53"/>
+      <c r="K123" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L123" s="50"/>
+      <c r="M123" s="50"/>
+      <c r="N123" s="50"/>
+      <c r="O123" s="50"/>
       <c r="P123" s="8"/>
       <c r="Q123" s="8"/>
     </row>
-    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="43" t="n">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="34" t="n">
         <v>108</v>
       </c>
-      <c r="B124" s="44"/>
-      <c r="C124" s="43" t="n">
+      <c r="B124" s="23"/>
+      <c r="C124" s="34" t="n">
         <v>104</v>
       </c>
-      <c r="D124" s="44"/>
+      <c r="D124" s="23"/>
       <c r="E124" s="23" t="s">
-        <v>386</v>
-      </c>
-      <c r="F124" s="44" t="s">
+        <v>391</v>
+      </c>
+      <c r="F124" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="G124" s="43" t="n">
+      <c r="G124" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H124" s="43" t="n">
+      <c r="H124" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I124" s="43" t="n">
+      <c r="I124" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J124" s="5"/>
-      <c r="K124" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L124" s="49"/>
-      <c r="M124" s="49"/>
-      <c r="N124" s="49"/>
-      <c r="O124" s="49"/>
+      <c r="K124" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L124" s="52"/>
+      <c r="M124" s="52"/>
+      <c r="N124" s="52"/>
+      <c r="O124" s="52"/>
       <c r="P124" s="5"/>
       <c r="Q124" s="5"/>
     </row>
-    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="43" t="n">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="34" t="n">
         <v>109</v>
       </c>
-      <c r="B125" s="44"/>
-      <c r="C125" s="43" t="n">
+      <c r="B125" s="23"/>
+      <c r="C125" s="34" t="n">
         <v>105</v>
       </c>
-      <c r="D125" s="44"/>
+      <c r="D125" s="23"/>
       <c r="E125" s="23" t="s">
-        <v>387</v>
-      </c>
-      <c r="F125" s="50" t="s">
+        <v>392</v>
+      </c>
+      <c r="F125" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="G125" s="43" t="n">
+      <c r="G125" s="34" t="n">
         <v>108</v>
       </c>
-      <c r="H125" s="43" t="n">
+      <c r="H125" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I125" s="43" t="n">
+      <c r="I125" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J125" s="5"/>
-      <c r="K125" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L125" s="49"/>
-      <c r="M125" s="49"/>
-      <c r="N125" s="49"/>
-      <c r="O125" s="49"/>
+      <c r="K125" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L125" s="52"/>
+      <c r="M125" s="52"/>
+      <c r="N125" s="52"/>
+      <c r="O125" s="52"/>
       <c r="P125" s="5"/>
       <c r="Q125" s="5"/>
     </row>
-    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="28"/>
       <c r="C126" s="28"/>
     </row>
-    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="28"/>
       <c r="C127" s="28"/>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="K5" r:id="rId2" display="PDF"/>
@@ -10158,7 +10198,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.15"/>
@@ -10199,7 +10239,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10209,7 +10249,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -10224,18 +10264,18 @@
       <c r="B6" s="24"/>
       <c r="C6" s="8"/>
       <c r="E6" s="10" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
         <v>27</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10244,10 +10284,10 @@
       <c r="C7" s="8"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
@@ -10261,10 +10301,10 @@
       <c r="C8" s="8"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8" t="s">
@@ -10277,7 +10317,7 @@
       <c r="B9" s="24"/>
       <c r="C9" s="8"/>
       <c r="E9" s="6" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="5"/>
@@ -10286,7 +10326,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10295,7 +10335,7 @@
       <c r="C10" s="8"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>39</v>
@@ -10305,7 +10345,7 @@
         <v>45</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10314,17 +10354,17 @@
       <c r="C11" s="8"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10332,11 +10372,11 @@
       <c r="B12" s="24"/>
       <c r="C12" s="8"/>
       <c r="E12" s="10" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="8" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8" t="s">
@@ -10350,10 +10390,10 @@
       <c r="C13" s="8"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8" t="s">
@@ -10367,10 +10407,10 @@
       <c r="C14" s="8"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8" t="s">
@@ -10384,14 +10424,14 @@
       <c r="C15" s="8"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="J15" s="8"/>
     </row>
@@ -10400,7 +10440,7 @@
       <c r="B16" s="24"/>
       <c r="C16" s="8"/>
       <c r="E16" s="6" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="5"/>
@@ -10413,7 +10453,7 @@
       <c r="B17" s="24"/>
       <c r="C17" s="8"/>
       <c r="E17" s="10" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="8"/>
@@ -10436,13 +10476,13 @@
         <v>79</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>83</v>

--- a/server_nestjs/src/storage/Kompetenzraster.xlsx
+++ b/server_nestjs/src/storage/Kompetenzraster.xlsx
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="416">
   <si>
     <t xml:space="preserve">Voraussetzungen lt. Modulhandbuch</t>
   </si>
@@ -757,7 +757,19 @@
     <t xml:space="preserve">Python bietet verschiedene Operatoren für mathematische Operationen, wie die Standardaddition, -subtraktion, -multiplikation und -division, sowie spezielle Operatoren für ganzzahlige Division (//), Modulus (%) und Exponentiation (**). Bei der Division von Ganzzahlen wird automatisch ein Fließkommawert zurückgegeben, während die ganzzahlige Division immer abrundet; zudem können alle Operatoren in Verbindung mit dem Zuweisungsoperator (z.B. +=, *=) für verkürzte Operationen verwendet werden.</t>
   </si>
   <si>
-    <t xml:space="preserve">9,10</t>
+    <t xml:space="preserve">2,8,16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Python repräsentieren Booleans die Wahrheitswerte True und False, während None ein spezieller Datentyp ist, der zur Initialisierung von Variablen verwendet wird und nur den Wert None annehmen kann. Diese Datentypen sind essentiell für Vergleichsoperationen und Kontrollstrukturen, wobei None oft genutzt wird, um den Zustand "kein Wert" oder "nicht initialisiert" darzustellen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,8,17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Python repräsentieren Booleans die Wahrheitswerte True und False, die häufig in Vergleichsoperationen verwendet werden, um logische Bedingungen zu testen. Der Datentyp None wird oft zur Initialisierung von Variablen verwendet und hat nur einen Wert, nämlich None selbst, was anzeigt, dass eine Variable noch keinen anderen Wert zugewiesen bekommen hat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9, 10,16,17</t>
   </si>
   <si>
     <t xml:space="preserve">2,8,10,11,12,13,15</t>
@@ -766,18 +778,6 @@
     <t xml:space="preserve">In Python können verschiedene Datentypen wie Int, Float und Komplex sowie Strings ineinander umgewandelt werden, indem man den entsprechenden Datentyp als Funktion verwendet (z.B. `int()`, `float()`, `str()`). Bei der Umwandlung von Eingaben ist zu beachten, dass `input()` immer einen String zurückgibt, der erst in einen numerischen Typ umgewandelt werden muss, um mathematische Operationen durchführen zu können.</t>
   </si>
   <si>
-    <t xml:space="preserve">2,8,16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Python repräsentieren Booleans die Wahrheitswerte True und False, während None ein spezieller Datentyp ist, der zur Initialisierung von Variablen verwendet wird und nur den Wert None annehmen kann. Diese Datentypen sind essentiell für Vergleichsoperationen und Kontrollstrukturen, wobei None oft genutzt wird, um den Zustand "kein Wert" oder "nicht initialisiert" darzustellen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,8,17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Python repräsentieren Booleans die Wahrheitswerte True und False, die häufig in Vergleichsoperationen verwendet werden, um logische Bedingungen zu testen. Der Datentyp None wird oft zur Initialisierung von Variablen verwendet und hat nur einen Wert, nämlich None selbst, was anzeigt, dass eine Variable noch keinen anderen Wert zugewiesen bekommen hat.</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,18</t>
   </si>
   <si>
@@ -814,6 +814,18 @@
     <t xml:space="preserve">In Python ermöglichen for-Schleifen das Durchlaufen von iterierbaren Objekten wie Listen, indem man eine Variable über die Elemente iterieren lässt, beispielsweise mit `for element in my_list`. Die `range`-Funktion wird oft in for-Schleifen verwendet, um über eine Sequenz von Zahlen zu iterieren, wobei man Start-, Stopp- und Schrittweite angeben kann, um beispielsweise mit `for i in range(1, 10, 3)` die Zahlen 1, 4 und 7 zu durchlaufen.</t>
   </si>
   <si>
+    <t xml:space="preserve">2,39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,39,40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,39,41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,39,42</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,23</t>
   </si>
   <si>
@@ -868,7 +880,19 @@
     <t xml:space="preserve">In Python können Variablen entweder mutable (veränderbar) oder immutable (unveränderbar) sein. Globale Variablen, die außerhalb von Funktionen definiert werden, können innerhalb von Funktionen gelesen und, wenn sie mutable sind, auch verändert werden, wobei die Änderungen dann global sichtbar sind; lokale Variablen hingegen sind nur innerhalb ihrer Funktion sichtbar und existieren außerhalb nicht.</t>
   </si>
   <si>
-    <t xml:space="preserve">23,29</t>
+    <t xml:space="preserve">2,34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rekursion in Python bezeichnet das Konzept, bei dem eine Funktion sich selbst aufruft, um ein Problem zu lösen. Es ist wichtig, eine Abbruchbedingung zu definieren, um unendliche Rekursionen und damit Programmabstürze zu vermeiden; rekursive Lösungen können eleganter oder mit weniger Code als iterative Lösungen sein und verhindern die Mutation von Variablen, was sie für funktionale Programmierung attraktiv macht.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rekursion in Python wird oft verwendet, um Probleme zu lösen, die sich in kleinere Instanzen desselben Problems aufteilen lassen, wie beispielsweise die Berechnung der Summe aller Zahlen bis zu einer gegebenen Zahl N oder die Fakultät einer Zahl. Im Transkript werden rekursive Funktionen zur Lösung solcher Probleme diskutiert, wobei die Basisfälle (Abbruchbedingungen) und die rekursiven Aufrufe, die das Problem in kleinere Teile zerlegen, zentrale Elemente sind. Ein weiteres Beispiel ist die rekursive Bestimmung von Primzahlen und die Primfaktorzerlegung einer Zahl, die ebenfalls im Transkript behandelt werden.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In dem Codebeispiel wird die Rekursion anhand verschiedener mathematischer Probleme in Python demonstriert, wie die Summe aller Zahlen bis N, die Fakultät einer Zahl und die Überprüfung, ob eine Zahl eine Primzahl ist. Die Rekursion wird dabei als Methode zur Problemlösung verwendet, indem ein großes Problem in kleinere Instanzen heruntergebrochen wird, bis eine Instanz erreicht ist, die direkt gelöst werden kann.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23,29,34</t>
   </si>
   <si>
     <t xml:space="preserve">2,31</t>
@@ -886,21 +910,6 @@
     <t xml:space="preserve">2,31,33</t>
   </si>
   <si>
-    <t xml:space="preserve">23,31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rekursion in Python bezeichnet das Konzept, bei dem eine Funktion sich selbst aufruft, um ein Problem zu lösen. Es ist wichtig, eine Abbruchbedingung zu definieren, um unendliche Rekursionen und damit Programmabstürze zu vermeiden; rekursive Lösungen können eleganter oder mit weniger Code als iterative Lösungen sein und verhindern die Mutation von Variablen, was sie für funktionale Programmierung attraktiv macht.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rekursion in Python wird oft verwendet, um Probleme zu lösen, die sich in kleinere Instanzen desselben Problems aufteilen lassen, wie beispielsweise die Berechnung der Summe aller Zahlen bis zu einer gegebenen Zahl N oder die Fakultät einer Zahl. Im Transkript werden rekursive Funktionen zur Lösung solcher Probleme diskutiert, wobei die Basisfälle (Abbruchbedingungen) und die rekursiven Aufrufe, die das Problem in kleinere Teile zerlegen, zentrale Elemente sind. Ein weiteres Beispiel ist die rekursive Bestimmung von Primzahlen und die Primfaktorzerlegung einer Zahl, die ebenfalls im Transkript behandelt werden.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In dem Codebeispiel wird die Rekursion anhand verschiedener mathematischer Probleme in Python demonstriert, wie die Summe aller Zahlen bis N, die Fakultät einer Zahl und die Überprüfung, ob eine Zahl eine Primzahl ist. Die Rekursion wird dabei als Methode zur Problemlösung verwendet, indem ein großes Problem in kleinere Instanzen heruntergebrochen wird, bis eine Instanz erreicht ist, die direkt gelöst werden kann.</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,35</t>
   </si>
   <si>
@@ -929,21 +938,6 @@
   </si>
   <si>
     <t xml:space="preserve">Der Befehl reduce nimmt auch eine Funktion und iterierbares Objekt (z.B. Liste oder Tupel) entgegen. Die Funktion muss zwei Elemente in dem iterierbaren Objekt auf eines abbilden und reduziert nun durch sukzessives Anwenden der Funktion das gesamte iterierbare Objekt auf ein Element.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,39,40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,39,41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,39,42</t>
   </si>
   <si>
     <t xml:space="preserve">Objektorientierte Programmierung mit Java</t>
@@ -1357,7 +1351,7 @@
     <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1437,8 +1431,24 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u val="single"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1460,13 +1470,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD0CECE"/>
-        <bgColor rgb="FFCCCCFF"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFE7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2B2B2"/>
+        <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
   </fills>
@@ -1508,7 +1524,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="73">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1645,30 +1661,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1677,15 +1669,27 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1693,16 +1697,36 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1713,28 +1737,16 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="4" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1742,11 +1754,43 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="4" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1799,7 +1843,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFD0CECE"/>
+      <rgbColor rgb="FFB2B2B2"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -1808,7 +1852,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0563C1"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD0CECE"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1852,7 +1896,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I245"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.15"/>
@@ -5334,12 +5378,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S127"/>
-  <sheetFormatPr defaultColWidth="10.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:S1048576"/>
+  <sheetFormatPr defaultColWidth="10.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="17.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="17.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="25" width="22.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="25" width="16.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.43"/>
@@ -5449,13 +5493,13 @@
       <c r="A4" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="23"/>
+      <c r="B4" s="24"/>
       <c r="C4" s="34"/>
       <c r="D4" s="35"/>
       <c r="E4" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="24" t="s">
         <v>67</v>
       </c>
       <c r="G4" s="34" t="n">
@@ -5465,65 +5509,65 @@
         <v>3</v>
       </c>
       <c r="I4" s="38"/>
-      <c r="J4" s="18"/>
+      <c r="J4" s="12"/>
       <c r="K4" s="39"/>
       <c r="L4" s="39"/>
       <c r="M4" s="39"/>
       <c r="N4" s="39"/>
       <c r="O4" s="39"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
       <c r="R4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="40" t="n">
+      <c r="A5" s="34" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="24"/>
-      <c r="C5" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="41"/>
+      <c r="C5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="35"/>
       <c r="E5" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="G5" s="40" t="n">
+      <c r="G5" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="42" t="n">
+      <c r="H5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="38" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="12"/>
-      <c r="K5" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
+      <c r="K5" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
       <c r="P5" s="12"/>
       <c r="Q5" s="12"/>
-      <c r="R5" s="45"/>
+      <c r="R5" s="42"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="23"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="34" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="35"/>
-      <c r="E6" s="46" t="s">
+      <c r="E6" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="40" t="s">
         <v>200</v>
       </c>
       <c r="G6" s="34" t="n">
@@ -5535,88 +5579,88 @@
       <c r="I6" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="K6" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L6" s="47" t="s">
+      <c r="K6" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M6" s="47"/>
+      <c r="M6" s="41"/>
       <c r="N6" s="39"/>
       <c r="O6" s="39"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="45"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="40" t="n">
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="42"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="40" t="n">
+      <c r="C7" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21" t="s">
+      <c r="D7" s="44"/>
+      <c r="E7" s="44" t="s">
         <v>203</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="40" t="n">
+      <c r="G7" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="48" t="n">
+      <c r="H7" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="8" t="s">
+      <c r="I7" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="K7" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L7" s="43" t="s">
+      <c r="K7" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M7" s="43"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="45"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="34" t="n">
+      <c r="M7" s="47"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="42"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="43" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="34" t="n">
+      <c r="C8" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46" t="s">
+      <c r="D8" s="44"/>
+      <c r="E8" s="44" t="s">
         <v>205</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="34" t="n">
+      <c r="G8" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="34" t="n">
+      <c r="H8" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="51" t="n">
+      <c r="I8" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="18" t="s">
@@ -5629,20 +5673,20 @@
         <v>202</v>
       </c>
       <c r="M8" s="47"/>
-      <c r="N8" s="52"/>
-      <c r="O8" s="52"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
-      <c r="R8" s="53"/>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="40" t="n">
+      <c r="R8" s="50"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="34" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="40"/>
+      <c r="C9" s="34"/>
       <c r="D9" s="21"/>
       <c r="E9" s="21" t="s">
         <v>207</v>
@@ -5650,105 +5694,105 @@
       <c r="F9" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="G9" s="40" t="n">
+      <c r="G9" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="40" t="n">
+      <c r="H9" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="49"/>
+      <c r="I9" s="51"/>
       <c r="J9" s="12"/>
-      <c r="K9" s="43" t="s">
+      <c r="K9" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="52"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="45"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="40" t="n">
+      <c r="R9" s="42"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="34" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="24"/>
-      <c r="C10" s="40" t="n">
+      <c r="C10" s="34" t="n">
         <v>5</v>
       </c>
       <c r="D10" s="24"/>
       <c r="E10" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="F10" s="54" t="s">
+      <c r="F10" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="40" t="n">
+      <c r="G10" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="H10" s="48" t="n">
+      <c r="H10" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="40" t="n">
+      <c r="I10" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="K10" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L10" s="43" t="s">
+      <c r="K10" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L10" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M10" s="43"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="50"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="52"/>
+      <c r="O10" s="52"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
-      <c r="R10" s="53"/>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="40" t="n">
+      <c r="R10" s="50"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="34" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="24"/>
-      <c r="C11" s="40" t="n">
+      <c r="C11" s="34" t="n">
         <v>6</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="F11" s="54" t="s">
+      <c r="F11" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="40" t="n">
+      <c r="G11" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="H11" s="48" t="n">
+      <c r="H11" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="40" t="n">
+      <c r="I11" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="8"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="50"/>
-      <c r="N11" s="50"/>
-      <c r="O11" s="50"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="52"/>
+      <c r="O11" s="52"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
-      <c r="R11" s="45"/>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="40" t="n">
+      <c r="R11" s="42"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="34" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="24"/>
-      <c r="C12" s="40" t="n">
+      <c r="C12" s="34" t="n">
         <v>7</v>
       </c>
       <c r="D12" s="24"/>
@@ -5758,37 +5802,37 @@
       <c r="F12" s="55" t="s">
         <v>133</v>
       </c>
-      <c r="G12" s="40" t="n">
+      <c r="G12" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="H12" s="40" t="n">
+      <c r="H12" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="I12" s="40" t="n">
+      <c r="I12" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="K12" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L12" s="43" t="s">
+      <c r="K12" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M12" s="43"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="52"/>
+      <c r="O12" s="52"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
-      <c r="R12" s="45"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="40" t="n">
+      <c r="R12" s="42"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="34" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="24"/>
-      <c r="C13" s="40" t="n">
+      <c r="C13" s="34" t="n">
         <v>8</v>
       </c>
       <c r="D13" s="24"/>
@@ -5798,37 +5842,37 @@
       <c r="F13" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="G13" s="40" t="n">
+      <c r="G13" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="H13" s="40" t="n">
+      <c r="H13" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="40" t="n">
+      <c r="I13" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="K13" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L13" s="43" t="s">
+      <c r="K13" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M13" s="43"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="50"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="52"/>
+      <c r="O13" s="52"/>
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
-      <c r="R13" s="45"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="40" t="n">
+      <c r="R13" s="42"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="34" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="24"/>
-      <c r="C14" s="40" t="n">
+      <c r="C14" s="34" t="n">
         <v>9</v>
       </c>
       <c r="D14" s="24"/>
@@ -5838,39 +5882,39 @@
       <c r="F14" s="55" t="s">
         <v>216</v>
       </c>
-      <c r="G14" s="40" t="n">
+      <c r="G14" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="H14" s="40" t="n">
+      <c r="H14" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="40" t="n">
+      <c r="I14" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="K14" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L14" s="43" t="s">
+      <c r="K14" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M14" s="43"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="50"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="52"/>
+      <c r="O14" s="52"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
-      <c r="R14" s="45"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="40" t="n">
+      <c r="R14" s="42"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="34" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="C15" s="40" t="n">
+      <c r="C15" s="34" t="n">
         <v>10</v>
       </c>
       <c r="D15" s="24"/>
@@ -5880,165 +5924,161 @@
       <c r="F15" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="40" t="n">
+      <c r="G15" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="40" t="n">
+      <c r="H15" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="40" t="n">
+      <c r="I15" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="K15" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L15" s="43" t="s">
+      <c r="K15" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L15" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M15" s="43"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="50"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="52"/>
+      <c r="O15" s="52"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
-      <c r="R15" s="45"/>
+      <c r="R15" s="42"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="40" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="C16" s="40" t="n">
-        <v>11</v>
+      <c r="A16" s="34" t="n">
+        <v>16</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="C16" s="34" t="n">
+        <v>12</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="F16" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="F16" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="G16" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="H16" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="K16" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L16" s="43" t="s">
+      <c r="K16" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L16" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M16" s="43"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="50"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="52"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
-      <c r="R16" s="45"/>
+      <c r="R16" s="42"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="24" t="n">
-        <v>15</v>
-      </c>
-      <c r="C17" s="40" t="n">
-        <v>12</v>
+      <c r="A17" s="34" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" s="24"/>
+      <c r="C17" s="34" t="n">
+        <v>13</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="F17" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="G17" s="40" t="n">
-        <v>8</v>
-      </c>
-      <c r="H17" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="K17" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L17" s="43" t="s">
+      <c r="K17" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L17" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M17" s="43"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="50"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="52"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
-      <c r="R17" s="45"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="40" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="24" t="n">
+      <c r="R17" s="42"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="C18" s="40" t="n">
-        <v>13</v>
+      <c r="B18" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="C18" s="34" t="n">
+        <v>11</v>
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="F18" s="56" t="s">
-        <v>98</v>
-      </c>
-      <c r="G18" s="40" t="n">
+      <c r="F18" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="G18" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="H18" s="40" t="n">
+      <c r="H18" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="40" t="n">
+      <c r="I18" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="K18" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L18" s="43" t="s">
+      <c r="K18" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L18" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M18" s="43"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="50"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="52"/>
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
-      <c r="R18" s="45"/>
+      <c r="R18" s="42"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="34" t="n">
+      <c r="A19" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="57" t="n">
+      <c r="B19" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="C19" s="34" t="n">
+      <c r="C19" s="43" t="n">
         <v>14</v>
       </c>
       <c r="D19" s="23"/>
@@ -6048,13 +6088,13 @@
       <c r="F19" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="G19" s="34" t="n">
+      <c r="G19" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="34" t="n">
+      <c r="H19" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="34" t="n">
+      <c r="I19" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="5" t="s">
@@ -6064,35 +6104,35 @@
       <c r="L19" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M19" s="52"/>
-      <c r="N19" s="52"/>
-      <c r="O19" s="52"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
-      <c r="R19" s="45"/>
+      <c r="R19" s="42"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="34" t="n">
+      <c r="A20" s="43" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="23"/>
-      <c r="C20" s="34" t="n">
+      <c r="C20" s="43" t="n">
         <v>15</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="F20" s="58" t="s">
+      <c r="F20" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="G20" s="34" t="n">
+      <c r="G20" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="H20" s="34" t="n">
+      <c r="H20" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="I20" s="34" t="n">
+      <c r="I20" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J20" s="5" t="s">
@@ -6109,16 +6149,16 @@
       <c r="O20" s="47"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
-      <c r="R20" s="53"/>
+      <c r="R20" s="50"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="34" t="n">
+      <c r="A21" s="43" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="34" t="n">
+      <c r="C21" s="43" t="n">
         <v>16</v>
       </c>
       <c r="D21" s="23" t="n">
@@ -6127,50 +6167,50 @@
       <c r="E21" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="F21" s="58" t="s">
+      <c r="F21" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="34" t="n">
+      <c r="G21" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="H21" s="34" t="n">
+      <c r="H21" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="I21" s="34" t="n">
+      <c r="I21" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="20"/>
       <c r="K21" s="47"/>
-      <c r="L21" s="52"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="52"/>
-      <c r="O21" s="52"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="48"/>
+      <c r="O21" s="48"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
-      <c r="R21" s="45"/>
+      <c r="R21" s="42"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34" t="n">
+      <c r="A22" s="43" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="23"/>
-      <c r="C22" s="34" t="n">
+      <c r="C22" s="43" t="n">
         <v>17</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="F22" s="59" t="s">
+      <c r="F22" s="57" t="s">
         <v>235</v>
       </c>
-      <c r="G22" s="34" t="n">
+      <c r="G22" s="43" t="n">
         <v>20</v>
       </c>
-      <c r="H22" s="34" t="n">
+      <c r="H22" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="I22" s="34" t="n">
+      <c r="I22" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="5" t="s">
@@ -6187,30 +6227,30 @@
       <c r="O22" s="47"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
-      <c r="R22" s="45"/>
+      <c r="R22" s="42"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="34" t="n">
+      <c r="A23" s="43" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="23"/>
-      <c r="C23" s="34" t="n">
+      <c r="C23" s="43" t="n">
         <v>18</v>
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="F23" s="59" t="s">
+      <c r="F23" s="57" t="s">
         <v>238</v>
       </c>
-      <c r="G23" s="34" t="n">
+      <c r="G23" s="43" t="n">
         <v>20</v>
       </c>
-      <c r="H23" s="34" t="n">
+      <c r="H23" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="I23" s="34" t="n">
+      <c r="I23" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J23" s="5" t="s">
@@ -6229,372 +6269,355 @@
       <c r="O23" s="47"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
-      <c r="R23" s="53"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="40" t="n">
+      <c r="R23" s="50"/>
+    </row>
+    <row r="24" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="58" t="n">
+        <v>39</v>
+      </c>
+      <c r="B24" s="59" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" s="58"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59" t="s">
+        <v>240</v>
+      </c>
+      <c r="F24" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="G24" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="58" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="58"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="61"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="61"/>
+      <c r="O24" s="61"/>
+      <c r="P24" s="60"/>
+      <c r="Q24" s="60"/>
+      <c r="R24" s="62"/>
+    </row>
+    <row r="25" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="58" t="n">
+        <v>40</v>
+      </c>
+      <c r="B25" s="59"/>
+      <c r="C25" s="58" t="n">
+        <v>42</v>
+      </c>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="F25" s="64" t="s">
+        <v>127</v>
+      </c>
+      <c r="G25" s="58" t="n">
+        <v>39</v>
+      </c>
+      <c r="H25" s="58" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="60"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="M25" s="61"/>
+      <c r="N25" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="O25" s="61"/>
+      <c r="P25" s="60"/>
+      <c r="Q25" s="60"/>
+      <c r="R25" s="66"/>
+    </row>
+    <row r="26" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="58" t="n">
+        <v>41</v>
+      </c>
+      <c r="B26" s="59"/>
+      <c r="C26" s="58" t="n">
+        <v>43</v>
+      </c>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="F26" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" s="58" t="n">
+        <v>39</v>
+      </c>
+      <c r="H26" s="58" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="60"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="O26" s="61"/>
+      <c r="P26" s="60"/>
+      <c r="Q26" s="60"/>
+      <c r="R26" s="66"/>
+    </row>
+    <row r="27" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="58" t="n">
+        <v>42</v>
+      </c>
+      <c r="B27" s="59"/>
+      <c r="C27" s="58" t="n">
+        <v>44</v>
+      </c>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59" t="s">
+        <v>243</v>
+      </c>
+      <c r="F27" s="64" t="s">
+        <v>129</v>
+      </c>
+      <c r="G27" s="58" t="n">
+        <v>39</v>
+      </c>
+      <c r="H27" s="58" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="60"/>
+      <c r="K27" s="61"/>
+      <c r="L27" s="61"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="O27" s="61"/>
+      <c r="P27" s="60"/>
+      <c r="Q27" s="60"/>
+      <c r="R27" s="66"/>
+    </row>
+    <row r="28" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="34" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="C24" s="40" t="n">
+      <c r="B28" s="24" t="n">
+        <v>8.39</v>
+      </c>
+      <c r="C28" s="34" t="n">
         <v>19</v>
-      </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="I24" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="8"/>
-      <c r="K24" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L24" s="50"/>
-      <c r="M24" s="50"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="50"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="45"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="40"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="F25" s="24"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="K25" s="50"/>
-      <c r="L25" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43" t="s">
-        <v>232</v>
-      </c>
-      <c r="O25" s="43"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="45"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="40"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="40" t="n">
-        <v>21</v>
-      </c>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="F26" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="G26" s="40" t="n">
-        <v>23</v>
-      </c>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="K26" s="43" t="s">
-        <v>232</v>
-      </c>
-      <c r="L26" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="M26" s="43"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="50"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="45"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="40" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="40" t="n">
-        <v>22</v>
-      </c>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="F27" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="G27" s="40" t="n">
-        <v>23</v>
-      </c>
-      <c r="H27" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="K27" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L27" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="M27" s="43"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="45"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="40" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="40" t="n">
-        <v>23</v>
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="F28" s="56" t="s">
-        <v>111</v>
-      </c>
-      <c r="G28" s="40" t="n">
-        <v>23</v>
-      </c>
-      <c r="H28" s="40" t="n">
+        <v>244</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="G28" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="I28" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="K28" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L28" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="M28" s="43"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="50"/>
+      <c r="I28" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="8"/>
+      <c r="K28" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L28" s="52"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="52"/>
+      <c r="O28" s="52"/>
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
-      <c r="R28" s="45"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="40" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" s="24" t="n">
-        <v>25</v>
-      </c>
-      <c r="C29" s="40" t="n">
-        <v>24</v>
+      <c r="R28" s="62"/>
+    </row>
+    <row r="29" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="34"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="34" t="n">
+        <v>20</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="F29" s="60" t="s">
-        <v>112</v>
-      </c>
-      <c r="G29" s="49" t="n">
-        <v>23</v>
-      </c>
-      <c r="H29" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="I29" s="40" t="n">
+        <v>244</v>
+      </c>
+      <c r="F29" s="24"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="K29" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L29" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="K29" s="52"/>
+      <c r="L29" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M29" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="N29" s="50"/>
-      <c r="O29" s="50"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="O29" s="41"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="8"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="40"/>
+      <c r="R29" s="62"/>
+    </row>
+    <row r="30" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="34"/>
       <c r="B30" s="24"/>
-      <c r="C30" s="40" t="n">
-        <v>25</v>
+      <c r="C30" s="34" t="n">
+        <v>21</v>
       </c>
       <c r="D30" s="24"/>
       <c r="E30" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="F30" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="G30" s="40" t="n">
+        <v>244</v>
+      </c>
+      <c r="F30" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" s="34" t="n">
         <v>23</v>
       </c>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="8"/>
-      <c r="K30" s="43" t="s">
+      <c r="H30" s="34"/>
+      <c r="I30" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="K30" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="L30" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="L30" s="50"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="50"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="52"/>
+      <c r="O30" s="52"/>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
-      <c r="R30" s="45"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="40" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C31" s="40" t="n">
-        <v>26</v>
+      <c r="R30" s="62"/>
+    </row>
+    <row r="31" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="24"/>
+      <c r="C31" s="34" t="n">
+        <v>22</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="F31" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="G31" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" s="40" t="n">
+        <v>247</v>
+      </c>
+      <c r="F31" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" s="34" t="n">
+        <v>23</v>
+      </c>
+      <c r="H31" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="I31" s="40" t="n">
+      <c r="I31" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="K31" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L31" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="K31" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L31" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M31" s="50"/>
-      <c r="N31" s="50"/>
-      <c r="O31" s="50"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="52"/>
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
-      <c r="R31" s="45"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="40" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="24" t="n">
-        <v>26</v>
-      </c>
-      <c r="C32" s="40" t="n">
-        <v>27</v>
+      <c r="R31" s="62"/>
+    </row>
+    <row r="32" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="34" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="24"/>
+      <c r="C32" s="34" t="n">
+        <v>23</v>
       </c>
       <c r="D32" s="24"/>
       <c r="E32" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="F32" s="56" t="s">
-        <v>73</v>
-      </c>
-      <c r="G32" s="40" t="n">
+        <v>249</v>
+      </c>
+      <c r="F32" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="G32" s="34" t="n">
         <v>23</v>
       </c>
-      <c r="H32" s="40" t="n">
+      <c r="H32" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="I32" s="40" t="n">
+      <c r="I32" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="K32" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L32" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="K32" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L32" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M32" s="50"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="50"/>
+      <c r="M32" s="41"/>
+      <c r="N32" s="52"/>
+      <c r="O32" s="52"/>
       <c r="P32" s="8"/>
       <c r="Q32" s="8"/>
-      <c r="R32" s="45"/>
-    </row>
-    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R32" s="62"/>
+    </row>
+    <row r="33" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="34" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="C33" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F33" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="G33" s="51" t="n">
         <v>23</v>
-      </c>
-      <c r="C33" s="34" t="n">
-        <v>28</v>
-      </c>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="F33" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="G33" s="51" t="n">
-        <v>2</v>
       </c>
       <c r="H33" s="51" t="n">
         <v>6</v>
@@ -6602,709 +6625,726 @@
       <c r="I33" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="K33" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L33" s="47" t="s">
+      <c r="J33" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="K33" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L33" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M33" s="52"/>
+      <c r="M33" s="41" t="s">
+        <v>202</v>
+      </c>
       <c r="N33" s="52"/>
       <c r="O33" s="52"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="45"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="34" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="23"/>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="8"/>
+    </row>
+    <row r="34" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="34"/>
+      <c r="B34" s="24"/>
       <c r="C34" s="34" t="n">
-        <v>29</v>
-      </c>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="F34" s="61" t="s">
-        <v>117</v>
-      </c>
-      <c r="G34" s="51" t="n">
-        <v>29</v>
-      </c>
-      <c r="H34" s="51" t="n">
-        <v>6</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F34" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="G34" s="34" t="n">
+        <v>23</v>
+      </c>
+      <c r="H34" s="34"/>
       <c r="I34" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="K34" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L34" s="47" t="s">
+      <c r="J34" s="8"/>
+      <c r="K34" s="41" t="s">
         <v>202</v>
       </c>
+      <c r="L34" s="52"/>
       <c r="M34" s="52"/>
       <c r="N34" s="52"/>
       <c r="O34" s="52"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-      <c r="R34" s="53"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="40" t="n">
-        <v>31</v>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="62"/>
+    </row>
+    <row r="35" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="34" t="n">
+        <v>27</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="C35" s="40"/>
+        <v>253</v>
+      </c>
+      <c r="C35" s="34" t="n">
+        <v>26</v>
+      </c>
       <c r="D35" s="24"/>
-      <c r="E35" s="62" t="s">
-        <v>259</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G35" s="49" t="n">
+      <c r="E35" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="F35" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="G35" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="I35" s="40"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="50"/>
+      <c r="H35" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="K35" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L35" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+      <c r="O35" s="52"/>
       <c r="P35" s="8"/>
       <c r="Q35" s="8"/>
-      <c r="R35" s="45"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="40" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="40" t="n">
-        <v>30</v>
+      <c r="R35" s="62"/>
+    </row>
+    <row r="36" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="34" t="n">
+        <v>28</v>
+      </c>
+      <c r="B36" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="C36" s="34" t="n">
+        <v>27</v>
       </c>
       <c r="D36" s="24"/>
       <c r="E36" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="F36" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="G36" s="40" t="n">
-        <v>31</v>
-      </c>
-      <c r="H36" s="40" t="n">
+        <v>256</v>
+      </c>
+      <c r="F36" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="G36" s="34" t="n">
+        <v>23</v>
+      </c>
+      <c r="H36" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="I36" s="40" t="n">
+      <c r="I36" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="K36" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L36" s="43" t="s">
+        <v>257</v>
+      </c>
+      <c r="K36" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L36" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="50"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="52"/>
+      <c r="O36" s="52"/>
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
-      <c r="R36" s="45"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="40"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="40" t="n">
+      <c r="R36" s="62"/>
+    </row>
+    <row r="37" s="63" customFormat="true" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="43" t="n">
+        <v>29</v>
+      </c>
+      <c r="B37" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="C37" s="43" t="n">
+        <v>28</v>
+      </c>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="F37" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="G37" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="I37" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="K37" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L37" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="62"/>
+    </row>
+    <row r="38" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B38" s="23"/>
+      <c r="C38" s="43" t="n">
+        <v>29</v>
+      </c>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="F38" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="G38" s="46" t="n">
+        <v>29</v>
+      </c>
+      <c r="H38" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="I38" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="K38" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L38" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M38" s="48"/>
+      <c r="N38" s="48"/>
+      <c r="O38" s="48"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="66"/>
+    </row>
+    <row r="39" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="58" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="59" t="n">
+        <v>23</v>
+      </c>
+      <c r="C39" s="58" t="n">
+        <v>33</v>
+      </c>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59" t="s">
+        <v>262</v>
+      </c>
+      <c r="F39" s="59" t="s">
+        <v>121</v>
+      </c>
+      <c r="G39" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="58" t="n">
+        <v>6</v>
+      </c>
+      <c r="I39" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="60" t="s">
+        <v>263</v>
+      </c>
+      <c r="K39" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="L39" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="M39" s="61"/>
+      <c r="N39" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="O39" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="P39" s="60"/>
+      <c r="Q39" s="60"/>
+      <c r="R39" s="62"/>
+    </row>
+    <row r="40" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="58"/>
+      <c r="B40" s="59"/>
+      <c r="C40" s="58" t="n">
+        <v>34</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59" t="s">
+        <v>262</v>
+      </c>
+      <c r="F40" s="59"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="58"/>
+      <c r="I40" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="K40" s="61"/>
+      <c r="L40" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="M40" s="61"/>
+      <c r="N40" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="O40" s="65"/>
+      <c r="P40" s="60"/>
+      <c r="Q40" s="60"/>
+      <c r="R40" s="62"/>
+    </row>
+    <row r="41" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="58"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="58" t="n">
+        <v>35</v>
+      </c>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59" t="s">
+        <v>262</v>
+      </c>
+      <c r="F41" s="64" t="s">
+        <v>109</v>
+      </c>
+      <c r="G41" s="58" t="n">
+        <v>34</v>
+      </c>
+      <c r="H41" s="58"/>
+      <c r="I41" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="60" t="s">
+        <v>265</v>
+      </c>
+      <c r="K41" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="L41" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="M41" s="61"/>
+      <c r="N41" s="61"/>
+      <c r="O41" s="61"/>
+      <c r="P41" s="60"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="66"/>
+    </row>
+    <row r="42" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="34" t="n">
         <v>31</v>
       </c>
-      <c r="D37" s="24"/>
-      <c r="E37" s="62" t="s">
-        <v>259</v>
-      </c>
-      <c r="F37" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="G37" s="40" t="n">
-        <v>31</v>
-      </c>
-      <c r="H37" s="40"/>
-      <c r="I37" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K37" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L37" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="M37" s="50"/>
-      <c r="N37" s="50"/>
-      <c r="O37" s="50"/>
-      <c r="P37" s="8"/>
-      <c r="Q37" s="8"/>
-      <c r="R37" s="53"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="40" t="n">
-        <v>33</v>
-      </c>
-      <c r="B38" s="24" t="n">
-        <v>32</v>
-      </c>
-      <c r="C38" s="40" t="n">
-        <v>32</v>
-      </c>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24" t="s">
-        <v>263</v>
-      </c>
-      <c r="F38" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="G38" s="40" t="n">
-        <v>31</v>
-      </c>
-      <c r="H38" s="40" t="n">
+      <c r="B42" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="C42" s="34"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="69" t="s">
+        <v>267</v>
+      </c>
+      <c r="F42" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G42" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="I38" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="8"/>
-      <c r="K38" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L38" s="50"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="50"/>
-      <c r="O38" s="50"/>
-      <c r="P38" s="8"/>
-      <c r="Q38" s="8"/>
-      <c r="R38" s="45"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="34" t="n">
-        <v>34</v>
-      </c>
-      <c r="B39" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="C39" s="34" t="n">
-        <v>33</v>
-      </c>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="G39" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="I39" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="K39" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L39" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M39" s="52"/>
-      <c r="N39" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="O39" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="45"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="34"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="34" t="n">
-        <v>34</v>
-      </c>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="F40" s="23"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="K40" s="52"/>
-      <c r="L40" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M40" s="52"/>
-      <c r="N40" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="O40" s="47"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="45"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="34"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="34" t="n">
-        <v>35</v>
-      </c>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="F41" s="58" t="s">
-        <v>109</v>
-      </c>
-      <c r="G41" s="34" t="n">
-        <v>34</v>
-      </c>
-      <c r="H41" s="34"/>
-      <c r="I41" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="K41" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="L41" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M41" s="52"/>
-      <c r="N41" s="52"/>
-      <c r="O41" s="52"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="53"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="40" t="n">
-        <v>35</v>
-      </c>
-      <c r="B42" s="24" t="n">
-        <v>23</v>
-      </c>
-      <c r="C42" s="40"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="F42" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="G42" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="I42" s="40"/>
+      <c r="I42" s="34"/>
       <c r="J42" s="8"/>
-      <c r="K42" s="50"/>
-      <c r="L42" s="50"/>
-      <c r="M42" s="50"/>
-      <c r="N42" s="50"/>
-      <c r="O42" s="50"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="52"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="52"/>
+      <c r="O42" s="52"/>
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
-      <c r="R42" s="45"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="40" t="n">
-        <v>36</v>
+      <c r="R42" s="62"/>
+    </row>
+    <row r="43" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="34" t="n">
+        <v>32</v>
       </c>
       <c r="B43" s="24"/>
-      <c r="C43" s="40" t="n">
-        <v>36</v>
+      <c r="C43" s="34" t="n">
+        <v>30</v>
       </c>
       <c r="D43" s="24"/>
       <c r="E43" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="F43" s="56" t="s">
-        <v>123</v>
-      </c>
-      <c r="G43" s="40" t="n">
-        <v>35</v>
-      </c>
-      <c r="H43" s="40" t="n">
+        <v>268</v>
+      </c>
+      <c r="F43" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="G43" s="34" t="n">
+        <v>31</v>
+      </c>
+      <c r="H43" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="I43" s="40" t="n">
+      <c r="I43" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="K43" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L43" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="K43" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L43" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M43" s="50"/>
-      <c r="N43" s="43" t="s">
-        <v>232</v>
-      </c>
-      <c r="O43" s="50"/>
+      <c r="M43" s="52"/>
+      <c r="N43" s="52"/>
+      <c r="O43" s="52"/>
       <c r="P43" s="8"/>
       <c r="Q43" s="8"/>
-      <c r="R43" s="53"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="40" t="n">
-        <v>37</v>
-      </c>
+      <c r="R43" s="62"/>
+    </row>
+    <row r="44" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="34"/>
       <c r="B44" s="24"/>
-      <c r="C44" s="40" t="n">
-        <v>37</v>
+      <c r="C44" s="34" t="n">
+        <v>31</v>
       </c>
       <c r="D44" s="24"/>
-      <c r="E44" s="24" t="s">
+      <c r="E44" s="69" t="s">
+        <v>267</v>
+      </c>
+      <c r="F44" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="G44" s="34" t="n">
+        <v>31</v>
+      </c>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="F44" s="56" t="s">
-        <v>124</v>
-      </c>
-      <c r="G44" s="40" t="n">
-        <v>35</v>
-      </c>
-      <c r="H44" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="I44" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="8"/>
-      <c r="K44" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L44" s="50"/>
-      <c r="M44" s="50"/>
-      <c r="N44" s="50"/>
-      <c r="O44" s="50"/>
-      <c r="P44" s="8" t="s">
-        <v>272</v>
-      </c>
+      <c r="K44" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L44" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="M44" s="52"/>
+      <c r="N44" s="52"/>
+      <c r="O44" s="52"/>
+      <c r="P44" s="8"/>
       <c r="Q44" s="8"/>
-      <c r="R44" s="53"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="40"/>
-      <c r="B45" s="24"/>
-      <c r="C45" s="40" t="n">
-        <v>38</v>
+      <c r="R44" s="66"/>
+    </row>
+    <row r="45" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B45" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="C45" s="34" t="n">
+        <v>32</v>
       </c>
       <c r="D45" s="24"/>
       <c r="E45" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="F45" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="G45" s="34" t="n">
+        <v>31</v>
+      </c>
+      <c r="H45" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I45" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="8"/>
+      <c r="K45" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="52"/>
+      <c r="O45" s="52"/>
+      <c r="P45" s="8"/>
+      <c r="Q45" s="8"/>
+      <c r="R45" s="62"/>
+    </row>
+    <row r="46" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="43" t="n">
+        <v>35</v>
+      </c>
+      <c r="B46" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="C46" s="43"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="F46" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="G46" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="I46" s="43"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="48"/>
+      <c r="L46" s="48"/>
+      <c r="M46" s="48"/>
+      <c r="N46" s="48"/>
+      <c r="O46" s="48"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="62"/>
+    </row>
+    <row r="47" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="43" t="n">
+        <v>36</v>
+      </c>
+      <c r="B47" s="23"/>
+      <c r="C47" s="43" t="n">
+        <v>36</v>
+      </c>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="F45" s="56"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="8"/>
-      <c r="K45" s="43" t="s">
+      <c r="F47" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="G47" s="43" t="n">
+        <v>35</v>
+      </c>
+      <c r="H47" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="I47" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="K47" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L47" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M47" s="48"/>
+      <c r="N47" s="47" t="s">
         <v>232</v>
       </c>
-      <c r="L45" s="50"/>
-      <c r="M45" s="50"/>
-      <c r="N45" s="50"/>
-      <c r="O45" s="50"/>
-      <c r="P45" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q45" s="8"/>
-      <c r="R45" s="53"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="40"/>
-      <c r="B46" s="24"/>
-      <c r="C46" s="40" t="n">
-        <v>39</v>
-      </c>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24" t="s">
+      <c r="O47" s="48"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="66"/>
+    </row>
+    <row r="48" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="43" t="n">
+        <v>37</v>
+      </c>
+      <c r="B48" s="23"/>
+      <c r="C48" s="43" t="n">
+        <v>37</v>
+      </c>
+      <c r="D48" s="23"/>
+      <c r="E48" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="F46" s="56"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="40"/>
-      <c r="I46" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="8"/>
-      <c r="K46" s="43" t="s">
-        <v>232</v>
-      </c>
-      <c r="L46" s="50"/>
-      <c r="M46" s="50"/>
-      <c r="N46" s="50"/>
-      <c r="O46" s="50"/>
-      <c r="P46" s="8" t="s">
+      <c r="F48" s="49" t="s">
+        <v>124</v>
+      </c>
+      <c r="G48" s="43" t="n">
+        <v>35</v>
+      </c>
+      <c r="H48" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="I48" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="5"/>
+      <c r="K48" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L48" s="48"/>
+      <c r="M48" s="48"/>
+      <c r="N48" s="48"/>
+      <c r="O48" s="48"/>
+      <c r="P48" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="Q46" s="8"/>
-      <c r="R46" s="53"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="40"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="40" t="n">
-        <v>40</v>
-      </c>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="F47" s="56"/>
-      <c r="G47" s="40"/>
-      <c r="H47" s="40"/>
-      <c r="I47" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="8"/>
-      <c r="K47" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="L47" s="50"/>
-      <c r="M47" s="50"/>
-      <c r="N47" s="50"/>
-      <c r="O47" s="50"/>
-      <c r="P47" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q47" s="8"/>
-      <c r="R47" s="45"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="40" t="n">
+      <c r="Q48" s="5"/>
+      <c r="R48" s="66"/>
+    </row>
+    <row r="49" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="43"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="43" t="n">
         <v>38</v>
       </c>
-      <c r="B48" s="24"/>
-      <c r="C48" s="40" t="n">
-        <v>41</v>
-      </c>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24" t="s">
-        <v>277</v>
-      </c>
-      <c r="F48" s="56" t="s">
-        <v>125</v>
-      </c>
-      <c r="G48" s="40" t="n">
-        <v>35</v>
-      </c>
-      <c r="H48" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="I48" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="K48" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L48" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="M48" s="50"/>
-      <c r="N48" s="43" t="s">
-        <v>232</v>
-      </c>
-      <c r="O48" s="50"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="8"/>
-      <c r="R48" s="53"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="34" t="n">
-        <v>39</v>
-      </c>
-      <c r="B49" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="C49" s="34"/>
       <c r="D49" s="23"/>
       <c r="E49" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="F49" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="G49" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="H49" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="I49" s="34"/>
+        <v>276</v>
+      </c>
+      <c r="F49" s="49"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43" t="n">
+        <v>1</v>
+      </c>
       <c r="J49" s="5"/>
-      <c r="K49" s="52"/>
-      <c r="L49" s="52"/>
-      <c r="M49" s="52"/>
-      <c r="N49" s="52"/>
-      <c r="O49" s="52"/>
-      <c r="P49" s="5"/>
+      <c r="K49" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="L49" s="48"/>
+      <c r="M49" s="48"/>
+      <c r="N49" s="48"/>
+      <c r="O49" s="48"/>
+      <c r="P49" s="5" t="s">
+        <v>277</v>
+      </c>
       <c r="Q49" s="5"/>
-      <c r="R49" s="45"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="34" t="n">
-        <v>40</v>
-      </c>
+      <c r="R49" s="66"/>
+    </row>
+    <row r="50" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="43"/>
       <c r="B50" s="23"/>
-      <c r="C50" s="34" t="n">
-        <v>42</v>
+      <c r="C50" s="43" t="n">
+        <v>39</v>
       </c>
       <c r="D50" s="23"/>
       <c r="E50" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="F50" s="58" t="s">
-        <v>127</v>
-      </c>
-      <c r="G50" s="34" t="n">
-        <v>39</v>
-      </c>
-      <c r="H50" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="I50" s="34" t="n">
+        <v>276</v>
+      </c>
+      <c r="F50" s="49"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J50" s="5"/>
-      <c r="K50" s="52"/>
-      <c r="L50" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M50" s="52"/>
-      <c r="N50" s="47" t="s">
+      <c r="K50" s="47" t="s">
         <v>232</v>
       </c>
-      <c r="O50" s="52"/>
-      <c r="P50" s="5"/>
+      <c r="L50" s="48"/>
+      <c r="M50" s="48"/>
+      <c r="N50" s="48"/>
+      <c r="O50" s="48"/>
+      <c r="P50" s="5" t="s">
+        <v>278</v>
+      </c>
       <c r="Q50" s="5"/>
-      <c r="R50" s="53"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="34" t="n">
-        <v>41</v>
-      </c>
+      <c r="R50" s="66"/>
+    </row>
+    <row r="51" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="43"/>
       <c r="B51" s="23"/>
-      <c r="C51" s="34" t="n">
-        <v>43</v>
+      <c r="C51" s="43" t="n">
+        <v>40</v>
       </c>
       <c r="D51" s="23"/>
       <c r="E51" s="23" t="s">
-        <v>282</v>
-      </c>
-      <c r="F51" s="58" t="s">
-        <v>128</v>
-      </c>
-      <c r="G51" s="34" t="n">
-        <v>39</v>
-      </c>
-      <c r="H51" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="I51" s="34" t="n">
+        <v>276</v>
+      </c>
+      <c r="F51" s="49"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="5"/>
-      <c r="K51" s="52"/>
-      <c r="L51" s="52"/>
-      <c r="M51" s="52"/>
-      <c r="N51" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="O51" s="52"/>
-      <c r="P51" s="5"/>
+      <c r="K51" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="L51" s="48"/>
+      <c r="M51" s="48"/>
+      <c r="N51" s="48"/>
+      <c r="O51" s="48"/>
+      <c r="P51" s="5" t="s">
+        <v>279</v>
+      </c>
       <c r="Q51" s="5"/>
-      <c r="R51" s="53"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="34" t="n">
-        <v>42</v>
+      <c r="R51" s="62"/>
+    </row>
+    <row r="52" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="43" t="n">
+        <v>38</v>
       </c>
       <c r="B52" s="23"/>
-      <c r="C52" s="34" t="n">
-        <v>44</v>
+      <c r="C52" s="43" t="n">
+        <v>41</v>
       </c>
       <c r="D52" s="23"/>
       <c r="E52" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="F52" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="G52" s="34" t="n">
-        <v>39</v>
-      </c>
-      <c r="H52" s="34" t="n">
+        <v>280</v>
+      </c>
+      <c r="F52" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="G52" s="43" t="n">
+        <v>35</v>
+      </c>
+      <c r="H52" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="I52" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="5"/>
-      <c r="K52" s="52"/>
-      <c r="L52" s="52"/>
-      <c r="M52" s="52"/>
+      <c r="I52" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="K52" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L52" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="M52" s="48"/>
       <c r="N52" s="47" t="s">
         <v>232</v>
       </c>
-      <c r="O52" s="52"/>
+      <c r="O52" s="48"/>
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
-      <c r="R52" s="53"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R52" s="66"/>
+    </row>
+    <row r="53" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="28"/>
       <c r="B53" s="29"/>
       <c r="C53" s="28"/>
@@ -7314,12 +7354,15 @@
       <c r="G53" s="28"/>
       <c r="H53" s="28"/>
       <c r="I53" s="28"/>
+      <c r="J53" s="0"/>
       <c r="K53" s="25"/>
       <c r="L53" s="25"/>
       <c r="M53" s="25"/>
       <c r="N53" s="25"/>
       <c r="O53" s="25"/>
-      <c r="R53" s="53"/>
+      <c r="P53" s="0"/>
+      <c r="Q53" s="0"/>
+      <c r="R53" s="66"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="28" t="n">
@@ -7334,7 +7377,7 @@
         <v>43</v>
       </c>
       <c r="F54" s="31" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G54" s="30" t="n">
         <v>1</v>
@@ -7348,480 +7391,480 @@
       <c r="M54" s="25"/>
       <c r="N54" s="25"/>
       <c r="O54" s="25"/>
-      <c r="R54" s="53"/>
+      <c r="R54" s="50"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="40" t="n">
+      <c r="A55" s="34" t="n">
         <v>44</v>
       </c>
       <c r="B55" s="24"/>
-      <c r="C55" s="40" t="n">
+      <c r="C55" s="34" t="n">
         <v>45</v>
       </c>
       <c r="D55" s="24"/>
       <c r="E55" s="24" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F55" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="G55" s="49" t="n">
+      <c r="G55" s="51" t="n">
         <v>43</v>
       </c>
-      <c r="H55" s="49" t="n">
+      <c r="H55" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="I55" s="40" t="n">
+      <c r="I55" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J55" s="8"/>
-      <c r="K55" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L55" s="50"/>
-      <c r="M55" s="50"/>
-      <c r="N55" s="50"/>
-      <c r="O55" s="50"/>
+      <c r="K55" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L55" s="52"/>
+      <c r="M55" s="52"/>
+      <c r="N55" s="52"/>
+      <c r="O55" s="52"/>
       <c r="P55" s="8"/>
       <c r="Q55" s="8"/>
-      <c r="R55" s="53"/>
+      <c r="R55" s="50"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="34" t="n">
+      <c r="A56" s="43" t="n">
         <v>45</v>
       </c>
       <c r="B56" s="23"/>
-      <c r="C56" s="34" t="n">
+      <c r="C56" s="43" t="n">
         <v>46</v>
       </c>
       <c r="D56" s="23"/>
       <c r="E56" s="23" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F56" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="G56" s="34" t="n">
+      <c r="G56" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H56" s="34" t="n">
+      <c r="H56" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="34" t="n">
+      <c r="I56" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="L56" s="52"/>
-      <c r="M56" s="52"/>
-      <c r="N56" s="52"/>
-      <c r="O56" s="52"/>
+      <c r="L56" s="48"/>
+      <c r="M56" s="48"/>
+      <c r="N56" s="48"/>
+      <c r="O56" s="48"/>
       <c r="P56" s="5"/>
       <c r="Q56" s="5"/>
-      <c r="R56" s="53"/>
+      <c r="R56" s="50"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="40" t="n">
+      <c r="A57" s="34" t="n">
         <v>46</v>
       </c>
       <c r="B57" s="24"/>
-      <c r="C57" s="40" t="n">
+      <c r="C57" s="34" t="n">
         <v>47</v>
       </c>
       <c r="D57" s="24"/>
       <c r="E57" s="24" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F57" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="G57" s="40" t="n">
+      <c r="G57" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H57" s="40" t="n">
+      <c r="H57" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I57" s="40" t="n">
+      <c r="I57" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J57" s="8"/>
-      <c r="K57" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L57" s="50"/>
-      <c r="M57" s="50"/>
-      <c r="N57" s="50"/>
-      <c r="O57" s="50"/>
+      <c r="K57" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L57" s="52"/>
+      <c r="M57" s="52"/>
+      <c r="N57" s="52"/>
+      <c r="O57" s="52"/>
       <c r="P57" s="8"/>
       <c r="Q57" s="8"/>
-      <c r="R57" s="53"/>
+      <c r="R57" s="50"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="40" t="n">
+      <c r="A58" s="34" t="n">
         <v>47</v>
       </c>
       <c r="B58" s="24"/>
-      <c r="C58" s="40" t="n">
+      <c r="C58" s="34" t="n">
         <v>48</v>
       </c>
       <c r="D58" s="24"/>
       <c r="E58" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="F58" s="56" t="s">
+        <v>286</v>
+      </c>
+      <c r="F58" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="G58" s="40" t="n">
+      <c r="G58" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="H58" s="40" t="n">
+      <c r="H58" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="40" t="n">
+      <c r="I58" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J58" s="8"/>
-      <c r="K58" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L58" s="50"/>
-      <c r="M58" s="50"/>
-      <c r="N58" s="50"/>
-      <c r="O58" s="50"/>
+      <c r="K58" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L58" s="52"/>
+      <c r="M58" s="52"/>
+      <c r="N58" s="52"/>
+      <c r="O58" s="52"/>
       <c r="P58" s="8"/>
       <c r="Q58" s="8"/>
-      <c r="R58" s="53"/>
+      <c r="R58" s="50"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="40" t="n">
+      <c r="A59" s="34" t="n">
         <v>48</v>
       </c>
       <c r="B59" s="24" t="n">
         <v>47</v>
       </c>
-      <c r="C59" s="40" t="n">
+      <c r="C59" s="34" t="n">
         <v>49</v>
       </c>
       <c r="D59" s="24"/>
       <c r="E59" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="F59" s="56" t="s">
+        <v>287</v>
+      </c>
+      <c r="F59" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="G59" s="40" t="n">
+      <c r="G59" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="H59" s="40" t="n">
+      <c r="H59" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I59" s="40" t="n">
+      <c r="I59" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J59" s="8"/>
-      <c r="K59" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L59" s="50"/>
-      <c r="M59" s="50"/>
-      <c r="N59" s="50"/>
-      <c r="O59" s="50"/>
+      <c r="K59" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L59" s="52"/>
+      <c r="M59" s="52"/>
+      <c r="N59" s="52"/>
+      <c r="O59" s="52"/>
       <c r="P59" s="8"/>
       <c r="Q59" s="8"/>
-      <c r="R59" s="53"/>
+      <c r="R59" s="50"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="40" t="n">
+      <c r="A60" s="34" t="n">
         <v>49</v>
       </c>
       <c r="B60" s="24"/>
-      <c r="C60" s="40" t="n">
+      <c r="C60" s="34" t="n">
         <v>50</v>
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="F60" s="56" t="s">
+        <v>288</v>
+      </c>
+      <c r="F60" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="G60" s="40" t="n">
+      <c r="G60" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="H60" s="40" t="n">
+      <c r="H60" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I60" s="40" t="n">
+      <c r="I60" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J60" s="8"/>
-      <c r="K60" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L60" s="50"/>
-      <c r="M60" s="50"/>
-      <c r="N60" s="50"/>
-      <c r="O60" s="50"/>
+      <c r="K60" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L60" s="52"/>
+      <c r="M60" s="52"/>
+      <c r="N60" s="52"/>
+      <c r="O60" s="52"/>
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
-      <c r="R60" s="53"/>
+      <c r="R60" s="50"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="40" t="n">
+      <c r="A61" s="34" t="n">
         <v>50</v>
       </c>
       <c r="B61" s="24"/>
-      <c r="C61" s="40" t="n">
+      <c r="C61" s="34" t="n">
         <v>51</v>
       </c>
       <c r="D61" s="24"/>
       <c r="E61" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="F61" s="56" t="s">
+        <v>289</v>
+      </c>
+      <c r="F61" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="G61" s="40" t="n">
+      <c r="G61" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="H61" s="40" t="n">
+      <c r="H61" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I61" s="40" t="n">
+      <c r="I61" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J61" s="8"/>
-      <c r="K61" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L61" s="50"/>
-      <c r="M61" s="50"/>
-      <c r="N61" s="50"/>
-      <c r="O61" s="50"/>
+      <c r="K61" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L61" s="52"/>
+      <c r="M61" s="52"/>
+      <c r="N61" s="52"/>
+      <c r="O61" s="52"/>
       <c r="P61" s="8"/>
       <c r="Q61" s="8"/>
-      <c r="R61" s="53"/>
+      <c r="R61" s="50"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="40" t="n">
+      <c r="A62" s="34" t="n">
         <v>51</v>
       </c>
       <c r="B62" s="24" t="n">
         <v>49</v>
       </c>
-      <c r="C62" s="40" t="n">
+      <c r="C62" s="34" t="n">
         <v>52</v>
       </c>
       <c r="D62" s="24"/>
       <c r="E62" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="F62" s="56" t="s">
+        <v>290</v>
+      </c>
+      <c r="F62" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="G62" s="40" t="n">
+      <c r="G62" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="H62" s="40" t="n">
+      <c r="H62" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I62" s="40" t="n">
+      <c r="I62" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J62" s="8"/>
-      <c r="K62" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L62" s="50"/>
-      <c r="M62" s="50"/>
-      <c r="N62" s="43" t="s">
+      <c r="K62" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L62" s="52"/>
+      <c r="M62" s="52"/>
+      <c r="N62" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="O62" s="50"/>
+      <c r="O62" s="52"/>
       <c r="P62" s="8"/>
       <c r="Q62" s="8"/>
-      <c r="R62" s="53"/>
+      <c r="R62" s="50"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="40" t="n">
+      <c r="A63" s="34" t="n">
         <v>52</v>
       </c>
       <c r="B63" s="24"/>
-      <c r="C63" s="40" t="n">
+      <c r="C63" s="34" t="n">
         <v>53</v>
       </c>
       <c r="D63" s="24"/>
       <c r="E63" s="24" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F63" s="55" t="s">
-        <v>294</v>
-      </c>
-      <c r="G63" s="40" t="n">
+        <v>292</v>
+      </c>
+      <c r="G63" s="34" t="n">
         <v>51</v>
       </c>
-      <c r="H63" s="40" t="n">
+      <c r="H63" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I63" s="40" t="n">
+      <c r="I63" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J63" s="8"/>
-      <c r="K63" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L63" s="50"/>
-      <c r="M63" s="50"/>
-      <c r="N63" s="50"/>
-      <c r="O63" s="50"/>
+      <c r="K63" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L63" s="52"/>
+      <c r="M63" s="52"/>
+      <c r="N63" s="52"/>
+      <c r="O63" s="52"/>
       <c r="P63" s="8"/>
       <c r="Q63" s="8"/>
-      <c r="R63" s="53"/>
+      <c r="R63" s="50"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="40" t="n">
+      <c r="A64" s="34" t="n">
         <v>53</v>
       </c>
       <c r="B64" s="24"/>
-      <c r="C64" s="40" t="n">
+      <c r="C64" s="34" t="n">
         <v>54</v>
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="24" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F64" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="G64" s="40" t="n">
+      <c r="G64" s="34" t="n">
         <v>51</v>
       </c>
-      <c r="H64" s="40" t="n">
+      <c r="H64" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I64" s="40" t="n">
+      <c r="I64" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J64" s="8"/>
-      <c r="K64" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L64" s="50"/>
-      <c r="M64" s="50"/>
-      <c r="N64" s="50"/>
-      <c r="O64" s="50"/>
+      <c r="K64" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L64" s="52"/>
+      <c r="M64" s="52"/>
+      <c r="N64" s="52"/>
+      <c r="O64" s="52"/>
       <c r="P64" s="8"/>
       <c r="Q64" s="8"/>
-      <c r="R64" s="45"/>
+      <c r="R64" s="42"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="40" t="n">
+      <c r="A65" s="34" t="n">
         <v>54</v>
       </c>
       <c r="B65" s="24"/>
-      <c r="C65" s="40" t="n">
+      <c r="C65" s="34" t="n">
         <v>55</v>
       </c>
       <c r="D65" s="24"/>
       <c r="E65" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="F65" s="56" t="s">
+        <v>294</v>
+      </c>
+      <c r="F65" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="G65" s="40" t="n">
+      <c r="G65" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="H65" s="40" t="n">
+      <c r="H65" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I65" s="40" t="n">
+      <c r="I65" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="K65" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L65" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="K65" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L65" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M65" s="50"/>
-      <c r="N65" s="50"/>
-      <c r="O65" s="50"/>
+      <c r="M65" s="52"/>
+      <c r="N65" s="52"/>
+      <c r="O65" s="52"/>
       <c r="P65" s="8"/>
       <c r="Q65" s="8"/>
-      <c r="R65" s="45"/>
+      <c r="R65" s="42"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="40" t="n">
+      <c r="A66" s="34" t="n">
         <v>55</v>
       </c>
       <c r="B66" s="24"/>
-      <c r="C66" s="40" t="n">
+      <c r="C66" s="34" t="n">
         <v>56</v>
       </c>
       <c r="D66" s="24"/>
       <c r="E66" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="F66" s="56" t="s">
+        <v>296</v>
+      </c>
+      <c r="F66" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="G66" s="40" t="n">
+      <c r="G66" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="H66" s="40" t="n">
+      <c r="H66" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I66" s="40" t="n">
+      <c r="I66" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="K66" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L66" s="43" t="s">
+        <v>297</v>
+      </c>
+      <c r="K66" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L66" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M66" s="50"/>
-      <c r="N66" s="50"/>
-      <c r="O66" s="50"/>
+      <c r="M66" s="52"/>
+      <c r="N66" s="52"/>
+      <c r="O66" s="52"/>
       <c r="P66" s="8"/>
       <c r="Q66" s="8"/>
-      <c r="R66" s="45"/>
+      <c r="R66" s="42"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="34" t="n">
+      <c r="A67" s="43" t="n">
         <v>56</v>
       </c>
       <c r="B67" s="23"/>
-      <c r="C67" s="34" t="n">
+      <c r="C67" s="43" t="n">
         <v>57</v>
       </c>
       <c r="D67" s="23"/>
       <c r="E67" s="23" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F67" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G67" s="34" t="n">
+      <c r="G67" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H67" s="63" t="n">
+      <c r="H67" s="70" t="n">
         <v>2</v>
       </c>
-      <c r="I67" s="34" t="n">
+      <c r="I67" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="K67" s="47" t="s">
         <v>87</v>
@@ -7829,293 +7872,293 @@
       <c r="L67" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M67" s="52"/>
-      <c r="N67" s="52"/>
-      <c r="O67" s="52"/>
+      <c r="M67" s="48"/>
+      <c r="N67" s="48"/>
+      <c r="O67" s="48"/>
       <c r="P67" s="5"/>
       <c r="Q67" s="5"/>
-      <c r="R67" s="53"/>
+      <c r="R67" s="50"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="40" t="n">
+      <c r="A68" s="34" t="n">
         <v>57</v>
       </c>
       <c r="B68" s="24"/>
-      <c r="C68" s="40"/>
+      <c r="C68" s="34"/>
       <c r="D68" s="24"/>
       <c r="E68" s="24" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F68" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G68" s="40" t="n">
+      <c r="G68" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H68" s="40" t="n">
+      <c r="H68" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I68" s="40"/>
+      <c r="I68" s="34"/>
       <c r="J68" s="8"/>
-      <c r="K68" s="43"/>
-      <c r="L68" s="50"/>
-      <c r="M68" s="50"/>
-      <c r="N68" s="50"/>
-      <c r="O68" s="50"/>
+      <c r="K68" s="41"/>
+      <c r="L68" s="52"/>
+      <c r="M68" s="52"/>
+      <c r="N68" s="52"/>
+      <c r="O68" s="52"/>
       <c r="P68" s="8"/>
       <c r="Q68" s="8"/>
-      <c r="R68" s="45"/>
+      <c r="R68" s="42"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="40" t="n">
+      <c r="A69" s="34" t="n">
         <v>58</v>
       </c>
       <c r="B69" s="24"/>
-      <c r="C69" s="40" t="n">
+      <c r="C69" s="34" t="n">
         <v>58</v>
       </c>
       <c r="D69" s="24"/>
       <c r="E69" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="F69" s="56" t="s">
+        <v>301</v>
+      </c>
+      <c r="F69" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="G69" s="40" t="n">
+      <c r="G69" s="34" t="n">
         <v>57</v>
       </c>
-      <c r="H69" s="40" t="n">
+      <c r="H69" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I69" s="40" t="n">
+      <c r="I69" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="K69" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L69" s="43" t="s">
+        <v>302</v>
+      </c>
+      <c r="K69" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L69" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M69" s="50"/>
-      <c r="N69" s="50"/>
-      <c r="O69" s="50"/>
+      <c r="M69" s="52"/>
+      <c r="N69" s="52"/>
+      <c r="O69" s="52"/>
       <c r="P69" s="8"/>
       <c r="Q69" s="8"/>
-      <c r="R69" s="45"/>
+      <c r="R69" s="42"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="40" t="n">
+      <c r="A70" s="34" t="n">
         <v>59</v>
       </c>
       <c r="B70" s="24"/>
-      <c r="C70" s="40" t="n">
+      <c r="C70" s="34" t="n">
         <v>59</v>
       </c>
       <c r="D70" s="24"/>
       <c r="E70" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="F70" s="56" t="s">
+        <v>303</v>
+      </c>
+      <c r="F70" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="G70" s="40" t="n">
+      <c r="G70" s="34" t="n">
         <v>57</v>
       </c>
-      <c r="H70" s="40" t="n">
+      <c r="H70" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I70" s="40" t="n">
+      <c r="I70" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="K70" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L70" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="K70" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L70" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M70" s="50"/>
-      <c r="N70" s="50"/>
-      <c r="O70" s="50"/>
+      <c r="M70" s="52"/>
+      <c r="N70" s="52"/>
+      <c r="O70" s="52"/>
       <c r="P70" s="8"/>
       <c r="Q70" s="8"/>
-      <c r="R70" s="45"/>
+      <c r="R70" s="42"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="40" t="n">
+      <c r="A71" s="34" t="n">
         <v>60</v>
       </c>
       <c r="B71" s="24"/>
-      <c r="C71" s="40" t="n">
+      <c r="C71" s="34" t="n">
         <v>60</v>
       </c>
       <c r="D71" s="24"/>
       <c r="E71" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="F71" s="56" t="s">
+        <v>305</v>
+      </c>
+      <c r="F71" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="G71" s="40" t="n">
+      <c r="G71" s="34" t="n">
         <v>57</v>
       </c>
-      <c r="H71" s="40" t="n">
+      <c r="H71" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I71" s="40" t="n">
+      <c r="I71" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="K71" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L71" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="K71" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L71" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M71" s="50"/>
-      <c r="N71" s="50"/>
-      <c r="O71" s="50"/>
+      <c r="M71" s="52"/>
+      <c r="N71" s="52"/>
+      <c r="O71" s="52"/>
       <c r="P71" s="8"/>
       <c r="Q71" s="8"/>
-      <c r="R71" s="45"/>
+      <c r="R71" s="42"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="40" t="n">
+      <c r="A72" s="34" t="n">
         <v>61</v>
       </c>
       <c r="B72" s="24"/>
-      <c r="C72" s="40" t="n">
+      <c r="C72" s="34" t="n">
         <v>61</v>
       </c>
       <c r="D72" s="24"/>
       <c r="E72" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="F72" s="56" t="s">
+        <v>307</v>
+      </c>
+      <c r="F72" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="G72" s="40" t="n">
+      <c r="G72" s="34" t="n">
         <v>57</v>
       </c>
-      <c r="H72" s="40" t="n">
+      <c r="H72" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I72" s="40" t="n">
+      <c r="I72" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="K72" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L72" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="K72" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L72" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M72" s="50"/>
-      <c r="N72" s="50"/>
-      <c r="O72" s="50"/>
+      <c r="M72" s="52"/>
+      <c r="N72" s="52"/>
+      <c r="O72" s="52"/>
       <c r="P72" s="8"/>
       <c r="Q72" s="8"/>
-      <c r="R72" s="53"/>
+      <c r="R72" s="50"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="40"/>
+      <c r="A73" s="34"/>
       <c r="B73" s="24"/>
-      <c r="C73" s="40" t="n">
+      <c r="C73" s="34" t="n">
         <v>62</v>
       </c>
       <c r="D73" s="24"/>
       <c r="E73" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="F73" s="56" t="s">
+        <v>300</v>
+      </c>
+      <c r="F73" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="G73" s="40" t="n">
+      <c r="G73" s="34" t="n">
         <v>57</v>
       </c>
-      <c r="H73" s="40"/>
-      <c r="I73" s="40" t="n">
+      <c r="H73" s="34"/>
+      <c r="I73" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J73" s="8"/>
-      <c r="K73" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L73" s="50"/>
-      <c r="M73" s="50"/>
-      <c r="N73" s="50"/>
-      <c r="O73" s="50"/>
+      <c r="K73" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L73" s="52"/>
+      <c r="M73" s="52"/>
+      <c r="N73" s="52"/>
+      <c r="O73" s="52"/>
       <c r="P73" s="8"/>
       <c r="Q73" s="8"/>
-      <c r="R73" s="53"/>
+      <c r="R73" s="50"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="34" t="n">
+      <c r="A74" s="43" t="n">
         <v>62</v>
       </c>
       <c r="B74" s="23"/>
-      <c r="C74" s="34"/>
+      <c r="C74" s="43"/>
       <c r="D74" s="23"/>
       <c r="E74" s="23" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F74" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="G74" s="34" t="n">
+      <c r="G74" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H74" s="34" t="n">
+      <c r="H74" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I74" s="34" t="n">
+      <c r="I74" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J74" s="5"/>
       <c r="K74" s="47"/>
-      <c r="L74" s="52"/>
-      <c r="M74" s="52"/>
-      <c r="N74" s="52"/>
-      <c r="O74" s="52"/>
+      <c r="L74" s="48"/>
+      <c r="M74" s="48"/>
+      <c r="N74" s="48"/>
+      <c r="O74" s="48"/>
       <c r="P74" s="5"/>
       <c r="Q74" s="5"/>
-      <c r="R74" s="45"/>
+      <c r="R74" s="42"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="34" t="n">
+      <c r="A75" s="43" t="n">
         <v>63</v>
       </c>
       <c r="B75" s="23"/>
-      <c r="C75" s="34" t="n">
+      <c r="C75" s="43" t="n">
         <v>63</v>
       </c>
       <c r="D75" s="23"/>
       <c r="E75" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="F75" s="58" t="s">
+        <v>310</v>
+      </c>
+      <c r="F75" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="G75" s="34" t="n">
+      <c r="G75" s="43" t="n">
         <v>62</v>
       </c>
-      <c r="H75" s="34" t="n">
+      <c r="H75" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I75" s="34" t="n">
+      <c r="I75" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="K75" s="47" t="s">
         <v>87</v>
@@ -8123,39 +8166,39 @@
       <c r="L75" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M75" s="52"/>
-      <c r="N75" s="52"/>
-      <c r="O75" s="52"/>
+      <c r="M75" s="48"/>
+      <c r="N75" s="48"/>
+      <c r="O75" s="48"/>
       <c r="P75" s="5"/>
       <c r="Q75" s="5"/>
-      <c r="R75" s="45"/>
+      <c r="R75" s="42"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="34" t="n">
+      <c r="A76" s="43" t="n">
         <v>64</v>
       </c>
       <c r="B76" s="23"/>
-      <c r="C76" s="34" t="n">
+      <c r="C76" s="43" t="n">
         <v>64</v>
       </c>
       <c r="D76" s="23"/>
       <c r="E76" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="F76" s="58" t="s">
+        <v>312</v>
+      </c>
+      <c r="F76" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="G76" s="34" t="n">
+      <c r="G76" s="43" t="n">
         <v>62</v>
       </c>
-      <c r="H76" s="34" t="n">
+      <c r="H76" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I76" s="34" t="n">
+      <c r="I76" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K76" s="47" t="s">
         <v>87</v>
@@ -8163,43 +8206,43 @@
       <c r="L76" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M76" s="52"/>
-      <c r="N76" s="52"/>
-      <c r="O76" s="52"/>
+      <c r="M76" s="48"/>
+      <c r="N76" s="48"/>
+      <c r="O76" s="48"/>
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
-      <c r="R76" s="45"/>
+      <c r="R76" s="42"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="34" t="n">
+      <c r="A77" s="43" t="n">
         <v>65</v>
       </c>
       <c r="B77" s="23" t="n">
         <v>63</v>
       </c>
-      <c r="C77" s="34" t="n">
+      <c r="C77" s="43" t="n">
         <v>65</v>
       </c>
       <c r="D77" s="23" t="n">
         <v>63</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="F77" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F77" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="G77" s="34" t="n">
+      <c r="G77" s="43" t="n">
         <v>62</v>
       </c>
-      <c r="H77" s="34" t="n">
+      <c r="H77" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I77" s="34" t="n">
+      <c r="I77" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="K77" s="47" t="s">
         <v>87</v>
@@ -8207,39 +8250,39 @@
       <c r="L77" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M77" s="52"/>
-      <c r="N77" s="52"/>
-      <c r="O77" s="52"/>
+      <c r="M77" s="48"/>
+      <c r="N77" s="48"/>
+      <c r="O77" s="48"/>
       <c r="P77" s="5"/>
       <c r="Q77" s="5"/>
-      <c r="R77" s="45"/>
+      <c r="R77" s="42"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="34" t="n">
+      <c r="A78" s="43" t="n">
         <v>66</v>
       </c>
       <c r="B78" s="23"/>
-      <c r="C78" s="34" t="n">
+      <c r="C78" s="43" t="n">
         <v>66</v>
       </c>
       <c r="D78" s="23"/>
       <c r="E78" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="F78" s="59" t="s">
+        <v>316</v>
+      </c>
+      <c r="F78" s="57" t="s">
         <v>235</v>
       </c>
-      <c r="G78" s="34" t="n">
+      <c r="G78" s="43" t="n">
         <v>65</v>
       </c>
-      <c r="H78" s="34" t="n">
+      <c r="H78" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I78" s="34" t="n">
+      <c r="I78" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K78" s="47" t="s">
         <v>87</v>
@@ -8247,39 +8290,39 @@
       <c r="L78" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M78" s="52"/>
-      <c r="N78" s="52"/>
-      <c r="O78" s="52"/>
+      <c r="M78" s="48"/>
+      <c r="N78" s="48"/>
+      <c r="O78" s="48"/>
       <c r="P78" s="5"/>
       <c r="Q78" s="5"/>
-      <c r="R78" s="45"/>
+      <c r="R78" s="42"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="34" t="n">
+      <c r="A79" s="43" t="n">
         <v>67</v>
       </c>
       <c r="B79" s="23"/>
-      <c r="C79" s="34" t="n">
+      <c r="C79" s="43" t="n">
         <v>67</v>
       </c>
       <c r="D79" s="23"/>
       <c r="E79" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="F79" s="59" t="s">
+        <v>318</v>
+      </c>
+      <c r="F79" s="57" t="s">
         <v>238</v>
       </c>
-      <c r="G79" s="34" t="n">
+      <c r="G79" s="43" t="n">
         <v>65</v>
       </c>
-      <c r="H79" s="34" t="n">
+      <c r="H79" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I79" s="34" t="n">
+      <c r="I79" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="K79" s="47" t="s">
         <v>87</v>
@@ -8287,454 +8330,454 @@
       <c r="L79" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M79" s="52"/>
-      <c r="N79" s="52"/>
-      <c r="O79" s="52"/>
+      <c r="M79" s="48"/>
+      <c r="N79" s="48"/>
+      <c r="O79" s="48"/>
       <c r="P79" s="5"/>
       <c r="Q79" s="5"/>
-      <c r="R79" s="45"/>
+      <c r="R79" s="42"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="34"/>
+      <c r="A80" s="43"/>
       <c r="B80" s="23"/>
-      <c r="C80" s="34" t="n">
+      <c r="C80" s="43" t="n">
         <v>68</v>
       </c>
       <c r="D80" s="23"/>
       <c r="E80" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="F80" s="57" t="s">
+        <v>321</v>
+      </c>
+      <c r="G80" s="43" t="n">
+        <v>65</v>
+      </c>
+      <c r="H80" s="43"/>
+      <c r="I80" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="F80" s="59" t="s">
-        <v>323</v>
-      </c>
-      <c r="G80" s="34" t="n">
-        <v>65</v>
-      </c>
-      <c r="H80" s="34"/>
-      <c r="I80" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="K80" s="52"/>
+      <c r="K80" s="48"/>
       <c r="L80" s="47" t="s">
         <v>202</v>
       </c>
       <c r="M80" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="N80" s="52"/>
-      <c r="O80" s="52"/>
+      <c r="N80" s="48"/>
+      <c r="O80" s="48"/>
       <c r="P80" s="5"/>
       <c r="Q80" s="5"/>
-      <c r="R80" s="53"/>
+      <c r="R80" s="50"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="40" t="n">
+      <c r="A81" s="34" t="n">
         <v>68</v>
       </c>
       <c r="B81" s="24"/>
-      <c r="C81" s="40"/>
+      <c r="C81" s="34"/>
       <c r="D81" s="24"/>
       <c r="E81" s="24" t="s">
-        <v>325</v>
-      </c>
-      <c r="F81" s="64" t="s">
+        <v>323</v>
+      </c>
+      <c r="F81" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="G81" s="48" t="n">
+      <c r="G81" s="54" t="n">
         <v>43</v>
       </c>
-      <c r="H81" s="40" t="n">
+      <c r="H81" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I81" s="40"/>
+      <c r="I81" s="34"/>
       <c r="J81" s="8"/>
-      <c r="K81" s="50"/>
-      <c r="L81" s="50"/>
-      <c r="M81" s="50"/>
-      <c r="N81" s="50"/>
-      <c r="O81" s="50"/>
+      <c r="K81" s="52"/>
+      <c r="L81" s="52"/>
+      <c r="M81" s="52"/>
+      <c r="N81" s="52"/>
+      <c r="O81" s="52"/>
       <c r="P81" s="8"/>
       <c r="Q81" s="8"/>
-      <c r="R81" s="53"/>
+      <c r="R81" s="50"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="40" t="n">
+      <c r="A82" s="34" t="n">
         <v>69</v>
       </c>
       <c r="B82" s="24"/>
-      <c r="C82" s="40" t="n">
+      <c r="C82" s="34" t="n">
         <v>69</v>
       </c>
       <c r="D82" s="24"/>
       <c r="E82" s="24" t="s">
-        <v>326</v>
-      </c>
-      <c r="F82" s="56" t="s">
+        <v>324</v>
+      </c>
+      <c r="F82" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="G82" s="40" t="n">
+      <c r="G82" s="34" t="n">
         <v>68</v>
       </c>
-      <c r="H82" s="40" t="n">
+      <c r="H82" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I82" s="40" t="n">
+      <c r="I82" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J82" s="8"/>
-      <c r="K82" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L82" s="50"/>
-      <c r="M82" s="50"/>
-      <c r="N82" s="50"/>
-      <c r="O82" s="50"/>
+      <c r="K82" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L82" s="52"/>
+      <c r="M82" s="52"/>
+      <c r="N82" s="52"/>
+      <c r="O82" s="52"/>
       <c r="P82" s="8"/>
       <c r="Q82" s="8"/>
-      <c r="R82" s="53"/>
+      <c r="R82" s="50"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="40" t="n">
+      <c r="A83" s="34" t="n">
         <v>70</v>
       </c>
       <c r="B83" s="24"/>
-      <c r="C83" s="40" t="n">
+      <c r="C83" s="34" t="n">
         <v>70</v>
       </c>
       <c r="D83" s="24"/>
       <c r="E83" s="24" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F83" s="55" t="s">
-        <v>328</v>
-      </c>
-      <c r="G83" s="40" t="n">
+        <v>326</v>
+      </c>
+      <c r="G83" s="34" t="n">
         <v>69</v>
       </c>
-      <c r="H83" s="40" t="n">
+      <c r="H83" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I83" s="40" t="n">
+      <c r="I83" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J83" s="8"/>
-      <c r="K83" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L83" s="50"/>
-      <c r="M83" s="50"/>
-      <c r="N83" s="50"/>
-      <c r="O83" s="50"/>
+      <c r="K83" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L83" s="52"/>
+      <c r="M83" s="52"/>
+      <c r="N83" s="52"/>
+      <c r="O83" s="52"/>
       <c r="P83" s="8"/>
       <c r="Q83" s="8"/>
-      <c r="R83" s="45"/>
+      <c r="R83" s="42"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="40" t="n">
+      <c r="A84" s="34" t="n">
         <v>71</v>
       </c>
       <c r="B84" s="24"/>
-      <c r="C84" s="40" t="n">
+      <c r="C84" s="34" t="n">
         <v>71</v>
       </c>
       <c r="D84" s="24"/>
       <c r="E84" s="24" t="s">
-        <v>329</v>
-      </c>
-      <c r="F84" s="56" t="s">
+        <v>327</v>
+      </c>
+      <c r="F84" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="G84" s="40" t="n">
+      <c r="G84" s="34" t="n">
         <v>68</v>
       </c>
-      <c r="H84" s="40" t="n">
+      <c r="H84" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I84" s="40" t="n">
+      <c r="I84" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="K84" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L84" s="43" t="s">
+        <v>328</v>
+      </c>
+      <c r="K84" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L84" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M84" s="50"/>
-      <c r="N84" s="50"/>
-      <c r="O84" s="50"/>
+      <c r="M84" s="52"/>
+      <c r="N84" s="52"/>
+      <c r="O84" s="52"/>
       <c r="P84" s="8"/>
       <c r="Q84" s="8"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="34" t="n">
+      <c r="A85" s="43" t="n">
         <v>72</v>
       </c>
       <c r="B85" s="23"/>
-      <c r="C85" s="34"/>
+      <c r="C85" s="43"/>
       <c r="D85" s="23"/>
       <c r="E85" s="23" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F85" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="G85" s="34" t="n">
+      <c r="G85" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H85" s="34" t="n">
+      <c r="H85" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I85" s="34"/>
+      <c r="I85" s="43"/>
       <c r="J85" s="5"/>
-      <c r="K85" s="52"/>
-      <c r="L85" s="52"/>
-      <c r="M85" s="52"/>
-      <c r="N85" s="52"/>
-      <c r="O85" s="52"/>
+      <c r="K85" s="48"/>
+      <c r="L85" s="48"/>
+      <c r="M85" s="48"/>
+      <c r="N85" s="48"/>
+      <c r="O85" s="48"/>
       <c r="P85" s="5"/>
       <c r="Q85" s="5"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="34" t="n">
+      <c r="A86" s="43" t="n">
         <v>73</v>
       </c>
       <c r="B86" s="23"/>
-      <c r="C86" s="34" t="n">
+      <c r="C86" s="43" t="n">
         <v>72</v>
       </c>
       <c r="D86" s="23"/>
       <c r="E86" s="23" t="s">
-        <v>332</v>
-      </c>
-      <c r="F86" s="58" t="s">
+        <v>330</v>
+      </c>
+      <c r="F86" s="49" t="s">
         <v>154</v>
       </c>
-      <c r="G86" s="34" t="n">
+      <c r="G86" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H86" s="34" t="n">
+      <c r="H86" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I86" s="34" t="n">
+      <c r="I86" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J86" s="5"/>
-      <c r="K86" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="L86" s="52"/>
-      <c r="M86" s="52"/>
-      <c r="N86" s="52"/>
-      <c r="O86" s="52"/>
+      <c r="K86" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="L86" s="48"/>
+      <c r="M86" s="48"/>
+      <c r="N86" s="48"/>
+      <c r="O86" s="48"/>
       <c r="P86" s="5"/>
       <c r="Q86" s="5"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="34" t="n">
+      <c r="A87" s="43" t="n">
         <v>74</v>
       </c>
       <c r="B87" s="23"/>
-      <c r="C87" s="34" t="n">
+      <c r="C87" s="43" t="n">
         <v>73</v>
       </c>
       <c r="D87" s="23"/>
       <c r="E87" s="23"/>
-      <c r="F87" s="58" t="s">
+      <c r="F87" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="G87" s="34" t="n">
+      <c r="G87" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H87" s="34" t="n">
+      <c r="H87" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I87" s="34" t="n">
+      <c r="I87" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J87" s="5"/>
-      <c r="K87" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="L87" s="52"/>
-      <c r="M87" s="52"/>
-      <c r="N87" s="52"/>
-      <c r="O87" s="52"/>
+      <c r="K87" s="72" t="s">
+        <v>87</v>
+      </c>
+      <c r="L87" s="48"/>
+      <c r="M87" s="48"/>
+      <c r="N87" s="48"/>
+      <c r="O87" s="48"/>
       <c r="P87" s="5"/>
       <c r="Q87" s="5"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="34" t="n">
+      <c r="A88" s="43" t="n">
         <v>75</v>
       </c>
       <c r="B88" s="23"/>
-      <c r="C88" s="34" t="n">
+      <c r="C88" s="43" t="n">
         <v>74</v>
       </c>
       <c r="D88" s="23"/>
       <c r="E88" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="F88" s="58" t="s">
+        <v>331</v>
+      </c>
+      <c r="F88" s="49" t="s">
         <v>156</v>
       </c>
-      <c r="G88" s="34" t="n">
+      <c r="G88" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H88" s="34" t="n">
+      <c r="H88" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I88" s="34" t="n">
+      <c r="I88" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J88" s="5"/>
       <c r="K88" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="L88" s="52"/>
-      <c r="M88" s="52"/>
-      <c r="N88" s="52"/>
-      <c r="O88" s="52"/>
+      <c r="L88" s="48"/>
+      <c r="M88" s="48"/>
+      <c r="N88" s="48"/>
+      <c r="O88" s="48"/>
       <c r="P88" s="5"/>
       <c r="Q88" s="5"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="34" t="n">
+      <c r="A89" s="43" t="n">
         <v>76</v>
       </c>
       <c r="B89" s="23" t="n">
         <v>75</v>
       </c>
-      <c r="C89" s="34" t="n">
+      <c r="C89" s="43" t="n">
         <v>75</v>
       </c>
       <c r="D89" s="23" t="n">
         <v>75</v>
       </c>
       <c r="E89" s="23" t="s">
-        <v>334</v>
-      </c>
-      <c r="F89" s="58" t="s">
+        <v>332</v>
+      </c>
+      <c r="F89" s="49" t="s">
         <v>157</v>
       </c>
-      <c r="G89" s="34" t="n">
+      <c r="G89" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H89" s="34" t="n">
+      <c r="H89" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I89" s="34" t="n">
+      <c r="I89" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J89" s="5"/>
       <c r="K89" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="L89" s="52"/>
-      <c r="M89" s="52"/>
-      <c r="N89" s="52"/>
-      <c r="O89" s="52"/>
+      <c r="L89" s="48"/>
+      <c r="M89" s="48"/>
+      <c r="N89" s="48"/>
+      <c r="O89" s="48"/>
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="34" t="n">
+      <c r="A90" s="43" t="n">
         <v>77</v>
       </c>
       <c r="B90" s="23" t="n">
         <v>75</v>
       </c>
-      <c r="C90" s="34"/>
+      <c r="C90" s="43"/>
       <c r="D90" s="23" t="n">
         <v>75</v>
       </c>
       <c r="E90" s="23"/>
-      <c r="F90" s="58" t="s">
-        <v>335</v>
-      </c>
-      <c r="G90" s="34" t="n">
+      <c r="F90" s="49" t="s">
+        <v>333</v>
+      </c>
+      <c r="G90" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H90" s="34" t="n">
+      <c r="H90" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I90" s="34"/>
+      <c r="I90" s="43"/>
       <c r="J90" s="5"/>
       <c r="K90" s="47"/>
-      <c r="L90" s="52"/>
-      <c r="M90" s="52"/>
-      <c r="N90" s="52"/>
-      <c r="O90" s="52"/>
+      <c r="L90" s="48"/>
+      <c r="M90" s="48"/>
+      <c r="N90" s="48"/>
+      <c r="O90" s="48"/>
       <c r="P90" s="5"/>
       <c r="Q90" s="5"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="34" t="n">
+      <c r="A91" s="43" t="n">
         <v>78</v>
       </c>
       <c r="B91" s="23"/>
-      <c r="C91" s="34" t="n">
+      <c r="C91" s="43" t="n">
         <v>76</v>
       </c>
       <c r="D91" s="23"/>
       <c r="E91" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="F91" s="59" t="s">
-        <v>337</v>
-      </c>
-      <c r="G91" s="34" t="n">
+        <v>334</v>
+      </c>
+      <c r="F91" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="G91" s="43" t="n">
         <v>77</v>
       </c>
-      <c r="H91" s="34" t="n">
+      <c r="H91" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I91" s="34" t="n">
+      <c r="I91" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J91" s="5"/>
       <c r="K91" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="L91" s="52"/>
-      <c r="M91" s="52"/>
-      <c r="N91" s="52"/>
-      <c r="O91" s="52"/>
+      <c r="L91" s="48"/>
+      <c r="M91" s="48"/>
+      <c r="N91" s="48"/>
+      <c r="O91" s="48"/>
       <c r="P91" s="5"/>
       <c r="Q91" s="5"/>
-      <c r="R91" s="45"/>
+      <c r="R91" s="42"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="34" t="n">
+      <c r="A92" s="43" t="n">
         <v>79</v>
       </c>
       <c r="B92" s="23"/>
-      <c r="C92" s="34" t="n">
+      <c r="C92" s="43" t="n">
         <v>77</v>
       </c>
       <c r="D92" s="23"/>
       <c r="E92" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="F92" s="57" t="s">
+        <v>337</v>
+      </c>
+      <c r="G92" s="43" t="n">
+        <v>77</v>
+      </c>
+      <c r="H92" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I92" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="5" t="s">
         <v>338</v>
-      </c>
-      <c r="F92" s="59" t="s">
-        <v>339</v>
-      </c>
-      <c r="G92" s="34" t="n">
-        <v>77</v>
-      </c>
-      <c r="H92" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I92" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="5" t="s">
-        <v>340</v>
       </c>
       <c r="K92" s="47" t="s">
         <v>87</v>
@@ -8742,255 +8785,255 @@
       <c r="L92" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M92" s="52"/>
+      <c r="M92" s="48"/>
       <c r="N92" s="47" t="s">
         <v>232</v>
       </c>
-      <c r="O92" s="52"/>
+      <c r="O92" s="48"/>
       <c r="P92" s="5"/>
       <c r="Q92" s="5"/>
-      <c r="R92" s="53"/>
+      <c r="R92" s="50"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="40" t="n">
+      <c r="A93" s="34" t="n">
         <v>80</v>
       </c>
       <c r="B93" s="24"/>
-      <c r="C93" s="40"/>
+      <c r="C93" s="34"/>
       <c r="D93" s="24"/>
       <c r="E93" s="24" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F93" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="G93" s="40" t="n">
+      <c r="G93" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H93" s="40" t="n">
+      <c r="H93" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I93" s="40"/>
+      <c r="I93" s="34"/>
       <c r="J93" s="8"/>
-      <c r="K93" s="43"/>
-      <c r="L93" s="43"/>
-      <c r="M93" s="50"/>
-      <c r="N93" s="43"/>
-      <c r="O93" s="50"/>
+      <c r="K93" s="41"/>
+      <c r="L93" s="41"/>
+      <c r="M93" s="52"/>
+      <c r="N93" s="41"/>
+      <c r="O93" s="52"/>
       <c r="P93" s="8"/>
       <c r="Q93" s="8"/>
-      <c r="R93" s="45"/>
+      <c r="R93" s="42"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="40" t="n">
+      <c r="A94" s="34" t="n">
         <v>81</v>
       </c>
       <c r="B94" s="24"/>
-      <c r="C94" s="40" t="n">
+      <c r="C94" s="34" t="n">
         <v>78</v>
       </c>
       <c r="D94" s="24"/>
       <c r="E94" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="F94" s="56" t="s">
+        <v>340</v>
+      </c>
+      <c r="F94" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="G94" s="40" t="n">
+      <c r="G94" s="34" t="n">
         <v>80</v>
       </c>
-      <c r="H94" s="40" t="n">
+      <c r="H94" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I94" s="40" t="n">
+      <c r="I94" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="K94" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L94" s="43" t="s">
+        <v>341</v>
+      </c>
+      <c r="K94" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L94" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M94" s="50"/>
-      <c r="N94" s="50"/>
-      <c r="O94" s="50"/>
+      <c r="M94" s="52"/>
+      <c r="N94" s="52"/>
+      <c r="O94" s="52"/>
       <c r="P94" s="8"/>
       <c r="Q94" s="8"/>
-      <c r="R94" s="45"/>
+      <c r="R94" s="42"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="40" t="n">
+      <c r="A95" s="34" t="n">
         <v>82</v>
       </c>
       <c r="B95" s="24"/>
-      <c r="C95" s="40" t="n">
+      <c r="C95" s="34" t="n">
         <v>79</v>
       </c>
       <c r="D95" s="24"/>
       <c r="E95" s="24" t="s">
-        <v>344</v>
-      </c>
-      <c r="F95" s="56" t="s">
+        <v>342</v>
+      </c>
+      <c r="F95" s="40" t="s">
         <v>162</v>
       </c>
-      <c r="G95" s="40" t="n">
+      <c r="G95" s="34" t="n">
         <v>80</v>
       </c>
-      <c r="H95" s="40" t="n">
+      <c r="H95" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I95" s="40" t="n">
+      <c r="I95" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="K95" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L95" s="43" t="s">
+        <v>343</v>
+      </c>
+      <c r="K95" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L95" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M95" s="50"/>
-      <c r="N95" s="50"/>
-      <c r="O95" s="50"/>
+      <c r="M95" s="52"/>
+      <c r="N95" s="52"/>
+      <c r="O95" s="52"/>
       <c r="P95" s="8"/>
       <c r="Q95" s="8"/>
-      <c r="R95" s="45"/>
+      <c r="R95" s="42"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="40" t="n">
+      <c r="A96" s="34" t="n">
         <v>83</v>
       </c>
       <c r="B96" s="24"/>
-      <c r="C96" s="40" t="n">
+      <c r="C96" s="34" t="n">
         <v>80</v>
       </c>
       <c r="D96" s="24"/>
       <c r="E96" s="24" t="s">
-        <v>346</v>
-      </c>
-      <c r="F96" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="F96" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="G96" s="40" t="n">
+      <c r="G96" s="34" t="n">
         <v>80</v>
       </c>
-      <c r="H96" s="40" t="n">
+      <c r="H96" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I96" s="40" t="n">
+      <c r="I96" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="K96" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L96" s="43" t="s">
+        <v>345</v>
+      </c>
+      <c r="K96" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L96" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M96" s="50"/>
-      <c r="N96" s="50"/>
-      <c r="O96" s="50"/>
+      <c r="M96" s="52"/>
+      <c r="N96" s="52"/>
+      <c r="O96" s="52"/>
       <c r="P96" s="8"/>
       <c r="Q96" s="8"/>
-      <c r="R96" s="45"/>
+      <c r="R96" s="42"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="40" t="n">
+      <c r="A97" s="34" t="n">
         <v>84</v>
       </c>
       <c r="B97" s="24"/>
-      <c r="C97" s="40" t="n">
+      <c r="C97" s="34" t="n">
         <v>81</v>
       </c>
       <c r="D97" s="24"/>
       <c r="E97" s="24" t="s">
-        <v>348</v>
-      </c>
-      <c r="F97" s="56" t="s">
+        <v>346</v>
+      </c>
+      <c r="F97" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="G97" s="40" t="n">
+      <c r="G97" s="34" t="n">
         <v>80</v>
       </c>
-      <c r="H97" s="40" t="n">
+      <c r="H97" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I97" s="40" t="n">
+      <c r="I97" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J97" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="K97" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L97" s="43" t="s">
+        <v>347</v>
+      </c>
+      <c r="K97" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L97" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M97" s="50"/>
-      <c r="N97" s="50"/>
-      <c r="O97" s="50"/>
+      <c r="M97" s="52"/>
+      <c r="N97" s="52"/>
+      <c r="O97" s="52"/>
       <c r="P97" s="8"/>
       <c r="Q97" s="8"/>
-      <c r="R97" s="53"/>
+      <c r="R97" s="50"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="34" t="n">
+      <c r="A98" s="43" t="n">
         <v>85</v>
       </c>
       <c r="B98" s="23"/>
-      <c r="C98" s="34"/>
+      <c r="C98" s="43"/>
       <c r="D98" s="23"/>
       <c r="E98" s="23"/>
       <c r="F98" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="G98" s="34" t="n">
+      <c r="G98" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H98" s="34" t="n">
+      <c r="H98" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I98" s="34"/>
+      <c r="I98" s="43"/>
       <c r="J98" s="5"/>
       <c r="K98" s="47"/>
       <c r="L98" s="47"/>
-      <c r="M98" s="52"/>
-      <c r="N98" s="52"/>
-      <c r="O98" s="52"/>
+      <c r="M98" s="48"/>
+      <c r="N98" s="48"/>
+      <c r="O98" s="48"/>
       <c r="P98" s="5"/>
       <c r="Q98" s="5"/>
-      <c r="R98" s="45"/>
+      <c r="R98" s="42"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="34"/>
+      <c r="A99" s="43"/>
       <c r="B99" s="23"/>
-      <c r="C99" s="34" t="n">
+      <c r="C99" s="43" t="n">
         <v>82</v>
       </c>
       <c r="D99" s="23"/>
       <c r="E99" s="23" t="s">
-        <v>350</v>
-      </c>
-      <c r="F99" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="F99" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="G99" s="34" t="n">
+      <c r="G99" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H99" s="34"/>
-      <c r="I99" s="34" t="n">
+      <c r="H99" s="43"/>
+      <c r="I99" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K99" s="47" t="s">
         <v>87</v>
@@ -8998,71 +9041,71 @@
       <c r="L99" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M99" s="52"/>
-      <c r="N99" s="52"/>
-      <c r="O99" s="52"/>
+      <c r="M99" s="48"/>
+      <c r="N99" s="48"/>
+      <c r="O99" s="48"/>
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
-      <c r="R99" s="53"/>
+      <c r="R99" s="50"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="34"/>
+      <c r="A100" s="43"/>
       <c r="B100" s="23"/>
-      <c r="C100" s="34" t="n">
+      <c r="C100" s="43" t="n">
         <v>83</v>
       </c>
       <c r="D100" s="23"/>
       <c r="E100" s="23" t="s">
-        <v>350</v>
-      </c>
-      <c r="F100" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="F100" s="49" t="s">
         <v>165</v>
       </c>
-      <c r="G100" s="34" t="n">
+      <c r="G100" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H100" s="34"/>
-      <c r="I100" s="34" t="n">
+      <c r="H100" s="43"/>
+      <c r="I100" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J100" s="5"/>
       <c r="K100" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="L100" s="52"/>
-      <c r="M100" s="52"/>
-      <c r="N100" s="52"/>
-      <c r="O100" s="52"/>
+      <c r="L100" s="48"/>
+      <c r="M100" s="48"/>
+      <c r="N100" s="48"/>
+      <c r="O100" s="48"/>
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
-      <c r="R100" s="45"/>
+      <c r="R100" s="42"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="34" t="n">
+      <c r="A101" s="43" t="n">
         <v>86</v>
       </c>
       <c r="B101" s="23"/>
-      <c r="C101" s="34" t="n">
+      <c r="C101" s="43" t="n">
         <v>84</v>
       </c>
       <c r="D101" s="23"/>
       <c r="E101" s="23" t="s">
-        <v>352</v>
-      </c>
-      <c r="F101" s="58" t="s">
+        <v>350</v>
+      </c>
+      <c r="F101" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="G101" s="34" t="n">
+      <c r="G101" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H101" s="34" t="n">
+      <c r="H101" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I101" s="34" t="n">
+      <c r="I101" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K101" s="47" t="s">
         <v>87</v>
@@ -9070,39 +9113,39 @@
       <c r="L101" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M101" s="52"/>
-      <c r="N101" s="52"/>
-      <c r="O101" s="52"/>
+      <c r="M101" s="48"/>
+      <c r="N101" s="48"/>
+      <c r="O101" s="48"/>
       <c r="P101" s="5"/>
       <c r="Q101" s="5"/>
-      <c r="R101" s="45"/>
+      <c r="R101" s="42"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="34" t="n">
+      <c r="A102" s="43" t="n">
         <v>87</v>
       </c>
       <c r="B102" s="23"/>
-      <c r="C102" s="34" t="n">
+      <c r="C102" s="43" t="n">
         <v>85</v>
       </c>
       <c r="D102" s="23"/>
       <c r="E102" s="23" t="s">
-        <v>354</v>
-      </c>
-      <c r="F102" s="58" t="s">
+        <v>352</v>
+      </c>
+      <c r="F102" s="49" t="s">
         <v>153</v>
       </c>
-      <c r="G102" s="34" t="n">
+      <c r="G102" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H102" s="34" t="n">
+      <c r="H102" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I102" s="34" t="n">
+      <c r="I102" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K102" s="47" t="s">
         <v>87</v>
@@ -9110,39 +9153,39 @@
       <c r="L102" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M102" s="52"/>
-      <c r="N102" s="52"/>
-      <c r="O102" s="52"/>
+      <c r="M102" s="48"/>
+      <c r="N102" s="48"/>
+      <c r="O102" s="48"/>
       <c r="P102" s="5"/>
       <c r="Q102" s="5"/>
-      <c r="R102" s="45"/>
+      <c r="R102" s="42"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="34" t="n">
+      <c r="A103" s="43" t="n">
         <v>88</v>
       </c>
       <c r="B103" s="23"/>
-      <c r="C103" s="34" t="n">
+      <c r="C103" s="43" t="n">
         <v>86</v>
       </c>
       <c r="D103" s="23"/>
       <c r="E103" s="23" t="s">
-        <v>356</v>
-      </c>
-      <c r="F103" s="58" t="s">
+        <v>354</v>
+      </c>
+      <c r="F103" s="49" t="s">
         <v>166</v>
       </c>
-      <c r="G103" s="34" t="n">
+      <c r="G103" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H103" s="34" t="n">
+      <c r="H103" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I103" s="34" t="n">
+      <c r="I103" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="K103" s="47" t="s">
         <v>87</v>
@@ -9150,39 +9193,39 @@
       <c r="L103" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M103" s="52"/>
-      <c r="N103" s="52"/>
-      <c r="O103" s="52"/>
+      <c r="M103" s="48"/>
+      <c r="N103" s="48"/>
+      <c r="O103" s="48"/>
       <c r="P103" s="5"/>
       <c r="Q103" s="5"/>
-      <c r="R103" s="45"/>
+      <c r="R103" s="42"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="34" t="n">
+      <c r="A104" s="43" t="n">
         <v>89</v>
       </c>
       <c r="B104" s="23"/>
-      <c r="C104" s="34" t="n">
+      <c r="C104" s="43" t="n">
         <v>87</v>
       </c>
       <c r="D104" s="23"/>
       <c r="E104" s="23" t="s">
-        <v>358</v>
-      </c>
-      <c r="F104" s="58" t="s">
+        <v>356</v>
+      </c>
+      <c r="F104" s="49" t="s">
         <v>167</v>
       </c>
-      <c r="G104" s="34" t="n">
+      <c r="G104" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H104" s="34" t="n">
+      <c r="H104" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I104" s="34" t="n">
+      <c r="I104" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="K104" s="47" t="s">
         <v>87</v>
@@ -9190,39 +9233,39 @@
       <c r="L104" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M104" s="52"/>
-      <c r="N104" s="52"/>
-      <c r="O104" s="52"/>
+      <c r="M104" s="48"/>
+      <c r="N104" s="48"/>
+      <c r="O104" s="48"/>
       <c r="P104" s="5"/>
       <c r="Q104" s="5"/>
-      <c r="R104" s="45"/>
+      <c r="R104" s="42"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="34" t="n">
+      <c r="A105" s="43" t="n">
         <v>90</v>
       </c>
       <c r="B105" s="23"/>
-      <c r="C105" s="34" t="n">
+      <c r="C105" s="43" t="n">
         <v>88</v>
       </c>
       <c r="D105" s="23"/>
       <c r="E105" s="23" t="s">
-        <v>360</v>
-      </c>
-      <c r="F105" s="58" t="s">
+        <v>358</v>
+      </c>
+      <c r="F105" s="49" t="s">
         <v>168</v>
       </c>
-      <c r="G105" s="34" t="n">
+      <c r="G105" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H105" s="34" t="n">
+      <c r="H105" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I105" s="34" t="n">
+      <c r="I105" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="K105" s="47" t="s">
         <v>87</v>
@@ -9230,39 +9273,39 @@
       <c r="L105" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M105" s="52"/>
-      <c r="N105" s="52"/>
-      <c r="O105" s="52"/>
+      <c r="M105" s="48"/>
+      <c r="N105" s="48"/>
+      <c r="O105" s="48"/>
       <c r="P105" s="5"/>
       <c r="Q105" s="5"/>
-      <c r="R105" s="45"/>
+      <c r="R105" s="42"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="34" t="n">
+      <c r="A106" s="43" t="n">
         <v>91</v>
       </c>
       <c r="B106" s="23"/>
-      <c r="C106" s="34" t="n">
+      <c r="C106" s="43" t="n">
         <v>89</v>
       </c>
       <c r="D106" s="23"/>
       <c r="E106" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="F106" s="57" t="s">
+        <v>361</v>
+      </c>
+      <c r="G106" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="H106" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I106" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" s="5" t="s">
         <v>362</v>
-      </c>
-      <c r="F106" s="59" t="s">
-        <v>363</v>
-      </c>
-      <c r="G106" s="34" t="n">
-        <v>90</v>
-      </c>
-      <c r="H106" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I106" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="5" t="s">
-        <v>364</v>
       </c>
       <c r="K106" s="47" t="s">
         <v>87</v>
@@ -9270,39 +9313,39 @@
       <c r="L106" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M106" s="52"/>
-      <c r="N106" s="52"/>
-      <c r="O106" s="52"/>
+      <c r="M106" s="48"/>
+      <c r="N106" s="48"/>
+      <c r="O106" s="48"/>
       <c r="P106" s="5"/>
       <c r="Q106" s="5"/>
-      <c r="R106" s="45"/>
+      <c r="R106" s="42"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="34" t="n">
+      <c r="A107" s="43" t="n">
         <v>92</v>
       </c>
       <c r="B107" s="23"/>
-      <c r="C107" s="34" t="n">
+      <c r="C107" s="43" t="n">
         <v>90</v>
       </c>
       <c r="D107" s="23"/>
       <c r="E107" s="23" t="s">
-        <v>365</v>
-      </c>
-      <c r="F107" s="58" t="s">
+        <v>363</v>
+      </c>
+      <c r="F107" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="G107" s="34" t="n">
+      <c r="G107" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H107" s="34" t="n">
+      <c r="H107" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I107" s="34" t="n">
+      <c r="I107" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="K107" s="47" t="s">
         <v>87</v>
@@ -9310,231 +9353,231 @@
       <c r="L107" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M107" s="52"/>
-      <c r="N107" s="52"/>
-      <c r="O107" s="52"/>
+      <c r="M107" s="48"/>
+      <c r="N107" s="48"/>
+      <c r="O107" s="48"/>
       <c r="P107" s="5"/>
       <c r="Q107" s="5"/>
-      <c r="R107" s="53"/>
+      <c r="R107" s="50"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="40" t="n">
+      <c r="A108" s="34" t="n">
         <v>93</v>
       </c>
       <c r="B108" s="24"/>
-      <c r="C108" s="40"/>
+      <c r="C108" s="34"/>
       <c r="D108" s="24"/>
       <c r="E108" s="24"/>
       <c r="F108" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="G108" s="40" t="n">
+      <c r="G108" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H108" s="40" t="n">
+      <c r="H108" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I108" s="40"/>
+      <c r="I108" s="34"/>
       <c r="J108" s="8"/>
-      <c r="K108" s="43"/>
-      <c r="L108" s="43"/>
-      <c r="M108" s="50"/>
-      <c r="N108" s="50"/>
-      <c r="O108" s="50"/>
+      <c r="K108" s="41"/>
+      <c r="L108" s="41"/>
+      <c r="M108" s="52"/>
+      <c r="N108" s="52"/>
+      <c r="O108" s="52"/>
       <c r="P108" s="8"/>
       <c r="Q108" s="8"/>
-      <c r="R108" s="45"/>
+      <c r="R108" s="42"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="40" t="n">
+      <c r="A109" s="34" t="n">
         <v>94</v>
       </c>
       <c r="B109" s="24"/>
-      <c r="C109" s="40" t="n">
+      <c r="C109" s="34" t="n">
         <v>91</v>
       </c>
       <c r="D109" s="24"/>
       <c r="E109" s="24" t="s">
-        <v>367</v>
-      </c>
-      <c r="F109" s="56" t="s">
+        <v>365</v>
+      </c>
+      <c r="F109" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="G109" s="40" t="n">
+      <c r="G109" s="34" t="n">
         <v>93</v>
       </c>
-      <c r="H109" s="40" t="n">
+      <c r="H109" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I109" s="40" t="n">
+      <c r="I109" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="K109" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L109" s="43" t="s">
+        <v>366</v>
+      </c>
+      <c r="K109" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L109" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M109" s="50"/>
-      <c r="N109" s="50"/>
-      <c r="O109" s="50"/>
+      <c r="M109" s="52"/>
+      <c r="N109" s="52"/>
+      <c r="O109" s="52"/>
       <c r="P109" s="8"/>
       <c r="Q109" s="8"/>
-      <c r="R109" s="45"/>
+      <c r="R109" s="42"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="40" t="n">
+      <c r="A110" s="34" t="n">
         <v>95</v>
       </c>
       <c r="B110" s="24"/>
-      <c r="C110" s="40" t="n">
+      <c r="C110" s="34" t="n">
         <v>92</v>
       </c>
       <c r="D110" s="24"/>
       <c r="E110" s="24" t="s">
-        <v>369</v>
-      </c>
-      <c r="F110" s="56" t="s">
+        <v>367</v>
+      </c>
+      <c r="F110" s="40" t="s">
         <v>173</v>
       </c>
-      <c r="G110" s="40" t="n">
+      <c r="G110" s="34" t="n">
         <v>93</v>
       </c>
-      <c r="H110" s="40" t="n">
+      <c r="H110" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I110" s="40" t="n">
+      <c r="I110" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="K110" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L110" s="43" t="s">
+        <v>368</v>
+      </c>
+      <c r="K110" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L110" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M110" s="50"/>
-      <c r="N110" s="50"/>
-      <c r="O110" s="50"/>
+      <c r="M110" s="52"/>
+      <c r="N110" s="52"/>
+      <c r="O110" s="52"/>
       <c r="P110" s="8"/>
       <c r="Q110" s="8"/>
-      <c r="R110" s="45"/>
+      <c r="R110" s="42"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="40" t="n">
+      <c r="A111" s="34" t="n">
         <v>96</v>
       </c>
       <c r="B111" s="24"/>
-      <c r="C111" s="40" t="n">
+      <c r="C111" s="34" t="n">
         <v>93</v>
       </c>
       <c r="D111" s="24"/>
       <c r="E111" s="24" t="s">
-        <v>371</v>
-      </c>
-      <c r="F111" s="56" t="s">
+        <v>369</v>
+      </c>
+      <c r="F111" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="G111" s="40" t="n">
+      <c r="G111" s="34" t="n">
         <v>93</v>
       </c>
-      <c r="H111" s="40" t="n">
+      <c r="H111" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I111" s="40" t="n">
+      <c r="I111" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="K111" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L111" s="43" t="s">
+        <v>370</v>
+      </c>
+      <c r="K111" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L111" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M111" s="50"/>
-      <c r="N111" s="43" t="s">
+      <c r="M111" s="52"/>
+      <c r="N111" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="O111" s="50"/>
+      <c r="O111" s="52"/>
       <c r="P111" s="8"/>
       <c r="Q111" s="8"/>
-      <c r="R111" s="45"/>
+      <c r="R111" s="42"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="40" t="n">
+      <c r="A112" s="34" t="n">
         <v>97</v>
       </c>
       <c r="B112" s="24"/>
-      <c r="C112" s="40" t="n">
+      <c r="C112" s="34" t="n">
         <v>94</v>
       </c>
       <c r="D112" s="24"/>
       <c r="E112" s="24" t="s">
-        <v>373</v>
-      </c>
-      <c r="F112" s="56" t="s">
+        <v>371</v>
+      </c>
+      <c r="F112" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="G112" s="40" t="n">
+      <c r="G112" s="34" t="n">
         <v>93</v>
       </c>
-      <c r="H112" s="40" t="n">
+      <c r="H112" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I112" s="40" t="n">
+      <c r="I112" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="K112" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L112" s="43" t="s">
+        <v>372</v>
+      </c>
+      <c r="K112" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L112" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M112" s="50"/>
-      <c r="N112" s="43" t="s">
+      <c r="M112" s="52"/>
+      <c r="N112" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="O112" s="50"/>
+      <c r="O112" s="52"/>
       <c r="P112" s="8"/>
       <c r="Q112" s="8"/>
-      <c r="R112" s="45"/>
+      <c r="R112" s="42"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="34" t="n">
+      <c r="A113" s="43" t="n">
         <v>98</v>
       </c>
       <c r="B113" s="23"/>
-      <c r="C113" s="34" t="n">
+      <c r="C113" s="43" t="n">
         <v>95</v>
       </c>
       <c r="D113" s="23"/>
       <c r="E113" s="23" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F113" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="G113" s="34" t="n">
+      <c r="G113" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H113" s="34" t="n">
+      <c r="H113" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I113" s="34" t="n">
+      <c r="I113" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J113" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K113" s="47" t="s">
         <v>87</v>
@@ -9542,39 +9585,39 @@
       <c r="L113" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M113" s="52"/>
-      <c r="N113" s="52"/>
-      <c r="O113" s="52"/>
+      <c r="M113" s="48"/>
+      <c r="N113" s="48"/>
+      <c r="O113" s="48"/>
       <c r="P113" s="5"/>
       <c r="Q113" s="5"/>
-      <c r="R113" s="45"/>
+      <c r="R113" s="42"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="34" t="n">
+      <c r="A114" s="43" t="n">
         <v>99</v>
       </c>
       <c r="B114" s="23"/>
-      <c r="C114" s="34" t="n">
+      <c r="C114" s="43" t="n">
         <v>96</v>
       </c>
       <c r="D114" s="23"/>
       <c r="E114" s="23" t="s">
-        <v>377</v>
-      </c>
-      <c r="F114" s="58" t="s">
+        <v>375</v>
+      </c>
+      <c r="F114" s="49" t="s">
         <v>176</v>
       </c>
-      <c r="G114" s="34" t="n">
+      <c r="G114" s="43" t="n">
         <v>98</v>
       </c>
-      <c r="H114" s="34" t="n">
+      <c r="H114" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I114" s="34" t="n">
+      <c r="I114" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J114" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="K114" s="47" t="s">
         <v>87</v>
@@ -9582,158 +9625,158 @@
       <c r="L114" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M114" s="52"/>
-      <c r="N114" s="52"/>
-      <c r="O114" s="52"/>
+      <c r="M114" s="48"/>
+      <c r="N114" s="48"/>
+      <c r="O114" s="48"/>
       <c r="P114" s="5"/>
       <c r="Q114" s="5"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="40" t="n">
+      <c r="A115" s="34" t="n">
         <v>100</v>
       </c>
       <c r="B115" s="24"/>
-      <c r="C115" s="40"/>
+      <c r="C115" s="34"/>
       <c r="D115" s="24"/>
       <c r="E115" s="24"/>
       <c r="F115" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="G115" s="40" t="n">
+      <c r="G115" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H115" s="40" t="n">
+      <c r="H115" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I115" s="40"/>
+      <c r="I115" s="34"/>
       <c r="J115" s="8"/>
-      <c r="K115" s="43"/>
-      <c r="L115" s="43"/>
-      <c r="M115" s="50"/>
-      <c r="N115" s="50"/>
-      <c r="O115" s="50"/>
+      <c r="K115" s="41"/>
+      <c r="L115" s="41"/>
+      <c r="M115" s="52"/>
+      <c r="N115" s="52"/>
+      <c r="O115" s="52"/>
       <c r="P115" s="8"/>
       <c r="Q115" s="8"/>
-      <c r="R115" s="45"/>
+      <c r="R115" s="42"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="40" t="n">
+      <c r="A116" s="34" t="n">
         <v>101</v>
       </c>
       <c r="B116" s="24"/>
-      <c r="C116" s="40" t="n">
+      <c r="C116" s="34" t="n">
         <v>97</v>
       </c>
       <c r="D116" s="24"/>
       <c r="E116" s="24" t="s">
-        <v>379</v>
-      </c>
-      <c r="F116" s="56" t="s">
+        <v>377</v>
+      </c>
+      <c r="F116" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="G116" s="40" t="n">
+      <c r="G116" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="H116" s="40" t="n">
+      <c r="H116" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I116" s="40" t="n">
+      <c r="I116" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J116" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="K116" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L116" s="43" t="s">
+        <v>378</v>
+      </c>
+      <c r="K116" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L116" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M116" s="50"/>
-      <c r="N116" s="50"/>
-      <c r="O116" s="50"/>
+      <c r="M116" s="52"/>
+      <c r="N116" s="52"/>
+      <c r="O116" s="52"/>
       <c r="P116" s="8"/>
       <c r="Q116" s="8"/>
-      <c r="R116" s="45"/>
+      <c r="R116" s="42"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="40" t="n">
+      <c r="A117" s="34" t="n">
         <v>102</v>
       </c>
       <c r="B117" s="24"/>
-      <c r="C117" s="40" t="n">
+      <c r="C117" s="34" t="n">
         <v>98</v>
       </c>
       <c r="D117" s="24"/>
       <c r="E117" s="24" t="s">
-        <v>381</v>
-      </c>
-      <c r="F117" s="56" t="s">
+        <v>379</v>
+      </c>
+      <c r="F117" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="G117" s="40" t="n">
+      <c r="G117" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="H117" s="40" t="n">
+      <c r="H117" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I117" s="40" t="n">
+      <c r="I117" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J117" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="K117" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L117" s="43" t="s">
+        <v>380</v>
+      </c>
+      <c r="K117" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L117" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M117" s="50"/>
-      <c r="N117" s="50"/>
-      <c r="O117" s="50"/>
+      <c r="M117" s="52"/>
+      <c r="N117" s="52"/>
+      <c r="O117" s="52"/>
       <c r="P117" s="8"/>
       <c r="Q117" s="8"/>
-      <c r="R117" s="45"/>
+      <c r="R117" s="42"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="40"/>
+      <c r="A118" s="34"/>
       <c r="B118" s="24"/>
-      <c r="C118" s="40" t="n">
+      <c r="C118" s="34" t="n">
         <v>99</v>
       </c>
       <c r="D118" s="24"/>
       <c r="E118" s="24" t="s">
+        <v>379</v>
+      </c>
+      <c r="F118" s="24"/>
+      <c r="G118" s="34"/>
+      <c r="H118" s="34"/>
+      <c r="I118" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="F118" s="24"/>
-      <c r="G118" s="40"/>
-      <c r="H118" s="40"/>
-      <c r="I118" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="K118" s="50"/>
-      <c r="L118" s="43" t="s">
+      <c r="K118" s="52"/>
+      <c r="L118" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="M118" s="50"/>
-      <c r="N118" s="43" t="s">
+      <c r="M118" s="52"/>
+      <c r="N118" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="O118" s="50"/>
+      <c r="O118" s="52"/>
       <c r="P118" s="8"/>
       <c r="Q118" s="8"/>
-      <c r="R118" s="53"/>
+      <c r="R118" s="50"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="34" t="n">
+      <c r="A119" s="43" t="n">
         <v>103</v>
       </c>
       <c r="B119" s="23"/>
-      <c r="C119" s="34"/>
+      <c r="C119" s="43"/>
       <c r="D119" s="23"/>
       <c r="E119" s="23" t="n">
         <v>43</v>
@@ -9741,49 +9784,49 @@
       <c r="F119" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="G119" s="34" t="n">
+      <c r="G119" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H119" s="34" t="n">
+      <c r="H119" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I119" s="34"/>
+      <c r="I119" s="43"/>
       <c r="J119" s="5"/>
       <c r="K119" s="47"/>
-      <c r="L119" s="52"/>
-      <c r="M119" s="52"/>
-      <c r="N119" s="52"/>
-      <c r="O119" s="52"/>
+      <c r="L119" s="48"/>
+      <c r="M119" s="48"/>
+      <c r="N119" s="48"/>
+      <c r="O119" s="48"/>
       <c r="P119" s="5"/>
       <c r="Q119" s="5"/>
-      <c r="R119" s="45"/>
+      <c r="R119" s="42"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="34" t="n">
+      <c r="A120" s="43" t="n">
         <v>104</v>
       </c>
       <c r="B120" s="23"/>
-      <c r="C120" s="34" t="n">
+      <c r="C120" s="43" t="n">
         <v>100</v>
       </c>
       <c r="D120" s="23"/>
       <c r="E120" s="23" t="s">
-        <v>384</v>
-      </c>
-      <c r="F120" s="58" t="s">
+        <v>382</v>
+      </c>
+      <c r="F120" s="49" t="s">
         <v>181</v>
       </c>
-      <c r="G120" s="34" t="n">
+      <c r="G120" s="43" t="n">
         <v>103</v>
       </c>
-      <c r="H120" s="34" t="n">
+      <c r="H120" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I120" s="34" t="n">
+      <c r="I120" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J120" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="K120" s="47" t="s">
         <v>87</v>
@@ -9791,39 +9834,39 @@
       <c r="L120" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M120" s="52"/>
-      <c r="N120" s="52"/>
-      <c r="O120" s="52"/>
+      <c r="M120" s="48"/>
+      <c r="N120" s="48"/>
+      <c r="O120" s="48"/>
       <c r="P120" s="5"/>
       <c r="Q120" s="5"/>
-      <c r="R120" s="45"/>
+      <c r="R120" s="42"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="34" t="n">
+      <c r="A121" s="43" t="n">
         <v>105</v>
       </c>
       <c r="B121" s="23"/>
-      <c r="C121" s="34" t="n">
+      <c r="C121" s="43" t="n">
         <v>101</v>
       </c>
       <c r="D121" s="23"/>
       <c r="E121" s="23" t="s">
-        <v>386</v>
-      </c>
-      <c r="F121" s="58" t="s">
+        <v>384</v>
+      </c>
+      <c r="F121" s="49" t="s">
         <v>182</v>
       </c>
-      <c r="G121" s="34" t="n">
+      <c r="G121" s="43" t="n">
         <v>103</v>
       </c>
-      <c r="H121" s="34" t="n">
+      <c r="H121" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I121" s="34" t="n">
+      <c r="I121" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J121" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K121" s="47" t="s">
         <v>87</v>
@@ -9831,41 +9874,41 @@
       <c r="L121" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M121" s="52"/>
+      <c r="M121" s="48"/>
       <c r="N121" s="47" t="s">
         <v>232</v>
       </c>
-      <c r="O121" s="52"/>
+      <c r="O121" s="48"/>
       <c r="P121" s="5"/>
       <c r="Q121" s="5"/>
-      <c r="R121" s="45"/>
+      <c r="R121" s="42"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="34" t="n">
+      <c r="A122" s="43" t="n">
         <v>106</v>
       </c>
       <c r="B122" s="23"/>
-      <c r="C122" s="34" t="n">
+      <c r="C122" s="43" t="n">
         <v>102</v>
       </c>
       <c r="D122" s="23"/>
       <c r="E122" s="23" t="s">
-        <v>388</v>
-      </c>
-      <c r="F122" s="58" t="s">
+        <v>386</v>
+      </c>
+      <c r="F122" s="49" t="s">
         <v>183</v>
       </c>
-      <c r="G122" s="34" t="n">
+      <c r="G122" s="43" t="n">
         <v>103</v>
       </c>
-      <c r="H122" s="34" t="n">
+      <c r="H122" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I122" s="34" t="n">
+      <c r="I122" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J122" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="K122" s="47" t="s">
         <v>87</v>
@@ -9873,116 +9916,116 @@
       <c r="L122" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="M122" s="52"/>
+      <c r="M122" s="48"/>
       <c r="N122" s="47" t="s">
         <v>232</v>
       </c>
-      <c r="O122" s="52"/>
+      <c r="O122" s="48"/>
       <c r="P122" s="5"/>
       <c r="Q122" s="5"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="40" t="n">
+      <c r="A123" s="34" t="n">
         <v>107</v>
       </c>
       <c r="B123" s="24"/>
-      <c r="C123" s="40" t="n">
+      <c r="C123" s="34" t="n">
         <v>103</v>
       </c>
       <c r="D123" s="24"/>
       <c r="E123" s="24" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F123" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G123" s="40" t="n">
+      <c r="G123" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="H123" s="40" t="n">
+      <c r="H123" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I123" s="40" t="n">
+      <c r="I123" s="34" t="n">
         <v>1</v>
       </c>
       <c r="J123" s="8"/>
-      <c r="K123" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="L123" s="50"/>
-      <c r="M123" s="50"/>
-      <c r="N123" s="50"/>
-      <c r="O123" s="50"/>
+      <c r="K123" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="L123" s="52"/>
+      <c r="M123" s="52"/>
+      <c r="N123" s="52"/>
+      <c r="O123" s="52"/>
       <c r="P123" s="8"/>
       <c r="Q123" s="8"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="34" t="n">
+      <c r="A124" s="43" t="n">
         <v>108</v>
       </c>
       <c r="B124" s="23"/>
-      <c r="C124" s="34" t="n">
+      <c r="C124" s="43" t="n">
         <v>104</v>
       </c>
       <c r="D124" s="23"/>
       <c r="E124" s="23" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F124" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="G124" s="34" t="n">
+      <c r="G124" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H124" s="34" t="n">
+      <c r="H124" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I124" s="34" t="n">
+      <c r="I124" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J124" s="5"/>
       <c r="K124" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="L124" s="52"/>
-      <c r="M124" s="52"/>
-      <c r="N124" s="52"/>
-      <c r="O124" s="52"/>
+      <c r="L124" s="48"/>
+      <c r="M124" s="48"/>
+      <c r="N124" s="48"/>
+      <c r="O124" s="48"/>
       <c r="P124" s="5"/>
       <c r="Q124" s="5"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="34" t="n">
+      <c r="A125" s="43" t="n">
         <v>109</v>
       </c>
       <c r="B125" s="23"/>
-      <c r="C125" s="34" t="n">
+      <c r="C125" s="43" t="n">
         <v>105</v>
       </c>
       <c r="D125" s="23"/>
       <c r="E125" s="23" t="s">
-        <v>392</v>
-      </c>
-      <c r="F125" s="58" t="s">
+        <v>390</v>
+      </c>
+      <c r="F125" s="49" t="s">
         <v>185</v>
       </c>
-      <c r="G125" s="34" t="n">
+      <c r="G125" s="43" t="n">
         <v>108</v>
       </c>
-      <c r="H125" s="34" t="n">
+      <c r="H125" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I125" s="34" t="n">
+      <c r="I125" s="43" t="n">
         <v>1</v>
       </c>
       <c r="J125" s="5"/>
       <c r="K125" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="L125" s="52"/>
-      <c r="M125" s="52"/>
-      <c r="N125" s="52"/>
-      <c r="O125" s="52"/>
+      <c r="L125" s="48"/>
+      <c r="M125" s="48"/>
+      <c r="N125" s="48"/>
+      <c r="O125" s="48"/>
       <c r="P125" s="5"/>
       <c r="Q125" s="5"/>
     </row>
@@ -9994,6 +10037,10 @@
       <c r="A127" s="28"/>
       <c r="C127" s="28"/>
     </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="K5" r:id="rId2" display="PDF"/>
@@ -10027,53 +10074,53 @@
     <hyperlink ref="K23" r:id="rId30" display="PDF"/>
     <hyperlink ref="L23" r:id="rId31" display="VIDEO"/>
     <hyperlink ref="N23" r:id="rId32" display="CODE"/>
-    <hyperlink ref="K24" r:id="rId33" display="PDF"/>
-    <hyperlink ref="L25" r:id="rId34" display="VIDEO"/>
-    <hyperlink ref="N25" r:id="rId35" display="CODE"/>
-    <hyperlink ref="K26" r:id="rId36" display="CODE"/>
-    <hyperlink ref="L26" r:id="rId37" display="VIDEO"/>
-    <hyperlink ref="K27" r:id="rId38" display="PDF"/>
-    <hyperlink ref="L27" r:id="rId39" display="VIDEO"/>
-    <hyperlink ref="K28" r:id="rId40" display="PDF"/>
-    <hyperlink ref="L28" r:id="rId41" display="VIDEO"/>
-    <hyperlink ref="K29" r:id="rId42" display="PDF"/>
-    <hyperlink ref="L29" r:id="rId43" display="VIDEO"/>
-    <hyperlink ref="M29" r:id="rId44" display="VIDEO"/>
-    <hyperlink ref="K30" r:id="rId45" display="VIDEO"/>
-    <hyperlink ref="K31" r:id="rId46" display="PDF"/>
-    <hyperlink ref="L31" r:id="rId47" display="VIDEO"/>
-    <hyperlink ref="K32" r:id="rId48" display="PDF"/>
-    <hyperlink ref="L32" r:id="rId49" display="VIDEO"/>
-    <hyperlink ref="K33" r:id="rId50" display="PDF"/>
-    <hyperlink ref="L33" r:id="rId51" display="VIDEO"/>
-    <hyperlink ref="K34" r:id="rId52" display="PDF"/>
-    <hyperlink ref="L34" r:id="rId53" display="VIDEO"/>
-    <hyperlink ref="K36" r:id="rId54" display="PDF"/>
-    <hyperlink ref="L36" r:id="rId55" display="VIDEO"/>
-    <hyperlink ref="K37" r:id="rId56" display="PDF"/>
-    <hyperlink ref="L37" r:id="rId57" display="VIDEO"/>
-    <hyperlink ref="K38" r:id="rId58" display="PDF"/>
-    <hyperlink ref="K39" r:id="rId59" display="PDF"/>
-    <hyperlink ref="L39" r:id="rId60" display="VIDEO"/>
-    <hyperlink ref="N39" r:id="rId61" display="CODE"/>
-    <hyperlink ref="O39" r:id="rId62" display="CODE"/>
-    <hyperlink ref="L40" r:id="rId63" display="VIDEO"/>
-    <hyperlink ref="N40" r:id="rId64" display="CODE"/>
-    <hyperlink ref="K41" r:id="rId65" display="CODE"/>
-    <hyperlink ref="L41" r:id="rId66" display="VIDEO"/>
-    <hyperlink ref="K43" r:id="rId67" display="PDF"/>
-    <hyperlink ref="L43" r:id="rId68" display="VIDEO"/>
-    <hyperlink ref="N43" r:id="rId69" display="CODE"/>
-    <hyperlink ref="K44" r:id="rId70" display="PDF"/>
-    <hyperlink ref="K45" r:id="rId71" display="CODE"/>
-    <hyperlink ref="K46" r:id="rId72" display="CODE"/>
-    <hyperlink ref="K47" r:id="rId73" display="VIDEO"/>
+    <hyperlink ref="L25" r:id="rId33" display="VIDEO"/>
+    <hyperlink ref="N25" r:id="rId34" display="CODE"/>
+    <hyperlink ref="N26" r:id="rId35" display="CODE"/>
+    <hyperlink ref="N27" r:id="rId36" display="CODE"/>
+    <hyperlink ref="K28" r:id="rId37" display="PDF"/>
+    <hyperlink ref="L29" r:id="rId38" display="VIDEO"/>
+    <hyperlink ref="N29" r:id="rId39" display="CODE"/>
+    <hyperlink ref="K30" r:id="rId40" display="CODE"/>
+    <hyperlink ref="L30" r:id="rId41" display="VIDEO"/>
+    <hyperlink ref="K31" r:id="rId42" display="PDF"/>
+    <hyperlink ref="L31" r:id="rId43" display="VIDEO"/>
+    <hyperlink ref="K32" r:id="rId44" display="PDF"/>
+    <hyperlink ref="L32" r:id="rId45" display="VIDEO"/>
+    <hyperlink ref="K33" r:id="rId46" display="PDF"/>
+    <hyperlink ref="L33" r:id="rId47" display="VIDEO"/>
+    <hyperlink ref="M33" r:id="rId48" display="VIDEO"/>
+    <hyperlink ref="K34" r:id="rId49" display="VIDEO"/>
+    <hyperlink ref="K35" r:id="rId50" display="PDF"/>
+    <hyperlink ref="L35" r:id="rId51" display="VIDEO"/>
+    <hyperlink ref="K36" r:id="rId52" display="PDF"/>
+    <hyperlink ref="L36" r:id="rId53" display="VIDEO"/>
+    <hyperlink ref="K37" r:id="rId54" display="PDF"/>
+    <hyperlink ref="L37" r:id="rId55" display="VIDEO"/>
+    <hyperlink ref="K38" r:id="rId56" display="PDF"/>
+    <hyperlink ref="L38" r:id="rId57" display="VIDEO"/>
+    <hyperlink ref="K39" r:id="rId58" display="PDF"/>
+    <hyperlink ref="L39" r:id="rId59" display="VIDEO"/>
+    <hyperlink ref="N39" r:id="rId60" display="CODE"/>
+    <hyperlink ref="O39" r:id="rId61" display="CODE"/>
+    <hyperlink ref="L40" r:id="rId62" display="VIDEO"/>
+    <hyperlink ref="N40" r:id="rId63" display="CODE"/>
+    <hyperlink ref="K41" r:id="rId64" display="CODE"/>
+    <hyperlink ref="L41" r:id="rId65" display="VIDEO"/>
+    <hyperlink ref="K43" r:id="rId66" display="PDF"/>
+    <hyperlink ref="L43" r:id="rId67" display="VIDEO"/>
+    <hyperlink ref="K44" r:id="rId68" display="PDF"/>
+    <hyperlink ref="L44" r:id="rId69" display="VIDEO"/>
+    <hyperlink ref="K45" r:id="rId70" display="PDF"/>
+    <hyperlink ref="K47" r:id="rId71" display="PDF"/>
+    <hyperlink ref="L47" r:id="rId72" display="VIDEO"/>
+    <hyperlink ref="N47" r:id="rId73" display="CODE"/>
     <hyperlink ref="K48" r:id="rId74" display="PDF"/>
-    <hyperlink ref="L48" r:id="rId75" display="VIDEO"/>
-    <hyperlink ref="N48" r:id="rId76" display="CODE"/>
-    <hyperlink ref="L50" r:id="rId77" display="VIDEO"/>
-    <hyperlink ref="N50" r:id="rId78" display="CODE"/>
-    <hyperlink ref="N51" r:id="rId79" display="CODE"/>
+    <hyperlink ref="K49" r:id="rId75" display="CODE"/>
+    <hyperlink ref="K50" r:id="rId76" display="CODE"/>
+    <hyperlink ref="K51" r:id="rId77" display="VIDEO"/>
+    <hyperlink ref="K52" r:id="rId78" display="PDF"/>
+    <hyperlink ref="L52" r:id="rId79" display="VIDEO"/>
     <hyperlink ref="N52" r:id="rId80" display="CODE"/>
     <hyperlink ref="K55" r:id="rId81" display="PDF"/>
     <hyperlink ref="K56" r:id="rId82" display="PDF"/>
@@ -10198,7 +10245,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.15"/>
@@ -10239,7 +10286,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10249,7 +10296,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -10264,18 +10311,18 @@
       <c r="B6" s="24"/>
       <c r="C6" s="8"/>
       <c r="E6" s="10" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
         <v>27</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10284,10 +10331,10 @@
       <c r="C7" s="8"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
@@ -10301,10 +10348,10 @@
       <c r="C8" s="8"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8" t="s">
@@ -10317,7 +10364,7 @@
       <c r="B9" s="24"/>
       <c r="C9" s="8"/>
       <c r="E9" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="5"/>
@@ -10326,7 +10373,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10335,7 +10382,7 @@
       <c r="C10" s="8"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>39</v>
@@ -10345,7 +10392,7 @@
         <v>45</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10354,17 +10401,17 @@
       <c r="C11" s="8"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10372,11 +10419,11 @@
       <c r="B12" s="24"/>
       <c r="C12" s="8"/>
       <c r="E12" s="10" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8" t="s">
@@ -10390,10 +10437,10 @@
       <c r="C13" s="8"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8" t="s">
@@ -10407,10 +10454,10 @@
       <c r="C14" s="8"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8" t="s">
@@ -10424,14 +10471,14 @@
       <c r="C15" s="8"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J15" s="8"/>
     </row>
@@ -10440,7 +10487,7 @@
       <c r="B16" s="24"/>
       <c r="C16" s="8"/>
       <c r="E16" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="5"/>
@@ -10453,7 +10500,7 @@
       <c r="B17" s="24"/>
       <c r="C17" s="8"/>
       <c r="E17" s="10" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="8"/>
@@ -10476,13 +10523,13 @@
         <v>79</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>83</v>

--- a/server_nestjs/src/storage/Kompetenzraster.xlsx
+++ b/server_nestjs/src/storage/Kompetenzraster.xlsx
@@ -62,7 +62,7 @@
     <author> </author>
   </authors>
   <commentList>
-    <comment ref="L6" authorId="0">
+    <comment ref="L5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="438">
   <si>
     <t xml:space="preserve">Voraussetzungen lt. Modulhandbuch</t>
   </si>
@@ -676,25 +676,31 @@
     <t xml:space="preserve">ContentElement</t>
   </si>
   <si>
-    <t xml:space="preserve">Content Beschreibung</t>
+    <t xml:space="preserve">ContentNode Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContentNode Beschreibung</t>
   </si>
   <si>
     <t xml:space="preserve">Funktionale Programmierung mit Python</t>
   </si>
   <si>
-    <t xml:space="preserve">Pro Zeile eine ContentNode = ContentView</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,3</t>
   </si>
   <si>
     <t xml:space="preserve">2,3,4</t>
   </si>
   <si>
+    <t xml:space="preserve">Einführung in Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class aptent taciti sociosqu ad litora torquent per conubia nostra, per inceptos himenaeos. Nullam imperdiet mauris vitae dignissim pulvinar. Nulla tempor id orci vel luctus. Vivamus ut rhoncus ligula. In hac habitasse platea dictumst. Curabitur neque orci, imperdiet non dictum eu, accumsan non arcu. Nullam condimentum est non dolor mattis. </t>
+  </si>
+  <si>
     <t xml:space="preserve">2,3,5</t>
   </si>
   <si>
-    <t xml:space="preserve">Installation von python</t>
+    <t xml:space="preserve">Installation von Python</t>
   </si>
   <si>
     <t xml:space="preserve">Python ist eine vielseitige und populäre Programmiersprache, die sich besonders für Data Science und Machine Learning eignet und durch ihre Einfachheit und die Verfügbarkeit vieler Bibliotheken auszeichnet. Für die Installation von Python wird häufig die Anaconda-Distribution empfohlen, die neben Python auch viele nützliche Bibliotheken und Entwicklungsumgebungen wie Spyder und Jupyter-Notebooks enthält, wobei Miniconda eine schlankere Alternative darstellt.</t>
@@ -703,12 +709,21 @@
     <t xml:space="preserve">VIDEO</t>
   </si>
   <si>
+    <t xml:space="preserve">Python Installationsanleitung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morbi massa leo, ultricies ut dolor scelerisque, luctus tincidunt ligula. Curabitur nec lacus at libero ornare varius sit amet ac neque. Aliquam erat volutpat. Phasellus consectetur lectus consectetur sagittis consequat. Integer varius eu diam sit amet tristique. Cras facilisis pellentesque nisi egestas porttitor. Aenean ut ante posuere, consequat justo nec.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,6</t>
   </si>
   <si>
     <t xml:space="preserve">Python-Variablen sind Namen, die auf Speicherorte verweisen und Daten eines bestimmten Typs enthalten, wobei der Wert einer Variablen im Laufe eines Programms verändert werden kann. Python ist eine dynamisch typisierte Sprache, was bedeutet, dass der Datentyp einer Variablen nicht explizit deklariert werden muss und sich während der Laufzeit ändern kann, wobei Variablennamen sinnvoll gewählt und Groß- und Kleinschreibung beachtet werden sollten.</t>
   </si>
   <si>
+    <t xml:space="preserve">Lorem ipsum dolor sit amet, consectetur adipiscing elit. In congue nisl nunc, a facilisis risus malesuada et. Vestibulum nec faucibus diam. Nulla in lacus elementum, volutpat dui sed, mattis nunc. Suspendisse dolor nisi, laoreet in mi eu, efficitur scelerisque lorem. Vestibulum tristique tincidunt elit, eu euismod neque eleifend sed. Fusce congue dapibus nunc, a fringilla velit accumsan non. Praesent a sem in lacus aliquet hendrerit ac vitae sem. Aliquam id. </t>
+  </si>
+  <si>
     <t xml:space="preserve">2,6,7</t>
   </si>
   <si>
@@ -724,6 +739,9 @@
     <t xml:space="preserve">In Python sind Strings eine Sequenz von Zeichen, die in einfachen, doppelten oder dreifachen Anführungszeichen definiert werden können, wobei letztere auch Zeilenumbrüche und Anführungszeichen im Text erlauben. Strings sind in Python unveränderlich (immutable), unterstützen aber eine Vielzahl von Operationen wie Konkatenation, Wiederholung, Indizierung und eingebaute Methoden wie split, replace und format, um nur einige zu nennen.</t>
   </si>
   <si>
+    <t xml:space="preserve">Strings</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,8,10</t>
   </si>
   <si>
@@ -748,6 +766,9 @@
     <t xml:space="preserve">In Python gibt es drei Arten von Zahlen: Integer (ganze Zahlen), Floats (Gleitkommazahlen) und komplexe Zahlen. Während Integer und Floats für alltägliche Berechnungen genutzt werden, wobei Floats aufgrund des IEEE 754 Standards zu Rundungsfehlern führen können, sind komplexe Zahlen mit einem imaginären Teil (in Python mit 'j' gekennzeichnet) ein speziellerer Datentyp, der seltener verwendet wird.</t>
   </si>
   <si>
+    <t xml:space="preserve">Komplexe Zahlen</t>
+  </si>
+  <si>
     <t xml:space="preserve">11,12,13</t>
   </si>
   <si>
@@ -784,25 +805,34 @@
     <t xml:space="preserve">Python Kontrollstrukturen umfassen If-Statements, die mit Vergleichsoperatoren wie gleich (==), nicht gleich (!=), größer (&gt;), kleiner (&lt;), größer gleich (&gt;=) und kleiner gleich (&lt;=) arbeiten, sowie logische Operatoren wie and, or und not, um boolesche Ausdrücke zu verknüpfen. Wichtig ist dabei die korrekte Einrückung, da sie die Programmlogik bestimmt, und Schleifen wie die while-Schleife, die zur Wiederholung von Code-Blöcken verwendet wird.</t>
   </si>
   <si>
+    <t xml:space="preserve">Kontrolle über Programme</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,18,19</t>
   </si>
   <si>
     <t xml:space="preserve">In Python ermöglichen if-else-Kontrollstrukturen die Ausführung von Codeblöcken basierend auf Bedingungen, die zu wahren (True) oder falschen (False) Werten evaluiert werden. Ein if-Statement führt den nachfolgenden Codeblock aus, wenn die Bedingung wahr ist, während ein else-Statement den Codeblock ausführt, wenn alle vorherigen Bedingungen falsch sind; elif-Statements bieten zusätzliche Bedingungsüberprüfungen.</t>
   </si>
   <si>
+    <t xml:space="preserve">if/else am Kartenspiel Beispiel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,18,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,18,20,21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">while</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In dem Code-Beispiel zur Python-Kontrollstruktur `while` wird eine Schleife verwendet, um ein Kartenspiel zu simulieren, bei dem Karten gezogen werden, bis keine mehr übrig sind. Die `while`-Schleife prüft dabei kontinuierlich, ob die Liste der Preiskarten noch Elemente enthält, und entfernt mit der `pop`-Methode jeweils das letzte Element, bis die Liste leer ist und die Schleife beendet wird.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CODE</t>
   </si>
   <si>
-    <t xml:space="preserve">2,18,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,18,20,21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">while</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In dem Code-Beispiel zur Python-Kontrollstruktur `while` wird eine Schleife verwendet, um ein Kartenspiel zu simulieren, bei dem Karten gezogen werden, bis keine mehr übrig sind. Die `while`-Schleife prüft dabei kontinuierlich, ob die Liste der Preiskarten noch Elemente enthält, und entfernt mit der `pop`-Methode jeweils das letzte Element, bis die Liste leer ist und die Schleife beendet wird.</t>
+    <t xml:space="preserve">while am Kartenspiel Beispiel</t>
   </si>
   <si>
     <t xml:space="preserve">2,18,20,22</t>
@@ -814,12 +844,18 @@
     <t xml:space="preserve">In Python ermöglichen for-Schleifen das Durchlaufen von iterierbaren Objekten wie Listen, indem man eine Variable über die Elemente iterieren lässt, beispielsweise mit `for element in my_list`. Die `range`-Funktion wird oft in for-Schleifen verwendet, um über eine Sequenz von Zahlen zu iterieren, wobei man Start-, Stopp- und Schrittweite angeben kann, um beispielsweise mit `for i in range(1, 10, 3)` die Zahlen 1, 4 und 7 zu durchlaufen.</t>
   </si>
   <si>
+    <t xml:space="preserve">For-Schleifen</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,39</t>
   </si>
   <si>
     <t xml:space="preserve">2,39,40</t>
   </si>
   <si>
+    <t xml:space="preserve">Listen</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,39,41</t>
   </si>
   <si>
@@ -832,27 +868,42 @@
     <t xml:space="preserve">Python-Funktionen ermöglichen es, Codeblöcke zu isolieren und in sinnvolle Abschnitte aufzuteilen, was die Übersichtlichkeit und Wartbarkeit von Programmen erheblich verbessert, insbesondere bei großen Projekten. Sie werden mit dem Schlüsselwort `def` definiert, können beliebig viele Eingabeargumente enthalten und mit `return` Werte zurückgeben, die dann im Hauptprogramm verwendet werden können.</t>
   </si>
   <si>
+    <t xml:space="preserve">Funktionen am Beispiel Addieren und Verdoppeln</t>
+  </si>
+  <si>
     <t xml:space="preserve">In dem Codebeispiel werden Teile eines Kartenspiels in Python-Funktionen ausgelagert, um den Code übersichtlicher und modularer zu gestalten. Die Funktionen `StrategieSpieler1` und `StrategieSpieler2` werden definiert, um die Strategie der Spieler zu kapseln, wobei die Funktionen Eingabeparameter wie den Wert der Preiskarte und die verbleibenden Karten des Spielers erhalten und die ausgewählte Karte zurückgeben.</t>
   </si>
   <si>
+    <t xml:space="preserve">Funktionen am Beispiel Goofspiel</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,23,24</t>
   </si>
   <si>
     <t xml:space="preserve">Python-Funktionen können mit Docstrings dokumentiert werden, die mit drei Anführungszeichen beginnen und eine systematische Beschreibung der Funktion, ihrer Parameter und Rückgabewerte enthalten. Docstrings sind besonders hilfreich in größeren Projekten, da sie es ermöglichen, die Funktionsweise von Code auch Monate später noch zu verstehen, und können mit der `help()`-Funktion abgerufen werden, um Nutzern und Entwicklern die Verwendung der Funktionen zu erleichtern.</t>
   </si>
   <si>
+    <t xml:space="preserve">Docstring und Kommentare</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,23,25</t>
   </si>
   <si>
     <t xml:space="preserve">Python-Funktionen können sowohl Positional Arguments als auch Keyword Arguments akzeptieren, wobei die Reihenfolge bei Positional Arguments wichtig ist und bei Keyword Arguments durch die explizite Benennung irrelevant wird. Zusätzlich können Funktionen in Python mit `*args` und `**kwargs` eine variable Anzahl von Positional bzw. Keyword Arguments empfangen, was die Flexibilität bei der Übergabe von Argumenten erhöht.</t>
   </si>
   <si>
+    <t xml:space="preserve">Eingabeargumente</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,23,26</t>
   </si>
   <si>
     <t xml:space="preserve">In Python können Funktionen als Variablen gespeichert und verwendet werden, was bedeutet, dass man eine Funktion einer Variablen zuweisen und dann diese Variable wie eine Funktion aufrufen kann. Dies ermöglicht es, Funktionen als Argumente an andere Funktionen zu übergeben und sogenannte Higher-Order Functions zu erstellen, die Funktionen höherer Ordnung sind und von anderen Funktionen abhängen können.</t>
   </si>
   <si>
+    <t xml:space="preserve">Funktionen als Variablen am Beispiel Goofspiel</t>
+  </si>
+  <si>
     <t xml:space="preserve">5, 23</t>
   </si>
   <si>
@@ -880,6 +931,9 @@
     <t xml:space="preserve">In Python können Variablen entweder mutable (veränderbar) oder immutable (unveränderbar) sein. Globale Variablen, die außerhalb von Funktionen definiert werden, können innerhalb von Funktionen gelesen und, wenn sie mutable sind, auch verändert werden, wobei die Änderungen dann global sichtbar sind; lokale Variablen hingegen sind nur innerhalb ihrer Funktion sichtbar und existieren außerhalb nicht.</t>
   </si>
   <si>
+    <t xml:space="preserve">Mutable und Immutable Variablen</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,34</t>
   </si>
   <si>
@@ -889,9 +943,15 @@
     <t xml:space="preserve">Rekursion in Python wird oft verwendet, um Probleme zu lösen, die sich in kleinere Instanzen desselben Problems aufteilen lassen, wie beispielsweise die Berechnung der Summe aller Zahlen bis zu einer gegebenen Zahl N oder die Fakultät einer Zahl. Im Transkript werden rekursive Funktionen zur Lösung solcher Probleme diskutiert, wobei die Basisfälle (Abbruchbedingungen) und die rekursiven Aufrufe, die das Problem in kleinere Teile zerlegen, zentrale Elemente sind. Ein weiteres Beispiel ist die rekursive Bestimmung von Primzahlen und die Primfaktorzerlegung einer Zahl, die ebenfalls im Transkript behandelt werden.</t>
   </si>
   <si>
+    <t xml:space="preserve">Rekursion mit Code-Beispielen</t>
+  </si>
+  <si>
     <t xml:space="preserve">In dem Codebeispiel wird die Rekursion anhand verschiedener mathematischer Probleme in Python demonstriert, wie die Summe aller Zahlen bis N, die Fakultät einer Zahl und die Überprüfung, ob eine Zahl eine Primzahl ist. Die Rekursion wird dabei als Methode zur Problemlösung verwendet, indem ein großes Problem in kleinere Instanzen heruntergebrochen wird, bis eine Instanz erreicht ist, die direkt gelöst werden kann.</t>
   </si>
   <si>
+    <t xml:space="preserve">Rekursion am Beispiel Goofspiel</t>
+  </si>
+  <si>
     <t xml:space="preserve">23,29,34</t>
   </si>
   <si>
@@ -907,6 +967,9 @@
     <t xml:space="preserve">Das Transkript behandelt die Unterscheidung zwischen lokalen und globalen Variablen in Python und wie sie innerhalb von Funktionen verwendet werden können. Globale Variablen können innerhalb von Funktionen gelesen werden, wenn sie vorher definiert wurden, während lokale Variablen nur innerhalb der Funktion existieren und außerhalb nicht sichtbar sind. Es wird auch erklärt, wie man mit dem Schlüsselwort `global` eine lokale Variable in einer Funktion als global deklarieren kann, sodass Änderungen an ihr auch außerhalb der Funktion sichtbar sind.</t>
   </si>
   <si>
+    <t xml:space="preserve">Goofspiel funktionaler machen</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,31,33</t>
   </si>
   <si>
@@ -919,25 +982,28 @@
     <t xml:space="preserve">Der Befehl map nimmt eine Funktion und ein iterierbares Objekt (z.B. Liste oder Tupel) entgegen und wendet die Funktion auf jedes Element des iterierbaren Objektes an. Genauer, bekommen wir einen Iterator zurück über welchen wir iterieren können oder Methoden wie __next__() aufrufen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Beschreibung PDF</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,35,37</t>
   </si>
   <si>
-    <t xml:space="preserve">Beschreibung CODE 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beschreibung CODE 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beschreibung VIDEO</t>
+    <t xml:space="preserve">Filter am Code-Beispiel Strings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,35,37,40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter am Code-Beispiel Listen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter Vorlesungsaufzeichnung</t>
   </si>
   <si>
     <t xml:space="preserve">2,35,38</t>
   </si>
   <si>
     <t xml:space="preserve">Der Befehl reduce nimmt auch eine Funktion und iterierbares Objekt (z.B. Liste oder Tupel) entgegen. Die Funktion muss zwei Elemente in dem iterierbaren Objekt auf eines abbilden und reduziert nun durch sukzessives Anwenden der Funktion das gesamte iterierbare Objekt auf ein Element.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reduce</t>
   </si>
   <si>
     <t xml:space="preserve">Objektorientierte Programmierung mit Java</t>
@@ -1637,14 +1703,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1746,7 +1804,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="5" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1754,7 +1812,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="5" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1802,6 +1860,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1896,7 +1962,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I245"/>
-  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.15"/>
@@ -5379,21 +5445,21 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:S1048576"/>
-  <sheetFormatPr defaultColWidth="10.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="17.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="25" width="16.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="43.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="31.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="25.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="11" style="0" width="12.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="11.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="63.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5445,4788 +5511,4838 @@
       <c r="P1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="Q1" s="1"/>
+      <c r="Q1" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="R1" s="27"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28"/>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="28" t="n">
+        <v>2</v>
+      </c>
       <c r="B2" s="29"/>
       <c r="C2" s="28"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="I2" s="28"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="G2" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" s="31"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="S2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="30" t="n">
+      <c r="A3" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="34" t="s">
+        <v>197</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="32" t="n">
+      <c r="H3" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="36"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="15"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="G3" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30" t="n">
+      <c r="H4" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="12"/>
+      <c r="K4" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
+      <c r="O4" s="37"/>
+      <c r="P4" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="R4" s="40"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="33"/>
+      <c r="E5" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="K5" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L5" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M5" s="39"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="R5" s="40"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="I3" s="33"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="S3" s="15" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="34" t="n">
+      <c r="B6" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="34" t="n">
+      <c r="D6" s="42"/>
+      <c r="E6" s="42" t="s">
+        <v>207</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="37" t="n">
+      <c r="H6" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="38"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="15"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="n">
+      <c r="I6" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="K6" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M6" s="45"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="R6" s="40"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="35"/>
-      <c r="E5" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="F5" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="G5" s="34" t="n">
+      <c r="D7" s="42"/>
+      <c r="E7" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="12"/>
-      <c r="K5" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="42"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="34" t="n">
+      <c r="H7" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="K7" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M7" s="45"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="48"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="32"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="49"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="L8" s="50"/>
+      <c r="M8" s="50"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="50"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="40"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" s="24"/>
+      <c r="C9" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="35"/>
-      <c r="E6" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="G6" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="K6" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L6" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M6" s="41"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="42"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="43" t="n">
+      <c r="D9" s="24"/>
+      <c r="E9" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="F9" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44" t="s">
-        <v>203</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="I9" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="K9" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L9" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="K7" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L7" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M7" s="47"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="48"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="42"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" s="43" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44" t="s">
-        <v>205</v>
-      </c>
-      <c r="F8" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="G8" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="K8" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L8" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M8" s="47"/>
-      <c r="N8" s="48"/>
-      <c r="O8" s="48"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="50"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="G9" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" s="51"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="L9" s="52"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="52"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="8"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="50"/>
+      <c r="P9" s="8" t="s">
+        <v>215</v>
+      </c>
       <c r="Q9" s="8"/>
-      <c r="R9" s="42"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="34" t="n">
-        <v>9</v>
+      <c r="R9" s="48"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="32" t="n">
+        <v>10</v>
       </c>
       <c r="B10" s="24"/>
-      <c r="C10" s="34" t="n">
-        <v>5</v>
-      </c>
+      <c r="C10" s="32"/>
       <c r="D10" s="24"/>
       <c r="E10" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="F10" s="53" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" s="34" t="n">
+        <v>216</v>
+      </c>
+      <c r="F10" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="H10" s="54" t="n">
+      <c r="H10" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="K10" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L10" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M10" s="41"/>
-      <c r="N10" s="52"/>
-      <c r="O10" s="52"/>
+      <c r="I10" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="50"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
-      <c r="R10" s="50"/>
+      <c r="R10" s="40"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="34" t="n">
-        <v>10</v>
+      <c r="A11" s="32" t="n">
+        <v>11</v>
       </c>
       <c r="B11" s="24"/>
-      <c r="C11" s="34" t="n">
-        <v>6</v>
+      <c r="C11" s="32" t="n">
+        <v>7</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="24" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="34" t="n">
+        <v>133</v>
+      </c>
+      <c r="G11" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="K11" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M11" s="39"/>
+      <c r="N11" s="50"/>
+      <c r="O11" s="50"/>
+      <c r="P11" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="40"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B12" s="24"/>
+      <c r="C12" s="32" t="n">
         <v>8</v>
-      </c>
-      <c r="H11" s="54" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="52"/>
-      <c r="O11" s="52"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="42"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="34" t="n">
-        <v>7</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="F12" s="55" t="s">
-        <v>133</v>
-      </c>
-      <c r="G12" s="34" t="n">
+        <v>219</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="G12" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="H12" s="34" t="n">
+      <c r="H12" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="I12" s="34" t="n">
+      <c r="I12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="K12" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L12" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M12" s="41"/>
-      <c r="N12" s="52"/>
-      <c r="O12" s="52"/>
-      <c r="P12" s="8"/>
+        <v>220</v>
+      </c>
+      <c r="K12" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M12" s="39"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="8" t="s">
+        <v>134</v>
+      </c>
       <c r="Q12" s="8"/>
-      <c r="R12" s="42"/>
+      <c r="R12" s="40"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34" t="n">
-        <v>12</v>
+      <c r="A13" s="32" t="n">
+        <v>13</v>
       </c>
       <c r="B13" s="24"/>
-      <c r="C13" s="34" t="n">
-        <v>8</v>
+      <c r="C13" s="32" t="n">
+        <v>9</v>
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="F13" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="G13" s="34" t="n">
+        <v>221</v>
+      </c>
+      <c r="F13" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="G13" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="H13" s="34" t="n">
+      <c r="H13" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="34" t="n">
+      <c r="I13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="K13" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L13" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M13" s="41"/>
-      <c r="N13" s="52"/>
-      <c r="O13" s="52"/>
-      <c r="P13" s="8"/>
+        <v>223</v>
+      </c>
+      <c r="K13" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M13" s="39"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="Q13" s="8"/>
-      <c r="R13" s="42"/>
+      <c r="R13" s="40"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="34" t="n">
-        <v>9</v>
+      <c r="A14" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="C14" s="32" t="n">
+        <v>10</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="F14" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="G14" s="34" t="n">
+        <v>226</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="H14" s="34" t="n">
+      <c r="H14" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="34" t="n">
+      <c r="I14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="K14" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L14" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M14" s="41"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="8"/>
+        <v>227</v>
+      </c>
+      <c r="K14" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M14" s="39"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="50"/>
+      <c r="P14" s="8" t="s">
+        <v>101</v>
+      </c>
       <c r="Q14" s="8"/>
-      <c r="R14" s="42"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="C15" s="34" t="n">
-        <v>10</v>
+      <c r="R14" s="40"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="B15" s="24"/>
+      <c r="C15" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="F15" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="G15" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="H15" s="34" t="n">
+        <v>228</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="34" t="n">
+      <c r="I15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="K15" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L15" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M15" s="41"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="52"/>
-      <c r="P15" s="8"/>
+        <v>229</v>
+      </c>
+      <c r="K15" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L15" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M15" s="39"/>
+      <c r="N15" s="50"/>
+      <c r="O15" s="50"/>
+      <c r="P15" s="8" t="s">
+        <v>97</v>
+      </c>
       <c r="Q15" s="8"/>
-      <c r="R15" s="42"/>
+      <c r="R15" s="40"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34" t="n">
-        <v>16</v>
+      <c r="A16" s="32" t="n">
+        <v>17</v>
       </c>
       <c r="B16" s="24"/>
-      <c r="C16" s="34" t="n">
-        <v>12</v>
+      <c r="C16" s="32" t="n">
+        <v>13</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="F16" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" s="34" t="n">
+        <v>230</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="H16" s="34" t="n">
+      <c r="H16" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="34" t="n">
+      <c r="I16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="K16" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L16" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M16" s="41"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="52"/>
-      <c r="P16" s="8"/>
+        <v>231</v>
+      </c>
+      <c r="K16" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L16" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M16" s="39"/>
+      <c r="N16" s="50"/>
+      <c r="O16" s="50"/>
+      <c r="P16" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="Q16" s="8"/>
-      <c r="R16" s="42"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="34" t="n">
-        <v>17</v>
-      </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="34" t="n">
-        <v>13</v>
+      <c r="R16" s="40"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="C17" s="32" t="n">
+        <v>11</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="F17" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="34" t="n">
+        <v>233</v>
+      </c>
+      <c r="F17" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="G17" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="H17" s="34" t="n">
+      <c r="H17" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="I17" s="34" t="n">
+      <c r="I17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="K17" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L17" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M17" s="41"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="8"/>
+        <v>234</v>
+      </c>
+      <c r="K17" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L17" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M17" s="39"/>
+      <c r="N17" s="50"/>
+      <c r="O17" s="50"/>
+      <c r="P17" s="8" t="s">
+        <v>100</v>
+      </c>
       <c r="Q17" s="8"/>
-      <c r="R17" s="42"/>
+      <c r="R17" s="40"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="34" t="n">
+      <c r="A18" s="41" t="n">
+        <v>18</v>
+      </c>
+      <c r="B18" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" s="41" t="n">
+        <v>14</v>
+      </c>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="40"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="41" t="n">
+        <v>19</v>
+      </c>
+      <c r="B19" s="23"/>
+      <c r="C19" s="41" t="n">
         <v>15</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="C18" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="F18" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="G18" s="51" t="n">
-        <v>8</v>
-      </c>
-      <c r="H18" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="K18" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L18" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M18" s="41"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="52"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="42"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="43" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="56" t="n">
-        <v>8</v>
-      </c>
-      <c r="C19" s="43" t="n">
-        <v>14</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="G19" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="43" t="n">
+        <v>238</v>
+      </c>
+      <c r="F19" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="G19" s="41" t="n">
+        <v>18</v>
+      </c>
+      <c r="H19" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="43" t="n">
+      <c r="I19" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="K19" s="47"/>
-      <c r="L19" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="5"/>
+        <v>239</v>
+      </c>
+      <c r="K19" s="45"/>
+      <c r="L19" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M19" s="45"/>
+      <c r="N19" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="O19" s="45"/>
+      <c r="P19" s="5" t="s">
+        <v>240</v>
+      </c>
       <c r="Q19" s="5"/>
-      <c r="R19" s="42"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="43" t="n">
+      <c r="R19" s="48"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="B20" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="43" t="n">
-        <v>15</v>
-      </c>
-      <c r="D20" s="23"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="23" t="n">
+        <v>19</v>
+      </c>
       <c r="E20" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="F20" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="G20" s="43" t="n">
+        <v>241</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" s="41" t="n">
         <v>18</v>
       </c>
-      <c r="H20" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M20" s="47"/>
-      <c r="N20" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="O20" s="47"/>
+      <c r="H20" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="I20" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="20"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="46"/>
+      <c r="O20" s="46"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
-      <c r="R20" s="50"/>
+      <c r="R20" s="40"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="43" t="n">
+      <c r="A21" s="41" t="n">
+        <v>21</v>
+      </c>
+      <c r="B21" s="23"/>
+      <c r="C21" s="41" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="F21" s="55" t="s">
+        <v>243</v>
+      </c>
+      <c r="G21" s="41" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="C21" s="43" t="n">
-        <v>16</v>
-      </c>
-      <c r="D21" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="F21" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="G21" s="43" t="n">
+      <c r="H21" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K21" s="45"/>
+      <c r="L21" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M21" s="45"/>
+      <c r="N21" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="O21" s="45"/>
+      <c r="P21" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="40"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="41" t="n">
+        <v>22</v>
+      </c>
+      <c r="B22" s="23"/>
+      <c r="C22" s="41" t="n">
         <v>18</v>
-      </c>
-      <c r="H21" s="43" t="n">
-        <v>6</v>
-      </c>
-      <c r="I21" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="20"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="48"/>
-      <c r="M21" s="48"/>
-      <c r="N21" s="48"/>
-      <c r="O21" s="48"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="42"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="43" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="43" t="n">
-        <v>17</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="F22" s="57" t="s">
-        <v>235</v>
-      </c>
-      <c r="G22" s="43" t="n">
+        <v>247</v>
+      </c>
+      <c r="F22" s="55" t="s">
+        <v>248</v>
+      </c>
+      <c r="G22" s="41" t="n">
         <v>20</v>
       </c>
-      <c r="H22" s="43" t="n">
+      <c r="H22" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="I22" s="43" t="n">
+      <c r="I22" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="K22" s="47"/>
-      <c r="L22" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M22" s="47"/>
-      <c r="N22" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="O22" s="47"/>
-      <c r="P22" s="5"/>
+        <v>249</v>
+      </c>
+      <c r="K22" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L22" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M22" s="45"/>
+      <c r="N22" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="O22" s="45"/>
+      <c r="P22" s="5" t="s">
+        <v>250</v>
+      </c>
       <c r="Q22" s="5"/>
-      <c r="R22" s="42"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="43" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="43" t="n">
-        <v>18</v>
-      </c>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23" t="s">
-        <v>237</v>
+      <c r="R22" s="48"/>
+    </row>
+    <row r="23" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="56" t="n">
+        <v>39</v>
+      </c>
+      <c r="B23" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" s="56"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57" t="s">
+        <v>251</v>
       </c>
       <c r="F23" s="57" t="s">
-        <v>238</v>
-      </c>
-      <c r="G23" s="43" t="n">
+        <v>126</v>
+      </c>
+      <c r="G23" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" s="56"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="59"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="59"/>
+      <c r="O23" s="59"/>
+      <c r="P23" s="58"/>
+      <c r="Q23" s="58"/>
+      <c r="R23" s="60"/>
+    </row>
+    <row r="24" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="56" t="n">
+        <v>40</v>
+      </c>
+      <c r="B24" s="57"/>
+      <c r="C24" s="56" t="n">
+        <v>42</v>
+      </c>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57" t="s">
+        <v>252</v>
+      </c>
+      <c r="F24" s="62" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" s="56" t="n">
+        <v>39</v>
+      </c>
+      <c r="H24" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="58"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="63" t="s">
+        <v>204</v>
+      </c>
+      <c r="M24" s="59"/>
+      <c r="N24" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="O24" s="59"/>
+      <c r="P24" s="58" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q24" s="58"/>
+      <c r="R24" s="64"/>
+    </row>
+    <row r="25" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="56" t="n">
+        <v>41</v>
+      </c>
+      <c r="B25" s="57"/>
+      <c r="C25" s="56" t="n">
+        <v>43</v>
+      </c>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57" t="s">
+        <v>254</v>
+      </c>
+      <c r="F25" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="56" t="n">
+        <v>39</v>
+      </c>
+      <c r="H25" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="58"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="O25" s="59"/>
+      <c r="P25" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q25" s="58"/>
+      <c r="R25" s="64"/>
+    </row>
+    <row r="26" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="56" t="n">
+        <v>42</v>
+      </c>
+      <c r="B26" s="57"/>
+      <c r="C26" s="56" t="n">
+        <v>44</v>
+      </c>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57" t="s">
+        <v>255</v>
+      </c>
+      <c r="F26" s="62" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" s="56" t="n">
+        <v>39</v>
+      </c>
+      <c r="H26" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="58"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="O26" s="59"/>
+      <c r="P26" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q26" s="58"/>
+      <c r="R26" s="64"/>
+    </row>
+    <row r="27" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>8.39</v>
+      </c>
+      <c r="C27" s="32" t="n">
+        <v>19</v>
+      </c>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="G27" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="8"/>
+      <c r="K27" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L27" s="50"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="50"/>
+      <c r="O27" s="50"/>
+      <c r="P27" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="60"/>
+    </row>
+    <row r="28" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="32"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="32" t="n">
         <v>20</v>
-      </c>
-      <c r="H23" s="43" t="n">
-        <v>6</v>
-      </c>
-      <c r="I23" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="K23" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L23" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="O23" s="47"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="50"/>
-    </row>
-    <row r="24" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="58" t="n">
-        <v>39</v>
-      </c>
-      <c r="B24" s="59" t="n">
-        <v>8</v>
-      </c>
-      <c r="C24" s="58"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59" t="s">
-        <v>240</v>
-      </c>
-      <c r="F24" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="G24" s="58" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="58" t="n">
-        <v>6</v>
-      </c>
-      <c r="I24" s="58"/>
-      <c r="J24" s="60"/>
-      <c r="K24" s="61"/>
-      <c r="L24" s="61"/>
-      <c r="M24" s="61"/>
-      <c r="N24" s="61"/>
-      <c r="O24" s="61"/>
-      <c r="P24" s="60"/>
-      <c r="Q24" s="60"/>
-      <c r="R24" s="62"/>
-    </row>
-    <row r="25" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="58" t="n">
-        <v>40</v>
-      </c>
-      <c r="B25" s="59"/>
-      <c r="C25" s="58" t="n">
-        <v>42</v>
-      </c>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59" t="s">
-        <v>241</v>
-      </c>
-      <c r="F25" s="64" t="s">
-        <v>127</v>
-      </c>
-      <c r="G25" s="58" t="n">
-        <v>39</v>
-      </c>
-      <c r="H25" s="58" t="n">
-        <v>6</v>
-      </c>
-      <c r="I25" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="60"/>
-      <c r="K25" s="61"/>
-      <c r="L25" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="M25" s="61"/>
-      <c r="N25" s="65" t="s">
-        <v>232</v>
-      </c>
-      <c r="O25" s="61"/>
-      <c r="P25" s="60"/>
-      <c r="Q25" s="60"/>
-      <c r="R25" s="66"/>
-    </row>
-    <row r="26" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="58" t="n">
-        <v>41</v>
-      </c>
-      <c r="B26" s="59"/>
-      <c r="C26" s="58" t="n">
-        <v>43</v>
-      </c>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59" t="s">
-        <v>242</v>
-      </c>
-      <c r="F26" s="64" t="s">
-        <v>128</v>
-      </c>
-      <c r="G26" s="58" t="n">
-        <v>39</v>
-      </c>
-      <c r="H26" s="58" t="n">
-        <v>6</v>
-      </c>
-      <c r="I26" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="60"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="61"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="65" t="s">
-        <v>232</v>
-      </c>
-      <c r="O26" s="61"/>
-      <c r="P26" s="60"/>
-      <c r="Q26" s="60"/>
-      <c r="R26" s="66"/>
-    </row>
-    <row r="27" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="58" t="n">
-        <v>42</v>
-      </c>
-      <c r="B27" s="59"/>
-      <c r="C27" s="58" t="n">
-        <v>44</v>
-      </c>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59" t="s">
-        <v>243</v>
-      </c>
-      <c r="F27" s="64" t="s">
-        <v>129</v>
-      </c>
-      <c r="G27" s="58" t="n">
-        <v>39</v>
-      </c>
-      <c r="H27" s="58" t="n">
-        <v>6</v>
-      </c>
-      <c r="I27" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="60"/>
-      <c r="K27" s="61"/>
-      <c r="L27" s="61"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="65" t="s">
-        <v>232</v>
-      </c>
-      <c r="O27" s="61"/>
-      <c r="P27" s="60"/>
-      <c r="Q27" s="60"/>
-      <c r="R27" s="66"/>
-    </row>
-    <row r="28" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34" t="n">
-        <v>23</v>
-      </c>
-      <c r="B28" s="24" t="n">
-        <v>8.39</v>
-      </c>
-      <c r="C28" s="34" t="n">
-        <v>19</v>
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="F28" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="G28" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="I28" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="8"/>
-      <c r="K28" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L28" s="52"/>
-      <c r="M28" s="52"/>
-      <c r="N28" s="52"/>
-      <c r="O28" s="52"/>
-      <c r="P28" s="8"/>
+        <v>256</v>
+      </c>
+      <c r="F28" s="24"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="K28" s="50"/>
+      <c r="L28" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M28" s="39"/>
+      <c r="N28" s="39" t="s">
+        <v>245</v>
+      </c>
+      <c r="O28" s="39"/>
+      <c r="P28" s="8" t="s">
+        <v>258</v>
+      </c>
       <c r="Q28" s="8"/>
-      <c r="R28" s="62"/>
-    </row>
-    <row r="29" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="34"/>
+      <c r="R28" s="60"/>
+    </row>
+    <row r="29" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="32"/>
       <c r="B29" s="24"/>
-      <c r="C29" s="34" t="n">
-        <v>20</v>
+      <c r="C29" s="32" t="n">
+        <v>21</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="F29" s="24"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34" t="n">
+        <v>256</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="G29" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="K29" s="39" t="s">
         <v>245</v>
       </c>
-      <c r="K29" s="52"/>
-      <c r="L29" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M29" s="41"/>
-      <c r="N29" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="O29" s="41"/>
-      <c r="P29" s="8"/>
+      <c r="L29" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M29" s="39"/>
+      <c r="N29" s="50"/>
+      <c r="O29" s="50"/>
+      <c r="P29" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="Q29" s="8"/>
-      <c r="R29" s="62"/>
-    </row>
-    <row r="30" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="34"/>
+      <c r="R29" s="60"/>
+    </row>
+    <row r="30" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="32" t="n">
+        <v>24</v>
+      </c>
       <c r="B30" s="24"/>
-      <c r="C30" s="34" t="n">
-        <v>21</v>
+      <c r="C30" s="32" t="n">
+        <v>22</v>
       </c>
       <c r="D30" s="24"/>
       <c r="E30" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="F30" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="G30" s="34" t="n">
+        <v>261</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G30" s="32" t="n">
         <v>23</v>
       </c>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34" t="n">
+      <c r="H30" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="K30" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="L30" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M30" s="41"/>
-      <c r="N30" s="52"/>
-      <c r="O30" s="52"/>
-      <c r="P30" s="8"/>
+        <v>262</v>
+      </c>
+      <c r="K30" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L30" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M30" s="39"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="50"/>
+      <c r="P30" s="8" t="s">
+        <v>263</v>
+      </c>
       <c r="Q30" s="8"/>
-      <c r="R30" s="62"/>
-    </row>
-    <row r="31" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="34" t="n">
-        <v>24</v>
+      <c r="R30" s="60"/>
+    </row>
+    <row r="31" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="32" t="n">
+        <v>25</v>
       </c>
       <c r="B31" s="24"/>
-      <c r="C31" s="34" t="n">
-        <v>22</v>
+      <c r="C31" s="32" t="n">
+        <v>23</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="F31" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="G31" s="34" t="n">
+        <v>264</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="32" t="n">
         <v>23</v>
       </c>
-      <c r="H31" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I31" s="34" t="n">
+      <c r="H31" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="K31" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L31" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M31" s="41"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="52"/>
-      <c r="P31" s="8"/>
+        <v>265</v>
+      </c>
+      <c r="K31" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L31" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M31" s="39"/>
+      <c r="N31" s="50"/>
+      <c r="O31" s="50"/>
+      <c r="P31" s="8" t="s">
+        <v>266</v>
+      </c>
       <c r="Q31" s="8"/>
-      <c r="R31" s="62"/>
-    </row>
-    <row r="32" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="34" t="n">
+      <c r="R31" s="60"/>
+    </row>
+    <row r="32" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="B32" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="34" t="n">
-        <v>23</v>
+      <c r="C32" s="32" t="n">
+        <v>24</v>
       </c>
       <c r="D32" s="24"/>
       <c r="E32" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="F32" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="G32" s="34" t="n">
+        <v>267</v>
+      </c>
+      <c r="F32" s="65" t="s">
+        <v>112</v>
+      </c>
+      <c r="G32" s="49" t="n">
         <v>23</v>
       </c>
-      <c r="H32" s="34" t="n">
+      <c r="H32" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="I32" s="34" t="n">
+      <c r="I32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="K32" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L32" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M32" s="41"/>
-      <c r="N32" s="52"/>
-      <c r="O32" s="52"/>
-      <c r="P32" s="8"/>
+        <v>268</v>
+      </c>
+      <c r="K32" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L32" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M32" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="N32" s="50"/>
+      <c r="O32" s="50"/>
+      <c r="P32" s="8" t="s">
+        <v>112</v>
+      </c>
       <c r="Q32" s="8"/>
-      <c r="R32" s="62"/>
-    </row>
-    <row r="33" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="34" t="n">
-        <v>26</v>
-      </c>
-      <c r="B33" s="24" t="n">
+    </row>
+    <row r="33" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="32"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="32" t="n">
         <v>25</v>
-      </c>
-      <c r="C33" s="34" t="n">
-        <v>24</v>
       </c>
       <c r="D33" s="24"/>
       <c r="E33" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="F33" s="67" t="s">
-        <v>112</v>
-      </c>
-      <c r="G33" s="51" t="n">
+        <v>267</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="G33" s="32" t="n">
         <v>23</v>
       </c>
-      <c r="H33" s="51" t="n">
-        <v>6</v>
-      </c>
-      <c r="I33" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="K33" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L33" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M33" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="N33" s="52"/>
-      <c r="O33" s="52"/>
-      <c r="P33" s="8"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="8"/>
+      <c r="K33" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="L33" s="50"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="50"/>
+      <c r="O33" s="50"/>
+      <c r="P33" s="8" t="s">
+        <v>269</v>
+      </c>
       <c r="Q33" s="8"/>
-    </row>
-    <row r="34" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="34"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="34" t="n">
-        <v>25</v>
+      <c r="R33" s="60"/>
+    </row>
+    <row r="34" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="C34" s="32" t="n">
+        <v>26</v>
       </c>
       <c r="D34" s="24"/>
       <c r="E34" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="F34" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="G34" s="34" t="n">
-        <v>23</v>
-      </c>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="8"/>
-      <c r="K34" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="L34" s="52"/>
-      <c r="M34" s="52"/>
-      <c r="N34" s="52"/>
-      <c r="O34" s="52"/>
-      <c r="P34" s="8"/>
+        <v>271</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="G34" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="K34" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L34" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M34" s="50"/>
+      <c r="N34" s="50"/>
+      <c r="O34" s="50"/>
+      <c r="P34" s="8" t="s">
+        <v>114</v>
+      </c>
       <c r="Q34" s="8"/>
-      <c r="R34" s="62"/>
-    </row>
-    <row r="35" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="34" t="n">
+      <c r="R34" s="60"/>
+    </row>
+    <row r="35" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="32" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="C35" s="32" t="n">
         <v>27</v>
-      </c>
-      <c r="B35" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="C35" s="34" t="n">
-        <v>26</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="F35" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="G35" s="34" t="n">
+        <v>273</v>
+      </c>
+      <c r="F35" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="G35" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="H35" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I35" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="K35" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L35" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M35" s="50"/>
+      <c r="N35" s="50"/>
+      <c r="O35" s="50"/>
+      <c r="P35" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q35" s="8"/>
+      <c r="R35" s="60"/>
+    </row>
+    <row r="36" s="61" customFormat="true" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="41" t="n">
+        <v>29</v>
+      </c>
+      <c r="B36" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="C36" s="41" t="n">
+        <v>28</v>
+      </c>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="F36" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="G36" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I35" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="K35" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L35" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="8"/>
-      <c r="Q35" s="8"/>
-      <c r="R35" s="62"/>
-    </row>
-    <row r="36" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="34" t="n">
-        <v>28</v>
-      </c>
-      <c r="B36" s="24" t="n">
-        <v>26</v>
-      </c>
-      <c r="C36" s="34" t="n">
-        <v>27</v>
-      </c>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="F36" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="G36" s="34" t="n">
-        <v>23</v>
-      </c>
-      <c r="H36" s="34" t="n">
+      <c r="H36" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="I36" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="K36" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L36" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="52"/>
-      <c r="P36" s="8"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="62"/>
-    </row>
-    <row r="37" s="63" customFormat="true" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="43" t="n">
+      <c r="I36" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="K36" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L36" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M36" s="46"/>
+      <c r="N36" s="46"/>
+      <c r="O36" s="46"/>
+      <c r="P36" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="60"/>
+    </row>
+    <row r="37" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="B37" s="23"/>
+      <c r="C37" s="41" t="n">
         <v>29</v>
-      </c>
-      <c r="B37" s="23" t="n">
-        <v>23</v>
-      </c>
-      <c r="C37" s="43" t="n">
-        <v>28</v>
       </c>
       <c r="D37" s="23"/>
       <c r="E37" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="F37" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="G37" s="46" t="n">
+        <v>277</v>
+      </c>
+      <c r="F37" s="66" t="s">
+        <v>117</v>
+      </c>
+      <c r="G37" s="44" t="n">
+        <v>29</v>
+      </c>
+      <c r="H37" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="I37" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="K37" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L37" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M37" s="46"/>
+      <c r="N37" s="46"/>
+      <c r="O37" s="46"/>
+      <c r="P37" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="64"/>
+    </row>
+    <row r="38" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="56" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="57" t="n">
+        <v>23</v>
+      </c>
+      <c r="C38" s="56" t="n">
+        <v>33</v>
+      </c>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57" t="s">
+        <v>280</v>
+      </c>
+      <c r="F38" s="57" t="s">
+        <v>121</v>
+      </c>
+      <c r="G38" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="H37" s="46" t="n">
+      <c r="H38" s="56" t="n">
         <v>6</v>
       </c>
-      <c r="I37" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="K37" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L37" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M37" s="48"/>
-      <c r="N37" s="48"/>
-      <c r="O37" s="48"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="62"/>
-    </row>
-    <row r="38" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="43" t="n">
+      <c r="I38" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="58" t="s">
+        <v>281</v>
+      </c>
+      <c r="K38" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="L38" s="63" t="s">
+        <v>204</v>
+      </c>
+      <c r="M38" s="59"/>
+      <c r="N38" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="O38" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="P38" s="58" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q38" s="58"/>
+      <c r="R38" s="60"/>
+    </row>
+    <row r="39" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="56"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="56" t="n">
+        <v>34</v>
+      </c>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57" t="s">
+        <v>280</v>
+      </c>
+      <c r="F39" s="57"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="58" t="s">
+        <v>282</v>
+      </c>
+      <c r="K39" s="59"/>
+      <c r="L39" s="63" t="s">
+        <v>204</v>
+      </c>
+      <c r="M39" s="59"/>
+      <c r="N39" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="O39" s="63"/>
+      <c r="P39" s="58" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q39" s="58"/>
+      <c r="R39" s="60"/>
+    </row>
+    <row r="40" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="56"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="56" t="n">
+        <v>35</v>
+      </c>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57" t="s">
+        <v>280</v>
+      </c>
+      <c r="F40" s="62" t="s">
+        <v>109</v>
+      </c>
+      <c r="G40" s="56" t="n">
+        <v>34</v>
+      </c>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="58" t="s">
+        <v>284</v>
+      </c>
+      <c r="K40" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="L40" s="63" t="s">
+        <v>204</v>
+      </c>
+      <c r="M40" s="59"/>
+      <c r="N40" s="59"/>
+      <c r="O40" s="59"/>
+      <c r="P40" s="58" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q40" s="58"/>
+      <c r="R40" s="64"/>
+    </row>
+    <row r="41" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B41" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="C41" s="32"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="67" t="s">
+        <v>287</v>
+      </c>
+      <c r="F41" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I41" s="32"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="50"/>
+      <c r="L41" s="50"/>
+      <c r="M41" s="50"/>
+      <c r="N41" s="50"/>
+      <c r="O41" s="50"/>
+      <c r="P41" s="8"/>
+      <c r="Q41" s="8"/>
+      <c r="R41" s="60"/>
+    </row>
+    <row r="42" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="B42" s="24"/>
+      <c r="C42" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="B38" s="23"/>
-      <c r="C38" s="43" t="n">
-        <v>29</v>
-      </c>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="F38" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="G38" s="46" t="n">
-        <v>29</v>
-      </c>
-      <c r="H38" s="46" t="n">
+      <c r="D42" s="24"/>
+      <c r="E42" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="G42" s="32" t="n">
+        <v>31</v>
+      </c>
+      <c r="H42" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="I38" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="K38" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L38" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M38" s="48"/>
-      <c r="N38" s="48"/>
-      <c r="O38" s="48"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="66"/>
-    </row>
-    <row r="39" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="58" t="n">
-        <v>34</v>
-      </c>
-      <c r="B39" s="59" t="n">
+      <c r="I42" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="K42" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L42" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M42" s="50"/>
+      <c r="N42" s="50"/>
+      <c r="O42" s="50"/>
+      <c r="P42" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q42" s="8"/>
+      <c r="R42" s="60"/>
+    </row>
+    <row r="43" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="32"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="32" t="n">
+        <v>31</v>
+      </c>
+      <c r="D43" s="24"/>
+      <c r="E43" s="67" t="s">
+        <v>287</v>
+      </c>
+      <c r="F43" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="G43" s="32" t="n">
+        <v>31</v>
+      </c>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="K43" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L43" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M43" s="50"/>
+      <c r="N43" s="50"/>
+      <c r="O43" s="50"/>
+      <c r="P43" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q43" s="8"/>
+      <c r="R43" s="64"/>
+    </row>
+    <row r="44" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="32" t="n">
+        <v>33</v>
+      </c>
+      <c r="B44" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="C44" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="F44" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="G44" s="32" t="n">
+        <v>31</v>
+      </c>
+      <c r="H44" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I44" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="8"/>
+      <c r="K44" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L44" s="50"/>
+      <c r="M44" s="50"/>
+      <c r="N44" s="50"/>
+      <c r="O44" s="50"/>
+      <c r="P44" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q44" s="8"/>
+      <c r="R44" s="60"/>
+    </row>
+    <row r="45" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="41" t="n">
+        <v>35</v>
+      </c>
+      <c r="B45" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="C39" s="58" t="n">
-        <v>33</v>
-      </c>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59" t="s">
-        <v>262</v>
-      </c>
-      <c r="F39" s="59" t="s">
-        <v>121</v>
-      </c>
-      <c r="G39" s="58" t="n">
+      <c r="C45" s="41"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="G45" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="H39" s="58" t="n">
+      <c r="H45" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="I39" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="60" t="s">
-        <v>263</v>
-      </c>
-      <c r="K39" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="L39" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="M39" s="61"/>
-      <c r="N39" s="65" t="s">
-        <v>232</v>
-      </c>
-      <c r="O39" s="65" t="s">
-        <v>232</v>
-      </c>
-      <c r="P39" s="60"/>
-      <c r="Q39" s="60"/>
-      <c r="R39" s="62"/>
-    </row>
-    <row r="40" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="58"/>
-      <c r="B40" s="59"/>
-      <c r="C40" s="58" t="n">
-        <v>34</v>
-      </c>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59" t="s">
-        <v>262</v>
-      </c>
-      <c r="F40" s="59"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="K40" s="61"/>
-      <c r="L40" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="M40" s="61"/>
-      <c r="N40" s="65" t="s">
-        <v>232</v>
-      </c>
-      <c r="O40" s="65"/>
-      <c r="P40" s="60"/>
-      <c r="Q40" s="60"/>
-      <c r="R40" s="62"/>
-    </row>
-    <row r="41" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="58"/>
-      <c r="B41" s="59"/>
-      <c r="C41" s="58" t="n">
-        <v>35</v>
-      </c>
-      <c r="D41" s="59"/>
-      <c r="E41" s="59" t="s">
-        <v>262</v>
-      </c>
-      <c r="F41" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="G41" s="58" t="n">
-        <v>34</v>
-      </c>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="60" t="s">
-        <v>265</v>
-      </c>
-      <c r="K41" s="65" t="s">
-        <v>232</v>
-      </c>
-      <c r="L41" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="M41" s="61"/>
-      <c r="N41" s="61"/>
-      <c r="O41" s="61"/>
-      <c r="P41" s="60"/>
-      <c r="Q41" s="60"/>
-      <c r="R41" s="66"/>
-    </row>
-    <row r="42" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B42" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="69" t="s">
-        <v>267</v>
-      </c>
-      <c r="F42" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G42" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" s="51" t="n">
-        <v>6</v>
-      </c>
-      <c r="I42" s="34"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="52"/>
-      <c r="M42" s="52"/>
-      <c r="N42" s="52"/>
-      <c r="O42" s="52"/>
-      <c r="P42" s="8"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="62"/>
-    </row>
-    <row r="43" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="34" t="n">
-        <v>32</v>
-      </c>
-      <c r="B43" s="24"/>
-      <c r="C43" s="34" t="n">
-        <v>30</v>
-      </c>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="F43" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="G43" s="34" t="n">
-        <v>31</v>
-      </c>
-      <c r="H43" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="I43" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="K43" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L43" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M43" s="52"/>
-      <c r="N43" s="52"/>
-      <c r="O43" s="52"/>
-      <c r="P43" s="8"/>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="62"/>
-    </row>
-    <row r="44" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="34"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="34" t="n">
-        <v>31</v>
-      </c>
-      <c r="D44" s="24"/>
-      <c r="E44" s="69" t="s">
-        <v>267</v>
-      </c>
-      <c r="F44" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="G44" s="34" t="n">
-        <v>31</v>
-      </c>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="K44" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L44" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M44" s="52"/>
-      <c r="N44" s="52"/>
-      <c r="O44" s="52"/>
-      <c r="P44" s="8"/>
-      <c r="Q44" s="8"/>
-      <c r="R44" s="66"/>
-    </row>
-    <row r="45" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B45" s="24" t="n">
-        <v>32</v>
-      </c>
-      <c r="C45" s="34" t="n">
-        <v>32</v>
-      </c>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="F45" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="G45" s="34" t="n">
-        <v>31</v>
-      </c>
-      <c r="H45" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="I45" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="8"/>
-      <c r="K45" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L45" s="52"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="52"/>
-      <c r="O45" s="52"/>
-      <c r="P45" s="8"/>
-      <c r="Q45" s="8"/>
-      <c r="R45" s="62"/>
-    </row>
-    <row r="46" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="43" t="n">
-        <v>35</v>
-      </c>
-      <c r="B46" s="23" t="n">
-        <v>23</v>
-      </c>
-      <c r="C46" s="43"/>
+      <c r="I45" s="41"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="46"/>
+      <c r="L45" s="46"/>
+      <c r="M45" s="46"/>
+      <c r="N45" s="46"/>
+      <c r="O45" s="46"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
+      <c r="R45" s="60"/>
+    </row>
+    <row r="46" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B46" s="23"/>
+      <c r="C46" s="41" t="n">
+        <v>36</v>
+      </c>
       <c r="D46" s="23"/>
       <c r="E46" s="23" t="s">
-        <v>272</v>
-      </c>
-      <c r="F46" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="G46" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" s="43" t="n">
+        <v>294</v>
+      </c>
+      <c r="F46" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="G46" s="41" t="n">
+        <v>35</v>
+      </c>
+      <c r="H46" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="I46" s="43"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="48"/>
-      <c r="L46" s="48"/>
-      <c r="M46" s="48"/>
-      <c r="N46" s="48"/>
-      <c r="O46" s="48"/>
-      <c r="P46" s="5"/>
+      <c r="I46" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="K46" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L46" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M46" s="46"/>
+      <c r="N46" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="O46" s="46"/>
+      <c r="P46" s="5" t="s">
+        <v>123</v>
+      </c>
       <c r="Q46" s="5"/>
-      <c r="R46" s="62"/>
-    </row>
-    <row r="47" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="43" t="n">
-        <v>36</v>
+      <c r="R46" s="64"/>
+    </row>
+    <row r="47" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="41" t="n">
+        <v>37</v>
       </c>
       <c r="B47" s="23"/>
-      <c r="C47" s="43" t="n">
-        <v>36</v>
+      <c r="C47" s="41" t="n">
+        <v>37</v>
       </c>
       <c r="D47" s="23"/>
       <c r="E47" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="F47" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="G47" s="43" t="n">
+        <v>294</v>
+      </c>
+      <c r="F47" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="G47" s="41" t="n">
         <v>35</v>
       </c>
-      <c r="H47" s="43" t="n">
+      <c r="H47" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="I47" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="K47" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L47" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M47" s="48"/>
-      <c r="N47" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="O47" s="48"/>
-      <c r="P47" s="5"/>
+      <c r="I47" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="5"/>
+      <c r="K47" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L47" s="46"/>
+      <c r="M47" s="46"/>
+      <c r="N47" s="46"/>
+      <c r="O47" s="46"/>
+      <c r="P47" s="5" t="s">
+        <v>124</v>
+      </c>
       <c r="Q47" s="5"/>
-      <c r="R47" s="66"/>
-    </row>
-    <row r="48" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="43" t="n">
-        <v>37</v>
-      </c>
+      <c r="R47" s="64"/>
+    </row>
+    <row r="48" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="41"/>
       <c r="B48" s="23"/>
-      <c r="C48" s="43" t="n">
-        <v>37</v>
+      <c r="C48" s="41" t="n">
+        <v>38</v>
       </c>
       <c r="D48" s="23"/>
       <c r="E48" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="F48" s="49" t="s">
-        <v>124</v>
-      </c>
-      <c r="G48" s="43" t="n">
-        <v>35</v>
-      </c>
-      <c r="H48" s="43" t="n">
-        <v>6</v>
-      </c>
-      <c r="I48" s="43" t="n">
+        <v>296</v>
+      </c>
+      <c r="F48" s="47"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="41"/>
+      <c r="I48" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J48" s="5"/>
-      <c r="K48" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L48" s="48"/>
-      <c r="M48" s="48"/>
-      <c r="N48" s="48"/>
-      <c r="O48" s="48"/>
+      <c r="K48" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="L48" s="46"/>
+      <c r="M48" s="46"/>
+      <c r="N48" s="46"/>
+      <c r="O48" s="46"/>
       <c r="P48" s="5" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="Q48" s="5"/>
-      <c r="R48" s="66"/>
-    </row>
-    <row r="49" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="43"/>
+      <c r="R48" s="64"/>
+    </row>
+    <row r="49" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="41"/>
       <c r="B49" s="23"/>
-      <c r="C49" s="43" t="n">
-        <v>38</v>
+      <c r="C49" s="41" t="n">
+        <v>39</v>
       </c>
       <c r="D49" s="23"/>
       <c r="E49" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="F49" s="49"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="43"/>
-      <c r="I49" s="43" t="n">
+        <v>298</v>
+      </c>
+      <c r="F49" s="47"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J49" s="5"/>
-      <c r="K49" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="L49" s="48"/>
-      <c r="M49" s="48"/>
-      <c r="N49" s="48"/>
-      <c r="O49" s="48"/>
+      <c r="K49" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="L49" s="46"/>
+      <c r="M49" s="46"/>
+      <c r="N49" s="46"/>
+      <c r="O49" s="46"/>
       <c r="P49" s="5" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="Q49" s="5"/>
-      <c r="R49" s="66"/>
-    </row>
-    <row r="50" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="43"/>
+      <c r="R49" s="64"/>
+    </row>
+    <row r="50" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="41"/>
       <c r="B50" s="23"/>
-      <c r="C50" s="43" t="n">
-        <v>39</v>
+      <c r="C50" s="41" t="n">
+        <v>40</v>
       </c>
       <c r="D50" s="23"/>
       <c r="E50" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="F50" s="49"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="43"/>
-      <c r="I50" s="43" t="n">
+        <v>296</v>
+      </c>
+      <c r="F50" s="47"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J50" s="5"/>
-      <c r="K50" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="L50" s="48"/>
-      <c r="M50" s="48"/>
-      <c r="N50" s="48"/>
-      <c r="O50" s="48"/>
+      <c r="K50" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="L50" s="46"/>
+      <c r="M50" s="46"/>
+      <c r="N50" s="46"/>
+      <c r="O50" s="46"/>
       <c r="P50" s="5" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="Q50" s="5"/>
-      <c r="R50" s="66"/>
-    </row>
-    <row r="51" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="43"/>
+      <c r="R50" s="60"/>
+    </row>
+    <row r="51" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="41" t="n">
+        <v>38</v>
+      </c>
       <c r="B51" s="23"/>
-      <c r="C51" s="43" t="n">
-        <v>40</v>
+      <c r="C51" s="41" t="n">
+        <v>41</v>
       </c>
       <c r="D51" s="23"/>
       <c r="E51" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="F51" s="49"/>
-      <c r="G51" s="43"/>
-      <c r="H51" s="43"/>
-      <c r="I51" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="5"/>
-      <c r="K51" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="L51" s="48"/>
-      <c r="M51" s="48"/>
-      <c r="N51" s="48"/>
-      <c r="O51" s="48"/>
+        <v>301</v>
+      </c>
+      <c r="F51" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="G51" s="41" t="n">
+        <v>35</v>
+      </c>
+      <c r="H51" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="I51" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="K51" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L51" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M51" s="46"/>
+      <c r="N51" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="O51" s="46"/>
       <c r="P51" s="5" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="Q51" s="5"/>
-      <c r="R51" s="62"/>
-    </row>
-    <row r="52" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="43" t="n">
-        <v>38</v>
-      </c>
-      <c r="B52" s="23"/>
-      <c r="C52" s="43" t="n">
-        <v>41</v>
-      </c>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="F52" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="G52" s="43" t="n">
-        <v>35</v>
-      </c>
-      <c r="H52" s="43" t="n">
-        <v>6</v>
-      </c>
-      <c r="I52" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="K52" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L52" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M52" s="48"/>
-      <c r="N52" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="O52" s="48"/>
-      <c r="P52" s="5"/>
-      <c r="Q52" s="5"/>
-      <c r="R52" s="66"/>
-    </row>
-    <row r="53" s="63" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="28"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="28"/>
-      <c r="D53" s="29"/>
-      <c r="E53" s="29"/>
-      <c r="F53" s="29"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="0"/>
-      <c r="K53" s="25"/>
-      <c r="L53" s="25"/>
-      <c r="M53" s="25"/>
-      <c r="N53" s="25"/>
-      <c r="O53" s="25"/>
-      <c r="P53" s="0"/>
-      <c r="Q53" s="0"/>
-      <c r="R53" s="66"/>
+      <c r="R51" s="64"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="68" t="n">
+        <v>43</v>
+      </c>
+      <c r="B52" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="68"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="69" t="n">
+        <v>43</v>
+      </c>
+      <c r="F52" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="G52" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="68" t="n">
+        <v>5</v>
+      </c>
+      <c r="I52" s="68"/>
+      <c r="K52" s="25"/>
+      <c r="L52" s="25"/>
+      <c r="M52" s="25"/>
+      <c r="N52" s="25"/>
+      <c r="O52" s="25"/>
+      <c r="R52" s="48"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="32" t="n">
+        <v>44</v>
+      </c>
+      <c r="B53" s="24"/>
+      <c r="C53" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="G53" s="49" t="n">
+        <v>43</v>
+      </c>
+      <c r="H53" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="8"/>
+      <c r="K53" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L53" s="50"/>
+      <c r="M53" s="50"/>
+      <c r="N53" s="50"/>
+      <c r="O53" s="50"/>
+      <c r="P53" s="8"/>
+      <c r="Q53" s="8"/>
+      <c r="R53" s="48"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="28" t="n">
+      <c r="A54" s="41" t="n">
+        <v>45</v>
+      </c>
+      <c r="B54" s="23"/>
+      <c r="C54" s="41" t="n">
+        <v>46</v>
+      </c>
+      <c r="D54" s="23"/>
+      <c r="E54" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="F54" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="G54" s="41" t="n">
         <v>43</v>
       </c>
-      <c r="B54" s="29" t="n">
+      <c r="H54" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="28"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="29" t="n">
-        <v>43</v>
-      </c>
-      <c r="F54" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="G54" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="I54" s="28"/>
-      <c r="K54" s="25"/>
-      <c r="L54" s="25"/>
-      <c r="M54" s="25"/>
-      <c r="N54" s="25"/>
-      <c r="O54" s="25"/>
-      <c r="R54" s="50"/>
+      <c r="I54" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="5"/>
+      <c r="K54" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L54" s="46"/>
+      <c r="M54" s="46"/>
+      <c r="N54" s="46"/>
+      <c r="O54" s="46"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5"/>
+      <c r="R54" s="48"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="34" t="n">
-        <v>44</v>
+      <c r="A55" s="32" t="n">
+        <v>46</v>
       </c>
       <c r="B55" s="24"/>
-      <c r="C55" s="34" t="n">
-        <v>45</v>
+      <c r="C55" s="32" t="n">
+        <v>47</v>
       </c>
       <c r="D55" s="24"/>
       <c r="E55" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="F55" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="G55" s="51" t="n">
+        <v>307</v>
+      </c>
+      <c r="F55" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="G55" s="32" t="n">
         <v>43</v>
       </c>
-      <c r="H55" s="51" t="n">
+      <c r="H55" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I55" s="34" t="n">
+      <c r="I55" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J55" s="8"/>
-      <c r="K55" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L55" s="52"/>
-      <c r="M55" s="52"/>
-      <c r="N55" s="52"/>
-      <c r="O55" s="52"/>
+      <c r="K55" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L55" s="50"/>
+      <c r="M55" s="50"/>
+      <c r="N55" s="50"/>
+      <c r="O55" s="50"/>
       <c r="P55" s="8"/>
       <c r="Q55" s="8"/>
-      <c r="R55" s="50"/>
+      <c r="R55" s="48"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="43" t="n">
-        <v>45</v>
-      </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="43" t="n">
+      <c r="A56" s="32" t="n">
+        <v>47</v>
+      </c>
+      <c r="B56" s="24"/>
+      <c r="C56" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="F56" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="G56" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="F56" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="G56" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="H56" s="43" t="n">
+      <c r="H56" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="5"/>
-      <c r="K56" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L56" s="48"/>
-      <c r="M56" s="48"/>
-      <c r="N56" s="48"/>
-      <c r="O56" s="48"/>
-      <c r="P56" s="5"/>
-      <c r="Q56" s="5"/>
-      <c r="R56" s="50"/>
+      <c r="I56" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="8"/>
+      <c r="K56" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L56" s="50"/>
+      <c r="M56" s="50"/>
+      <c r="N56" s="50"/>
+      <c r="O56" s="50"/>
+      <c r="P56" s="8"/>
+      <c r="Q56" s="8"/>
+      <c r="R56" s="48"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="34" t="n">
-        <v>46</v>
-      </c>
-      <c r="B57" s="24"/>
-      <c r="C57" s="34" t="n">
+      <c r="A57" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="B57" s="24" t="n">
         <v>47</v>
+      </c>
+      <c r="C57" s="32" t="n">
+        <v>49</v>
       </c>
       <c r="D57" s="24"/>
       <c r="E57" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="F57" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="G57" s="34" t="n">
-        <v>43</v>
-      </c>
-      <c r="H57" s="34" t="n">
+        <v>309</v>
+      </c>
+      <c r="F57" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="G57" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="H57" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I57" s="34" t="n">
+      <c r="I57" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J57" s="8"/>
-      <c r="K57" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L57" s="52"/>
-      <c r="M57" s="52"/>
-      <c r="N57" s="52"/>
-      <c r="O57" s="52"/>
+      <c r="K57" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L57" s="50"/>
+      <c r="M57" s="50"/>
+      <c r="N57" s="50"/>
+      <c r="O57" s="50"/>
       <c r="P57" s="8"/>
       <c r="Q57" s="8"/>
-      <c r="R57" s="50"/>
+      <c r="R57" s="48"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="34" t="n">
-        <v>47</v>
+      <c r="A58" s="32" t="n">
+        <v>49</v>
       </c>
       <c r="B58" s="24"/>
-      <c r="C58" s="34" t="n">
-        <v>48</v>
+      <c r="C58" s="32" t="n">
+        <v>50</v>
       </c>
       <c r="D58" s="24"/>
       <c r="E58" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="F58" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="G58" s="34" t="n">
+        <v>310</v>
+      </c>
+      <c r="F58" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="G58" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="H58" s="34" t="n">
+      <c r="H58" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="34" t="n">
+      <c r="I58" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J58" s="8"/>
-      <c r="K58" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L58" s="52"/>
-      <c r="M58" s="52"/>
-      <c r="N58" s="52"/>
-      <c r="O58" s="52"/>
+      <c r="K58" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L58" s="50"/>
+      <c r="M58" s="50"/>
+      <c r="N58" s="50"/>
+      <c r="O58" s="50"/>
       <c r="P58" s="8"/>
       <c r="Q58" s="8"/>
-      <c r="R58" s="50"/>
+      <c r="R58" s="48"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="34" t="n">
-        <v>48</v>
-      </c>
-      <c r="B59" s="24" t="n">
-        <v>47</v>
-      </c>
-      <c r="C59" s="34" t="n">
-        <v>49</v>
+      <c r="A59" s="32" t="n">
+        <v>50</v>
+      </c>
+      <c r="B59" s="24"/>
+      <c r="C59" s="32" t="n">
+        <v>51</v>
       </c>
       <c r="D59" s="24"/>
       <c r="E59" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="F59" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="G59" s="34" t="n">
+        <v>311</v>
+      </c>
+      <c r="F59" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="G59" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="H59" s="34" t="n">
+      <c r="H59" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I59" s="34" t="n">
+      <c r="I59" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J59" s="8"/>
-      <c r="K59" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L59" s="52"/>
-      <c r="M59" s="52"/>
-      <c r="N59" s="52"/>
-      <c r="O59" s="52"/>
+      <c r="K59" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L59" s="50"/>
+      <c r="M59" s="50"/>
+      <c r="N59" s="50"/>
+      <c r="O59" s="50"/>
       <c r="P59" s="8"/>
       <c r="Q59" s="8"/>
-      <c r="R59" s="50"/>
+      <c r="R59" s="48"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="34" t="n">
+      <c r="A60" s="32" t="n">
+        <v>51</v>
+      </c>
+      <c r="B60" s="24" t="n">
         <v>49</v>
       </c>
-      <c r="B60" s="24"/>
-      <c r="C60" s="34" t="n">
-        <v>50</v>
+      <c r="C60" s="32" t="n">
+        <v>52</v>
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="F60" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="G60" s="34" t="n">
+        <v>312</v>
+      </c>
+      <c r="F60" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="G60" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="H60" s="34" t="n">
+      <c r="H60" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I60" s="34" t="n">
+      <c r="I60" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J60" s="8"/>
-      <c r="K60" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L60" s="52"/>
-      <c r="M60" s="52"/>
-      <c r="N60" s="52"/>
-      <c r="O60" s="52"/>
+      <c r="K60" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L60" s="50"/>
+      <c r="M60" s="50"/>
+      <c r="N60" s="39" t="s">
+        <v>245</v>
+      </c>
+      <c r="O60" s="50"/>
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
-      <c r="R60" s="50"/>
+      <c r="R60" s="48"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="34" t="n">
-        <v>50</v>
+      <c r="A61" s="32" t="n">
+        <v>52</v>
       </c>
       <c r="B61" s="24"/>
-      <c r="C61" s="34" t="n">
-        <v>51</v>
+      <c r="C61" s="32" t="n">
+        <v>53</v>
       </c>
       <c r="D61" s="24"/>
       <c r="E61" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="F61" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="G61" s="34" t="n">
-        <v>46</v>
-      </c>
-      <c r="H61" s="34" t="n">
+        <v>313</v>
+      </c>
+      <c r="F61" s="53" t="s">
+        <v>314</v>
+      </c>
+      <c r="G61" s="32" t="n">
+        <v>51</v>
+      </c>
+      <c r="H61" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I61" s="34" t="n">
+      <c r="I61" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J61" s="8"/>
-      <c r="K61" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L61" s="52"/>
-      <c r="M61" s="52"/>
-      <c r="N61" s="52"/>
-      <c r="O61" s="52"/>
+      <c r="K61" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L61" s="50"/>
+      <c r="M61" s="50"/>
+      <c r="N61" s="50"/>
+      <c r="O61" s="50"/>
       <c r="P61" s="8"/>
       <c r="Q61" s="8"/>
-      <c r="R61" s="50"/>
+      <c r="R61" s="48"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="34" t="n">
-        <v>51</v>
-      </c>
-      <c r="B62" s="24" t="n">
-        <v>49</v>
-      </c>
-      <c r="C62" s="34" t="n">
-        <v>52</v>
+      <c r="A62" s="32" t="n">
+        <v>53</v>
+      </c>
+      <c r="B62" s="24"/>
+      <c r="C62" s="32" t="n">
+        <v>54</v>
       </c>
       <c r="D62" s="24"/>
       <c r="E62" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="F62" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="G62" s="34" t="n">
-        <v>46</v>
-      </c>
-      <c r="H62" s="34" t="n">
+        <v>315</v>
+      </c>
+      <c r="F62" s="53" t="s">
+        <v>160</v>
+      </c>
+      <c r="G62" s="32" t="n">
+        <v>51</v>
+      </c>
+      <c r="H62" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I62" s="34" t="n">
+      <c r="I62" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J62" s="8"/>
-      <c r="K62" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L62" s="52"/>
-      <c r="M62" s="52"/>
-      <c r="N62" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="O62" s="52"/>
+      <c r="K62" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L62" s="50"/>
+      <c r="M62" s="50"/>
+      <c r="N62" s="50"/>
+      <c r="O62" s="50"/>
       <c r="P62" s="8"/>
       <c r="Q62" s="8"/>
-      <c r="R62" s="50"/>
+      <c r="R62" s="40"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="34" t="n">
-        <v>52</v>
+      <c r="A63" s="32" t="n">
+        <v>54</v>
       </c>
       <c r="B63" s="24"/>
-      <c r="C63" s="34" t="n">
-        <v>53</v>
+      <c r="C63" s="32" t="n">
+        <v>55</v>
       </c>
       <c r="D63" s="24"/>
       <c r="E63" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="F63" s="55" t="s">
-        <v>292</v>
-      </c>
-      <c r="G63" s="34" t="n">
-        <v>51</v>
-      </c>
-      <c r="H63" s="34" t="n">
+        <v>316</v>
+      </c>
+      <c r="F63" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="G63" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="H63" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I63" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="8"/>
-      <c r="K63" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L63" s="52"/>
-      <c r="M63" s="52"/>
-      <c r="N63" s="52"/>
-      <c r="O63" s="52"/>
+      <c r="I63" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="K63" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L63" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M63" s="50"/>
+      <c r="N63" s="50"/>
+      <c r="O63" s="50"/>
       <c r="P63" s="8"/>
       <c r="Q63" s="8"/>
-      <c r="R63" s="50"/>
+      <c r="R63" s="40"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="34" t="n">
-        <v>53</v>
+      <c r="A64" s="32" t="n">
+        <v>55</v>
       </c>
       <c r="B64" s="24"/>
-      <c r="C64" s="34" t="n">
-        <v>54</v>
+      <c r="C64" s="32" t="n">
+        <v>56</v>
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="F64" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="G64" s="34" t="n">
-        <v>51</v>
-      </c>
-      <c r="H64" s="34" t="n">
+        <v>318</v>
+      </c>
+      <c r="F64" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="G64" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="H64" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I64" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="8"/>
-      <c r="K64" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L64" s="52"/>
-      <c r="M64" s="52"/>
-      <c r="N64" s="52"/>
-      <c r="O64" s="52"/>
+      <c r="I64" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="K64" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L64" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M64" s="50"/>
+      <c r="N64" s="50"/>
+      <c r="O64" s="50"/>
       <c r="P64" s="8"/>
       <c r="Q64" s="8"/>
-      <c r="R64" s="42"/>
+      <c r="R64" s="40"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="34" t="n">
-        <v>54</v>
-      </c>
-      <c r="B65" s="24"/>
-      <c r="C65" s="34" t="n">
-        <v>55</v>
-      </c>
-      <c r="D65" s="24"/>
-      <c r="E65" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="F65" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="G65" s="34" t="n">
-        <v>46</v>
-      </c>
-      <c r="H65" s="34" t="n">
+      <c r="A65" s="41" t="n">
+        <v>56</v>
+      </c>
+      <c r="B65" s="23"/>
+      <c r="C65" s="41" t="n">
+        <v>57</v>
+      </c>
+      <c r="D65" s="23"/>
+      <c r="E65" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="F65" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G65" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="H65" s="70" t="n">
         <v>2</v>
       </c>
-      <c r="I65" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="K65" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L65" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M65" s="52"/>
-      <c r="N65" s="52"/>
-      <c r="O65" s="52"/>
-      <c r="P65" s="8"/>
-      <c r="Q65" s="8"/>
-      <c r="R65" s="42"/>
+      <c r="I65" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="K65" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L65" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M65" s="46"/>
+      <c r="N65" s="46"/>
+      <c r="O65" s="46"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="5"/>
+      <c r="R65" s="48"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="34" t="n">
-        <v>55</v>
+      <c r="A66" s="32" t="n">
+        <v>57</v>
       </c>
       <c r="B66" s="24"/>
-      <c r="C66" s="34" t="n">
-        <v>56</v>
-      </c>
+      <c r="C66" s="32"/>
       <c r="D66" s="24"/>
       <c r="E66" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="F66" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="G66" s="34" t="n">
-        <v>46</v>
-      </c>
-      <c r="H66" s="34" t="n">
+        <v>322</v>
+      </c>
+      <c r="F66" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G66" s="32" t="n">
+        <v>43</v>
+      </c>
+      <c r="H66" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I66" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="K66" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L66" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M66" s="52"/>
-      <c r="N66" s="52"/>
-      <c r="O66" s="52"/>
+      <c r="I66" s="32"/>
+      <c r="J66" s="8"/>
+      <c r="K66" s="39"/>
+      <c r="L66" s="50"/>
+      <c r="M66" s="50"/>
+      <c r="N66" s="50"/>
+      <c r="O66" s="50"/>
       <c r="P66" s="8"/>
       <c r="Q66" s="8"/>
-      <c r="R66" s="42"/>
+      <c r="R66" s="40"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="43" t="n">
-        <v>56</v>
-      </c>
-      <c r="B67" s="23"/>
-      <c r="C67" s="43" t="n">
+      <c r="A67" s="32" t="n">
+        <v>58</v>
+      </c>
+      <c r="B67" s="24"/>
+      <c r="C67" s="32" t="n">
+        <v>58</v>
+      </c>
+      <c r="D67" s="24"/>
+      <c r="E67" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="F67" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="G67" s="32" t="n">
         <v>57</v>
       </c>
-      <c r="D67" s="23"/>
-      <c r="E67" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="F67" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="G67" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="H67" s="70" t="n">
+      <c r="H67" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I67" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="K67" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L67" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M67" s="48"/>
-      <c r="N67" s="48"/>
-      <c r="O67" s="48"/>
-      <c r="P67" s="5"/>
-      <c r="Q67" s="5"/>
-      <c r="R67" s="50"/>
+      <c r="I67" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="K67" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L67" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M67" s="50"/>
+      <c r="N67" s="50"/>
+      <c r="O67" s="50"/>
+      <c r="P67" s="8"/>
+      <c r="Q67" s="8"/>
+      <c r="R67" s="40"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="34" t="n">
-        <v>57</v>
+      <c r="A68" s="32" t="n">
+        <v>59</v>
       </c>
       <c r="B68" s="24"/>
-      <c r="C68" s="34"/>
+      <c r="C68" s="32" t="n">
+        <v>59</v>
+      </c>
       <c r="D68" s="24"/>
       <c r="E68" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="F68" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="G68" s="34" t="n">
-        <v>43</v>
-      </c>
-      <c r="H68" s="34" t="n">
+        <v>325</v>
+      </c>
+      <c r="F68" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>57</v>
+      </c>
+      <c r="H68" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I68" s="34"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="41"/>
-      <c r="L68" s="52"/>
-      <c r="M68" s="52"/>
-      <c r="N68" s="52"/>
-      <c r="O68" s="52"/>
+      <c r="I68" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="K68" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L68" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M68" s="50"/>
+      <c r="N68" s="50"/>
+      <c r="O68" s="50"/>
       <c r="P68" s="8"/>
       <c r="Q68" s="8"/>
-      <c r="R68" s="42"/>
+      <c r="R68" s="40"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="34" t="n">
-        <v>58</v>
+      <c r="A69" s="32" t="n">
+        <v>60</v>
       </c>
       <c r="B69" s="24"/>
-      <c r="C69" s="34" t="n">
-        <v>58</v>
+      <c r="C69" s="32" t="n">
+        <v>60</v>
       </c>
       <c r="D69" s="24"/>
       <c r="E69" s="24" t="s">
-        <v>301</v>
-      </c>
-      <c r="F69" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="G69" s="34" t="n">
+        <v>327</v>
+      </c>
+      <c r="F69" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="G69" s="32" t="n">
         <v>57</v>
       </c>
-      <c r="H69" s="34" t="n">
+      <c r="H69" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I69" s="34" t="n">
+      <c r="I69" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="K69" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L69" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M69" s="52"/>
-      <c r="N69" s="52"/>
-      <c r="O69" s="52"/>
+        <v>328</v>
+      </c>
+      <c r="K69" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L69" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M69" s="50"/>
+      <c r="N69" s="50"/>
+      <c r="O69" s="50"/>
       <c r="P69" s="8"/>
       <c r="Q69" s="8"/>
-      <c r="R69" s="42"/>
+      <c r="R69" s="40"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="34" t="n">
-        <v>59</v>
+      <c r="A70" s="32" t="n">
+        <v>61</v>
       </c>
       <c r="B70" s="24"/>
-      <c r="C70" s="34" t="n">
-        <v>59</v>
+      <c r="C70" s="32" t="n">
+        <v>61</v>
       </c>
       <c r="D70" s="24"/>
       <c r="E70" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="F70" s="40" t="s">
-        <v>5</v>
-      </c>
-      <c r="G70" s="34" t="n">
+        <v>329</v>
+      </c>
+      <c r="F70" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="G70" s="32" t="n">
         <v>57</v>
       </c>
-      <c r="H70" s="34" t="n">
+      <c r="H70" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I70" s="34" t="n">
+      <c r="I70" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="K70" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L70" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M70" s="52"/>
-      <c r="N70" s="52"/>
-      <c r="O70" s="52"/>
+        <v>330</v>
+      </c>
+      <c r="K70" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L70" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M70" s="50"/>
+      <c r="N70" s="50"/>
+      <c r="O70" s="50"/>
       <c r="P70" s="8"/>
       <c r="Q70" s="8"/>
-      <c r="R70" s="42"/>
+      <c r="R70" s="48"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="34" t="n">
-        <v>60</v>
-      </c>
+      <c r="A71" s="32"/>
       <c r="B71" s="24"/>
-      <c r="C71" s="34" t="n">
-        <v>60</v>
+      <c r="C71" s="32" t="n">
+        <v>62</v>
       </c>
       <c r="D71" s="24"/>
       <c r="E71" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="F71" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="G71" s="34" t="n">
+        <v>322</v>
+      </c>
+      <c r="F71" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="G71" s="32" t="n">
         <v>57</v>
       </c>
-      <c r="H71" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I71" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="K71" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L71" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M71" s="52"/>
-      <c r="N71" s="52"/>
-      <c r="O71" s="52"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="8"/>
+      <c r="K71" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L71" s="50"/>
+      <c r="M71" s="50"/>
+      <c r="N71" s="50"/>
+      <c r="O71" s="50"/>
       <c r="P71" s="8"/>
       <c r="Q71" s="8"/>
-      <c r="R71" s="42"/>
+      <c r="R71" s="48"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="34" t="n">
-        <v>61</v>
-      </c>
-      <c r="B72" s="24"/>
-      <c r="C72" s="34" t="n">
-        <v>61</v>
-      </c>
-      <c r="D72" s="24"/>
-      <c r="E72" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="F72" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="G72" s="34" t="n">
-        <v>57</v>
-      </c>
-      <c r="H72" s="34" t="n">
+      <c r="A72" s="41" t="n">
+        <v>62</v>
+      </c>
+      <c r="B72" s="23"/>
+      <c r="C72" s="41"/>
+      <c r="D72" s="23"/>
+      <c r="E72" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="F72" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="G72" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="H72" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I72" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="K72" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L72" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M72" s="52"/>
-      <c r="N72" s="52"/>
-      <c r="O72" s="52"/>
-      <c r="P72" s="8"/>
-      <c r="Q72" s="8"/>
-      <c r="R72" s="50"/>
+      <c r="I72" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="5"/>
+      <c r="K72" s="45"/>
+      <c r="L72" s="46"/>
+      <c r="M72" s="46"/>
+      <c r="N72" s="46"/>
+      <c r="O72" s="46"/>
+      <c r="P72" s="5"/>
+      <c r="Q72" s="5"/>
+      <c r="R72" s="40"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="34"/>
-      <c r="B73" s="24"/>
-      <c r="C73" s="34" t="n">
+      <c r="A73" s="41" t="n">
+        <v>63</v>
+      </c>
+      <c r="B73" s="23"/>
+      <c r="C73" s="41" t="n">
+        <v>63</v>
+      </c>
+      <c r="D73" s="23"/>
+      <c r="E73" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="F73" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="G73" s="41" t="n">
         <v>62</v>
       </c>
-      <c r="D73" s="24"/>
-      <c r="E73" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="F73" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="G73" s="34" t="n">
-        <v>57</v>
-      </c>
-      <c r="H73" s="34"/>
-      <c r="I73" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="8"/>
-      <c r="K73" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L73" s="52"/>
-      <c r="M73" s="52"/>
-      <c r="N73" s="52"/>
-      <c r="O73" s="52"/>
-      <c r="P73" s="8"/>
-      <c r="Q73" s="8"/>
-      <c r="R73" s="50"/>
+      <c r="H73" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="K73" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L73" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M73" s="46"/>
+      <c r="N73" s="46"/>
+      <c r="O73" s="46"/>
+      <c r="P73" s="5"/>
+      <c r="Q73" s="5"/>
+      <c r="R73" s="40"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="43" t="n">
-        <v>62</v>
+      <c r="A74" s="41" t="n">
+        <v>64</v>
       </c>
       <c r="B74" s="23"/>
-      <c r="C74" s="43"/>
+      <c r="C74" s="41" t="n">
+        <v>64</v>
+      </c>
       <c r="D74" s="23"/>
       <c r="E74" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="F74" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="G74" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="H74" s="43" t="n">
+        <v>334</v>
+      </c>
+      <c r="F74" s="47" t="s">
+        <v>147</v>
+      </c>
+      <c r="G74" s="41" t="n">
+        <v>62</v>
+      </c>
+      <c r="H74" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I74" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="5"/>
-      <c r="K74" s="47"/>
-      <c r="L74" s="48"/>
-      <c r="M74" s="48"/>
-      <c r="N74" s="48"/>
-      <c r="O74" s="48"/>
+      <c r="I74" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="K74" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L74" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M74" s="46"/>
+      <c r="N74" s="46"/>
+      <c r="O74" s="46"/>
       <c r="P74" s="5"/>
       <c r="Q74" s="5"/>
-      <c r="R74" s="42"/>
+      <c r="R74" s="40"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="43" t="n">
+      <c r="A75" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="B75" s="23" t="n">
         <v>63</v>
       </c>
-      <c r="B75" s="23"/>
-      <c r="C75" s="43" t="n">
+      <c r="C75" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="D75" s="23" t="n">
         <v>63</v>
       </c>
-      <c r="D75" s="23"/>
       <c r="E75" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="F75" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="G75" s="43" t="n">
+        <v>336</v>
+      </c>
+      <c r="F75" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="G75" s="41" t="n">
         <v>62</v>
       </c>
-      <c r="H75" s="43" t="n">
+      <c r="H75" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I75" s="43" t="n">
+      <c r="I75" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="K75" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L75" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M75" s="48"/>
-      <c r="N75" s="48"/>
-      <c r="O75" s="48"/>
+        <v>337</v>
+      </c>
+      <c r="K75" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L75" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M75" s="46"/>
+      <c r="N75" s="46"/>
+      <c r="O75" s="46"/>
       <c r="P75" s="5"/>
       <c r="Q75" s="5"/>
-      <c r="R75" s="42"/>
+      <c r="R75" s="40"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="43" t="n">
-        <v>64</v>
+      <c r="A76" s="41" t="n">
+        <v>66</v>
       </c>
       <c r="B76" s="23"/>
-      <c r="C76" s="43" t="n">
-        <v>64</v>
+      <c r="C76" s="41" t="n">
+        <v>66</v>
       </c>
       <c r="D76" s="23"/>
       <c r="E76" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="F76" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="G76" s="43" t="n">
-        <v>62</v>
-      </c>
-      <c r="H76" s="43" t="n">
+        <v>338</v>
+      </c>
+      <c r="F76" s="55" t="s">
+        <v>243</v>
+      </c>
+      <c r="G76" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="H76" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I76" s="43" t="n">
+      <c r="I76" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="K76" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L76" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M76" s="48"/>
-      <c r="N76" s="48"/>
-      <c r="O76" s="48"/>
+        <v>339</v>
+      </c>
+      <c r="K76" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L76" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M76" s="46"/>
+      <c r="N76" s="46"/>
+      <c r="O76" s="46"/>
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
-      <c r="R76" s="42"/>
+      <c r="R76" s="40"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="43" t="n">
+      <c r="A77" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="B77" s="23"/>
+      <c r="C77" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="D77" s="23"/>
+      <c r="E77" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="F77" s="55" t="s">
+        <v>248</v>
+      </c>
+      <c r="G77" s="41" t="n">
         <v>65</v>
       </c>
-      <c r="B77" s="23" t="n">
-        <v>63</v>
-      </c>
-      <c r="C77" s="43" t="n">
-        <v>65</v>
-      </c>
-      <c r="D77" s="23" t="n">
-        <v>63</v>
-      </c>
-      <c r="E77" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="F77" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="G77" s="43" t="n">
-        <v>62</v>
-      </c>
-      <c r="H77" s="43" t="n">
+      <c r="H77" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I77" s="43" t="n">
+      <c r="I77" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="K77" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L77" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M77" s="48"/>
-      <c r="N77" s="48"/>
-      <c r="O77" s="48"/>
+        <v>341</v>
+      </c>
+      <c r="K77" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L77" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M77" s="46"/>
+      <c r="N77" s="46"/>
+      <c r="O77" s="46"/>
       <c r="P77" s="5"/>
       <c r="Q77" s="5"/>
-      <c r="R77" s="42"/>
+      <c r="R77" s="40"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="43" t="n">
-        <v>66</v>
-      </c>
+      <c r="A78" s="41"/>
       <c r="B78" s="23"/>
-      <c r="C78" s="43" t="n">
-        <v>66</v>
+      <c r="C78" s="41" t="n">
+        <v>68</v>
       </c>
       <c r="D78" s="23"/>
       <c r="E78" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="F78" s="57" t="s">
-        <v>235</v>
-      </c>
-      <c r="G78" s="43" t="n">
+        <v>342</v>
+      </c>
+      <c r="F78" s="55" t="s">
+        <v>343</v>
+      </c>
+      <c r="G78" s="41" t="n">
         <v>65</v>
       </c>
-      <c r="H78" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I78" s="43" t="n">
+      <c r="H78" s="41"/>
+      <c r="I78" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="K78" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L78" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M78" s="48"/>
-      <c r="N78" s="48"/>
-      <c r="O78" s="48"/>
+        <v>344</v>
+      </c>
+      <c r="K78" s="46"/>
+      <c r="L78" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M78" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="N78" s="46"/>
+      <c r="O78" s="46"/>
       <c r="P78" s="5"/>
       <c r="Q78" s="5"/>
-      <c r="R78" s="42"/>
+      <c r="R78" s="48"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="43" t="n">
-        <v>67</v>
-      </c>
-      <c r="B79" s="23"/>
-      <c r="C79" s="43" t="n">
-        <v>67</v>
-      </c>
-      <c r="D79" s="23"/>
-      <c r="E79" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="F79" s="57" t="s">
-        <v>238</v>
-      </c>
-      <c r="G79" s="43" t="n">
-        <v>65</v>
-      </c>
-      <c r="H79" s="43" t="n">
+      <c r="A79" s="32" t="n">
+        <v>68</v>
+      </c>
+      <c r="B79" s="24"/>
+      <c r="C79" s="32"/>
+      <c r="D79" s="24"/>
+      <c r="E79" s="24" t="s">
+        <v>345</v>
+      </c>
+      <c r="F79" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="G79" s="52" t="n">
+        <v>43</v>
+      </c>
+      <c r="H79" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I79" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="K79" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L79" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M79" s="48"/>
-      <c r="N79" s="48"/>
-      <c r="O79" s="48"/>
-      <c r="P79" s="5"/>
-      <c r="Q79" s="5"/>
-      <c r="R79" s="42"/>
+      <c r="I79" s="32"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="50"/>
+      <c r="L79" s="50"/>
+      <c r="M79" s="50"/>
+      <c r="N79" s="50"/>
+      <c r="O79" s="50"/>
+      <c r="P79" s="8"/>
+      <c r="Q79" s="8"/>
+      <c r="R79" s="48"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="43"/>
-      <c r="B80" s="23"/>
-      <c r="C80" s="43" t="n">
+      <c r="A80" s="32" t="n">
+        <v>69</v>
+      </c>
+      <c r="B80" s="24"/>
+      <c r="C80" s="32" t="n">
+        <v>69</v>
+      </c>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="F80" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="G80" s="32" t="n">
         <v>68</v>
       </c>
-      <c r="D80" s="23"/>
-      <c r="E80" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="F80" s="57" t="s">
-        <v>321</v>
-      </c>
-      <c r="G80" s="43" t="n">
-        <v>65</v>
-      </c>
-      <c r="H80" s="43"/>
-      <c r="I80" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="K80" s="48"/>
-      <c r="L80" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M80" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="N80" s="48"/>
-      <c r="O80" s="48"/>
-      <c r="P80" s="5"/>
-      <c r="Q80" s="5"/>
-      <c r="R80" s="50"/>
+      <c r="H80" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I80" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="8"/>
+      <c r="K80" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L80" s="50"/>
+      <c r="M80" s="50"/>
+      <c r="N80" s="50"/>
+      <c r="O80" s="50"/>
+      <c r="P80" s="8"/>
+      <c r="Q80" s="8"/>
+      <c r="R80" s="48"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="34" t="n">
-        <v>68</v>
+      <c r="A81" s="32" t="n">
+        <v>70</v>
       </c>
       <c r="B81" s="24"/>
-      <c r="C81" s="34"/>
+      <c r="C81" s="32" t="n">
+        <v>70</v>
+      </c>
       <c r="D81" s="24"/>
       <c r="E81" s="24" t="s">
-        <v>323</v>
-      </c>
-      <c r="F81" s="71" t="s">
-        <v>126</v>
-      </c>
-      <c r="G81" s="54" t="n">
-        <v>43</v>
-      </c>
-      <c r="H81" s="34" t="n">
+        <v>347</v>
+      </c>
+      <c r="F81" s="53" t="s">
+        <v>348</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>69</v>
+      </c>
+      <c r="H81" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I81" s="34"/>
+      <c r="I81" s="32" t="n">
+        <v>1</v>
+      </c>
       <c r="J81" s="8"/>
-      <c r="K81" s="52"/>
-      <c r="L81" s="52"/>
-      <c r="M81" s="52"/>
-      <c r="N81" s="52"/>
-      <c r="O81" s="52"/>
+      <c r="K81" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L81" s="50"/>
+      <c r="M81" s="50"/>
+      <c r="N81" s="50"/>
+      <c r="O81" s="50"/>
       <c r="P81" s="8"/>
       <c r="Q81" s="8"/>
-      <c r="R81" s="50"/>
+      <c r="R81" s="40"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="34" t="n">
-        <v>69</v>
+      <c r="A82" s="32" t="n">
+        <v>71</v>
       </c>
       <c r="B82" s="24"/>
-      <c r="C82" s="34" t="n">
-        <v>69</v>
+      <c r="C82" s="32" t="n">
+        <v>71</v>
       </c>
       <c r="D82" s="24"/>
       <c r="E82" s="24" t="s">
-        <v>324</v>
-      </c>
-      <c r="F82" s="40" t="s">
-        <v>150</v>
-      </c>
-      <c r="G82" s="34" t="n">
+        <v>349</v>
+      </c>
+      <c r="F82" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="G82" s="32" t="n">
         <v>68</v>
       </c>
-      <c r="H82" s="34" t="n">
+      <c r="H82" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I82" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="8"/>
-      <c r="K82" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L82" s="52"/>
-      <c r="M82" s="52"/>
-      <c r="N82" s="52"/>
-      <c r="O82" s="52"/>
+      <c r="I82" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="K82" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L82" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M82" s="50"/>
+      <c r="N82" s="50"/>
+      <c r="O82" s="50"/>
       <c r="P82" s="8"/>
       <c r="Q82" s="8"/>
-      <c r="R82" s="50"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="34" t="n">
-        <v>70</v>
-      </c>
-      <c r="B83" s="24"/>
-      <c r="C83" s="34" t="n">
-        <v>70</v>
-      </c>
-      <c r="D83" s="24"/>
-      <c r="E83" s="24" t="s">
-        <v>325</v>
-      </c>
-      <c r="F83" s="55" t="s">
-        <v>326</v>
-      </c>
-      <c r="G83" s="34" t="n">
-        <v>69</v>
-      </c>
-      <c r="H83" s="34" t="n">
+      <c r="A83" s="41" t="n">
+        <v>72</v>
+      </c>
+      <c r="B83" s="23"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="23"/>
+      <c r="E83" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="F83" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="G83" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="H83" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I83" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="8"/>
-      <c r="K83" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L83" s="52"/>
-      <c r="M83" s="52"/>
-      <c r="N83" s="52"/>
-      <c r="O83" s="52"/>
-      <c r="P83" s="8"/>
-      <c r="Q83" s="8"/>
-      <c r="R83" s="42"/>
+      <c r="I83" s="41"/>
+      <c r="J83" s="5"/>
+      <c r="K83" s="46"/>
+      <c r="L83" s="46"/>
+      <c r="M83" s="46"/>
+      <c r="N83" s="46"/>
+      <c r="O83" s="46"/>
+      <c r="P83" s="5"/>
+      <c r="Q83" s="5"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="34" t="n">
-        <v>71</v>
-      </c>
-      <c r="B84" s="24"/>
-      <c r="C84" s="34" t="n">
-        <v>71</v>
-      </c>
-      <c r="D84" s="24"/>
-      <c r="E84" s="24" t="s">
-        <v>327</v>
-      </c>
-      <c r="F84" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="G84" s="34" t="n">
-        <v>68</v>
-      </c>
-      <c r="H84" s="34" t="n">
+      <c r="A84" s="41" t="n">
+        <v>73</v>
+      </c>
+      <c r="B84" s="23"/>
+      <c r="C84" s="41" t="n">
+        <v>72</v>
+      </c>
+      <c r="D84" s="23"/>
+      <c r="E84" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="F84" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="G84" s="41" t="n">
+        <v>72</v>
+      </c>
+      <c r="H84" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I84" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="K84" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L84" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M84" s="52"/>
-      <c r="N84" s="52"/>
-      <c r="O84" s="52"/>
-      <c r="P84" s="8"/>
-      <c r="Q84" s="8"/>
+      <c r="I84" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="5"/>
+      <c r="K84" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="L84" s="46"/>
+      <c r="M84" s="46"/>
+      <c r="N84" s="46"/>
+      <c r="O84" s="46"/>
+      <c r="P84" s="5"/>
+      <c r="Q84" s="5"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="43" t="n">
+      <c r="A85" s="41" t="n">
+        <v>74</v>
+      </c>
+      <c r="B85" s="23"/>
+      <c r="C85" s="41" t="n">
+        <v>73</v>
+      </c>
+      <c r="D85" s="23"/>
+      <c r="E85" s="23"/>
+      <c r="F85" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="G85" s="41" t="n">
         <v>72</v>
       </c>
-      <c r="B85" s="23"/>
-      <c r="C85" s="43"/>
-      <c r="D85" s="23"/>
-      <c r="E85" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="F85" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="G85" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="H85" s="43" t="n">
+      <c r="H85" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I85" s="43"/>
+      <c r="I85" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="J85" s="5"/>
-      <c r="K85" s="48"/>
-      <c r="L85" s="48"/>
-      <c r="M85" s="48"/>
-      <c r="N85" s="48"/>
-      <c r="O85" s="48"/>
+      <c r="K85" s="72" t="s">
+        <v>87</v>
+      </c>
+      <c r="L85" s="46"/>
+      <c r="M85" s="46"/>
+      <c r="N85" s="46"/>
+      <c r="O85" s="46"/>
       <c r="P85" s="5"/>
       <c r="Q85" s="5"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="43" t="n">
-        <v>73</v>
+      <c r="A86" s="41" t="n">
+        <v>75</v>
       </c>
       <c r="B86" s="23"/>
-      <c r="C86" s="43" t="n">
-        <v>72</v>
+      <c r="C86" s="41" t="n">
+        <v>74</v>
       </c>
       <c r="D86" s="23"/>
       <c r="E86" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="F86" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="G86" s="43" t="n">
+        <v>353</v>
+      </c>
+      <c r="F86" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="G86" s="41" t="n">
         <v>72</v>
       </c>
-      <c r="H86" s="43" t="n">
+      <c r="H86" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I86" s="43" t="n">
+      <c r="I86" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J86" s="5"/>
-      <c r="K86" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="L86" s="48"/>
-      <c r="M86" s="48"/>
-      <c r="N86" s="48"/>
-      <c r="O86" s="48"/>
+      <c r="K86" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L86" s="46"/>
+      <c r="M86" s="46"/>
+      <c r="N86" s="46"/>
+      <c r="O86" s="46"/>
       <c r="P86" s="5"/>
       <c r="Q86" s="5"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="43" t="n">
-        <v>74</v>
-      </c>
-      <c r="B87" s="23"/>
-      <c r="C87" s="43" t="n">
-        <v>73</v>
-      </c>
-      <c r="D87" s="23"/>
-      <c r="E87" s="23"/>
-      <c r="F87" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="G87" s="43" t="n">
+      <c r="A87" s="41" t="n">
+        <v>76</v>
+      </c>
+      <c r="B87" s="23" t="n">
+        <v>75</v>
+      </c>
+      <c r="C87" s="41" t="n">
+        <v>75</v>
+      </c>
+      <c r="D87" s="23" t="n">
+        <v>75</v>
+      </c>
+      <c r="E87" s="23" t="s">
+        <v>354</v>
+      </c>
+      <c r="F87" s="47" t="s">
+        <v>157</v>
+      </c>
+      <c r="G87" s="41" t="n">
         <v>72</v>
       </c>
-      <c r="H87" s="43" t="n">
+      <c r="H87" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I87" s="43" t="n">
+      <c r="I87" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J87" s="5"/>
-      <c r="K87" s="72" t="s">
-        <v>87</v>
-      </c>
-      <c r="L87" s="48"/>
-      <c r="M87" s="48"/>
-      <c r="N87" s="48"/>
-      <c r="O87" s="48"/>
+      <c r="K87" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L87" s="46"/>
+      <c r="M87" s="46"/>
+      <c r="N87" s="46"/>
+      <c r="O87" s="46"/>
       <c r="P87" s="5"/>
       <c r="Q87" s="5"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="43" t="n">
+      <c r="A88" s="41" t="n">
+        <v>77</v>
+      </c>
+      <c r="B88" s="23" t="n">
         <v>75</v>
       </c>
-      <c r="B88" s="23"/>
-      <c r="C88" s="43" t="n">
-        <v>74</v>
-      </c>
-      <c r="D88" s="23"/>
-      <c r="E88" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="F88" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="G88" s="43" t="n">
+      <c r="C88" s="41"/>
+      <c r="D88" s="23" t="n">
+        <v>75</v>
+      </c>
+      <c r="E88" s="23"/>
+      <c r="F88" s="47" t="s">
+        <v>355</v>
+      </c>
+      <c r="G88" s="41" t="n">
         <v>72</v>
       </c>
-      <c r="H88" s="43" t="n">
+      <c r="H88" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I88" s="43" t="n">
-        <v>1</v>
-      </c>
+      <c r="I88" s="41"/>
       <c r="J88" s="5"/>
-      <c r="K88" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L88" s="48"/>
-      <c r="M88" s="48"/>
-      <c r="N88" s="48"/>
-      <c r="O88" s="48"/>
+      <c r="K88" s="45"/>
+      <c r="L88" s="46"/>
+      <c r="M88" s="46"/>
+      <c r="N88" s="46"/>
+      <c r="O88" s="46"/>
       <c r="P88" s="5"/>
       <c r="Q88" s="5"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="43" t="n">
+      <c r="A89" s="41" t="n">
+        <v>78</v>
+      </c>
+      <c r="B89" s="23"/>
+      <c r="C89" s="41" t="n">
         <v>76</v>
       </c>
-      <c r="B89" s="23" t="n">
-        <v>75</v>
-      </c>
-      <c r="C89" s="43" t="n">
-        <v>75</v>
-      </c>
-      <c r="D89" s="23" t="n">
-        <v>75</v>
-      </c>
+      <c r="D89" s="23"/>
       <c r="E89" s="23" t="s">
-        <v>332</v>
-      </c>
-      <c r="F89" s="49" t="s">
-        <v>157</v>
-      </c>
-      <c r="G89" s="43" t="n">
-        <v>72</v>
-      </c>
-      <c r="H89" s="43" t="n">
+        <v>356</v>
+      </c>
+      <c r="F89" s="55" t="s">
+        <v>357</v>
+      </c>
+      <c r="G89" s="41" t="n">
+        <v>77</v>
+      </c>
+      <c r="H89" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I89" s="43" t="n">
+      <c r="I89" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J89" s="5"/>
-      <c r="K89" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L89" s="48"/>
-      <c r="M89" s="48"/>
-      <c r="N89" s="48"/>
-      <c r="O89" s="48"/>
+      <c r="K89" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L89" s="46"/>
+      <c r="M89" s="46"/>
+      <c r="N89" s="46"/>
+      <c r="O89" s="46"/>
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
+      <c r="R89" s="40"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="43" t="n">
+      <c r="A90" s="41" t="n">
+        <v>79</v>
+      </c>
+      <c r="B90" s="23"/>
+      <c r="C90" s="41" t="n">
         <v>77</v>
       </c>
-      <c r="B90" s="23" t="n">
-        <v>75</v>
-      </c>
-      <c r="C90" s="43"/>
-      <c r="D90" s="23" t="n">
-        <v>75</v>
-      </c>
-      <c r="E90" s="23"/>
-      <c r="F90" s="49" t="s">
-        <v>333</v>
-      </c>
-      <c r="G90" s="43" t="n">
-        <v>72</v>
-      </c>
-      <c r="H90" s="43" t="n">
+      <c r="D90" s="23"/>
+      <c r="E90" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="F90" s="55" t="s">
+        <v>359</v>
+      </c>
+      <c r="G90" s="41" t="n">
+        <v>77</v>
+      </c>
+      <c r="H90" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I90" s="43"/>
-      <c r="J90" s="5"/>
-      <c r="K90" s="47"/>
-      <c r="L90" s="48"/>
-      <c r="M90" s="48"/>
-      <c r="N90" s="48"/>
-      <c r="O90" s="48"/>
+      <c r="I90" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="K90" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L90" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M90" s="46"/>
+      <c r="N90" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="O90" s="46"/>
       <c r="P90" s="5"/>
       <c r="Q90" s="5"/>
+      <c r="R90" s="48"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="43" t="n">
+      <c r="A91" s="32" t="n">
+        <v>80</v>
+      </c>
+      <c r="B91" s="24"/>
+      <c r="C91" s="32"/>
+      <c r="D91" s="24"/>
+      <c r="E91" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="F91" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="G91" s="32" t="n">
+        <v>43</v>
+      </c>
+      <c r="H91" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" s="32"/>
+      <c r="J91" s="8"/>
+      <c r="K91" s="39"/>
+      <c r="L91" s="39"/>
+      <c r="M91" s="50"/>
+      <c r="N91" s="39"/>
+      <c r="O91" s="50"/>
+      <c r="P91" s="8"/>
+      <c r="Q91" s="8"/>
+      <c r="R91" s="40"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="B92" s="24"/>
+      <c r="C92" s="32" t="n">
         <v>78</v>
       </c>
-      <c r="B91" s="23"/>
-      <c r="C91" s="43" t="n">
-        <v>76</v>
-      </c>
-      <c r="D91" s="23"/>
-      <c r="E91" s="23" t="s">
-        <v>334</v>
-      </c>
-      <c r="F91" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="G91" s="43" t="n">
-        <v>77</v>
-      </c>
-      <c r="H91" s="43" t="n">
+      <c r="D92" s="24"/>
+      <c r="E92" s="24" t="s">
+        <v>362</v>
+      </c>
+      <c r="F92" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="G92" s="32" t="n">
+        <v>80</v>
+      </c>
+      <c r="H92" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I91" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="5"/>
-      <c r="K91" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L91" s="48"/>
-      <c r="M91" s="48"/>
-      <c r="N91" s="48"/>
-      <c r="O91" s="48"/>
-      <c r="P91" s="5"/>
-      <c r="Q91" s="5"/>
-      <c r="R91" s="42"/>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="43" t="n">
+      <c r="I92" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="K92" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L92" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M92" s="50"/>
+      <c r="N92" s="50"/>
+      <c r="O92" s="50"/>
+      <c r="P92" s="8"/>
+      <c r="Q92" s="8"/>
+      <c r="R92" s="40"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="32" t="n">
+        <v>82</v>
+      </c>
+      <c r="B93" s="24"/>
+      <c r="C93" s="32" t="n">
         <v>79</v>
       </c>
-      <c r="B92" s="23"/>
-      <c r="C92" s="43" t="n">
-        <v>77</v>
-      </c>
-      <c r="D92" s="23"/>
-      <c r="E92" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="F92" s="57" t="s">
-        <v>337</v>
-      </c>
-      <c r="G92" s="43" t="n">
-        <v>77</v>
-      </c>
-      <c r="H92" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I92" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="K92" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L92" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M92" s="48"/>
-      <c r="N92" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="O92" s="48"/>
-      <c r="P92" s="5"/>
-      <c r="Q92" s="5"/>
-      <c r="R92" s="50"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="34" t="n">
-        <v>80</v>
-      </c>
-      <c r="B93" s="24"/>
-      <c r="C93" s="34"/>
       <c r="D93" s="24"/>
       <c r="E93" s="24" t="s">
-        <v>339</v>
-      </c>
-      <c r="F93" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="G93" s="34" t="n">
-        <v>43</v>
-      </c>
-      <c r="H93" s="34" t="n">
+        <v>364</v>
+      </c>
+      <c r="F93" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="G93" s="32" t="n">
+        <v>80</v>
+      </c>
+      <c r="H93" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I93" s="34"/>
-      <c r="J93" s="8"/>
-      <c r="K93" s="41"/>
-      <c r="L93" s="41"/>
-      <c r="M93" s="52"/>
-      <c r="N93" s="41"/>
-      <c r="O93" s="52"/>
+      <c r="I93" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="K93" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L93" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M93" s="50"/>
+      <c r="N93" s="50"/>
+      <c r="O93" s="50"/>
       <c r="P93" s="8"/>
       <c r="Q93" s="8"/>
-      <c r="R93" s="42"/>
+      <c r="R93" s="40"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="34" t="n">
-        <v>81</v>
+      <c r="A94" s="32" t="n">
+        <v>83</v>
       </c>
       <c r="B94" s="24"/>
-      <c r="C94" s="34" t="n">
-        <v>78</v>
+      <c r="C94" s="32" t="n">
+        <v>80</v>
       </c>
       <c r="D94" s="24"/>
       <c r="E94" s="24" t="s">
-        <v>340</v>
-      </c>
-      <c r="F94" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="G94" s="34" t="n">
+        <v>366</v>
+      </c>
+      <c r="F94" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="G94" s="32" t="n">
         <v>80</v>
       </c>
-      <c r="H94" s="34" t="n">
+      <c r="H94" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I94" s="34" t="n">
+      <c r="I94" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="K94" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L94" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M94" s="52"/>
-      <c r="N94" s="52"/>
-      <c r="O94" s="52"/>
+        <v>367</v>
+      </c>
+      <c r="K94" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L94" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M94" s="50"/>
+      <c r="N94" s="50"/>
+      <c r="O94" s="50"/>
       <c r="P94" s="8"/>
       <c r="Q94" s="8"/>
-      <c r="R94" s="42"/>
+      <c r="R94" s="40"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="34" t="n">
-        <v>82</v>
+      <c r="A95" s="32" t="n">
+        <v>84</v>
       </c>
       <c r="B95" s="24"/>
-      <c r="C95" s="34" t="n">
-        <v>79</v>
+      <c r="C95" s="32" t="n">
+        <v>81</v>
       </c>
       <c r="D95" s="24"/>
       <c r="E95" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="F95" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="G95" s="34" t="n">
+        <v>368</v>
+      </c>
+      <c r="F95" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="G95" s="32" t="n">
         <v>80</v>
       </c>
-      <c r="H95" s="34" t="n">
+      <c r="H95" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I95" s="34" t="n">
+      <c r="I95" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="K95" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L95" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M95" s="52"/>
-      <c r="N95" s="52"/>
-      <c r="O95" s="52"/>
+        <v>369</v>
+      </c>
+      <c r="K95" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L95" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M95" s="50"/>
+      <c r="N95" s="50"/>
+      <c r="O95" s="50"/>
       <c r="P95" s="8"/>
       <c r="Q95" s="8"/>
-      <c r="R95" s="42"/>
+      <c r="R95" s="48"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="34" t="n">
+      <c r="A96" s="41" t="n">
+        <v>85</v>
+      </c>
+      <c r="B96" s="23"/>
+      <c r="C96" s="41"/>
+      <c r="D96" s="23"/>
+      <c r="E96" s="23"/>
+      <c r="F96" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="G96" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="H96" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" s="41"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="45"/>
+      <c r="L96" s="45"/>
+      <c r="M96" s="46"/>
+      <c r="N96" s="46"/>
+      <c r="O96" s="46"/>
+      <c r="P96" s="5"/>
+      <c r="Q96" s="5"/>
+      <c r="R96" s="40"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="41"/>
+      <c r="B97" s="23"/>
+      <c r="C97" s="41" t="n">
+        <v>82</v>
+      </c>
+      <c r="D97" s="23"/>
+      <c r="E97" s="23" t="s">
+        <v>370</v>
+      </c>
+      <c r="F97" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="G97" s="41" t="n">
+        <v>85</v>
+      </c>
+      <c r="H97" s="41"/>
+      <c r="I97" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="K97" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L97" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M97" s="46"/>
+      <c r="N97" s="46"/>
+      <c r="O97" s="46"/>
+      <c r="P97" s="5"/>
+      <c r="Q97" s="5"/>
+      <c r="R97" s="48"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="41"/>
+      <c r="B98" s="23"/>
+      <c r="C98" s="41" t="n">
         <v>83</v>
       </c>
-      <c r="B96" s="24"/>
-      <c r="C96" s="34" t="n">
-        <v>80</v>
-      </c>
-      <c r="D96" s="24"/>
-      <c r="E96" s="24" t="s">
-        <v>344</v>
-      </c>
-      <c r="F96" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="G96" s="34" t="n">
-        <v>80</v>
-      </c>
-      <c r="H96" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I96" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="K96" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L96" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M96" s="52"/>
-      <c r="N96" s="52"/>
-      <c r="O96" s="52"/>
-      <c r="P96" s="8"/>
-      <c r="Q96" s="8"/>
-      <c r="R96" s="42"/>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="34" t="n">
-        <v>84</v>
-      </c>
-      <c r="B97" s="24"/>
-      <c r="C97" s="34" t="n">
-        <v>81</v>
-      </c>
-      <c r="D97" s="24"/>
-      <c r="E97" s="24" t="s">
-        <v>346</v>
-      </c>
-      <c r="F97" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G97" s="34" t="n">
-        <v>80</v>
-      </c>
-      <c r="H97" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I97" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="K97" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L97" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M97" s="52"/>
-      <c r="N97" s="52"/>
-      <c r="O97" s="52"/>
-      <c r="P97" s="8"/>
-      <c r="Q97" s="8"/>
-      <c r="R97" s="50"/>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="43" t="n">
+      <c r="D98" s="23"/>
+      <c r="E98" s="23" t="s">
+        <v>370</v>
+      </c>
+      <c r="F98" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="G98" s="41" t="n">
         <v>85</v>
       </c>
-      <c r="B98" s="23"/>
-      <c r="C98" s="43"/>
-      <c r="D98" s="23"/>
-      <c r="E98" s="23"/>
-      <c r="F98" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="G98" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="H98" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I98" s="43"/>
+      <c r="H98" s="41"/>
+      <c r="I98" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="J98" s="5"/>
-      <c r="K98" s="47"/>
-      <c r="L98" s="47"/>
-      <c r="M98" s="48"/>
-      <c r="N98" s="48"/>
-      <c r="O98" s="48"/>
+      <c r="K98" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L98" s="46"/>
+      <c r="M98" s="46"/>
+      <c r="N98" s="46"/>
+      <c r="O98" s="46"/>
       <c r="P98" s="5"/>
       <c r="Q98" s="5"/>
-      <c r="R98" s="42"/>
+      <c r="R98" s="40"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="43"/>
+      <c r="A99" s="41" t="n">
+        <v>86</v>
+      </c>
       <c r="B99" s="23"/>
-      <c r="C99" s="43" t="n">
-        <v>82</v>
+      <c r="C99" s="41" t="n">
+        <v>84</v>
       </c>
       <c r="D99" s="23"/>
       <c r="E99" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="F99" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="G99" s="43" t="n">
+        <v>372</v>
+      </c>
+      <c r="F99" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="G99" s="41" t="n">
         <v>85</v>
       </c>
-      <c r="H99" s="43"/>
-      <c r="I99" s="43" t="n">
+      <c r="H99" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I99" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="K99" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L99" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M99" s="48"/>
-      <c r="N99" s="48"/>
-      <c r="O99" s="48"/>
+        <v>373</v>
+      </c>
+      <c r="K99" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L99" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M99" s="46"/>
+      <c r="N99" s="46"/>
+      <c r="O99" s="46"/>
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
-      <c r="R99" s="50"/>
+      <c r="R99" s="40"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="43"/>
+      <c r="A100" s="41" t="n">
+        <v>87</v>
+      </c>
       <c r="B100" s="23"/>
-      <c r="C100" s="43" t="n">
-        <v>83</v>
+      <c r="C100" s="41" t="n">
+        <v>85</v>
       </c>
       <c r="D100" s="23"/>
       <c r="E100" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="F100" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="G100" s="43" t="n">
+        <v>374</v>
+      </c>
+      <c r="F100" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="G100" s="41" t="n">
         <v>85</v>
       </c>
-      <c r="H100" s="43"/>
-      <c r="I100" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" s="5"/>
-      <c r="K100" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L100" s="48"/>
-      <c r="M100" s="48"/>
-      <c r="N100" s="48"/>
-      <c r="O100" s="48"/>
+      <c r="H100" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I100" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="K100" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L100" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M100" s="46"/>
+      <c r="N100" s="46"/>
+      <c r="O100" s="46"/>
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
-      <c r="R100" s="42"/>
+      <c r="R100" s="40"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="43" t="n">
+      <c r="A101" s="41" t="n">
+        <v>88</v>
+      </c>
+      <c r="B101" s="23"/>
+      <c r="C101" s="41" t="n">
         <v>86</v>
-      </c>
-      <c r="B101" s="23"/>
-      <c r="C101" s="43" t="n">
-        <v>84</v>
       </c>
       <c r="D101" s="23"/>
       <c r="E101" s="23" t="s">
-        <v>350</v>
-      </c>
-      <c r="F101" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="G101" s="43" t="n">
+        <v>376</v>
+      </c>
+      <c r="F101" s="47" t="s">
+        <v>166</v>
+      </c>
+      <c r="G101" s="41" t="n">
         <v>85</v>
       </c>
-      <c r="H101" s="43" t="n">
+      <c r="H101" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I101" s="43" t="n">
+      <c r="I101" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="K101" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L101" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M101" s="48"/>
-      <c r="N101" s="48"/>
-      <c r="O101" s="48"/>
+        <v>377</v>
+      </c>
+      <c r="K101" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L101" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M101" s="46"/>
+      <c r="N101" s="46"/>
+      <c r="O101" s="46"/>
       <c r="P101" s="5"/>
       <c r="Q101" s="5"/>
-      <c r="R101" s="42"/>
+      <c r="R101" s="40"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="43" t="n">
-        <v>87</v>
+      <c r="A102" s="41" t="n">
+        <v>89</v>
       </c>
       <c r="B102" s="23"/>
-      <c r="C102" s="43" t="n">
-        <v>85</v>
+      <c r="C102" s="41" t="n">
+        <v>87</v>
       </c>
       <c r="D102" s="23"/>
       <c r="E102" s="23" t="s">
-        <v>352</v>
-      </c>
-      <c r="F102" s="49" t="s">
-        <v>153</v>
-      </c>
-      <c r="G102" s="43" t="n">
+        <v>378</v>
+      </c>
+      <c r="F102" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="G102" s="41" t="n">
         <v>85</v>
       </c>
-      <c r="H102" s="43" t="n">
+      <c r="H102" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I102" s="43" t="n">
+      <c r="I102" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="K102" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L102" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M102" s="48"/>
-      <c r="N102" s="48"/>
-      <c r="O102" s="48"/>
+        <v>379</v>
+      </c>
+      <c r="K102" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L102" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M102" s="46"/>
+      <c r="N102" s="46"/>
+      <c r="O102" s="46"/>
       <c r="P102" s="5"/>
       <c r="Q102" s="5"/>
-      <c r="R102" s="42"/>
+      <c r="R102" s="40"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="43" t="n">
+      <c r="A103" s="41" t="n">
+        <v>90</v>
+      </c>
+      <c r="B103" s="23"/>
+      <c r="C103" s="41" t="n">
         <v>88</v>
-      </c>
-      <c r="B103" s="23"/>
-      <c r="C103" s="43" t="n">
-        <v>86</v>
       </c>
       <c r="D103" s="23"/>
       <c r="E103" s="23" t="s">
-        <v>354</v>
-      </c>
-      <c r="F103" s="49" t="s">
-        <v>166</v>
-      </c>
-      <c r="G103" s="43" t="n">
+        <v>380</v>
+      </c>
+      <c r="F103" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="G103" s="41" t="n">
         <v>85</v>
       </c>
-      <c r="H103" s="43" t="n">
+      <c r="H103" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I103" s="43" t="n">
+      <c r="I103" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="K103" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L103" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M103" s="48"/>
-      <c r="N103" s="48"/>
-      <c r="O103" s="48"/>
+        <v>381</v>
+      </c>
+      <c r="K103" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L103" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M103" s="46"/>
+      <c r="N103" s="46"/>
+      <c r="O103" s="46"/>
       <c r="P103" s="5"/>
       <c r="Q103" s="5"/>
-      <c r="R103" s="42"/>
+      <c r="R103" s="40"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="43" t="n">
+      <c r="A104" s="41" t="n">
+        <v>91</v>
+      </c>
+      <c r="B104" s="23"/>
+      <c r="C104" s="41" t="n">
         <v>89</v>
-      </c>
-      <c r="B104" s="23"/>
-      <c r="C104" s="43" t="n">
-        <v>87</v>
       </c>
       <c r="D104" s="23"/>
       <c r="E104" s="23" t="s">
-        <v>356</v>
-      </c>
-      <c r="F104" s="49" t="s">
-        <v>167</v>
-      </c>
-      <c r="G104" s="43" t="n">
-        <v>85</v>
-      </c>
-      <c r="H104" s="43" t="n">
+        <v>382</v>
+      </c>
+      <c r="F104" s="55" t="s">
+        <v>383</v>
+      </c>
+      <c r="G104" s="41" t="n">
+        <v>90</v>
+      </c>
+      <c r="H104" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I104" s="43" t="n">
+      <c r="I104" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="K104" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L104" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M104" s="48"/>
-      <c r="N104" s="48"/>
-      <c r="O104" s="48"/>
+        <v>384</v>
+      </c>
+      <c r="K104" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L104" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M104" s="46"/>
+      <c r="N104" s="46"/>
+      <c r="O104" s="46"/>
       <c r="P104" s="5"/>
       <c r="Q104" s="5"/>
-      <c r="R104" s="42"/>
+      <c r="R104" s="40"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="43" t="n">
+      <c r="A105" s="41" t="n">
+        <v>92</v>
+      </c>
+      <c r="B105" s="23"/>
+      <c r="C105" s="41" t="n">
         <v>90</v>
-      </c>
-      <c r="B105" s="23"/>
-      <c r="C105" s="43" t="n">
-        <v>88</v>
       </c>
       <c r="D105" s="23"/>
       <c r="E105" s="23" t="s">
-        <v>358</v>
-      </c>
-      <c r="F105" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="G105" s="43" t="n">
+        <v>385</v>
+      </c>
+      <c r="F105" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="G105" s="41" t="n">
         <v>85</v>
       </c>
-      <c r="H105" s="43" t="n">
+      <c r="H105" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I105" s="43" t="n">
+      <c r="I105" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="K105" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L105" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M105" s="48"/>
-      <c r="N105" s="48"/>
-      <c r="O105" s="48"/>
+        <v>386</v>
+      </c>
+      <c r="K105" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L105" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M105" s="46"/>
+      <c r="N105" s="46"/>
+      <c r="O105" s="46"/>
       <c r="P105" s="5"/>
       <c r="Q105" s="5"/>
-      <c r="R105" s="42"/>
+      <c r="R105" s="48"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="43" t="n">
+      <c r="A106" s="32" t="n">
+        <v>93</v>
+      </c>
+      <c r="B106" s="24"/>
+      <c r="C106" s="32"/>
+      <c r="D106" s="24"/>
+      <c r="E106" s="24"/>
+      <c r="F106" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="G106" s="32" t="n">
+        <v>43</v>
+      </c>
+      <c r="H106" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I106" s="32"/>
+      <c r="J106" s="8"/>
+      <c r="K106" s="39"/>
+      <c r="L106" s="39"/>
+      <c r="M106" s="50"/>
+      <c r="N106" s="50"/>
+      <c r="O106" s="50"/>
+      <c r="P106" s="8"/>
+      <c r="Q106" s="8"/>
+      <c r="R106" s="40"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="32" t="n">
+        <v>94</v>
+      </c>
+      <c r="B107" s="24"/>
+      <c r="C107" s="32" t="n">
         <v>91</v>
       </c>
-      <c r="B106" s="23"/>
-      <c r="C106" s="43" t="n">
-        <v>89</v>
-      </c>
-      <c r="D106" s="23"/>
-      <c r="E106" s="23" t="s">
-        <v>360</v>
-      </c>
-      <c r="F106" s="57" t="s">
-        <v>361</v>
-      </c>
-      <c r="G106" s="43" t="n">
-        <v>90</v>
-      </c>
-      <c r="H106" s="43" t="n">
+      <c r="D107" s="24"/>
+      <c r="E107" s="24" t="s">
+        <v>387</v>
+      </c>
+      <c r="F107" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="G107" s="32" t="n">
+        <v>93</v>
+      </c>
+      <c r="H107" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I106" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="K106" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L106" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M106" s="48"/>
-      <c r="N106" s="48"/>
-      <c r="O106" s="48"/>
-      <c r="P106" s="5"/>
-      <c r="Q106" s="5"/>
-      <c r="R106" s="42"/>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="43" t="n">
+      <c r="I107" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K107" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L107" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M107" s="50"/>
+      <c r="N107" s="50"/>
+      <c r="O107" s="50"/>
+      <c r="P107" s="8"/>
+      <c r="Q107" s="8"/>
+      <c r="R107" s="40"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="B108" s="24"/>
+      <c r="C108" s="32" t="n">
         <v>92</v>
       </c>
-      <c r="B107" s="23"/>
-      <c r="C107" s="43" t="n">
-        <v>90</v>
-      </c>
-      <c r="D107" s="23"/>
-      <c r="E107" s="23" t="s">
-        <v>363</v>
-      </c>
-      <c r="F107" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="G107" s="43" t="n">
-        <v>85</v>
-      </c>
-      <c r="H107" s="43" t="n">
+      <c r="D108" s="24"/>
+      <c r="E108" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="F108" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="G108" s="32" t="n">
+        <v>93</v>
+      </c>
+      <c r="H108" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I107" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="K107" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L107" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M107" s="48"/>
-      <c r="N107" s="48"/>
-      <c r="O107" s="48"/>
-      <c r="P107" s="5"/>
-      <c r="Q107" s="5"/>
-      <c r="R107" s="50"/>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="34" t="n">
-        <v>93</v>
-      </c>
-      <c r="B108" s="24"/>
-      <c r="C108" s="34"/>
-      <c r="D108" s="24"/>
-      <c r="E108" s="24"/>
-      <c r="F108" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="G108" s="34" t="n">
-        <v>43</v>
-      </c>
-      <c r="H108" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I108" s="34"/>
-      <c r="J108" s="8"/>
-      <c r="K108" s="41"/>
-      <c r="L108" s="41"/>
-      <c r="M108" s="52"/>
-      <c r="N108" s="52"/>
-      <c r="O108" s="52"/>
+      <c r="I108" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K108" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L108" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M108" s="50"/>
+      <c r="N108" s="50"/>
+      <c r="O108" s="50"/>
       <c r="P108" s="8"/>
       <c r="Q108" s="8"/>
-      <c r="R108" s="42"/>
+      <c r="R108" s="40"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="34" t="n">
-        <v>94</v>
+      <c r="A109" s="32" t="n">
+        <v>96</v>
       </c>
       <c r="B109" s="24"/>
-      <c r="C109" s="34" t="n">
-        <v>91</v>
+      <c r="C109" s="32" t="n">
+        <v>93</v>
       </c>
       <c r="D109" s="24"/>
       <c r="E109" s="24" t="s">
-        <v>365</v>
-      </c>
-      <c r="F109" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="G109" s="34" t="n">
+        <v>391</v>
+      </c>
+      <c r="F109" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="G109" s="32" t="n">
         <v>93</v>
       </c>
-      <c r="H109" s="34" t="n">
+      <c r="H109" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I109" s="34" t="n">
+      <c r="I109" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="K109" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L109" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M109" s="52"/>
-      <c r="N109" s="52"/>
-      <c r="O109" s="52"/>
+        <v>392</v>
+      </c>
+      <c r="K109" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L109" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M109" s="50"/>
+      <c r="N109" s="39" t="s">
+        <v>245</v>
+      </c>
+      <c r="O109" s="50"/>
       <c r="P109" s="8"/>
       <c r="Q109" s="8"/>
-      <c r="R109" s="42"/>
+      <c r="R109" s="40"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="34" t="n">
-        <v>95</v>
+      <c r="A110" s="32" t="n">
+        <v>97</v>
       </c>
       <c r="B110" s="24"/>
-      <c r="C110" s="34" t="n">
-        <v>92</v>
+      <c r="C110" s="32" t="n">
+        <v>94</v>
       </c>
       <c r="D110" s="24"/>
       <c r="E110" s="24" t="s">
-        <v>367</v>
-      </c>
-      <c r="F110" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="G110" s="34" t="n">
+        <v>393</v>
+      </c>
+      <c r="F110" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="G110" s="32" t="n">
         <v>93</v>
       </c>
-      <c r="H110" s="34" t="n">
+      <c r="H110" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I110" s="34" t="n">
+      <c r="I110" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="K110" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L110" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M110" s="52"/>
-      <c r="N110" s="52"/>
-      <c r="O110" s="52"/>
+        <v>394</v>
+      </c>
+      <c r="K110" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L110" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M110" s="50"/>
+      <c r="N110" s="39" t="s">
+        <v>245</v>
+      </c>
+      <c r="O110" s="50"/>
       <c r="P110" s="8"/>
       <c r="Q110" s="8"/>
-      <c r="R110" s="42"/>
+      <c r="R110" s="40"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="34" t="n">
+      <c r="A111" s="41" t="n">
+        <v>98</v>
+      </c>
+      <c r="B111" s="23"/>
+      <c r="C111" s="41" t="n">
+        <v>95</v>
+      </c>
+      <c r="D111" s="23"/>
+      <c r="E111" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="F111" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="G111" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="H111" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="K111" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L111" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M111" s="46"/>
+      <c r="N111" s="46"/>
+      <c r="O111" s="46"/>
+      <c r="P111" s="5"/>
+      <c r="Q111" s="5"/>
+      <c r="R111" s="40"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="41" t="n">
+        <v>99</v>
+      </c>
+      <c r="B112" s="23"/>
+      <c r="C112" s="41" t="n">
         <v>96</v>
       </c>
-      <c r="B111" s="24"/>
-      <c r="C111" s="34" t="n">
-        <v>93</v>
-      </c>
-      <c r="D111" s="24"/>
-      <c r="E111" s="24" t="s">
-        <v>369</v>
-      </c>
-      <c r="F111" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="G111" s="34" t="n">
-        <v>93</v>
-      </c>
-      <c r="H111" s="34" t="n">
+      <c r="D112" s="23"/>
+      <c r="E112" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="F112" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="G112" s="41" t="n">
+        <v>98</v>
+      </c>
+      <c r="H112" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I111" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J111" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="K111" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L111" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M111" s="52"/>
-      <c r="N111" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="O111" s="52"/>
-      <c r="P111" s="8"/>
-      <c r="Q111" s="8"/>
-      <c r="R111" s="42"/>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="34" t="n">
+      <c r="I112" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="K112" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L112" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M112" s="46"/>
+      <c r="N112" s="46"/>
+      <c r="O112" s="46"/>
+      <c r="P112" s="5"/>
+      <c r="Q112" s="5"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="B113" s="24"/>
+      <c r="C113" s="32"/>
+      <c r="D113" s="24"/>
+      <c r="E113" s="24"/>
+      <c r="F113" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="G113" s="32" t="n">
+        <v>43</v>
+      </c>
+      <c r="H113" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I113" s="32"/>
+      <c r="J113" s="8"/>
+      <c r="K113" s="39"/>
+      <c r="L113" s="39"/>
+      <c r="M113" s="50"/>
+      <c r="N113" s="50"/>
+      <c r="O113" s="50"/>
+      <c r="P113" s="8"/>
+      <c r="Q113" s="8"/>
+      <c r="R113" s="40"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="32" t="n">
+        <v>101</v>
+      </c>
+      <c r="B114" s="24"/>
+      <c r="C114" s="32" t="n">
         <v>97</v>
       </c>
-      <c r="B112" s="24"/>
-      <c r="C112" s="34" t="n">
-        <v>94</v>
-      </c>
-      <c r="D112" s="24"/>
-      <c r="E112" s="24" t="s">
-        <v>371</v>
-      </c>
-      <c r="F112" s="40" t="s">
-        <v>171</v>
-      </c>
-      <c r="G112" s="34" t="n">
-        <v>93</v>
-      </c>
-      <c r="H112" s="34" t="n">
+      <c r="D114" s="24"/>
+      <c r="E114" s="24" t="s">
+        <v>399</v>
+      </c>
+      <c r="F114" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="G114" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="H114" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I112" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J112" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="K112" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L112" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M112" s="52"/>
-      <c r="N112" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="O112" s="52"/>
-      <c r="P112" s="8"/>
-      <c r="Q112" s="8"/>
-      <c r="R112" s="42"/>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="43" t="n">
+      <c r="I114" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="K114" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L114" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M114" s="50"/>
+      <c r="N114" s="50"/>
+      <c r="O114" s="50"/>
+      <c r="P114" s="8"/>
+      <c r="Q114" s="8"/>
+      <c r="R114" s="40"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="32" t="n">
+        <v>102</v>
+      </c>
+      <c r="B115" s="24"/>
+      <c r="C115" s="32" t="n">
         <v>98</v>
       </c>
-      <c r="B113" s="23"/>
-      <c r="C113" s="43" t="n">
-        <v>95</v>
-      </c>
-      <c r="D113" s="23"/>
-      <c r="E113" s="23" t="s">
-        <v>373</v>
-      </c>
-      <c r="F113" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="G113" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="H113" s="43" t="n">
+      <c r="D115" s="24"/>
+      <c r="E115" s="24" t="s">
+        <v>401</v>
+      </c>
+      <c r="F115" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="G115" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="H115" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I113" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="K113" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L113" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M113" s="48"/>
-      <c r="N113" s="48"/>
-      <c r="O113" s="48"/>
-      <c r="P113" s="5"/>
-      <c r="Q113" s="5"/>
-      <c r="R113" s="42"/>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="43" t="n">
-        <v>99</v>
-      </c>
-      <c r="B114" s="23"/>
-      <c r="C114" s="43" t="n">
-        <v>96</v>
-      </c>
-      <c r="D114" s="23"/>
-      <c r="E114" s="23" t="s">
-        <v>375</v>
-      </c>
-      <c r="F114" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="G114" s="43" t="n">
-        <v>98</v>
-      </c>
-      <c r="H114" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I114" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J114" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="K114" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L114" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M114" s="48"/>
-      <c r="N114" s="48"/>
-      <c r="O114" s="48"/>
-      <c r="P114" s="5"/>
-      <c r="Q114" s="5"/>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="34" t="n">
-        <v>100</v>
-      </c>
-      <c r="B115" s="24"/>
-      <c r="C115" s="34"/>
-      <c r="D115" s="24"/>
-      <c r="E115" s="24"/>
-      <c r="F115" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="G115" s="34" t="n">
-        <v>43</v>
-      </c>
-      <c r="H115" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I115" s="34"/>
-      <c r="J115" s="8"/>
-      <c r="K115" s="41"/>
-      <c r="L115" s="41"/>
-      <c r="M115" s="52"/>
-      <c r="N115" s="52"/>
-      <c r="O115" s="52"/>
+      <c r="I115" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K115" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L115" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M115" s="50"/>
+      <c r="N115" s="50"/>
+      <c r="O115" s="50"/>
       <c r="P115" s="8"/>
       <c r="Q115" s="8"/>
-      <c r="R115" s="42"/>
+      <c r="R115" s="40"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="34" t="n">
-        <v>101</v>
-      </c>
+      <c r="A116" s="32"/>
       <c r="B116" s="24"/>
-      <c r="C116" s="34" t="n">
-        <v>97</v>
+      <c r="C116" s="32" t="n">
+        <v>99</v>
       </c>
       <c r="D116" s="24"/>
       <c r="E116" s="24" t="s">
-        <v>377</v>
-      </c>
-      <c r="F116" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="G116" s="34" t="n">
-        <v>100</v>
-      </c>
-      <c r="H116" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I116" s="34" t="n">
+        <v>401</v>
+      </c>
+      <c r="F116" s="24"/>
+      <c r="G116" s="32"/>
+      <c r="H116" s="32"/>
+      <c r="I116" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J116" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="K116" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L116" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M116" s="52"/>
-      <c r="N116" s="52"/>
-      <c r="O116" s="52"/>
+        <v>403</v>
+      </c>
+      <c r="K116" s="50"/>
+      <c r="L116" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M116" s="50"/>
+      <c r="N116" s="39" t="s">
+        <v>245</v>
+      </c>
+      <c r="O116" s="50"/>
       <c r="P116" s="8"/>
       <c r="Q116" s="8"/>
-      <c r="R116" s="42"/>
+      <c r="R116" s="48"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="34" t="n">
-        <v>102</v>
-      </c>
-      <c r="B117" s="24"/>
-      <c r="C117" s="34" t="n">
-        <v>98</v>
-      </c>
-      <c r="D117" s="24"/>
-      <c r="E117" s="24" t="s">
-        <v>379</v>
-      </c>
-      <c r="F117" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="G117" s="34" t="n">
+      <c r="A117" s="41" t="n">
+        <v>103</v>
+      </c>
+      <c r="B117" s="23"/>
+      <c r="C117" s="41"/>
+      <c r="D117" s="23"/>
+      <c r="E117" s="23" t="n">
+        <v>43</v>
+      </c>
+      <c r="F117" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="G117" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="H117" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I117" s="41"/>
+      <c r="J117" s="5"/>
+      <c r="K117" s="45"/>
+      <c r="L117" s="46"/>
+      <c r="M117" s="46"/>
+      <c r="N117" s="46"/>
+      <c r="O117" s="46"/>
+      <c r="P117" s="5"/>
+      <c r="Q117" s="5"/>
+      <c r="R117" s="40"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="41" t="n">
+        <v>104</v>
+      </c>
+      <c r="B118" s="23"/>
+      <c r="C118" s="41" t="n">
         <v>100</v>
       </c>
-      <c r="H117" s="34" t="n">
+      <c r="D118" s="23"/>
+      <c r="E118" s="23" t="s">
+        <v>404</v>
+      </c>
+      <c r="F118" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="G118" s="41" t="n">
+        <v>103</v>
+      </c>
+      <c r="H118" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I117" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J117" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="K117" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L117" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M117" s="52"/>
-      <c r="N117" s="52"/>
-      <c r="O117" s="52"/>
-      <c r="P117" s="8"/>
-      <c r="Q117" s="8"/>
-      <c r="R117" s="42"/>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="34"/>
-      <c r="B118" s="24"/>
-      <c r="C118" s="34" t="n">
-        <v>99</v>
-      </c>
-      <c r="D118" s="24"/>
-      <c r="E118" s="24" t="s">
-        <v>379</v>
-      </c>
-      <c r="F118" s="24"/>
-      <c r="G118" s="34"/>
-      <c r="H118" s="34"/>
-      <c r="I118" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="K118" s="52"/>
-      <c r="L118" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="M118" s="52"/>
-      <c r="N118" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="O118" s="52"/>
-      <c r="P118" s="8"/>
-      <c r="Q118" s="8"/>
-      <c r="R118" s="50"/>
+      <c r="I118" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="K118" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L118" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M118" s="46"/>
+      <c r="N118" s="46"/>
+      <c r="O118" s="46"/>
+      <c r="P118" s="5"/>
+      <c r="Q118" s="5"/>
+      <c r="R118" s="40"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="43" t="n">
+      <c r="A119" s="41" t="n">
+        <v>105</v>
+      </c>
+      <c r="B119" s="23"/>
+      <c r="C119" s="41" t="n">
+        <v>101</v>
+      </c>
+      <c r="D119" s="23"/>
+      <c r="E119" s="23" t="s">
+        <v>406</v>
+      </c>
+      <c r="F119" s="47" t="s">
+        <v>182</v>
+      </c>
+      <c r="G119" s="41" t="n">
         <v>103</v>
       </c>
-      <c r="B119" s="23"/>
-      <c r="C119" s="43"/>
-      <c r="D119" s="23"/>
-      <c r="E119" s="23" t="n">
-        <v>43</v>
-      </c>
-      <c r="F119" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="G119" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="H119" s="43" t="n">
+      <c r="H119" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I119" s="43"/>
-      <c r="J119" s="5"/>
-      <c r="K119" s="47"/>
-      <c r="L119" s="48"/>
-      <c r="M119" s="48"/>
-      <c r="N119" s="48"/>
-      <c r="O119" s="48"/>
+      <c r="I119" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="K119" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L119" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M119" s="46"/>
+      <c r="N119" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="O119" s="46"/>
       <c r="P119" s="5"/>
       <c r="Q119" s="5"/>
-      <c r="R119" s="42"/>
+      <c r="R119" s="40"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="43" t="n">
-        <v>104</v>
+      <c r="A120" s="41" t="n">
+        <v>106</v>
       </c>
       <c r="B120" s="23"/>
-      <c r="C120" s="43" t="n">
-        <v>100</v>
+      <c r="C120" s="41" t="n">
+        <v>102</v>
       </c>
       <c r="D120" s="23"/>
       <c r="E120" s="23" t="s">
-        <v>382</v>
-      </c>
-      <c r="F120" s="49" t="s">
-        <v>181</v>
-      </c>
-      <c r="G120" s="43" t="n">
+        <v>408</v>
+      </c>
+      <c r="F120" s="47" t="s">
+        <v>183</v>
+      </c>
+      <c r="G120" s="41" t="n">
         <v>103</v>
       </c>
-      <c r="H120" s="43" t="n">
+      <c r="H120" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I120" s="43" t="n">
+      <c r="I120" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J120" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="K120" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L120" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M120" s="48"/>
-      <c r="N120" s="48"/>
-      <c r="O120" s="48"/>
+        <v>409</v>
+      </c>
+      <c r="K120" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L120" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="M120" s="46"/>
+      <c r="N120" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="O120" s="46"/>
       <c r="P120" s="5"/>
       <c r="Q120" s="5"/>
-      <c r="R120" s="42"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="43" t="n">
-        <v>105</v>
-      </c>
-      <c r="B121" s="23"/>
-      <c r="C121" s="43" t="n">
-        <v>101</v>
-      </c>
-      <c r="D121" s="23"/>
-      <c r="E121" s="23" t="s">
-        <v>384</v>
-      </c>
-      <c r="F121" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="G121" s="43" t="n">
+      <c r="A121" s="32" t="n">
+        <v>107</v>
+      </c>
+      <c r="B121" s="24"/>
+      <c r="C121" s="32" t="n">
         <v>103</v>
       </c>
-      <c r="H121" s="43" t="n">
+      <c r="D121" s="24"/>
+      <c r="E121" s="24" t="s">
+        <v>410</v>
+      </c>
+      <c r="F121" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="G121" s="32" t="n">
+        <v>43</v>
+      </c>
+      <c r="H121" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I121" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J121" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="K121" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L121" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M121" s="48"/>
-      <c r="N121" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="O121" s="48"/>
-      <c r="P121" s="5"/>
-      <c r="Q121" s="5"/>
-      <c r="R121" s="42"/>
+      <c r="I121" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="8"/>
+      <c r="K121" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L121" s="50"/>
+      <c r="M121" s="50"/>
+      <c r="N121" s="50"/>
+      <c r="O121" s="50"/>
+      <c r="P121" s="8"/>
+      <c r="Q121" s="8"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="43" t="n">
-        <v>106</v>
+      <c r="A122" s="41" t="n">
+        <v>108</v>
       </c>
       <c r="B122" s="23"/>
-      <c r="C122" s="43" t="n">
-        <v>102</v>
+      <c r="C122" s="41" t="n">
+        <v>104</v>
       </c>
       <c r="D122" s="23"/>
       <c r="E122" s="23" t="s">
-        <v>386</v>
-      </c>
-      <c r="F122" s="49" t="s">
-        <v>183</v>
-      </c>
-      <c r="G122" s="43" t="n">
-        <v>103</v>
-      </c>
-      <c r="H122" s="43" t="n">
+        <v>411</v>
+      </c>
+      <c r="F122" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="G122" s="41" t="n">
+        <v>43</v>
+      </c>
+      <c r="H122" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I122" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J122" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="K122" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L122" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="M122" s="48"/>
-      <c r="N122" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="O122" s="48"/>
+      <c r="I122" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" s="5"/>
+      <c r="K122" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L122" s="46"/>
+      <c r="M122" s="46"/>
+      <c r="N122" s="46"/>
+      <c r="O122" s="46"/>
       <c r="P122" s="5"/>
       <c r="Q122" s="5"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="34" t="n">
-        <v>107</v>
-      </c>
-      <c r="B123" s="24"/>
-      <c r="C123" s="34" t="n">
-        <v>103</v>
-      </c>
-      <c r="D123" s="24"/>
-      <c r="E123" s="24" t="s">
-        <v>388</v>
-      </c>
-      <c r="F123" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="G123" s="34" t="n">
-        <v>43</v>
-      </c>
-      <c r="H123" s="34" t="n">
+      <c r="A123" s="41" t="n">
+        <v>109</v>
+      </c>
+      <c r="B123" s="23"/>
+      <c r="C123" s="41" t="n">
+        <v>105</v>
+      </c>
+      <c r="D123" s="23"/>
+      <c r="E123" s="23" t="s">
+        <v>412</v>
+      </c>
+      <c r="F123" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="G123" s="41" t="n">
+        <v>108</v>
+      </c>
+      <c r="H123" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="I123" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J123" s="8"/>
-      <c r="K123" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="L123" s="52"/>
-      <c r="M123" s="52"/>
-      <c r="N123" s="52"/>
-      <c r="O123" s="52"/>
-      <c r="P123" s="8"/>
-      <c r="Q123" s="8"/>
+      <c r="I123" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" s="5"/>
+      <c r="K123" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L123" s="46"/>
+      <c r="M123" s="46"/>
+      <c r="N123" s="46"/>
+      <c r="O123" s="46"/>
+      <c r="P123" s="5"/>
+      <c r="Q123" s="5"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="43" t="n">
-        <v>108</v>
-      </c>
-      <c r="B124" s="23"/>
-      <c r="C124" s="43" t="n">
-        <v>104</v>
-      </c>
-      <c r="D124" s="23"/>
-      <c r="E124" s="23" t="s">
-        <v>389</v>
-      </c>
-      <c r="F124" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="G124" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="H124" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I124" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J124" s="5"/>
-      <c r="K124" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L124" s="48"/>
-      <c r="M124" s="48"/>
-      <c r="N124" s="48"/>
-      <c r="O124" s="48"/>
-      <c r="P124" s="5"/>
-      <c r="Q124" s="5"/>
+      <c r="A124" s="68"/>
+      <c r="C124" s="68"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="43" t="n">
-        <v>109</v>
-      </c>
-      <c r="B125" s="23"/>
-      <c r="C125" s="43" t="n">
-        <v>105</v>
-      </c>
-      <c r="D125" s="23"/>
-      <c r="E125" s="23" t="s">
-        <v>390</v>
-      </c>
-      <c r="F125" s="49" t="s">
-        <v>185</v>
-      </c>
-      <c r="G125" s="43" t="n">
-        <v>108</v>
-      </c>
-      <c r="H125" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I125" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J125" s="5"/>
-      <c r="K125" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="L125" s="48"/>
-      <c r="M125" s="48"/>
-      <c r="N125" s="48"/>
-      <c r="O125" s="48"/>
-      <c r="P125" s="5"/>
-      <c r="Q125" s="5"/>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="28"/>
-      <c r="C126" s="28"/>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="28"/>
-      <c r="C127" s="28"/>
-    </row>
+      <c r="A125" s="68"/>
+      <c r="C125" s="68"/>
+    </row>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K5" r:id="rId2" display="PDF"/>
-    <hyperlink ref="K6" r:id="rId3" display="PDF"/>
-    <hyperlink ref="L6" r:id="rId4" display="VIDEO"/>
-    <hyperlink ref="K7" r:id="rId5" display="PDF"/>
-    <hyperlink ref="L7" r:id="rId6" display="VIDEO"/>
-    <hyperlink ref="K8" r:id="rId7" display="PDF"/>
-    <hyperlink ref="L8" r:id="rId8" display="VIDEO"/>
-    <hyperlink ref="K10" r:id="rId9" display="PDF"/>
-    <hyperlink ref="L10" r:id="rId10" display="VIDEO"/>
-    <hyperlink ref="K12" r:id="rId11" display="PDF"/>
-    <hyperlink ref="L12" r:id="rId12" display="VIDEO"/>
-    <hyperlink ref="K13" r:id="rId13" display="PDF"/>
-    <hyperlink ref="L13" r:id="rId14" display="VIDEO"/>
-    <hyperlink ref="K14" r:id="rId15" display="PDF"/>
-    <hyperlink ref="L14" r:id="rId16" display="VIDEO"/>
-    <hyperlink ref="K15" r:id="rId17" display="PDF"/>
-    <hyperlink ref="L15" r:id="rId18" display="VIDEO"/>
-    <hyperlink ref="K16" r:id="rId19" display="PDF"/>
-    <hyperlink ref="L16" r:id="rId20" display="VIDEO"/>
-    <hyperlink ref="K17" r:id="rId21" display="PDF"/>
-    <hyperlink ref="L17" r:id="rId22" display="VIDEO"/>
-    <hyperlink ref="K18" r:id="rId23" display="PDF"/>
-    <hyperlink ref="L18" r:id="rId24" display="VIDEO"/>
-    <hyperlink ref="L19" r:id="rId25" display="VIDEO"/>
-    <hyperlink ref="L20" r:id="rId26" display="VIDEO"/>
-    <hyperlink ref="N20" r:id="rId27" display="CODE"/>
-    <hyperlink ref="L22" r:id="rId28" display="VIDEO"/>
-    <hyperlink ref="N22" r:id="rId29" display="CODE"/>
-    <hyperlink ref="K23" r:id="rId30" display="PDF"/>
-    <hyperlink ref="L23" r:id="rId31" display="VIDEO"/>
-    <hyperlink ref="N23" r:id="rId32" display="CODE"/>
-    <hyperlink ref="L25" r:id="rId33" display="VIDEO"/>
+    <hyperlink ref="K4" r:id="rId2" display="PDF"/>
+    <hyperlink ref="K5" r:id="rId3" display="PDF"/>
+    <hyperlink ref="L5" r:id="rId4" display="VIDEO"/>
+    <hyperlink ref="K6" r:id="rId5" display="PDF"/>
+    <hyperlink ref="L6" r:id="rId6" display="VIDEO"/>
+    <hyperlink ref="K7" r:id="rId7" display="PDF"/>
+    <hyperlink ref="L7" r:id="rId8" display="VIDEO"/>
+    <hyperlink ref="K9" r:id="rId9" display="PDF"/>
+    <hyperlink ref="L9" r:id="rId10" display="VIDEO"/>
+    <hyperlink ref="K11" r:id="rId11" display="PDF"/>
+    <hyperlink ref="L11" r:id="rId12" display="VIDEO"/>
+    <hyperlink ref="K12" r:id="rId13" display="PDF"/>
+    <hyperlink ref="L12" r:id="rId14" display="VIDEO"/>
+    <hyperlink ref="K13" r:id="rId15" display="PDF"/>
+    <hyperlink ref="L13" r:id="rId16" display="VIDEO"/>
+    <hyperlink ref="K14" r:id="rId17" display="PDF"/>
+    <hyperlink ref="L14" r:id="rId18" display="VIDEO"/>
+    <hyperlink ref="K15" r:id="rId19" display="PDF"/>
+    <hyperlink ref="L15" r:id="rId20" display="VIDEO"/>
+    <hyperlink ref="K16" r:id="rId21" display="PDF"/>
+    <hyperlink ref="L16" r:id="rId22" display="VIDEO"/>
+    <hyperlink ref="K17" r:id="rId23" display="PDF"/>
+    <hyperlink ref="L17" r:id="rId24" display="VIDEO"/>
+    <hyperlink ref="L18" r:id="rId25" display="VIDEO"/>
+    <hyperlink ref="L19" r:id="rId26" display="VIDEO"/>
+    <hyperlink ref="L21" r:id="rId27" display="VIDEO"/>
+    <hyperlink ref="N21" r:id="rId28" display="CODE"/>
+    <hyperlink ref="K22" r:id="rId29" display="PDF"/>
+    <hyperlink ref="L22" r:id="rId30" display="VIDEO"/>
+    <hyperlink ref="N22" r:id="rId31" display="CODE"/>
+    <hyperlink ref="L24" r:id="rId32" display="VIDEO"/>
+    <hyperlink ref="N24" r:id="rId33" display="CODE"/>
     <hyperlink ref="N25" r:id="rId34" display="CODE"/>
     <hyperlink ref="N26" r:id="rId35" display="CODE"/>
-    <hyperlink ref="N27" r:id="rId36" display="CODE"/>
-    <hyperlink ref="K28" r:id="rId37" display="PDF"/>
-    <hyperlink ref="L29" r:id="rId38" display="VIDEO"/>
-    <hyperlink ref="N29" r:id="rId39" display="CODE"/>
-    <hyperlink ref="K30" r:id="rId40" display="CODE"/>
-    <hyperlink ref="L30" r:id="rId41" display="VIDEO"/>
-    <hyperlink ref="K31" r:id="rId42" display="PDF"/>
-    <hyperlink ref="L31" r:id="rId43" display="VIDEO"/>
-    <hyperlink ref="K32" r:id="rId44" display="PDF"/>
-    <hyperlink ref="L32" r:id="rId45" display="VIDEO"/>
-    <hyperlink ref="K33" r:id="rId46" display="PDF"/>
-    <hyperlink ref="L33" r:id="rId47" display="VIDEO"/>
-    <hyperlink ref="M33" r:id="rId48" display="VIDEO"/>
-    <hyperlink ref="K34" r:id="rId49" display="VIDEO"/>
-    <hyperlink ref="K35" r:id="rId50" display="PDF"/>
-    <hyperlink ref="L35" r:id="rId51" display="VIDEO"/>
-    <hyperlink ref="K36" r:id="rId52" display="PDF"/>
-    <hyperlink ref="L36" r:id="rId53" display="VIDEO"/>
-    <hyperlink ref="K37" r:id="rId54" display="PDF"/>
-    <hyperlink ref="L37" r:id="rId55" display="VIDEO"/>
-    <hyperlink ref="K38" r:id="rId56" display="PDF"/>
-    <hyperlink ref="L38" r:id="rId57" display="VIDEO"/>
-    <hyperlink ref="K39" r:id="rId58" display="PDF"/>
-    <hyperlink ref="L39" r:id="rId59" display="VIDEO"/>
-    <hyperlink ref="N39" r:id="rId60" display="CODE"/>
-    <hyperlink ref="O39" r:id="rId61" display="CODE"/>
-    <hyperlink ref="L40" r:id="rId62" display="VIDEO"/>
-    <hyperlink ref="N40" r:id="rId63" display="CODE"/>
-    <hyperlink ref="K41" r:id="rId64" display="CODE"/>
-    <hyperlink ref="L41" r:id="rId65" display="VIDEO"/>
-    <hyperlink ref="K43" r:id="rId66" display="PDF"/>
-    <hyperlink ref="L43" r:id="rId67" display="VIDEO"/>
-    <hyperlink ref="K44" r:id="rId68" display="PDF"/>
-    <hyperlink ref="L44" r:id="rId69" display="VIDEO"/>
-    <hyperlink ref="K45" r:id="rId70" display="PDF"/>
-    <hyperlink ref="K47" r:id="rId71" display="PDF"/>
-    <hyperlink ref="L47" r:id="rId72" display="VIDEO"/>
-    <hyperlink ref="N47" r:id="rId73" display="CODE"/>
-    <hyperlink ref="K48" r:id="rId74" display="PDF"/>
+    <hyperlink ref="K27" r:id="rId36" display="PDF"/>
+    <hyperlink ref="L28" r:id="rId37" display="VIDEO"/>
+    <hyperlink ref="N28" r:id="rId38" display="CODE"/>
+    <hyperlink ref="K29" r:id="rId39" display="CODE"/>
+    <hyperlink ref="L29" r:id="rId40" display="VIDEO"/>
+    <hyperlink ref="K30" r:id="rId41" display="PDF"/>
+    <hyperlink ref="L30" r:id="rId42" display="VIDEO"/>
+    <hyperlink ref="K31" r:id="rId43" display="PDF"/>
+    <hyperlink ref="L31" r:id="rId44" display="VIDEO"/>
+    <hyperlink ref="K32" r:id="rId45" display="PDF"/>
+    <hyperlink ref="L32" r:id="rId46" display="VIDEO"/>
+    <hyperlink ref="M32" r:id="rId47" display="VIDEO"/>
+    <hyperlink ref="K33" r:id="rId48" display="VIDEO"/>
+    <hyperlink ref="K34" r:id="rId49" display="PDF"/>
+    <hyperlink ref="L34" r:id="rId50" display="VIDEO"/>
+    <hyperlink ref="K35" r:id="rId51" display="PDF"/>
+    <hyperlink ref="L35" r:id="rId52" display="VIDEO"/>
+    <hyperlink ref="K36" r:id="rId53" display="PDF"/>
+    <hyperlink ref="L36" r:id="rId54" display="VIDEO"/>
+    <hyperlink ref="K37" r:id="rId55" display="PDF"/>
+    <hyperlink ref="L37" r:id="rId56" display="VIDEO"/>
+    <hyperlink ref="K38" r:id="rId57" display="PDF"/>
+    <hyperlink ref="L38" r:id="rId58" display="VIDEO"/>
+    <hyperlink ref="N38" r:id="rId59" display="CODE"/>
+    <hyperlink ref="O38" r:id="rId60" display="CODE"/>
+    <hyperlink ref="L39" r:id="rId61" display="VIDEO"/>
+    <hyperlink ref="N39" r:id="rId62" display="CODE"/>
+    <hyperlink ref="K40" r:id="rId63" display="CODE"/>
+    <hyperlink ref="L40" r:id="rId64" display="VIDEO"/>
+    <hyperlink ref="K42" r:id="rId65" display="PDF"/>
+    <hyperlink ref="L42" r:id="rId66" display="VIDEO"/>
+    <hyperlink ref="K43" r:id="rId67" display="PDF"/>
+    <hyperlink ref="L43" r:id="rId68" display="VIDEO"/>
+    <hyperlink ref="K44" r:id="rId69" display="PDF"/>
+    <hyperlink ref="K46" r:id="rId70" display="PDF"/>
+    <hyperlink ref="L46" r:id="rId71" display="VIDEO"/>
+    <hyperlink ref="N46" r:id="rId72" display="CODE"/>
+    <hyperlink ref="K47" r:id="rId73" display="PDF"/>
+    <hyperlink ref="K48" r:id="rId74" display="CODE"/>
     <hyperlink ref="K49" r:id="rId75" display="CODE"/>
-    <hyperlink ref="K50" r:id="rId76" display="CODE"/>
-    <hyperlink ref="K51" r:id="rId77" display="VIDEO"/>
-    <hyperlink ref="K52" r:id="rId78" display="PDF"/>
-    <hyperlink ref="L52" r:id="rId79" display="VIDEO"/>
-    <hyperlink ref="N52" r:id="rId80" display="CODE"/>
-    <hyperlink ref="K55" r:id="rId81" display="PDF"/>
-    <hyperlink ref="K56" r:id="rId82" display="PDF"/>
-    <hyperlink ref="K57" r:id="rId83" display="PDF"/>
-    <hyperlink ref="K58" r:id="rId84" display="PDF"/>
-    <hyperlink ref="K59" r:id="rId85" display="PDF"/>
-    <hyperlink ref="K60" r:id="rId86" display="PDF"/>
-    <hyperlink ref="K61" r:id="rId87" display="PDF"/>
-    <hyperlink ref="K62" r:id="rId88" display="PDF"/>
-    <hyperlink ref="N62" r:id="rId89" display="CODE"/>
-    <hyperlink ref="K63" r:id="rId90" display="PDF"/>
-    <hyperlink ref="K64" r:id="rId91" display="PDF"/>
-    <hyperlink ref="K65" r:id="rId92" display="PDF"/>
-    <hyperlink ref="L65" r:id="rId93" display="VIDEO"/>
-    <hyperlink ref="K66" r:id="rId94" display="PDF"/>
-    <hyperlink ref="L66" r:id="rId95" display="VIDEO"/>
-    <hyperlink ref="K67" r:id="rId96" display="PDF"/>
-    <hyperlink ref="L67" r:id="rId97" display="VIDEO"/>
-    <hyperlink ref="K69" r:id="rId98" display="PDF"/>
-    <hyperlink ref="L69" r:id="rId99" display="VIDEO"/>
-    <hyperlink ref="K70" r:id="rId100" display="PDF"/>
-    <hyperlink ref="L70" r:id="rId101" display="VIDEO"/>
-    <hyperlink ref="K71" r:id="rId102" display="PDF"/>
-    <hyperlink ref="L71" r:id="rId103" display="VIDEO"/>
-    <hyperlink ref="K72" r:id="rId104" display="PDF"/>
-    <hyperlink ref="L72" r:id="rId105" display="VIDEO"/>
+    <hyperlink ref="K50" r:id="rId76" display="VIDEO"/>
+    <hyperlink ref="K51" r:id="rId77" display="PDF"/>
+    <hyperlink ref="L51" r:id="rId78" display="VIDEO"/>
+    <hyperlink ref="N51" r:id="rId79" display="CODE"/>
+    <hyperlink ref="K53" r:id="rId80" display="PDF"/>
+    <hyperlink ref="K54" r:id="rId81" display="PDF"/>
+    <hyperlink ref="K55" r:id="rId82" display="PDF"/>
+    <hyperlink ref="K56" r:id="rId83" display="PDF"/>
+    <hyperlink ref="K57" r:id="rId84" display="PDF"/>
+    <hyperlink ref="K58" r:id="rId85" display="PDF"/>
+    <hyperlink ref="K59" r:id="rId86" display="PDF"/>
+    <hyperlink ref="K60" r:id="rId87" display="PDF"/>
+    <hyperlink ref="N60" r:id="rId88" display="CODE"/>
+    <hyperlink ref="K61" r:id="rId89" display="PDF"/>
+    <hyperlink ref="K62" r:id="rId90" display="PDF"/>
+    <hyperlink ref="K63" r:id="rId91" display="PDF"/>
+    <hyperlink ref="L63" r:id="rId92" display="VIDEO"/>
+    <hyperlink ref="K64" r:id="rId93" display="PDF"/>
+    <hyperlink ref="L64" r:id="rId94" display="VIDEO"/>
+    <hyperlink ref="K65" r:id="rId95" display="PDF"/>
+    <hyperlink ref="L65" r:id="rId96" display="VIDEO"/>
+    <hyperlink ref="K67" r:id="rId97" display="PDF"/>
+    <hyperlink ref="L67" r:id="rId98" display="VIDEO"/>
+    <hyperlink ref="K68" r:id="rId99" display="PDF"/>
+    <hyperlink ref="L68" r:id="rId100" display="VIDEO"/>
+    <hyperlink ref="K69" r:id="rId101" display="PDF"/>
+    <hyperlink ref="L69" r:id="rId102" display="VIDEO"/>
+    <hyperlink ref="K70" r:id="rId103" display="PDF"/>
+    <hyperlink ref="L70" r:id="rId104" display="VIDEO"/>
+    <hyperlink ref="K71" r:id="rId105" display="PDF"/>
     <hyperlink ref="K73" r:id="rId106" display="PDF"/>
-    <hyperlink ref="K75" r:id="rId107" display="PDF"/>
-    <hyperlink ref="L75" r:id="rId108" display="VIDEO"/>
-    <hyperlink ref="K76" r:id="rId109" display="PDF"/>
-    <hyperlink ref="L76" r:id="rId110" display="VIDEO"/>
-    <hyperlink ref="K77" r:id="rId111" display="PDF"/>
-    <hyperlink ref="L77" r:id="rId112" display="VIDEO"/>
-    <hyperlink ref="K78" r:id="rId113" display="PDF"/>
-    <hyperlink ref="L78" r:id="rId114" display="VIDEO"/>
-    <hyperlink ref="K79" r:id="rId115" display="PDF"/>
-    <hyperlink ref="L79" r:id="rId116" display="VIDEO"/>
-    <hyperlink ref="L80" r:id="rId117" display="VIDEO"/>
-    <hyperlink ref="M80" r:id="rId118" display="VIDEO"/>
-    <hyperlink ref="K82" r:id="rId119" display="PDF"/>
-    <hyperlink ref="K83" r:id="rId120" display="PDF"/>
-    <hyperlink ref="K84" r:id="rId121" display="PDF"/>
-    <hyperlink ref="L84" r:id="rId122" display="VIDEO"/>
+    <hyperlink ref="L73" r:id="rId107" display="VIDEO"/>
+    <hyperlink ref="K74" r:id="rId108" display="PDF"/>
+    <hyperlink ref="L74" r:id="rId109" display="VIDEO"/>
+    <hyperlink ref="K75" r:id="rId110" display="PDF"/>
+    <hyperlink ref="L75" r:id="rId111" display="VIDEO"/>
+    <hyperlink ref="K76" r:id="rId112" display="PDF"/>
+    <hyperlink ref="L76" r:id="rId113" display="VIDEO"/>
+    <hyperlink ref="K77" r:id="rId114" display="PDF"/>
+    <hyperlink ref="L77" r:id="rId115" display="VIDEO"/>
+    <hyperlink ref="L78" r:id="rId116" display="VIDEO"/>
+    <hyperlink ref="M78" r:id="rId117" display="VIDEO"/>
+    <hyperlink ref="K80" r:id="rId118" display="PDF"/>
+    <hyperlink ref="K81" r:id="rId119" display="PDF"/>
+    <hyperlink ref="K82" r:id="rId120" display="PDF"/>
+    <hyperlink ref="L82" r:id="rId121" display="VIDEO"/>
+    <hyperlink ref="K84" r:id="rId122" display="PDF"/>
     <hyperlink ref="K86" r:id="rId123" display="PDF"/>
-    <hyperlink ref="K88" r:id="rId124" display="PDF"/>
+    <hyperlink ref="K87" r:id="rId124" display="PDF"/>
     <hyperlink ref="K89" r:id="rId125" display="PDF"/>
-    <hyperlink ref="K91" r:id="rId126" display="PDF"/>
-    <hyperlink ref="K92" r:id="rId127" display="PDF"/>
-    <hyperlink ref="L92" r:id="rId128" display="VIDEO"/>
-    <hyperlink ref="N92" r:id="rId129" display="CODE"/>
-    <hyperlink ref="K94" r:id="rId130" display="PDF"/>
-    <hyperlink ref="L94" r:id="rId131" display="VIDEO"/>
-    <hyperlink ref="K95" r:id="rId132" display="PDF"/>
-    <hyperlink ref="L95" r:id="rId133" display="VIDEO"/>
-    <hyperlink ref="K96" r:id="rId134" display="PDF"/>
-    <hyperlink ref="L96" r:id="rId135" display="VIDEO"/>
-    <hyperlink ref="K97" r:id="rId136" display="PDF"/>
-    <hyperlink ref="L97" r:id="rId137" display="VIDEO"/>
-    <hyperlink ref="K99" r:id="rId138" display="PDF"/>
-    <hyperlink ref="L99" r:id="rId139" display="VIDEO"/>
-    <hyperlink ref="K100" r:id="rId140" display="PDF"/>
-    <hyperlink ref="K101" r:id="rId141" display="PDF"/>
-    <hyperlink ref="L101" r:id="rId142" display="VIDEO"/>
-    <hyperlink ref="K102" r:id="rId143" display="PDF"/>
-    <hyperlink ref="L102" r:id="rId144" display="VIDEO"/>
-    <hyperlink ref="K103" r:id="rId145" display="PDF"/>
-    <hyperlink ref="L103" r:id="rId146" display="VIDEO"/>
-    <hyperlink ref="K104" r:id="rId147" display="PDF"/>
-    <hyperlink ref="L104" r:id="rId148" display="VIDEO"/>
-    <hyperlink ref="K105" r:id="rId149" display="PDF"/>
-    <hyperlink ref="L105" r:id="rId150" display="VIDEO"/>
-    <hyperlink ref="K106" r:id="rId151" display="PDF"/>
-    <hyperlink ref="L106" r:id="rId152" display="VIDEO"/>
-    <hyperlink ref="K107" r:id="rId153" display="PDF"/>
-    <hyperlink ref="L107" r:id="rId154" display="VIDEO"/>
-    <hyperlink ref="K109" r:id="rId155" display="PDF"/>
-    <hyperlink ref="L109" r:id="rId156" display="VIDEO"/>
-    <hyperlink ref="K110" r:id="rId157" display="PDF"/>
-    <hyperlink ref="L110" r:id="rId158" display="VIDEO"/>
-    <hyperlink ref="K111" r:id="rId159" display="PDF"/>
-    <hyperlink ref="L111" r:id="rId160" display="VIDEO"/>
-    <hyperlink ref="N111" r:id="rId161" display="CODE"/>
-    <hyperlink ref="K112" r:id="rId162" display="PDF"/>
-    <hyperlink ref="L112" r:id="rId163" display="VIDEO"/>
-    <hyperlink ref="N112" r:id="rId164" display="CODE"/>
-    <hyperlink ref="K113" r:id="rId165" display="PDF"/>
-    <hyperlink ref="L113" r:id="rId166" display="VIDEO"/>
-    <hyperlink ref="K114" r:id="rId167" display="PDF"/>
-    <hyperlink ref="L114" r:id="rId168" display="VIDEO"/>
-    <hyperlink ref="K116" r:id="rId169" display="PDF"/>
-    <hyperlink ref="L116" r:id="rId170" display="VIDEO"/>
-    <hyperlink ref="K117" r:id="rId171" display="PDF"/>
-    <hyperlink ref="L117" r:id="rId172" display="VIDEO"/>
-    <hyperlink ref="L118" r:id="rId173" display="VIDEO"/>
-    <hyperlink ref="N118" r:id="rId174" display="CODE"/>
-    <hyperlink ref="K120" r:id="rId175" display="PDF"/>
-    <hyperlink ref="L120" r:id="rId176" display="VIDEO"/>
-    <hyperlink ref="K121" r:id="rId177" display="PDF"/>
-    <hyperlink ref="L121" r:id="rId178" display="VIDEO"/>
-    <hyperlink ref="N121" r:id="rId179" display="CODE"/>
-    <hyperlink ref="K122" r:id="rId180" display="PDF"/>
-    <hyperlink ref="L122" r:id="rId181" display="VIDEO"/>
-    <hyperlink ref="N122" r:id="rId182" display="CODE"/>
-    <hyperlink ref="K123" r:id="rId183" display="PDF"/>
-    <hyperlink ref="K124" r:id="rId184" display="PDF"/>
-    <hyperlink ref="K125" r:id="rId185" display="PDF"/>
+    <hyperlink ref="K90" r:id="rId126" display="PDF"/>
+    <hyperlink ref="L90" r:id="rId127" display="VIDEO"/>
+    <hyperlink ref="N90" r:id="rId128" display="CODE"/>
+    <hyperlink ref="K92" r:id="rId129" display="PDF"/>
+    <hyperlink ref="L92" r:id="rId130" display="VIDEO"/>
+    <hyperlink ref="K93" r:id="rId131" display="PDF"/>
+    <hyperlink ref="L93" r:id="rId132" display="VIDEO"/>
+    <hyperlink ref="K94" r:id="rId133" display="PDF"/>
+    <hyperlink ref="L94" r:id="rId134" display="VIDEO"/>
+    <hyperlink ref="K95" r:id="rId135" display="PDF"/>
+    <hyperlink ref="L95" r:id="rId136" display="VIDEO"/>
+    <hyperlink ref="K97" r:id="rId137" display="PDF"/>
+    <hyperlink ref="L97" r:id="rId138" display="VIDEO"/>
+    <hyperlink ref="K98" r:id="rId139" display="PDF"/>
+    <hyperlink ref="K99" r:id="rId140" display="PDF"/>
+    <hyperlink ref="L99" r:id="rId141" display="VIDEO"/>
+    <hyperlink ref="K100" r:id="rId142" display="PDF"/>
+    <hyperlink ref="L100" r:id="rId143" display="VIDEO"/>
+    <hyperlink ref="K101" r:id="rId144" display="PDF"/>
+    <hyperlink ref="L101" r:id="rId145" display="VIDEO"/>
+    <hyperlink ref="K102" r:id="rId146" display="PDF"/>
+    <hyperlink ref="L102" r:id="rId147" display="VIDEO"/>
+    <hyperlink ref="K103" r:id="rId148" display="PDF"/>
+    <hyperlink ref="L103" r:id="rId149" display="VIDEO"/>
+    <hyperlink ref="K104" r:id="rId150" display="PDF"/>
+    <hyperlink ref="L104" r:id="rId151" display="VIDEO"/>
+    <hyperlink ref="K105" r:id="rId152" display="PDF"/>
+    <hyperlink ref="L105" r:id="rId153" display="VIDEO"/>
+    <hyperlink ref="K107" r:id="rId154" display="PDF"/>
+    <hyperlink ref="L107" r:id="rId155" display="VIDEO"/>
+    <hyperlink ref="K108" r:id="rId156" display="PDF"/>
+    <hyperlink ref="L108" r:id="rId157" display="VIDEO"/>
+    <hyperlink ref="K109" r:id="rId158" display="PDF"/>
+    <hyperlink ref="L109" r:id="rId159" display="VIDEO"/>
+    <hyperlink ref="N109" r:id="rId160" display="CODE"/>
+    <hyperlink ref="K110" r:id="rId161" display="PDF"/>
+    <hyperlink ref="L110" r:id="rId162" display="VIDEO"/>
+    <hyperlink ref="N110" r:id="rId163" display="CODE"/>
+    <hyperlink ref="K111" r:id="rId164" display="PDF"/>
+    <hyperlink ref="L111" r:id="rId165" display="VIDEO"/>
+    <hyperlink ref="K112" r:id="rId166" display="PDF"/>
+    <hyperlink ref="L112" r:id="rId167" display="VIDEO"/>
+    <hyperlink ref="K114" r:id="rId168" display="PDF"/>
+    <hyperlink ref="L114" r:id="rId169" display="VIDEO"/>
+    <hyperlink ref="K115" r:id="rId170" display="PDF"/>
+    <hyperlink ref="L115" r:id="rId171" display="VIDEO"/>
+    <hyperlink ref="L116" r:id="rId172" display="VIDEO"/>
+    <hyperlink ref="N116" r:id="rId173" display="CODE"/>
+    <hyperlink ref="K118" r:id="rId174" display="PDF"/>
+    <hyperlink ref="L118" r:id="rId175" display="VIDEO"/>
+    <hyperlink ref="K119" r:id="rId176" display="PDF"/>
+    <hyperlink ref="L119" r:id="rId177" display="VIDEO"/>
+    <hyperlink ref="N119" r:id="rId178" display="CODE"/>
+    <hyperlink ref="K120" r:id="rId179" display="PDF"/>
+    <hyperlink ref="L120" r:id="rId180" display="VIDEO"/>
+    <hyperlink ref="N120" r:id="rId181" display="CODE"/>
+    <hyperlink ref="K121" r:id="rId182" display="PDF"/>
+    <hyperlink ref="K122" r:id="rId183" display="PDF"/>
+    <hyperlink ref="K123" r:id="rId184" display="PDF"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.700694444444444" right="0.700694444444444" top="0.7875" bottom="0.7875" header="0.511805555555555" footer="0.511805555555555"/>
@@ -10235,7 +10351,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <legacyDrawing r:id="rId186"/>
+  <legacyDrawing r:id="rId185"/>
 </worksheet>
 </file>
 
@@ -10245,7 +10361,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.15"/>
@@ -10286,7 +10402,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10296,7 +10412,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -10311,18 +10427,18 @@
       <c r="B6" s="24"/>
       <c r="C6" s="8"/>
       <c r="E6" s="10" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
         <v>27</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10331,10 +10447,10 @@
       <c r="C7" s="8"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
@@ -10348,10 +10464,10 @@
       <c r="C8" s="8"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8" t="s">
@@ -10364,7 +10480,7 @@
       <c r="B9" s="24"/>
       <c r="C9" s="8"/>
       <c r="E9" s="6" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="5"/>
@@ -10373,7 +10489,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10382,7 +10498,7 @@
       <c r="C10" s="8"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>39</v>
@@ -10392,7 +10508,7 @@
         <v>45</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10401,17 +10517,17 @@
       <c r="C11" s="8"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10419,11 +10535,11 @@
       <c r="B12" s="24"/>
       <c r="C12" s="8"/>
       <c r="E12" s="10" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="8" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8" t="s">
@@ -10437,10 +10553,10 @@
       <c r="C13" s="8"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8" t="s">
@@ -10454,10 +10570,10 @@
       <c r="C14" s="8"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8" t="s">
@@ -10471,14 +10587,14 @@
       <c r="C15" s="8"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="J15" s="8"/>
     </row>
@@ -10487,7 +10603,7 @@
       <c r="B16" s="24"/>
       <c r="C16" s="8"/>
       <c r="E16" s="6" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="5"/>
@@ -10500,7 +10616,7 @@
       <c r="B17" s="24"/>
       <c r="C17" s="8"/>
       <c r="E17" s="10" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="8"/>
@@ -10509,8 +10625,8 @@
       <c r="J17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29"/>
+      <c r="A18" s="69"/>
+      <c r="B18" s="69"/>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
@@ -10523,13 +10639,13 @@
         <v>79</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>83</v>

--- a/server_nestjs/src/storage/Kompetenzraster.xlsx
+++ b/server_nestjs/src/storage/Kompetenzraster.xlsx
@@ -56,43 +56,8 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author> </author>
-  </authors>
-  <commentList>
-    <comment ref="L5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="0"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Sven Jacobs:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Position
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="619">
   <si>
     <t xml:space="preserve">Voraussetzungen lt. Modulhandbuch</t>
   </si>
@@ -691,10 +656,13 @@
     <t xml:space="preserve">2,3,4</t>
   </si>
   <si>
+    <t xml:space="preserve">c7b42b44-2aa9-4041-9816-680af38d5f8f</t>
+  </si>
+  <si>
     <t xml:space="preserve">Einführung in Python</t>
   </si>
   <si>
-    <t xml:space="preserve">Class aptent taciti sociosqu ad litora torquent per conubia nostra, per inceptos himenaeos. Nullam imperdiet mauris vitae dignissim pulvinar. Nulla tempor id orci vel luctus. Vivamus ut rhoncus ligula. In hac habitasse platea dictumst. Curabitur neque orci, imperdiet non dictum eu, accumsan non arcu. Nullam condimentum est non dolor mattis. </t>
+    <t xml:space="preserve">Cras condimentum nisl vel tortor pellentesque, nec luctus justo facilisis. Suspendisse accumsan eros eros, convallis pretium mi pellentesque in. Nunc.</t>
   </si>
   <si>
     <t xml:space="preserve">2,3,5</t>
@@ -706,22 +674,25 @@
     <t xml:space="preserve">Python ist eine vielseitige und populäre Programmiersprache, die sich besonders für Data Science und Machine Learning eignet und durch ihre Einfachheit und die Verfügbarkeit vieler Bibliotheken auszeichnet. Für die Installation von Python wird häufig die Anaconda-Distribution empfohlen, die neben Python auch viele nützliche Bibliotheken und Entwicklungsumgebungen wie Spyder und Jupyter-Notebooks enthält, wobei Miniconda eine schlankere Alternative darstellt.</t>
   </si>
   <si>
-    <t xml:space="preserve">VIDEO</t>
+    <t xml:space="preserve">6d66e5c1-3a03-4ad3-8c23-5c7fb7b90ea2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43150eb1-e82d-4a63-8073-45b6ae026171</t>
   </si>
   <si>
     <t xml:space="preserve">Python Installationsanleitung</t>
   </si>
   <si>
-    <t xml:space="preserve">Morbi massa leo, ultricies ut dolor scelerisque, luctus tincidunt ligula. Curabitur nec lacus at libero ornare varius sit amet ac neque. Aliquam erat volutpat. Phasellus consectetur lectus consectetur sagittis consequat. Integer varius eu diam sit amet tristique. Cras facilisis pellentesque nisi egestas porttitor. Aenean ut ante posuere, consequat justo nec.</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,6</t>
   </si>
   <si>
     <t xml:space="preserve">Python-Variablen sind Namen, die auf Speicherorte verweisen und Daten eines bestimmten Typs enthalten, wobei der Wert einer Variablen im Laufe eines Programms verändert werden kann. Python ist eine dynamisch typisierte Sprache, was bedeutet, dass der Datentyp einer Variablen nicht explizit deklariert werden muss und sich während der Laufzeit ändern kann, wobei Variablennamen sinnvoll gewählt und Groß- und Kleinschreibung beachtet werden sollten.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lorem ipsum dolor sit amet, consectetur adipiscing elit. In congue nisl nunc, a facilisis risus malesuada et. Vestibulum nec faucibus diam. Nulla in lacus elementum, volutpat dui sed, mattis nunc. Suspendisse dolor nisi, laoreet in mi eu, efficitur scelerisque lorem. Vestibulum tristique tincidunt elit, eu euismod neque eleifend sed. Fusce congue dapibus nunc, a fringilla velit accumsan non. Praesent a sem in lacus aliquet hendrerit ac vitae sem. Aliquam id. </t>
+    <t xml:space="preserve">3903342b-bb39-4592-8b4d-364800f09ba7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00c25c46-8346-4d81-86a6-3dbc39e4a6e3</t>
   </si>
   <si>
     <t xml:space="preserve">2,6,7</t>
@@ -730,6 +701,12 @@
     <t xml:space="preserve">In Python sind Anweisungen (Statements) Instruktionen, die vom Interpreter ausgeführt werden, wie zum Beispiel Funktionsaufrufe oder Wertzuweisungen an Variablen. Ausdrücke (Expressions) hingegen sind spezielle Anweisungen, die einen Wert zurückliefern, wie arithmetische Berechnungen, wobei das Gleichheitszeichen in der Programmierung als Zuweisungsoperator dient und sich von der mathematischen Bedeutung unterscheidet.</t>
   </si>
   <si>
+    <t xml:space="preserve">6de52e3c-8bf7-4f10-b4bc-11f633d3fd50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9ce7cb4b-8dc6-49ad-990a-76d73bf31ef7</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,8</t>
   </si>
   <si>
@@ -739,6 +716,12 @@
     <t xml:space="preserve">In Python sind Strings eine Sequenz von Zeichen, die in einfachen, doppelten oder dreifachen Anführungszeichen definiert werden können, wobei letztere auch Zeilenumbrüche und Anführungszeichen im Text erlauben. Strings sind in Python unveränderlich (immutable), unterstützen aber eine Vielzahl von Operationen wie Konkatenation, Wiederholung, Indizierung und eingebaute Methoden wie split, replace und format, um nur einige zu nennen.</t>
   </si>
   <si>
+    <t xml:space="preserve">ad1eb799-2e9e-4279-b396-2788a52a2c28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46d632d3-e5be-4872-86da-be692e81e424</t>
+  </si>
+  <si>
     <t xml:space="preserve">Strings</t>
   </si>
   <si>
@@ -751,12 +734,24 @@
     <t xml:space="preserve">In Python gibt es drei Haupttypen von Zahlen: Integer (ganze Zahlen), Floats (Gleitkommazahlen) und komplexe Zahlen. Während Integer und Floats für alltägliche Berechnungen verwendet werden, wobei Floats aufgrund des IEEE 754 Standards zu Rundungsfehlern führen können, sind komplexe Zahlen mit einem imaginären Teil (in Python mit 'j' gekennzeichnet) für spezielle mathematische Anwendungen gedacht.</t>
   </si>
   <si>
+    <t xml:space="preserve">e6e07da5-6eb5-4e34-a7b0-944cbdb4d484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74feba64-e05e-4f58-83dd-fcaf65406b5d</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,8,10,12</t>
   </si>
   <si>
     <t xml:space="preserve">In Python gibt es drei Arten von Zahlen: Integer (ganze Zahlen), Floats (Gleitkommazahlen) und komplexe Zahlen. Während Integer und Floats für alltägliche Berechnungen genutzt werden, wobei Floats aufgrund des IEEE 754 Standards zu Rundungsfehlern führen können, sind komplexe Zahlen mit einem imaginären Teil (in Python mit 'j' gekennzeichnet) für spezielle mathematische Anwendungen vorgesehen.</t>
   </si>
   <si>
+    <t xml:space="preserve">0da90d38-8a08-4714-bfdd-a99c86f1e982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02f37e4b-e28c-4eb0-ad16-9fd02d346f61</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,8,10,13</t>
   </si>
   <si>
@@ -766,6 +761,12 @@
     <t xml:space="preserve">In Python gibt es drei Arten von Zahlen: Integer (ganze Zahlen), Floats (Gleitkommazahlen) und komplexe Zahlen. Während Integer und Floats für alltägliche Berechnungen genutzt werden, wobei Floats aufgrund des IEEE 754 Standards zu Rundungsfehlern führen können, sind komplexe Zahlen mit einem imaginären Teil (in Python mit 'j' gekennzeichnet) ein speziellerer Datentyp, der seltener verwendet wird.</t>
   </si>
   <si>
+    <t xml:space="preserve">b4d5191b-7b2c-4047-833e-c27417f4e345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47ace2db-fe3b-4dcd-ae92-d5d00a12843d</t>
+  </si>
+  <si>
     <t xml:space="preserve">Komplexe Zahlen</t>
   </si>
   <si>
@@ -778,18 +779,36 @@
     <t xml:space="preserve">Python bietet verschiedene Operatoren für mathematische Operationen, wie die Standardaddition, -subtraktion, -multiplikation und -division, sowie spezielle Operatoren für ganzzahlige Division (//), Modulus (%) und Exponentiation (**). Bei der Division von Ganzzahlen wird automatisch ein Fließkommawert zurückgegeben, während die ganzzahlige Division immer abrundet; zudem können alle Operatoren in Verbindung mit dem Zuweisungsoperator (z.B. +=, *=) für verkürzte Operationen verwendet werden.</t>
   </si>
   <si>
+    <t xml:space="preserve">03efcfad-eda1-4b7c-9ccf-d75f50fa3e5e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01600171-cee2-4c72-a432-8127c2788391</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,8,16</t>
   </si>
   <si>
     <t xml:space="preserve">In Python repräsentieren Booleans die Wahrheitswerte True und False, während None ein spezieller Datentyp ist, der zur Initialisierung von Variablen verwendet wird und nur den Wert None annehmen kann. Diese Datentypen sind essentiell für Vergleichsoperationen und Kontrollstrukturen, wobei None oft genutzt wird, um den Zustand "kein Wert" oder "nicht initialisiert" darzustellen.</t>
   </si>
   <si>
+    <t xml:space="preserve">34e378fc-083d-4cf2-be91-49fd8832b619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ce6d2406-f733-473b-ad99-ff339462c919</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,8,17</t>
   </si>
   <si>
     <t xml:space="preserve">In Python repräsentieren Booleans die Wahrheitswerte True und False, die häufig in Vergleichsoperationen verwendet werden, um logische Bedingungen zu testen. Der Datentyp None wird oft zur Initialisierung von Variablen verwendet und hat nur einen Wert, nämlich None selbst, was anzeigt, dass eine Variable noch keinen anderen Wert zugewiesen bekommen hat.</t>
   </si>
   <si>
+    <t xml:space="preserve">489bad95-fd32-46e7-952b-268c283cfe4a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e51df41b-baeb-4043-897a-a2103ecb4a02</t>
+  </si>
+  <si>
     <t xml:space="preserve">9, 10,16,17</t>
   </si>
   <si>
@@ -799,12 +818,21 @@
     <t xml:space="preserve">In Python können verschiedene Datentypen wie Int, Float und Komplex sowie Strings ineinander umgewandelt werden, indem man den entsprechenden Datentyp als Funktion verwendet (z.B. `int()`, `float()`, `str()`). Bei der Umwandlung von Eingaben ist zu beachten, dass `input()` immer einen String zurückgibt, der erst in einen numerischen Typ umgewandelt werden muss, um mathematische Operationen durchführen zu können.</t>
   </si>
   <si>
+    <t xml:space="preserve">fb6ac78c-acf4-42f1-8b65-ab55d1522566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c2affb31-d442-463f-a1fa-0aef94c24bad</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,18</t>
   </si>
   <si>
     <t xml:space="preserve">Python Kontrollstrukturen umfassen If-Statements, die mit Vergleichsoperatoren wie gleich (==), nicht gleich (!=), größer (&gt;), kleiner (&lt;), größer gleich (&gt;=) und kleiner gleich (&lt;=) arbeiten, sowie logische Operatoren wie and, or und not, um boolesche Ausdrücke zu verknüpfen. Wichtig ist dabei die korrekte Einrückung, da sie die Programmlogik bestimmt, und Schleifen wie die while-Schleife, die zur Wiederholung von Code-Blöcken verwendet wird.</t>
   </si>
   <si>
+    <t xml:space="preserve">78d7c159-7c83-4443-8838-edf61d02f7a9</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kontrolle über Programme</t>
   </si>
   <si>
@@ -814,6 +842,12 @@
     <t xml:space="preserve">In Python ermöglichen if-else-Kontrollstrukturen die Ausführung von Codeblöcken basierend auf Bedingungen, die zu wahren (True) oder falschen (False) Werten evaluiert werden. Ein if-Statement führt den nachfolgenden Codeblock aus, wenn die Bedingung wahr ist, während ein else-Statement den Codeblock ausführt, wenn alle vorherigen Bedingungen falsch sind; elif-Statements bieten zusätzliche Bedingungsüberprüfungen.</t>
   </si>
   <si>
+    <t xml:space="preserve">7746f92a-3fc5-4566-8a04-6bab9bf3c34e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62265751-3ac6-4e84-af5f-1c8190b35a2b</t>
+  </si>
+  <si>
     <t xml:space="preserve">if/else am Kartenspiel Beispiel</t>
   </si>
   <si>
@@ -829,7 +863,10 @@
     <t xml:space="preserve">In dem Code-Beispiel zur Python-Kontrollstruktur `while` wird eine Schleife verwendet, um ein Kartenspiel zu simulieren, bei dem Karten gezogen werden, bis keine mehr übrig sind. Die `while`-Schleife prüft dabei kontinuierlich, ob die Liste der Preiskarten noch Elemente enthält, und entfernt mit der `pop`-Methode jeweils das letzte Element, bis die Liste leer ist und die Schleife beendet wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">CODE</t>
+    <t xml:space="preserve">10197a89-4d56-4c27-8d0c-5b0398db9af8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e2709d08-70eb-4974-800e-d7a8ea834b0d</t>
   </si>
   <si>
     <t xml:space="preserve">while am Kartenspiel Beispiel</t>
@@ -844,6 +881,15 @@
     <t xml:space="preserve">In Python ermöglichen for-Schleifen das Durchlaufen von iterierbaren Objekten wie Listen, indem man eine Variable über die Elemente iterieren lässt, beispielsweise mit `for element in my_list`. Die `range`-Funktion wird oft in for-Schleifen verwendet, um über eine Sequenz von Zahlen zu iterieren, wobei man Start-, Stopp- und Schrittweite angeben kann, um beispielsweise mit `for i in range(1, 10, 3)` die Zahlen 1, 4 und 7 zu durchlaufen.</t>
   </si>
   <si>
+    <t xml:space="preserve">a7a30f58-631e-4d64-9f61-c93bc59e65ea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a33456d7-0175-4dd2-b6f9-599f3a9a1305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1e1012c0-76bb-4bf9-8f7e-5a4b53f40e60</t>
+  </si>
+  <si>
     <t xml:space="preserve">For-Schleifen</t>
   </si>
   <si>
@@ -853,27 +899,54 @@
     <t xml:space="preserve">2,39,40</t>
   </si>
   <si>
+    <t xml:space="preserve">c81c925d-9104-4807-9e11-2e5e5d1f6cc4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d2f03dde-b793-4d4a-8c3f-030dd01e11de</t>
+  </si>
+  <si>
     <t xml:space="preserve">Listen</t>
   </si>
   <si>
     <t xml:space="preserve">2,39,41</t>
   </si>
   <si>
+    <t xml:space="preserve">dc3a876f-2fba-4494-bf16-aa80914fdec2</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,39,42</t>
   </si>
   <si>
+    <t xml:space="preserve">24bec9c7-6e78-4b46-ba4d-a1faa644620d</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,23</t>
   </si>
   <si>
+    <t xml:space="preserve">19aca104-2bd1-472b-9a5e-74f2dc5a6b1a</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python-Funktionen ermöglichen es, Codeblöcke zu isolieren und in sinnvolle Abschnitte aufzuteilen, was die Übersichtlichkeit und Wartbarkeit von Programmen erheblich verbessert, insbesondere bei großen Projekten. Sie werden mit dem Schlüsselwort `def` definiert, können beliebig viele Eingabeargumente enthalten und mit `return` Werte zurückgeben, die dann im Hauptprogramm verwendet werden können.</t>
   </si>
   <si>
+    <t xml:space="preserve">769f3f92-09cc-4eb4-9a5f-f6763f9d2f08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9c563338-623f-4c75-80b4-ad24c1e11fa0</t>
+  </si>
+  <si>
     <t xml:space="preserve">Funktionen am Beispiel Addieren und Verdoppeln</t>
   </si>
   <si>
     <t xml:space="preserve">In dem Codebeispiel werden Teile eines Kartenspiels in Python-Funktionen ausgelagert, um den Code übersichtlicher und modularer zu gestalten. Die Funktionen `StrategieSpieler1` und `StrategieSpieler2` werden definiert, um die Strategie der Spieler zu kapseln, wobei die Funktionen Eingabeparameter wie den Wert der Preiskarte und die verbleibenden Karten des Spielers erhalten und die ausgewählte Karte zurückgeben.</t>
   </si>
   <si>
+    <t xml:space="preserve">54ac4b8c-91ab-477d-9342-e9b019c858ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302d6f24-b92b-45b0-b845-f7d56a403464</t>
+  </si>
+  <si>
     <t xml:space="preserve">Funktionen am Beispiel Goofspiel</t>
   </si>
   <si>
@@ -883,6 +956,12 @@
     <t xml:space="preserve">Python-Funktionen können mit Docstrings dokumentiert werden, die mit drei Anführungszeichen beginnen und eine systematische Beschreibung der Funktion, ihrer Parameter und Rückgabewerte enthalten. Docstrings sind besonders hilfreich in größeren Projekten, da sie es ermöglichen, die Funktionsweise von Code auch Monate später noch zu verstehen, und können mit der `help()`-Funktion abgerufen werden, um Nutzern und Entwicklern die Verwendung der Funktionen zu erleichtern.</t>
   </si>
   <si>
+    <t xml:space="preserve">916876d2-d005-485d-afd9-14a36d45a5b2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81e936ec-02c4-449f-96ec-e70edc85403a</t>
+  </si>
+  <si>
     <t xml:space="preserve">Docstring und Kommentare</t>
   </si>
   <si>
@@ -892,6 +971,12 @@
     <t xml:space="preserve">Python-Funktionen können sowohl Positional Arguments als auch Keyword Arguments akzeptieren, wobei die Reihenfolge bei Positional Arguments wichtig ist und bei Keyword Arguments durch die explizite Benennung irrelevant wird. Zusätzlich können Funktionen in Python mit `*args` und `**kwargs` eine variable Anzahl von Positional bzw. Keyword Arguments empfangen, was die Flexibilität bei der Übergabe von Argumenten erhöht.</t>
   </si>
   <si>
+    <t xml:space="preserve">0586d1bc-a676-4adb-8cdb-59a27c06b232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155bae80-afc1-4ff1-9cac-9db40cd01e66</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eingabeargumente</t>
   </si>
   <si>
@@ -901,6 +986,18 @@
     <t xml:space="preserve">In Python können Funktionen als Variablen gespeichert und verwendet werden, was bedeutet, dass man eine Funktion einer Variablen zuweisen und dann diese Variable wie eine Funktion aufrufen kann. Dies ermöglicht es, Funktionen als Argumente an andere Funktionen zu übergeben und sogenannte Higher-Order Functions zu erstellen, die Funktionen höherer Ordnung sind und von anderen Funktionen abhängen können.</t>
   </si>
   <si>
+    <t xml:space="preserve">ef0c4946-e519-41fd-b9ea-9169c1ee0f67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274ca37b-beee-4cd1-972b-c2d258b75258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8f5f8470-6f2f-4fd1-9b12-0914554cc301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65730c57-4e80-4cb7-ad2f-a058640eaa8f</t>
+  </si>
+  <si>
     <t xml:space="preserve">Funktionen als Variablen am Beispiel Goofspiel</t>
   </si>
   <si>
@@ -913,24 +1010,48 @@
     <t xml:space="preserve">Python-Funktionen können in ausgelagerten Dateien organisiert und mit dem `import`-Befehl in andere Skripte eingebunden werden, wobei der Namespace des importierten Moduls verwendet wird. Um Funktionen direkt im Namensraum verfügbar zu machen, kann `from Modul import Funktionsname` verwendet werden, während `import Modul as Alias` es ermöglicht, Funktionen mit einem benutzerdefinierten Namespace anzusprechen.</t>
   </si>
   <si>
+    <t xml:space="preserve">5a8cf9ca-0145-4c82-901a-fcdbb26ac401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b8d62fbc-2913-4319-99b2-08c5854aa054</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,23,28</t>
   </si>
   <si>
     <t xml:space="preserve">Python-Funktionen höherer Ordnung sind Funktionen, die andere Funktionen als Argumente entgegennehmen und auf Elemente einer Liste anwenden. Sie ermöglichen es, Operationen wie das Quadrieren von Zahlen oder das Hinzufügen von Absätzen zu Strings in Listen effizient durchzuführen, indem man eine allgemeine Funktion wie "auf jedes Element" definiert und diese dann mit spezifischen Funktionen für unterschiedliche Aufgaben verwendet.</t>
   </si>
   <si>
+    <t xml:space="preserve">3817eef2-f212-41b2-9b22-70f0a934e291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4265c9b9-3149-41cc-b16b-63aeb6963dcf</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,29</t>
   </si>
   <si>
     <t xml:space="preserve">In Python können Variablen entweder global oder lokal sein, wobei globale Variablen überall im Code verwendet werden können und lokale Variablen nur innerhalb der Funktion, in der sie definiert wurden. Änderungen an globalen, veränderbaren (mutable) Variablen innerhalb einer Funktion sind auch außerhalb sichtbar, während Änderungen an lokalen Variablen nach dem Funktionsaufruf nicht bestehen bleiben.</t>
   </si>
   <si>
+    <t xml:space="preserve">7185bc4d-a06f-4326-9d37-932f2920ae4f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1ff4220c-821e-4bc6-b916-87e85f363d51</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,29,30</t>
   </si>
   <si>
     <t xml:space="preserve">In Python können Variablen entweder mutable (veränderbar) oder immutable (unveränderbar) sein. Globale Variablen, die außerhalb von Funktionen definiert werden, können innerhalb von Funktionen gelesen und, wenn sie mutable sind, auch verändert werden, wobei die Änderungen dann global sichtbar sind; lokale Variablen hingegen sind nur innerhalb ihrer Funktion sichtbar und existieren außerhalb nicht.</t>
   </si>
   <si>
+    <t xml:space="preserve">38bcbb98-a103-488d-b627-e5808a8e6780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b76fa07c-0c40-4b30-bd43-ccf768a7a09a</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mutable und Immutable Variablen</t>
   </si>
   <si>
@@ -940,15 +1061,39 @@
     <t xml:space="preserve">Rekursion in Python bezeichnet das Konzept, bei dem eine Funktion sich selbst aufruft, um ein Problem zu lösen. Es ist wichtig, eine Abbruchbedingung zu definieren, um unendliche Rekursionen und damit Programmabstürze zu vermeiden; rekursive Lösungen können eleganter oder mit weniger Code als iterative Lösungen sein und verhindern die Mutation von Variablen, was sie für funktionale Programmierung attraktiv macht.</t>
   </si>
   <si>
+    <t xml:space="preserve">a854c7a7-b49f-42b3-bf79-b69ca27a9740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07d327af-e56c-4b05-99d3-8e35aaba650b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fa6a028b-2f42-4d67-be18-c4c41f64cafd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a92f962a-3402-4153-ad26-fbaa5c29bdcd</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rekursion in Python wird oft verwendet, um Probleme zu lösen, die sich in kleinere Instanzen desselben Problems aufteilen lassen, wie beispielsweise die Berechnung der Summe aller Zahlen bis zu einer gegebenen Zahl N oder die Fakultät einer Zahl. Im Transkript werden rekursive Funktionen zur Lösung solcher Probleme diskutiert, wobei die Basisfälle (Abbruchbedingungen) und die rekursiven Aufrufe, die das Problem in kleinere Teile zerlegen, zentrale Elemente sind. Ein weiteres Beispiel ist die rekursive Bestimmung von Primzahlen und die Primfaktorzerlegung einer Zahl, die ebenfalls im Transkript behandelt werden.</t>
   </si>
   <si>
+    <t xml:space="preserve">5e8ff001-3c5d-4509-a897-2f8ae1a19ba2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d6f6f2a2-a096-4300-bd50-7a6d928537e7</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rekursion mit Code-Beispielen</t>
   </si>
   <si>
     <t xml:space="preserve">In dem Codebeispiel wird die Rekursion anhand verschiedener mathematischer Probleme in Python demonstriert, wie die Summe aller Zahlen bis N, die Fakultät einer Zahl und die Überprüfung, ob eine Zahl eine Primzahl ist. Die Rekursion wird dabei als Methode zur Problemlösung verwendet, indem ein großes Problem in kleinere Instanzen heruntergebrochen wird, bis eine Instanz erreicht ist, die direkt gelöst werden kann.</t>
   </si>
   <si>
+    <t xml:space="preserve">28633773-8edd-41f1-9d9b-5c60c195e40d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4a4d2c7b-3593-4c8f-bd6b-a2bf03856e64</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rekursion am Beispiel Goofspiel</t>
   </si>
   <si>
@@ -964,15 +1109,30 @@
     <t xml:space="preserve">In Python können Variablen, die außerhalb einer Funktion definiert wurden, innerhalb der Funktion verwendet werden, sofern sie vor der Funktionsdefinition initialisiert wurden; sie gelten dann als globale Variablen. Lokale Variablen hingegen sind nur innerhalb der Funktion bekannt und Änderungen an ihnen sind außerhalb der Funktion nicht sichtbar, es sei denn, sie werden explizit als global innerhalb der Funktion deklariert.</t>
   </si>
   <si>
+    <t xml:space="preserve">658c43ba-f341-44ec-acf7-ef3da6b292bf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5fbfe84d-7a96-4e6f-ab62-8472a5f7999a</t>
+  </si>
+  <si>
     <t xml:space="preserve">Das Transkript behandelt die Unterscheidung zwischen lokalen und globalen Variablen in Python und wie sie innerhalb von Funktionen verwendet werden können. Globale Variablen können innerhalb von Funktionen gelesen werden, wenn sie vorher definiert wurden, während lokale Variablen nur innerhalb der Funktion existieren und außerhalb nicht sichtbar sind. Es wird auch erklärt, wie man mit dem Schlüsselwort `global` eine lokale Variable in einer Funktion als global deklarieren kann, sodass Änderungen an ihr auch außerhalb der Funktion sichtbar sind.</t>
   </si>
   <si>
+    <t xml:space="preserve">f294a4fc-c912-40ab-9d2c-9e341d79ab3b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50cc4e39-6613-441c-bee2-60883a0ce4b7</t>
+  </si>
+  <si>
     <t xml:space="preserve">Goofspiel funktionaler machen</t>
   </si>
   <si>
     <t xml:space="preserve">2,31,33</t>
   </si>
   <si>
+    <t xml:space="preserve">fdaf9cbc-2335-4b93-92d2-cae6c8e8c366</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,35</t>
   </si>
   <si>
@@ -982,18 +1142,39 @@
     <t xml:space="preserve">Der Befehl map nimmt eine Funktion und ein iterierbares Objekt (z.B. Liste oder Tupel) entgegen und wendet die Funktion auf jedes Element des iterierbaren Objektes an. Genauer, bekommen wir einen Iterator zurück über welchen wir iterieren können oder Methoden wie __next__() aufrufen.</t>
   </si>
   <si>
+    <t xml:space="preserve">4a3358bd-ed98-4e83-a6b7-1c59113b8c55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">914cbb7d-82b5-4ac0-9e58-be128f23495d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9a618080-fbdd-45a1-b3e2-5cbc26f8d1e7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1f5cc88f-56db-4eba-b911-362642ab6bd5</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,35,37</t>
   </si>
   <si>
+    <t xml:space="preserve">165cc4be-bb61-4d3a-9f63-e4c980456a5d</t>
+  </si>
+  <si>
     <t xml:space="preserve">Filter am Code-Beispiel Strings</t>
   </si>
   <si>
     <t xml:space="preserve">2,35,37,40</t>
   </si>
   <si>
+    <t xml:space="preserve">f13d935f-4101-4bc6-aa13-a3e665aaa83c</t>
+  </si>
+  <si>
     <t xml:space="preserve">Filter am Code-Beispiel Listen</t>
   </si>
   <si>
+    <t xml:space="preserve">94c03466-3ce2-4a5e-a9b8-085c2ffca379</t>
+  </si>
+  <si>
     <t xml:space="preserve">Filter Vorlesungsaufzeichnung</t>
   </si>
   <si>
@@ -1003,6 +1184,15 @@
     <t xml:space="preserve">Der Befehl reduce nimmt auch eine Funktion und iterierbares Objekt (z.B. Liste oder Tupel) entgegen. Die Funktion muss zwei Elemente in dem iterierbaren Objekt auf eines abbilden und reduziert nun durch sukzessives Anwenden der Funktion das gesamte iterierbare Objekt auf ein Element.</t>
   </si>
   <si>
+    <t xml:space="preserve">a7ac76ff-1ac1-4de5-92ff-fd24a68619cb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6bdadf55-b0b3-4d65-af42-a7cca8466c8d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6bfb79f3-d017-47f4-86df-de628eb0cf81</t>
+  </si>
+  <si>
     <t xml:space="preserve">reduce</t>
   </si>
   <si>
@@ -1012,54 +1202,108 @@
     <t xml:space="preserve">43,44</t>
   </si>
   <si>
+    <t xml:space="preserve">cfd5773a-cf3c-4d9a-bc23-fd52af37798e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pellentesque bibendum aliquet enim, quis ornare metus aliquet lobortis. Sed pellentesque lorem turpis, vitae tempor nunc finibus mollis. Suspendisse quis.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,45</t>
   </si>
   <si>
+    <t xml:space="preserve">d84e6630-244f-46f3-9fa9-4c3e391677f4</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46</t>
   </si>
   <si>
+    <t xml:space="preserve">ceee4725-8691-42ae-be01-c63164ede826</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,47</t>
   </si>
   <si>
+    <t xml:space="preserve">b44cb78c-a8ff-4a2d-b8fa-5c0d88629667</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,48</t>
   </si>
   <si>
+    <t xml:space="preserve">5f03b842-f8c2-4f63-8bb9-83142d6f98b3</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,49</t>
   </si>
   <si>
+    <t xml:space="preserve">5b9ff9c4-8f45-4ce2-ae79-43fee72e6ecb</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,50</t>
   </si>
   <si>
+    <t xml:space="preserve">ac5c805f-3619-4e90-99b5-3377c6d7458c</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,51</t>
   </si>
   <si>
+    <t xml:space="preserve">7f4461ab-864c-4531-8656-4616b739f5fa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6168e707-a273-4cf4-9144-9f8ef201e775</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,51,52</t>
   </si>
   <si>
     <t xml:space="preserve">Operationen auf Strings</t>
   </si>
   <si>
+    <t xml:space="preserve">74940c23-af14-4330-a019-a3f51090d4a6</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,51,53</t>
   </si>
   <si>
+    <t xml:space="preserve">2960e92b-b82d-443a-8b32-ed87447c76e1</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,54</t>
   </si>
   <si>
     <t xml:space="preserve">In Java müssen Variablen einen spezifischen Typ haben, der ihre Verwendung und die Art der Werte, die sie speichern können, bestimmt. Fehler bei der Zuweisung von Typen oder der Verwendung von Konstanten können zu Fehlermeldungen oder unerwünschtem Verhalten der Anwendung führen.</t>
   </si>
   <si>
+    <t xml:space="preserve">f16f3f43-404e-44cb-b813-9de902878f39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23023ee4-4376-432e-ab0f-7cf29c0c6204</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,55</t>
   </si>
   <si>
     <t xml:space="preserve">In Java können Typkonversionen implizit oder explizit erfolgen, wobei implizite Konversionen meist von einem kleineren zu einem größeren Datentyp ohne Informationsverlust möglich sind. Explizite Konversionen erfordern die Verwendung von Klammern und können zu Informationsverlust führen, wie beim Konvertieren von Fließkommazahlen zu Ganzzahlen, und nicht alle Typen, wie Booleans, können konvertiert werden.</t>
   </si>
   <si>
+    <t xml:space="preserve">acb1bed9-2c68-4456-b748-2c635f506b32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73b26d8e-22e0-4ebc-9bba-cd9e006296e5</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,56</t>
   </si>
   <si>
     <t xml:space="preserve">In Java werden Variablen mit einem spezifischen Namen und Typ deklariert, wobei das Schlüsselwort `final` eine Variable als unveränderliche Konstante kennzeichnet. Variablen haben einen definierten Gültigkeitsbereich, der durch Codeblöcke mit geschweiften Klammern festgelegt wird, und innerhalb desselben Gültigkeitsbereichs darf ein Variablenname nicht mehrfach verwendet werden.</t>
   </si>
   <si>
+    <t xml:space="preserve">89685233-4c76-4311-8e85-140d638192b0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4a250618-eec3-4ec9-864a-0e07d2b553d5</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,57</t>
   </si>
   <si>
@@ -1069,24 +1313,51 @@
     <t xml:space="preserve">In Java können Variablen als `final` deklariert werden, was bedeutet, dass ihr Wert nach der Initialisierung nicht mehr geändert werden kann, und sie werden somit zu Konstanten. Jede Variable hat einen bestimmten Gültigkeitsbereich, der durch Blöcke mit geschweiften Klammern definiert wird, und innerhalb dessen die Variable aktiv und bekannt ist, außerhalb jedoch nicht mehr gültig ist.</t>
   </si>
   <si>
+    <t xml:space="preserve">b29462eb-fdfa-41c2-8098-7931d3201f7c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21c7cc0d-9687-4c34-96af-6d8d714eb54d</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,57,59</t>
   </si>
   <si>
     <t xml:space="preserve">Java bietet eine Vielzahl von Operatoren, die für verschiedene Arten von Operationen verwendet werden können, darunter arithmetische, unäre, binäre und ternäre Operatoren. Zu den arithmetischen Operatoren gehören Addition, Subtraktion, Multiplikation und Division, während Vergleichsoperatoren und logische Operatoren in bedingten Anweisungen wie if-Tests verwendet werden, um Werte zu vergleichen und Boolesche Ausdrücke zu bilden.</t>
   </si>
   <si>
+    <t xml:space="preserve">e272fd46-2e10-4b71-ba54-2d9ce76e3369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440e4f75-5960-4f1c-b453-293c4f8e4484</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,57,60</t>
   </si>
   <si>
     <t xml:space="preserve">In Java sind Zuweisungen Anweisungen, bei denen Variablen Werte zugewiesen werden, wie beispielsweise bei der Zuweisung von 7 zu den Variablen x und y. Diese Zuweisungen können auch arithmetische Operationen beinhalten, wie etwa x gleich x minus 5, und werden für verschiedene Datentypen wie Integer, Float oder Double verwendet, wobei der berechnete Wert der Variablen zugewiesen wird.</t>
   </si>
   <si>
+    <t xml:space="preserve">e2815f41-b1cd-48f5-bb46-1d7403c8f7ba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21f1a4c3-c92c-4e2d-9280-4d5d1d1adf47</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,57,61</t>
   </si>
   <si>
     <t xml:space="preserve">In Java ist ein Block ein Codeabschnitt, der von geschweiften Klammern umgeben ist, innerhalb dessen definierte Variablen nur innerhalb dieses Blocks existieren und nach dessen Ende nicht mehr verfügbar sind. Anweisungen innerhalb eines Blocks werden sequenziell von oben nach unten und von links nach rechts ausgeführt, wobei jede Anweisung durch einen Strichpunkt getrennt wird, außer bei Blöcken selbst, bei denen der abschließende Strichpunkt weggelassen werden kann.</t>
   </si>
   <si>
+    <t xml:space="preserve">1a63423b-646f-40b3-927f-4c3bdd4dc01b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46d89583-f737-42ac-96ee-67dabd699552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21064003-7fec-42c1-bf24-3fb64408e567</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,62</t>
   </si>
   <si>
@@ -1096,30 +1367,60 @@
     <t xml:space="preserve">Java-Kontrollstrukturen wie if-else nutzen Blöcke, die durch geschweifte Klammern definiert sind, um Variablen und Anweisungen zu umschließen, die nur innerhalb dieser Blöcke gültig und lebendig sind. Anweisungen innerhalb eines Blocks werden sequenziell von oben nach unten und von links nach rechts ausgeführt, wobei jede Anweisung durch einen Strichpunkt getrennt wird, außer bei Blöcken selbst, bei denen der abschließende Strichpunkt weggelassen werden kann.</t>
   </si>
   <si>
+    <t xml:space="preserve">9b507e1f-590f-4e4d-82d4-7e6343e64475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e9858a81-ce4b-4969-85fe-99556d38e819</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,62,64</t>
   </si>
   <si>
     <t xml:space="preserve">Die Switch-Anweisung in Java ermöglicht es, einen Wert gegen eine Reihe von Konstanten zu prüfen und entsprechend unterschiedliche Blöcke von Anweisungen auszuführen. Jeder Block wird durch das Schlüsselwort "case" eingeleitet und muss mit einem "break" enden, um die Ausführung der Switch-Anweisung zu beenden; andernfalls wird die Ausführung fortgesetzt, bis ein "break" erreicht wird oder die gesamte Anweisung abgearbeitet ist, wobei "default" für alle nicht explizit aufgeführten Fälle verwendet wird.</t>
   </si>
   <si>
+    <t xml:space="preserve">581dc905-7db5-4223-838b-264f0dcb4301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e9587ee2-72aa-46cd-8750-a8eec7fa185a</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,62,65</t>
   </si>
   <si>
     <t xml:space="preserve">Java bietet verschiedene Schleifentypen für unterschiedliche Anwendungsfälle: Die for-Schleife eignet sich besonders, wenn die Anzahl der Durchläufe bekannt ist, wie etwa das Durchlaufen von Zahlenbereichen. Die while- und do-while-Schleifen sind hingegen nützlich, wenn die Anzahl der Wiederholungen nicht im Voraus bekannt ist, wobei die do-while-Schleife den Schleifenblock mindestens einmal ausführt, bevor die Bedingung geprüft wird, im Gegensatz zur while-Schleife, die die Bedingung vor dem ersten Durchlauf prüft.</t>
   </si>
   <si>
+    <t xml:space="preserve">746c83ca-40a6-46ef-a6f5-8a229767ab50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fdc7853c-2536-4ef2-b821-82f623b127fb</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,62,65,66</t>
   </si>
   <si>
     <t xml:space="preserve">Die while-Schleife in Java beginnt mit dem Keyword "while", gefolgt von einer Bedingung in runden Klammern; wenn diese Bedingung wahr ist, werden die in geschweiften Klammern eingeschlossenen Anweisungen ausgeführt. Die do-while-Schleife hingegen führt die Anweisungen mindestens einmal aus, bevor die Bedingung am Ende der Schleife geprüft wird, und wiederholt den Vorgang, solange die Bedingung wahr ist.</t>
   </si>
   <si>
+    <t xml:space="preserve">15d2c1fa-c6cf-4096-8ec7-c403ce84e552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9eeabe03-4fd1-42bf-ace6-d1e607a5d3dc</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,62,65,67</t>
   </si>
   <si>
     <t xml:space="preserve">Java bietet mit der For-Schleife eine Kontrollstruktur, die aus drei Teilen in runden Klammern besteht: Initialisierung (z.B. `int i = 0`), Bedingung (z.B. `i &lt;= 10`) und Inkrementierung (z.B. `i++`), die es ermöglichen, einen Codeblock wiederholt auszuführen, solange die Bedingung wahr ist. Es ist möglich, mehrere Operationen in den einzelnen Teilen der For-Schleife durchzuführen, aber üblicherweise wird sie für einfache Iterationen verwendet, wobei manchmal auch Befehle wie `continue` und `break` genutzt werden können, um die Schleifenausführung zu steuern.</t>
   </si>
   <si>
+    <t xml:space="preserve">acf82bde-ab5e-4f91-9613-3cb9e339abf0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30fc0f03-396a-4aa7-aadc-e31f812a3b7d</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,62,65,66,67</t>
   </si>
   <si>
@@ -1129,36 +1430,63 @@
     <t xml:space="preserve">In dem Beispiel BigX wird gezeigt, wie man mit Java Kontrollstrukturen wie for-Schleifen und if-Anweisungen ein großes "X" in der Konsole darstellen kann. Die Größe des "X" wird durch eine Variable bestimmt, und durch geschachtelte for-Schleifen und Bedingungen wird für jede Zeile und Spalte entschieden, ob ein "X" oder ein Leerzeichen ausgegeben wird, um die Form des "X" zu erzeugen.</t>
   </si>
   <si>
+    <t xml:space="preserve">2fc1faa3-550a-4714-a93c-eabeacdae78f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f6e07b01-b881-497c-b9fe-edf3ed625ca0</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,68</t>
   </si>
   <si>
     <t xml:space="preserve">43,68,69</t>
   </si>
   <si>
+    <t xml:space="preserve">9f2444dc-c1c9-4daa-82b9-26b916f003ae</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,68,69,70</t>
   </si>
   <si>
     <t xml:space="preserve">mehrdimansionales Array</t>
   </si>
   <si>
+    <t xml:space="preserve">bb1b43c5-9f89-42e1-a9d1-4e522837aba4</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,68,71</t>
   </si>
   <si>
     <t xml:space="preserve">Java bietet eine Vielzahl von Klassen und Paketen zur Dateiverarbeitung, die man durch Import-Anweisungen in den eigenen Code einbinden kann. Um Dateien zu lesen, zu schreiben und zu bearbeiten, muss man die entsprechenden Klassen und Methoden kennen und nutzen, wie zum Beispiel die File-Klasse für Dateioperationen und verschiedene Methoden für das Öffnen, Schließen, Lesen und Schreiben von Dateien, wobei oft ein Puffer verwendet wird, um die Effizienz zu steigern.</t>
   </si>
   <si>
+    <t xml:space="preserve">a900435c-ff38-4581-b0b5-ea7a8bb19f5b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0fe0045b-e705-469a-b03c-f7518b289627</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,72</t>
   </si>
   <si>
     <t xml:space="preserve">43,72,73</t>
   </si>
   <si>
+    <t xml:space="preserve">8e4c8072-9711-4698-9a43-337207ddcd77</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,72,75</t>
   </si>
   <si>
+    <t xml:space="preserve">8301ca1c-9896-4344-b47e-75b9352bc23e</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,72,76</t>
   </si>
   <si>
+    <t xml:space="preserve">3b6d1967-16f1-4b42-8e74-d854d40e6951</t>
+  </si>
+  <si>
     <t xml:space="preserve">Objektreferenzen</t>
   </si>
   <si>
@@ -1168,6 +1496,9 @@
     <t xml:space="preserve">Attribute und Methoden</t>
   </si>
   <si>
+    <t xml:space="preserve">61d2b624-53b5-4879-8485-952c1d7dcb20</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,72,77,79</t>
   </si>
   <si>
@@ -1177,6 +1508,15 @@
     <t xml:space="preserve">In Java können Arrays nicht nur primitive Datentypen wie Integers oder Doubles enthalten, sondern auch Objekte, wie zum Beispiel Instanzen der Klasse String oder benutzerdefinierte Klassen wie Enemies in einem Spiel. Um ein Array von Objekten zu verwenden, muss zuerst Speicherplatz für das Array reserviert werden, und anschließend müssen die einzelnen Objekte im Array mit dem Schlüsselwort 'new' tatsächlich erstellt werden, da anfänglich nur Referenzen ohne zugewiesene Objekte existieren.</t>
   </si>
   <si>
+    <t xml:space="preserve">455206d3-9539-4992-bf35-22de72eebeb7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58f8c18d-9384-492a-a888-cb04cab44d6e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9f6ad498-221e-4dfc-bb43-d92e764c1512</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,80</t>
   </si>
   <si>
@@ -1186,60 +1526,123 @@
     <t xml:space="preserve">In Java werden Methoden aufgerufen, indem man ihnen Parameter übergibt, die als Call-by-Value kopiert werden, wodurch die ursprünglichen Variablen unverändert bleiben. Beim Methodenaufruf werden die Parameterwerte auf den Stack kopiert und die Methode ausgeführt, wobei nach Beendigung der Methode die temporären Variablen auf dem Stack gelöscht werden und die ursprünglichen Variablen unverändert bleiben.</t>
   </si>
   <si>
+    <t xml:space="preserve">2d3d318f-4e05-4874-8e7f-d14921296fb2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e48e4f32-cde6-4945-be3f-b120b1713a23</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,80,82</t>
   </si>
   <si>
     <t xml:space="preserve">In Java werden Objekte und Arrays als Referenzen an Methoden übergeben (Call-by-Reference), was bedeutet, dass Änderungen an den Objekten innerhalb der Methode auch außerhalb sichtbar sind, da nicht die Werte, sondern die Referenzen auf die Speicherorte der Objekte übergeben werden. Im Gegensatz dazu werden primitive Datentypen wie int als Werte übergeben (Call-by-Value), sodass Änderungen an diesen Parametern innerhalb der Methode nicht außerhalb der Methode sichtbar sind, da Kopien der Werte übergeben werden.</t>
   </si>
   <si>
+    <t xml:space="preserve">ab7afeb0-e17f-44e9-8be8-b17cbc8f94b9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79876b13-9a54-4588-8591-644510f129fc</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,80,83</t>
   </si>
   <si>
     <t xml:space="preserve">In Java können Methoden überladen werden, indem man mehrere Methoden mit demselben Namen, aber unterschiedlichen Parametertypen oder -anzahlen definiert, sodass der Compiler anhand der übergebenen Argumente die richtige Methode auswählen kann. Überladene Methoden müssen sich in der Parameterliste unterscheiden, da der Rückgabetyp allein nicht ausreicht, um für den Compiler eine eindeutige Unterscheidung zu ermöglichen, was sonst zu Fehlern führen würde.</t>
   </si>
   <si>
+    <t xml:space="preserve">36266628-c243-4351-9c54-72dbf08b903d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35a82a7b-2154-47e1-b3d2-20b47898197a</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,80,84</t>
   </si>
   <si>
     <t xml:space="preserve">Java-Methoden können rekursiv definiert werden, indem sie sich selbst innerhalb ihrer eigenen Definition aufrufen. Ein klassisches Beispiel für Rekursion in Java ist die Berechnung der Fakultät einer Zahl, bei der die Methode sich mit einem verminderten Wert erneut aufruft, bis der Basisfall erreicht ist, und dann die Ergebnisse auf dem Weg zurück nach oben multipliziert.</t>
   </si>
   <si>
+    <t xml:space="preserve">7821b45e-3488-4818-930f-be6bde95f277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b2fab559-c5e9-417b-8340-a5b1be313da9</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,85</t>
   </si>
   <si>
     <t xml:space="preserve">Java UML bezieht sich auf die Verwendung von Unified Modeling Language (UML) Diagrammen zur Darstellung und Planung der Struktur von Java-Programmen. UML-Diagramme helfen dabei, einen Überblick über die verschiedenen Klassen und ihre Beziehungen zueinander zu schaffen, was besonders nützlich ist, wenn Projekte komplexer werden und mehrere Klassen und Objekte involviert sind.</t>
   </si>
   <si>
+    <t xml:space="preserve">67eea819-ab11-42ab-8c06-3bb5ad6aab13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3371631e-d626-4bfd-83a3-e3a4b8a9c3ce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b681b280-c818-4970-a531-2aafcf5b49c8</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,85,86</t>
   </si>
   <si>
     <t xml:space="preserve">Java UML Klassen dienen als Blaupausen für Objekte und definieren deren Struktur durch Attribute und Methoden. Während Attribute die Eigenschaften einer Klasse festlegen und Initialwerte haben können, ermöglichen Methoden die Manipulation dieser Eigenschaften und das Ausführen von Operationen; Klassen können in UML-Diagrammen unterschiedlich dargestellt werden, je nachdem ob sie Attribute, Methoden oder beides enthalten.</t>
   </si>
   <si>
+    <t xml:space="preserve">8f589647-2d48-4438-b5cf-9d4988ba00f0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4dddc1e-5025-44ce-86bd-6813eaf394c3</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,85,87</t>
   </si>
   <si>
     <t xml:space="preserve">In UML (Unified Modeling Language) können Objekte als Instanzen von Klassen dargestellt werden, wobei Objekte klein und Klassen groß geschrieben werden, getrennt durch einen Doppelpunkt. Objekte werden mit ihren Attributen und Werten gezeigt, und Beziehungen zwischen Objekten werden durch Linien repräsentiert, wobei die Identität und Gleichheit von Objekten im Speicher durch ihre Darstellung unterschieden werden kann.</t>
   </si>
   <si>
+    <t xml:space="preserve">7af88cb2-bab7-474c-a721-90b29cc868fa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23df0c13-c751-428f-86c9-6e615982aae8</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,85,88</t>
   </si>
   <si>
     <t xml:space="preserve">Java UML Attribute repräsentieren die Eigenschaften einer Klasse und können mit einer Multiplizität versehen werden, die angibt, wie viele Instanzen eines Attributs existieren dürfen. Diese Multiplizität wird in eckigen Klammern dargestellt, wobei die Untergrenze und Obergrenze durch zwei Punkte getrennt sind, und ein Stern (*) steht für eine unbestimmte Anzahl von Instanzen.</t>
   </si>
   <si>
+    <t xml:space="preserve">6156a4db-89f9-4f8f-b510-37e12793acec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4c43045d-3129-4be2-afc6-e04409e0a98e</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,85,89</t>
   </si>
   <si>
     <t xml:space="preserve">In UML werden Operationen (Methoden) einer Klasse durch runde Klammern dargestellt, um sie von Attributen zu unterscheiden, die keine Klammern haben. Die Rückgabetypen und Parameter der Operationen werden in UML spezifiziert, wobei Parameter mit "In" für Eingabeparameter gekennzeichnet werden können und der Typ mit einem Doppelpunkt vom Namen getrennt wird, wobei UML im Gegensatz zu Java nicht sofort Typfehler aufzeigt.</t>
   </si>
   <si>
+    <t xml:space="preserve">9ce7ca44-357a-4395-9c38-157fb9b2afb2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ef2671f7-8ed4-4b6f-ae89-8a3a7ba115df</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,85,90</t>
   </si>
   <si>
     <t xml:space="preserve">Java UML Assoziationen beschreiben die Beziehungen zwischen verschiedenen Klassen in einem Klassendiagramm, wobei Assoziationen die Verbindungen zwischen Objekten darstellen und durch Linien repräsentiert werden. Diese Assoziationen können verschiedene Multiplizitäten aufweisen, die angeben, wie viele Instanzen einer Klasse mit Instanzen einer anderen Klasse in Beziehung stehen können, und können auch Rollennamen enthalten, die die Art der Beziehung näher spezifizieren.</t>
   </si>
   <si>
+    <t xml:space="preserve">0e0fd849-4f1a-4485-9cdf-f79c487d50a9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7d587b36-db9d-40ab-b5a9-c248dd71001f</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,85,90,91</t>
   </si>
   <si>
@@ -1249,88 +1652,193 @@
     <t xml:space="preserve">In UML-Diagrammen kann die Navigierbarkeit von Assoziationen zwischen Klassen durch Pfeile dargestellt werden, wobei die Richtung des Pfeils die Richtung der Navigierbarkeit angibt. In Java wird diese Navigierbarkeit durch Referenzvariablen als Attribute in den Klassen implementiert, wodurch Objekte einer Klasse auf assoziierte Objekte einer anderen Klasse zugreifen können.</t>
   </si>
   <si>
+    <t xml:space="preserve">9f8bca8c-032a-4118-9eb4-96594f14fe3c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad65fa04-8848-499c-8654-55e3f68d1fbb</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,85,92</t>
   </si>
   <si>
     <t xml:space="preserve">In Java UML Sichtbarkeit werden Attribute üblicherweise als privat (private) deklariert, um die Prinzipien der Objektorientierung wie Kapselung und klare Schnittstellen zu wahren. UML verwendet spezielle Symbole, um die Sichtbarkeit zu kennzeichnen: ein Plus für öffentlich (public), ein Minus für privat (private) und ein Pfund-Symbol für geschützt (protected), wobei Get- und Set-Methoden definiert werden müssen, um den Zugriff auf private Attribute zu ermöglichen.</t>
   </si>
   <si>
+    <t xml:space="preserve">98667aa3-81c3-472e-8eda-849c71e4e278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95017bb3-978d-4cdd-917a-ba8de3c73014</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,93,94</t>
   </si>
   <si>
     <t xml:space="preserve">In Java Vererbung und Generalisierung ermöglichen es, Klassen zu schaffen, die gemeinsame Attribute und Methoden von einer Oberklasse erben, um Redundanz zu vermeiden und eine hierarchische Struktur zu schaffen. Durch die Definition einer allgemeinen Klasse wie "Person" mit grundlegenden Eigenschaften und Methoden können spezifischere Klassen wie "Angestellter", "Student" und "Hilfskraft" diese erben und um zusätzliche, spezifische Merkmale erweitern, wodurch eine klare und effiziente Objekthierarchie entsteht.</t>
   </si>
   <si>
+    <t xml:space="preserve">15904bb0-804e-4ec1-b8f4-47b06070b23c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">536e041b-9888-4a91-acfa-908959ba9471</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,93,95</t>
   </si>
   <si>
     <t xml:space="preserve">In Java können Klassen und Operationen als abstrakt definiert werden, wobei abstrakte Klassen als Vorlage dienen, von denen andere Klassen Attribute und Methoden erben, ohne dass von der abstrakten Klasse selbst Objekte instanziiert werden. UML visualisiert abstrakte Klassen und Operationen durch Kursivschrift oder das Schlüsselwort "abstrakt", und in Java wird das Schlüsselwort `abstract` verwendet, um zu kennzeichnen, dass eine Klasse oder Methode abstrakt ist und von abgeleiteten Klassen implementiert werden muss.</t>
   </si>
   <si>
+    <t xml:space="preserve">464f6a24-ba4e-44b2-bcea-e066758e1b24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">961e89af-cd16-4ede-ac9b-e16d8ddf9679</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,85,93,96</t>
   </si>
   <si>
     <t xml:space="preserve">Java UML Interfaces repräsentieren abstrakte Klassen mit ausschließlich abstrakten Methoden, die als Schnittstellen dienen und die vollständige Abkapselung von Funktionalitäten ermöglichen. Sie legen fest, welche Methoden von implementierenden Klassen definiert werden müssen, ohne selbst Instanzen zu erzeugen, und dienen als Verträge zwischen verschiedenen Entwicklern, um die Interaktion zwischen verschiedenen Teilen eines Programms zu koordinieren.</t>
   </si>
   <si>
+    <t xml:space="preserve">46fd92aa-34de-4782-bf0c-3e5e4279c427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3f8ffed4-abd2-4c50-9c79-9788810b1ef3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36acc1c6-a4ec-41f1-9868-f597862a0c1a</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,85,93,97</t>
   </si>
   <si>
     <t xml:space="preserve">In Java UML Vererbung übernimmt eine Unterklasse alle Attribute, Methoden und Anfangswerte der Oberklasse, wobei Unterklassen nie etwas von der geerbten Funktionalität löschen können. Zusätzlich können Unterklassen das Verhalten von Methoden neu definieren, indem sie diese überschreiben, wobei die überschriebenen Methoden die gleiche Signatur wie die der Oberklasse haben müssen.</t>
   </si>
   <si>
+    <t xml:space="preserve">6aeac450-f0f5-4235-b7df-cafcc9ae555f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4762eccf-5763-48d2-ab0f-21884328780c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ff59f2a4-660f-4f14-9f13-ce969939461a</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,98</t>
   </si>
   <si>
     <t xml:space="preserve">In Java ermöglicht Polymorphie, dass Methoden und Operatoren mehrere Formen annehmen können, indem sie mehrmals definiert und implementiert werden. Die Vererbungshierarchie und die Möglichkeit, Methoden zu überladen und zu überschreiben, erlauben es, dass Objekte einer Oberklasse als Objekte einer Unterklasse interpretiert werden können, wodurch zur Laufzeit die passende Methode dynamisch gebunden und ausgeführt wird, was als Polymorphismus bezeichnet wird.</t>
   </si>
   <si>
+    <t xml:space="preserve">518e1e49-1530-450d-9935-11e1b558532a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de0b421b-5139-4136-baac-0b787b4753f3</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,98,99</t>
   </si>
   <si>
     <t xml:space="preserve">In Java ist jede Klasse, die definiert wird, implizit eine Unterklasse der zentralen Objektklasse, wenn keine explizite Oberklasse angegeben wird. Diese Objektklasse stellt grundlegende Methoden wie toString und equals zur Verfügung, die von allen abgeleiteten Klassen genutzt und überschrieben werden können, um Polymorphie und andere objektorientierte Konzepte zu unterstützen.</t>
   </si>
   <si>
+    <t xml:space="preserve">eaaf62a0-6720-469c-91c0-52b9e68bbbe6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a4d090b7-221c-4932-a309-ffab11522825</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,100,101</t>
   </si>
   <si>
     <t xml:space="preserve">In Java bezeichnet der Begriff "Exceptions" Ausnahmesituationen, die während der Ausführung eines Programms auftreten können, wenn etwas Unerwartetes geschieht, wie beispielsweise eine Division durch Null. Um solche Ausnahmen zu behandeln, bietet Java die Try-Catch-Blöcke an, in denen der Code, der eine Ausnahme auslösen könnte, in einem Try-Block platziert wird und die Behandlung der Ausnahme im zugehörigen Catch-Block erfolgt, wodurch der Code übersichtlicher und robuster gegenüber Fehlern wird.</t>
   </si>
   <si>
+    <t xml:space="preserve">92fec94f-be2b-4558-bf29-b623ed45131a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">570d6e9a-69cc-4479-abda-431dc9e17355</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,100,101,102</t>
   </si>
   <si>
     <t xml:space="preserve">In Java können Entwickler eigene Ausnahmen definieren und mit dem Schlüsselwort `throw` auslösen, wobei oft ein neues Ausnahmeobjekt mit `new` erstellt wird. Die Ausnahmebehandlung erfolgt durch `try`-Blöcke, die gefolgt von `catch`-Blöcken sind, um spezifische Fehler zu fangen und zu behandeln, und optional einem `finally`-Block für Aufräumarbeiten, der unabhängig vom Erfolg der Fehlerbehandlung ausgeführt wird.</t>
   </si>
   <si>
+    <t xml:space="preserve">f22f543e-2cbc-48aa-a268-549bbcdf8e34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c5228462-fbf2-477a-965b-31a18ecef87d</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java können Ausnahmen mit Try-Catch-Blöcken behandelt werden, um Fehler während der Laufzeit zu handhaben, wie im Beispiel des WURTLE-Spiels gezeigt, bei dem Wörter aus einer Datei geladen werden. Wenn beim Laden der Datei ein Fehler auftritt, fängt der Catch-Block die Ausnahme ab und ermöglicht es dem Programm, mit einem Fallback-Wörterarray fortzufahren, ohne dass der Benutzer einen Fehler bemerkt.</t>
   </si>
   <si>
+    <t xml:space="preserve">21699b3f-2e32-45e2-a0a5-f671a0f98694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0c24b88b-ea6b-49f5-b6e2-a2ba29305814</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,103,104</t>
   </si>
   <si>
     <t xml:space="preserve">Java Dateien Streams ermöglichen es, sequenziell Daten zu lesen und zu schreiben, indem sie eine konzeptionelle Darstellung von Datenflüssen als Ströme (Streams) verwenden. In Java gibt es verschiedene Klassen im Paket java.io, wie File-InputStream und File-OutputStream, um Dateien zu lesen bzw. zu schreiben, sowie weitere spezialisierte Streams für bidirektionale Zugriffe oder das Verarbeiten von Objekten und primitiven Datentypen.</t>
   </si>
   <si>
+    <t xml:space="preserve">28d36645-53cb-48fe-93cc-2dc2b3876c8a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ff472184-baa6-4bd0-92ed-2ca9e91215f9</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,103,105</t>
   </si>
   <si>
     <t xml:space="preserve">Java-Dateien-Serialisierung ermöglicht es, komplexe Objektstrukturen, die im Speicher eines Programms existieren, in eine sequenzielle Byte-Reihenfolge umzuwandeln und dauerhaft zu speichern, um sie später wiederherstellen zu können. In Java wird dies durch die Implementierung des Serializable-Interfaces erreicht, wobei die Serialisierung und Deserialisierung von Objekten rekursiv erfolgt, um alle verknüpften Objekte und deren Attribute zu erfassen und in einem Stream zu speichern oder aus diesem zu lesen.</t>
   </si>
   <si>
+    <t xml:space="preserve">1e770da7-7997-4b68-870b-b217491e3b49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e870474f-0b0d-4268-b517-a861b8f795a6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">922d59cb-9209-4533-a6a7-80f0b501a2f0</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,103,106</t>
   </si>
   <si>
     <t xml:space="preserve">Java bietet mit Reader und Writer Klassen eine Möglichkeit, Text zeichenorientiert statt byte-orientiert zu verarbeiten, was insbesondere für die strukturierte Ausgabe von Daten wie Studenteninformationen in Textdateien nützlich ist. Diese Klassen ermöglichen es, Daten zu lesen und zu schreiben, wobei die Daten als Strings repräsentiert werden, was mehr Speicherplatz beanspruchen kann als die reine Byte-Darstellung.</t>
   </si>
   <si>
+    <t xml:space="preserve">85929eed-e41b-4ad3-8824-fe50066cefdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">755c961e-2b0f-46a7-bcf0-eae69016c103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fab0567f-4eac-4351-a5b1-ea323b1549be</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,107</t>
   </si>
   <si>
+    <t xml:space="preserve">1b9afa84-fae6-4682-b16a-8bdb3def80d3</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,108</t>
   </si>
   <si>
+    <t xml:space="preserve">cd49aafd-4a0a-4670-b4d7-83ba456fcfd3</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,108,109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fe681e57-e984-4ef6-9bbc-0c6ddc6fc85e</t>
   </si>
   <si>
     <t xml:space="preserve">Zusatz ohne Ziel- bzw. Kompetenzfomulierung</t>
@@ -1417,7 +1925,7 @@
     <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1488,6 +1996,21 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF2A6099"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2A6099"/>
+      <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1590,7 +2113,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="71">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1739,19 +2262,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1771,12 +2294,8 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1791,10 +2310,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1804,7 +2319,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="5" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="7" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1812,7 +2327,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="5" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="7" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1827,15 +2342,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1843,11 +2358,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1871,6 +2382,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1879,8 +2394,8 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1941,7 +2456,7 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF2A6099"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
@@ -1962,7 +2477,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I245"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.15"/>
@@ -5445,7 +5960,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:S1048576"/>
-  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.76953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.41"/>
@@ -5459,7 +5974,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="31.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="11" style="0" width="12.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="63.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="63.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5546,7 +6061,7 @@
       <c r="Q2" s="1"/>
       <c r="S2" s="15"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="n">
         <v>3</v>
       </c>
@@ -5602,17 +6117,17 @@
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="39" t="s">
-        <v>87</v>
+        <v>199</v>
       </c>
       <c r="L4" s="37"/>
       <c r="M4" s="37"/>
       <c r="N4" s="37"/>
       <c r="O4" s="37"/>
       <c r="P4" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="R4" s="40"/>
     </row>
@@ -5626,10 +6141,10 @@
       </c>
       <c r="D5" s="33"/>
       <c r="E5" s="21" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G5" s="32" t="n">
         <v>2</v>
@@ -5641,26 +6156,26 @@
         <v>1</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>87</v>
+        <v>205</v>
       </c>
       <c r="L5" s="39" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M5" s="39"/>
       <c r="N5" s="37"/>
       <c r="O5" s="37"/>
       <c r="P5" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="R5" s="40"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="41" t="n">
         <v>6</v>
       </c>
@@ -5672,7 +6187,7 @@
       </c>
       <c r="D6" s="42"/>
       <c r="E6" s="42" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>90</v>
@@ -5687,22 +6202,22 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K6" s="45" t="s">
-        <v>87</v>
+        <v>210</v>
       </c>
       <c r="L6" s="45" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="M6" s="45"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="46"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
       <c r="P6" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="Q6" s="5" t="s">
-        <v>209</v>
+      <c r="Q6" s="8" t="s">
+        <v>201</v>
       </c>
       <c r="R6" s="40"/>
     </row>
@@ -5718,9 +6233,9 @@
       </c>
       <c r="D7" s="42"/>
       <c r="E7" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="F7" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" s="46" t="s">
         <v>91</v>
       </c>
       <c r="G7" s="41" t="n">
@@ -5733,24 +6248,26 @@
         <v>1</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K7" s="45" t="s">
-        <v>87</v>
+        <v>214</v>
       </c>
       <c r="L7" s="45" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="M7" s="45"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="45"/>
       <c r="P7" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="48"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q7" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R7" s="47"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="n">
         <v>8</v>
       </c>
@@ -5760,7 +6277,7 @@
       <c r="C8" s="32"/>
       <c r="D8" s="21"/>
       <c r="E8" s="21" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F8" s="24" t="s">
         <v>92</v>
@@ -5771,20 +6288,22 @@
       <c r="H8" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="49"/>
+      <c r="I8" s="48"/>
       <c r="J8" s="12"/>
       <c r="K8" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="50"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
       <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
+      <c r="Q8" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="R8" s="40"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="n">
         <v>9</v>
       </c>
@@ -5794,37 +6313,39 @@
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="F9" s="51" t="s">
+        <v>217</v>
+      </c>
+      <c r="F9" s="49" t="s">
         <v>93</v>
       </c>
       <c r="G9" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="H9" s="52" t="n">
+      <c r="H9" s="50" t="n">
         <v>3</v>
       </c>
       <c r="I9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>87</v>
+        <v>219</v>
       </c>
       <c r="L9" s="39" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="M9" s="39"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="39"/>
       <c r="P9" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="48"/>
+        <v>221</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R9" s="47"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="n">
@@ -5834,15 +6355,15 @@
       <c r="C10" s="32"/>
       <c r="D10" s="24"/>
       <c r="E10" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="F10" s="51" t="s">
+        <v>222</v>
+      </c>
+      <c r="F10" s="49" t="s">
         <v>94</v>
       </c>
       <c r="G10" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="H10" s="52" t="n">
+      <c r="H10" s="50" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="32" t="n">
@@ -5850,15 +6371,17 @@
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="39"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="50"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="39"/>
       <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
+      <c r="Q10" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="R10" s="40"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="n">
         <v>11</v>
       </c>
@@ -5868,9 +6391,9 @@
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="F11" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="F11" s="51" t="s">
         <v>133</v>
       </c>
       <c r="G11" s="32" t="n">
@@ -5883,24 +6406,26 @@
         <v>1</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="K11" s="39" t="s">
-        <v>87</v>
+        <v>225</v>
       </c>
       <c r="L11" s="39" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="M11" s="39"/>
-      <c r="N11" s="50"/>
-      <c r="O11" s="50"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
       <c r="P11" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="Q11" s="8"/>
+      <c r="Q11" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="R11" s="40"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="n">
         <v>12</v>
       </c>
@@ -5910,9 +6435,9 @@
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="F12" s="53" t="s">
+        <v>227</v>
+      </c>
+      <c r="F12" s="51" t="s">
         <v>134</v>
       </c>
       <c r="G12" s="32" t="n">
@@ -5925,24 +6450,26 @@
         <v>1</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>87</v>
+        <v>229</v>
       </c>
       <c r="L12" s="39" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="M12" s="39"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
       <c r="P12" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="Q12" s="8"/>
+      <c r="Q12" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="R12" s="40"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="n">
         <v>13</v>
       </c>
@@ -5952,10 +6479,10 @@
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="F13" s="53" t="s">
-        <v>222</v>
+        <v>231</v>
+      </c>
+      <c r="F13" s="51" t="s">
+        <v>232</v>
       </c>
       <c r="G13" s="32" t="n">
         <v>10</v>
@@ -5967,38 +6494,40 @@
         <v>1</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="K13" s="39" t="s">
-        <v>87</v>
+        <v>234</v>
       </c>
       <c r="L13" s="39" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="M13" s="39"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="50"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
       <c r="P13" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q13" s="8"/>
+        <v>236</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="R13" s="40"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="n">
         <v>14</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C14" s="32" t="n">
         <v>10</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="F14" s="53" t="s">
+        <v>238</v>
+      </c>
+      <c r="F14" s="51" t="s">
         <v>101</v>
       </c>
       <c r="G14" s="32" t="n">
@@ -6011,21 +6540,23 @@
         <v>1</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>87</v>
+        <v>240</v>
       </c>
       <c r="L14" s="39" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="M14" s="39"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="50"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
       <c r="P14" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="Q14" s="8"/>
+      <c r="Q14" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="R14" s="40"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6038,7 +6569,7 @@
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="24" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F15" s="38" t="s">
         <v>97</v>
@@ -6053,21 +6584,23 @@
         <v>1</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="K15" s="39" t="s">
-        <v>87</v>
+        <v>244</v>
       </c>
       <c r="L15" s="39" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="M15" s="39"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="50"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
       <c r="P15" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="Q15" s="8"/>
+      <c r="Q15" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="R15" s="40"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6080,7 +6613,7 @@
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>98</v>
@@ -6095,41 +6628,43 @@
         <v>1</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="K16" s="39" t="s">
-        <v>87</v>
+        <v>248</v>
       </c>
       <c r="L16" s="39" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="M16" s="39"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="50"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
       <c r="P16" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="Q16" s="8"/>
+      <c r="Q16" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="R16" s="40"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="C17" s="32" t="n">
         <v>11</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="F17" s="53" t="s">
+        <v>251</v>
+      </c>
+      <c r="F17" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G17" s="49" t="n">
+      <c r="G17" s="48" t="n">
         <v>8</v>
       </c>
       <c r="H17" s="32" t="n">
@@ -6139,28 +6674,30 @@
         <v>1</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="K17" s="39" t="s">
-        <v>87</v>
+        <v>253</v>
       </c>
       <c r="L17" s="39" t="s">
-        <v>204</v>
+        <v>254</v>
       </c>
       <c r="M17" s="39"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="50"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="39"/>
       <c r="P17" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="Q17" s="8"/>
+      <c r="Q17" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="R17" s="40"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="41" t="n">
         <v>18</v>
       </c>
-      <c r="B18" s="54" t="n">
+      <c r="B18" s="52" t="n">
         <v>8</v>
       </c>
       <c r="C18" s="41" t="n">
@@ -6168,7 +6705,7 @@
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="23" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="F18" s="23" t="s">
         <v>102</v>
@@ -6183,19 +6720,21 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="K18" s="45"/>
       <c r="L18" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M18" s="46"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="46"/>
+        <v>257</v>
+      </c>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="45"/>
       <c r="P18" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q18" s="5"/>
+        <v>258</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="R18" s="40"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6208,9 +6747,9 @@
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="F19" s="47" t="s">
+        <v>259</v>
+      </c>
+      <c r="F19" s="46" t="s">
         <v>103</v>
       </c>
       <c r="G19" s="41" t="n">
@@ -6223,22 +6762,24 @@
         <v>1</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="K19" s="45"/>
+        <v>260</v>
+      </c>
+      <c r="K19" s="45" t="s">
+        <v>261</v>
+      </c>
       <c r="L19" s="45" t="s">
-        <v>204</v>
+        <v>262</v>
       </c>
       <c r="M19" s="45"/>
-      <c r="N19" s="45" t="s">
-        <v>87</v>
-      </c>
+      <c r="N19" s="45"/>
       <c r="O19" s="45"/>
       <c r="P19" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="48"/>
+        <v>263</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R19" s="47"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="41" t="n">
@@ -6252,9 +6793,9 @@
         <v>19</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="F20" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="F20" s="46" t="s">
         <v>105</v>
       </c>
       <c r="G20" s="41" t="n">
@@ -6268,15 +6809,17 @@
       </c>
       <c r="J20" s="20"/>
       <c r="K20" s="45"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="46"/>
-      <c r="O20" s="46"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="45"/>
       <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
+      <c r="Q20" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="R20" s="40"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="41" t="n">
         <v>21</v>
       </c>
@@ -6286,10 +6829,10 @@
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="23" t="s">
-        <v>242</v>
-      </c>
-      <c r="F21" s="55" t="s">
-        <v>243</v>
+        <v>265</v>
+      </c>
+      <c r="F21" s="53" t="s">
+        <v>266</v>
       </c>
       <c r="G21" s="41" t="n">
         <v>20</v>
@@ -6301,24 +6844,26 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="K21" s="45"/>
       <c r="L21" s="45" t="s">
-        <v>204</v>
+        <v>268</v>
       </c>
       <c r="M21" s="45"/>
       <c r="N21" s="45" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="O21" s="45"/>
       <c r="P21" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q21" s="5"/>
+        <v>270</v>
+      </c>
+      <c r="Q21" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="R21" s="40"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="41" t="n">
         <v>22</v>
       </c>
@@ -6328,10 +6873,10 @@
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="F22" s="55" t="s">
-        <v>248</v>
+        <v>271</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>272</v>
       </c>
       <c r="G22" s="41" t="n">
         <v>20</v>
@@ -6343,174 +6888,184 @@
         <v>1</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="K22" s="45" t="s">
-        <v>87</v>
+        <v>274</v>
       </c>
       <c r="L22" s="45" t="s">
-        <v>204</v>
+        <v>275</v>
       </c>
       <c r="M22" s="45"/>
       <c r="N22" s="45" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="O22" s="45"/>
       <c r="P22" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="48"/>
-    </row>
-    <row r="23" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="56" t="n">
+        <v>277</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R22" s="47"/>
+    </row>
+    <row r="23" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="54" t="n">
         <v>39</v>
       </c>
-      <c r="B23" s="57" t="n">
+      <c r="B23" s="55" t="n">
         <v>8</v>
       </c>
-      <c r="C23" s="56"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57" t="s">
-        <v>251</v>
-      </c>
-      <c r="F23" s="57" t="s">
+      <c r="C23" s="54"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55" t="s">
+        <v>278</v>
+      </c>
+      <c r="F23" s="55" t="s">
         <v>126</v>
       </c>
-      <c r="G23" s="56" t="n">
+      <c r="G23" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="56" t="n">
+      <c r="H23" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="I23" s="56"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="59"/>
-      <c r="L23" s="59"/>
-      <c r="M23" s="59"/>
-      <c r="N23" s="59"/>
-      <c r="O23" s="59"/>
-      <c r="P23" s="58"/>
-      <c r="Q23" s="58"/>
-      <c r="R23" s="60"/>
-    </row>
-    <row r="24" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="56" t="n">
+      <c r="I23" s="54"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="57"/>
+      <c r="P23" s="56"/>
+      <c r="Q23" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R23" s="58"/>
+    </row>
+    <row r="24" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="54" t="n">
         <v>40</v>
       </c>
-      <c r="B24" s="57"/>
-      <c r="C24" s="56" t="n">
+      <c r="B24" s="55"/>
+      <c r="C24" s="54" t="n">
         <v>42</v>
       </c>
-      <c r="D24" s="57"/>
-      <c r="E24" s="57" t="s">
-        <v>252</v>
-      </c>
-      <c r="F24" s="62" t="s">
+      <c r="D24" s="55"/>
+      <c r="E24" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="F24" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="56" t="n">
+      <c r="G24" s="54" t="n">
         <v>39</v>
       </c>
-      <c r="H24" s="56" t="n">
+      <c r="H24" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="I24" s="56" t="n">
+      <c r="I24" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="58"/>
-      <c r="K24" s="59"/>
-      <c r="L24" s="63" t="s">
-        <v>204</v>
-      </c>
-      <c r="M24" s="59"/>
-      <c r="N24" s="63" t="s">
-        <v>245</v>
-      </c>
-      <c r="O24" s="59"/>
-      <c r="P24" s="58" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q24" s="58"/>
-      <c r="R24" s="64"/>
-    </row>
-    <row r="25" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="56" t="n">
+      <c r="J24" s="56"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="57" t="s">
+        <v>280</v>
+      </c>
+      <c r="M24" s="57"/>
+      <c r="N24" s="57" t="s">
+        <v>281</v>
+      </c>
+      <c r="O24" s="57"/>
+      <c r="P24" s="56" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R24" s="61"/>
+    </row>
+    <row r="25" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="54" t="n">
         <v>41</v>
       </c>
-      <c r="B25" s="57"/>
-      <c r="C25" s="56" t="n">
+      <c r="B25" s="55"/>
+      <c r="C25" s="54" t="n">
         <v>43</v>
       </c>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57" t="s">
-        <v>254</v>
-      </c>
-      <c r="F25" s="62" t="s">
+      <c r="D25" s="55"/>
+      <c r="E25" s="55" t="s">
+        <v>283</v>
+      </c>
+      <c r="F25" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="G25" s="56" t="n">
+      <c r="G25" s="54" t="n">
         <v>39</v>
       </c>
-      <c r="H25" s="56" t="n">
+      <c r="H25" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="I25" s="56" t="n">
+      <c r="I25" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="58"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="63" t="s">
-        <v>245</v>
-      </c>
-      <c r="O25" s="59"/>
-      <c r="P25" s="58" t="s">
+      <c r="J25" s="56"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="57" t="s">
+        <v>284</v>
+      </c>
+      <c r="O25" s="57"/>
+      <c r="P25" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="64"/>
-    </row>
-    <row r="26" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="56" t="n">
+      <c r="Q25" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R25" s="61"/>
+    </row>
+    <row r="26" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="54" t="n">
         <v>42</v>
       </c>
-      <c r="B26" s="57"/>
-      <c r="C26" s="56" t="n">
+      <c r="B26" s="55"/>
+      <c r="C26" s="54" t="n">
         <v>44</v>
       </c>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57" t="s">
-        <v>255</v>
-      </c>
-      <c r="F26" s="62" t="s">
+      <c r="D26" s="55"/>
+      <c r="E26" s="55" t="s">
+        <v>285</v>
+      </c>
+      <c r="F26" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="G26" s="56" t="n">
+      <c r="G26" s="54" t="n">
         <v>39</v>
       </c>
-      <c r="H26" s="56" t="n">
+      <c r="H26" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="I26" s="56" t="n">
+      <c r="I26" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="58"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="59"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="63" t="s">
-        <v>245</v>
-      </c>
-      <c r="O26" s="59"/>
-      <c r="P26" s="58" t="s">
+      <c r="J26" s="56"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="O26" s="57"/>
+      <c r="P26" s="56" t="s">
         <v>129</v>
       </c>
-      <c r="Q26" s="58"/>
-      <c r="R26" s="64"/>
-    </row>
-    <row r="27" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q26" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R26" s="61"/>
+    </row>
+    <row r="27" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="32" t="n">
         <v>23</v>
       </c>
@@ -6522,7 +7077,7 @@
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="24" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="F27" s="24" t="s">
         <v>108</v>
@@ -6538,19 +7093,21 @@
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L27" s="50"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="50"/>
+        <v>288</v>
+      </c>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
       <c r="P27" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="60"/>
-    </row>
-    <row r="28" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q27" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R27" s="58"/>
+    </row>
+    <row r="28" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="32"/>
       <c r="B28" s="24"/>
       <c r="C28" s="32" t="n">
@@ -6558,7 +7115,7 @@
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="24" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="F28" s="24"/>
       <c r="G28" s="32"/>
@@ -6567,24 +7124,26 @@
         <v>1</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="K28" s="50"/>
+        <v>289</v>
+      </c>
+      <c r="K28" s="39"/>
       <c r="L28" s="39" t="s">
-        <v>204</v>
+        <v>290</v>
       </c>
       <c r="M28" s="39"/>
       <c r="N28" s="39" t="s">
-        <v>245</v>
+        <v>291</v>
       </c>
       <c r="O28" s="39"/>
       <c r="P28" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="60"/>
-    </row>
-    <row r="29" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>292</v>
+      </c>
+      <c r="Q28" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R28" s="58"/>
+    </row>
+    <row r="29" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="32"/>
       <c r="B29" s="24"/>
       <c r="C29" s="32" t="n">
@@ -6592,7 +7151,7 @@
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="24" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>109</v>
@@ -6605,24 +7164,26 @@
         <v>1</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>259</v>
+        <v>293</v>
       </c>
       <c r="K29" s="39" t="s">
-        <v>245</v>
+        <v>294</v>
       </c>
       <c r="L29" s="39" t="s">
-        <v>204</v>
+        <v>295</v>
       </c>
       <c r="M29" s="39"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="50"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="39"/>
       <c r="P29" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="60"/>
-    </row>
-    <row r="30" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>296</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R29" s="58"/>
+    </row>
+    <row r="30" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="32" t="n">
         <v>24</v>
       </c>
@@ -6632,7 +7193,7 @@
       </c>
       <c r="D30" s="24"/>
       <c r="E30" s="24" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="F30" s="38" t="s">
         <v>110</v>
@@ -6647,24 +7208,26 @@
         <v>1</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="K30" s="39" t="s">
-        <v>87</v>
+        <v>299</v>
       </c>
       <c r="L30" s="39" t="s">
-        <v>204</v>
+        <v>300</v>
       </c>
       <c r="M30" s="39"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="50"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="39"/>
       <c r="P30" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q30" s="8"/>
-      <c r="R30" s="60"/>
-    </row>
-    <row r="31" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>301</v>
+      </c>
+      <c r="Q30" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R30" s="58"/>
+    </row>
+    <row r="31" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="32" t="n">
         <v>25</v>
       </c>
@@ -6674,7 +7237,7 @@
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24" t="s">
-        <v>264</v>
+        <v>302</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>111</v>
@@ -6689,24 +7252,26 @@
         <v>1</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="K31" s="39" t="s">
-        <v>87</v>
+        <v>304</v>
       </c>
       <c r="L31" s="39" t="s">
-        <v>204</v>
+        <v>305</v>
       </c>
       <c r="M31" s="39"/>
-      <c r="N31" s="50"/>
-      <c r="O31" s="50"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="39"/>
       <c r="P31" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="60"/>
-    </row>
-    <row r="32" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>306</v>
+      </c>
+      <c r="Q31" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R31" s="58"/>
+    </row>
+    <row r="32" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="32" t="n">
         <v>26</v>
       </c>
@@ -6718,40 +7283,42 @@
       </c>
       <c r="D32" s="24"/>
       <c r="E32" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="F32" s="65" t="s">
+        <v>307</v>
+      </c>
+      <c r="F32" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="G32" s="49" t="n">
+      <c r="G32" s="48" t="n">
         <v>23</v>
       </c>
-      <c r="H32" s="49" t="n">
+      <c r="H32" s="48" t="n">
         <v>6</v>
       </c>
       <c r="I32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="K32" s="39" t="s">
-        <v>87</v>
+        <v>309</v>
       </c>
       <c r="L32" s="39" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="M32" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="N32" s="50"/>
-      <c r="O32" s="50"/>
+        <v>311</v>
+      </c>
+      <c r="N32" s="39"/>
+      <c r="O32" s="39"/>
       <c r="P32" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="Q32" s="8"/>
-    </row>
-    <row r="33" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q32" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="32"/>
       <c r="B33" s="24"/>
       <c r="C33" s="32" t="n">
@@ -6759,7 +7326,7 @@
       </c>
       <c r="D33" s="24"/>
       <c r="E33" s="24" t="s">
-        <v>267</v>
+        <v>307</v>
       </c>
       <c r="F33" s="38" t="s">
         <v>113</v>
@@ -6773,31 +7340,33 @@
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="L33" s="50"/>
-      <c r="M33" s="50"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="50"/>
+        <v>312</v>
+      </c>
+      <c r="L33" s="39"/>
+      <c r="M33" s="39"/>
+      <c r="N33" s="39"/>
+      <c r="O33" s="39"/>
       <c r="P33" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="60"/>
-    </row>
-    <row r="34" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>313</v>
+      </c>
+      <c r="Q33" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R33" s="58"/>
+    </row>
+    <row r="34" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="32" t="n">
         <v>27</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>270</v>
+        <v>314</v>
       </c>
       <c r="C34" s="32" t="n">
         <v>26</v>
       </c>
       <c r="D34" s="24"/>
       <c r="E34" s="24" t="s">
-        <v>271</v>
+        <v>315</v>
       </c>
       <c r="F34" s="38" t="s">
         <v>114</v>
@@ -6812,24 +7381,26 @@
         <v>1</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>272</v>
+        <v>316</v>
       </c>
       <c r="K34" s="39" t="s">
-        <v>87</v>
+        <v>317</v>
       </c>
       <c r="L34" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M34" s="50"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="50"/>
+        <v>318</v>
+      </c>
+      <c r="M34" s="39"/>
+      <c r="N34" s="39"/>
+      <c r="O34" s="39"/>
       <c r="P34" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="60"/>
-    </row>
-    <row r="35" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q34" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R34" s="58"/>
+    </row>
+    <row r="35" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="32" t="n">
         <v>28</v>
       </c>
@@ -6841,7 +7412,7 @@
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="24" t="s">
-        <v>273</v>
+        <v>319</v>
       </c>
       <c r="F35" s="38" t="s">
         <v>73</v>
@@ -6856,24 +7427,26 @@
         <v>1</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>274</v>
+        <v>320</v>
       </c>
       <c r="K35" s="39" t="s">
-        <v>87</v>
+        <v>321</v>
       </c>
       <c r="L35" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M35" s="50"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="50"/>
+        <v>322</v>
+      </c>
+      <c r="M35" s="39"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="39"/>
       <c r="P35" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="Q35" s="8"/>
-      <c r="R35" s="60"/>
-    </row>
-    <row r="36" s="61" customFormat="true" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q35" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R35" s="58"/>
+    </row>
+    <row r="36" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="41" t="n">
         <v>29</v>
       </c>
@@ -6885,7 +7458,7 @@
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="23" t="s">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="F36" s="42" t="s">
         <v>115</v>
@@ -6900,24 +7473,26 @@
         <v>1</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>276</v>
+        <v>324</v>
       </c>
       <c r="K36" s="45" t="s">
-        <v>87</v>
+        <v>325</v>
       </c>
       <c r="L36" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M36" s="46"/>
-      <c r="N36" s="46"/>
-      <c r="O36" s="46"/>
+        <v>326</v>
+      </c>
+      <c r="M36" s="45"/>
+      <c r="N36" s="45"/>
+      <c r="O36" s="45"/>
       <c r="P36" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="60"/>
-    </row>
-    <row r="37" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q36" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R36" s="58"/>
+    </row>
+    <row r="37" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="41" t="n">
         <v>30</v>
       </c>
@@ -6927,9 +7502,9 @@
       </c>
       <c r="D37" s="23"/>
       <c r="E37" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="F37" s="66" t="s">
+        <v>327</v>
+      </c>
+      <c r="F37" s="63" t="s">
         <v>117</v>
       </c>
       <c r="G37" s="44" t="n">
@@ -6942,176 +7517,186 @@
         <v>1</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="K37" s="45" t="s">
-        <v>87</v>
+        <v>329</v>
       </c>
       <c r="L37" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M37" s="46"/>
-      <c r="N37" s="46"/>
-      <c r="O37" s="46"/>
+        <v>330</v>
+      </c>
+      <c r="M37" s="45"/>
+      <c r="N37" s="45"/>
+      <c r="O37" s="45"/>
       <c r="P37" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="64"/>
-    </row>
-    <row r="38" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="56" t="n">
+        <v>331</v>
+      </c>
+      <c r="Q37" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R37" s="61"/>
+    </row>
+    <row r="38" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="54" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="57" t="n">
+      <c r="B38" s="55" t="n">
         <v>23</v>
       </c>
-      <c r="C38" s="56" t="n">
+      <c r="C38" s="54" t="n">
         <v>33</v>
       </c>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57" t="s">
-        <v>280</v>
-      </c>
-      <c r="F38" s="57" t="s">
+      <c r="D38" s="55"/>
+      <c r="E38" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="F38" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="G38" s="56" t="n">
+      <c r="G38" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="56" t="n">
+      <c r="H38" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="I38" s="56" t="n">
+      <c r="I38" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="58" t="s">
-        <v>281</v>
-      </c>
-      <c r="K38" s="63" t="s">
-        <v>87</v>
-      </c>
-      <c r="L38" s="63" t="s">
-        <v>204</v>
-      </c>
-      <c r="M38" s="59"/>
-      <c r="N38" s="63" t="s">
-        <v>245</v>
-      </c>
-      <c r="O38" s="63" t="s">
-        <v>245</v>
-      </c>
-      <c r="P38" s="58" t="s">
+      <c r="J38" s="56" t="s">
+        <v>333</v>
+      </c>
+      <c r="K38" s="57" t="s">
+        <v>334</v>
+      </c>
+      <c r="L38" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="M38" s="57"/>
+      <c r="N38" s="57" t="s">
+        <v>336</v>
+      </c>
+      <c r="O38" s="57" t="s">
+        <v>337</v>
+      </c>
+      <c r="P38" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="Q38" s="58"/>
-      <c r="R38" s="60"/>
-    </row>
-    <row r="39" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="56"/>
-      <c r="B39" s="57"/>
-      <c r="C39" s="56" t="n">
+      <c r="Q38" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R38" s="58"/>
+    </row>
+    <row r="39" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="54"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="54" t="n">
         <v>34</v>
       </c>
-      <c r="D39" s="57"/>
-      <c r="E39" s="57" t="s">
-        <v>280</v>
-      </c>
-      <c r="F39" s="57"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="56" t="n">
+      <c r="D39" s="55"/>
+      <c r="E39" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="F39" s="55"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="58" t="s">
-        <v>282</v>
-      </c>
-      <c r="K39" s="59"/>
-      <c r="L39" s="63" t="s">
-        <v>204</v>
-      </c>
-      <c r="M39" s="59"/>
-      <c r="N39" s="63" t="s">
-        <v>245</v>
-      </c>
-      <c r="O39" s="63"/>
-      <c r="P39" s="58" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q39" s="58"/>
-      <c r="R39" s="60"/>
-    </row>
-    <row r="40" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="56"/>
-      <c r="B40" s="57"/>
-      <c r="C40" s="56" t="n">
+      <c r="J39" s="56" t="s">
+        <v>338</v>
+      </c>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57" t="s">
+        <v>339</v>
+      </c>
+      <c r="M39" s="57"/>
+      <c r="N39" s="57" t="s">
+        <v>340</v>
+      </c>
+      <c r="O39" s="57"/>
+      <c r="P39" s="56" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q39" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R39" s="58"/>
+    </row>
+    <row r="40" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="54"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="54" t="n">
         <v>35</v>
       </c>
-      <c r="D40" s="57"/>
-      <c r="E40" s="57" t="s">
-        <v>280</v>
-      </c>
-      <c r="F40" s="62" t="s">
+      <c r="D40" s="55"/>
+      <c r="E40" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="F40" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="G40" s="56" t="n">
+      <c r="G40" s="54" t="n">
         <v>34</v>
       </c>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56" t="n">
+      <c r="H40" s="54"/>
+      <c r="I40" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="58" t="s">
-        <v>284</v>
-      </c>
-      <c r="K40" s="63" t="s">
-        <v>245</v>
-      </c>
-      <c r="L40" s="63" t="s">
-        <v>204</v>
-      </c>
-      <c r="M40" s="59"/>
-      <c r="N40" s="59"/>
-      <c r="O40" s="59"/>
-      <c r="P40" s="58" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q40" s="58"/>
-      <c r="R40" s="64"/>
-    </row>
-    <row r="41" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J40" s="56" t="s">
+        <v>342</v>
+      </c>
+      <c r="K40" s="57" t="s">
+        <v>343</v>
+      </c>
+      <c r="L40" s="57" t="s">
+        <v>344</v>
+      </c>
+      <c r="M40" s="57"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="57"/>
+      <c r="P40" s="56" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q40" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R40" s="61"/>
+    </row>
+    <row r="41" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="32" t="n">
         <v>31</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>286</v>
+        <v>346</v>
       </c>
       <c r="C41" s="32"/>
       <c r="D41" s="24"/>
-      <c r="E41" s="67" t="s">
-        <v>287</v>
+      <c r="E41" s="64" t="s">
+        <v>347</v>
       </c>
       <c r="F41" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="G41" s="49" t="n">
+      <c r="G41" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="49" t="n">
+      <c r="H41" s="48" t="n">
         <v>6</v>
       </c>
       <c r="I41" s="32"/>
       <c r="J41" s="8"/>
-      <c r="K41" s="50"/>
-      <c r="L41" s="50"/>
-      <c r="M41" s="50"/>
-      <c r="N41" s="50"/>
-      <c r="O41" s="50"/>
+      <c r="K41" s="39"/>
+      <c r="L41" s="39"/>
+      <c r="M41" s="39"/>
+      <c r="N41" s="39"/>
+      <c r="O41" s="39"/>
       <c r="P41" s="8"/>
-      <c r="Q41" s="8"/>
-      <c r="R41" s="60"/>
-    </row>
-    <row r="42" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q41" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R41" s="58"/>
+    </row>
+    <row r="42" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="32" t="n">
         <v>32</v>
       </c>
@@ -7121,7 +7706,7 @@
       </c>
       <c r="D42" s="24"/>
       <c r="E42" s="24" t="s">
-        <v>288</v>
+        <v>348</v>
       </c>
       <c r="F42" s="38" t="s">
         <v>118</v>
@@ -7136,32 +7721,34 @@
         <v>1</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>289</v>
+        <v>349</v>
       </c>
       <c r="K42" s="39" t="s">
-        <v>87</v>
+        <v>350</v>
       </c>
       <c r="L42" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M42" s="50"/>
-      <c r="N42" s="50"/>
-      <c r="O42" s="50"/>
+        <v>351</v>
+      </c>
+      <c r="M42" s="39"/>
+      <c r="N42" s="39"/>
+      <c r="O42" s="39"/>
       <c r="P42" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="60"/>
-    </row>
-    <row r="43" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q42" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R42" s="58"/>
+    </row>
+    <row r="43" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="32"/>
       <c r="B43" s="24"/>
       <c r="C43" s="32" t="n">
         <v>31</v>
       </c>
       <c r="D43" s="24"/>
-      <c r="E43" s="67" t="s">
-        <v>287</v>
+      <c r="E43" s="64" t="s">
+        <v>347</v>
       </c>
       <c r="F43" s="38" t="s">
         <v>109</v>
@@ -7174,24 +7761,26 @@
         <v>1</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>290</v>
+        <v>352</v>
       </c>
       <c r="K43" s="39" t="s">
-        <v>87</v>
+        <v>353</v>
       </c>
       <c r="L43" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M43" s="50"/>
-      <c r="N43" s="50"/>
-      <c r="O43" s="50"/>
+        <v>354</v>
+      </c>
+      <c r="M43" s="39"/>
+      <c r="N43" s="39"/>
+      <c r="O43" s="39"/>
       <c r="P43" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="64"/>
-    </row>
-    <row r="44" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>355</v>
+      </c>
+      <c r="Q43" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R43" s="61"/>
+    </row>
+    <row r="44" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="32" t="n">
         <v>33</v>
       </c>
@@ -7203,7 +7792,7 @@
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="24" t="s">
-        <v>292</v>
+        <v>356</v>
       </c>
       <c r="F44" s="38" t="s">
         <v>119</v>
@@ -7219,19 +7808,21 @@
       </c>
       <c r="J44" s="8"/>
       <c r="K44" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L44" s="50"/>
-      <c r="M44" s="50"/>
-      <c r="N44" s="50"/>
-      <c r="O44" s="50"/>
+        <v>357</v>
+      </c>
+      <c r="L44" s="39"/>
+      <c r="M44" s="39"/>
+      <c r="N44" s="39"/>
+      <c r="O44" s="39"/>
       <c r="P44" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="Q44" s="8"/>
-      <c r="R44" s="60"/>
-    </row>
-    <row r="45" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q44" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R44" s="58"/>
+    </row>
+    <row r="45" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="41" t="n">
         <v>35</v>
       </c>
@@ -7241,7 +7832,7 @@
       <c r="C45" s="41"/>
       <c r="D45" s="23"/>
       <c r="E45" s="23" t="s">
-        <v>293</v>
+        <v>358</v>
       </c>
       <c r="F45" s="23" t="s">
         <v>122</v>
@@ -7254,16 +7845,18 @@
       </c>
       <c r="I45" s="41"/>
       <c r="J45" s="5"/>
-      <c r="K45" s="46"/>
-      <c r="L45" s="46"/>
-      <c r="M45" s="46"/>
-      <c r="N45" s="46"/>
-      <c r="O45" s="46"/>
+      <c r="K45" s="45"/>
+      <c r="L45" s="45"/>
+      <c r="M45" s="45"/>
+      <c r="N45" s="45"/>
+      <c r="O45" s="45"/>
       <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
-      <c r="R45" s="60"/>
-    </row>
-    <row r="46" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q45" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R45" s="58"/>
+    </row>
+    <row r="46" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="41" t="n">
         <v>36</v>
       </c>
@@ -7273,9 +7866,9 @@
       </c>
       <c r="D46" s="23"/>
       <c r="E46" s="23" t="s">
-        <v>294</v>
-      </c>
-      <c r="F46" s="47" t="s">
+        <v>359</v>
+      </c>
+      <c r="F46" s="46" t="s">
         <v>123</v>
       </c>
       <c r="G46" s="41" t="n">
@@ -7288,26 +7881,28 @@
         <v>1</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>295</v>
+        <v>360</v>
       </c>
       <c r="K46" s="45" t="s">
-        <v>87</v>
+        <v>361</v>
       </c>
       <c r="L46" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M46" s="46"/>
+        <v>362</v>
+      </c>
+      <c r="M46" s="45"/>
       <c r="N46" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="O46" s="46"/>
+        <v>363</v>
+      </c>
+      <c r="O46" s="45"/>
       <c r="P46" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="64"/>
-    </row>
-    <row r="47" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q46" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R46" s="61"/>
+    </row>
+    <row r="47" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="41" t="n">
         <v>37</v>
       </c>
@@ -7317,9 +7912,9 @@
       </c>
       <c r="D47" s="23"/>
       <c r="E47" s="23" t="s">
-        <v>294</v>
-      </c>
-      <c r="F47" s="47" t="s">
+        <v>359</v>
+      </c>
+      <c r="F47" s="46" t="s">
         <v>124</v>
       </c>
       <c r="G47" s="41" t="n">
@@ -7333,19 +7928,21 @@
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="L47" s="46"/>
-      <c r="M47" s="46"/>
-      <c r="N47" s="46"/>
-      <c r="O47" s="46"/>
+        <v>364</v>
+      </c>
+      <c r="L47" s="45"/>
+      <c r="M47" s="45"/>
+      <c r="N47" s="45"/>
+      <c r="O47" s="45"/>
       <c r="P47" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="Q47" s="5"/>
-      <c r="R47" s="64"/>
-    </row>
-    <row r="48" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q47" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R47" s="61"/>
+    </row>
+    <row r="48" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="41"/>
       <c r="B48" s="23"/>
       <c r="C48" s="41" t="n">
@@ -7353,9 +7950,9 @@
       </c>
       <c r="D48" s="23"/>
       <c r="E48" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="F48" s="47"/>
+        <v>365</v>
+      </c>
+      <c r="F48" s="46"/>
       <c r="G48" s="41"/>
       <c r="H48" s="41"/>
       <c r="I48" s="41" t="n">
@@ -7363,19 +7960,21 @@
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="L48" s="46"/>
-      <c r="M48" s="46"/>
-      <c r="N48" s="46"/>
-      <c r="O48" s="46"/>
+        <v>366</v>
+      </c>
+      <c r="L48" s="45"/>
+      <c r="M48" s="45"/>
+      <c r="N48" s="45"/>
+      <c r="O48" s="45"/>
       <c r="P48" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q48" s="5"/>
-      <c r="R48" s="64"/>
-    </row>
-    <row r="49" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>367</v>
+      </c>
+      <c r="Q48" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R48" s="61"/>
+    </row>
+    <row r="49" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="41"/>
       <c r="B49" s="23"/>
       <c r="C49" s="41" t="n">
@@ -7383,9 +7982,9 @@
       </c>
       <c r="D49" s="23"/>
       <c r="E49" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="F49" s="47"/>
+        <v>368</v>
+      </c>
+      <c r="F49" s="46"/>
       <c r="G49" s="41"/>
       <c r="H49" s="41"/>
       <c r="I49" s="41" t="n">
@@ -7393,19 +7992,21 @@
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="L49" s="46"/>
-      <c r="M49" s="46"/>
-      <c r="N49" s="46"/>
-      <c r="O49" s="46"/>
+        <v>369</v>
+      </c>
+      <c r="L49" s="45"/>
+      <c r="M49" s="45"/>
+      <c r="N49" s="45"/>
+      <c r="O49" s="45"/>
       <c r="P49" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q49" s="5"/>
-      <c r="R49" s="64"/>
-    </row>
-    <row r="50" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>370</v>
+      </c>
+      <c r="Q49" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R49" s="61"/>
+    </row>
+    <row r="50" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="41"/>
       <c r="B50" s="23"/>
       <c r="C50" s="41" t="n">
@@ -7413,9 +8014,9 @@
       </c>
       <c r="D50" s="23"/>
       <c r="E50" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="F50" s="47"/>
+        <v>365</v>
+      </c>
+      <c r="F50" s="46"/>
       <c r="G50" s="41"/>
       <c r="H50" s="41"/>
       <c r="I50" s="41" t="n">
@@ -7423,19 +8024,21 @@
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="L50" s="46"/>
-      <c r="M50" s="46"/>
-      <c r="N50" s="46"/>
-      <c r="O50" s="46"/>
+        <v>371</v>
+      </c>
+      <c r="L50" s="45"/>
+      <c r="M50" s="45"/>
+      <c r="N50" s="45"/>
+      <c r="O50" s="45"/>
       <c r="P50" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q50" s="5"/>
-      <c r="R50" s="60"/>
-    </row>
-    <row r="51" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>372</v>
+      </c>
+      <c r="Q50" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R50" s="58"/>
+    </row>
+    <row r="51" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="41" t="n">
         <v>38</v>
       </c>
@@ -7445,9 +8048,9 @@
       </c>
       <c r="D51" s="23"/>
       <c r="E51" s="23" t="s">
-        <v>301</v>
-      </c>
-      <c r="F51" s="47" t="s">
+        <v>373</v>
+      </c>
+      <c r="F51" s="46" t="s">
         <v>125</v>
       </c>
       <c r="G51" s="41" t="n">
@@ -7460,55 +8063,57 @@
         <v>1</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>302</v>
+        <v>374</v>
       </c>
       <c r="K51" s="45" t="s">
-        <v>87</v>
+        <v>375</v>
       </c>
       <c r="L51" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M51" s="46"/>
+        <v>376</v>
+      </c>
+      <c r="M51" s="45"/>
       <c r="N51" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="O51" s="46"/>
+        <v>377</v>
+      </c>
+      <c r="O51" s="45"/>
       <c r="P51" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q51" s="5"/>
-      <c r="R51" s="64"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="68" t="n">
+        <v>378</v>
+      </c>
+      <c r="Q51" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R51" s="61"/>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="65" t="n">
         <v>43</v>
       </c>
-      <c r="B52" s="69" t="n">
+      <c r="B52" s="66" t="n">
         <v>2</v>
       </c>
-      <c r="C52" s="68"/>
-      <c r="D52" s="69"/>
-      <c r="E52" s="69" t="n">
+      <c r="C52" s="65"/>
+      <c r="D52" s="66"/>
+      <c r="E52" s="66" t="n">
         <v>43</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>304</v>
+        <v>379</v>
       </c>
       <c r="G52" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="68" t="n">
+      <c r="H52" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="I52" s="68"/>
-      <c r="K52" s="25"/>
-      <c r="L52" s="25"/>
-      <c r="M52" s="25"/>
-      <c r="N52" s="25"/>
-      <c r="O52" s="25"/>
-      <c r="R52" s="48"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I52" s="65"/>
+      <c r="K52" s="67"/>
+      <c r="L52" s="67"/>
+      <c r="M52" s="67"/>
+      <c r="N52" s="67"/>
+      <c r="O52" s="67"/>
+      <c r="R52" s="47"/>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="32" t="n">
         <v>44</v>
       </c>
@@ -7518,15 +8123,15 @@
       </c>
       <c r="D53" s="24"/>
       <c r="E53" s="24" t="s">
-        <v>305</v>
+        <v>380</v>
       </c>
       <c r="F53" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="G53" s="49" t="n">
+      <c r="G53" s="48" t="n">
         <v>43</v>
       </c>
-      <c r="H53" s="49" t="n">
+      <c r="H53" s="48" t="n">
         <v>2</v>
       </c>
       <c r="I53" s="32" t="n">
@@ -7534,17 +8139,19 @@
       </c>
       <c r="J53" s="8"/>
       <c r="K53" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L53" s="50"/>
-      <c r="M53" s="50"/>
-      <c r="N53" s="50"/>
-      <c r="O53" s="50"/>
+        <v>381</v>
+      </c>
+      <c r="L53" s="39"/>
+      <c r="M53" s="39"/>
+      <c r="N53" s="39"/>
+      <c r="O53" s="39"/>
       <c r="P53" s="8"/>
-      <c r="Q53" s="8"/>
-      <c r="R53" s="48"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q53" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R53" s="47"/>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="41" t="n">
         <v>45</v>
       </c>
@@ -7554,7 +8161,7 @@
       </c>
       <c r="D54" s="23"/>
       <c r="E54" s="23" t="s">
-        <v>306</v>
+        <v>383</v>
       </c>
       <c r="F54" s="23" t="s">
         <v>132</v>
@@ -7570,17 +8177,19 @@
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="L54" s="46"/>
-      <c r="M54" s="46"/>
-      <c r="N54" s="46"/>
-      <c r="O54" s="46"/>
+        <v>384</v>
+      </c>
+      <c r="L54" s="45"/>
+      <c r="M54" s="45"/>
+      <c r="N54" s="45"/>
+      <c r="O54" s="45"/>
       <c r="P54" s="5"/>
-      <c r="Q54" s="5"/>
-      <c r="R54" s="48"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q54" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R54" s="47"/>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="32" t="n">
         <v>46</v>
       </c>
@@ -7590,7 +8199,7 @@
       </c>
       <c r="D55" s="24"/>
       <c r="E55" s="24" t="s">
-        <v>307</v>
+        <v>385</v>
       </c>
       <c r="F55" s="24" t="s">
         <v>92</v>
@@ -7606,17 +8215,19 @@
       </c>
       <c r="J55" s="8"/>
       <c r="K55" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L55" s="50"/>
-      <c r="M55" s="50"/>
-      <c r="N55" s="50"/>
-      <c r="O55" s="50"/>
+        <v>386</v>
+      </c>
+      <c r="L55" s="39"/>
+      <c r="M55" s="39"/>
+      <c r="N55" s="39"/>
+      <c r="O55" s="39"/>
       <c r="P55" s="8"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="48"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q55" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R55" s="47"/>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="32" t="n">
         <v>47</v>
       </c>
@@ -7626,7 +8237,7 @@
       </c>
       <c r="D56" s="24"/>
       <c r="E56" s="24" t="s">
-        <v>308</v>
+        <v>387</v>
       </c>
       <c r="F56" s="38" t="s">
         <v>133</v>
@@ -7642,17 +8253,19 @@
       </c>
       <c r="J56" s="8"/>
       <c r="K56" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L56" s="50"/>
-      <c r="M56" s="50"/>
-      <c r="N56" s="50"/>
-      <c r="O56" s="50"/>
+        <v>388</v>
+      </c>
+      <c r="L56" s="39"/>
+      <c r="M56" s="39"/>
+      <c r="N56" s="39"/>
+      <c r="O56" s="39"/>
       <c r="P56" s="8"/>
-      <c r="Q56" s="8"/>
-      <c r="R56" s="48"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q56" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R56" s="47"/>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="32" t="n">
         <v>48</v>
       </c>
@@ -7664,7 +8277,7 @@
       </c>
       <c r="D57" s="24"/>
       <c r="E57" s="24" t="s">
-        <v>309</v>
+        <v>389</v>
       </c>
       <c r="F57" s="38" t="s">
         <v>134</v>
@@ -7680,17 +8293,19 @@
       </c>
       <c r="J57" s="8"/>
       <c r="K57" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L57" s="50"/>
-      <c r="M57" s="50"/>
-      <c r="N57" s="50"/>
-      <c r="O57" s="50"/>
+        <v>390</v>
+      </c>
+      <c r="L57" s="39"/>
+      <c r="M57" s="39"/>
+      <c r="N57" s="39"/>
+      <c r="O57" s="39"/>
       <c r="P57" s="8"/>
-      <c r="Q57" s="8"/>
-      <c r="R57" s="48"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q57" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R57" s="47"/>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="32" t="n">
         <v>49</v>
       </c>
@@ -7700,7 +8315,7 @@
       </c>
       <c r="D58" s="24"/>
       <c r="E58" s="24" t="s">
-        <v>310</v>
+        <v>391</v>
       </c>
       <c r="F58" s="38" t="s">
         <v>135</v>
@@ -7716,17 +8331,19 @@
       </c>
       <c r="J58" s="8"/>
       <c r="K58" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L58" s="50"/>
-      <c r="M58" s="50"/>
-      <c r="N58" s="50"/>
-      <c r="O58" s="50"/>
+        <v>392</v>
+      </c>
+      <c r="L58" s="39"/>
+      <c r="M58" s="39"/>
+      <c r="N58" s="39"/>
+      <c r="O58" s="39"/>
       <c r="P58" s="8"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="48"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q58" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R58" s="47"/>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="32" t="n">
         <v>50</v>
       </c>
@@ -7736,7 +8353,7 @@
       </c>
       <c r="D59" s="24"/>
       <c r="E59" s="24" t="s">
-        <v>311</v>
+        <v>393</v>
       </c>
       <c r="F59" s="38" t="s">
         <v>97</v>
@@ -7752,17 +8369,19 @@
       </c>
       <c r="J59" s="8"/>
       <c r="K59" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L59" s="50"/>
-      <c r="M59" s="50"/>
-      <c r="N59" s="50"/>
-      <c r="O59" s="50"/>
+        <v>394</v>
+      </c>
+      <c r="L59" s="39"/>
+      <c r="M59" s="39"/>
+      <c r="N59" s="39"/>
+      <c r="O59" s="39"/>
       <c r="P59" s="8"/>
-      <c r="Q59" s="8"/>
-      <c r="R59" s="48"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q59" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R59" s="47"/>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="32" t="n">
         <v>51</v>
       </c>
@@ -7774,7 +8393,7 @@
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="24" t="s">
-        <v>312</v>
+        <v>395</v>
       </c>
       <c r="F60" s="38" t="s">
         <v>93</v>
@@ -7790,19 +8409,21 @@
       </c>
       <c r="J60" s="8"/>
       <c r="K60" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L60" s="50"/>
-      <c r="M60" s="50"/>
+        <v>396</v>
+      </c>
+      <c r="L60" s="39"/>
+      <c r="M60" s="39"/>
       <c r="N60" s="39" t="s">
-        <v>245</v>
-      </c>
-      <c r="O60" s="50"/>
+        <v>397</v>
+      </c>
+      <c r="O60" s="39"/>
       <c r="P60" s="8"/>
-      <c r="Q60" s="8"/>
-      <c r="R60" s="48"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q60" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R60" s="47"/>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="32" t="n">
         <v>52</v>
       </c>
@@ -7812,10 +8433,10 @@
       </c>
       <c r="D61" s="24"/>
       <c r="E61" s="24" t="s">
-        <v>313</v>
-      </c>
-      <c r="F61" s="53" t="s">
-        <v>314</v>
+        <v>398</v>
+      </c>
+      <c r="F61" s="51" t="s">
+        <v>399</v>
       </c>
       <c r="G61" s="32" t="n">
         <v>51</v>
@@ -7828,17 +8449,19 @@
       </c>
       <c r="J61" s="8"/>
       <c r="K61" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L61" s="50"/>
-      <c r="M61" s="50"/>
-      <c r="N61" s="50"/>
-      <c r="O61" s="50"/>
+        <v>400</v>
+      </c>
+      <c r="L61" s="39"/>
+      <c r="M61" s="39"/>
+      <c r="N61" s="39"/>
+      <c r="O61" s="39"/>
       <c r="P61" s="8"/>
-      <c r="Q61" s="8"/>
-      <c r="R61" s="48"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q61" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R61" s="47"/>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="32" t="n">
         <v>53</v>
       </c>
@@ -7848,9 +8471,9 @@
       </c>
       <c r="D62" s="24"/>
       <c r="E62" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="F62" s="53" t="s">
+        <v>401</v>
+      </c>
+      <c r="F62" s="51" t="s">
         <v>160</v>
       </c>
       <c r="G62" s="32" t="n">
@@ -7864,17 +8487,19 @@
       </c>
       <c r="J62" s="8"/>
       <c r="K62" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L62" s="50"/>
-      <c r="M62" s="50"/>
-      <c r="N62" s="50"/>
-      <c r="O62" s="50"/>
+        <v>402</v>
+      </c>
+      <c r="L62" s="39"/>
+      <c r="M62" s="39"/>
+      <c r="N62" s="39"/>
+      <c r="O62" s="39"/>
       <c r="P62" s="8"/>
-      <c r="Q62" s="8"/>
+      <c r="Q62" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R62" s="40"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="32" t="n">
         <v>54</v>
       </c>
@@ -7884,7 +8509,7 @@
       </c>
       <c r="D63" s="24"/>
       <c r="E63" s="24" t="s">
-        <v>316</v>
+        <v>403</v>
       </c>
       <c r="F63" s="38" t="s">
         <v>138</v>
@@ -7899,22 +8524,24 @@
         <v>1</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>317</v>
+        <v>404</v>
       </c>
       <c r="K63" s="39" t="s">
-        <v>87</v>
+        <v>405</v>
       </c>
       <c r="L63" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M63" s="50"/>
-      <c r="N63" s="50"/>
-      <c r="O63" s="50"/>
+        <v>406</v>
+      </c>
+      <c r="M63" s="39"/>
+      <c r="N63" s="39"/>
+      <c r="O63" s="39"/>
       <c r="P63" s="8"/>
-      <c r="Q63" s="8"/>
+      <c r="Q63" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R63" s="40"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="32" t="n">
         <v>55</v>
       </c>
@@ -7924,7 +8551,7 @@
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="24" t="s">
-        <v>318</v>
+        <v>407</v>
       </c>
       <c r="F64" s="38" t="s">
         <v>139</v>
@@ -7939,22 +8566,24 @@
         <v>1</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>319</v>
+        <v>408</v>
       </c>
       <c r="K64" s="39" t="s">
-        <v>87</v>
+        <v>409</v>
       </c>
       <c r="L64" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M64" s="50"/>
-      <c r="N64" s="50"/>
-      <c r="O64" s="50"/>
+        <v>410</v>
+      </c>
+      <c r="M64" s="39"/>
+      <c r="N64" s="39"/>
+      <c r="O64" s="39"/>
       <c r="P64" s="8"/>
-      <c r="Q64" s="8"/>
+      <c r="Q64" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R64" s="40"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="41" t="n">
         <v>56</v>
       </c>
@@ -7964,7 +8593,7 @@
       </c>
       <c r="D65" s="23"/>
       <c r="E65" s="23" t="s">
-        <v>320</v>
+        <v>411</v>
       </c>
       <c r="F65" s="23" t="s">
         <v>90</v>
@@ -7972,29 +8601,31 @@
       <c r="G65" s="41" t="n">
         <v>43</v>
       </c>
-      <c r="H65" s="70" t="n">
+      <c r="H65" s="68" t="n">
         <v>2</v>
       </c>
       <c r="I65" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>321</v>
+        <v>412</v>
       </c>
       <c r="K65" s="45" t="s">
-        <v>87</v>
+        <v>413</v>
       </c>
       <c r="L65" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M65" s="46"/>
-      <c r="N65" s="46"/>
-      <c r="O65" s="46"/>
+        <v>414</v>
+      </c>
+      <c r="M65" s="45"/>
+      <c r="N65" s="45"/>
+      <c r="O65" s="45"/>
       <c r="P65" s="5"/>
-      <c r="Q65" s="5"/>
-      <c r="R65" s="48"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q65" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R65" s="47"/>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="32" t="n">
         <v>57</v>
       </c>
@@ -8002,7 +8633,7 @@
       <c r="C66" s="32"/>
       <c r="D66" s="24"/>
       <c r="E66" s="24" t="s">
-        <v>322</v>
+        <v>415</v>
       </c>
       <c r="F66" s="24" t="s">
         <v>140</v>
@@ -8016,15 +8647,17 @@
       <c r="I66" s="32"/>
       <c r="J66" s="8"/>
       <c r="K66" s="39"/>
-      <c r="L66" s="50"/>
-      <c r="M66" s="50"/>
-      <c r="N66" s="50"/>
-      <c r="O66" s="50"/>
+      <c r="L66" s="39"/>
+      <c r="M66" s="39"/>
+      <c r="N66" s="39"/>
+      <c r="O66" s="39"/>
       <c r="P66" s="8"/>
-      <c r="Q66" s="8"/>
+      <c r="Q66" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R66" s="40"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="32" t="n">
         <v>58</v>
       </c>
@@ -8034,7 +8667,7 @@
       </c>
       <c r="D67" s="24"/>
       <c r="E67" s="24" t="s">
-        <v>323</v>
+        <v>416</v>
       </c>
       <c r="F67" s="38" t="s">
         <v>141</v>
@@ -8049,22 +8682,24 @@
         <v>1</v>
       </c>
       <c r="J67" s="8" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="K67" s="39" t="s">
-        <v>87</v>
+        <v>418</v>
       </c>
       <c r="L67" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M67" s="50"/>
-      <c r="N67" s="50"/>
-      <c r="O67" s="50"/>
+        <v>419</v>
+      </c>
+      <c r="M67" s="39"/>
+      <c r="N67" s="39"/>
+      <c r="O67" s="39"/>
       <c r="P67" s="8"/>
-      <c r="Q67" s="8"/>
+      <c r="Q67" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R67" s="40"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="32" t="n">
         <v>59</v>
       </c>
@@ -8074,7 +8709,7 @@
       </c>
       <c r="D68" s="24"/>
       <c r="E68" s="24" t="s">
-        <v>325</v>
+        <v>420</v>
       </c>
       <c r="F68" s="38" t="s">
         <v>5</v>
@@ -8089,22 +8724,24 @@
         <v>1</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>326</v>
+        <v>421</v>
       </c>
       <c r="K68" s="39" t="s">
-        <v>87</v>
+        <v>422</v>
       </c>
       <c r="L68" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M68" s="50"/>
-      <c r="N68" s="50"/>
-      <c r="O68" s="50"/>
+        <v>423</v>
+      </c>
+      <c r="M68" s="39"/>
+      <c r="N68" s="39"/>
+      <c r="O68" s="39"/>
       <c r="P68" s="8"/>
-      <c r="Q68" s="8"/>
+      <c r="Q68" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R68" s="40"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="32" t="n">
         <v>60</v>
       </c>
@@ -8114,7 +8751,7 @@
       </c>
       <c r="D69" s="24"/>
       <c r="E69" s="24" t="s">
-        <v>327</v>
+        <v>424</v>
       </c>
       <c r="F69" s="38" t="s">
         <v>143</v>
@@ -8129,22 +8766,24 @@
         <v>1</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>328</v>
+        <v>425</v>
       </c>
       <c r="K69" s="39" t="s">
-        <v>87</v>
+        <v>426</v>
       </c>
       <c r="L69" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M69" s="50"/>
-      <c r="N69" s="50"/>
-      <c r="O69" s="50"/>
+        <v>427</v>
+      </c>
+      <c r="M69" s="39"/>
+      <c r="N69" s="39"/>
+      <c r="O69" s="39"/>
       <c r="P69" s="8"/>
-      <c r="Q69" s="8"/>
+      <c r="Q69" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R69" s="40"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="32" t="n">
         <v>61</v>
       </c>
@@ -8154,7 +8793,7 @@
       </c>
       <c r="D70" s="24"/>
       <c r="E70" s="24" t="s">
-        <v>329</v>
+        <v>428</v>
       </c>
       <c r="F70" s="38" t="s">
         <v>144</v>
@@ -8169,22 +8808,24 @@
         <v>1</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>330</v>
+        <v>429</v>
       </c>
       <c r="K70" s="39" t="s">
-        <v>87</v>
+        <v>430</v>
       </c>
       <c r="L70" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M70" s="50"/>
-      <c r="N70" s="50"/>
-      <c r="O70" s="50"/>
+        <v>431</v>
+      </c>
+      <c r="M70" s="39"/>
+      <c r="N70" s="39"/>
+      <c r="O70" s="39"/>
       <c r="P70" s="8"/>
-      <c r="Q70" s="8"/>
-      <c r="R70" s="48"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q70" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R70" s="47"/>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="32"/>
       <c r="B71" s="24"/>
       <c r="C71" s="32" t="n">
@@ -8192,7 +8833,7 @@
       </c>
       <c r="D71" s="24"/>
       <c r="E71" s="24" t="s">
-        <v>322</v>
+        <v>415</v>
       </c>
       <c r="F71" s="38" t="s">
         <v>145</v>
@@ -8206,17 +8847,19 @@
       </c>
       <c r="J71" s="8"/>
       <c r="K71" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L71" s="50"/>
-      <c r="M71" s="50"/>
-      <c r="N71" s="50"/>
-      <c r="O71" s="50"/>
+        <v>432</v>
+      </c>
+      <c r="L71" s="39"/>
+      <c r="M71" s="39"/>
+      <c r="N71" s="39"/>
+      <c r="O71" s="39"/>
       <c r="P71" s="8"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="48"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q71" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R71" s="47"/>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="41" t="n">
         <v>62</v>
       </c>
@@ -8224,7 +8867,7 @@
       <c r="C72" s="41"/>
       <c r="D72" s="23"/>
       <c r="E72" s="23" t="s">
-        <v>331</v>
+        <v>433</v>
       </c>
       <c r="F72" s="23" t="s">
         <v>146</v>
@@ -8240,15 +8883,17 @@
       </c>
       <c r="J72" s="5"/>
       <c r="K72" s="45"/>
-      <c r="L72" s="46"/>
-      <c r="M72" s="46"/>
-      <c r="N72" s="46"/>
-      <c r="O72" s="46"/>
+      <c r="L72" s="45"/>
+      <c r="M72" s="45"/>
+      <c r="N72" s="45"/>
+      <c r="O72" s="45"/>
       <c r="P72" s="5"/>
-      <c r="Q72" s="5"/>
+      <c r="Q72" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R72" s="40"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="41" t="n">
         <v>63</v>
       </c>
@@ -8258,9 +8903,9 @@
       </c>
       <c r="D73" s="23"/>
       <c r="E73" s="23" t="s">
-        <v>332</v>
-      </c>
-      <c r="F73" s="47" t="s">
+        <v>434</v>
+      </c>
+      <c r="F73" s="46" t="s">
         <v>103</v>
       </c>
       <c r="G73" s="41" t="n">
@@ -8273,22 +8918,24 @@
         <v>1</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>333</v>
+        <v>435</v>
       </c>
       <c r="K73" s="45" t="s">
-        <v>87</v>
+        <v>436</v>
       </c>
       <c r="L73" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M73" s="46"/>
-      <c r="N73" s="46"/>
-      <c r="O73" s="46"/>
+        <v>437</v>
+      </c>
+      <c r="M73" s="45"/>
+      <c r="N73" s="45"/>
+      <c r="O73" s="45"/>
       <c r="P73" s="5"/>
-      <c r="Q73" s="5"/>
+      <c r="Q73" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R73" s="40"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="41" t="n">
         <v>64</v>
       </c>
@@ -8298,9 +8945,9 @@
       </c>
       <c r="D74" s="23"/>
       <c r="E74" s="23" t="s">
-        <v>334</v>
-      </c>
-      <c r="F74" s="47" t="s">
+        <v>438</v>
+      </c>
+      <c r="F74" s="46" t="s">
         <v>147</v>
       </c>
       <c r="G74" s="41" t="n">
@@ -8313,22 +8960,24 @@
         <v>1</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>335</v>
+        <v>439</v>
       </c>
       <c r="K74" s="45" t="s">
-        <v>87</v>
+        <v>440</v>
       </c>
       <c r="L74" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M74" s="46"/>
-      <c r="N74" s="46"/>
-      <c r="O74" s="46"/>
+        <v>441</v>
+      </c>
+      <c r="M74" s="45"/>
+      <c r="N74" s="45"/>
+      <c r="O74" s="45"/>
       <c r="P74" s="5"/>
-      <c r="Q74" s="5"/>
+      <c r="Q74" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R74" s="40"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="41" t="n">
         <v>65</v>
       </c>
@@ -8342,9 +8991,9 @@
         <v>63</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="F75" s="47" t="s">
+        <v>442</v>
+      </c>
+      <c r="F75" s="46" t="s">
         <v>105</v>
       </c>
       <c r="G75" s="41" t="n">
@@ -8357,22 +9006,24 @@
         <v>1</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>337</v>
+        <v>443</v>
       </c>
       <c r="K75" s="45" t="s">
-        <v>87</v>
+        <v>444</v>
       </c>
       <c r="L75" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M75" s="46"/>
-      <c r="N75" s="46"/>
-      <c r="O75" s="46"/>
+        <v>445</v>
+      </c>
+      <c r="M75" s="45"/>
+      <c r="N75" s="45"/>
+      <c r="O75" s="45"/>
       <c r="P75" s="5"/>
-      <c r="Q75" s="5"/>
+      <c r="Q75" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R75" s="40"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="41" t="n">
         <v>66</v>
       </c>
@@ -8382,10 +9033,10 @@
       </c>
       <c r="D76" s="23"/>
       <c r="E76" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="F76" s="55" t="s">
-        <v>243</v>
+        <v>446</v>
+      </c>
+      <c r="F76" s="53" t="s">
+        <v>266</v>
       </c>
       <c r="G76" s="41" t="n">
         <v>65</v>
@@ -8397,22 +9048,24 @@
         <v>1</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>339</v>
+        <v>447</v>
       </c>
       <c r="K76" s="45" t="s">
-        <v>87</v>
+        <v>448</v>
       </c>
       <c r="L76" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M76" s="46"/>
-      <c r="N76" s="46"/>
-      <c r="O76" s="46"/>
+        <v>449</v>
+      </c>
+      <c r="M76" s="45"/>
+      <c r="N76" s="45"/>
+      <c r="O76" s="45"/>
       <c r="P76" s="5"/>
-      <c r="Q76" s="5"/>
+      <c r="Q76" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R76" s="40"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="41" t="n">
         <v>67</v>
       </c>
@@ -8422,10 +9075,10 @@
       </c>
       <c r="D77" s="23"/>
       <c r="E77" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="F77" s="55" t="s">
-        <v>248</v>
+        <v>450</v>
+      </c>
+      <c r="F77" s="53" t="s">
+        <v>272</v>
       </c>
       <c r="G77" s="41" t="n">
         <v>65</v>
@@ -8437,22 +9090,24 @@
         <v>1</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>341</v>
+        <v>451</v>
       </c>
       <c r="K77" s="45" t="s">
-        <v>87</v>
+        <v>452</v>
       </c>
       <c r="L77" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M77" s="46"/>
-      <c r="N77" s="46"/>
-      <c r="O77" s="46"/>
+        <v>453</v>
+      </c>
+      <c r="M77" s="45"/>
+      <c r="N77" s="45"/>
+      <c r="O77" s="45"/>
       <c r="P77" s="5"/>
-      <c r="Q77" s="5"/>
+      <c r="Q77" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R77" s="40"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="41"/>
       <c r="B78" s="23"/>
       <c r="C78" s="41" t="n">
@@ -8460,10 +9115,10 @@
       </c>
       <c r="D78" s="23"/>
       <c r="E78" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="F78" s="55" t="s">
-        <v>343</v>
+        <v>454</v>
+      </c>
+      <c r="F78" s="53" t="s">
+        <v>455</v>
       </c>
       <c r="G78" s="41" t="n">
         <v>65</v>
@@ -8473,22 +9128,24 @@
         <v>1</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="K78" s="46"/>
+        <v>456</v>
+      </c>
+      <c r="K78" s="45"/>
       <c r="L78" s="45" t="s">
-        <v>204</v>
+        <v>457</v>
       </c>
       <c r="M78" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="N78" s="46"/>
-      <c r="O78" s="46"/>
+        <v>458</v>
+      </c>
+      <c r="N78" s="45"/>
+      <c r="O78" s="45"/>
       <c r="P78" s="5"/>
-      <c r="Q78" s="5"/>
-      <c r="R78" s="48"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q78" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R78" s="47"/>
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="32" t="n">
         <v>68</v>
       </c>
@@ -8496,12 +9153,12 @@
       <c r="C79" s="32"/>
       <c r="D79" s="24"/>
       <c r="E79" s="24" t="s">
-        <v>345</v>
-      </c>
-      <c r="F79" s="71" t="s">
+        <v>459</v>
+      </c>
+      <c r="F79" s="69" t="s">
         <v>126</v>
       </c>
-      <c r="G79" s="52" t="n">
+      <c r="G79" s="50" t="n">
         <v>43</v>
       </c>
       <c r="H79" s="32" t="n">
@@ -8509,16 +9166,18 @@
       </c>
       <c r="I79" s="32"/>
       <c r="J79" s="8"/>
-      <c r="K79" s="50"/>
-      <c r="L79" s="50"/>
-      <c r="M79" s="50"/>
-      <c r="N79" s="50"/>
-      <c r="O79" s="50"/>
+      <c r="K79" s="39"/>
+      <c r="L79" s="39"/>
+      <c r="M79" s="39"/>
+      <c r="N79" s="39"/>
+      <c r="O79" s="39"/>
       <c r="P79" s="8"/>
-      <c r="Q79" s="8"/>
-      <c r="R79" s="48"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q79" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R79" s="47"/>
+    </row>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="32" t="n">
         <v>69</v>
       </c>
@@ -8528,7 +9187,7 @@
       </c>
       <c r="D80" s="24"/>
       <c r="E80" s="24" t="s">
-        <v>346</v>
+        <v>460</v>
       </c>
       <c r="F80" s="38" t="s">
         <v>150</v>
@@ -8544,17 +9203,19 @@
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L80" s="50"/>
-      <c r="M80" s="50"/>
-      <c r="N80" s="50"/>
-      <c r="O80" s="50"/>
+        <v>461</v>
+      </c>
+      <c r="L80" s="39"/>
+      <c r="M80" s="39"/>
+      <c r="N80" s="39"/>
+      <c r="O80" s="39"/>
       <c r="P80" s="8"/>
-      <c r="Q80" s="8"/>
-      <c r="R80" s="48"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q80" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R80" s="47"/>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="32" t="n">
         <v>70</v>
       </c>
@@ -8564,10 +9225,10 @@
       </c>
       <c r="D81" s="24"/>
       <c r="E81" s="24" t="s">
-        <v>347</v>
-      </c>
-      <c r="F81" s="53" t="s">
-        <v>348</v>
+        <v>462</v>
+      </c>
+      <c r="F81" s="51" t="s">
+        <v>463</v>
       </c>
       <c r="G81" s="32" t="n">
         <v>69</v>
@@ -8580,17 +9241,19 @@
       </c>
       <c r="J81" s="8"/>
       <c r="K81" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L81" s="50"/>
-      <c r="M81" s="50"/>
-      <c r="N81" s="50"/>
-      <c r="O81" s="50"/>
+        <v>464</v>
+      </c>
+      <c r="L81" s="39"/>
+      <c r="M81" s="39"/>
+      <c r="N81" s="39"/>
+      <c r="O81" s="39"/>
       <c r="P81" s="8"/>
-      <c r="Q81" s="8"/>
+      <c r="Q81" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R81" s="40"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="32" t="n">
         <v>71</v>
       </c>
@@ -8600,7 +9263,7 @@
       </c>
       <c r="D82" s="24"/>
       <c r="E82" s="24" t="s">
-        <v>349</v>
+        <v>465</v>
       </c>
       <c r="F82" s="38" t="s">
         <v>152</v>
@@ -8615,21 +9278,23 @@
         <v>1</v>
       </c>
       <c r="J82" s="8" t="s">
-        <v>350</v>
+        <v>466</v>
       </c>
       <c r="K82" s="39" t="s">
-        <v>87</v>
+        <v>467</v>
       </c>
       <c r="L82" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M82" s="50"/>
-      <c r="N82" s="50"/>
-      <c r="O82" s="50"/>
+        <v>468</v>
+      </c>
+      <c r="M82" s="39"/>
+      <c r="N82" s="39"/>
+      <c r="O82" s="39"/>
       <c r="P82" s="8"/>
-      <c r="Q82" s="8"/>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q82" s="8" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="41" t="n">
         <v>72</v>
       </c>
@@ -8637,7 +9302,7 @@
       <c r="C83" s="41"/>
       <c r="D83" s="23"/>
       <c r="E83" s="23" t="s">
-        <v>351</v>
+        <v>469</v>
       </c>
       <c r="F83" s="23" t="s">
         <v>153</v>
@@ -8650,15 +9315,17 @@
       </c>
       <c r="I83" s="41"/>
       <c r="J83" s="5"/>
-      <c r="K83" s="46"/>
-      <c r="L83" s="46"/>
-      <c r="M83" s="46"/>
-      <c r="N83" s="46"/>
-      <c r="O83" s="46"/>
+      <c r="K83" s="45"/>
+      <c r="L83" s="45"/>
+      <c r="M83" s="45"/>
+      <c r="N83" s="45"/>
+      <c r="O83" s="45"/>
       <c r="P83" s="5"/>
-      <c r="Q83" s="5"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q83" s="8" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="41" t="n">
         <v>73</v>
       </c>
@@ -8668,9 +9335,9 @@
       </c>
       <c r="D84" s="23"/>
       <c r="E84" s="23" t="s">
-        <v>352</v>
-      </c>
-      <c r="F84" s="47" t="s">
+        <v>470</v>
+      </c>
+      <c r="F84" s="46" t="s">
         <v>154</v>
       </c>
       <c r="G84" s="41" t="n">
@@ -8683,17 +9350,19 @@
         <v>1</v>
       </c>
       <c r="J84" s="5"/>
-      <c r="K84" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="L84" s="46"/>
-      <c r="M84" s="46"/>
-      <c r="N84" s="46"/>
-      <c r="O84" s="46"/>
+      <c r="K84" s="45" t="s">
+        <v>471</v>
+      </c>
+      <c r="L84" s="45"/>
+      <c r="M84" s="45"/>
+      <c r="N84" s="45"/>
+      <c r="O84" s="45"/>
       <c r="P84" s="5"/>
-      <c r="Q84" s="5"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q84" s="8" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="41" t="n">
         <v>74</v>
       </c>
@@ -8703,7 +9372,7 @@
       </c>
       <c r="D85" s="23"/>
       <c r="E85" s="23"/>
-      <c r="F85" s="47" t="s">
+      <c r="F85" s="46" t="s">
         <v>155</v>
       </c>
       <c r="G85" s="41" t="n">
@@ -8716,17 +9385,17 @@
         <v>1</v>
       </c>
       <c r="J85" s="5"/>
-      <c r="K85" s="72" t="s">
-        <v>87</v>
-      </c>
-      <c r="L85" s="46"/>
-      <c r="M85" s="46"/>
-      <c r="N85" s="46"/>
-      <c r="O85" s="46"/>
+      <c r="K85" s="70"/>
+      <c r="L85" s="45"/>
+      <c r="M85" s="45"/>
+      <c r="N85" s="45"/>
+      <c r="O85" s="45"/>
       <c r="P85" s="5"/>
-      <c r="Q85" s="5"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q85" s="8" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="41" t="n">
         <v>75</v>
       </c>
@@ -8736,9 +9405,9 @@
       </c>
       <c r="D86" s="23"/>
       <c r="E86" s="23" t="s">
-        <v>353</v>
-      </c>
-      <c r="F86" s="47" t="s">
+        <v>472</v>
+      </c>
+      <c r="F86" s="46" t="s">
         <v>156</v>
       </c>
       <c r="G86" s="41" t="n">
@@ -8752,16 +9421,18 @@
       </c>
       <c r="J86" s="5"/>
       <c r="K86" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="L86" s="46"/>
-      <c r="M86" s="46"/>
-      <c r="N86" s="46"/>
-      <c r="O86" s="46"/>
+        <v>473</v>
+      </c>
+      <c r="L86" s="45"/>
+      <c r="M86" s="45"/>
+      <c r="N86" s="45"/>
+      <c r="O86" s="45"/>
       <c r="P86" s="5"/>
-      <c r="Q86" s="5"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q86" s="8" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="41" t="n">
         <v>76</v>
       </c>
@@ -8775,9 +9446,9 @@
         <v>75</v>
       </c>
       <c r="E87" s="23" t="s">
-        <v>354</v>
-      </c>
-      <c r="F87" s="47" t="s">
+        <v>474</v>
+      </c>
+      <c r="F87" s="46" t="s">
         <v>157</v>
       </c>
       <c r="G87" s="41" t="n">
@@ -8791,16 +9462,18 @@
       </c>
       <c r="J87" s="5"/>
       <c r="K87" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="L87" s="46"/>
-      <c r="M87" s="46"/>
-      <c r="N87" s="46"/>
-      <c r="O87" s="46"/>
+        <v>475</v>
+      </c>
+      <c r="L87" s="45"/>
+      <c r="M87" s="45"/>
+      <c r="N87" s="45"/>
+      <c r="O87" s="45"/>
       <c r="P87" s="5"/>
-      <c r="Q87" s="5"/>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q87" s="8" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="41" t="n">
         <v>77</v>
       </c>
@@ -8812,8 +9485,8 @@
         <v>75</v>
       </c>
       <c r="E88" s="23"/>
-      <c r="F88" s="47" t="s">
-        <v>355</v>
+      <c r="F88" s="46" t="s">
+        <v>476</v>
       </c>
       <c r="G88" s="41" t="n">
         <v>72</v>
@@ -8824,14 +9497,16 @@
       <c r="I88" s="41"/>
       <c r="J88" s="5"/>
       <c r="K88" s="45"/>
-      <c r="L88" s="46"/>
-      <c r="M88" s="46"/>
-      <c r="N88" s="46"/>
-      <c r="O88" s="46"/>
+      <c r="L88" s="45"/>
+      <c r="M88" s="45"/>
+      <c r="N88" s="45"/>
+      <c r="O88" s="45"/>
       <c r="P88" s="5"/>
-      <c r="Q88" s="5"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q88" s="8" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="41" t="n">
         <v>78</v>
       </c>
@@ -8841,10 +9516,10 @@
       </c>
       <c r="D89" s="23"/>
       <c r="E89" s="23" t="s">
-        <v>356</v>
-      </c>
-      <c r="F89" s="55" t="s">
-        <v>357</v>
+        <v>477</v>
+      </c>
+      <c r="F89" s="53" t="s">
+        <v>478</v>
       </c>
       <c r="G89" s="41" t="n">
         <v>77</v>
@@ -8857,17 +9532,19 @@
       </c>
       <c r="J89" s="5"/>
       <c r="K89" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="L89" s="46"/>
-      <c r="M89" s="46"/>
-      <c r="N89" s="46"/>
-      <c r="O89" s="46"/>
+        <v>479</v>
+      </c>
+      <c r="L89" s="45"/>
+      <c r="M89" s="45"/>
+      <c r="N89" s="45"/>
+      <c r="O89" s="45"/>
       <c r="P89" s="5"/>
-      <c r="Q89" s="5"/>
+      <c r="Q89" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R89" s="40"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="41" t="n">
         <v>79</v>
       </c>
@@ -8877,10 +9554,10 @@
       </c>
       <c r="D90" s="23"/>
       <c r="E90" s="23" t="s">
-        <v>358</v>
-      </c>
-      <c r="F90" s="55" t="s">
-        <v>359</v>
+        <v>480</v>
+      </c>
+      <c r="F90" s="53" t="s">
+        <v>481</v>
       </c>
       <c r="G90" s="41" t="n">
         <v>77</v>
@@ -8892,24 +9569,26 @@
         <v>1</v>
       </c>
       <c r="J90" s="5" t="s">
-        <v>360</v>
+        <v>482</v>
       </c>
       <c r="K90" s="45" t="s">
-        <v>87</v>
+        <v>483</v>
       </c>
       <c r="L90" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M90" s="46"/>
+        <v>484</v>
+      </c>
+      <c r="M90" s="45"/>
       <c r="N90" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="O90" s="46"/>
+        <v>485</v>
+      </c>
+      <c r="O90" s="45"/>
       <c r="P90" s="5"/>
-      <c r="Q90" s="5"/>
-      <c r="R90" s="48"/>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q90" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R90" s="47"/>
+    </row>
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="32" t="n">
         <v>80</v>
       </c>
@@ -8917,7 +9596,7 @@
       <c r="C91" s="32"/>
       <c r="D91" s="24"/>
       <c r="E91" s="24" t="s">
-        <v>361</v>
+        <v>486</v>
       </c>
       <c r="F91" s="24" t="s">
         <v>160</v>
@@ -8932,14 +9611,16 @@
       <c r="J91" s="8"/>
       <c r="K91" s="39"/>
       <c r="L91" s="39"/>
-      <c r="M91" s="50"/>
+      <c r="M91" s="39"/>
       <c r="N91" s="39"/>
-      <c r="O91" s="50"/>
+      <c r="O91" s="39"/>
       <c r="P91" s="8"/>
-      <c r="Q91" s="8"/>
+      <c r="Q91" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R91" s="40"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="32" t="n">
         <v>81</v>
       </c>
@@ -8949,7 +9630,7 @@
       </c>
       <c r="D92" s="24"/>
       <c r="E92" s="24" t="s">
-        <v>362</v>
+        <v>487</v>
       </c>
       <c r="F92" s="38" t="s">
         <v>161</v>
@@ -8964,22 +9645,24 @@
         <v>1</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>363</v>
+        <v>488</v>
       </c>
       <c r="K92" s="39" t="s">
-        <v>87</v>
+        <v>489</v>
       </c>
       <c r="L92" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M92" s="50"/>
-      <c r="N92" s="50"/>
-      <c r="O92" s="50"/>
+        <v>490</v>
+      </c>
+      <c r="M92" s="39"/>
+      <c r="N92" s="39"/>
+      <c r="O92" s="39"/>
       <c r="P92" s="8"/>
-      <c r="Q92" s="8"/>
+      <c r="Q92" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R92" s="40"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="32" t="n">
         <v>82</v>
       </c>
@@ -8989,7 +9672,7 @@
       </c>
       <c r="D93" s="24"/>
       <c r="E93" s="24" t="s">
-        <v>364</v>
+        <v>491</v>
       </c>
       <c r="F93" s="38" t="s">
         <v>162</v>
@@ -9004,22 +9687,24 @@
         <v>1</v>
       </c>
       <c r="J93" s="8" t="s">
-        <v>365</v>
+        <v>492</v>
       </c>
       <c r="K93" s="39" t="s">
-        <v>87</v>
+        <v>493</v>
       </c>
       <c r="L93" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M93" s="50"/>
-      <c r="N93" s="50"/>
-      <c r="O93" s="50"/>
+        <v>494</v>
+      </c>
+      <c r="M93" s="39"/>
+      <c r="N93" s="39"/>
+      <c r="O93" s="39"/>
       <c r="P93" s="8"/>
-      <c r="Q93" s="8"/>
+      <c r="Q93" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R93" s="40"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="32" t="n">
         <v>83</v>
       </c>
@@ -9029,7 +9714,7 @@
       </c>
       <c r="D94" s="24"/>
       <c r="E94" s="24" t="s">
-        <v>366</v>
+        <v>495</v>
       </c>
       <c r="F94" s="38" t="s">
         <v>163</v>
@@ -9044,22 +9729,24 @@
         <v>1</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>367</v>
+        <v>496</v>
       </c>
       <c r="K94" s="39" t="s">
-        <v>87</v>
+        <v>497</v>
       </c>
       <c r="L94" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M94" s="50"/>
-      <c r="N94" s="50"/>
-      <c r="O94" s="50"/>
+        <v>498</v>
+      </c>
+      <c r="M94" s="39"/>
+      <c r="N94" s="39"/>
+      <c r="O94" s="39"/>
       <c r="P94" s="8"/>
-      <c r="Q94" s="8"/>
+      <c r="Q94" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R94" s="40"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="32" t="n">
         <v>84</v>
       </c>
@@ -9069,7 +9756,7 @@
       </c>
       <c r="D95" s="24"/>
       <c r="E95" s="24" t="s">
-        <v>368</v>
+        <v>499</v>
       </c>
       <c r="F95" s="38" t="s">
         <v>121</v>
@@ -9084,22 +9771,24 @@
         <v>1</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>369</v>
+        <v>500</v>
       </c>
       <c r="K95" s="39" t="s">
-        <v>87</v>
+        <v>501</v>
       </c>
       <c r="L95" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M95" s="50"/>
-      <c r="N95" s="50"/>
-      <c r="O95" s="50"/>
+        <v>502</v>
+      </c>
+      <c r="M95" s="39"/>
+      <c r="N95" s="39"/>
+      <c r="O95" s="39"/>
       <c r="P95" s="8"/>
-      <c r="Q95" s="8"/>
-      <c r="R95" s="48"/>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q95" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R95" s="47"/>
+    </row>
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="41" t="n">
         <v>85</v>
       </c>
@@ -9120,14 +9809,16 @@
       <c r="J96" s="5"/>
       <c r="K96" s="45"/>
       <c r="L96" s="45"/>
-      <c r="M96" s="46"/>
-      <c r="N96" s="46"/>
-      <c r="O96" s="46"/>
+      <c r="M96" s="45"/>
+      <c r="N96" s="45"/>
+      <c r="O96" s="45"/>
       <c r="P96" s="5"/>
-      <c r="Q96" s="5"/>
+      <c r="Q96" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R96" s="40"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="41"/>
       <c r="B97" s="23"/>
       <c r="C97" s="41" t="n">
@@ -9135,9 +9826,9 @@
       </c>
       <c r="D97" s="23"/>
       <c r="E97" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="F97" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="F97" s="46" t="s">
         <v>67</v>
       </c>
       <c r="G97" s="41" t="n">
@@ -9148,22 +9839,24 @@
         <v>1</v>
       </c>
       <c r="J97" s="5" t="s">
-        <v>371</v>
+        <v>504</v>
       </c>
       <c r="K97" s="45" t="s">
-        <v>87</v>
+        <v>505</v>
       </c>
       <c r="L97" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M97" s="46"/>
-      <c r="N97" s="46"/>
-      <c r="O97" s="46"/>
+        <v>506</v>
+      </c>
+      <c r="M97" s="45"/>
+      <c r="N97" s="45"/>
+      <c r="O97" s="45"/>
       <c r="P97" s="5"/>
-      <c r="Q97" s="5"/>
-      <c r="R97" s="48"/>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q97" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R97" s="47"/>
+    </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="41"/>
       <c r="B98" s="23"/>
       <c r="C98" s="41" t="n">
@@ -9171,9 +9864,9 @@
       </c>
       <c r="D98" s="23"/>
       <c r="E98" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="F98" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="F98" s="46" t="s">
         <v>165</v>
       </c>
       <c r="G98" s="41" t="n">
@@ -9185,17 +9878,19 @@
       </c>
       <c r="J98" s="5"/>
       <c r="K98" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="L98" s="46"/>
-      <c r="M98" s="46"/>
-      <c r="N98" s="46"/>
-      <c r="O98" s="46"/>
+        <v>507</v>
+      </c>
+      <c r="L98" s="45"/>
+      <c r="M98" s="45"/>
+      <c r="N98" s="45"/>
+      <c r="O98" s="45"/>
       <c r="P98" s="5"/>
-      <c r="Q98" s="5"/>
+      <c r="Q98" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R98" s="40"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="41" t="n">
         <v>86</v>
       </c>
@@ -9205,9 +9900,9 @@
       </c>
       <c r="D99" s="23"/>
       <c r="E99" s="23" t="s">
-        <v>372</v>
-      </c>
-      <c r="F99" s="47" t="s">
+        <v>508</v>
+      </c>
+      <c r="F99" s="46" t="s">
         <v>155</v>
       </c>
       <c r="G99" s="41" t="n">
@@ -9220,22 +9915,24 @@
         <v>1</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>373</v>
+        <v>509</v>
       </c>
       <c r="K99" s="45" t="s">
-        <v>87</v>
+        <v>510</v>
       </c>
       <c r="L99" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M99" s="46"/>
-      <c r="N99" s="46"/>
-      <c r="O99" s="46"/>
+        <v>511</v>
+      </c>
+      <c r="M99" s="45"/>
+      <c r="N99" s="45"/>
+      <c r="O99" s="45"/>
       <c r="P99" s="5"/>
-      <c r="Q99" s="5"/>
+      <c r="Q99" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R99" s="40"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="41" t="n">
         <v>87</v>
       </c>
@@ -9245,9 +9942,9 @@
       </c>
       <c r="D100" s="23"/>
       <c r="E100" s="23" t="s">
-        <v>374</v>
-      </c>
-      <c r="F100" s="47" t="s">
+        <v>512</v>
+      </c>
+      <c r="F100" s="46" t="s">
         <v>153</v>
       </c>
       <c r="G100" s="41" t="n">
@@ -9260,22 +9957,24 @@
         <v>1</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>375</v>
+        <v>513</v>
       </c>
       <c r="K100" s="45" t="s">
-        <v>87</v>
+        <v>514</v>
       </c>
       <c r="L100" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M100" s="46"/>
-      <c r="N100" s="46"/>
-      <c r="O100" s="46"/>
+        <v>515</v>
+      </c>
+      <c r="M100" s="45"/>
+      <c r="N100" s="45"/>
+      <c r="O100" s="45"/>
       <c r="P100" s="5"/>
-      <c r="Q100" s="5"/>
+      <c r="Q100" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R100" s="40"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="41" t="n">
         <v>88</v>
       </c>
@@ -9285,9 +9984,9 @@
       </c>
       <c r="D101" s="23"/>
       <c r="E101" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="F101" s="47" t="s">
+        <v>516</v>
+      </c>
+      <c r="F101" s="46" t="s">
         <v>166</v>
       </c>
       <c r="G101" s="41" t="n">
@@ -9300,22 +9999,24 @@
         <v>1</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>377</v>
+        <v>517</v>
       </c>
       <c r="K101" s="45" t="s">
-        <v>87</v>
+        <v>518</v>
       </c>
       <c r="L101" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M101" s="46"/>
-      <c r="N101" s="46"/>
-      <c r="O101" s="46"/>
+        <v>519</v>
+      </c>
+      <c r="M101" s="45"/>
+      <c r="N101" s="45"/>
+      <c r="O101" s="45"/>
       <c r="P101" s="5"/>
-      <c r="Q101" s="5"/>
+      <c r="Q101" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R101" s="40"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="41" t="n">
         <v>89</v>
       </c>
@@ -9325,9 +10026,9 @@
       </c>
       <c r="D102" s="23"/>
       <c r="E102" s="23" t="s">
-        <v>378</v>
-      </c>
-      <c r="F102" s="47" t="s">
+        <v>520</v>
+      </c>
+      <c r="F102" s="46" t="s">
         <v>167</v>
       </c>
       <c r="G102" s="41" t="n">
@@ -9340,22 +10041,24 @@
         <v>1</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>379</v>
+        <v>521</v>
       </c>
       <c r="K102" s="45" t="s">
-        <v>87</v>
+        <v>522</v>
       </c>
       <c r="L102" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M102" s="46"/>
-      <c r="N102" s="46"/>
-      <c r="O102" s="46"/>
+        <v>523</v>
+      </c>
+      <c r="M102" s="45"/>
+      <c r="N102" s="45"/>
+      <c r="O102" s="45"/>
       <c r="P102" s="5"/>
-      <c r="Q102" s="5"/>
+      <c r="Q102" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R102" s="40"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="41" t="n">
         <v>90</v>
       </c>
@@ -9365,9 +10068,9 @@
       </c>
       <c r="D103" s="23"/>
       <c r="E103" s="23" t="s">
-        <v>380</v>
-      </c>
-      <c r="F103" s="47" t="s">
+        <v>524</v>
+      </c>
+      <c r="F103" s="46" t="s">
         <v>168</v>
       </c>
       <c r="G103" s="41" t="n">
@@ -9380,22 +10083,24 @@
         <v>1</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>381</v>
+        <v>525</v>
       </c>
       <c r="K103" s="45" t="s">
-        <v>87</v>
+        <v>526</v>
       </c>
       <c r="L103" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M103" s="46"/>
-      <c r="N103" s="46"/>
-      <c r="O103" s="46"/>
+        <v>527</v>
+      </c>
+      <c r="M103" s="45"/>
+      <c r="N103" s="45"/>
+      <c r="O103" s="45"/>
       <c r="P103" s="5"/>
-      <c r="Q103" s="5"/>
+      <c r="Q103" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R103" s="40"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="41" t="n">
         <v>91</v>
       </c>
@@ -9405,10 +10110,10 @@
       </c>
       <c r="D104" s="23"/>
       <c r="E104" s="23" t="s">
-        <v>382</v>
-      </c>
-      <c r="F104" s="55" t="s">
-        <v>383</v>
+        <v>528</v>
+      </c>
+      <c r="F104" s="53" t="s">
+        <v>529</v>
       </c>
       <c r="G104" s="41" t="n">
         <v>90</v>
@@ -9420,22 +10125,24 @@
         <v>1</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>384</v>
+        <v>530</v>
       </c>
       <c r="K104" s="45" t="s">
-        <v>87</v>
+        <v>531</v>
       </c>
       <c r="L104" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M104" s="46"/>
-      <c r="N104" s="46"/>
-      <c r="O104" s="46"/>
+        <v>532</v>
+      </c>
+      <c r="M104" s="45"/>
+      <c r="N104" s="45"/>
+      <c r="O104" s="45"/>
       <c r="P104" s="5"/>
-      <c r="Q104" s="5"/>
+      <c r="Q104" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R104" s="40"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="41" t="n">
         <v>92</v>
       </c>
@@ -9445,9 +10152,9 @@
       </c>
       <c r="D105" s="23"/>
       <c r="E105" s="23" t="s">
-        <v>385</v>
-      </c>
-      <c r="F105" s="47" t="s">
+        <v>533</v>
+      </c>
+      <c r="F105" s="46" t="s">
         <v>170</v>
       </c>
       <c r="G105" s="41" t="n">
@@ -9460,22 +10167,24 @@
         <v>1</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>386</v>
+        <v>534</v>
       </c>
       <c r="K105" s="45" t="s">
-        <v>87</v>
+        <v>535</v>
       </c>
       <c r="L105" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M105" s="46"/>
-      <c r="N105" s="46"/>
-      <c r="O105" s="46"/>
+        <v>536</v>
+      </c>
+      <c r="M105" s="45"/>
+      <c r="N105" s="45"/>
+      <c r="O105" s="45"/>
       <c r="P105" s="5"/>
-      <c r="Q105" s="5"/>
-      <c r="R105" s="48"/>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q105" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R105" s="47"/>
+    </row>
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="32" t="n">
         <v>93</v>
       </c>
@@ -9496,14 +10205,16 @@
       <c r="J106" s="8"/>
       <c r="K106" s="39"/>
       <c r="L106" s="39"/>
-      <c r="M106" s="50"/>
-      <c r="N106" s="50"/>
-      <c r="O106" s="50"/>
+      <c r="M106" s="39"/>
+      <c r="N106" s="39"/>
+      <c r="O106" s="39"/>
       <c r="P106" s="8"/>
-      <c r="Q106" s="8"/>
+      <c r="Q106" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R106" s="40"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="32" t="n">
         <v>94</v>
       </c>
@@ -9513,7 +10224,7 @@
       </c>
       <c r="D107" s="24"/>
       <c r="E107" s="24" t="s">
-        <v>387</v>
+        <v>537</v>
       </c>
       <c r="F107" s="38" t="s">
         <v>172</v>
@@ -9528,22 +10239,24 @@
         <v>1</v>
       </c>
       <c r="J107" s="8" t="s">
-        <v>388</v>
+        <v>538</v>
       </c>
       <c r="K107" s="39" t="s">
-        <v>87</v>
+        <v>539</v>
       </c>
       <c r="L107" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M107" s="50"/>
-      <c r="N107" s="50"/>
-      <c r="O107" s="50"/>
+        <v>540</v>
+      </c>
+      <c r="M107" s="39"/>
+      <c r="N107" s="39"/>
+      <c r="O107" s="39"/>
       <c r="P107" s="8"/>
-      <c r="Q107" s="8"/>
+      <c r="Q107" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R107" s="40"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="32" t="n">
         <v>95</v>
       </c>
@@ -9553,7 +10266,7 @@
       </c>
       <c r="D108" s="24"/>
       <c r="E108" s="24" t="s">
-        <v>389</v>
+        <v>541</v>
       </c>
       <c r="F108" s="38" t="s">
         <v>173</v>
@@ -9568,22 +10281,24 @@
         <v>1</v>
       </c>
       <c r="J108" s="8" t="s">
-        <v>390</v>
+        <v>542</v>
       </c>
       <c r="K108" s="39" t="s">
-        <v>87</v>
+        <v>543</v>
       </c>
       <c r="L108" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M108" s="50"/>
-      <c r="N108" s="50"/>
-      <c r="O108" s="50"/>
+        <v>544</v>
+      </c>
+      <c r="M108" s="39"/>
+      <c r="N108" s="39"/>
+      <c r="O108" s="39"/>
       <c r="P108" s="8"/>
-      <c r="Q108" s="8"/>
+      <c r="Q108" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R108" s="40"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="32" t="n">
         <v>96</v>
       </c>
@@ -9593,7 +10308,7 @@
       </c>
       <c r="D109" s="24"/>
       <c r="E109" s="24" t="s">
-        <v>391</v>
+        <v>545</v>
       </c>
       <c r="F109" s="38" t="s">
         <v>174</v>
@@ -9608,24 +10323,26 @@
         <v>1</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>392</v>
+        <v>546</v>
       </c>
       <c r="K109" s="39" t="s">
-        <v>87</v>
+        <v>547</v>
       </c>
       <c r="L109" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M109" s="50"/>
+        <v>548</v>
+      </c>
+      <c r="M109" s="39"/>
       <c r="N109" s="39" t="s">
-        <v>245</v>
-      </c>
-      <c r="O109" s="50"/>
+        <v>549</v>
+      </c>
+      <c r="O109" s="39"/>
       <c r="P109" s="8"/>
-      <c r="Q109" s="8"/>
+      <c r="Q109" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R109" s="40"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="32" t="n">
         <v>97</v>
       </c>
@@ -9635,7 +10352,7 @@
       </c>
       <c r="D110" s="24"/>
       <c r="E110" s="24" t="s">
-        <v>393</v>
+        <v>550</v>
       </c>
       <c r="F110" s="38" t="s">
         <v>171</v>
@@ -9650,24 +10367,26 @@
         <v>1</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>394</v>
+        <v>551</v>
       </c>
       <c r="K110" s="39" t="s">
-        <v>87</v>
+        <v>552</v>
       </c>
       <c r="L110" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M110" s="50"/>
+        <v>553</v>
+      </c>
+      <c r="M110" s="39"/>
       <c r="N110" s="39" t="s">
-        <v>245</v>
-      </c>
-      <c r="O110" s="50"/>
+        <v>554</v>
+      </c>
+      <c r="O110" s="39"/>
       <c r="P110" s="8"/>
-      <c r="Q110" s="8"/>
+      <c r="Q110" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R110" s="40"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="41" t="n">
         <v>98</v>
       </c>
@@ -9677,7 +10396,7 @@
       </c>
       <c r="D111" s="23"/>
       <c r="E111" s="23" t="s">
-        <v>395</v>
+        <v>555</v>
       </c>
       <c r="F111" s="23" t="s">
         <v>175</v>
@@ -9692,22 +10411,24 @@
         <v>1</v>
       </c>
       <c r="J111" s="5" t="s">
-        <v>396</v>
+        <v>556</v>
       </c>
       <c r="K111" s="45" t="s">
-        <v>87</v>
+        <v>557</v>
       </c>
       <c r="L111" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M111" s="46"/>
-      <c r="N111" s="46"/>
-      <c r="O111" s="46"/>
+        <v>558</v>
+      </c>
+      <c r="M111" s="45"/>
+      <c r="N111" s="45"/>
+      <c r="O111" s="45"/>
       <c r="P111" s="5"/>
-      <c r="Q111" s="5"/>
+      <c r="Q111" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R111" s="40"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="41" t="n">
         <v>99</v>
       </c>
@@ -9717,9 +10438,9 @@
       </c>
       <c r="D112" s="23"/>
       <c r="E112" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="F112" s="47" t="s">
+        <v>559</v>
+      </c>
+      <c r="F112" s="46" t="s">
         <v>176</v>
       </c>
       <c r="G112" s="41" t="n">
@@ -9732,21 +10453,23 @@
         <v>1</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>398</v>
+        <v>560</v>
       </c>
       <c r="K112" s="45" t="s">
-        <v>87</v>
+        <v>561</v>
       </c>
       <c r="L112" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M112" s="46"/>
-      <c r="N112" s="46"/>
-      <c r="O112" s="46"/>
+        <v>562</v>
+      </c>
+      <c r="M112" s="45"/>
+      <c r="N112" s="45"/>
+      <c r="O112" s="45"/>
       <c r="P112" s="5"/>
-      <c r="Q112" s="5"/>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q112" s="8" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="32" t="n">
         <v>100</v>
       </c>
@@ -9767,14 +10490,16 @@
       <c r="J113" s="8"/>
       <c r="K113" s="39"/>
       <c r="L113" s="39"/>
-      <c r="M113" s="50"/>
-      <c r="N113" s="50"/>
-      <c r="O113" s="50"/>
+      <c r="M113" s="39"/>
+      <c r="N113" s="39"/>
+      <c r="O113" s="39"/>
       <c r="P113" s="8"/>
-      <c r="Q113" s="8"/>
+      <c r="Q113" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R113" s="40"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="32" t="n">
         <v>101</v>
       </c>
@@ -9784,7 +10509,7 @@
       </c>
       <c r="D114" s="24"/>
       <c r="E114" s="24" t="s">
-        <v>399</v>
+        <v>563</v>
       </c>
       <c r="F114" s="38" t="s">
         <v>178</v>
@@ -9799,22 +10524,24 @@
         <v>1</v>
       </c>
       <c r="J114" s="8" t="s">
-        <v>400</v>
+        <v>564</v>
       </c>
       <c r="K114" s="39" t="s">
-        <v>87</v>
+        <v>565</v>
       </c>
       <c r="L114" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M114" s="50"/>
-      <c r="N114" s="50"/>
-      <c r="O114" s="50"/>
+        <v>566</v>
+      </c>
+      <c r="M114" s="39"/>
+      <c r="N114" s="39"/>
+      <c r="O114" s="39"/>
       <c r="P114" s="8"/>
-      <c r="Q114" s="8"/>
+      <c r="Q114" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R114" s="40"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="32" t="n">
         <v>102</v>
       </c>
@@ -9824,7 +10551,7 @@
       </c>
       <c r="D115" s="24"/>
       <c r="E115" s="24" t="s">
-        <v>401</v>
+        <v>567</v>
       </c>
       <c r="F115" s="38" t="s">
         <v>179</v>
@@ -9839,22 +10566,24 @@
         <v>1</v>
       </c>
       <c r="J115" s="8" t="s">
-        <v>402</v>
+        <v>568</v>
       </c>
       <c r="K115" s="39" t="s">
-        <v>87</v>
+        <v>569</v>
       </c>
       <c r="L115" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M115" s="50"/>
-      <c r="N115" s="50"/>
-      <c r="O115" s="50"/>
+        <v>570</v>
+      </c>
+      <c r="M115" s="39"/>
+      <c r="N115" s="39"/>
+      <c r="O115" s="39"/>
       <c r="P115" s="8"/>
-      <c r="Q115" s="8"/>
+      <c r="Q115" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R115" s="40"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="32"/>
       <c r="B116" s="24"/>
       <c r="C116" s="32" t="n">
@@ -9862,7 +10591,7 @@
       </c>
       <c r="D116" s="24"/>
       <c r="E116" s="24" t="s">
-        <v>401</v>
+        <v>567</v>
       </c>
       <c r="F116" s="24"/>
       <c r="G116" s="32"/>
@@ -9871,22 +10600,24 @@
         <v>1</v>
       </c>
       <c r="J116" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="K116" s="50"/>
+        <v>571</v>
+      </c>
+      <c r="K116" s="39"/>
       <c r="L116" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="M116" s="50"/>
+        <v>572</v>
+      </c>
+      <c r="M116" s="39"/>
       <c r="N116" s="39" t="s">
-        <v>245</v>
-      </c>
-      <c r="O116" s="50"/>
+        <v>573</v>
+      </c>
+      <c r="O116" s="39"/>
       <c r="P116" s="8"/>
-      <c r="Q116" s="8"/>
-      <c r="R116" s="48"/>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q116" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="R116" s="47"/>
+    </row>
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="41" t="n">
         <v>103</v>
       </c>
@@ -9908,15 +10639,17 @@
       <c r="I117" s="41"/>
       <c r="J117" s="5"/>
       <c r="K117" s="45"/>
-      <c r="L117" s="46"/>
-      <c r="M117" s="46"/>
-      <c r="N117" s="46"/>
-      <c r="O117" s="46"/>
+      <c r="L117" s="45"/>
+      <c r="M117" s="45"/>
+      <c r="N117" s="45"/>
+      <c r="O117" s="45"/>
       <c r="P117" s="5"/>
-      <c r="Q117" s="5"/>
+      <c r="Q117" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R117" s="40"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="41" t="n">
         <v>104</v>
       </c>
@@ -9926,9 +10659,9 @@
       </c>
       <c r="D118" s="23"/>
       <c r="E118" s="23" t="s">
-        <v>404</v>
-      </c>
-      <c r="F118" s="47" t="s">
+        <v>574</v>
+      </c>
+      <c r="F118" s="46" t="s">
         <v>181</v>
       </c>
       <c r="G118" s="41" t="n">
@@ -9941,22 +10674,24 @@
         <v>1</v>
       </c>
       <c r="J118" s="5" t="s">
-        <v>405</v>
+        <v>575</v>
       </c>
       <c r="K118" s="45" t="s">
-        <v>87</v>
+        <v>576</v>
       </c>
       <c r="L118" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M118" s="46"/>
-      <c r="N118" s="46"/>
-      <c r="O118" s="46"/>
+        <v>577</v>
+      </c>
+      <c r="M118" s="45"/>
+      <c r="N118" s="45"/>
+      <c r="O118" s="45"/>
       <c r="P118" s="5"/>
-      <c r="Q118" s="5"/>
+      <c r="Q118" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R118" s="40"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="41" t="n">
         <v>105</v>
       </c>
@@ -9966,9 +10701,9 @@
       </c>
       <c r="D119" s="23"/>
       <c r="E119" s="23" t="s">
-        <v>406</v>
-      </c>
-      <c r="F119" s="47" t="s">
+        <v>578</v>
+      </c>
+      <c r="F119" s="46" t="s">
         <v>182</v>
       </c>
       <c r="G119" s="41" t="n">
@@ -9981,24 +10716,26 @@
         <v>1</v>
       </c>
       <c r="J119" s="5" t="s">
-        <v>407</v>
+        <v>579</v>
       </c>
       <c r="K119" s="45" t="s">
-        <v>87</v>
+        <v>580</v>
       </c>
       <c r="L119" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M119" s="46"/>
+        <v>581</v>
+      </c>
+      <c r="M119" s="45"/>
       <c r="N119" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="O119" s="46"/>
+        <v>582</v>
+      </c>
+      <c r="O119" s="45"/>
       <c r="P119" s="5"/>
-      <c r="Q119" s="5"/>
+      <c r="Q119" s="8" t="s">
+        <v>382</v>
+      </c>
       <c r="R119" s="40"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="41" t="n">
         <v>106</v>
       </c>
@@ -10008,9 +10745,9 @@
       </c>
       <c r="D120" s="23"/>
       <c r="E120" s="23" t="s">
-        <v>408</v>
-      </c>
-      <c r="F120" s="47" t="s">
+        <v>583</v>
+      </c>
+      <c r="F120" s="46" t="s">
         <v>183</v>
       </c>
       <c r="G120" s="41" t="n">
@@ -10023,23 +10760,25 @@
         <v>1</v>
       </c>
       <c r="J120" s="5" t="s">
-        <v>409</v>
+        <v>584</v>
       </c>
       <c r="K120" s="45" t="s">
-        <v>87</v>
+        <v>585</v>
       </c>
       <c r="L120" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="M120" s="46"/>
+        <v>586</v>
+      </c>
+      <c r="M120" s="45"/>
       <c r="N120" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="O120" s="46"/>
+        <v>587</v>
+      </c>
+      <c r="O120" s="45"/>
       <c r="P120" s="5"/>
-      <c r="Q120" s="5"/>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q120" s="8" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="32" t="n">
         <v>107</v>
       </c>
@@ -10049,7 +10788,7 @@
       </c>
       <c r="D121" s="24"/>
       <c r="E121" s="24" t="s">
-        <v>410</v>
+        <v>588</v>
       </c>
       <c r="F121" s="24" t="s">
         <v>36</v>
@@ -10065,16 +10804,18 @@
       </c>
       <c r="J121" s="8"/>
       <c r="K121" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L121" s="50"/>
-      <c r="M121" s="50"/>
-      <c r="N121" s="50"/>
-      <c r="O121" s="50"/>
+        <v>589</v>
+      </c>
+      <c r="L121" s="39"/>
+      <c r="M121" s="39"/>
+      <c r="N121" s="39"/>
+      <c r="O121" s="39"/>
       <c r="P121" s="8"/>
-      <c r="Q121" s="8"/>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q121" s="8" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="41" t="n">
         <v>108</v>
       </c>
@@ -10084,7 +10825,7 @@
       </c>
       <c r="D122" s="23"/>
       <c r="E122" s="23" t="s">
-        <v>411</v>
+        <v>590</v>
       </c>
       <c r="F122" s="23" t="s">
         <v>184</v>
@@ -10100,16 +10841,18 @@
       </c>
       <c r="J122" s="5"/>
       <c r="K122" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="L122" s="46"/>
-      <c r="M122" s="46"/>
-      <c r="N122" s="46"/>
-      <c r="O122" s="46"/>
+        <v>591</v>
+      </c>
+      <c r="L122" s="45"/>
+      <c r="M122" s="45"/>
+      <c r="N122" s="45"/>
+      <c r="O122" s="45"/>
       <c r="P122" s="5"/>
-      <c r="Q122" s="5"/>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q122" s="8" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="41" t="n">
         <v>109</v>
       </c>
@@ -10119,9 +10862,9 @@
       </c>
       <c r="D123" s="23"/>
       <c r="E123" s="23" t="s">
-        <v>412</v>
-      </c>
-      <c r="F123" s="47" t="s">
+        <v>592</v>
+      </c>
+      <c r="F123" s="46" t="s">
         <v>185</v>
       </c>
       <c r="G123" s="41" t="n">
@@ -10135,22 +10878,24 @@
       </c>
       <c r="J123" s="5"/>
       <c r="K123" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="L123" s="46"/>
-      <c r="M123" s="46"/>
-      <c r="N123" s="46"/>
-      <c r="O123" s="46"/>
+        <v>593</v>
+      </c>
+      <c r="L123" s="45"/>
+      <c r="M123" s="45"/>
+      <c r="N123" s="45"/>
+      <c r="O123" s="45"/>
       <c r="P123" s="5"/>
-      <c r="Q123" s="5"/>
+      <c r="Q123" s="8" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="68"/>
-      <c r="C124" s="68"/>
+      <c r="A124" s="65"/>
+      <c r="C124" s="65"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="68"/>
-      <c r="C125" s="68"/>
+      <c r="A125" s="65"/>
+      <c r="C125" s="65"/>
     </row>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -10159,191 +10904,6 @@
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="K4" r:id="rId2" display="PDF"/>
-    <hyperlink ref="K5" r:id="rId3" display="PDF"/>
-    <hyperlink ref="L5" r:id="rId4" display="VIDEO"/>
-    <hyperlink ref="K6" r:id="rId5" display="PDF"/>
-    <hyperlink ref="L6" r:id="rId6" display="VIDEO"/>
-    <hyperlink ref="K7" r:id="rId7" display="PDF"/>
-    <hyperlink ref="L7" r:id="rId8" display="VIDEO"/>
-    <hyperlink ref="K9" r:id="rId9" display="PDF"/>
-    <hyperlink ref="L9" r:id="rId10" display="VIDEO"/>
-    <hyperlink ref="K11" r:id="rId11" display="PDF"/>
-    <hyperlink ref="L11" r:id="rId12" display="VIDEO"/>
-    <hyperlink ref="K12" r:id="rId13" display="PDF"/>
-    <hyperlink ref="L12" r:id="rId14" display="VIDEO"/>
-    <hyperlink ref="K13" r:id="rId15" display="PDF"/>
-    <hyperlink ref="L13" r:id="rId16" display="VIDEO"/>
-    <hyperlink ref="K14" r:id="rId17" display="PDF"/>
-    <hyperlink ref="L14" r:id="rId18" display="VIDEO"/>
-    <hyperlink ref="K15" r:id="rId19" display="PDF"/>
-    <hyperlink ref="L15" r:id="rId20" display="VIDEO"/>
-    <hyperlink ref="K16" r:id="rId21" display="PDF"/>
-    <hyperlink ref="L16" r:id="rId22" display="VIDEO"/>
-    <hyperlink ref="K17" r:id="rId23" display="PDF"/>
-    <hyperlink ref="L17" r:id="rId24" display="VIDEO"/>
-    <hyperlink ref="L18" r:id="rId25" display="VIDEO"/>
-    <hyperlink ref="L19" r:id="rId26" display="VIDEO"/>
-    <hyperlink ref="L21" r:id="rId27" display="VIDEO"/>
-    <hyperlink ref="N21" r:id="rId28" display="CODE"/>
-    <hyperlink ref="K22" r:id="rId29" display="PDF"/>
-    <hyperlink ref="L22" r:id="rId30" display="VIDEO"/>
-    <hyperlink ref="N22" r:id="rId31" display="CODE"/>
-    <hyperlink ref="L24" r:id="rId32" display="VIDEO"/>
-    <hyperlink ref="N24" r:id="rId33" display="CODE"/>
-    <hyperlink ref="N25" r:id="rId34" display="CODE"/>
-    <hyperlink ref="N26" r:id="rId35" display="CODE"/>
-    <hyperlink ref="K27" r:id="rId36" display="PDF"/>
-    <hyperlink ref="L28" r:id="rId37" display="VIDEO"/>
-    <hyperlink ref="N28" r:id="rId38" display="CODE"/>
-    <hyperlink ref="K29" r:id="rId39" display="CODE"/>
-    <hyperlink ref="L29" r:id="rId40" display="VIDEO"/>
-    <hyperlink ref="K30" r:id="rId41" display="PDF"/>
-    <hyperlink ref="L30" r:id="rId42" display="VIDEO"/>
-    <hyperlink ref="K31" r:id="rId43" display="PDF"/>
-    <hyperlink ref="L31" r:id="rId44" display="VIDEO"/>
-    <hyperlink ref="K32" r:id="rId45" display="PDF"/>
-    <hyperlink ref="L32" r:id="rId46" display="VIDEO"/>
-    <hyperlink ref="M32" r:id="rId47" display="VIDEO"/>
-    <hyperlink ref="K33" r:id="rId48" display="VIDEO"/>
-    <hyperlink ref="K34" r:id="rId49" display="PDF"/>
-    <hyperlink ref="L34" r:id="rId50" display="VIDEO"/>
-    <hyperlink ref="K35" r:id="rId51" display="PDF"/>
-    <hyperlink ref="L35" r:id="rId52" display="VIDEO"/>
-    <hyperlink ref="K36" r:id="rId53" display="PDF"/>
-    <hyperlink ref="L36" r:id="rId54" display="VIDEO"/>
-    <hyperlink ref="K37" r:id="rId55" display="PDF"/>
-    <hyperlink ref="L37" r:id="rId56" display="VIDEO"/>
-    <hyperlink ref="K38" r:id="rId57" display="PDF"/>
-    <hyperlink ref="L38" r:id="rId58" display="VIDEO"/>
-    <hyperlink ref="N38" r:id="rId59" display="CODE"/>
-    <hyperlink ref="O38" r:id="rId60" display="CODE"/>
-    <hyperlink ref="L39" r:id="rId61" display="VIDEO"/>
-    <hyperlink ref="N39" r:id="rId62" display="CODE"/>
-    <hyperlink ref="K40" r:id="rId63" display="CODE"/>
-    <hyperlink ref="L40" r:id="rId64" display="VIDEO"/>
-    <hyperlink ref="K42" r:id="rId65" display="PDF"/>
-    <hyperlink ref="L42" r:id="rId66" display="VIDEO"/>
-    <hyperlink ref="K43" r:id="rId67" display="PDF"/>
-    <hyperlink ref="L43" r:id="rId68" display="VIDEO"/>
-    <hyperlink ref="K44" r:id="rId69" display="PDF"/>
-    <hyperlink ref="K46" r:id="rId70" display="PDF"/>
-    <hyperlink ref="L46" r:id="rId71" display="VIDEO"/>
-    <hyperlink ref="N46" r:id="rId72" display="CODE"/>
-    <hyperlink ref="K47" r:id="rId73" display="PDF"/>
-    <hyperlink ref="K48" r:id="rId74" display="CODE"/>
-    <hyperlink ref="K49" r:id="rId75" display="CODE"/>
-    <hyperlink ref="K50" r:id="rId76" display="VIDEO"/>
-    <hyperlink ref="K51" r:id="rId77" display="PDF"/>
-    <hyperlink ref="L51" r:id="rId78" display="VIDEO"/>
-    <hyperlink ref="N51" r:id="rId79" display="CODE"/>
-    <hyperlink ref="K53" r:id="rId80" display="PDF"/>
-    <hyperlink ref="K54" r:id="rId81" display="PDF"/>
-    <hyperlink ref="K55" r:id="rId82" display="PDF"/>
-    <hyperlink ref="K56" r:id="rId83" display="PDF"/>
-    <hyperlink ref="K57" r:id="rId84" display="PDF"/>
-    <hyperlink ref="K58" r:id="rId85" display="PDF"/>
-    <hyperlink ref="K59" r:id="rId86" display="PDF"/>
-    <hyperlink ref="K60" r:id="rId87" display="PDF"/>
-    <hyperlink ref="N60" r:id="rId88" display="CODE"/>
-    <hyperlink ref="K61" r:id="rId89" display="PDF"/>
-    <hyperlink ref="K62" r:id="rId90" display="PDF"/>
-    <hyperlink ref="K63" r:id="rId91" display="PDF"/>
-    <hyperlink ref="L63" r:id="rId92" display="VIDEO"/>
-    <hyperlink ref="K64" r:id="rId93" display="PDF"/>
-    <hyperlink ref="L64" r:id="rId94" display="VIDEO"/>
-    <hyperlink ref="K65" r:id="rId95" display="PDF"/>
-    <hyperlink ref="L65" r:id="rId96" display="VIDEO"/>
-    <hyperlink ref="K67" r:id="rId97" display="PDF"/>
-    <hyperlink ref="L67" r:id="rId98" display="VIDEO"/>
-    <hyperlink ref="K68" r:id="rId99" display="PDF"/>
-    <hyperlink ref="L68" r:id="rId100" display="VIDEO"/>
-    <hyperlink ref="K69" r:id="rId101" display="PDF"/>
-    <hyperlink ref="L69" r:id="rId102" display="VIDEO"/>
-    <hyperlink ref="K70" r:id="rId103" display="PDF"/>
-    <hyperlink ref="L70" r:id="rId104" display="VIDEO"/>
-    <hyperlink ref="K71" r:id="rId105" display="PDF"/>
-    <hyperlink ref="K73" r:id="rId106" display="PDF"/>
-    <hyperlink ref="L73" r:id="rId107" display="VIDEO"/>
-    <hyperlink ref="K74" r:id="rId108" display="PDF"/>
-    <hyperlink ref="L74" r:id="rId109" display="VIDEO"/>
-    <hyperlink ref="K75" r:id="rId110" display="PDF"/>
-    <hyperlink ref="L75" r:id="rId111" display="VIDEO"/>
-    <hyperlink ref="K76" r:id="rId112" display="PDF"/>
-    <hyperlink ref="L76" r:id="rId113" display="VIDEO"/>
-    <hyperlink ref="K77" r:id="rId114" display="PDF"/>
-    <hyperlink ref="L77" r:id="rId115" display="VIDEO"/>
-    <hyperlink ref="L78" r:id="rId116" display="VIDEO"/>
-    <hyperlink ref="M78" r:id="rId117" display="VIDEO"/>
-    <hyperlink ref="K80" r:id="rId118" display="PDF"/>
-    <hyperlink ref="K81" r:id="rId119" display="PDF"/>
-    <hyperlink ref="K82" r:id="rId120" display="PDF"/>
-    <hyperlink ref="L82" r:id="rId121" display="VIDEO"/>
-    <hyperlink ref="K84" r:id="rId122" display="PDF"/>
-    <hyperlink ref="K86" r:id="rId123" display="PDF"/>
-    <hyperlink ref="K87" r:id="rId124" display="PDF"/>
-    <hyperlink ref="K89" r:id="rId125" display="PDF"/>
-    <hyperlink ref="K90" r:id="rId126" display="PDF"/>
-    <hyperlink ref="L90" r:id="rId127" display="VIDEO"/>
-    <hyperlink ref="N90" r:id="rId128" display="CODE"/>
-    <hyperlink ref="K92" r:id="rId129" display="PDF"/>
-    <hyperlink ref="L92" r:id="rId130" display="VIDEO"/>
-    <hyperlink ref="K93" r:id="rId131" display="PDF"/>
-    <hyperlink ref="L93" r:id="rId132" display="VIDEO"/>
-    <hyperlink ref="K94" r:id="rId133" display="PDF"/>
-    <hyperlink ref="L94" r:id="rId134" display="VIDEO"/>
-    <hyperlink ref="K95" r:id="rId135" display="PDF"/>
-    <hyperlink ref="L95" r:id="rId136" display="VIDEO"/>
-    <hyperlink ref="K97" r:id="rId137" display="PDF"/>
-    <hyperlink ref="L97" r:id="rId138" display="VIDEO"/>
-    <hyperlink ref="K98" r:id="rId139" display="PDF"/>
-    <hyperlink ref="K99" r:id="rId140" display="PDF"/>
-    <hyperlink ref="L99" r:id="rId141" display="VIDEO"/>
-    <hyperlink ref="K100" r:id="rId142" display="PDF"/>
-    <hyperlink ref="L100" r:id="rId143" display="VIDEO"/>
-    <hyperlink ref="K101" r:id="rId144" display="PDF"/>
-    <hyperlink ref="L101" r:id="rId145" display="VIDEO"/>
-    <hyperlink ref="K102" r:id="rId146" display="PDF"/>
-    <hyperlink ref="L102" r:id="rId147" display="VIDEO"/>
-    <hyperlink ref="K103" r:id="rId148" display="PDF"/>
-    <hyperlink ref="L103" r:id="rId149" display="VIDEO"/>
-    <hyperlink ref="K104" r:id="rId150" display="PDF"/>
-    <hyperlink ref="L104" r:id="rId151" display="VIDEO"/>
-    <hyperlink ref="K105" r:id="rId152" display="PDF"/>
-    <hyperlink ref="L105" r:id="rId153" display="VIDEO"/>
-    <hyperlink ref="K107" r:id="rId154" display="PDF"/>
-    <hyperlink ref="L107" r:id="rId155" display="VIDEO"/>
-    <hyperlink ref="K108" r:id="rId156" display="PDF"/>
-    <hyperlink ref="L108" r:id="rId157" display="VIDEO"/>
-    <hyperlink ref="K109" r:id="rId158" display="PDF"/>
-    <hyperlink ref="L109" r:id="rId159" display="VIDEO"/>
-    <hyperlink ref="N109" r:id="rId160" display="CODE"/>
-    <hyperlink ref="K110" r:id="rId161" display="PDF"/>
-    <hyperlink ref="L110" r:id="rId162" display="VIDEO"/>
-    <hyperlink ref="N110" r:id="rId163" display="CODE"/>
-    <hyperlink ref="K111" r:id="rId164" display="PDF"/>
-    <hyperlink ref="L111" r:id="rId165" display="VIDEO"/>
-    <hyperlink ref="K112" r:id="rId166" display="PDF"/>
-    <hyperlink ref="L112" r:id="rId167" display="VIDEO"/>
-    <hyperlink ref="K114" r:id="rId168" display="PDF"/>
-    <hyperlink ref="L114" r:id="rId169" display="VIDEO"/>
-    <hyperlink ref="K115" r:id="rId170" display="PDF"/>
-    <hyperlink ref="L115" r:id="rId171" display="VIDEO"/>
-    <hyperlink ref="L116" r:id="rId172" display="VIDEO"/>
-    <hyperlink ref="N116" r:id="rId173" display="CODE"/>
-    <hyperlink ref="K118" r:id="rId174" display="PDF"/>
-    <hyperlink ref="L118" r:id="rId175" display="VIDEO"/>
-    <hyperlink ref="K119" r:id="rId176" display="PDF"/>
-    <hyperlink ref="L119" r:id="rId177" display="VIDEO"/>
-    <hyperlink ref="N119" r:id="rId178" display="CODE"/>
-    <hyperlink ref="K120" r:id="rId179" display="PDF"/>
-    <hyperlink ref="L120" r:id="rId180" display="VIDEO"/>
-    <hyperlink ref="N120" r:id="rId181" display="CODE"/>
-    <hyperlink ref="K121" r:id="rId182" display="PDF"/>
-    <hyperlink ref="K122" r:id="rId183" display="PDF"/>
-    <hyperlink ref="K123" r:id="rId184" display="PDF"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.700694444444444" right="0.700694444444444" top="0.7875" bottom="0.7875" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -10351,7 +10911,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <legacyDrawing r:id="rId185"/>
 </worksheet>
 </file>
 
@@ -10361,7 +10920,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.15"/>
@@ -10402,7 +10961,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>413</v>
+        <v>594</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10412,7 +10971,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>414</v>
+        <v>595</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -10427,18 +10986,18 @@
       <c r="B6" s="24"/>
       <c r="C6" s="8"/>
       <c r="E6" s="10" t="s">
-        <v>415</v>
+        <v>596</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8" t="s">
-        <v>416</v>
+        <v>597</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
         <v>27</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>417</v>
+        <v>598</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10447,10 +11006,10 @@
       <c r="C7" s="8"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>418</v>
+        <v>599</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>419</v>
+        <v>600</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
@@ -10464,10 +11023,10 @@
       <c r="C8" s="8"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
-        <v>420</v>
+        <v>601</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>421</v>
+        <v>602</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8" t="s">
@@ -10480,7 +11039,7 @@
       <c r="B9" s="24"/>
       <c r="C9" s="8"/>
       <c r="E9" s="6" t="s">
-        <v>422</v>
+        <v>603</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="5"/>
@@ -10489,7 +11048,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>423</v>
+        <v>604</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10498,7 +11057,7 @@
       <c r="C10" s="8"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>424</v>
+        <v>605</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>39</v>
@@ -10508,7 +11067,7 @@
         <v>45</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>423</v>
+        <v>604</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10517,17 +11076,17 @@
       <c r="C11" s="8"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>425</v>
+        <v>606</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>426</v>
+        <v>607</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
-        <v>427</v>
+        <v>608</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>423</v>
+        <v>604</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10535,11 +11094,11 @@
       <c r="B12" s="24"/>
       <c r="C12" s="8"/>
       <c r="E12" s="10" t="s">
-        <v>428</v>
+        <v>609</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="8" t="s">
-        <v>429</v>
+        <v>610</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8" t="s">
@@ -10553,10 +11112,10 @@
       <c r="C13" s="8"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10" t="s">
-        <v>430</v>
+        <v>611</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>429</v>
+        <v>610</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8" t="s">
@@ -10570,10 +11129,10 @@
       <c r="C14" s="8"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10" t="s">
-        <v>431</v>
+        <v>612</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>429</v>
+        <v>610</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8" t="s">
@@ -10587,14 +11146,14 @@
       <c r="C15" s="8"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10" t="s">
-        <v>432</v>
+        <v>613</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>429</v>
+        <v>610</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8" t="s">
-        <v>433</v>
+        <v>614</v>
       </c>
       <c r="J15" s="8"/>
     </row>
@@ -10603,7 +11162,7 @@
       <c r="B16" s="24"/>
       <c r="C16" s="8"/>
       <c r="E16" s="6" t="s">
-        <v>434</v>
+        <v>615</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="5"/>
@@ -10616,7 +11175,7 @@
       <c r="B17" s="24"/>
       <c r="C17" s="8"/>
       <c r="E17" s="10" t="s">
-        <v>435</v>
+        <v>616</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="8"/>
@@ -10625,8 +11184,8 @@
       <c r="J17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="69"/>
-      <c r="B18" s="69"/>
+      <c r="A18" s="66"/>
+      <c r="B18" s="66"/>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
@@ -10639,13 +11198,13 @@
         <v>79</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>436</v>
+        <v>617</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>437</v>
+        <v>618</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>83</v>

--- a/server_nestjs/src/storage/Kompetenzraster.xlsx
+++ b/server_nestjs/src/storage/Kompetenzraster.xlsx
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="663">
   <si>
     <t xml:space="preserve">Voraussetzungen lt. Modulhandbuch</t>
   </si>
@@ -653,6 +653,9 @@
     <t xml:space="preserve">2,3</t>
   </si>
   <si>
+    <t xml:space="preserve"> Python unterstützt die funktionale Programmierung, indem es ermöglicht, dass Funktionen in Variablen gespeichert, als Argumente übergeben oder zurückgegeben werden können. Darüber hinaus bietet Python eine Vielzahl von Funktionen höherer Ordnung sowie die Möglichkeit zur Arbeit mit unveränderlichen Datentypen und Datenstrukturen, was es zu einer idealen Sprache für die Erstellung funktionaler Programme macht.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,3,4</t>
   </si>
   <si>
@@ -662,7 +665,7 @@
     <t xml:space="preserve">Einführung in Python</t>
   </si>
   <si>
-    <t xml:space="preserve">Cras condimentum nisl vel tortor pellentesque, nec luctus justo facilisis. Suspendisse accumsan eros eros, convallis pretium mi pellentesque in. Nunc.</t>
+    <t xml:space="preserve">Obwohl es verlockend ist, sich auf künstliche Intelligenz und Large Language Models zu verlassen, bleibt das Erlernen von objektorientierter und funktionaler Programmierung in der Informatik unerlässlich, um effiziente Lösungen und ein tiefes Verständnis für die Funktionsweise von Software und Hardware zu erlangen.</t>
   </si>
   <si>
     <t xml:space="preserve">2,3,5</t>
@@ -710,6 +713,9 @@
     <t xml:space="preserve">2,8</t>
   </si>
   <si>
+    <t xml:space="preserve">In Python wird die funktionale Programmierung durch den Einsatz von Funktionen und Unveränderlichkeit von Daten unterstützt, um Seiteneffekte zu vermeiden und die Code-Wartbarkeit zu verbessern. Python bietet verschiedene Datentypen wie Listen, Tupel und Dictionary, welche es ermöglichen, auf eine deklarative Weise mit Funktionen höherer Ordnung zu arbeiten. Dazu gehören Lambda-Ausdrücke und eingebaute Funktionen wie map, filter und reduce, die dabei helfen, Daten effizient und einfach zu verarbeiten.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,8,9</t>
   </si>
   <si>
@@ -728,6 +734,9 @@
     <t xml:space="preserve">2,8,10</t>
   </si>
   <si>
+    <t xml:space="preserve">Integer sind ganze Zahlen ohne Dezimalstellen, die in der funktionalen Programmierung als grundlegender Datentyp für Zählvorgänge, Indexierung und mathematische Berechnungen verwendet werden. Sie ermöglichen es, deterministische Funktionen zu schreiben, die mit diskreten Werten arbeiten und somit eine wichtige Rolle in der Struktur und Logik von Algorithmen spielen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,8,10,11</t>
   </si>
   <si>
@@ -854,6 +863,9 @@
     <t xml:space="preserve">2,18,20</t>
   </si>
   <si>
+    <t xml:space="preserve">Schleifen sind Strukturen in der Programmierung, die es ermöglichen, einen Codeblock wiederholt auszuführen, solange eine bestimmte Bedingung erfüllt ist oder über eine Sammlung von Elementen zu iterieren. In Python werden häufig `for`- und `while`-Schleifen verwendet, um iterative Aufgaben effizient zu bewältigen, wie das Durchlaufen von Listen oder das wiederholte Ausführen von Berechnungen bis eine Bedingung nicht mehr zutrifft.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,18,20,21</t>
   </si>
   <si>
@@ -896,6 +908,9 @@
     <t xml:space="preserve">2,39</t>
   </si>
   <si>
+    <t xml:space="preserve">Datenstrukturen sind grundlegende Konzepte in der Informatik, die es ermöglichen, Daten effizient zu speichern, zu organisieren und darauf zuzugreifen. In der funktionalen Programmierung werden sie genutzt, um Daten unveränderlich zu halten und Operationen darauf durch Funktionen auszudrücken, die keine Seiteneffekte haben und oft rekursiv sind.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,39,40</t>
   </si>
   <si>
@@ -908,24 +923,36 @@
     <t xml:space="preserve">Listen</t>
   </si>
   <si>
+    <t xml:space="preserve">Listen in der funktionalen Programmierung mit Python sind grundlegende Datenstrukturen, die es ermöglichen, eine Sammlung von Elementen zu speichern und zu manipulieren. Sie unterstützen Operationen wie das Filtern, Abbilden und Falten von Daten, wodurch sie für die Anwendung funktionaler Konzepte wie Unveränderlichkeit und Funktionen höherer Ordnung zentral sind.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,39,41</t>
   </si>
   <si>
     <t xml:space="preserve">dc3a876f-2fba-4494-bf16-aa80914fdec2</t>
   </si>
   <si>
+    <t xml:space="preserve">Tupel in Python sind unveränderliche (immutable) Datenstrukturen, die es ermöglichen, eine geordnete Sammlung von Elementen unterschiedlicher Datentypen zu speichern. Sie werden häufig in funktionalen Programmieransätzen verwendet, um Daten zu gruppieren und Funktionen zu ermöglichen, mehrere Werte sicher und ohne Seiteneffekte zu verarbeiten.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,39,42</t>
   </si>
   <si>
     <t xml:space="preserve">24bec9c7-6e78-4b46-ba4d-a1faa644620d</t>
   </si>
   <si>
+    <t xml:space="preserve">Ein Dictionary in Python ist eine Sammlung von Schlüssel-Wert-Paaren, die es ermöglicht, Werte effizient über Schlüssel zu speichern und abzurufen. Es unterstützt Operationen wie das Einfügen, Ändern und Löschen von Elementen und ist besonders nützlich, um Assoziationen zwischen eindeutigen Schlüsseln und zugehörigen Daten zu verwalten.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,23</t>
   </si>
   <si>
     <t xml:space="preserve">19aca104-2bd1-472b-9a5e-74f2dc5a6b1a</t>
   </si>
   <si>
+    <t xml:space="preserve">Funktionen in der Programmierung sind wiederverwendbare Codeblöcke, die spezifische Aufgaben ausführen und dabei Eingabewerte verarbeiten können, um Ergebnisse zurückzugeben. Sie fördern die Modularität und Wartbarkeit des Codes, indem sie es ermöglichen, komplexe Probleme in kleinere, handhabbare Teile zu zerlegen und diese Teile unabhängig voneinander zu testen und zu verwenden.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python-Funktionen ermöglichen es, Codeblöcke zu isolieren und in sinnvolle Abschnitte aufzuteilen, was die Übersichtlichkeit und Wartbarkeit von Programmen erheblich verbessert, insbesondere bei großen Projekten. Sie werden mit dem Schlüsselwort `def` definiert, können beliebig viele Eingabeargumente enthalten und mit `return` Werte zurückgeben, die dann im Hauptprogramm verwendet werden können.</t>
   </si>
   <si>
@@ -1103,6 +1130,9 @@
     <t xml:space="preserve">2,31</t>
   </si>
   <si>
+    <t xml:space="preserve">Funktionale Programmierung ist ein Paradigma, das mathematische Funktionen zur Strukturierung von Code verwendet und Konzepte wie Unveränderlichkeit von Daten und Funktionen höherer Ordnung betont. In Python ermöglicht es die Verwendung von Funktionen wie `map`, `filter`, `reduce` und Lambda-Ausdrücken, um Code zu schreiben, der klar, konzise und oft leichter zu verstehen ist.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,31,32</t>
   </si>
   <si>
@@ -1133,9 +1163,15 @@
     <t xml:space="preserve">fdaf9cbc-2335-4b93-92d2-cae6c8e8c366</t>
   </si>
   <si>
+    <t xml:space="preserve">Currying ist eine Technik in der funktionalen Programmierung, bei der eine Funktion, die mehrere Argumente erwartet, in eine Sequenz von Funktionen umgewandelt wird, die jeweils genau ein Argument nehmen. Auf diese Weise kann eine Funktion mit mehreren Parametern schrittweise angewendet werden, indem sie für jedes Argument eine neue Funktion zurückgibt, bis alle Argumente verarbeitet sind.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,35</t>
   </si>
   <si>
+    <t xml:space="preserve">Python bietet eine Vielzahl von Tools, die die funktionale Programmierung unterstützen, wie zum Beispiel Lambda-Funktionen, die map(), filter() und reduce() Funktionen sowie umfassende Module wie functools und itertools, die fortgeschrittene funktionale Konzepte ermöglichen. Diese Tools erleichtern es, in Python sauberen, modularen und effizienten Code zu schreiben, der die Prinzipien der funktionalen Programmierung wie Unveränderlichkeit und Funktionen höherer Ordnung nutzt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,35,36</t>
   </si>
   <si>
@@ -1154,6 +1190,9 @@
     <t xml:space="preserve">1f5cc88f-56db-4eba-b911-362642ab6bd5</t>
   </si>
   <si>
+    <t xml:space="preserve">Filter sind Funktionen in der funktionalen Programmierung, die eine Sammlung von Daten durchlaufen und Elemente auswählen, die eine bestimmte Bedingung erfüllen. In Python kann die eingebaute Funktion `filter()` verwendet werden, um eine neue Liste zu erstellen, die nur die Elemente enthält, die bei Anwendung einer gegebenen Funktion als wahr bewertet werden.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,35,37</t>
   </si>
   <si>
@@ -1205,7 +1244,7 @@
     <t xml:space="preserve">cfd5773a-cf3c-4d9a-bc23-fd52af37798e</t>
   </si>
   <si>
-    <t xml:space="preserve">Pellentesque bibendum aliquet enim, quis ornare metus aliquet lobortis. Sed pellentesque lorem turpis, vitae tempor nunc finibus mollis. Suspendisse quis.</t>
+    <t xml:space="preserve">Das Erstellen von Programmen umfasst das Verfassen von Quellcode, der die gewünschten Funktionen und Verhaltensweisen in einer strukturierten und lesbaren Form definiert, wobei objektorientierte Konzepte wie Klassen, Objekte, Vererbung und Polymorphismus zum Einsatz kommen. Die Ausführung dieser Programme erfolgt durch einen Compiler oder Interpreter, der den Quellcode in maschinenverständlichen Code übersetzt und auf einer Zielplattform ausführt, wobei in Java die Java Virtual Machine (JVM) als Zwischenschicht für plattformunabhängige Ausführung sorgt.</t>
   </si>
   <si>
     <t xml:space="preserve">43,45</t>
@@ -1214,36 +1253,54 @@
     <t xml:space="preserve">d84e6630-244f-46f3-9fa9-4c3e391677f4</t>
   </si>
   <si>
+    <t xml:space="preserve">Syntaktische Grundelemente sind die Bausteine einer Programmiersprache, die festlegen, wie Befehle und Anweisungen strukturiert sein müssen, um vom Compiler verstanden und ausgeführt zu werden. In der objektorientierten Programmierung mit Java beinhalten diese Elemente unter anderem Klassen, Methoden, Variablen, Datentypen und Kontrollstrukturen, die zusammen das Gerüst für die Erstellung von Objekten und die Definition ihres Verhaltens bilden.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46</t>
   </si>
   <si>
     <t xml:space="preserve">ceee4725-8691-42ae-be01-c63164ede826</t>
   </si>
   <si>
+    <t xml:space="preserve">Datentypen in der Programmierung definieren die Art der Werte, die eine Variable speichern kann, und legen fest, welche Operationen mit diesen Werten durchgeführt werden können. In Java gibt es primitive Datentypen wie int, char und float für grundlegende Werte sowie Referenzdatentypen für Objekte und Arrays, die auf komplexe Datenstrukturen verweisen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,47</t>
   </si>
   <si>
     <t xml:space="preserve">b44cb78c-a8ff-4a2d-b8fa-5c0d88629667</t>
   </si>
   <si>
+    <t xml:space="preserve">Integer in der Programmierung repräsentieren ganze Zahlen und sind ein fundamentaler Datentyp, der in vielen Programmiersprachen, einschließlich Java, verwendet wird. In Java ist `Integer` auch eine Klasse, die Methoden zur Manipulation von ganzen Zahlen bereitstellt und es ermöglicht, ganze Zahlen als Objekte zu behandeln, was für die objektorientierte Programmierung wichtig ist.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,48</t>
   </si>
   <si>
     <t xml:space="preserve">5f03b842-f8c2-4f63-8bb9-83142d6f98b3</t>
   </si>
   <si>
+    <t xml:space="preserve">Ein Float in der Programmierung bezeichnet einen Datentyp, der eine Gleitkommazahl repräsentiert und wird verwendet, um numerische Werte mit Dezimalstellen zu speichern und zu verarbeiten. In Java ist `float` ein primitiver Datentyp, der 32 Bit Speicherplatz belegt und eine geringere Präzision als der 64 Bit `double` Datentyp bietet, was bei der Entwicklung von Anwendungen, die hohe numerische Genauigkeit erfordern, berücksichtigt werden muss.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,49</t>
   </si>
   <si>
     <t xml:space="preserve">5b9ff9c4-8f45-4ce2-ae79-43fee72e6ecb</t>
   </si>
   <si>
+    <t xml:space="preserve">Der Datentyp `char` in Java wird verwendet, um einzelne Zeichen zu speichern, die durch 16-Bit Unicode-Zeichen repräsentiert werden, was es ermöglicht, nahezu jedes Zeichen aus jedem Sprachalphabet darzustellen. Ein `char`-Wert kann innerhalb eines Programms für die Verarbeitung von Textdaten, wie das Lesen von Eingaben oder das Darstellen von Zeichenketten, genutzt werden.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,50</t>
   </si>
   <si>
     <t xml:space="preserve">ac5c805f-3619-4e90-99b5-3377c6d7458c</t>
   </si>
   <si>
+    <t xml:space="preserve">Boolesche Werte, repräsentiert durch den Datentyp `boolean` in Java, sind grundlegende Elemente der Programmierung, die nur zwei mögliche Zustände annehmen können: `true` oder `false`. Sie spielen eine zentrale Rolle in der Steuerung des Programmflusses durch bedingte Anweisungen wie `if`-`else` und Schleifen wie `while` und `for`, indem sie als Bedingungen verwendet werden, die bestimmen, ob bestimmte Blöcke von Code ausgeführt werden sollen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,51</t>
   </si>
   <si>
@@ -1253,6 +1310,9 @@
     <t xml:space="preserve">6168e707-a273-4cf4-9144-9f8ef201e775</t>
   </si>
   <si>
+    <t xml:space="preserve">Ein String in der Programmierung ist eine Sequenz von Zeichen, die als Datentyp in vielen Programmiersprachen, einschließlich Java, verwendet wird, um Text zu repräsentieren. In Java ist String eine Klasse, die Methoden zur Manipulation von Text, wie das Suchen von Zeichen, das Vergleichen von Strings oder das Ändern von Textinhalten, bereitstellt und aufgrund ihrer Unveränderlichkeit besondere Überlegungen im Hinblick auf Speichereffizienz und Performance erfordert.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,51,52</t>
   </si>
   <si>
@@ -1262,12 +1322,18 @@
     <t xml:space="preserve">74940c23-af14-4330-a019-a3f51090d4a6</t>
   </si>
   <si>
+    <t xml:space="preserve">Operationen auf Strings in der Programmierung ermöglichen es, Textdaten zu manipulieren, indem Funktionen wie das Verketten, Teilen, Suchen und Ersetzen von Teilstrings sowie das Umwandeln von Groß- und Kleinschreibung angewendet werden. In Java werden diese Operationen durch Methoden der Klasse `String` bereitgestellt, die unveränderliche Objekte repräsentiert, wobei jede Änderung an einem String ein neues Objekt erzeugt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,51,53</t>
   </si>
   <si>
     <t xml:space="preserve">2960e92b-b82d-443a-8b32-ed87447c76e1</t>
   </si>
   <si>
+    <t xml:space="preserve">Es werden grundlegende Konzepte der objektorientierten Programmierung wie Klassen, Objekte, Vererbung, Polymorphismus und Kapselung vermittelt. Methoden in Java sind dabei essenzielle Bausteine, die Verhalten und Funktionalitäten von Objekten definieren und es ermöglichen, wiederverwendbaren und modularen Code zu schreiben.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,46,54</t>
   </si>
   <si>
@@ -1307,6 +1373,9 @@
     <t xml:space="preserve">43,57</t>
   </si>
   <si>
+    <t xml:space="preserve">Anweisungen in der objekorientierten Programmierung sind die Bausteine, die es ermöglichen, Aktionen auszuführen, Zustände zu verändern und die Kontrollflusssteuerung innerhalb von Methoden zu definieren. In Java werden diese Anweisungen durch Sprachelemente wie Schleifen (for, while), Verzweigungen (if, switch), Zuweisungen und Methodenaufrufe repräsentiert, um komplexe Logik innerhalb von Objekten zu implementieren.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,57,58</t>
   </si>
   <si>
@@ -1358,9 +1427,15 @@
     <t xml:space="preserve">21064003-7fec-42c1-bf24-3fb64408e567</t>
   </si>
   <si>
+    <t xml:space="preserve">Programmier-Konventionen sind Richtlinien zur Gestaltung des Quellcodes, die dazu beitragen, die Lesbarkeit, Wartbarkeit und Konsistenz in Softwareprojekten zu verbessern. Sie umfassen Namenskonventionen, Formatierungsregeln und Best Practices für die Strukturierung von Code, wie die Verwendung von Einrückungen und Kommentaren, und sind besonders wichtig in der objekorientierten Programmierung, um die Komplexität von Klassen, Methoden und Objekten zu managen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,62</t>
   </si>
   <si>
+    <t xml:space="preserve">Kontrollstrukturen sind entscheidend in der Programmierung, da sie den Fluss der Ausführung steuern, indem sie bedingte Anweisungen (if-else), Schleifen (for, while, do-while) und Sprunganweisungen (break, continue) bereitstellen. Diese Strukturen ermöglichen es Entwicklern, komplexe Logik zu implementieren, indem sie bestimmen, wann und wie oft bestimmte Codeblöcke ausgeführt werden.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,62,63</t>
   </si>
   <si>
@@ -1439,12 +1514,18 @@
     <t xml:space="preserve">43,68</t>
   </si>
   <si>
+    <t xml:space="preserve">Datenstrukturen sind Sammlungen von Datenwerten, die Beziehungen untereinander aufweisen und ermöglichen es, Daten effizient zu organisieren, zu verarbeiten und zu speichern. Zu den grundlegenden Datenstrukturen gehören Arrays, Listen, Stacks, Queues, Bäume und Graphen, die jeweils unterschiedliche Operationen wie Einfügen, Löschen und Suchen von Daten optimieren.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,68,69</t>
   </si>
   <si>
     <t xml:space="preserve">9f2444dc-c1c9-4daa-82b9-26b916f003ae</t>
   </si>
   <si>
+    <t xml:space="preserve">Ein Array in Java ist eine Datenstruktur, die es ermöglicht, mehrere Werte eines bestimmten Typs in einer einzigen Variablen zu speichern, wobei jeder Wert über einen Index zugänglich ist. Arrays sind nützlich, um Sammlungen von Daten wie Zahlenreihen oder Zeichenketten effizient zu verwalten und zu manipulieren, und sind ein grundlegendes Konzept in der objektorientierten Programmierung.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,68,69,70</t>
   </si>
   <si>
@@ -1454,6 +1535,9 @@
     <t xml:space="preserve">bb1b43c5-9f89-42e1-a9d1-4e522837aba4</t>
   </si>
   <si>
+    <t xml:space="preserve">Mehrdimensionale Arrays in Java sind Sammlungen von Elementen, die in einem Raster angeordnet sind, wobei jede Dimension des Arrays einen eigenen Indexbereich hat. Sie ermöglichen die Speicherung und Verwaltung von komplexen Datenstrukturen wie Matrizen oder Tabellen, indem sie beispielsweise Zeilen und Spalten durch verschachtelte Arrays repräsentieren.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,68,71</t>
   </si>
   <si>
@@ -1469,27 +1553,45 @@
     <t xml:space="preserve">43,72</t>
   </si>
   <si>
+    <t xml:space="preserve">Objekte in der objektorientierten Programmierung sind Instanzen von Klassen, die sowohl Daten in Form von Attributen als auch Verhalten durch Methoden kapseln. Sie ermöglichen die Modellierung realer oder abstrakter Konzepte durch Wiederverwendung und Erweiterung von Code, was zu einer strukturierten und wartbaren Softwarearchitektur führt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,72,73</t>
   </si>
   <si>
     <t xml:space="preserve">8e4c8072-9711-4698-9a43-337207ddcd77</t>
   </si>
   <si>
+    <t xml:space="preserve">Objektorientierung ist ein Programmierparadigma, das auf Konzepten wie Klassen, Objekten, Vererbung, Polymorphismus und Kapselung basiert, um Softwareentwicklung modularer und wiederverwendbarer zu gestalten. In Java ermöglicht es Entwicklern, Code zu strukturieren, indem sie Daten und Verhalten in Objekten kapseln, die reale Entitäten modellieren und durch Klassen definiert werden, wodurch komplexe Systeme effizienter und wartbarer implementiert werden können.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klassen in der objektorientierten Programmierung sind Schablonen, die die Struktur und das Verhalten von Objekten definieren, indem sie Attribute (Datenfelder) und Methoden (Funktionen) zusammenfassen. Sie ermöglichen die Wiederverwendung von Code, erleichtern die Wartung und fördern die Modularität von Software durch die Kapselung von Daten und Funktionen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,72,75</t>
   </si>
   <si>
     <t xml:space="preserve">8301ca1c-9896-4344-b47e-75b9352bc23e</t>
   </si>
   <si>
+    <t xml:space="preserve">In der objektorientierten Programmierung dienen Konstruktoren dazu, neue Instanzen einer Klasse zu erzeugen, indem sie die Initialisierung von Objekten mit spezifischen Anfangswerten ermöglichen. In Java werden Konstruktoren durch Methoden definiert, die den gleichen Namen wie die Klasse haben und keine Rückgabetypen spezifizieren, wodurch bei der Objekterstellung automatisch die entsprechenden Anfangszustände gesetzt werden.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,72,76</t>
   </si>
   <si>
     <t xml:space="preserve">3b6d1967-16f1-4b42-8e74-d854d40e6951</t>
   </si>
   <si>
+    <t xml:space="preserve">In der objektorientierten Programmierung werden Objekte erstellt, die während ihrer Lebensdauer im Speicher existieren und mit denen interagiert werden kann. Sobald ein Objekt nicht mehr benötigt wird oder keine Referenzen mehr darauf zeigen, kann es durch den Garbage Collector der Laufzeitumgebung, wie beispielsweise in Java, automatisch gelöscht werden, um Speicherplatz freizugeben.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Objektreferenzen</t>
   </si>
   <si>
+    <t xml:space="preserve">Objektreferenzen in der objektorientierten Programmierung sind Verweise auf Speicherorte, an denen die Daten eines Objekts abgelegt sind, und ermöglichen es, mit diesen Objekten innerhalb des Codes zu interagieren. Sie dienen als Zugriffspunkte, um Methoden aufzurufen und Eigenschaften von Objekten zu manipulieren, ohne die tatsächlichen Daten kopieren zu müssen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,72,77,78</t>
   </si>
   <si>
@@ -1499,6 +1601,9 @@
     <t xml:space="preserve">61d2b624-53b5-4879-8485-952c1d7dcb20</t>
   </si>
   <si>
+    <t xml:space="preserve">Attribute sind Variablen innerhalb einer Klasse, die den Zustand oder die Eigenschaften eines Objekts repräsentieren, während Methoden die Funktionen oder Aktionen darstellen, die ein Objekt ausführen kann. In der objektorientierten Programmierung definieren Attribute und Methoden gemeinsam das Verhalten und die Schnittstelle eines Objekts, wobei Attribute typischerweise über Methoden abgefragt und manipuliert werden.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,72,77,79</t>
   </si>
   <si>
@@ -1520,6 +1625,9 @@
     <t xml:space="preserve">43,80</t>
   </si>
   <si>
+    <t xml:space="preserve">Es werden grundlegende Konzepte der objektorientierten Programmierung wie Klassen, Objekte, Vererbung, Polymorphismus und Kapselung vermittelt. Methoden in Java sind dabei essenzielle Bausteine, die Verhalten und Funktionalitäten von Objekten definieren und es ermöglichen, wiederverwendbaren und gut strukturierten Code zu schreiben.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,80,81</t>
   </si>
   <si>
@@ -1568,6 +1676,9 @@
     <t xml:space="preserve">b2fab559-c5e9-417b-8340-a5b1be313da9</t>
   </si>
   <si>
+    <t xml:space="preserve">Die Unified Modeling Language (UML) ist eine standardisierte Modellierungssprache, die eine visuelle Darstellung von Software-Systemen ermöglicht, um Strukturen und Verhaltensweisen objektorientierter Programme zu veranschaulichen. Sie umfasst verschiedene Diagrammtypen wie Klassendiagramme, Sequenzdiagramme und Zustandsdiagramme, die Entwicklern helfen, Entwurfsmuster zu definieren und die Kommunikation innerhalb des Entwicklungsteams zu verbessern.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,85</t>
   </si>
   <si>
@@ -1583,6 +1694,9 @@
     <t xml:space="preserve">b681b280-c818-4970-a531-2aafcf5b49c8</t>
   </si>
   <si>
+    <t xml:space="preserve">Die Unified Modeling Language (UML) ist eine standardisierte Modellierungssprache, die verwendet wird, um die Struktur und das Design von Software-Systemen visuell darzustellen. In einem UML-Beispiel könnten Diagramme wie Klassendiagramme, Sequenzdiagramme und Zustandsdiagramme genutzt werden, um die Beziehungen zwischen Objekten, deren Verhalten und Lebenszyklen in einem objektorientierten Programm zu veranschaulichen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,85,86</t>
   </si>
   <si>
@@ -1670,6 +1784,9 @@
     <t xml:space="preserve">95017bb3-978d-4cdd-917a-ba8de3c73014</t>
   </si>
   <si>
+    <t xml:space="preserve">Vererbung in der objektorientierten Programmierung ermöglicht es, dass eine neue Klasse (Unterklasse) die Eigenschaften und Verhaltensweisen einer bestehenden Klasse (Oberklasse) übernehmen kann, wodurch Code-Wiederverwendung und hierarchische Klassifizierung unterstützt werden. Durch diesen Mechanismus können Unterklasse-Objekte auch als Instanzen ihrer Oberklasse betrachtet werden, was Polymorphismus und eine flexible und erweiterbare Code-Struktur fördert.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,93,94</t>
   </si>
   <si>
@@ -1748,6 +1865,9 @@
     <t xml:space="preserve">a4d090b7-221c-4932-a309-ffab11522825</t>
   </si>
   <si>
+    <t xml:space="preserve">Die Ausnahmebehandlung in der Programmierung ermöglicht es, auf Fehler während der Ausführung eines Programms zu reagieren, indem Ausnahmen (Exceptions) abgefangen und entsprechend behandelt werden. In Java werden Ausnahmen mit try-catch-Blöcken gehandhabt, wobei der Code, der eine Ausnahme auslösen könnte, in den try-Block eingefügt und die Logik zur Fehlerbehandlung im catch-Block implementiert wird.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,100,101</t>
   </si>
   <si>
@@ -1781,6 +1901,9 @@
     <t xml:space="preserve">0c24b88b-ea6b-49f5-b6e2-a2ba29305814</t>
   </si>
   <si>
+    <t xml:space="preserve">Dateien sind digitale Container, die Daten auf Speichermedien wie Festplatten oder SSDs speichern und es ermöglichen, Informationen dauerhaft zu bewahren und zu übertragen. In der objektorientierten Programmierung, wie in Java, werden Dateien mithilfe von Klassen und Methoden gelesen, geschrieben und verwaltet, wobei die Abstraktion und Kapselung von Dateioperationen die Interaktion mit dem Dateisystem vereinfacht und sicherer macht.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,103,104</t>
   </si>
   <si>
@@ -1829,16 +1952,25 @@
     <t xml:space="preserve">1b9afa84-fae6-4682-b16a-8bdb3def80d3</t>
   </si>
   <si>
+    <t xml:space="preserve">Threads in Java sind eigenständige Ausführungspfade, die es ermöglichen, mehrere Operationen gleichzeitig innerhalb eines Programms durchzuführen. Sie werden genutzt, um die Effizienz zu steigern und eine reaktive Benutzeroberfläche zu gewährleisten, indem langwierige Prozesse im Hintergrund ablaufen, ohne die Hauptanwendung zu blockieren.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,108</t>
   </si>
   <si>
     <t xml:space="preserve">cd49aafd-4a0a-4670-b4d7-83ba456fcfd3</t>
   </si>
   <si>
+    <t xml:space="preserve">Sockets sind Endpunkte für die Kommunikation zwischen zwei Maschinen über ein Netzwerk, wobei in Java die Klassen `Socket` für Client-Anwendungen und `ServerSocket` für Server-Anwendungen verwendet werden, um eine Verbindung herzustellen und Daten auszutauschen. Sie ermöglichen es Programmen, über TCP/IP-Protokolle zu kommunizieren, indem sie Datenströme für das Senden und Empfangen von Informationen bereitstellen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">43,108,109</t>
   </si>
   <si>
     <t xml:space="preserve">fe681e57-e984-4ef6-9bbc-0c6ddc6fc85e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server-Sockets in Java sind Endpunkte, die auf eingehende Netzwerkverbindungen an einem spezifischen Port lauschen und es ermöglichen, dass ein Server-Prozess mit einem oder mehreren Clients kommunizieren kann. Sie werden verwendet, um eine stabile Verbindung aufzubauen, über die Daten gesendet und empfangen werden können, wobei die Java-Klassen `ServerSocket` und `Socket` die Grundlage für die Netzwerkkommunikation in einem objektorientierten Ansatz bilden.</t>
   </si>
   <si>
     <t xml:space="preserve">Zusatz ohne Ziel- bzw. Kompetenzfomulierung</t>
@@ -1925,7 +2057,7 @@
     <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2021,6 +2153,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <u val="single"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2113,7 +2252,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2266,6 +2405,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2319,15 +2462,19 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="7" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="9" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="7" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="9" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -2346,11 +2493,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2358,7 +2505,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2477,7 +2624,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I245"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.15"/>
@@ -5960,7 +6107,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:S1048576"/>
-  <sheetFormatPr defaultColWidth="10.76953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.41"/>
@@ -6088,7 +6235,9 @@
       <c r="N3" s="37"/>
       <c r="O3" s="37"/>
       <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
+      <c r="Q3" s="38" t="s">
+        <v>198</v>
+      </c>
       <c r="R3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6101,9 +6250,9 @@
       </c>
       <c r="D4" s="33"/>
       <c r="E4" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="F4" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="F4" s="39" t="s">
         <v>86</v>
       </c>
       <c r="G4" s="32" t="n">
@@ -6116,20 +6265,20 @@
         <v>1</v>
       </c>
       <c r="J4" s="12"/>
-      <c r="K4" s="39" t="s">
-        <v>199</v>
+      <c r="K4" s="40" t="s">
+        <v>200</v>
       </c>
       <c r="L4" s="37"/>
       <c r="M4" s="37"/>
       <c r="N4" s="37"/>
       <c r="O4" s="37"/>
       <c r="P4" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q4" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="R4" s="40"/>
+      <c r="Q4" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="R4" s="41"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="n">
@@ -6141,10 +6290,10 @@
       </c>
       <c r="D5" s="33"/>
       <c r="E5" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="F5" s="38" t="s">
         <v>203</v>
+      </c>
+      <c r="F5" s="39" t="s">
+        <v>204</v>
       </c>
       <c r="G5" s="32" t="n">
         <v>2</v>
@@ -6156,116 +6305,116 @@
         <v>1</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="K5" s="39" t="s">
         <v>205</v>
       </c>
-      <c r="L5" s="39" t="s">
+      <c r="K5" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="M5" s="39"/>
+      <c r="L5" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="M5" s="40"/>
       <c r="N5" s="37"/>
       <c r="O5" s="37"/>
       <c r="P5" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R5" s="40"/>
+        <v>205</v>
+      </c>
+      <c r="R5" s="41"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="41" t="n">
+      <c r="A6" s="42" t="n">
         <v>6</v>
       </c>
       <c r="B6" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42" t="s">
-        <v>208</v>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43" t="s">
+        <v>209</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G6" s="41" t="n">
+      <c r="G6" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="43" t="n">
+      <c r="H6" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="44" t="n">
+      <c r="I6" s="45" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="K6" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="L6" s="45" t="s">
+      <c r="K6" s="46" t="s">
         <v>211</v>
       </c>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
+      <c r="L6" s="46" t="s">
+        <v>212</v>
+      </c>
+      <c r="M6" s="46"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
       <c r="P6" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="Q6" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R6" s="40"/>
+      <c r="Q6" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="R6" s="41"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="41" t="n">
+      <c r="A7" s="42" t="n">
         <v>7</v>
       </c>
       <c r="B7" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="41" t="n">
+      <c r="C7" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42" t="s">
-        <v>212</v>
-      </c>
-      <c r="F7" s="46" t="s">
+      <c r="D7" s="43"/>
+      <c r="E7" s="43" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="41" t="n">
+      <c r="G7" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="41" t="n">
+      <c r="H7" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="44" t="n">
+      <c r="I7" s="45" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="K7" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="L7" s="45" t="s">
+      <c r="K7" s="46" t="s">
         <v>215</v>
       </c>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
+      <c r="L7" s="46" t="s">
+        <v>216</v>
+      </c>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
       <c r="P7" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="Q7" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R7" s="47"/>
+      <c r="Q7" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="R7" s="48"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="n">
@@ -6277,7 +6426,7 @@
       <c r="C8" s="32"/>
       <c r="D8" s="21"/>
       <c r="E8" s="21" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F8" s="24" t="s">
         <v>92</v>
@@ -6288,20 +6437,20 @@
       <c r="H8" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="48"/>
+      <c r="I8" s="49"/>
       <c r="J8" s="12"/>
-      <c r="K8" s="39" t="s">
+      <c r="K8" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="39"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="40"/>
       <c r="P8" s="8"/>
-      <c r="Q8" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R8" s="40"/>
+      <c r="Q8" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="R8" s="41"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="n">
@@ -6313,39 +6462,39 @@
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="F9" s="49" t="s">
+        <v>219</v>
+      </c>
+      <c r="F9" s="50" t="s">
         <v>93</v>
       </c>
       <c r="G9" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="H9" s="50" t="n">
+      <c r="H9" s="51" t="n">
         <v>3</v>
       </c>
       <c r="I9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="K9" s="39" t="s">
-        <v>219</v>
-      </c>
-      <c r="L9" s="39" t="s">
         <v>220</v>
       </c>
-      <c r="M9" s="39"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="39"/>
+      <c r="K9" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="L9" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
       <c r="P9" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R9" s="47"/>
+        <v>220</v>
+      </c>
+      <c r="R9" s="48"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="n">
@@ -6355,31 +6504,31 @@
       <c r="C10" s="32"/>
       <c r="D10" s="24"/>
       <c r="E10" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="F10" s="49" t="s">
+        <v>224</v>
+      </c>
+      <c r="F10" s="50" t="s">
         <v>94</v>
       </c>
       <c r="G10" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="H10" s="50" t="n">
+      <c r="H10" s="51" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="8"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="39"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R10" s="40"/>
+        <v>225</v>
+      </c>
+      <c r="R10" s="41"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="n">
@@ -6391,9 +6540,9 @@
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="F11" s="51" t="s">
+        <v>226</v>
+      </c>
+      <c r="F11" s="52" t="s">
         <v>133</v>
       </c>
       <c r="G11" s="32" t="n">
@@ -6406,24 +6555,24 @@
         <v>1</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="K11" s="39" t="s">
-        <v>225</v>
-      </c>
-      <c r="L11" s="39" t="s">
-        <v>226</v>
-      </c>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
+        <v>227</v>
+      </c>
+      <c r="K11" s="40" t="s">
+        <v>228</v>
+      </c>
+      <c r="L11" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
       <c r="P11" s="8" t="s">
         <v>133</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R11" s="40"/>
+        <v>227</v>
+      </c>
+      <c r="R11" s="41"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="n">
@@ -6435,9 +6584,9 @@
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="F12" s="51" t="s">
+        <v>230</v>
+      </c>
+      <c r="F12" s="52" t="s">
         <v>134</v>
       </c>
       <c r="G12" s="32" t="n">
@@ -6450,24 +6599,24 @@
         <v>1</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="K12" s="39" t="s">
-        <v>229</v>
-      </c>
-      <c r="L12" s="39" t="s">
-        <v>230</v>
-      </c>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
+        <v>231</v>
+      </c>
+      <c r="K12" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="L12" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
       <c r="P12" s="8" t="s">
         <v>134</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R12" s="40"/>
+        <v>231</v>
+      </c>
+      <c r="R12" s="41"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="n">
@@ -6479,10 +6628,10 @@
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="F13" s="51" t="s">
-        <v>232</v>
+        <v>234</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>235</v>
       </c>
       <c r="G13" s="32" t="n">
         <v>10</v>
@@ -6494,40 +6643,40 @@
         <v>1</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="K13" s="39" t="s">
-        <v>234</v>
-      </c>
-      <c r="L13" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
+        <v>236</v>
+      </c>
+      <c r="K13" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="L13" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
       <c r="P13" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q13" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="Q13" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R13" s="40"/>
+      <c r="R13" s="41"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="n">
         <v>14</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C14" s="32" t="n">
         <v>10</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="F14" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="F14" s="52" t="s">
         <v>101</v>
       </c>
       <c r="G14" s="32" t="n">
@@ -6540,24 +6689,24 @@
         <v>1</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="K14" s="39" t="s">
-        <v>240</v>
-      </c>
-      <c r="L14" s="39" t="s">
-        <v>241</v>
-      </c>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="39"/>
+        <v>242</v>
+      </c>
+      <c r="K14" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="L14" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="M14" s="40"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="40"/>
       <c r="P14" s="8" t="s">
         <v>101</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R14" s="40"/>
+        <v>242</v>
+      </c>
+      <c r="R14" s="41"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="n">
@@ -6569,9 +6718,9 @@
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="F15" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="F15" s="39" t="s">
         <v>97</v>
       </c>
       <c r="G15" s="32" t="n">
@@ -6584,24 +6733,24 @@
         <v>1</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="K15" s="39" t="s">
-        <v>244</v>
-      </c>
-      <c r="L15" s="39" t="s">
-        <v>245</v>
-      </c>
-      <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="39"/>
+        <v>246</v>
+      </c>
+      <c r="K15" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="L15" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
       <c r="P15" s="8" t="s">
         <v>97</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R15" s="40"/>
+        <v>246</v>
+      </c>
+      <c r="R15" s="41"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="n">
@@ -6613,9 +6762,9 @@
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="F16" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="F16" s="39" t="s">
         <v>98</v>
       </c>
       <c r="G16" s="32" t="n">
@@ -6628,43 +6777,43 @@
         <v>1</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="K16" s="39" t="s">
-        <v>248</v>
-      </c>
-      <c r="L16" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="39"/>
+        <v>250</v>
+      </c>
+      <c r="K16" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="L16" s="40" t="s">
+        <v>252</v>
+      </c>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
       <c r="P16" s="8" t="s">
         <v>98</v>
       </c>
       <c r="Q16" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R16" s="40"/>
+        <v>250</v>
+      </c>
+      <c r="R16" s="41"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C17" s="32" t="n">
         <v>11</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="F17" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="G17" s="48" t="n">
+      <c r="G17" s="49" t="n">
         <v>8</v>
       </c>
       <c r="H17" s="32" t="n">
@@ -6674,398 +6823,398 @@
         <v>1</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="K17" s="39" t="s">
-        <v>253</v>
-      </c>
-      <c r="L17" s="39" t="s">
-        <v>254</v>
-      </c>
-      <c r="M17" s="39"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="39"/>
+        <v>255</v>
+      </c>
+      <c r="K17" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="L17" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="M17" s="40"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="40"/>
       <c r="P17" s="8" t="s">
         <v>100</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R17" s="40"/>
+        <v>255</v>
+      </c>
+      <c r="R17" s="41"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="41" t="n">
+      <c r="A18" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="B18" s="52" t="n">
+      <c r="B18" s="53" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="41" t="n">
+      <c r="C18" s="42" t="n">
         <v>14</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="23" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F18" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="41" t="n">
+      <c r="G18" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="41" t="n">
+      <c r="H18" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="41" t="n">
+      <c r="I18" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45" t="s">
-        <v>257</v>
-      </c>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
+        <v>259</v>
+      </c>
+      <c r="K18" s="46"/>
+      <c r="L18" s="46" t="s">
+        <v>260</v>
+      </c>
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
       <c r="P18" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R18" s="40"/>
+        <v>261</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="R18" s="41"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="41" t="n">
+      <c r="A19" s="42" t="n">
         <v>19</v>
       </c>
       <c r="B19" s="23"/>
-      <c r="C19" s="41" t="n">
+      <c r="C19" s="42" t="n">
         <v>15</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="F19" s="46" t="s">
+        <v>262</v>
+      </c>
+      <c r="F19" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="G19" s="41" t="n">
+      <c r="G19" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="H19" s="41" t="n">
+      <c r="H19" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="41" t="n">
+      <c r="I19" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="K19" s="45" t="s">
-        <v>261</v>
-      </c>
-      <c r="L19" s="45" t="s">
-        <v>262</v>
-      </c>
-      <c r="M19" s="45"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="45"/>
+        <v>263</v>
+      </c>
+      <c r="K19" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="L19" s="46" t="s">
+        <v>265</v>
+      </c>
+      <c r="M19" s="46"/>
+      <c r="N19" s="46"/>
+      <c r="O19" s="46"/>
       <c r="P19" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q19" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="Q19" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R19" s="47"/>
+      <c r="R19" s="48"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="41" t="n">
+      <c r="A20" s="42" t="n">
         <v>20</v>
       </c>
       <c r="B20" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="41"/>
+      <c r="C20" s="42"/>
       <c r="D20" s="23" t="n">
         <v>19</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="F20" s="46" t="s">
+        <v>267</v>
+      </c>
+      <c r="F20" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="G20" s="41" t="n">
+      <c r="G20" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="H20" s="41" t="n">
+      <c r="H20" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="I20" s="41" t="n">
+      <c r="I20" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J20" s="20"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="45"/>
-      <c r="M20" s="45"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="45"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="46"/>
+      <c r="O20" s="46"/>
       <c r="P20" s="5"/>
-      <c r="Q20" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R20" s="40"/>
+      <c r="Q20" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="R20" s="41"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="41" t="n">
+      <c r="A21" s="42" t="n">
         <v>21</v>
       </c>
       <c r="B21" s="23"/>
-      <c r="C21" s="41" t="n">
+      <c r="C21" s="42" t="n">
         <v>17</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="F21" s="53" t="s">
-        <v>266</v>
-      </c>
-      <c r="G21" s="41" t="n">
+        <v>269</v>
+      </c>
+      <c r="F21" s="55" t="s">
+        <v>270</v>
+      </c>
+      <c r="G21" s="42" t="n">
         <v>20</v>
       </c>
-      <c r="H21" s="41" t="n">
+      <c r="H21" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="I21" s="41" t="n">
+      <c r="I21" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="K21" s="45"/>
-      <c r="L21" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45" t="s">
-        <v>269</v>
-      </c>
-      <c r="O21" s="45"/>
+        <v>271</v>
+      </c>
+      <c r="K21" s="46"/>
+      <c r="L21" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="M21" s="46"/>
+      <c r="N21" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="O21" s="46"/>
       <c r="P21" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q21" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R21" s="40"/>
+        <v>274</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="R21" s="41"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="41" t="n">
+      <c r="A22" s="42" t="n">
         <v>22</v>
       </c>
       <c r="B22" s="23"/>
-      <c r="C22" s="41" t="n">
+      <c r="C22" s="42" t="n">
         <v>18</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="F22" s="53" t="s">
-        <v>272</v>
-      </c>
-      <c r="G22" s="41" t="n">
+        <v>275</v>
+      </c>
+      <c r="F22" s="55" t="s">
+        <v>276</v>
+      </c>
+      <c r="G22" s="42" t="n">
         <v>20</v>
       </c>
-      <c r="H22" s="41" t="n">
+      <c r="H22" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="I22" s="41" t="n">
+      <c r="I22" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="K22" s="45" t="s">
-        <v>274</v>
-      </c>
-      <c r="L22" s="45" t="s">
-        <v>275</v>
-      </c>
-      <c r="M22" s="45"/>
-      <c r="N22" s="45" t="s">
-        <v>276</v>
-      </c>
-      <c r="O22" s="45"/>
+        <v>277</v>
+      </c>
+      <c r="K22" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="L22" s="46" t="s">
+        <v>279</v>
+      </c>
+      <c r="M22" s="46"/>
+      <c r="N22" s="46" t="s">
+        <v>280</v>
+      </c>
+      <c r="O22" s="46"/>
       <c r="P22" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q22" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="Q22" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R22" s="47"/>
-    </row>
-    <row r="23" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="54" t="n">
+      <c r="R22" s="48"/>
+    </row>
+    <row r="23" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="56" t="n">
         <v>39</v>
       </c>
-      <c r="B23" s="55" t="n">
+      <c r="B23" s="57" t="n">
         <v>8</v>
       </c>
-      <c r="C23" s="54"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55" t="s">
-        <v>278</v>
-      </c>
-      <c r="F23" s="55" t="s">
+      <c r="C23" s="56"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57" t="s">
+        <v>282</v>
+      </c>
+      <c r="F23" s="57" t="s">
         <v>126</v>
       </c>
-      <c r="G23" s="54" t="n">
+      <c r="G23" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="54" t="n">
+      <c r="H23" s="56" t="n">
         <v>6</v>
       </c>
-      <c r="I23" s="54"/>
-      <c r="J23" s="56"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="57"/>
-      <c r="N23" s="57"/>
-      <c r="O23" s="57"/>
-      <c r="P23" s="56"/>
-      <c r="Q23" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R23" s="58"/>
-    </row>
-    <row r="24" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="54" t="n">
+      <c r="I23" s="56"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="59"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="59"/>
+      <c r="O23" s="59"/>
+      <c r="P23" s="58"/>
+      <c r="Q23" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="R23" s="60"/>
+    </row>
+    <row r="24" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="56" t="n">
         <v>40</v>
       </c>
-      <c r="B24" s="55"/>
-      <c r="C24" s="54" t="n">
+      <c r="B24" s="57"/>
+      <c r="C24" s="56" t="n">
         <v>42</v>
       </c>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55" t="s">
-        <v>279</v>
-      </c>
-      <c r="F24" s="60" t="s">
+      <c r="D24" s="57"/>
+      <c r="E24" s="57" t="s">
+        <v>284</v>
+      </c>
+      <c r="F24" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="54" t="n">
+      <c r="G24" s="56" t="n">
         <v>39</v>
       </c>
-      <c r="H24" s="54" t="n">
+      <c r="H24" s="56" t="n">
         <v>6</v>
       </c>
-      <c r="I24" s="54" t="n">
+      <c r="I24" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="56"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="57" t="s">
-        <v>280</v>
-      </c>
-      <c r="M24" s="57"/>
-      <c r="N24" s="57" t="s">
-        <v>281</v>
-      </c>
-      <c r="O24" s="57"/>
-      <c r="P24" s="56" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q24" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R24" s="61"/>
-    </row>
-    <row r="25" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="54" t="n">
+      <c r="J24" s="58"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="59" t="s">
+        <v>285</v>
+      </c>
+      <c r="M24" s="59"/>
+      <c r="N24" s="59" t="s">
+        <v>286</v>
+      </c>
+      <c r="O24" s="59"/>
+      <c r="P24" s="58" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="R24" s="63"/>
+    </row>
+    <row r="25" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="56" t="n">
         <v>41</v>
       </c>
-      <c r="B25" s="55"/>
-      <c r="C25" s="54" t="n">
+      <c r="B25" s="57"/>
+      <c r="C25" s="56" t="n">
         <v>43</v>
       </c>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55" t="s">
-        <v>283</v>
-      </c>
-      <c r="F25" s="60" t="s">
+      <c r="D25" s="57"/>
+      <c r="E25" s="57" t="s">
+        <v>289</v>
+      </c>
+      <c r="F25" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="G25" s="54" t="n">
+      <c r="G25" s="56" t="n">
         <v>39</v>
       </c>
-      <c r="H25" s="54" t="n">
+      <c r="H25" s="56" t="n">
         <v>6</v>
       </c>
-      <c r="I25" s="54" t="n">
+      <c r="I25" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="56"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="57"/>
-      <c r="M25" s="57"/>
-      <c r="N25" s="57" t="s">
-        <v>284</v>
-      </c>
-      <c r="O25" s="57"/>
-      <c r="P25" s="56" t="s">
+      <c r="J25" s="58"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="59" t="s">
+        <v>290</v>
+      </c>
+      <c r="O25" s="59"/>
+      <c r="P25" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="Q25" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R25" s="61"/>
-    </row>
-    <row r="26" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="54" t="n">
+      <c r="Q25" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="R25" s="63"/>
+    </row>
+    <row r="26" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="56" t="n">
         <v>42</v>
       </c>
-      <c r="B26" s="55"/>
-      <c r="C26" s="54" t="n">
+      <c r="B26" s="57"/>
+      <c r="C26" s="56" t="n">
         <v>44</v>
       </c>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55" t="s">
-        <v>285</v>
-      </c>
-      <c r="F26" s="60" t="s">
+      <c r="D26" s="57"/>
+      <c r="E26" s="57" t="s">
+        <v>292</v>
+      </c>
+      <c r="F26" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="G26" s="54" t="n">
+      <c r="G26" s="56" t="n">
         <v>39</v>
       </c>
-      <c r="H26" s="54" t="n">
+      <c r="H26" s="56" t="n">
         <v>6</v>
       </c>
-      <c r="I26" s="54" t="n">
+      <c r="I26" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="56"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="57"/>
-      <c r="N26" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="O26" s="57"/>
-      <c r="P26" s="56" t="s">
+      <c r="J26" s="58"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="59" t="s">
+        <v>293</v>
+      </c>
+      <c r="O26" s="59"/>
+      <c r="P26" s="58" t="s">
         <v>129</v>
       </c>
-      <c r="Q26" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R26" s="61"/>
-    </row>
-    <row r="27" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q26" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="R26" s="63"/>
+    </row>
+    <row r="27" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="32" t="n">
         <v>23</v>
       </c>
@@ -7077,7 +7226,7 @@
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="24" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="F27" s="24" t="s">
         <v>108</v>
@@ -7092,22 +7241,22 @@
         <v>1</v>
       </c>
       <c r="J27" s="8"/>
-      <c r="K27" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="L27" s="39"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="39"/>
+      <c r="K27" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="L27" s="40"/>
+      <c r="M27" s="40"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="40"/>
       <c r="P27" s="8" t="s">
         <v>108</v>
       </c>
       <c r="Q27" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R27" s="58"/>
-    </row>
-    <row r="28" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>297</v>
+      </c>
+      <c r="R27" s="60"/>
+    </row>
+    <row r="28" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="32"/>
       <c r="B28" s="24"/>
       <c r="C28" s="32" t="n">
@@ -7115,7 +7264,7 @@
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="24" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="F28" s="24"/>
       <c r="G28" s="32"/>
@@ -7124,26 +7273,26 @@
         <v>1</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="K28" s="39"/>
-      <c r="L28" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39" t="s">
-        <v>291</v>
-      </c>
-      <c r="O28" s="39"/>
+        <v>298</v>
+      </c>
+      <c r="K28" s="40"/>
+      <c r="L28" s="40" t="s">
+        <v>299</v>
+      </c>
+      <c r="M28" s="40"/>
+      <c r="N28" s="40" t="s">
+        <v>300</v>
+      </c>
+      <c r="O28" s="40"/>
       <c r="P28" s="8" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R28" s="58"/>
-    </row>
-    <row r="29" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>298</v>
+      </c>
+      <c r="R28" s="60"/>
+    </row>
+    <row r="29" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="32"/>
       <c r="B29" s="24"/>
       <c r="C29" s="32" t="n">
@@ -7151,9 +7300,9 @@
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="F29" s="38" t="s">
+        <v>295</v>
+      </c>
+      <c r="F29" s="39" t="s">
         <v>109</v>
       </c>
       <c r="G29" s="32" t="n">
@@ -7164,26 +7313,26 @@
         <v>1</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K29" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="L29" s="39" t="s">
-        <v>295</v>
-      </c>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
+        <v>302</v>
+      </c>
+      <c r="K29" s="40" t="s">
+        <v>303</v>
+      </c>
+      <c r="L29" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
       <c r="P29" s="8" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R29" s="58"/>
-    </row>
-    <row r="30" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>302</v>
+      </c>
+      <c r="R29" s="60"/>
+    </row>
+    <row r="30" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="32" t="n">
         <v>24</v>
       </c>
@@ -7193,9 +7342,9 @@
       </c>
       <c r="D30" s="24"/>
       <c r="E30" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="F30" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="F30" s="39" t="s">
         <v>110</v>
       </c>
       <c r="G30" s="32" t="n">
@@ -7208,26 +7357,26 @@
         <v>1</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="K30" s="39" t="s">
-        <v>299</v>
-      </c>
-      <c r="L30" s="39" t="s">
-        <v>300</v>
-      </c>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
+        <v>307</v>
+      </c>
+      <c r="K30" s="40" t="s">
+        <v>308</v>
+      </c>
+      <c r="L30" s="40" t="s">
+        <v>309</v>
+      </c>
+      <c r="M30" s="40"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="40"/>
       <c r="P30" s="8" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="Q30" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R30" s="58"/>
-    </row>
-    <row r="31" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>307</v>
+      </c>
+      <c r="R30" s="60"/>
+    </row>
+    <row r="31" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="32" t="n">
         <v>25</v>
       </c>
@@ -7237,9 +7386,9 @@
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="F31" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="F31" s="39" t="s">
         <v>111</v>
       </c>
       <c r="G31" s="32" t="n">
@@ -7252,26 +7401,26 @@
         <v>1</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="K31" s="39" t="s">
-        <v>304</v>
-      </c>
-      <c r="L31" s="39" t="s">
-        <v>305</v>
-      </c>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="39"/>
+        <v>312</v>
+      </c>
+      <c r="K31" s="40" t="s">
+        <v>313</v>
+      </c>
+      <c r="L31" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="M31" s="40"/>
+      <c r="N31" s="40"/>
+      <c r="O31" s="40"/>
       <c r="P31" s="8" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="Q31" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R31" s="58"/>
-    </row>
-    <row r="32" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>312</v>
+      </c>
+      <c r="R31" s="60"/>
+    </row>
+    <row r="32" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="32" t="n">
         <v>26</v>
       </c>
@@ -7283,42 +7432,42 @@
       </c>
       <c r="D32" s="24"/>
       <c r="E32" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="F32" s="62" t="s">
+        <v>316</v>
+      </c>
+      <c r="F32" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="G32" s="48" t="n">
+      <c r="G32" s="49" t="n">
         <v>23</v>
       </c>
-      <c r="H32" s="48" t="n">
+      <c r="H32" s="49" t="n">
         <v>6</v>
       </c>
       <c r="I32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="K32" s="39" t="s">
-        <v>309</v>
-      </c>
-      <c r="L32" s="39" t="s">
-        <v>310</v>
-      </c>
-      <c r="M32" s="39" t="s">
-        <v>311</v>
-      </c>
-      <c r="N32" s="39"/>
-      <c r="O32" s="39"/>
+        <v>317</v>
+      </c>
+      <c r="K32" s="40" t="s">
+        <v>318</v>
+      </c>
+      <c r="L32" s="40" t="s">
+        <v>319</v>
+      </c>
+      <c r="M32" s="40" t="s">
+        <v>320</v>
+      </c>
+      <c r="N32" s="40"/>
+      <c r="O32" s="40"/>
       <c r="P32" s="8" t="s">
         <v>112</v>
       </c>
       <c r="Q32" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="33" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="33" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="32"/>
       <c r="B33" s="24"/>
       <c r="C33" s="32" t="n">
@@ -7326,9 +7475,9 @@
       </c>
       <c r="D33" s="24"/>
       <c r="E33" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="F33" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="F33" s="39" t="s">
         <v>113</v>
       </c>
       <c r="G33" s="32" t="n">
@@ -7339,36 +7488,34 @@
         <v>1</v>
       </c>
       <c r="J33" s="8"/>
-      <c r="K33" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="L33" s="39"/>
-      <c r="M33" s="39"/>
-      <c r="N33" s="39"/>
-      <c r="O33" s="39"/>
+      <c r="K33" s="40" t="s">
+        <v>321</v>
+      </c>
+      <c r="L33" s="40"/>
+      <c r="M33" s="40"/>
+      <c r="N33" s="40"/>
+      <c r="O33" s="40"/>
       <c r="P33" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q33" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R33" s="58"/>
-    </row>
-    <row r="34" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>322</v>
+      </c>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="60"/>
+    </row>
+    <row r="34" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="32" t="n">
         <v>27</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="C34" s="32" t="n">
         <v>26</v>
       </c>
       <c r="D34" s="24"/>
       <c r="E34" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="F34" s="38" t="s">
+        <v>324</v>
+      </c>
+      <c r="F34" s="39" t="s">
         <v>114</v>
       </c>
       <c r="G34" s="32" t="n">
@@ -7381,26 +7528,26 @@
         <v>1</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="K34" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="L34" s="39" t="s">
-        <v>318</v>
-      </c>
-      <c r="M34" s="39"/>
-      <c r="N34" s="39"/>
-      <c r="O34" s="39"/>
+        <v>325</v>
+      </c>
+      <c r="K34" s="40" t="s">
+        <v>326</v>
+      </c>
+      <c r="L34" s="40" t="s">
+        <v>327</v>
+      </c>
+      <c r="M34" s="40"/>
+      <c r="N34" s="40"/>
+      <c r="O34" s="40"/>
       <c r="P34" s="8" t="s">
         <v>114</v>
       </c>
       <c r="Q34" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R34" s="58"/>
-    </row>
-    <row r="35" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>325</v>
+      </c>
+      <c r="R34" s="60"/>
+    </row>
+    <row r="35" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="32" t="n">
         <v>28</v>
       </c>
@@ -7412,9 +7559,9 @@
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="24" t="s">
-        <v>319</v>
-      </c>
-      <c r="F35" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="F35" s="39" t="s">
         <v>73</v>
       </c>
       <c r="G35" s="32" t="n">
@@ -7427,276 +7574,276 @@
         <v>1</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="K35" s="39" t="s">
-        <v>321</v>
-      </c>
-      <c r="L35" s="39" t="s">
-        <v>322</v>
-      </c>
-      <c r="M35" s="39"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="39"/>
+        <v>329</v>
+      </c>
+      <c r="K35" s="40" t="s">
+        <v>330</v>
+      </c>
+      <c r="L35" s="40" t="s">
+        <v>331</v>
+      </c>
+      <c r="M35" s="40"/>
+      <c r="N35" s="40"/>
+      <c r="O35" s="40"/>
       <c r="P35" s="8" t="s">
         <v>73</v>
       </c>
       <c r="Q35" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R35" s="58"/>
-    </row>
-    <row r="36" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="41" t="n">
+        <v>329</v>
+      </c>
+      <c r="R35" s="60"/>
+    </row>
+    <row r="36" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="42" t="n">
         <v>29</v>
       </c>
       <c r="B36" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="C36" s="41" t="n">
+      <c r="C36" s="42" t="n">
         <v>28</v>
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="F36" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="F36" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="G36" s="44" t="n">
+      <c r="G36" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="44" t="n">
+      <c r="H36" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="I36" s="41" t="n">
+      <c r="I36" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="K36" s="45" t="s">
-        <v>325</v>
-      </c>
-      <c r="L36" s="45" t="s">
-        <v>326</v>
-      </c>
-      <c r="M36" s="45"/>
-      <c r="N36" s="45"/>
-      <c r="O36" s="45"/>
+        <v>333</v>
+      </c>
+      <c r="K36" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="L36" s="46" t="s">
+        <v>335</v>
+      </c>
+      <c r="M36" s="46"/>
+      <c r="N36" s="46"/>
+      <c r="O36" s="46"/>
       <c r="P36" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="Q36" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R36" s="58"/>
-    </row>
-    <row r="37" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="41" t="n">
+      <c r="Q36" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="R36" s="60"/>
+    </row>
+    <row r="37" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="42" t="n">
         <v>30</v>
       </c>
       <c r="B37" s="23"/>
-      <c r="C37" s="41" t="n">
+      <c r="C37" s="42" t="n">
         <v>29</v>
       </c>
       <c r="D37" s="23"/>
       <c r="E37" s="23" t="s">
-        <v>327</v>
-      </c>
-      <c r="F37" s="63" t="s">
+        <v>336</v>
+      </c>
+      <c r="F37" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="G37" s="44" t="n">
+      <c r="G37" s="45" t="n">
         <v>29</v>
       </c>
-      <c r="H37" s="44" t="n">
+      <c r="H37" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="I37" s="41" t="n">
+      <c r="I37" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="K37" s="45" t="s">
-        <v>329</v>
-      </c>
-      <c r="L37" s="45" t="s">
-        <v>330</v>
-      </c>
-      <c r="M37" s="45"/>
-      <c r="N37" s="45"/>
-      <c r="O37" s="45"/>
+        <v>337</v>
+      </c>
+      <c r="K37" s="46" t="s">
+        <v>338</v>
+      </c>
+      <c r="L37" s="46" t="s">
+        <v>339</v>
+      </c>
+      <c r="M37" s="46"/>
+      <c r="N37" s="46"/>
+      <c r="O37" s="46"/>
       <c r="P37" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q37" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R37" s="61"/>
-    </row>
-    <row r="38" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="54" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q37" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="R37" s="63"/>
+    </row>
+    <row r="38" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="56" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="55" t="n">
+      <c r="B38" s="57" t="n">
         <v>23</v>
       </c>
-      <c r="C38" s="54" t="n">
+      <c r="C38" s="56" t="n">
         <v>33</v>
       </c>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55" t="s">
-        <v>332</v>
-      </c>
-      <c r="F38" s="55" t="s">
+      <c r="D38" s="57"/>
+      <c r="E38" s="57" t="s">
+        <v>341</v>
+      </c>
+      <c r="F38" s="57" t="s">
         <v>121</v>
       </c>
-      <c r="G38" s="54" t="n">
+      <c r="G38" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="54" t="n">
+      <c r="H38" s="56" t="n">
         <v>6</v>
       </c>
-      <c r="I38" s="54" t="n">
+      <c r="I38" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="56" t="s">
-        <v>333</v>
-      </c>
-      <c r="K38" s="57" t="s">
-        <v>334</v>
-      </c>
-      <c r="L38" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="M38" s="57"/>
-      <c r="N38" s="57" t="s">
-        <v>336</v>
-      </c>
-      <c r="O38" s="57" t="s">
-        <v>337</v>
-      </c>
-      <c r="P38" s="56" t="s">
+      <c r="J38" s="58" t="s">
+        <v>342</v>
+      </c>
+      <c r="K38" s="59" t="s">
+        <v>343</v>
+      </c>
+      <c r="L38" s="59" t="s">
+        <v>344</v>
+      </c>
+      <c r="M38" s="59"/>
+      <c r="N38" s="59" t="s">
+        <v>345</v>
+      </c>
+      <c r="O38" s="59" t="s">
+        <v>346</v>
+      </c>
+      <c r="P38" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="Q38" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R38" s="58"/>
-    </row>
-    <row r="39" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="54"/>
-      <c r="B39" s="55"/>
-      <c r="C39" s="54" t="n">
+      <c r="Q38" s="58" t="s">
+        <v>342</v>
+      </c>
+      <c r="R38" s="60"/>
+    </row>
+    <row r="39" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="56"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="56" t="n">
         <v>34</v>
       </c>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55" t="s">
-        <v>332</v>
-      </c>
-      <c r="F39" s="55"/>
-      <c r="G39" s="54"/>
-      <c r="H39" s="54"/>
-      <c r="I39" s="54" t="n">
+      <c r="D39" s="57"/>
+      <c r="E39" s="57" t="s">
+        <v>341</v>
+      </c>
+      <c r="F39" s="57"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="56" t="s">
-        <v>338</v>
-      </c>
-      <c r="K39" s="57"/>
-      <c r="L39" s="57" t="s">
-        <v>339</v>
-      </c>
-      <c r="M39" s="57"/>
-      <c r="N39" s="57" t="s">
-        <v>340</v>
-      </c>
-      <c r="O39" s="57"/>
-      <c r="P39" s="56" t="s">
+      <c r="J39" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="K39" s="59"/>
+      <c r="L39" s="59" t="s">
+        <v>348</v>
+      </c>
+      <c r="M39" s="59"/>
+      <c r="N39" s="59" t="s">
+        <v>349</v>
+      </c>
+      <c r="O39" s="59"/>
+      <c r="P39" s="58" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q39" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="R39" s="60"/>
+    </row>
+    <row r="40" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="56"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="56" t="n">
+        <v>35</v>
+      </c>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57" t="s">
         <v>341</v>
       </c>
-      <c r="Q39" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R39" s="58"/>
-    </row>
-    <row r="40" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="54"/>
-      <c r="B40" s="55"/>
-      <c r="C40" s="54" t="n">
-        <v>35</v>
-      </c>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55" t="s">
-        <v>332</v>
-      </c>
-      <c r="F40" s="60" t="s">
+      <c r="F40" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="G40" s="54" t="n">
+      <c r="G40" s="56" t="n">
         <v>34</v>
       </c>
-      <c r="H40" s="54"/>
-      <c r="I40" s="54" t="n">
+      <c r="H40" s="56"/>
+      <c r="I40" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="56" t="s">
-        <v>342</v>
-      </c>
-      <c r="K40" s="57" t="s">
-        <v>343</v>
-      </c>
-      <c r="L40" s="57" t="s">
-        <v>344</v>
-      </c>
-      <c r="M40" s="57"/>
-      <c r="N40" s="57"/>
-      <c r="O40" s="57"/>
-      <c r="P40" s="56" t="s">
-        <v>345</v>
-      </c>
-      <c r="Q40" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R40" s="61"/>
-    </row>
-    <row r="41" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J40" s="58" t="s">
+        <v>351</v>
+      </c>
+      <c r="K40" s="59" t="s">
+        <v>352</v>
+      </c>
+      <c r="L40" s="59" t="s">
+        <v>353</v>
+      </c>
+      <c r="M40" s="59"/>
+      <c r="N40" s="59"/>
+      <c r="O40" s="59"/>
+      <c r="P40" s="58" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q40" s="58" t="s">
+        <v>351</v>
+      </c>
+      <c r="R40" s="63"/>
+    </row>
+    <row r="41" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="32" t="n">
         <v>31</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C41" s="32"/>
       <c r="D41" s="24"/>
-      <c r="E41" s="64" t="s">
-        <v>347</v>
+      <c r="E41" s="66" t="s">
+        <v>356</v>
       </c>
       <c r="F41" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="G41" s="48" t="n">
+      <c r="G41" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="48" t="n">
+      <c r="H41" s="49" t="n">
         <v>6</v>
       </c>
       <c r="I41" s="32"/>
       <c r="J41" s="8"/>
-      <c r="K41" s="39"/>
-      <c r="L41" s="39"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="39"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
       <c r="P41" s="8"/>
       <c r="Q41" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R41" s="58"/>
-    </row>
-    <row r="42" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>357</v>
+      </c>
+      <c r="R41" s="60"/>
+    </row>
+    <row r="42" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="32" t="n">
         <v>32</v>
       </c>
@@ -7706,9 +7853,9 @@
       </c>
       <c r="D42" s="24"/>
       <c r="E42" s="24" t="s">
-        <v>348</v>
-      </c>
-      <c r="F42" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="F42" s="39" t="s">
         <v>118</v>
       </c>
       <c r="G42" s="32" t="n">
@@ -7721,36 +7868,36 @@
         <v>1</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="K42" s="39" t="s">
-        <v>350</v>
-      </c>
-      <c r="L42" s="39" t="s">
-        <v>351</v>
-      </c>
-      <c r="M42" s="39"/>
-      <c r="N42" s="39"/>
-      <c r="O42" s="39"/>
+        <v>359</v>
+      </c>
+      <c r="K42" s="40" t="s">
+        <v>360</v>
+      </c>
+      <c r="L42" s="40" t="s">
+        <v>361</v>
+      </c>
+      <c r="M42" s="40"/>
+      <c r="N42" s="40"/>
+      <c r="O42" s="40"/>
       <c r="P42" s="8" t="s">
         <v>118</v>
       </c>
       <c r="Q42" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R42" s="58"/>
-    </row>
-    <row r="43" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>359</v>
+      </c>
+      <c r="R42" s="60"/>
+    </row>
+    <row r="43" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="32"/>
       <c r="B43" s="24"/>
       <c r="C43" s="32" t="n">
         <v>31</v>
       </c>
       <c r="D43" s="24"/>
-      <c r="E43" s="64" t="s">
-        <v>347</v>
-      </c>
-      <c r="F43" s="38" t="s">
+      <c r="E43" s="66" t="s">
+        <v>356</v>
+      </c>
+      <c r="F43" s="39" t="s">
         <v>109</v>
       </c>
       <c r="G43" s="32" t="n">
@@ -7761,26 +7908,26 @@
         <v>1</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="K43" s="39" t="s">
-        <v>353</v>
-      </c>
-      <c r="L43" s="39" t="s">
-        <v>354</v>
-      </c>
-      <c r="M43" s="39"/>
-      <c r="N43" s="39"/>
-      <c r="O43" s="39"/>
+        <v>362</v>
+      </c>
+      <c r="K43" s="40" t="s">
+        <v>363</v>
+      </c>
+      <c r="L43" s="40" t="s">
+        <v>364</v>
+      </c>
+      <c r="M43" s="40"/>
+      <c r="N43" s="40"/>
+      <c r="O43" s="40"/>
       <c r="P43" s="8" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="Q43" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R43" s="61"/>
-    </row>
-    <row r="44" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>362</v>
+      </c>
+      <c r="R43" s="63"/>
+    </row>
+    <row r="44" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="32" t="n">
         <v>33</v>
       </c>
@@ -7792,9 +7939,9 @@
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="24" t="s">
-        <v>356</v>
-      </c>
-      <c r="F44" s="38" t="s">
+        <v>366</v>
+      </c>
+      <c r="F44" s="39" t="s">
         <v>119</v>
       </c>
       <c r="G44" s="32" t="n">
@@ -7807,311 +7954,311 @@
         <v>1</v>
       </c>
       <c r="J44" s="8"/>
-      <c r="K44" s="39" t="s">
-        <v>357</v>
-      </c>
-      <c r="L44" s="39"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="39"/>
-      <c r="O44" s="39"/>
+      <c r="K44" s="40" t="s">
+        <v>367</v>
+      </c>
+      <c r="L44" s="40"/>
+      <c r="M44" s="40"/>
+      <c r="N44" s="40"/>
+      <c r="O44" s="40"/>
       <c r="P44" s="8" t="s">
         <v>119</v>
       </c>
       <c r="Q44" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R44" s="58"/>
-    </row>
-    <row r="45" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="41" t="n">
+        <v>368</v>
+      </c>
+      <c r="R44" s="60"/>
+    </row>
+    <row r="45" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="42" t="n">
         <v>35</v>
       </c>
       <c r="B45" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="C45" s="41"/>
+      <c r="C45" s="42"/>
       <c r="D45" s="23"/>
       <c r="E45" s="23" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F45" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="G45" s="41" t="n">
+      <c r="G45" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="H45" s="41" t="n">
+      <c r="H45" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="I45" s="41"/>
+      <c r="I45" s="42"/>
       <c r="J45" s="5"/>
-      <c r="K45" s="45"/>
-      <c r="L45" s="45"/>
-      <c r="M45" s="45"/>
-      <c r="N45" s="45"/>
-      <c r="O45" s="45"/>
+      <c r="K45" s="46"/>
+      <c r="L45" s="46"/>
+      <c r="M45" s="46"/>
+      <c r="N45" s="46"/>
+      <c r="O45" s="46"/>
       <c r="P45" s="5"/>
       <c r="Q45" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R45" s="58"/>
-    </row>
-    <row r="46" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="41" t="n">
+        <v>370</v>
+      </c>
+      <c r="R45" s="60"/>
+    </row>
+    <row r="46" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="42" t="n">
         <v>36</v>
       </c>
       <c r="B46" s="23"/>
-      <c r="C46" s="41" t="n">
+      <c r="C46" s="42" t="n">
         <v>36</v>
       </c>
       <c r="D46" s="23"/>
       <c r="E46" s="23" t="s">
-        <v>359</v>
-      </c>
-      <c r="F46" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="F46" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="G46" s="41" t="n">
+      <c r="G46" s="42" t="n">
         <v>35</v>
       </c>
-      <c r="H46" s="41" t="n">
+      <c r="H46" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="I46" s="41" t="n">
+      <c r="I46" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="K46" s="45" t="s">
-        <v>361</v>
-      </c>
-      <c r="L46" s="45" t="s">
-        <v>362</v>
-      </c>
-      <c r="M46" s="45"/>
-      <c r="N46" s="45" t="s">
-        <v>363</v>
-      </c>
-      <c r="O46" s="45"/>
+        <v>372</v>
+      </c>
+      <c r="K46" s="46" t="s">
+        <v>373</v>
+      </c>
+      <c r="L46" s="46" t="s">
+        <v>374</v>
+      </c>
+      <c r="M46" s="46"/>
+      <c r="N46" s="46" t="s">
+        <v>375</v>
+      </c>
+      <c r="O46" s="46"/>
       <c r="P46" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="Q46" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R46" s="61"/>
-    </row>
-    <row r="47" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="41" t="n">
+      <c r="Q46" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="R46" s="63"/>
+    </row>
+    <row r="47" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="42" t="n">
         <v>37</v>
       </c>
       <c r="B47" s="23"/>
-      <c r="C47" s="41" t="n">
+      <c r="C47" s="42" t="n">
         <v>37</v>
       </c>
       <c r="D47" s="23"/>
       <c r="E47" s="23" t="s">
-        <v>359</v>
-      </c>
-      <c r="F47" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="F47" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="G47" s="41" t="n">
+      <c r="G47" s="42" t="n">
         <v>35</v>
       </c>
-      <c r="H47" s="41" t="n">
+      <c r="H47" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="I47" s="41" t="n">
+      <c r="I47" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J47" s="5"/>
-      <c r="K47" s="45" t="s">
-        <v>364</v>
-      </c>
-      <c r="L47" s="45"/>
-      <c r="M47" s="45"/>
-      <c r="N47" s="45"/>
-      <c r="O47" s="45"/>
+      <c r="K47" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="L47" s="46"/>
+      <c r="M47" s="46"/>
+      <c r="N47" s="46"/>
+      <c r="O47" s="46"/>
       <c r="P47" s="5" t="s">
         <v>124</v>
       </c>
       <c r="Q47" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R47" s="61"/>
-    </row>
-    <row r="48" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="41"/>
+        <v>377</v>
+      </c>
+      <c r="R47" s="63"/>
+    </row>
+    <row r="48" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="42"/>
       <c r="B48" s="23"/>
-      <c r="C48" s="41" t="n">
+      <c r="C48" s="42" t="n">
         <v>38</v>
       </c>
       <c r="D48" s="23"/>
       <c r="E48" s="23" t="s">
-        <v>365</v>
-      </c>
-      <c r="F48" s="46"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="41"/>
-      <c r="I48" s="41" t="n">
+        <v>378</v>
+      </c>
+      <c r="F48" s="47"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="42"/>
+      <c r="I48" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J48" s="5"/>
-      <c r="K48" s="45" t="s">
-        <v>366</v>
-      </c>
-      <c r="L48" s="45"/>
-      <c r="M48" s="45"/>
-      <c r="N48" s="45"/>
-      <c r="O48" s="45"/>
+      <c r="K48" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="L48" s="46"/>
+      <c r="M48" s="46"/>
+      <c r="N48" s="46"/>
+      <c r="O48" s="46"/>
       <c r="P48" s="5" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="Q48" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R48" s="61"/>
-    </row>
-    <row r="49" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="41"/>
+        <v>377</v>
+      </c>
+      <c r="R48" s="63"/>
+    </row>
+    <row r="49" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="42"/>
       <c r="B49" s="23"/>
-      <c r="C49" s="41" t="n">
+      <c r="C49" s="42" t="n">
         <v>39</v>
       </c>
       <c r="D49" s="23"/>
       <c r="E49" s="23" t="s">
-        <v>368</v>
-      </c>
-      <c r="F49" s="46"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41" t="n">
+        <v>381</v>
+      </c>
+      <c r="F49" s="47"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J49" s="5"/>
-      <c r="K49" s="45" t="s">
-        <v>369</v>
-      </c>
-      <c r="L49" s="45"/>
-      <c r="M49" s="45"/>
-      <c r="N49" s="45"/>
-      <c r="O49" s="45"/>
+      <c r="K49" s="46" t="s">
+        <v>382</v>
+      </c>
+      <c r="L49" s="46"/>
+      <c r="M49" s="46"/>
+      <c r="N49" s="46"/>
+      <c r="O49" s="46"/>
       <c r="P49" s="5" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="Q49" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R49" s="61"/>
-    </row>
-    <row r="50" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="41"/>
+        <v>377</v>
+      </c>
+      <c r="R49" s="63"/>
+    </row>
+    <row r="50" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="42"/>
       <c r="B50" s="23"/>
-      <c r="C50" s="41" t="n">
+      <c r="C50" s="42" t="n">
         <v>40</v>
       </c>
       <c r="D50" s="23"/>
       <c r="E50" s="23" t="s">
-        <v>365</v>
-      </c>
-      <c r="F50" s="46"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="41" t="n">
+        <v>378</v>
+      </c>
+      <c r="F50" s="47"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J50" s="5"/>
-      <c r="K50" s="45" t="s">
-        <v>371</v>
-      </c>
-      <c r="L50" s="45"/>
-      <c r="M50" s="45"/>
-      <c r="N50" s="45"/>
-      <c r="O50" s="45"/>
+      <c r="K50" s="46" t="s">
+        <v>384</v>
+      </c>
+      <c r="L50" s="46"/>
+      <c r="M50" s="46"/>
+      <c r="N50" s="46"/>
+      <c r="O50" s="46"/>
       <c r="P50" s="5" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="Q50" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R50" s="58"/>
-    </row>
-    <row r="51" s="59" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="41" t="n">
+        <v>377</v>
+      </c>
+      <c r="R50" s="60"/>
+    </row>
+    <row r="51" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="42" t="n">
         <v>38</v>
       </c>
       <c r="B51" s="23"/>
-      <c r="C51" s="41" t="n">
+      <c r="C51" s="42" t="n">
         <v>41</v>
       </c>
       <c r="D51" s="23"/>
       <c r="E51" s="23" t="s">
-        <v>373</v>
-      </c>
-      <c r="F51" s="46" t="s">
+        <v>386</v>
+      </c>
+      <c r="F51" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="G51" s="41" t="n">
+      <c r="G51" s="42" t="n">
         <v>35</v>
       </c>
-      <c r="H51" s="41" t="n">
+      <c r="H51" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="I51" s="41" t="n">
+      <c r="I51" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="K51" s="45" t="s">
-        <v>375</v>
-      </c>
-      <c r="L51" s="45" t="s">
-        <v>376</v>
-      </c>
-      <c r="M51" s="45"/>
-      <c r="N51" s="45" t="s">
-        <v>377</v>
-      </c>
-      <c r="O51" s="45"/>
+        <v>387</v>
+      </c>
+      <c r="K51" s="46" t="s">
+        <v>388</v>
+      </c>
+      <c r="L51" s="46" t="s">
+        <v>389</v>
+      </c>
+      <c r="M51" s="46"/>
+      <c r="N51" s="46" t="s">
+        <v>390</v>
+      </c>
+      <c r="O51" s="46"/>
       <c r="P51" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="Q51" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="R51" s="61"/>
+        <v>391</v>
+      </c>
+      <c r="Q51" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="R51" s="63"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="65" t="n">
+      <c r="A52" s="67" t="n">
         <v>43</v>
       </c>
-      <c r="B52" s="66" t="n">
+      <c r="B52" s="68" t="n">
         <v>2</v>
       </c>
-      <c r="C52" s="65"/>
-      <c r="D52" s="66"/>
-      <c r="E52" s="66" t="n">
+      <c r="C52" s="67"/>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68" t="n">
         <v>43</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="G52" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="65" t="n">
+      <c r="H52" s="67" t="n">
         <v>5</v>
       </c>
-      <c r="I52" s="65"/>
-      <c r="K52" s="67"/>
-      <c r="L52" s="67"/>
-      <c r="M52" s="67"/>
-      <c r="N52" s="67"/>
-      <c r="O52" s="67"/>
-      <c r="R52" s="47"/>
+      <c r="I52" s="67"/>
+      <c r="K52" s="69"/>
+      <c r="L52" s="69"/>
+      <c r="M52" s="69"/>
+      <c r="N52" s="69"/>
+      <c r="O52" s="69"/>
+      <c r="R52" s="48"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="32" t="n">
@@ -8123,71 +8270,71 @@
       </c>
       <c r="D53" s="24"/>
       <c r="E53" s="24" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="F53" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="G53" s="48" t="n">
+      <c r="G53" s="49" t="n">
         <v>43</v>
       </c>
-      <c r="H53" s="48" t="n">
+      <c r="H53" s="49" t="n">
         <v>2</v>
       </c>
       <c r="I53" s="32" t="n">
         <v>1</v>
       </c>
       <c r="J53" s="8"/>
-      <c r="K53" s="39" t="s">
-        <v>381</v>
-      </c>
-      <c r="L53" s="39"/>
-      <c r="M53" s="39"/>
-      <c r="N53" s="39"/>
-      <c r="O53" s="39"/>
+      <c r="K53" s="40" t="s">
+        <v>394</v>
+      </c>
+      <c r="L53" s="40"/>
+      <c r="M53" s="40"/>
+      <c r="N53" s="40"/>
+      <c r="O53" s="40"/>
       <c r="P53" s="8"/>
       <c r="Q53" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R53" s="47"/>
+        <v>395</v>
+      </c>
+      <c r="R53" s="48"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="41" t="n">
+      <c r="A54" s="42" t="n">
         <v>45</v>
       </c>
       <c r="B54" s="23"/>
-      <c r="C54" s="41" t="n">
+      <c r="C54" s="42" t="n">
         <v>46</v>
       </c>
       <c r="D54" s="23"/>
       <c r="E54" s="23" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="F54" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="G54" s="41" t="n">
+      <c r="G54" s="42" t="n">
         <v>43</v>
       </c>
-      <c r="H54" s="41" t="n">
+      <c r="H54" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I54" s="41" t="n">
+      <c r="I54" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J54" s="5"/>
-      <c r="K54" s="45" t="s">
-        <v>384</v>
-      </c>
-      <c r="L54" s="45"/>
-      <c r="M54" s="45"/>
-      <c r="N54" s="45"/>
-      <c r="O54" s="45"/>
+      <c r="K54" s="46" t="s">
+        <v>397</v>
+      </c>
+      <c r="L54" s="46"/>
+      <c r="M54" s="46"/>
+      <c r="N54" s="46"/>
+      <c r="O54" s="46"/>
       <c r="P54" s="5"/>
-      <c r="Q54" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R54" s="47"/>
+      <c r="Q54" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="R54" s="48"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="32" t="n">
@@ -8199,7 +8346,7 @@
       </c>
       <c r="D55" s="24"/>
       <c r="E55" s="24" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="F55" s="24" t="s">
         <v>92</v>
@@ -8214,18 +8361,18 @@
         <v>1</v>
       </c>
       <c r="J55" s="8"/>
-      <c r="K55" s="39" t="s">
-        <v>386</v>
-      </c>
-      <c r="L55" s="39"/>
-      <c r="M55" s="39"/>
-      <c r="N55" s="39"/>
-      <c r="O55" s="39"/>
+      <c r="K55" s="40" t="s">
+        <v>400</v>
+      </c>
+      <c r="L55" s="40"/>
+      <c r="M55" s="40"/>
+      <c r="N55" s="40"/>
+      <c r="O55" s="40"/>
       <c r="P55" s="8"/>
       <c r="Q55" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R55" s="47"/>
+        <v>401</v>
+      </c>
+      <c r="R55" s="48"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="32" t="n">
@@ -8237,9 +8384,9 @@
       </c>
       <c r="D56" s="24"/>
       <c r="E56" s="24" t="s">
-        <v>387</v>
-      </c>
-      <c r="F56" s="38" t="s">
+        <v>402</v>
+      </c>
+      <c r="F56" s="39" t="s">
         <v>133</v>
       </c>
       <c r="G56" s="32" t="n">
@@ -8252,18 +8399,18 @@
         <v>1</v>
       </c>
       <c r="J56" s="8"/>
-      <c r="K56" s="39" t="s">
-        <v>388</v>
-      </c>
-      <c r="L56" s="39"/>
-      <c r="M56" s="39"/>
-      <c r="N56" s="39"/>
-      <c r="O56" s="39"/>
+      <c r="K56" s="40" t="s">
+        <v>403</v>
+      </c>
+      <c r="L56" s="40"/>
+      <c r="M56" s="40"/>
+      <c r="N56" s="40"/>
+      <c r="O56" s="40"/>
       <c r="P56" s="8"/>
       <c r="Q56" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R56" s="47"/>
+        <v>404</v>
+      </c>
+      <c r="R56" s="48"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="32" t="n">
@@ -8277,9 +8424,9 @@
       </c>
       <c r="D57" s="24"/>
       <c r="E57" s="24" t="s">
-        <v>389</v>
-      </c>
-      <c r="F57" s="38" t="s">
+        <v>405</v>
+      </c>
+      <c r="F57" s="39" t="s">
         <v>134</v>
       </c>
       <c r="G57" s="32" t="n">
@@ -8292,18 +8439,18 @@
         <v>1</v>
       </c>
       <c r="J57" s="8"/>
-      <c r="K57" s="39" t="s">
-        <v>390</v>
-      </c>
-      <c r="L57" s="39"/>
-      <c r="M57" s="39"/>
-      <c r="N57" s="39"/>
-      <c r="O57" s="39"/>
+      <c r="K57" s="40" t="s">
+        <v>406</v>
+      </c>
+      <c r="L57" s="40"/>
+      <c r="M57" s="40"/>
+      <c r="N57" s="40"/>
+      <c r="O57" s="40"/>
       <c r="P57" s="8"/>
       <c r="Q57" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R57" s="47"/>
+        <v>407</v>
+      </c>
+      <c r="R57" s="48"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="32" t="n">
@@ -8315,9 +8462,9 @@
       </c>
       <c r="D58" s="24"/>
       <c r="E58" s="24" t="s">
-        <v>391</v>
-      </c>
-      <c r="F58" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="F58" s="39" t="s">
         <v>135</v>
       </c>
       <c r="G58" s="32" t="n">
@@ -8330,18 +8477,18 @@
         <v>1</v>
       </c>
       <c r="J58" s="8"/>
-      <c r="K58" s="39" t="s">
-        <v>392</v>
-      </c>
-      <c r="L58" s="39"/>
-      <c r="M58" s="39"/>
-      <c r="N58" s="39"/>
-      <c r="O58" s="39"/>
+      <c r="K58" s="40" t="s">
+        <v>409</v>
+      </c>
+      <c r="L58" s="40"/>
+      <c r="M58" s="40"/>
+      <c r="N58" s="40"/>
+      <c r="O58" s="40"/>
       <c r="P58" s="8"/>
       <c r="Q58" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R58" s="47"/>
+        <v>410</v>
+      </c>
+      <c r="R58" s="48"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="32" t="n">
@@ -8353,9 +8500,9 @@
       </c>
       <c r="D59" s="24"/>
       <c r="E59" s="24" t="s">
-        <v>393</v>
-      </c>
-      <c r="F59" s="38" t="s">
+        <v>411</v>
+      </c>
+      <c r="F59" s="39" t="s">
         <v>97</v>
       </c>
       <c r="G59" s="32" t="n">
@@ -8368,18 +8515,18 @@
         <v>1</v>
       </c>
       <c r="J59" s="8"/>
-      <c r="K59" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="L59" s="39"/>
-      <c r="M59" s="39"/>
-      <c r="N59" s="39"/>
-      <c r="O59" s="39"/>
+      <c r="K59" s="40" t="s">
+        <v>412</v>
+      </c>
+      <c r="L59" s="40"/>
+      <c r="M59" s="40"/>
+      <c r="N59" s="40"/>
+      <c r="O59" s="40"/>
       <c r="P59" s="8"/>
       <c r="Q59" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R59" s="47"/>
+        <v>413</v>
+      </c>
+      <c r="R59" s="48"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="32" t="n">
@@ -8393,9 +8540,9 @@
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="24" t="s">
-        <v>395</v>
-      </c>
-      <c r="F60" s="38" t="s">
+        <v>414</v>
+      </c>
+      <c r="F60" s="39" t="s">
         <v>93</v>
       </c>
       <c r="G60" s="32" t="n">
@@ -8408,20 +8555,20 @@
         <v>1</v>
       </c>
       <c r="J60" s="8"/>
-      <c r="K60" s="39" t="s">
-        <v>396</v>
-      </c>
-      <c r="L60" s="39"/>
-      <c r="M60" s="39"/>
-      <c r="N60" s="39" t="s">
-        <v>397</v>
-      </c>
-      <c r="O60" s="39"/>
+      <c r="K60" s="40" t="s">
+        <v>415</v>
+      </c>
+      <c r="L60" s="40"/>
+      <c r="M60" s="40"/>
+      <c r="N60" s="40" t="s">
+        <v>416</v>
+      </c>
+      <c r="O60" s="40"/>
       <c r="P60" s="8"/>
       <c r="Q60" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R60" s="47"/>
+        <v>417</v>
+      </c>
+      <c r="R60" s="48"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="32" t="n">
@@ -8433,10 +8580,10 @@
       </c>
       <c r="D61" s="24"/>
       <c r="E61" s="24" t="s">
-        <v>398</v>
-      </c>
-      <c r="F61" s="51" t="s">
-        <v>399</v>
+        <v>418</v>
+      </c>
+      <c r="F61" s="52" t="s">
+        <v>419</v>
       </c>
       <c r="G61" s="32" t="n">
         <v>51</v>
@@ -8448,18 +8595,18 @@
         <v>1</v>
       </c>
       <c r="J61" s="8"/>
-      <c r="K61" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="L61" s="39"/>
-      <c r="M61" s="39"/>
-      <c r="N61" s="39"/>
-      <c r="O61" s="39"/>
+      <c r="K61" s="40" t="s">
+        <v>420</v>
+      </c>
+      <c r="L61" s="40"/>
+      <c r="M61" s="40"/>
+      <c r="N61" s="40"/>
+      <c r="O61" s="40"/>
       <c r="P61" s="8"/>
       <c r="Q61" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R61" s="47"/>
+        <v>421</v>
+      </c>
+      <c r="R61" s="48"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="32" t="n">
@@ -8471,9 +8618,9 @@
       </c>
       <c r="D62" s="24"/>
       <c r="E62" s="24" t="s">
-        <v>401</v>
-      </c>
-      <c r="F62" s="51" t="s">
+        <v>422</v>
+      </c>
+      <c r="F62" s="52" t="s">
         <v>160</v>
       </c>
       <c r="G62" s="32" t="n">
@@ -8486,18 +8633,18 @@
         <v>1</v>
       </c>
       <c r="J62" s="8"/>
-      <c r="K62" s="39" t="s">
-        <v>402</v>
-      </c>
-      <c r="L62" s="39"/>
-      <c r="M62" s="39"/>
-      <c r="N62" s="39"/>
-      <c r="O62" s="39"/>
+      <c r="K62" s="40" t="s">
+        <v>423</v>
+      </c>
+      <c r="L62" s="40"/>
+      <c r="M62" s="40"/>
+      <c r="N62" s="40"/>
+      <c r="O62" s="40"/>
       <c r="P62" s="8"/>
       <c r="Q62" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R62" s="40"/>
+        <v>424</v>
+      </c>
+      <c r="R62" s="41"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="32" t="n">
@@ -8509,9 +8656,9 @@
       </c>
       <c r="D63" s="24"/>
       <c r="E63" s="24" t="s">
-        <v>403</v>
-      </c>
-      <c r="F63" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="F63" s="39" t="s">
         <v>138</v>
       </c>
       <c r="G63" s="32" t="n">
@@ -8524,22 +8671,22 @@
         <v>1</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="K63" s="39" t="s">
-        <v>405</v>
-      </c>
-      <c r="L63" s="39" t="s">
-        <v>406</v>
-      </c>
-      <c r="M63" s="39"/>
-      <c r="N63" s="39"/>
-      <c r="O63" s="39"/>
+        <v>426</v>
+      </c>
+      <c r="K63" s="40" t="s">
+        <v>427</v>
+      </c>
+      <c r="L63" s="40" t="s">
+        <v>428</v>
+      </c>
+      <c r="M63" s="40"/>
+      <c r="N63" s="40"/>
+      <c r="O63" s="40"/>
       <c r="P63" s="8"/>
       <c r="Q63" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R63" s="40"/>
+        <v>426</v>
+      </c>
+      <c r="R63" s="41"/>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="32" t="n">
@@ -8551,9 +8698,9 @@
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="24" t="s">
-        <v>407</v>
-      </c>
-      <c r="F64" s="38" t="s">
+        <v>429</v>
+      </c>
+      <c r="F64" s="39" t="s">
         <v>139</v>
       </c>
       <c r="G64" s="32" t="n">
@@ -8566,64 +8713,64 @@
         <v>1</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="K64" s="39" t="s">
-        <v>409</v>
-      </c>
-      <c r="L64" s="39" t="s">
-        <v>410</v>
-      </c>
-      <c r="M64" s="39"/>
-      <c r="N64" s="39"/>
-      <c r="O64" s="39"/>
+        <v>430</v>
+      </c>
+      <c r="K64" s="40" t="s">
+        <v>431</v>
+      </c>
+      <c r="L64" s="40" t="s">
+        <v>432</v>
+      </c>
+      <c r="M64" s="40"/>
+      <c r="N64" s="40"/>
+      <c r="O64" s="40"/>
       <c r="P64" s="8"/>
       <c r="Q64" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R64" s="40"/>
+        <v>430</v>
+      </c>
+      <c r="R64" s="41"/>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="41" t="n">
+      <c r="A65" s="42" t="n">
         <v>56</v>
       </c>
       <c r="B65" s="23"/>
-      <c r="C65" s="41" t="n">
+      <c r="C65" s="42" t="n">
         <v>57</v>
       </c>
       <c r="D65" s="23"/>
       <c r="E65" s="23" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="F65" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G65" s="41" t="n">
+      <c r="G65" s="42" t="n">
         <v>43</v>
       </c>
-      <c r="H65" s="68" t="n">
+      <c r="H65" s="70" t="n">
         <v>2</v>
       </c>
-      <c r="I65" s="41" t="n">
+      <c r="I65" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="K65" s="45" t="s">
-        <v>413</v>
-      </c>
-      <c r="L65" s="45" t="s">
-        <v>414</v>
-      </c>
-      <c r="M65" s="45"/>
-      <c r="N65" s="45"/>
-      <c r="O65" s="45"/>
+        <v>434</v>
+      </c>
+      <c r="K65" s="46" t="s">
+        <v>435</v>
+      </c>
+      <c r="L65" s="46" t="s">
+        <v>436</v>
+      </c>
+      <c r="M65" s="46"/>
+      <c r="N65" s="46"/>
+      <c r="O65" s="46"/>
       <c r="P65" s="5"/>
-      <c r="Q65" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R65" s="47"/>
+      <c r="Q65" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="R65" s="48"/>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="32" t="n">
@@ -8633,7 +8780,7 @@
       <c r="C66" s="32"/>
       <c r="D66" s="24"/>
       <c r="E66" s="24" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="F66" s="24" t="s">
         <v>140</v>
@@ -8646,16 +8793,16 @@
       </c>
       <c r="I66" s="32"/>
       <c r="J66" s="8"/>
-      <c r="K66" s="39"/>
-      <c r="L66" s="39"/>
-      <c r="M66" s="39"/>
-      <c r="N66" s="39"/>
-      <c r="O66" s="39"/>
+      <c r="K66" s="40"/>
+      <c r="L66" s="40"/>
+      <c r="M66" s="40"/>
+      <c r="N66" s="40"/>
+      <c r="O66" s="40"/>
       <c r="P66" s="8"/>
       <c r="Q66" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R66" s="40"/>
+        <v>438</v>
+      </c>
+      <c r="R66" s="41"/>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="32" t="n">
@@ -8667,9 +8814,9 @@
       </c>
       <c r="D67" s="24"/>
       <c r="E67" s="24" t="s">
-        <v>416</v>
-      </c>
-      <c r="F67" s="38" t="s">
+        <v>439</v>
+      </c>
+      <c r="F67" s="39" t="s">
         <v>141</v>
       </c>
       <c r="G67" s="32" t="n">
@@ -8682,22 +8829,22 @@
         <v>1</v>
       </c>
       <c r="J67" s="8" t="s">
-        <v>417</v>
-      </c>
-      <c r="K67" s="39" t="s">
-        <v>418</v>
-      </c>
-      <c r="L67" s="39" t="s">
-        <v>419</v>
-      </c>
-      <c r="M67" s="39"/>
-      <c r="N67" s="39"/>
-      <c r="O67" s="39"/>
+        <v>440</v>
+      </c>
+      <c r="K67" s="40" t="s">
+        <v>441</v>
+      </c>
+      <c r="L67" s="40" t="s">
+        <v>442</v>
+      </c>
+      <c r="M67" s="40"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
       <c r="P67" s="8"/>
       <c r="Q67" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R67" s="40"/>
+        <v>440</v>
+      </c>
+      <c r="R67" s="41"/>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="32" t="n">
@@ -8709,9 +8856,9 @@
       </c>
       <c r="D68" s="24"/>
       <c r="E68" s="24" t="s">
-        <v>420</v>
-      </c>
-      <c r="F68" s="38" t="s">
+        <v>443</v>
+      </c>
+      <c r="F68" s="39" t="s">
         <v>5</v>
       </c>
       <c r="G68" s="32" t="n">
@@ -8724,22 +8871,22 @@
         <v>1</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K68" s="39" t="s">
-        <v>422</v>
-      </c>
-      <c r="L68" s="39" t="s">
-        <v>423</v>
-      </c>
-      <c r="M68" s="39"/>
-      <c r="N68" s="39"/>
-      <c r="O68" s="39"/>
+        <v>444</v>
+      </c>
+      <c r="K68" s="40" t="s">
+        <v>445</v>
+      </c>
+      <c r="L68" s="40" t="s">
+        <v>446</v>
+      </c>
+      <c r="M68" s="40"/>
+      <c r="N68" s="40"/>
+      <c r="O68" s="40"/>
       <c r="P68" s="8"/>
       <c r="Q68" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R68" s="40"/>
+        <v>444</v>
+      </c>
+      <c r="R68" s="41"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="32" t="n">
@@ -8751,9 +8898,9 @@
       </c>
       <c r="D69" s="24"/>
       <c r="E69" s="24" t="s">
-        <v>424</v>
-      </c>
-      <c r="F69" s="38" t="s">
+        <v>447</v>
+      </c>
+      <c r="F69" s="39" t="s">
         <v>143</v>
       </c>
       <c r="G69" s="32" t="n">
@@ -8766,22 +8913,22 @@
         <v>1</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="K69" s="39" t="s">
-        <v>426</v>
-      </c>
-      <c r="L69" s="39" t="s">
-        <v>427</v>
-      </c>
-      <c r="M69" s="39"/>
-      <c r="N69" s="39"/>
-      <c r="O69" s="39"/>
+        <v>448</v>
+      </c>
+      <c r="K69" s="40" t="s">
+        <v>449</v>
+      </c>
+      <c r="L69" s="40" t="s">
+        <v>450</v>
+      </c>
+      <c r="M69" s="40"/>
+      <c r="N69" s="40"/>
+      <c r="O69" s="40"/>
       <c r="P69" s="8"/>
       <c r="Q69" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R69" s="40"/>
+        <v>448</v>
+      </c>
+      <c r="R69" s="41"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="32" t="n">
@@ -8793,9 +8940,9 @@
       </c>
       <c r="D70" s="24"/>
       <c r="E70" s="24" t="s">
-        <v>428</v>
-      </c>
-      <c r="F70" s="38" t="s">
+        <v>451</v>
+      </c>
+      <c r="F70" s="39" t="s">
         <v>144</v>
       </c>
       <c r="G70" s="32" t="n">
@@ -8808,22 +8955,22 @@
         <v>1</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="K70" s="39" t="s">
-        <v>430</v>
-      </c>
-      <c r="L70" s="39" t="s">
-        <v>431</v>
-      </c>
-      <c r="M70" s="39"/>
-      <c r="N70" s="39"/>
-      <c r="O70" s="39"/>
+        <v>452</v>
+      </c>
+      <c r="K70" s="40" t="s">
+        <v>453</v>
+      </c>
+      <c r="L70" s="40" t="s">
+        <v>454</v>
+      </c>
+      <c r="M70" s="40"/>
+      <c r="N70" s="40"/>
+      <c r="O70" s="40"/>
       <c r="P70" s="8"/>
       <c r="Q70" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R70" s="47"/>
+        <v>452</v>
+      </c>
+      <c r="R70" s="48"/>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="32"/>
@@ -8833,9 +8980,9 @@
       </c>
       <c r="D71" s="24"/>
       <c r="E71" s="24" t="s">
-        <v>415</v>
-      </c>
-      <c r="F71" s="38" t="s">
+        <v>437</v>
+      </c>
+      <c r="F71" s="39" t="s">
         <v>145</v>
       </c>
       <c r="G71" s="32" t="n">
@@ -8846,304 +8993,304 @@
         <v>1</v>
       </c>
       <c r="J71" s="8"/>
-      <c r="K71" s="39" t="s">
-        <v>432</v>
-      </c>
-      <c r="L71" s="39"/>
-      <c r="M71" s="39"/>
-      <c r="N71" s="39"/>
-      <c r="O71" s="39"/>
+      <c r="K71" s="40" t="s">
+        <v>455</v>
+      </c>
+      <c r="L71" s="40"/>
+      <c r="M71" s="40"/>
+      <c r="N71" s="40"/>
+      <c r="O71" s="40"/>
       <c r="P71" s="8"/>
       <c r="Q71" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R71" s="47"/>
+        <v>456</v>
+      </c>
+      <c r="R71" s="48"/>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="41" t="n">
+      <c r="A72" s="42" t="n">
         <v>62</v>
       </c>
       <c r="B72" s="23"/>
-      <c r="C72" s="41"/>
+      <c r="C72" s="42"/>
       <c r="D72" s="23"/>
       <c r="E72" s="23" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="F72" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="G72" s="41" t="n">
+      <c r="G72" s="42" t="n">
         <v>43</v>
       </c>
-      <c r="H72" s="41" t="n">
+      <c r="H72" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I72" s="41" t="n">
+      <c r="I72" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J72" s="5"/>
-      <c r="K72" s="45"/>
-      <c r="L72" s="45"/>
-      <c r="M72" s="45"/>
-      <c r="N72" s="45"/>
-      <c r="O72" s="45"/>
+      <c r="K72" s="46"/>
+      <c r="L72" s="46"/>
+      <c r="M72" s="46"/>
+      <c r="N72" s="46"/>
+      <c r="O72" s="46"/>
       <c r="P72" s="5"/>
-      <c r="Q72" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R72" s="40"/>
+      <c r="Q72" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="R72" s="41"/>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="41" t="n">
+      <c r="A73" s="42" t="n">
         <v>63</v>
       </c>
       <c r="B73" s="23"/>
-      <c r="C73" s="41" t="n">
+      <c r="C73" s="42" t="n">
         <v>63</v>
       </c>
       <c r="D73" s="23"/>
       <c r="E73" s="23" t="s">
-        <v>434</v>
-      </c>
-      <c r="F73" s="46" t="s">
+        <v>459</v>
+      </c>
+      <c r="F73" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="G73" s="41" t="n">
+      <c r="G73" s="42" t="n">
         <v>62</v>
       </c>
-      <c r="H73" s="41" t="n">
+      <c r="H73" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I73" s="41" t="n">
+      <c r="I73" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="K73" s="45" t="s">
-        <v>436</v>
-      </c>
-      <c r="L73" s="45" t="s">
-        <v>437</v>
-      </c>
-      <c r="M73" s="45"/>
-      <c r="N73" s="45"/>
-      <c r="O73" s="45"/>
+        <v>460</v>
+      </c>
+      <c r="K73" s="46" t="s">
+        <v>461</v>
+      </c>
+      <c r="L73" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="M73" s="46"/>
+      <c r="N73" s="46"/>
+      <c r="O73" s="46"/>
       <c r="P73" s="5"/>
-      <c r="Q73" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R73" s="40"/>
+      <c r="Q73" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="R73" s="41"/>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="41" t="n">
+      <c r="A74" s="42" t="n">
         <v>64</v>
       </c>
       <c r="B74" s="23"/>
-      <c r="C74" s="41" t="n">
+      <c r="C74" s="42" t="n">
         <v>64</v>
       </c>
       <c r="D74" s="23"/>
       <c r="E74" s="23" t="s">
-        <v>438</v>
-      </c>
-      <c r="F74" s="46" t="s">
+        <v>463</v>
+      </c>
+      <c r="F74" s="47" t="s">
         <v>147</v>
       </c>
-      <c r="G74" s="41" t="n">
+      <c r="G74" s="42" t="n">
         <v>62</v>
       </c>
-      <c r="H74" s="41" t="n">
+      <c r="H74" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I74" s="41" t="n">
+      <c r="I74" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="K74" s="45" t="s">
-        <v>440</v>
-      </c>
-      <c r="L74" s="45" t="s">
-        <v>441</v>
-      </c>
-      <c r="M74" s="45"/>
-      <c r="N74" s="45"/>
-      <c r="O74" s="45"/>
+        <v>464</v>
+      </c>
+      <c r="K74" s="46" t="s">
+        <v>465</v>
+      </c>
+      <c r="L74" s="46" t="s">
+        <v>466</v>
+      </c>
+      <c r="M74" s="46"/>
+      <c r="N74" s="46"/>
+      <c r="O74" s="46"/>
       <c r="P74" s="5"/>
-      <c r="Q74" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R74" s="40"/>
+      <c r="Q74" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="R74" s="41"/>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="41" t="n">
+      <c r="A75" s="42" t="n">
         <v>65</v>
       </c>
       <c r="B75" s="23" t="n">
         <v>63</v>
       </c>
-      <c r="C75" s="41" t="n">
+      <c r="C75" s="42" t="n">
         <v>65</v>
       </c>
       <c r="D75" s="23" t="n">
         <v>63</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>442</v>
-      </c>
-      <c r="F75" s="46" t="s">
+        <v>467</v>
+      </c>
+      <c r="F75" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="G75" s="41" t="n">
+      <c r="G75" s="42" t="n">
         <v>62</v>
       </c>
-      <c r="H75" s="41" t="n">
+      <c r="H75" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I75" s="41" t="n">
+      <c r="I75" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="K75" s="45" t="s">
-        <v>444</v>
-      </c>
-      <c r="L75" s="45" t="s">
-        <v>445</v>
-      </c>
-      <c r="M75" s="45"/>
-      <c r="N75" s="45"/>
-      <c r="O75" s="45"/>
+        <v>468</v>
+      </c>
+      <c r="K75" s="46" t="s">
+        <v>469</v>
+      </c>
+      <c r="L75" s="46" t="s">
+        <v>470</v>
+      </c>
+      <c r="M75" s="46"/>
+      <c r="N75" s="46"/>
+      <c r="O75" s="46"/>
       <c r="P75" s="5"/>
-      <c r="Q75" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R75" s="40"/>
+      <c r="Q75" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="R75" s="41"/>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="41" t="n">
+      <c r="A76" s="42" t="n">
         <v>66</v>
       </c>
       <c r="B76" s="23"/>
-      <c r="C76" s="41" t="n">
+      <c r="C76" s="42" t="n">
         <v>66</v>
       </c>
       <c r="D76" s="23"/>
       <c r="E76" s="23" t="s">
-        <v>446</v>
-      </c>
-      <c r="F76" s="53" t="s">
-        <v>266</v>
-      </c>
-      <c r="G76" s="41" t="n">
+        <v>471</v>
+      </c>
+      <c r="F76" s="55" t="s">
+        <v>270</v>
+      </c>
+      <c r="G76" s="42" t="n">
         <v>65</v>
       </c>
-      <c r="H76" s="41" t="n">
+      <c r="H76" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I76" s="41" t="n">
+      <c r="I76" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="K76" s="45" t="s">
-        <v>448</v>
-      </c>
-      <c r="L76" s="45" t="s">
-        <v>449</v>
-      </c>
-      <c r="M76" s="45"/>
-      <c r="N76" s="45"/>
-      <c r="O76" s="45"/>
+        <v>472</v>
+      </c>
+      <c r="K76" s="46" t="s">
+        <v>473</v>
+      </c>
+      <c r="L76" s="46" t="s">
+        <v>474</v>
+      </c>
+      <c r="M76" s="46"/>
+      <c r="N76" s="46"/>
+      <c r="O76" s="46"/>
       <c r="P76" s="5"/>
-      <c r="Q76" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R76" s="40"/>
+      <c r="Q76" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="R76" s="41"/>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="41" t="n">
+      <c r="A77" s="42" t="n">
         <v>67</v>
       </c>
       <c r="B77" s="23"/>
-      <c r="C77" s="41" t="n">
+      <c r="C77" s="42" t="n">
         <v>67</v>
       </c>
       <c r="D77" s="23"/>
       <c r="E77" s="23" t="s">
-        <v>450</v>
-      </c>
-      <c r="F77" s="53" t="s">
-        <v>272</v>
-      </c>
-      <c r="G77" s="41" t="n">
+        <v>475</v>
+      </c>
+      <c r="F77" s="55" t="s">
+        <v>276</v>
+      </c>
+      <c r="G77" s="42" t="n">
         <v>65</v>
       </c>
-      <c r="H77" s="41" t="n">
+      <c r="H77" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I77" s="41" t="n">
+      <c r="I77" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="K77" s="45" t="s">
-        <v>452</v>
-      </c>
-      <c r="L77" s="45" t="s">
-        <v>453</v>
-      </c>
-      <c r="M77" s="45"/>
-      <c r="N77" s="45"/>
-      <c r="O77" s="45"/>
+        <v>476</v>
+      </c>
+      <c r="K77" s="46" t="s">
+        <v>477</v>
+      </c>
+      <c r="L77" s="46" t="s">
+        <v>478</v>
+      </c>
+      <c r="M77" s="46"/>
+      <c r="N77" s="46"/>
+      <c r="O77" s="46"/>
       <c r="P77" s="5"/>
-      <c r="Q77" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R77" s="40"/>
+      <c r="Q77" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="R77" s="41"/>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="41"/>
+      <c r="A78" s="42"/>
       <c r="B78" s="23"/>
-      <c r="C78" s="41" t="n">
+      <c r="C78" s="42" t="n">
         <v>68</v>
       </c>
       <c r="D78" s="23"/>
       <c r="E78" s="23" t="s">
-        <v>454</v>
-      </c>
-      <c r="F78" s="53" t="s">
-        <v>455</v>
-      </c>
-      <c r="G78" s="41" t="n">
+        <v>479</v>
+      </c>
+      <c r="F78" s="55" t="s">
+        <v>480</v>
+      </c>
+      <c r="G78" s="42" t="n">
         <v>65</v>
       </c>
-      <c r="H78" s="41"/>
-      <c r="I78" s="41" t="n">
+      <c r="H78" s="42"/>
+      <c r="I78" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="K78" s="45"/>
-      <c r="L78" s="45" t="s">
-        <v>457</v>
-      </c>
-      <c r="M78" s="45" t="s">
-        <v>458</v>
-      </c>
-      <c r="N78" s="45"/>
-      <c r="O78" s="45"/>
+        <v>481</v>
+      </c>
+      <c r="K78" s="46"/>
+      <c r="L78" s="46" t="s">
+        <v>482</v>
+      </c>
+      <c r="M78" s="46" t="s">
+        <v>483</v>
+      </c>
+      <c r="N78" s="46"/>
+      <c r="O78" s="46"/>
       <c r="P78" s="5"/>
-      <c r="Q78" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R78" s="47"/>
+      <c r="Q78" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="R78" s="48"/>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="32" t="n">
@@ -9153,12 +9300,12 @@
       <c r="C79" s="32"/>
       <c r="D79" s="24"/>
       <c r="E79" s="24" t="s">
-        <v>459</v>
-      </c>
-      <c r="F79" s="69" t="s">
+        <v>484</v>
+      </c>
+      <c r="F79" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="G79" s="50" t="n">
+      <c r="G79" s="51" t="n">
         <v>43</v>
       </c>
       <c r="H79" s="32" t="n">
@@ -9166,16 +9313,16 @@
       </c>
       <c r="I79" s="32"/>
       <c r="J79" s="8"/>
-      <c r="K79" s="39"/>
-      <c r="L79" s="39"/>
-      <c r="M79" s="39"/>
-      <c r="N79" s="39"/>
-      <c r="O79" s="39"/>
+      <c r="K79" s="40"/>
+      <c r="L79" s="40"/>
+      <c r="M79" s="40"/>
+      <c r="N79" s="40"/>
+      <c r="O79" s="40"/>
       <c r="P79" s="8"/>
       <c r="Q79" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R79" s="47"/>
+        <v>485</v>
+      </c>
+      <c r="R79" s="48"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="32" t="n">
@@ -9187,9 +9334,9 @@
       </c>
       <c r="D80" s="24"/>
       <c r="E80" s="24" t="s">
-        <v>460</v>
-      </c>
-      <c r="F80" s="38" t="s">
+        <v>486</v>
+      </c>
+      <c r="F80" s="39" t="s">
         <v>150</v>
       </c>
       <c r="G80" s="32" t="n">
@@ -9202,18 +9349,18 @@
         <v>1</v>
       </c>
       <c r="J80" s="8"/>
-      <c r="K80" s="39" t="s">
-        <v>461</v>
-      </c>
-      <c r="L80" s="39"/>
-      <c r="M80" s="39"/>
-      <c r="N80" s="39"/>
-      <c r="O80" s="39"/>
+      <c r="K80" s="40" t="s">
+        <v>487</v>
+      </c>
+      <c r="L80" s="40"/>
+      <c r="M80" s="40"/>
+      <c r="N80" s="40"/>
+      <c r="O80" s="40"/>
       <c r="P80" s="8"/>
       <c r="Q80" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R80" s="47"/>
+        <v>488</v>
+      </c>
+      <c r="R80" s="48"/>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="32" t="n">
@@ -9225,10 +9372,10 @@
       </c>
       <c r="D81" s="24"/>
       <c r="E81" s="24" t="s">
-        <v>462</v>
-      </c>
-      <c r="F81" s="51" t="s">
-        <v>463</v>
+        <v>489</v>
+      </c>
+      <c r="F81" s="52" t="s">
+        <v>490</v>
       </c>
       <c r="G81" s="32" t="n">
         <v>69</v>
@@ -9240,18 +9387,18 @@
         <v>1</v>
       </c>
       <c r="J81" s="8"/>
-      <c r="K81" s="39" t="s">
-        <v>464</v>
-      </c>
-      <c r="L81" s="39"/>
-      <c r="M81" s="39"/>
-      <c r="N81" s="39"/>
-      <c r="O81" s="39"/>
+      <c r="K81" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="L81" s="40"/>
+      <c r="M81" s="40"/>
+      <c r="N81" s="40"/>
+      <c r="O81" s="40"/>
       <c r="P81" s="8"/>
       <c r="Q81" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R81" s="40"/>
+        <v>492</v>
+      </c>
+      <c r="R81" s="41"/>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="32" t="n">
@@ -9263,9 +9410,9 @@
       </c>
       <c r="D82" s="24"/>
       <c r="E82" s="24" t="s">
-        <v>465</v>
-      </c>
-      <c r="F82" s="38" t="s">
+        <v>493</v>
+      </c>
+      <c r="F82" s="39" t="s">
         <v>152</v>
       </c>
       <c r="G82" s="32" t="n">
@@ -9278,315 +9425,315 @@
         <v>1</v>
       </c>
       <c r="J82" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="K82" s="39" t="s">
-        <v>467</v>
-      </c>
-      <c r="L82" s="39" t="s">
-        <v>468</v>
-      </c>
-      <c r="M82" s="39"/>
-      <c r="N82" s="39"/>
-      <c r="O82" s="39"/>
+        <v>494</v>
+      </c>
+      <c r="K82" s="40" t="s">
+        <v>495</v>
+      </c>
+      <c r="L82" s="40" t="s">
+        <v>496</v>
+      </c>
+      <c r="M82" s="40"/>
+      <c r="N82" s="40"/>
+      <c r="O82" s="40"/>
       <c r="P82" s="8"/>
       <c r="Q82" s="8" t="s">
-        <v>382</v>
+        <v>494</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="41" t="n">
+      <c r="A83" s="42" t="n">
         <v>72</v>
       </c>
       <c r="B83" s="23"/>
-      <c r="C83" s="41"/>
+      <c r="C83" s="42"/>
       <c r="D83" s="23"/>
       <c r="E83" s="23" t="s">
-        <v>469</v>
+        <v>497</v>
       </c>
       <c r="F83" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="G83" s="41" t="n">
+      <c r="G83" s="42" t="n">
         <v>43</v>
       </c>
-      <c r="H83" s="41" t="n">
+      <c r="H83" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I83" s="41"/>
+      <c r="I83" s="42"/>
       <c r="J83" s="5"/>
-      <c r="K83" s="45"/>
-      <c r="L83" s="45"/>
-      <c r="M83" s="45"/>
-      <c r="N83" s="45"/>
-      <c r="O83" s="45"/>
+      <c r="K83" s="46"/>
+      <c r="L83" s="46"/>
+      <c r="M83" s="46"/>
+      <c r="N83" s="46"/>
+      <c r="O83" s="46"/>
       <c r="P83" s="5"/>
-      <c r="Q83" s="8" t="s">
-        <v>382</v>
+      <c r="Q83" s="5" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="41" t="n">
+      <c r="A84" s="42" t="n">
         <v>73</v>
       </c>
       <c r="B84" s="23"/>
-      <c r="C84" s="41" t="n">
+      <c r="C84" s="42" t="n">
         <v>72</v>
       </c>
       <c r="D84" s="23"/>
       <c r="E84" s="23" t="s">
-        <v>470</v>
-      </c>
-      <c r="F84" s="46" t="s">
+        <v>499</v>
+      </c>
+      <c r="F84" s="47" t="s">
         <v>154</v>
       </c>
-      <c r="G84" s="41" t="n">
+      <c r="G84" s="42" t="n">
         <v>72</v>
       </c>
-      <c r="H84" s="41" t="n">
+      <c r="H84" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I84" s="41" t="n">
+      <c r="I84" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J84" s="5"/>
-      <c r="K84" s="45" t="s">
-        <v>471</v>
-      </c>
-      <c r="L84" s="45"/>
-      <c r="M84" s="45"/>
-      <c r="N84" s="45"/>
-      <c r="O84" s="45"/>
+      <c r="K84" s="46" t="s">
+        <v>500</v>
+      </c>
+      <c r="L84" s="46"/>
+      <c r="M84" s="46"/>
+      <c r="N84" s="46"/>
+      <c r="O84" s="46"/>
       <c r="P84" s="5"/>
-      <c r="Q84" s="8" t="s">
-        <v>382</v>
+      <c r="Q84" s="5" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="41" t="n">
+      <c r="A85" s="42" t="n">
         <v>74</v>
       </c>
       <c r="B85" s="23"/>
-      <c r="C85" s="41" t="n">
+      <c r="C85" s="42" t="n">
         <v>73</v>
       </c>
       <c r="D85" s="23"/>
       <c r="E85" s="23"/>
-      <c r="F85" s="46" t="s">
+      <c r="F85" s="47" t="s">
         <v>155</v>
       </c>
-      <c r="G85" s="41" t="n">
+      <c r="G85" s="42" t="n">
         <v>72</v>
       </c>
-      <c r="H85" s="41" t="n">
+      <c r="H85" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I85" s="41" t="n">
+      <c r="I85" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J85" s="5"/>
-      <c r="K85" s="70"/>
-      <c r="L85" s="45"/>
-      <c r="M85" s="45"/>
-      <c r="N85" s="45"/>
-      <c r="O85" s="45"/>
+      <c r="K85" s="72"/>
+      <c r="L85" s="46"/>
+      <c r="M85" s="46"/>
+      <c r="N85" s="46"/>
+      <c r="O85" s="46"/>
       <c r="P85" s="5"/>
-      <c r="Q85" s="8" t="s">
-        <v>382</v>
+      <c r="Q85" s="5" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="41" t="n">
+      <c r="A86" s="42" t="n">
         <v>75</v>
       </c>
       <c r="B86" s="23"/>
-      <c r="C86" s="41" t="n">
+      <c r="C86" s="42" t="n">
         <v>74</v>
       </c>
       <c r="D86" s="23"/>
       <c r="E86" s="23" t="s">
-        <v>472</v>
-      </c>
-      <c r="F86" s="46" t="s">
+        <v>503</v>
+      </c>
+      <c r="F86" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="G86" s="41" t="n">
+      <c r="G86" s="42" t="n">
         <v>72</v>
       </c>
-      <c r="H86" s="41" t="n">
+      <c r="H86" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I86" s="41" t="n">
+      <c r="I86" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J86" s="5"/>
-      <c r="K86" s="45" t="s">
-        <v>473</v>
-      </c>
-      <c r="L86" s="45"/>
-      <c r="M86" s="45"/>
-      <c r="N86" s="45"/>
-      <c r="O86" s="45"/>
+      <c r="K86" s="46" t="s">
+        <v>504</v>
+      </c>
+      <c r="L86" s="46"/>
+      <c r="M86" s="46"/>
+      <c r="N86" s="46"/>
+      <c r="O86" s="46"/>
       <c r="P86" s="5"/>
-      <c r="Q86" s="8" t="s">
-        <v>382</v>
+      <c r="Q86" s="5" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="41" t="n">
+      <c r="A87" s="42" t="n">
         <v>76</v>
       </c>
       <c r="B87" s="23" t="n">
         <v>75</v>
       </c>
-      <c r="C87" s="41" t="n">
+      <c r="C87" s="42" t="n">
         <v>75</v>
       </c>
       <c r="D87" s="23" t="n">
         <v>75</v>
       </c>
       <c r="E87" s="23" t="s">
-        <v>474</v>
-      </c>
-      <c r="F87" s="46" t="s">
+        <v>506</v>
+      </c>
+      <c r="F87" s="47" t="s">
         <v>157</v>
       </c>
-      <c r="G87" s="41" t="n">
+      <c r="G87" s="42" t="n">
         <v>72</v>
       </c>
-      <c r="H87" s="41" t="n">
+      <c r="H87" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I87" s="41" t="n">
+      <c r="I87" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J87" s="5"/>
-      <c r="K87" s="45" t="s">
-        <v>475</v>
-      </c>
-      <c r="L87" s="45"/>
-      <c r="M87" s="45"/>
-      <c r="N87" s="45"/>
-      <c r="O87" s="45"/>
+      <c r="K87" s="46" t="s">
+        <v>507</v>
+      </c>
+      <c r="L87" s="46"/>
+      <c r="M87" s="46"/>
+      <c r="N87" s="46"/>
+      <c r="O87" s="46"/>
       <c r="P87" s="5"/>
-      <c r="Q87" s="8" t="s">
-        <v>382</v>
+      <c r="Q87" s="5" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="41" t="n">
+      <c r="A88" s="42" t="n">
         <v>77</v>
       </c>
       <c r="B88" s="23" t="n">
         <v>75</v>
       </c>
-      <c r="C88" s="41"/>
+      <c r="C88" s="42"/>
       <c r="D88" s="23" t="n">
         <v>75</v>
       </c>
       <c r="E88" s="23"/>
-      <c r="F88" s="46" t="s">
-        <v>476</v>
-      </c>
-      <c r="G88" s="41" t="n">
+      <c r="F88" s="47" t="s">
+        <v>509</v>
+      </c>
+      <c r="G88" s="42" t="n">
         <v>72</v>
       </c>
-      <c r="H88" s="41" t="n">
+      <c r="H88" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I88" s="41"/>
+      <c r="I88" s="42"/>
       <c r="J88" s="5"/>
-      <c r="K88" s="45"/>
-      <c r="L88" s="45"/>
-      <c r="M88" s="45"/>
-      <c r="N88" s="45"/>
-      <c r="O88" s="45"/>
+      <c r="K88" s="46"/>
+      <c r="L88" s="46"/>
+      <c r="M88" s="46"/>
+      <c r="N88" s="46"/>
+      <c r="O88" s="46"/>
       <c r="P88" s="5"/>
-      <c r="Q88" s="8" t="s">
-        <v>382</v>
+      <c r="Q88" s="5" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="41" t="n">
+      <c r="A89" s="42" t="n">
         <v>78</v>
       </c>
       <c r="B89" s="23"/>
-      <c r="C89" s="41" t="n">
+      <c r="C89" s="42" t="n">
         <v>76</v>
       </c>
       <c r="D89" s="23"/>
       <c r="E89" s="23" t="s">
-        <v>477</v>
-      </c>
-      <c r="F89" s="53" t="s">
-        <v>478</v>
-      </c>
-      <c r="G89" s="41" t="n">
+        <v>511</v>
+      </c>
+      <c r="F89" s="55" t="s">
+        <v>512</v>
+      </c>
+      <c r="G89" s="42" t="n">
         <v>77</v>
       </c>
-      <c r="H89" s="41" t="n">
+      <c r="H89" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I89" s="41" t="n">
+      <c r="I89" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J89" s="5"/>
-      <c r="K89" s="45" t="s">
-        <v>479</v>
-      </c>
-      <c r="L89" s="45"/>
-      <c r="M89" s="45"/>
-      <c r="N89" s="45"/>
-      <c r="O89" s="45"/>
+      <c r="K89" s="46" t="s">
+        <v>513</v>
+      </c>
+      <c r="L89" s="46"/>
+      <c r="M89" s="46"/>
+      <c r="N89" s="46"/>
+      <c r="O89" s="46"/>
       <c r="P89" s="5"/>
-      <c r="Q89" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R89" s="40"/>
+      <c r="Q89" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="R89" s="41"/>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="41" t="n">
+      <c r="A90" s="42" t="n">
         <v>79</v>
       </c>
       <c r="B90" s="23"/>
-      <c r="C90" s="41" t="n">
+      <c r="C90" s="42" t="n">
         <v>77</v>
       </c>
       <c r="D90" s="23"/>
       <c r="E90" s="23" t="s">
-        <v>480</v>
-      </c>
-      <c r="F90" s="53" t="s">
-        <v>481</v>
-      </c>
-      <c r="G90" s="41" t="n">
+        <v>515</v>
+      </c>
+      <c r="F90" s="55" t="s">
+        <v>516</v>
+      </c>
+      <c r="G90" s="42" t="n">
         <v>77</v>
       </c>
-      <c r="H90" s="41" t="n">
+      <c r="H90" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I90" s="41" t="n">
+      <c r="I90" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J90" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="K90" s="45" t="s">
-        <v>483</v>
-      </c>
-      <c r="L90" s="45" t="s">
-        <v>484</v>
-      </c>
-      <c r="M90" s="45"/>
-      <c r="N90" s="45" t="s">
-        <v>485</v>
-      </c>
-      <c r="O90" s="45"/>
+        <v>517</v>
+      </c>
+      <c r="K90" s="46" t="s">
+        <v>518</v>
+      </c>
+      <c r="L90" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="M90" s="46"/>
+      <c r="N90" s="46" t="s">
+        <v>520</v>
+      </c>
+      <c r="O90" s="46"/>
       <c r="P90" s="5"/>
-      <c r="Q90" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R90" s="47"/>
+      <c r="Q90" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="R90" s="48"/>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="32" t="n">
@@ -9596,7 +9743,7 @@
       <c r="C91" s="32"/>
       <c r="D91" s="24"/>
       <c r="E91" s="24" t="s">
-        <v>486</v>
+        <v>521</v>
       </c>
       <c r="F91" s="24" t="s">
         <v>160</v>
@@ -9609,16 +9756,16 @@
       </c>
       <c r="I91" s="32"/>
       <c r="J91" s="8"/>
-      <c r="K91" s="39"/>
-      <c r="L91" s="39"/>
-      <c r="M91" s="39"/>
-      <c r="N91" s="39"/>
-      <c r="O91" s="39"/>
+      <c r="K91" s="40"/>
+      <c r="L91" s="40"/>
+      <c r="M91" s="40"/>
+      <c r="N91" s="40"/>
+      <c r="O91" s="40"/>
       <c r="P91" s="8"/>
       <c r="Q91" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R91" s="40"/>
+        <v>522</v>
+      </c>
+      <c r="R91" s="41"/>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="32" t="n">
@@ -9630,9 +9777,9 @@
       </c>
       <c r="D92" s="24"/>
       <c r="E92" s="24" t="s">
-        <v>487</v>
-      </c>
-      <c r="F92" s="38" t="s">
+        <v>523</v>
+      </c>
+      <c r="F92" s="39" t="s">
         <v>161</v>
       </c>
       <c r="G92" s="32" t="n">
@@ -9645,22 +9792,22 @@
         <v>1</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="K92" s="39" t="s">
-        <v>489</v>
-      </c>
-      <c r="L92" s="39" t="s">
-        <v>490</v>
-      </c>
-      <c r="M92" s="39"/>
-      <c r="N92" s="39"/>
-      <c r="O92" s="39"/>
+        <v>524</v>
+      </c>
+      <c r="K92" s="40" t="s">
+        <v>525</v>
+      </c>
+      <c r="L92" s="40" t="s">
+        <v>526</v>
+      </c>
+      <c r="M92" s="40"/>
+      <c r="N92" s="40"/>
+      <c r="O92" s="40"/>
       <c r="P92" s="8"/>
       <c r="Q92" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R92" s="40"/>
+        <v>524</v>
+      </c>
+      <c r="R92" s="41"/>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="32" t="n">
@@ -9672,9 +9819,9 @@
       </c>
       <c r="D93" s="24"/>
       <c r="E93" s="24" t="s">
-        <v>491</v>
-      </c>
-      <c r="F93" s="38" t="s">
+        <v>527</v>
+      </c>
+      <c r="F93" s="39" t="s">
         <v>162</v>
       </c>
       <c r="G93" s="32" t="n">
@@ -9687,22 +9834,22 @@
         <v>1</v>
       </c>
       <c r="J93" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="K93" s="39" t="s">
-        <v>493</v>
-      </c>
-      <c r="L93" s="39" t="s">
-        <v>494</v>
-      </c>
-      <c r="M93" s="39"/>
-      <c r="N93" s="39"/>
-      <c r="O93" s="39"/>
+        <v>528</v>
+      </c>
+      <c r="K93" s="40" t="s">
+        <v>529</v>
+      </c>
+      <c r="L93" s="40" t="s">
+        <v>530</v>
+      </c>
+      <c r="M93" s="40"/>
+      <c r="N93" s="40"/>
+      <c r="O93" s="40"/>
       <c r="P93" s="8"/>
       <c r="Q93" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R93" s="40"/>
+        <v>528</v>
+      </c>
+      <c r="R93" s="41"/>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="32" t="n">
@@ -9714,9 +9861,9 @@
       </c>
       <c r="D94" s="24"/>
       <c r="E94" s="24" t="s">
-        <v>495</v>
-      </c>
-      <c r="F94" s="38" t="s">
+        <v>531</v>
+      </c>
+      <c r="F94" s="39" t="s">
         <v>163</v>
       </c>
       <c r="G94" s="32" t="n">
@@ -9729,22 +9876,22 @@
         <v>1</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="K94" s="39" t="s">
-        <v>497</v>
-      </c>
-      <c r="L94" s="39" t="s">
-        <v>498</v>
-      </c>
-      <c r="M94" s="39"/>
-      <c r="N94" s="39"/>
-      <c r="O94" s="39"/>
+        <v>532</v>
+      </c>
+      <c r="K94" s="40" t="s">
+        <v>533</v>
+      </c>
+      <c r="L94" s="40" t="s">
+        <v>534</v>
+      </c>
+      <c r="M94" s="40"/>
+      <c r="N94" s="40"/>
+      <c r="O94" s="40"/>
       <c r="P94" s="8"/>
       <c r="Q94" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R94" s="40"/>
+        <v>532</v>
+      </c>
+      <c r="R94" s="41"/>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="32" t="n">
@@ -9756,9 +9903,9 @@
       </c>
       <c r="D95" s="24"/>
       <c r="E95" s="24" t="s">
-        <v>499</v>
-      </c>
-      <c r="F95" s="38" t="s">
+        <v>535</v>
+      </c>
+      <c r="F95" s="39" t="s">
         <v>121</v>
       </c>
       <c r="G95" s="32" t="n">
@@ -9771,418 +9918,418 @@
         <v>1</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="K95" s="39" t="s">
-        <v>501</v>
-      </c>
-      <c r="L95" s="39" t="s">
-        <v>502</v>
-      </c>
-      <c r="M95" s="39"/>
-      <c r="N95" s="39"/>
-      <c r="O95" s="39"/>
+        <v>536</v>
+      </c>
+      <c r="K95" s="40" t="s">
+        <v>537</v>
+      </c>
+      <c r="L95" s="40" t="s">
+        <v>538</v>
+      </c>
+      <c r="M95" s="40"/>
+      <c r="N95" s="40"/>
+      <c r="O95" s="40"/>
       <c r="P95" s="8"/>
       <c r="Q95" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R95" s="47"/>
+        <v>536</v>
+      </c>
+      <c r="R95" s="48"/>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="41" t="n">
+      <c r="A96" s="42" t="n">
         <v>85</v>
       </c>
       <c r="B96" s="23"/>
-      <c r="C96" s="41"/>
+      <c r="C96" s="42"/>
       <c r="D96" s="23"/>
       <c r="E96" s="23"/>
       <c r="F96" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="G96" s="41" t="n">
+      <c r="G96" s="42" t="n">
         <v>43</v>
       </c>
-      <c r="H96" s="41" t="n">
+      <c r="H96" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I96" s="41"/>
+      <c r="I96" s="42"/>
       <c r="J96" s="5"/>
-      <c r="K96" s="45"/>
-      <c r="L96" s="45"/>
-      <c r="M96" s="45"/>
-      <c r="N96" s="45"/>
-      <c r="O96" s="45"/>
+      <c r="K96" s="46"/>
+      <c r="L96" s="46"/>
+      <c r="M96" s="46"/>
+      <c r="N96" s="46"/>
+      <c r="O96" s="46"/>
       <c r="P96" s="5"/>
-      <c r="Q96" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R96" s="40"/>
+      <c r="Q96" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="R96" s="41"/>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="41"/>
+      <c r="A97" s="42"/>
       <c r="B97" s="23"/>
-      <c r="C97" s="41" t="n">
+      <c r="C97" s="42" t="n">
         <v>82</v>
       </c>
       <c r="D97" s="23"/>
       <c r="E97" s="23" t="s">
-        <v>503</v>
-      </c>
-      <c r="F97" s="46" t="s">
+        <v>540</v>
+      </c>
+      <c r="F97" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="G97" s="41" t="n">
+      <c r="G97" s="42" t="n">
         <v>85</v>
       </c>
-      <c r="H97" s="41"/>
-      <c r="I97" s="41" t="n">
+      <c r="H97" s="42"/>
+      <c r="I97" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J97" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="K97" s="45" t="s">
-        <v>505</v>
-      </c>
-      <c r="L97" s="45" t="s">
-        <v>506</v>
-      </c>
-      <c r="M97" s="45"/>
-      <c r="N97" s="45"/>
-      <c r="O97" s="45"/>
+        <v>541</v>
+      </c>
+      <c r="K97" s="46" t="s">
+        <v>542</v>
+      </c>
+      <c r="L97" s="46" t="s">
+        <v>543</v>
+      </c>
+      <c r="M97" s="46"/>
+      <c r="N97" s="46"/>
+      <c r="O97" s="46"/>
       <c r="P97" s="5"/>
-      <c r="Q97" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R97" s="47"/>
+      <c r="Q97" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="R97" s="48"/>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="41"/>
+      <c r="A98" s="42"/>
       <c r="B98" s="23"/>
-      <c r="C98" s="41" t="n">
+      <c r="C98" s="42" t="n">
         <v>83</v>
       </c>
       <c r="D98" s="23"/>
       <c r="E98" s="23" t="s">
-        <v>503</v>
-      </c>
-      <c r="F98" s="46" t="s">
+        <v>540</v>
+      </c>
+      <c r="F98" s="47" t="s">
         <v>165</v>
       </c>
-      <c r="G98" s="41" t="n">
+      <c r="G98" s="42" t="n">
         <v>85</v>
       </c>
-      <c r="H98" s="41"/>
-      <c r="I98" s="41" t="n">
+      <c r="H98" s="42"/>
+      <c r="I98" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J98" s="5"/>
-      <c r="K98" s="45" t="s">
-        <v>507</v>
-      </c>
-      <c r="L98" s="45"/>
-      <c r="M98" s="45"/>
-      <c r="N98" s="45"/>
-      <c r="O98" s="45"/>
+      <c r="K98" s="46" t="s">
+        <v>544</v>
+      </c>
+      <c r="L98" s="46"/>
+      <c r="M98" s="46"/>
+      <c r="N98" s="46"/>
+      <c r="O98" s="46"/>
       <c r="P98" s="5"/>
-      <c r="Q98" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R98" s="40"/>
+      <c r="Q98" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="R98" s="41"/>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="41" t="n">
+      <c r="A99" s="42" t="n">
         <v>86</v>
       </c>
       <c r="B99" s="23"/>
-      <c r="C99" s="41" t="n">
+      <c r="C99" s="42" t="n">
         <v>84</v>
       </c>
       <c r="D99" s="23"/>
       <c r="E99" s="23" t="s">
-        <v>508</v>
-      </c>
-      <c r="F99" s="46" t="s">
+        <v>546</v>
+      </c>
+      <c r="F99" s="47" t="s">
         <v>155</v>
       </c>
-      <c r="G99" s="41" t="n">
+      <c r="G99" s="42" t="n">
         <v>85</v>
       </c>
-      <c r="H99" s="41" t="n">
+      <c r="H99" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I99" s="41" t="n">
+      <c r="I99" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="K99" s="45" t="s">
-        <v>510</v>
-      </c>
-      <c r="L99" s="45" t="s">
-        <v>511</v>
-      </c>
-      <c r="M99" s="45"/>
-      <c r="N99" s="45"/>
-      <c r="O99" s="45"/>
+        <v>547</v>
+      </c>
+      <c r="K99" s="46" t="s">
+        <v>548</v>
+      </c>
+      <c r="L99" s="46" t="s">
+        <v>549</v>
+      </c>
+      <c r="M99" s="46"/>
+      <c r="N99" s="46"/>
+      <c r="O99" s="46"/>
       <c r="P99" s="5"/>
-      <c r="Q99" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R99" s="40"/>
+      <c r="Q99" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="R99" s="41"/>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="41" t="n">
+      <c r="A100" s="42" t="n">
         <v>87</v>
       </c>
       <c r="B100" s="23"/>
-      <c r="C100" s="41" t="n">
+      <c r="C100" s="42" t="n">
         <v>85</v>
       </c>
       <c r="D100" s="23"/>
       <c r="E100" s="23" t="s">
-        <v>512</v>
-      </c>
-      <c r="F100" s="46" t="s">
+        <v>550</v>
+      </c>
+      <c r="F100" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="G100" s="41" t="n">
+      <c r="G100" s="42" t="n">
         <v>85</v>
       </c>
-      <c r="H100" s="41" t="n">
+      <c r="H100" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I100" s="41" t="n">
+      <c r="I100" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="K100" s="45" t="s">
-        <v>514</v>
-      </c>
-      <c r="L100" s="45" t="s">
-        <v>515</v>
-      </c>
-      <c r="M100" s="45"/>
-      <c r="N100" s="45"/>
-      <c r="O100" s="45"/>
+        <v>551</v>
+      </c>
+      <c r="K100" s="46" t="s">
+        <v>552</v>
+      </c>
+      <c r="L100" s="46" t="s">
+        <v>553</v>
+      </c>
+      <c r="M100" s="46"/>
+      <c r="N100" s="46"/>
+      <c r="O100" s="46"/>
       <c r="P100" s="5"/>
-      <c r="Q100" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R100" s="40"/>
+      <c r="Q100" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="R100" s="41"/>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="41" t="n">
+      <c r="A101" s="42" t="n">
         <v>88</v>
       </c>
       <c r="B101" s="23"/>
-      <c r="C101" s="41" t="n">
+      <c r="C101" s="42" t="n">
         <v>86</v>
       </c>
       <c r="D101" s="23"/>
       <c r="E101" s="23" t="s">
-        <v>516</v>
-      </c>
-      <c r="F101" s="46" t="s">
+        <v>554</v>
+      </c>
+      <c r="F101" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="G101" s="41" t="n">
+      <c r="G101" s="42" t="n">
         <v>85</v>
       </c>
-      <c r="H101" s="41" t="n">
+      <c r="H101" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I101" s="41" t="n">
+      <c r="I101" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="K101" s="45" t="s">
-        <v>518</v>
-      </c>
-      <c r="L101" s="45" t="s">
-        <v>519</v>
-      </c>
-      <c r="M101" s="45"/>
-      <c r="N101" s="45"/>
-      <c r="O101" s="45"/>
+        <v>555</v>
+      </c>
+      <c r="K101" s="46" t="s">
+        <v>556</v>
+      </c>
+      <c r="L101" s="46" t="s">
+        <v>557</v>
+      </c>
+      <c r="M101" s="46"/>
+      <c r="N101" s="46"/>
+      <c r="O101" s="46"/>
       <c r="P101" s="5"/>
-      <c r="Q101" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R101" s="40"/>
+      <c r="Q101" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="R101" s="41"/>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="41" t="n">
+      <c r="A102" s="42" t="n">
         <v>89</v>
       </c>
       <c r="B102" s="23"/>
-      <c r="C102" s="41" t="n">
+      <c r="C102" s="42" t="n">
         <v>87</v>
       </c>
       <c r="D102" s="23"/>
       <c r="E102" s="23" t="s">
-        <v>520</v>
-      </c>
-      <c r="F102" s="46" t="s">
+        <v>558</v>
+      </c>
+      <c r="F102" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="G102" s="41" t="n">
+      <c r="G102" s="42" t="n">
         <v>85</v>
       </c>
-      <c r="H102" s="41" t="n">
+      <c r="H102" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I102" s="41" t="n">
+      <c r="I102" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="K102" s="45" t="s">
-        <v>522</v>
-      </c>
-      <c r="L102" s="45" t="s">
-        <v>523</v>
-      </c>
-      <c r="M102" s="45"/>
-      <c r="N102" s="45"/>
-      <c r="O102" s="45"/>
+        <v>559</v>
+      </c>
+      <c r="K102" s="46" t="s">
+        <v>560</v>
+      </c>
+      <c r="L102" s="46" t="s">
+        <v>561</v>
+      </c>
+      <c r="M102" s="46"/>
+      <c r="N102" s="46"/>
+      <c r="O102" s="46"/>
       <c r="P102" s="5"/>
-      <c r="Q102" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R102" s="40"/>
+      <c r="Q102" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="R102" s="41"/>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="41" t="n">
+      <c r="A103" s="42" t="n">
         <v>90</v>
       </c>
       <c r="B103" s="23"/>
-      <c r="C103" s="41" t="n">
+      <c r="C103" s="42" t="n">
         <v>88</v>
       </c>
       <c r="D103" s="23"/>
       <c r="E103" s="23" t="s">
-        <v>524</v>
-      </c>
-      <c r="F103" s="46" t="s">
+        <v>562</v>
+      </c>
+      <c r="F103" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="G103" s="41" t="n">
+      <c r="G103" s="42" t="n">
         <v>85</v>
       </c>
-      <c r="H103" s="41" t="n">
+      <c r="H103" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I103" s="41" t="n">
+      <c r="I103" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="K103" s="45" t="s">
-        <v>526</v>
-      </c>
-      <c r="L103" s="45" t="s">
-        <v>527</v>
-      </c>
-      <c r="M103" s="45"/>
-      <c r="N103" s="45"/>
-      <c r="O103" s="45"/>
+        <v>563</v>
+      </c>
+      <c r="K103" s="46" t="s">
+        <v>564</v>
+      </c>
+      <c r="L103" s="46" t="s">
+        <v>565</v>
+      </c>
+      <c r="M103" s="46"/>
+      <c r="N103" s="46"/>
+      <c r="O103" s="46"/>
       <c r="P103" s="5"/>
-      <c r="Q103" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R103" s="40"/>
+      <c r="Q103" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="R103" s="41"/>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="41" t="n">
+      <c r="A104" s="42" t="n">
         <v>91</v>
       </c>
       <c r="B104" s="23"/>
-      <c r="C104" s="41" t="n">
+      <c r="C104" s="42" t="n">
         <v>89</v>
       </c>
       <c r="D104" s="23"/>
       <c r="E104" s="23" t="s">
-        <v>528</v>
-      </c>
-      <c r="F104" s="53" t="s">
-        <v>529</v>
-      </c>
-      <c r="G104" s="41" t="n">
+        <v>566</v>
+      </c>
+      <c r="F104" s="55" t="s">
+        <v>567</v>
+      </c>
+      <c r="G104" s="42" t="n">
         <v>90</v>
       </c>
-      <c r="H104" s="41" t="n">
+      <c r="H104" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I104" s="41" t="n">
+      <c r="I104" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="K104" s="45" t="s">
-        <v>531</v>
-      </c>
-      <c r="L104" s="45" t="s">
-        <v>532</v>
-      </c>
-      <c r="M104" s="45"/>
-      <c r="N104" s="45"/>
-      <c r="O104" s="45"/>
+        <v>568</v>
+      </c>
+      <c r="K104" s="46" t="s">
+        <v>569</v>
+      </c>
+      <c r="L104" s="46" t="s">
+        <v>570</v>
+      </c>
+      <c r="M104" s="46"/>
+      <c r="N104" s="46"/>
+      <c r="O104" s="46"/>
       <c r="P104" s="5"/>
-      <c r="Q104" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R104" s="40"/>
+      <c r="Q104" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="R104" s="41"/>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="41" t="n">
+      <c r="A105" s="42" t="n">
         <v>92</v>
       </c>
       <c r="B105" s="23"/>
-      <c r="C105" s="41" t="n">
+      <c r="C105" s="42" t="n">
         <v>90</v>
       </c>
       <c r="D105" s="23"/>
       <c r="E105" s="23" t="s">
-        <v>533</v>
-      </c>
-      <c r="F105" s="46" t="s">
+        <v>571</v>
+      </c>
+      <c r="F105" s="47" t="s">
         <v>170</v>
       </c>
-      <c r="G105" s="41" t="n">
+      <c r="G105" s="42" t="n">
         <v>85</v>
       </c>
-      <c r="H105" s="41" t="n">
+      <c r="H105" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I105" s="41" t="n">
+      <c r="I105" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="K105" s="45" t="s">
-        <v>535</v>
-      </c>
-      <c r="L105" s="45" t="s">
-        <v>536</v>
-      </c>
-      <c r="M105" s="45"/>
-      <c r="N105" s="45"/>
-      <c r="O105" s="45"/>
+        <v>572</v>
+      </c>
+      <c r="K105" s="46" t="s">
+        <v>573</v>
+      </c>
+      <c r="L105" s="46" t="s">
+        <v>574</v>
+      </c>
+      <c r="M105" s="46"/>
+      <c r="N105" s="46"/>
+      <c r="O105" s="46"/>
       <c r="P105" s="5"/>
-      <c r="Q105" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R105" s="47"/>
+      <c r="Q105" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="R105" s="48"/>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="32" t="n">
@@ -10203,16 +10350,16 @@
       </c>
       <c r="I106" s="32"/>
       <c r="J106" s="8"/>
-      <c r="K106" s="39"/>
-      <c r="L106" s="39"/>
-      <c r="M106" s="39"/>
-      <c r="N106" s="39"/>
-      <c r="O106" s="39"/>
+      <c r="K106" s="40"/>
+      <c r="L106" s="40"/>
+      <c r="M106" s="40"/>
+      <c r="N106" s="40"/>
+      <c r="O106" s="40"/>
       <c r="P106" s="8"/>
       <c r="Q106" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R106" s="40"/>
+        <v>575</v>
+      </c>
+      <c r="R106" s="41"/>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="32" t="n">
@@ -10224,9 +10371,9 @@
       </c>
       <c r="D107" s="24"/>
       <c r="E107" s="24" t="s">
-        <v>537</v>
-      </c>
-      <c r="F107" s="38" t="s">
+        <v>576</v>
+      </c>
+      <c r="F107" s="39" t="s">
         <v>172</v>
       </c>
       <c r="G107" s="32" t="n">
@@ -10239,22 +10386,22 @@
         <v>1</v>
       </c>
       <c r="J107" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="K107" s="39" t="s">
-        <v>539</v>
-      </c>
-      <c r="L107" s="39" t="s">
-        <v>540</v>
-      </c>
-      <c r="M107" s="39"/>
-      <c r="N107" s="39"/>
-      <c r="O107" s="39"/>
+        <v>577</v>
+      </c>
+      <c r="K107" s="40" t="s">
+        <v>578</v>
+      </c>
+      <c r="L107" s="40" t="s">
+        <v>579</v>
+      </c>
+      <c r="M107" s="40"/>
+      <c r="N107" s="40"/>
+      <c r="O107" s="40"/>
       <c r="P107" s="8"/>
       <c r="Q107" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R107" s="40"/>
+        <v>577</v>
+      </c>
+      <c r="R107" s="41"/>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="32" t="n">
@@ -10266,9 +10413,9 @@
       </c>
       <c r="D108" s="24"/>
       <c r="E108" s="24" t="s">
-        <v>541</v>
-      </c>
-      <c r="F108" s="38" t="s">
+        <v>580</v>
+      </c>
+      <c r="F108" s="39" t="s">
         <v>173</v>
       </c>
       <c r="G108" s="32" t="n">
@@ -10281,22 +10428,22 @@
         <v>1</v>
       </c>
       <c r="J108" s="8" t="s">
-        <v>542</v>
-      </c>
-      <c r="K108" s="39" t="s">
-        <v>543</v>
-      </c>
-      <c r="L108" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="M108" s="39"/>
-      <c r="N108" s="39"/>
-      <c r="O108" s="39"/>
+        <v>581</v>
+      </c>
+      <c r="K108" s="40" t="s">
+        <v>582</v>
+      </c>
+      <c r="L108" s="40" t="s">
+        <v>583</v>
+      </c>
+      <c r="M108" s="40"/>
+      <c r="N108" s="40"/>
+      <c r="O108" s="40"/>
       <c r="P108" s="8"/>
       <c r="Q108" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R108" s="40"/>
+        <v>581</v>
+      </c>
+      <c r="R108" s="41"/>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="32" t="n">
@@ -10308,9 +10455,9 @@
       </c>
       <c r="D109" s="24"/>
       <c r="E109" s="24" t="s">
-        <v>545</v>
-      </c>
-      <c r="F109" s="38" t="s">
+        <v>584</v>
+      </c>
+      <c r="F109" s="39" t="s">
         <v>174</v>
       </c>
       <c r="G109" s="32" t="n">
@@ -10323,24 +10470,24 @@
         <v>1</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>546</v>
-      </c>
-      <c r="K109" s="39" t="s">
-        <v>547</v>
-      </c>
-      <c r="L109" s="39" t="s">
-        <v>548</v>
-      </c>
-      <c r="M109" s="39"/>
-      <c r="N109" s="39" t="s">
-        <v>549</v>
-      </c>
-      <c r="O109" s="39"/>
+        <v>585</v>
+      </c>
+      <c r="K109" s="40" t="s">
+        <v>586</v>
+      </c>
+      <c r="L109" s="40" t="s">
+        <v>587</v>
+      </c>
+      <c r="M109" s="40"/>
+      <c r="N109" s="40" t="s">
+        <v>588</v>
+      </c>
+      <c r="O109" s="40"/>
       <c r="P109" s="8"/>
       <c r="Q109" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R109" s="40"/>
+        <v>585</v>
+      </c>
+      <c r="R109" s="41"/>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="32" t="n">
@@ -10352,9 +10499,9 @@
       </c>
       <c r="D110" s="24"/>
       <c r="E110" s="24" t="s">
-        <v>550</v>
-      </c>
-      <c r="F110" s="38" t="s">
+        <v>589</v>
+      </c>
+      <c r="F110" s="39" t="s">
         <v>171</v>
       </c>
       <c r="G110" s="32" t="n">
@@ -10367,106 +10514,106 @@
         <v>1</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>551</v>
-      </c>
-      <c r="K110" s="39" t="s">
-        <v>552</v>
-      </c>
-      <c r="L110" s="39" t="s">
-        <v>553</v>
-      </c>
-      <c r="M110" s="39"/>
-      <c r="N110" s="39" t="s">
-        <v>554</v>
-      </c>
-      <c r="O110" s="39"/>
+        <v>590</v>
+      </c>
+      <c r="K110" s="40" t="s">
+        <v>591</v>
+      </c>
+      <c r="L110" s="40" t="s">
+        <v>592</v>
+      </c>
+      <c r="M110" s="40"/>
+      <c r="N110" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="O110" s="40"/>
       <c r="P110" s="8"/>
       <c r="Q110" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R110" s="40"/>
+        <v>590</v>
+      </c>
+      <c r="R110" s="41"/>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="41" t="n">
+      <c r="A111" s="42" t="n">
         <v>98</v>
       </c>
       <c r="B111" s="23"/>
-      <c r="C111" s="41" t="n">
+      <c r="C111" s="42" t="n">
         <v>95</v>
       </c>
       <c r="D111" s="23"/>
       <c r="E111" s="23" t="s">
-        <v>555</v>
+        <v>594</v>
       </c>
       <c r="F111" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="G111" s="41" t="n">
+      <c r="G111" s="42" t="n">
         <v>43</v>
       </c>
-      <c r="H111" s="41" t="n">
+      <c r="H111" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I111" s="41" t="n">
+      <c r="I111" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J111" s="5" t="s">
-        <v>556</v>
-      </c>
-      <c r="K111" s="45" t="s">
-        <v>557</v>
-      </c>
-      <c r="L111" s="45" t="s">
-        <v>558</v>
-      </c>
-      <c r="M111" s="45"/>
-      <c r="N111" s="45"/>
-      <c r="O111" s="45"/>
+        <v>595</v>
+      </c>
+      <c r="K111" s="46" t="s">
+        <v>596</v>
+      </c>
+      <c r="L111" s="46" t="s">
+        <v>597</v>
+      </c>
+      <c r="M111" s="46"/>
+      <c r="N111" s="46"/>
+      <c r="O111" s="46"/>
       <c r="P111" s="5"/>
-      <c r="Q111" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R111" s="40"/>
+      <c r="Q111" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="R111" s="41"/>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="41" t="n">
+      <c r="A112" s="42" t="n">
         <v>99</v>
       </c>
       <c r="B112" s="23"/>
-      <c r="C112" s="41" t="n">
+      <c r="C112" s="42" t="n">
         <v>96</v>
       </c>
       <c r="D112" s="23"/>
       <c r="E112" s="23" t="s">
-        <v>559</v>
-      </c>
-      <c r="F112" s="46" t="s">
+        <v>598</v>
+      </c>
+      <c r="F112" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="G112" s="41" t="n">
+      <c r="G112" s="42" t="n">
         <v>98</v>
       </c>
-      <c r="H112" s="41" t="n">
+      <c r="H112" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I112" s="41" t="n">
+      <c r="I112" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>560</v>
-      </c>
-      <c r="K112" s="45" t="s">
-        <v>561</v>
-      </c>
-      <c r="L112" s="45" t="s">
-        <v>562</v>
-      </c>
-      <c r="M112" s="45"/>
-      <c r="N112" s="45"/>
-      <c r="O112" s="45"/>
+        <v>599</v>
+      </c>
+      <c r="K112" s="46" t="s">
+        <v>600</v>
+      </c>
+      <c r="L112" s="46" t="s">
+        <v>601</v>
+      </c>
+      <c r="M112" s="46"/>
+      <c r="N112" s="46"/>
+      <c r="O112" s="46"/>
       <c r="P112" s="5"/>
-      <c r="Q112" s="8" t="s">
-        <v>382</v>
+      <c r="Q112" s="5" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10488,16 +10635,16 @@
       </c>
       <c r="I113" s="32"/>
       <c r="J113" s="8"/>
-      <c r="K113" s="39"/>
-      <c r="L113" s="39"/>
-      <c r="M113" s="39"/>
-      <c r="N113" s="39"/>
-      <c r="O113" s="39"/>
+      <c r="K113" s="40"/>
+      <c r="L113" s="40"/>
+      <c r="M113" s="40"/>
+      <c r="N113" s="40"/>
+      <c r="O113" s="40"/>
       <c r="P113" s="8"/>
       <c r="Q113" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R113" s="40"/>
+        <v>602</v>
+      </c>
+      <c r="R113" s="41"/>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="32" t="n">
@@ -10509,9 +10656,9 @@
       </c>
       <c r="D114" s="24"/>
       <c r="E114" s="24" t="s">
-        <v>563</v>
-      </c>
-      <c r="F114" s="38" t="s">
+        <v>603</v>
+      </c>
+      <c r="F114" s="39" t="s">
         <v>178</v>
       </c>
       <c r="G114" s="32" t="n">
@@ -10524,22 +10671,22 @@
         <v>1</v>
       </c>
       <c r="J114" s="8" t="s">
-        <v>564</v>
-      </c>
-      <c r="K114" s="39" t="s">
-        <v>565</v>
-      </c>
-      <c r="L114" s="39" t="s">
-        <v>566</v>
-      </c>
-      <c r="M114" s="39"/>
-      <c r="N114" s="39"/>
-      <c r="O114" s="39"/>
+        <v>604</v>
+      </c>
+      <c r="K114" s="40" t="s">
+        <v>605</v>
+      </c>
+      <c r="L114" s="40" t="s">
+        <v>606</v>
+      </c>
+      <c r="M114" s="40"/>
+      <c r="N114" s="40"/>
+      <c r="O114" s="40"/>
       <c r="P114" s="8"/>
       <c r="Q114" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R114" s="40"/>
+        <v>604</v>
+      </c>
+      <c r="R114" s="41"/>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="32" t="n">
@@ -10551,9 +10698,9 @@
       </c>
       <c r="D115" s="24"/>
       <c r="E115" s="24" t="s">
-        <v>567</v>
-      </c>
-      <c r="F115" s="38" t="s">
+        <v>607</v>
+      </c>
+      <c r="F115" s="39" t="s">
         <v>179</v>
       </c>
       <c r="G115" s="32" t="n">
@@ -10566,22 +10713,22 @@
         <v>1</v>
       </c>
       <c r="J115" s="8" t="s">
-        <v>568</v>
-      </c>
-      <c r="K115" s="39" t="s">
-        <v>569</v>
-      </c>
-      <c r="L115" s="39" t="s">
-        <v>570</v>
-      </c>
-      <c r="M115" s="39"/>
-      <c r="N115" s="39"/>
-      <c r="O115" s="39"/>
+        <v>608</v>
+      </c>
+      <c r="K115" s="40" t="s">
+        <v>609</v>
+      </c>
+      <c r="L115" s="40" t="s">
+        <v>610</v>
+      </c>
+      <c r="M115" s="40"/>
+      <c r="N115" s="40"/>
+      <c r="O115" s="40"/>
       <c r="P115" s="8"/>
       <c r="Q115" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R115" s="40"/>
+        <v>608</v>
+      </c>
+      <c r="R115" s="41"/>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="32"/>
@@ -10591,7 +10738,7 @@
       </c>
       <c r="D116" s="24"/>
       <c r="E116" s="24" t="s">
-        <v>567</v>
+        <v>607</v>
       </c>
       <c r="F116" s="24"/>
       <c r="G116" s="32"/>
@@ -10600,29 +10747,29 @@
         <v>1</v>
       </c>
       <c r="J116" s="8" t="s">
-        <v>571</v>
-      </c>
-      <c r="K116" s="39"/>
-      <c r="L116" s="39" t="s">
-        <v>572</v>
-      </c>
-      <c r="M116" s="39"/>
-      <c r="N116" s="39" t="s">
-        <v>573</v>
-      </c>
-      <c r="O116" s="39"/>
+        <v>611</v>
+      </c>
+      <c r="K116" s="40"/>
+      <c r="L116" s="40" t="s">
+        <v>612</v>
+      </c>
+      <c r="M116" s="40"/>
+      <c r="N116" s="40" t="s">
+        <v>613</v>
+      </c>
+      <c r="O116" s="40"/>
       <c r="P116" s="8"/>
       <c r="Q116" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R116" s="47"/>
+        <v>611</v>
+      </c>
+      <c r="R116" s="48"/>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="41" t="n">
+      <c r="A117" s="42" t="n">
         <v>103</v>
       </c>
       <c r="B117" s="23"/>
-      <c r="C117" s="41"/>
+      <c r="C117" s="42"/>
       <c r="D117" s="23"/>
       <c r="E117" s="23" t="n">
         <v>43</v>
@@ -10630,152 +10777,152 @@
       <c r="F117" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="G117" s="41" t="n">
+      <c r="G117" s="42" t="n">
         <v>43</v>
       </c>
-      <c r="H117" s="41" t="n">
+      <c r="H117" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I117" s="41"/>
+      <c r="I117" s="42"/>
       <c r="J117" s="5"/>
-      <c r="K117" s="45"/>
-      <c r="L117" s="45"/>
-      <c r="M117" s="45"/>
-      <c r="N117" s="45"/>
-      <c r="O117" s="45"/>
+      <c r="K117" s="46"/>
+      <c r="L117" s="46"/>
+      <c r="M117" s="46"/>
+      <c r="N117" s="46"/>
+      <c r="O117" s="46"/>
       <c r="P117" s="5"/>
-      <c r="Q117" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R117" s="40"/>
+      <c r="Q117" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="R117" s="41"/>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="41" t="n">
+      <c r="A118" s="42" t="n">
         <v>104</v>
       </c>
       <c r="B118" s="23"/>
-      <c r="C118" s="41" t="n">
+      <c r="C118" s="42" t="n">
         <v>100</v>
       </c>
       <c r="D118" s="23"/>
       <c r="E118" s="23" t="s">
-        <v>574</v>
-      </c>
-      <c r="F118" s="46" t="s">
+        <v>615</v>
+      </c>
+      <c r="F118" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="G118" s="41" t="n">
+      <c r="G118" s="42" t="n">
         <v>103</v>
       </c>
-      <c r="H118" s="41" t="n">
+      <c r="H118" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I118" s="41" t="n">
+      <c r="I118" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J118" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="K118" s="45" t="s">
-        <v>576</v>
-      </c>
-      <c r="L118" s="45" t="s">
-        <v>577</v>
-      </c>
-      <c r="M118" s="45"/>
-      <c r="N118" s="45"/>
-      <c r="O118" s="45"/>
+        <v>616</v>
+      </c>
+      <c r="K118" s="46" t="s">
+        <v>617</v>
+      </c>
+      <c r="L118" s="46" t="s">
+        <v>618</v>
+      </c>
+      <c r="M118" s="46"/>
+      <c r="N118" s="46"/>
+      <c r="O118" s="46"/>
       <c r="P118" s="5"/>
-      <c r="Q118" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R118" s="40"/>
+      <c r="Q118" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="R118" s="41"/>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="41" t="n">
+      <c r="A119" s="42" t="n">
         <v>105</v>
       </c>
       <c r="B119" s="23"/>
-      <c r="C119" s="41" t="n">
+      <c r="C119" s="42" t="n">
         <v>101</v>
       </c>
       <c r="D119" s="23"/>
       <c r="E119" s="23" t="s">
-        <v>578</v>
-      </c>
-      <c r="F119" s="46" t="s">
+        <v>619</v>
+      </c>
+      <c r="F119" s="47" t="s">
         <v>182</v>
       </c>
-      <c r="G119" s="41" t="n">
+      <c r="G119" s="42" t="n">
         <v>103</v>
       </c>
-      <c r="H119" s="41" t="n">
+      <c r="H119" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I119" s="41" t="n">
+      <c r="I119" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J119" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="K119" s="45" t="s">
-        <v>580</v>
-      </c>
-      <c r="L119" s="45" t="s">
-        <v>581</v>
-      </c>
-      <c r="M119" s="45"/>
-      <c r="N119" s="45" t="s">
-        <v>582</v>
-      </c>
-      <c r="O119" s="45"/>
+        <v>620</v>
+      </c>
+      <c r="K119" s="46" t="s">
+        <v>621</v>
+      </c>
+      <c r="L119" s="46" t="s">
+        <v>622</v>
+      </c>
+      <c r="M119" s="46"/>
+      <c r="N119" s="46" t="s">
+        <v>623</v>
+      </c>
+      <c r="O119" s="46"/>
       <c r="P119" s="5"/>
-      <c r="Q119" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="R119" s="40"/>
+      <c r="Q119" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="R119" s="41"/>
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="41" t="n">
+      <c r="A120" s="42" t="n">
         <v>106</v>
       </c>
       <c r="B120" s="23"/>
-      <c r="C120" s="41" t="n">
+      <c r="C120" s="42" t="n">
         <v>102</v>
       </c>
       <c r="D120" s="23"/>
       <c r="E120" s="23" t="s">
-        <v>583</v>
-      </c>
-      <c r="F120" s="46" t="s">
+        <v>624</v>
+      </c>
+      <c r="F120" s="47" t="s">
         <v>183</v>
       </c>
-      <c r="G120" s="41" t="n">
+      <c r="G120" s="42" t="n">
         <v>103</v>
       </c>
-      <c r="H120" s="41" t="n">
+      <c r="H120" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I120" s="41" t="n">
+      <c r="I120" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J120" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="K120" s="45" t="s">
-        <v>585</v>
-      </c>
-      <c r="L120" s="45" t="s">
-        <v>586</v>
-      </c>
-      <c r="M120" s="45"/>
-      <c r="N120" s="45" t="s">
-        <v>587</v>
-      </c>
-      <c r="O120" s="45"/>
+        <v>625</v>
+      </c>
+      <c r="K120" s="46" t="s">
+        <v>626</v>
+      </c>
+      <c r="L120" s="46" t="s">
+        <v>627</v>
+      </c>
+      <c r="M120" s="46"/>
+      <c r="N120" s="46" t="s">
+        <v>628</v>
+      </c>
+      <c r="O120" s="46"/>
       <c r="P120" s="5"/>
-      <c r="Q120" s="8" t="s">
-        <v>382</v>
+      <c r="Q120" s="5" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10788,7 +10935,7 @@
       </c>
       <c r="D121" s="24"/>
       <c r="E121" s="24" t="s">
-        <v>588</v>
+        <v>629</v>
       </c>
       <c r="F121" s="24" t="s">
         <v>36</v>
@@ -10803,99 +10950,99 @@
         <v>1</v>
       </c>
       <c r="J121" s="8"/>
-      <c r="K121" s="39" t="s">
-        <v>589</v>
-      </c>
-      <c r="L121" s="39"/>
-      <c r="M121" s="39"/>
-      <c r="N121" s="39"/>
-      <c r="O121" s="39"/>
+      <c r="K121" s="40" t="s">
+        <v>630</v>
+      </c>
+      <c r="L121" s="40"/>
+      <c r="M121" s="40"/>
+      <c r="N121" s="40"/>
+      <c r="O121" s="40"/>
       <c r="P121" s="8"/>
       <c r="Q121" s="8" t="s">
-        <v>382</v>
+        <v>631</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="41" t="n">
+      <c r="A122" s="42" t="n">
         <v>108</v>
       </c>
       <c r="B122" s="23"/>
-      <c r="C122" s="41" t="n">
+      <c r="C122" s="42" t="n">
         <v>104</v>
       </c>
       <c r="D122" s="23"/>
       <c r="E122" s="23" t="s">
-        <v>590</v>
+        <v>632</v>
       </c>
       <c r="F122" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="G122" s="41" t="n">
+      <c r="G122" s="42" t="n">
         <v>43</v>
       </c>
-      <c r="H122" s="41" t="n">
+      <c r="H122" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I122" s="41" t="n">
+      <c r="I122" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J122" s="5"/>
-      <c r="K122" s="45" t="s">
-        <v>591</v>
-      </c>
-      <c r="L122" s="45"/>
-      <c r="M122" s="45"/>
-      <c r="N122" s="45"/>
-      <c r="O122" s="45"/>
+      <c r="K122" s="46" t="s">
+        <v>633</v>
+      </c>
+      <c r="L122" s="46"/>
+      <c r="M122" s="46"/>
+      <c r="N122" s="46"/>
+      <c r="O122" s="46"/>
       <c r="P122" s="5"/>
-      <c r="Q122" s="8" t="s">
-        <v>382</v>
+      <c r="Q122" s="5" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="41" t="n">
+      <c r="A123" s="42" t="n">
         <v>109</v>
       </c>
       <c r="B123" s="23"/>
-      <c r="C123" s="41" t="n">
+      <c r="C123" s="42" t="n">
         <v>105</v>
       </c>
       <c r="D123" s="23"/>
       <c r="E123" s="23" t="s">
-        <v>592</v>
-      </c>
-      <c r="F123" s="46" t="s">
+        <v>635</v>
+      </c>
+      <c r="F123" s="47" t="s">
         <v>185</v>
       </c>
-      <c r="G123" s="41" t="n">
+      <c r="G123" s="42" t="n">
         <v>108</v>
       </c>
-      <c r="H123" s="41" t="n">
+      <c r="H123" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="I123" s="41" t="n">
+      <c r="I123" s="42" t="n">
         <v>1</v>
       </c>
       <c r="J123" s="5"/>
-      <c r="K123" s="45" t="s">
-        <v>593</v>
-      </c>
-      <c r="L123" s="45"/>
-      <c r="M123" s="45"/>
-      <c r="N123" s="45"/>
-      <c r="O123" s="45"/>
+      <c r="K123" s="46" t="s">
+        <v>636</v>
+      </c>
+      <c r="L123" s="46"/>
+      <c r="M123" s="46"/>
+      <c r="N123" s="46"/>
+      <c r="O123" s="46"/>
       <c r="P123" s="5"/>
-      <c r="Q123" s="8" t="s">
-        <v>382</v>
+      <c r="Q123" s="5" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="65"/>
-      <c r="C124" s="65"/>
+      <c r="A124" s="67"/>
+      <c r="C124" s="67"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="65"/>
-      <c r="C125" s="65"/>
+      <c r="A125" s="67"/>
+      <c r="C125" s="67"/>
     </row>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -10920,7 +11067,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.15"/>
@@ -10961,7 +11108,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>594</v>
+        <v>638</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10971,7 +11118,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>595</v>
+        <v>639</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -10986,18 +11133,18 @@
       <c r="B6" s="24"/>
       <c r="C6" s="8"/>
       <c r="E6" s="10" t="s">
-        <v>596</v>
+        <v>640</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8" t="s">
-        <v>597</v>
+        <v>641</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
         <v>27</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>598</v>
+        <v>642</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11006,10 +11153,10 @@
       <c r="C7" s="8"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>599</v>
+        <v>643</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>600</v>
+        <v>644</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
@@ -11023,10 +11170,10 @@
       <c r="C8" s="8"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
-        <v>601</v>
+        <v>645</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>602</v>
+        <v>646</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8" t="s">
@@ -11039,7 +11186,7 @@
       <c r="B9" s="24"/>
       <c r="C9" s="8"/>
       <c r="E9" s="6" t="s">
-        <v>603</v>
+        <v>647</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="5"/>
@@ -11048,7 +11195,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>604</v>
+        <v>648</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11057,7 +11204,7 @@
       <c r="C10" s="8"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>605</v>
+        <v>649</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>39</v>
@@ -11067,7 +11214,7 @@
         <v>45</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>604</v>
+        <v>648</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11076,17 +11223,17 @@
       <c r="C11" s="8"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>606</v>
+        <v>650</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>607</v>
+        <v>651</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>604</v>
+        <v>648</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11094,11 +11241,11 @@
       <c r="B12" s="24"/>
       <c r="C12" s="8"/>
       <c r="E12" s="10" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="8" t="s">
-        <v>610</v>
+        <v>654</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8" t="s">
@@ -11112,10 +11259,10 @@
       <c r="C13" s="8"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10" t="s">
-        <v>611</v>
+        <v>655</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>610</v>
+        <v>654</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8" t="s">
@@ -11129,10 +11276,10 @@
       <c r="C14" s="8"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10" t="s">
-        <v>612</v>
+        <v>656</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>610</v>
+        <v>654</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8" t="s">
@@ -11146,14 +11293,14 @@
       <c r="C15" s="8"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10" t="s">
-        <v>613</v>
+        <v>657</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>610</v>
+        <v>654</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8" t="s">
-        <v>614</v>
+        <v>658</v>
       </c>
       <c r="J15" s="8"/>
     </row>
@@ -11162,7 +11309,7 @@
       <c r="B16" s="24"/>
       <c r="C16" s="8"/>
       <c r="E16" s="6" t="s">
-        <v>615</v>
+        <v>659</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="5"/>
@@ -11175,7 +11322,7 @@
       <c r="B17" s="24"/>
       <c r="C17" s="8"/>
       <c r="E17" s="10" t="s">
-        <v>616</v>
+        <v>660</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="8"/>
@@ -11184,8 +11331,8 @@
       <c r="J17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="66"/>
-      <c r="B18" s="66"/>
+      <c r="A18" s="68"/>
+      <c r="B18" s="68"/>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
@@ -11198,13 +11345,13 @@
         <v>79</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>617</v>
+        <v>661</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>618</v>
+        <v>662</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>83</v>

--- a/server_nestjs/src/storage/Kompetenzraster.xlsx
+++ b/server_nestjs/src/storage/Kompetenzraster.xlsx
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="663">
   <si>
     <t xml:space="preserve">Voraussetzungen lt. Modulhandbuch</t>
   </si>
@@ -674,42 +674,42 @@
     <t xml:space="preserve">Installation von Python</t>
   </si>
   <si>
+    <t xml:space="preserve">6d66e5c1-3a03-4ad3-8c23-5c7fb7b90ea2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43150eb1-e82d-4a63-8073-45b6ae026171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python Installationsanleitung</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python ist eine vielseitige und populäre Programmiersprache, die sich besonders für Data Science und Machine Learning eignet und durch ihre Einfachheit und die Verfügbarkeit vieler Bibliotheken auszeichnet. Für die Installation von Python wird häufig die Anaconda-Distribution empfohlen, die neben Python auch viele nützliche Bibliotheken und Entwicklungsumgebungen wie Spyder und Jupyter-Notebooks enthält, wobei Miniconda eine schlankere Alternative darstellt.</t>
   </si>
   <si>
-    <t xml:space="preserve">6d66e5c1-3a03-4ad3-8c23-5c7fb7b90ea2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43150eb1-e82d-4a63-8073-45b6ae026171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python Installationsanleitung</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,6</t>
   </si>
   <si>
+    <t xml:space="preserve">3903342b-bb39-4592-8b4d-364800f09ba7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00c25c46-8346-4d81-86a6-3dbc39e4a6e3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python-Variablen sind Namen, die auf Speicherorte verweisen und Daten eines bestimmten Typs enthalten, wobei der Wert einer Variablen im Laufe eines Programms verändert werden kann. Python ist eine dynamisch typisierte Sprache, was bedeutet, dass der Datentyp einer Variablen nicht explizit deklariert werden muss und sich während der Laufzeit ändern kann, wobei Variablennamen sinnvoll gewählt und Groß- und Kleinschreibung beachtet werden sollten.</t>
   </si>
   <si>
-    <t xml:space="preserve">3903342b-bb39-4592-8b4d-364800f09ba7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00c25c46-8346-4d81-86a6-3dbc39e4a6e3</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,6,7</t>
   </si>
   <si>
+    <t xml:space="preserve">6de52e3c-8bf7-4f10-b4bc-11f633d3fd50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9ce7cb4b-8dc6-49ad-990a-76d73bf31ef7</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Python sind Anweisungen (Statements) Instruktionen, die vom Interpreter ausgeführt werden, wie zum Beispiel Funktionsaufrufe oder Wertzuweisungen an Variablen. Ausdrücke (Expressions) hingegen sind spezielle Anweisungen, die einen Wert zurückliefern, wie arithmetische Berechnungen, wobei das Gleichheitszeichen in der Programmierung als Zuweisungsoperator dient und sich von der mathematischen Bedeutung unterscheidet.</t>
   </si>
   <si>
-    <t xml:space="preserve">6de52e3c-8bf7-4f10-b4bc-11f633d3fd50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9ce7cb4b-8dc6-49ad-990a-76d73bf31ef7</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,8</t>
   </si>
   <si>
@@ -719,18 +719,18 @@
     <t xml:space="preserve">2,8,9</t>
   </si>
   <si>
+    <t xml:space="preserve">ad1eb799-2e9e-4279-b396-2788a52a2c28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46d632d3-e5be-4872-86da-be692e81e424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strings</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Python sind Strings eine Sequenz von Zeichen, die in einfachen, doppelten oder dreifachen Anführungszeichen definiert werden können, wobei letztere auch Zeilenumbrüche und Anführungszeichen im Text erlauben. Strings sind in Python unveränderlich (immutable), unterstützen aber eine Vielzahl von Operationen wie Konkatenation, Wiederholung, Indizierung und eingebaute Methoden wie split, replace und format, um nur einige zu nennen.</t>
   </si>
   <si>
-    <t xml:space="preserve">ad1eb799-2e9e-4279-b396-2788a52a2c28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46d632d3-e5be-4872-86da-be692e81e424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strings</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,8,10</t>
   </si>
   <si>
@@ -740,126 +740,126 @@
     <t xml:space="preserve">2,8,10,11</t>
   </si>
   <si>
+    <t xml:space="preserve">e6e07da5-6eb5-4e34-a7b0-944cbdb4d484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74feba64-e05e-4f58-83dd-fcaf65406b5d</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Python gibt es drei Haupttypen von Zahlen: Integer (ganze Zahlen), Floats (Gleitkommazahlen) und komplexe Zahlen. Während Integer und Floats für alltägliche Berechnungen verwendet werden, wobei Floats aufgrund des IEEE 754 Standards zu Rundungsfehlern führen können, sind komplexe Zahlen mit einem imaginären Teil (in Python mit 'j' gekennzeichnet) für spezielle mathematische Anwendungen gedacht.</t>
   </si>
   <si>
-    <t xml:space="preserve">e6e07da5-6eb5-4e34-a7b0-944cbdb4d484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74feba64-e05e-4f58-83dd-fcaf65406b5d</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,8,10,12</t>
   </si>
   <si>
+    <t xml:space="preserve">0da90d38-8a08-4714-bfdd-a99c86f1e982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02f37e4b-e28c-4eb0-ad16-9fd02d346f61</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Python gibt es drei Arten von Zahlen: Integer (ganze Zahlen), Floats (Gleitkommazahlen) und komplexe Zahlen. Während Integer und Floats für alltägliche Berechnungen genutzt werden, wobei Floats aufgrund des IEEE 754 Standards zu Rundungsfehlern führen können, sind komplexe Zahlen mit einem imaginären Teil (in Python mit 'j' gekennzeichnet) für spezielle mathematische Anwendungen vorgesehen.</t>
   </si>
   <si>
-    <t xml:space="preserve">0da90d38-8a08-4714-bfdd-a99c86f1e982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02f37e4b-e28c-4eb0-ad16-9fd02d346f61</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,8,10,13</t>
   </si>
   <si>
     <t xml:space="preserve">Complex</t>
   </si>
   <si>
+    <t xml:space="preserve">b4d5191b-7b2c-4047-833e-c27417f4e345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47ace2db-fe3b-4dcd-ae92-d5d00a12843d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Komplexe Zahlen</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Python gibt es drei Arten von Zahlen: Integer (ganze Zahlen), Floats (Gleitkommazahlen) und komplexe Zahlen. Während Integer und Floats für alltägliche Berechnungen genutzt werden, wobei Floats aufgrund des IEEE 754 Standards zu Rundungsfehlern führen können, sind komplexe Zahlen mit einem imaginären Teil (in Python mit 'j' gekennzeichnet) ein speziellerer Datentyp, der seltener verwendet wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">b4d5191b-7b2c-4047-833e-c27417f4e345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47ace2db-fe3b-4dcd-ae92-d5d00a12843d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Komplexe Zahlen</t>
-  </si>
-  <si>
     <t xml:space="preserve">11,12,13</t>
   </si>
   <si>
     <t xml:space="preserve">2,8,10,14</t>
   </si>
   <si>
+    <t xml:space="preserve">03efcfad-eda1-4b7c-9ccf-d75f50fa3e5e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01600171-cee2-4c72-a432-8127c2788391</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python bietet verschiedene Operatoren für mathematische Operationen, wie die Standardaddition, -subtraktion, -multiplikation und -division, sowie spezielle Operatoren für ganzzahlige Division (//), Modulus (%) und Exponentiation (**). Bei der Division von Ganzzahlen wird automatisch ein Fließkommawert zurückgegeben, während die ganzzahlige Division immer abrundet; zudem können alle Operatoren in Verbindung mit dem Zuweisungsoperator (z.B. +=, *=) für verkürzte Operationen verwendet werden.</t>
   </si>
   <si>
-    <t xml:space="preserve">03efcfad-eda1-4b7c-9ccf-d75f50fa3e5e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01600171-cee2-4c72-a432-8127c2788391</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,8,16</t>
   </si>
   <si>
+    <t xml:space="preserve">34e378fc-083d-4cf2-be91-49fd8832b619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ce6d2406-f733-473b-ad99-ff339462c919</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Python repräsentieren Booleans die Wahrheitswerte True und False, während None ein spezieller Datentyp ist, der zur Initialisierung von Variablen verwendet wird und nur den Wert None annehmen kann. Diese Datentypen sind essentiell für Vergleichsoperationen und Kontrollstrukturen, wobei None oft genutzt wird, um den Zustand "kein Wert" oder "nicht initialisiert" darzustellen.</t>
   </si>
   <si>
-    <t xml:space="preserve">34e378fc-083d-4cf2-be91-49fd8832b619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ce6d2406-f733-473b-ad99-ff339462c919</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,8,17</t>
   </si>
   <si>
+    <t xml:space="preserve">489bad95-fd32-46e7-952b-268c283cfe4a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e51df41b-baeb-4043-897a-a2103ecb4a02</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Python repräsentieren Booleans die Wahrheitswerte True und False, die häufig in Vergleichsoperationen verwendet werden, um logische Bedingungen zu testen. Der Datentyp None wird oft zur Initialisierung von Variablen verwendet und hat nur einen Wert, nämlich None selbst, was anzeigt, dass eine Variable noch keinen anderen Wert zugewiesen bekommen hat.</t>
   </si>
   <si>
-    <t xml:space="preserve">489bad95-fd32-46e7-952b-268c283cfe4a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e51df41b-baeb-4043-897a-a2103ecb4a02</t>
-  </si>
-  <si>
     <t xml:space="preserve">9, 10,16,17</t>
   </si>
   <si>
     <t xml:space="preserve">2,8,10,11,12,13,15</t>
   </si>
   <si>
+    <t xml:space="preserve">fb6ac78c-acf4-42f1-8b65-ab55d1522566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c2affb31-d442-463f-a1fa-0aef94c24bad</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Python können verschiedene Datentypen wie Int, Float und Komplex sowie Strings ineinander umgewandelt werden, indem man den entsprechenden Datentyp als Funktion verwendet (z.B. `int()`, `float()`, `str()`). Bei der Umwandlung von Eingaben ist zu beachten, dass `input()` immer einen String zurückgibt, der erst in einen numerischen Typ umgewandelt werden muss, um mathematische Operationen durchführen zu können.</t>
   </si>
   <si>
-    <t xml:space="preserve">fb6ac78c-acf4-42f1-8b65-ab55d1522566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c2affb31-d442-463f-a1fa-0aef94c24bad</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,18</t>
   </si>
   <si>
+    <t xml:space="preserve">78d7c159-7c83-4443-8838-edf61d02f7a9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontrolle über Programme</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python Kontrollstrukturen umfassen If-Statements, die mit Vergleichsoperatoren wie gleich (==), nicht gleich (!=), größer (&gt;), kleiner (&lt;), größer gleich (&gt;=) und kleiner gleich (&lt;=) arbeiten, sowie logische Operatoren wie and, or und not, um boolesche Ausdrücke zu verknüpfen. Wichtig ist dabei die korrekte Einrückung, da sie die Programmlogik bestimmt, und Schleifen wie die while-Schleife, die zur Wiederholung von Code-Blöcken verwendet wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">78d7c159-7c83-4443-8838-edf61d02f7a9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontrolle über Programme</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,18,19</t>
   </si>
   <si>
+    <t xml:space="preserve">7746f92a-3fc5-4566-8a04-6bab9bf3c34e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62265751-3ac6-4e84-af5f-1c8190b35a2b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if/else am Kartenspiel Beispiel</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Python ermöglichen if-else-Kontrollstrukturen die Ausführung von Codeblöcken basierend auf Bedingungen, die zu wahren (True) oder falschen (False) Werten evaluiert werden. Ein if-Statement führt den nachfolgenden Codeblock aus, wenn die Bedingung wahr ist, während ein else-Statement den Codeblock ausführt, wenn alle vorherigen Bedingungen falsch sind; elif-Statements bieten zusätzliche Bedingungsüberprüfungen.</t>
   </si>
   <si>
-    <t xml:space="preserve">7746f92a-3fc5-4566-8a04-6bab9bf3c34e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62265751-3ac6-4e84-af5f-1c8190b35a2b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if/else am Kartenspiel Beispiel</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,18,20</t>
   </si>
   <si>
@@ -872,39 +872,39 @@
     <t xml:space="preserve">while</t>
   </si>
   <si>
+    <t xml:space="preserve">10197a89-4d56-4c27-8d0c-5b0398db9af8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e2709d08-70eb-4974-800e-d7a8ea834b0d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">while am Kartenspiel Beispiel</t>
+  </si>
+  <si>
     <t xml:space="preserve">In dem Code-Beispiel zur Python-Kontrollstruktur `while` wird eine Schleife verwendet, um ein Kartenspiel zu simulieren, bei dem Karten gezogen werden, bis keine mehr übrig sind. Die `while`-Schleife prüft dabei kontinuierlich, ob die Liste der Preiskarten noch Elemente enthält, und entfernt mit der `pop`-Methode jeweils das letzte Element, bis die Liste leer ist und die Schleife beendet wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">10197a89-4d56-4c27-8d0c-5b0398db9af8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e2709d08-70eb-4974-800e-d7a8ea834b0d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">while am Kartenspiel Beispiel</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,18,20,22</t>
   </si>
   <si>
     <t xml:space="preserve">for</t>
   </si>
   <si>
+    <t xml:space="preserve">a7a30f58-631e-4d64-9f61-c93bc59e65ea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a33456d7-0175-4dd2-b6f9-599f3a9a1305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1e1012c0-76bb-4bf9-8f7e-5a4b53f40e60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For-Schleifen</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Python ermöglichen for-Schleifen das Durchlaufen von iterierbaren Objekten wie Listen, indem man eine Variable über die Elemente iterieren lässt, beispielsweise mit `for element in my_list`. Die `range`-Funktion wird oft in for-Schleifen verwendet, um über eine Sequenz von Zahlen zu iterieren, wobei man Start-, Stopp- und Schrittweite angeben kann, um beispielsweise mit `for i in range(1, 10, 3)` die Zahlen 1, 4 und 7 zu durchlaufen.</t>
   </si>
   <si>
-    <t xml:space="preserve">a7a30f58-631e-4d64-9f61-c93bc59e65ea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a33456d7-0175-4dd2-b6f9-599f3a9a1305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1e1012c0-76bb-4bf9-8f7e-5a4b53f40e60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For-Schleifen</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,39</t>
   </si>
   <si>
@@ -953,75 +953,75 @@
     <t xml:space="preserve">Funktionen in der Programmierung sind wiederverwendbare Codeblöcke, die spezifische Aufgaben ausführen und dabei Eingabewerte verarbeiten können, um Ergebnisse zurückzugeben. Sie fördern die Modularität und Wartbarkeit des Codes, indem sie es ermöglichen, komplexe Probleme in kleinere, handhabbare Teile zu zerlegen und diese Teile unabhängig voneinander zu testen und zu verwenden.</t>
   </si>
   <si>
+    <t xml:space="preserve">769f3f92-09cc-4eb4-9a5f-f6763f9d2f08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9c563338-623f-4c75-80b4-ad24c1e11fa0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funktionen am Beispiel Addieren und Verdoppeln</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python-Funktionen ermöglichen es, Codeblöcke zu isolieren und in sinnvolle Abschnitte aufzuteilen, was die Übersichtlichkeit und Wartbarkeit von Programmen erheblich verbessert, insbesondere bei großen Projekten. Sie werden mit dem Schlüsselwort `def` definiert, können beliebig viele Eingabeargumente enthalten und mit `return` Werte zurückgeben, die dann im Hauptprogramm verwendet werden können.</t>
   </si>
   <si>
-    <t xml:space="preserve">769f3f92-09cc-4eb4-9a5f-f6763f9d2f08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9c563338-623f-4c75-80b4-ad24c1e11fa0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funktionen am Beispiel Addieren und Verdoppeln</t>
+    <t xml:space="preserve">54ac4b8c-91ab-477d-9342-e9b019c858ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302d6f24-b92b-45b0-b845-f7d56a403464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funktionen am Beispiel Goofspiel</t>
   </si>
   <si>
     <t xml:space="preserve">In dem Codebeispiel werden Teile eines Kartenspiels in Python-Funktionen ausgelagert, um den Code übersichtlicher und modularer zu gestalten. Die Funktionen `StrategieSpieler1` und `StrategieSpieler2` werden definiert, um die Strategie der Spieler zu kapseln, wobei die Funktionen Eingabeparameter wie den Wert der Preiskarte und die verbleibenden Karten des Spielers erhalten und die ausgewählte Karte zurückgeben.</t>
   </si>
   <si>
-    <t xml:space="preserve">54ac4b8c-91ab-477d-9342-e9b019c858ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302d6f24-b92b-45b0-b845-f7d56a403464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funktionen am Beispiel Goofspiel</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,23,24</t>
   </si>
   <si>
+    <t xml:space="preserve">916876d2-d005-485d-afd9-14a36d45a5b2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81e936ec-02c4-449f-96ec-e70edc85403a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docstring und Kommentare</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python-Funktionen können mit Docstrings dokumentiert werden, die mit drei Anführungszeichen beginnen und eine systematische Beschreibung der Funktion, ihrer Parameter und Rückgabewerte enthalten. Docstrings sind besonders hilfreich in größeren Projekten, da sie es ermöglichen, die Funktionsweise von Code auch Monate später noch zu verstehen, und können mit der `help()`-Funktion abgerufen werden, um Nutzern und Entwicklern die Verwendung der Funktionen zu erleichtern.</t>
   </si>
   <si>
-    <t xml:space="preserve">916876d2-d005-485d-afd9-14a36d45a5b2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81e936ec-02c4-449f-96ec-e70edc85403a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docstring und Kommentare</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,23,25</t>
   </si>
   <si>
+    <t xml:space="preserve">0586d1bc-a676-4adb-8cdb-59a27c06b232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155bae80-afc1-4ff1-9cac-9db40cd01e66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eingabeargumente</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python-Funktionen können sowohl Positional Arguments als auch Keyword Arguments akzeptieren, wobei die Reihenfolge bei Positional Arguments wichtig ist und bei Keyword Arguments durch die explizite Benennung irrelevant wird. Zusätzlich können Funktionen in Python mit `*args` und `**kwargs` eine variable Anzahl von Positional bzw. Keyword Arguments empfangen, was die Flexibilität bei der Übergabe von Argumenten erhöht.</t>
   </si>
   <si>
-    <t xml:space="preserve">0586d1bc-a676-4adb-8cdb-59a27c06b232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155bae80-afc1-4ff1-9cac-9db40cd01e66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eingabeargumente</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,23,26</t>
   </si>
   <si>
+    <t xml:space="preserve">ef0c4946-e519-41fd-b9ea-9169c1ee0f67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274ca37b-beee-4cd1-972b-c2d258b75258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8f5f8470-6f2f-4fd1-9b12-0914554cc301</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Python können Funktionen als Variablen gespeichert und verwendet werden, was bedeutet, dass man eine Funktion einer Variablen zuweisen und dann diese Variable wie eine Funktion aufrufen kann. Dies ermöglicht es, Funktionen als Argumente an andere Funktionen zu übergeben und sogenannte Higher-Order Functions zu erstellen, die Funktionen höherer Ordnung sind und von anderen Funktionen abhängen können.</t>
   </si>
   <si>
-    <t xml:space="preserve">ef0c4946-e519-41fd-b9ea-9169c1ee0f67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274ca37b-beee-4cd1-972b-c2d258b75258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8f5f8470-6f2f-4fd1-9b12-0914554cc301</t>
-  </si>
-  <si>
     <t xml:space="preserve">65730c57-4e80-4cb7-ad2f-a058640eaa8f</t>
   </si>
   <si>
@@ -1034,96 +1034,96 @@
     <t xml:space="preserve">2,23,27</t>
   </si>
   <si>
+    <t xml:space="preserve">5a8cf9ca-0145-4c82-901a-fcdbb26ac401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b8d62fbc-2913-4319-99b2-08c5854aa054</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python-Funktionen können in ausgelagerten Dateien organisiert und mit dem `import`-Befehl in andere Skripte eingebunden werden, wobei der Namespace des importierten Moduls verwendet wird. Um Funktionen direkt im Namensraum verfügbar zu machen, kann `from Modul import Funktionsname` verwendet werden, während `import Modul as Alias` es ermöglicht, Funktionen mit einem benutzerdefinierten Namespace anzusprechen.</t>
   </si>
   <si>
-    <t xml:space="preserve">5a8cf9ca-0145-4c82-901a-fcdbb26ac401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b8d62fbc-2913-4319-99b2-08c5854aa054</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,23,28</t>
   </si>
   <si>
+    <t xml:space="preserve">3817eef2-f212-41b2-9b22-70f0a934e291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4265c9b9-3149-41cc-b16b-63aeb6963dcf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python-Funktionen höherer Ordnung sind Funktionen, die andere Funktionen als Argumente entgegennehmen und auf Elemente einer Liste anwenden. Sie ermöglichen es, Operationen wie das Quadrieren von Zahlen oder das Hinzufügen von Absätzen zu Strings in Listen effizient durchzuführen, indem man eine allgemeine Funktion wie "auf jedes Element" definiert und diese dann mit spezifischen Funktionen für unterschiedliche Aufgaben verwendet.</t>
   </si>
   <si>
-    <t xml:space="preserve">3817eef2-f212-41b2-9b22-70f0a934e291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4265c9b9-3149-41cc-b16b-63aeb6963dcf</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,29</t>
   </si>
   <si>
+    <t xml:space="preserve">7185bc4d-a06f-4326-9d37-932f2920ae4f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1ff4220c-821e-4bc6-b916-87e85f363d51</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Python können Variablen entweder global oder lokal sein, wobei globale Variablen überall im Code verwendet werden können und lokale Variablen nur innerhalb der Funktion, in der sie definiert wurden. Änderungen an globalen, veränderbaren (mutable) Variablen innerhalb einer Funktion sind auch außerhalb sichtbar, während Änderungen an lokalen Variablen nach dem Funktionsaufruf nicht bestehen bleiben.</t>
   </si>
   <si>
-    <t xml:space="preserve">7185bc4d-a06f-4326-9d37-932f2920ae4f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1ff4220c-821e-4bc6-b916-87e85f363d51</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,29,30</t>
   </si>
   <si>
+    <t xml:space="preserve">38bcbb98-a103-488d-b627-e5808a8e6780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b76fa07c-0c40-4b30-bd43-ccf768a7a09a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mutable und Immutable Variablen</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Python können Variablen entweder mutable (veränderbar) oder immutable (unveränderbar) sein. Globale Variablen, die außerhalb von Funktionen definiert werden, können innerhalb von Funktionen gelesen und, wenn sie mutable sind, auch verändert werden, wobei die Änderungen dann global sichtbar sind; lokale Variablen hingegen sind nur innerhalb ihrer Funktion sichtbar und existieren außerhalb nicht.</t>
   </si>
   <si>
-    <t xml:space="preserve">38bcbb98-a103-488d-b627-e5808a8e6780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b76fa07c-0c40-4b30-bd43-ccf768a7a09a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mutable und Immutable Variablen</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,34</t>
   </si>
   <si>
+    <t xml:space="preserve">a854c7a7-b49f-42b3-bf79-b69ca27a9740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07d327af-e56c-4b05-99d3-8e35aaba650b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fa6a028b-2f42-4d67-be18-c4c41f64cafd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a92f962a-3402-4153-ad26-fbaa5c29bdcd</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rekursion in Python bezeichnet das Konzept, bei dem eine Funktion sich selbst aufruft, um ein Problem zu lösen. Es ist wichtig, eine Abbruchbedingung zu definieren, um unendliche Rekursionen und damit Programmabstürze zu vermeiden; rekursive Lösungen können eleganter oder mit weniger Code als iterative Lösungen sein und verhindern die Mutation von Variablen, was sie für funktionale Programmierung attraktiv macht.</t>
   </si>
   <si>
-    <t xml:space="preserve">a854c7a7-b49f-42b3-bf79-b69ca27a9740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07d327af-e56c-4b05-99d3-8e35aaba650b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fa6a028b-2f42-4d67-be18-c4c41f64cafd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a92f962a-3402-4153-ad26-fbaa5c29bdcd</t>
+    <t xml:space="preserve">5e8ff001-3c5d-4509-a897-2f8ae1a19ba2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d6f6f2a2-a096-4300-bd50-7a6d928537e7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rekursion mit Code-Beispielen</t>
   </si>
   <si>
     <t xml:space="preserve">Rekursion in Python wird oft verwendet, um Probleme zu lösen, die sich in kleinere Instanzen desselben Problems aufteilen lassen, wie beispielsweise die Berechnung der Summe aller Zahlen bis zu einer gegebenen Zahl N oder die Fakultät einer Zahl. Im Transkript werden rekursive Funktionen zur Lösung solcher Probleme diskutiert, wobei die Basisfälle (Abbruchbedingungen) und die rekursiven Aufrufe, die das Problem in kleinere Teile zerlegen, zentrale Elemente sind. Ein weiteres Beispiel ist die rekursive Bestimmung von Primzahlen und die Primfaktorzerlegung einer Zahl, die ebenfalls im Transkript behandelt werden.</t>
   </si>
   <si>
-    <t xml:space="preserve">5e8ff001-3c5d-4509-a897-2f8ae1a19ba2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d6f6f2a2-a096-4300-bd50-7a6d928537e7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rekursion mit Code-Beispielen</t>
+    <t xml:space="preserve">28633773-8edd-41f1-9d9b-5c60c195e40d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4a4d2c7b-3593-4c8f-bd6b-a2bf03856e64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rekursion am Beispiel Goofspiel</t>
   </si>
   <si>
     <t xml:space="preserve">In dem Codebeispiel wird die Rekursion anhand verschiedener mathematischer Probleme in Python demonstriert, wie die Summe aller Zahlen bis N, die Fakultät einer Zahl und die Überprüfung, ob eine Zahl eine Primzahl ist. Die Rekursion wird dabei als Methode zur Problemlösung verwendet, indem ein großes Problem in kleinere Instanzen heruntergebrochen wird, bis eine Instanz erreicht ist, die direkt gelöst werden kann.</t>
   </si>
   <si>
-    <t xml:space="preserve">28633773-8edd-41f1-9d9b-5c60c195e40d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4a4d2c7b-3593-4c8f-bd6b-a2bf03856e64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rekursion am Beispiel Goofspiel</t>
-  </si>
-  <si>
     <t xml:space="preserve">23,29,34</t>
   </si>
   <si>
@@ -1136,27 +1136,27 @@
     <t xml:space="preserve">2,31,32</t>
   </si>
   <si>
+    <t xml:space="preserve">658c43ba-f341-44ec-acf7-ef3da6b292bf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5fbfe84d-7a96-4e6f-ab62-8472a5f7999a</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Python können Variablen, die außerhalb einer Funktion definiert wurden, innerhalb der Funktion verwendet werden, sofern sie vor der Funktionsdefinition initialisiert wurden; sie gelten dann als globale Variablen. Lokale Variablen hingegen sind nur innerhalb der Funktion bekannt und Änderungen an ihnen sind außerhalb der Funktion nicht sichtbar, es sei denn, sie werden explizit als global innerhalb der Funktion deklariert.</t>
   </si>
   <si>
-    <t xml:space="preserve">658c43ba-f341-44ec-acf7-ef3da6b292bf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5fbfe84d-7a96-4e6f-ab62-8472a5f7999a</t>
+    <t xml:space="preserve">f294a4fc-c912-40ab-9d2c-9e341d79ab3b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50cc4e39-6613-441c-bee2-60883a0ce4b7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goofspiel funktionaler machen</t>
   </si>
   <si>
     <t xml:space="preserve">Das Transkript behandelt die Unterscheidung zwischen lokalen und globalen Variablen in Python und wie sie innerhalb von Funktionen verwendet werden können. Globale Variablen können innerhalb von Funktionen gelesen werden, wenn sie vorher definiert wurden, während lokale Variablen nur innerhalb der Funktion existieren und außerhalb nicht sichtbar sind. Es wird auch erklärt, wie man mit dem Schlüsselwort `global` eine lokale Variable in einer Funktion als global deklarieren kann, sodass Änderungen an ihr auch außerhalb der Funktion sichtbar sind.</t>
   </si>
   <si>
-    <t xml:space="preserve">f294a4fc-c912-40ab-9d2c-9e341d79ab3b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50cc4e39-6613-441c-bee2-60883a0ce4b7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goofspiel funktionaler machen</t>
-  </si>
-  <si>
     <t xml:space="preserve">2,31,33</t>
   </si>
   <si>
@@ -1175,18 +1175,18 @@
     <t xml:space="preserve">2,35,36</t>
   </si>
   <si>
+    <t xml:space="preserve">4a3358bd-ed98-4e83-a6b7-1c59113b8c55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">914cbb7d-82b5-4ac0-9e58-be128f23495d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9a618080-fbdd-45a1-b3e2-5cbc26f8d1e7</t>
+  </si>
+  <si>
     <t xml:space="preserve">Der Befehl map nimmt eine Funktion und ein iterierbares Objekt (z.B. Liste oder Tupel) entgegen und wendet die Funktion auf jedes Element des iterierbaren Objektes an. Genauer, bekommen wir einen Iterator zurück über welchen wir iterieren können oder Methoden wie __next__() aufrufen.</t>
   </si>
   <si>
-    <t xml:space="preserve">4a3358bd-ed98-4e83-a6b7-1c59113b8c55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">914cbb7d-82b5-4ac0-9e58-be128f23495d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9a618080-fbdd-45a1-b3e2-5cbc26f8d1e7</t>
-  </si>
-  <si>
     <t xml:space="preserve">1f5cc88f-56db-4eba-b911-362642ab6bd5</t>
   </si>
   <si>
@@ -1220,21 +1220,21 @@
     <t xml:space="preserve">2,35,38</t>
   </si>
   <si>
+    <t xml:space="preserve">a7ac76ff-1ac1-4de5-92ff-fd24a68619cb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6bdadf55-b0b3-4d65-af42-a7cca8466c8d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6bfb79f3-d017-47f4-86df-de628eb0cf81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reduce</t>
+  </si>
+  <si>
     <t xml:space="preserve">Der Befehl reduce nimmt auch eine Funktion und iterierbares Objekt (z.B. Liste oder Tupel) entgegen. Die Funktion muss zwei Elemente in dem iterierbaren Objekt auf eines abbilden und reduziert nun durch sukzessives Anwenden der Funktion das gesamte iterierbare Objekt auf ein Element.</t>
   </si>
   <si>
-    <t xml:space="preserve">a7ac76ff-1ac1-4de5-92ff-fd24a68619cb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6bdadf55-b0b3-4d65-af42-a7cca8466c8d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6bfb79f3-d017-47f4-86df-de628eb0cf81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reduce</t>
-  </si>
-  <si>
     <t xml:space="preserve">Objektorientierte Programmierung mit Java</t>
   </si>
   <si>
@@ -1337,39 +1337,39 @@
     <t xml:space="preserve">43,46,54</t>
   </si>
   <si>
+    <t xml:space="preserve">f16f3f43-404e-44cb-b813-9de902878f39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23023ee4-4376-432e-ab0f-7cf29c0c6204</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java müssen Variablen einen spezifischen Typ haben, der ihre Verwendung und die Art der Werte, die sie speichern können, bestimmt. Fehler bei der Zuweisung von Typen oder der Verwendung von Konstanten können zu Fehlermeldungen oder unerwünschtem Verhalten der Anwendung führen.</t>
   </si>
   <si>
-    <t xml:space="preserve">f16f3f43-404e-44cb-b813-9de902878f39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23023ee4-4376-432e-ab0f-7cf29c0c6204</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,46,55</t>
   </si>
   <si>
+    <t xml:space="preserve">acb1bed9-2c68-4456-b748-2c635f506b32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73b26d8e-22e0-4ebc-9bba-cd9e006296e5</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java können Typkonversionen implizit oder explizit erfolgen, wobei implizite Konversionen meist von einem kleineren zu einem größeren Datentyp ohne Informationsverlust möglich sind. Explizite Konversionen erfordern die Verwendung von Klammern und können zu Informationsverlust führen, wie beim Konvertieren von Fließkommazahlen zu Ganzzahlen, und nicht alle Typen, wie Booleans, können konvertiert werden.</t>
   </si>
   <si>
-    <t xml:space="preserve">acb1bed9-2c68-4456-b748-2c635f506b32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73b26d8e-22e0-4ebc-9bba-cd9e006296e5</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,56</t>
   </si>
   <si>
+    <t xml:space="preserve">89685233-4c76-4311-8e85-140d638192b0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4a250618-eec3-4ec9-864a-0e07d2b553d5</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java werden Variablen mit einem spezifischen Namen und Typ deklariert, wobei das Schlüsselwort `final` eine Variable als unveränderliche Konstante kennzeichnet. Variablen haben einen definierten Gültigkeitsbereich, der durch Codeblöcke mit geschweiften Klammern festgelegt wird, und innerhalb desselben Gültigkeitsbereichs darf ein Variablenname nicht mehrfach verwendet werden.</t>
   </si>
   <si>
-    <t xml:space="preserve">89685233-4c76-4311-8e85-140d638192b0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4a250618-eec3-4ec9-864a-0e07d2b553d5</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,57</t>
   </si>
   <si>
@@ -1379,51 +1379,51 @@
     <t xml:space="preserve">43,57,58</t>
   </si>
   <si>
+    <t xml:space="preserve">b29462eb-fdfa-41c2-8098-7931d3201f7c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21c7cc0d-9687-4c34-96af-6d8d714eb54d</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java können Variablen als `final` deklariert werden, was bedeutet, dass ihr Wert nach der Initialisierung nicht mehr geändert werden kann, und sie werden somit zu Konstanten. Jede Variable hat einen bestimmten Gültigkeitsbereich, der durch Blöcke mit geschweiften Klammern definiert wird, und innerhalb dessen die Variable aktiv und bekannt ist, außerhalb jedoch nicht mehr gültig ist.</t>
   </si>
   <si>
-    <t xml:space="preserve">b29462eb-fdfa-41c2-8098-7931d3201f7c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21c7cc0d-9687-4c34-96af-6d8d714eb54d</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,57,59</t>
   </si>
   <si>
+    <t xml:space="preserve">e272fd46-2e10-4b71-ba54-2d9ce76e3369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440e4f75-5960-4f1c-b453-293c4f8e4484</t>
+  </si>
+  <si>
     <t xml:space="preserve">Java bietet eine Vielzahl von Operatoren, die für verschiedene Arten von Operationen verwendet werden können, darunter arithmetische, unäre, binäre und ternäre Operatoren. Zu den arithmetischen Operatoren gehören Addition, Subtraktion, Multiplikation und Division, während Vergleichsoperatoren und logische Operatoren in bedingten Anweisungen wie if-Tests verwendet werden, um Werte zu vergleichen und Boolesche Ausdrücke zu bilden.</t>
   </si>
   <si>
-    <t xml:space="preserve">e272fd46-2e10-4b71-ba54-2d9ce76e3369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440e4f75-5960-4f1c-b453-293c4f8e4484</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,57,60</t>
   </si>
   <si>
+    <t xml:space="preserve">e2815f41-b1cd-48f5-bb46-1d7403c8f7ba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21f1a4c3-c92c-4e2d-9280-4d5d1d1adf47</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java sind Zuweisungen Anweisungen, bei denen Variablen Werte zugewiesen werden, wie beispielsweise bei der Zuweisung von 7 zu den Variablen x und y. Diese Zuweisungen können auch arithmetische Operationen beinhalten, wie etwa x gleich x minus 5, und werden für verschiedene Datentypen wie Integer, Float oder Double verwendet, wobei der berechnete Wert der Variablen zugewiesen wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">e2815f41-b1cd-48f5-bb46-1d7403c8f7ba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21f1a4c3-c92c-4e2d-9280-4d5d1d1adf47</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,57,61</t>
   </si>
   <si>
+    <t xml:space="preserve">1a63423b-646f-40b3-927f-4c3bdd4dc01b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46d89583-f737-42ac-96ee-67dabd699552</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java ist ein Block ein Codeabschnitt, der von geschweiften Klammern umgeben ist, innerhalb dessen definierte Variablen nur innerhalb dieses Blocks existieren und nach dessen Ende nicht mehr verfügbar sind. Anweisungen innerhalb eines Blocks werden sequenziell von oben nach unten und von links nach rechts ausgeführt, wobei jede Anweisung durch einen Strichpunkt getrennt wird, außer bei Blöcken selbst, bei denen der abschließende Strichpunkt weggelassen werden kann.</t>
   </si>
   <si>
-    <t xml:space="preserve">1a63423b-646f-40b3-927f-4c3bdd4dc01b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46d89583-f737-42ac-96ee-67dabd699552</t>
-  </si>
-  <si>
     <t xml:space="preserve">21064003-7fec-42c1-bf24-3fb64408e567</t>
   </si>
   <si>
@@ -1439,78 +1439,78 @@
     <t xml:space="preserve">43,62,63</t>
   </si>
   <si>
+    <t xml:space="preserve">9b507e1f-590f-4e4d-82d4-7e6343e64475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e9858a81-ce4b-4969-85fe-99556d38e819</t>
+  </si>
+  <si>
     <t xml:space="preserve">Java-Kontrollstrukturen wie if-else nutzen Blöcke, die durch geschweifte Klammern definiert sind, um Variablen und Anweisungen zu umschließen, die nur innerhalb dieser Blöcke gültig und lebendig sind. Anweisungen innerhalb eines Blocks werden sequenziell von oben nach unten und von links nach rechts ausgeführt, wobei jede Anweisung durch einen Strichpunkt getrennt wird, außer bei Blöcken selbst, bei denen der abschließende Strichpunkt weggelassen werden kann.</t>
   </si>
   <si>
-    <t xml:space="preserve">9b507e1f-590f-4e4d-82d4-7e6343e64475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e9858a81-ce4b-4969-85fe-99556d38e819</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,62,64</t>
   </si>
   <si>
+    <t xml:space="preserve">581dc905-7db5-4223-838b-264f0dcb4301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e9587ee2-72aa-46cd-8750-a8eec7fa185a</t>
+  </si>
+  <si>
     <t xml:space="preserve">Die Switch-Anweisung in Java ermöglicht es, einen Wert gegen eine Reihe von Konstanten zu prüfen und entsprechend unterschiedliche Blöcke von Anweisungen auszuführen. Jeder Block wird durch das Schlüsselwort "case" eingeleitet und muss mit einem "break" enden, um die Ausführung der Switch-Anweisung zu beenden; andernfalls wird die Ausführung fortgesetzt, bis ein "break" erreicht wird oder die gesamte Anweisung abgearbeitet ist, wobei "default" für alle nicht explizit aufgeführten Fälle verwendet wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">581dc905-7db5-4223-838b-264f0dcb4301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e9587ee2-72aa-46cd-8750-a8eec7fa185a</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,62,65</t>
   </si>
   <si>
+    <t xml:space="preserve">746c83ca-40a6-46ef-a6f5-8a229767ab50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fdc7853c-2536-4ef2-b821-82f623b127fb</t>
+  </si>
+  <si>
     <t xml:space="preserve">Java bietet verschiedene Schleifentypen für unterschiedliche Anwendungsfälle: Die for-Schleife eignet sich besonders, wenn die Anzahl der Durchläufe bekannt ist, wie etwa das Durchlaufen von Zahlenbereichen. Die while- und do-while-Schleifen sind hingegen nützlich, wenn die Anzahl der Wiederholungen nicht im Voraus bekannt ist, wobei die do-while-Schleife den Schleifenblock mindestens einmal ausführt, bevor die Bedingung geprüft wird, im Gegensatz zur while-Schleife, die die Bedingung vor dem ersten Durchlauf prüft.</t>
   </si>
   <si>
-    <t xml:space="preserve">746c83ca-40a6-46ef-a6f5-8a229767ab50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fdc7853c-2536-4ef2-b821-82f623b127fb</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,62,65,66</t>
   </si>
   <si>
+    <t xml:space="preserve">15d2c1fa-c6cf-4096-8ec7-c403ce84e552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9eeabe03-4fd1-42bf-ace6-d1e607a5d3dc</t>
+  </si>
+  <si>
     <t xml:space="preserve">Die while-Schleife in Java beginnt mit dem Keyword "while", gefolgt von einer Bedingung in runden Klammern; wenn diese Bedingung wahr ist, werden die in geschweiften Klammern eingeschlossenen Anweisungen ausgeführt. Die do-while-Schleife hingegen führt die Anweisungen mindestens einmal aus, bevor die Bedingung am Ende der Schleife geprüft wird, und wiederholt den Vorgang, solange die Bedingung wahr ist.</t>
   </si>
   <si>
-    <t xml:space="preserve">15d2c1fa-c6cf-4096-8ec7-c403ce84e552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9eeabe03-4fd1-42bf-ace6-d1e607a5d3dc</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,62,65,67</t>
   </si>
   <si>
+    <t xml:space="preserve">acf82bde-ab5e-4f91-9613-3cb9e339abf0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30fc0f03-396a-4aa7-aadc-e31f812a3b7d</t>
+  </si>
+  <si>
     <t xml:space="preserve">Java bietet mit der For-Schleife eine Kontrollstruktur, die aus drei Teilen in runden Klammern besteht: Initialisierung (z.B. `int i = 0`), Bedingung (z.B. `i &lt;= 10`) und Inkrementierung (z.B. `i++`), die es ermöglichen, einen Codeblock wiederholt auszuführen, solange die Bedingung wahr ist. Es ist möglich, mehrere Operationen in den einzelnen Teilen der For-Schleife durchzuführen, aber üblicherweise wird sie für einfache Iterationen verwendet, wobei manchmal auch Befehle wie `continue` und `break` genutzt werden können, um die Schleifenausführung zu steuern.</t>
   </si>
   <si>
-    <t xml:space="preserve">acf82bde-ab5e-4f91-9613-3cb9e339abf0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30fc0f03-396a-4aa7-aadc-e31f812a3b7d</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,62,65,66,67</t>
   </si>
   <si>
     <t xml:space="preserve">Beispiele</t>
   </si>
   <si>
+    <t xml:space="preserve">2fc1faa3-550a-4714-a93c-eabeacdae78f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f6e07b01-b881-497c-b9fe-edf3ed625ca0</t>
+  </si>
+  <si>
     <t xml:space="preserve">In dem Beispiel BigX wird gezeigt, wie man mit Java Kontrollstrukturen wie for-Schleifen und if-Anweisungen ein großes "X" in der Konsole darstellen kann. Die Größe des "X" wird durch eine Variable bestimmt, und durch geschachtelte for-Schleifen und Bedingungen wird für jede Zeile und Spalte entschieden, ob ein "X" oder ein Leerzeichen ausgegeben wird, um die Form des "X" zu erzeugen.</t>
   </si>
   <si>
-    <t xml:space="preserve">2fc1faa3-550a-4714-a93c-eabeacdae78f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f6e07b01-b881-497c-b9fe-edf3ed625ca0</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,68</t>
   </si>
   <si>
@@ -1541,15 +1541,15 @@
     <t xml:space="preserve">43,68,71</t>
   </si>
   <si>
+    <t xml:space="preserve">a900435c-ff38-4581-b0b5-ea7a8bb19f5b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0fe0045b-e705-469a-b03c-f7518b289627</t>
+  </si>
+  <si>
     <t xml:space="preserve">Java bietet eine Vielzahl von Klassen und Paketen zur Dateiverarbeitung, die man durch Import-Anweisungen in den eigenen Code einbinden kann. Um Dateien zu lesen, zu schreiben und zu bearbeiten, muss man die entsprechenden Klassen und Methoden kennen und nutzen, wie zum Beispiel die File-Klasse für Dateioperationen und verschiedene Methoden für das Öffnen, Schließen, Lesen und Schreiben von Dateien, wobei oft ein Puffer verwendet wird, um die Effizienz zu steigern.</t>
   </si>
   <si>
-    <t xml:space="preserve">a900435c-ff38-4581-b0b5-ea7a8bb19f5b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0fe0045b-e705-469a-b03c-f7518b289627</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,72</t>
   </si>
   <si>
@@ -1610,18 +1610,18 @@
     <t xml:space="preserve">Arrays von Objekten</t>
   </si>
   <si>
+    <t xml:space="preserve">455206d3-9539-4992-bf35-22de72eebeb7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58f8c18d-9384-492a-a888-cb04cab44d6e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9f6ad498-221e-4dfc-bb43-d92e764c1512</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java können Arrays nicht nur primitive Datentypen wie Integers oder Doubles enthalten, sondern auch Objekte, wie zum Beispiel Instanzen der Klasse String oder benutzerdefinierte Klassen wie Enemies in einem Spiel. Um ein Array von Objekten zu verwenden, muss zuerst Speicherplatz für das Array reserviert werden, und anschließend müssen die einzelnen Objekte im Array mit dem Schlüsselwort 'new' tatsächlich erstellt werden, da anfänglich nur Referenzen ohne zugewiesene Objekte existieren.</t>
   </si>
   <si>
-    <t xml:space="preserve">455206d3-9539-4992-bf35-22de72eebeb7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58f8c18d-9384-492a-a888-cb04cab44d6e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9f6ad498-221e-4dfc-bb43-d92e764c1512</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,80</t>
   </si>
   <si>
@@ -1631,66 +1631,66 @@
     <t xml:space="preserve">43,80,81</t>
   </si>
   <si>
+    <t xml:space="preserve">2d3d318f-4e05-4874-8e7f-d14921296fb2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e48e4f32-cde6-4945-be3f-b120b1713a23</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java werden Methoden aufgerufen, indem man ihnen Parameter übergibt, die als Call-by-Value kopiert werden, wodurch die ursprünglichen Variablen unverändert bleiben. Beim Methodenaufruf werden die Parameterwerte auf den Stack kopiert und die Methode ausgeführt, wobei nach Beendigung der Methode die temporären Variablen auf dem Stack gelöscht werden und die ursprünglichen Variablen unverändert bleiben.</t>
   </si>
   <si>
-    <t xml:space="preserve">2d3d318f-4e05-4874-8e7f-d14921296fb2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e48e4f32-cde6-4945-be3f-b120b1713a23</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,80,82</t>
   </si>
   <si>
+    <t xml:space="preserve">ab7afeb0-e17f-44e9-8be8-b17cbc8f94b9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79876b13-9a54-4588-8591-644510f129fc</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java werden Objekte und Arrays als Referenzen an Methoden übergeben (Call-by-Reference), was bedeutet, dass Änderungen an den Objekten innerhalb der Methode auch außerhalb sichtbar sind, da nicht die Werte, sondern die Referenzen auf die Speicherorte der Objekte übergeben werden. Im Gegensatz dazu werden primitive Datentypen wie int als Werte übergeben (Call-by-Value), sodass Änderungen an diesen Parametern innerhalb der Methode nicht außerhalb der Methode sichtbar sind, da Kopien der Werte übergeben werden.</t>
   </si>
   <si>
-    <t xml:space="preserve">ab7afeb0-e17f-44e9-8be8-b17cbc8f94b9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79876b13-9a54-4588-8591-644510f129fc</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,80,83</t>
   </si>
   <si>
+    <t xml:space="preserve">36266628-c243-4351-9c54-72dbf08b903d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35a82a7b-2154-47e1-b3d2-20b47898197a</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java können Methoden überladen werden, indem man mehrere Methoden mit demselben Namen, aber unterschiedlichen Parametertypen oder -anzahlen definiert, sodass der Compiler anhand der übergebenen Argumente die richtige Methode auswählen kann. Überladene Methoden müssen sich in der Parameterliste unterscheiden, da der Rückgabetyp allein nicht ausreicht, um für den Compiler eine eindeutige Unterscheidung zu ermöglichen, was sonst zu Fehlern führen würde.</t>
   </si>
   <si>
-    <t xml:space="preserve">36266628-c243-4351-9c54-72dbf08b903d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35a82a7b-2154-47e1-b3d2-20b47898197a</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,80,84</t>
   </si>
   <si>
+    <t xml:space="preserve">7821b45e-3488-4818-930f-be6bde95f277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b2fab559-c5e9-417b-8340-a5b1be313da9</t>
+  </si>
+  <si>
     <t xml:space="preserve">Java-Methoden können rekursiv definiert werden, indem sie sich selbst innerhalb ihrer eigenen Definition aufrufen. Ein klassisches Beispiel für Rekursion in Java ist die Berechnung der Fakultät einer Zahl, bei der die Methode sich mit einem verminderten Wert erneut aufruft, bis der Basisfall erreicht ist, und dann die Ergebnisse auf dem Weg zurück nach oben multipliziert.</t>
   </si>
   <si>
-    <t xml:space="preserve">7821b45e-3488-4818-930f-be6bde95f277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b2fab559-c5e9-417b-8340-a5b1be313da9</t>
-  </si>
-  <si>
     <t xml:space="preserve">Die Unified Modeling Language (UML) ist eine standardisierte Modellierungssprache, die eine visuelle Darstellung von Software-Systemen ermöglicht, um Strukturen und Verhaltensweisen objektorientierter Programme zu veranschaulichen. Sie umfasst verschiedene Diagrammtypen wie Klassendiagramme, Sequenzdiagramme und Zustandsdiagramme, die Entwicklern helfen, Entwurfsmuster zu definieren und die Kommunikation innerhalb des Entwicklungsteams zu verbessern.</t>
   </si>
   <si>
     <t xml:space="preserve">43,85</t>
   </si>
   <si>
+    <t xml:space="preserve">67eea819-ab11-42ab-8c06-3bb5ad6aab13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3371631e-d626-4bfd-83a3-e3a4b8a9c3ce</t>
+  </si>
+  <si>
     <t xml:space="preserve">Java UML bezieht sich auf die Verwendung von Unified Modeling Language (UML) Diagrammen zur Darstellung und Planung der Struktur von Java-Programmen. UML-Diagramme helfen dabei, einen Überblick über die verschiedenen Klassen und ihre Beziehungen zueinander zu schaffen, was besonders nützlich ist, wenn Projekte komplexer werden und mehrere Klassen und Objekte involviert sind.</t>
   </si>
   <si>
-    <t xml:space="preserve">67eea819-ab11-42ab-8c06-3bb5ad6aab13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3371631e-d626-4bfd-83a3-e3a4b8a9c3ce</t>
-  </si>
-  <si>
     <t xml:space="preserve">b681b280-c818-4970-a531-2aafcf5b49c8</t>
   </si>
   <si>
@@ -1700,250 +1700,250 @@
     <t xml:space="preserve">43,85,86</t>
   </si>
   <si>
+    <t xml:space="preserve">8f589647-2d48-4438-b5cf-9d4988ba00f0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4dddc1e-5025-44ce-86bd-6813eaf394c3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Java UML Klassen dienen als Blaupausen für Objekte und definieren deren Struktur durch Attribute und Methoden. Während Attribute die Eigenschaften einer Klasse festlegen und Initialwerte haben können, ermöglichen Methoden die Manipulation dieser Eigenschaften und das Ausführen von Operationen; Klassen können in UML-Diagrammen unterschiedlich dargestellt werden, je nachdem ob sie Attribute, Methoden oder beides enthalten.</t>
   </si>
   <si>
-    <t xml:space="preserve">8f589647-2d48-4438-b5cf-9d4988ba00f0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d4dddc1e-5025-44ce-86bd-6813eaf394c3</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,85,87</t>
   </si>
   <si>
+    <t xml:space="preserve">7af88cb2-bab7-474c-a721-90b29cc868fa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23df0c13-c751-428f-86c9-6e615982aae8</t>
+  </si>
+  <si>
     <t xml:space="preserve">In UML (Unified Modeling Language) können Objekte als Instanzen von Klassen dargestellt werden, wobei Objekte klein und Klassen groß geschrieben werden, getrennt durch einen Doppelpunkt. Objekte werden mit ihren Attributen und Werten gezeigt, und Beziehungen zwischen Objekten werden durch Linien repräsentiert, wobei die Identität und Gleichheit von Objekten im Speicher durch ihre Darstellung unterschieden werden kann.</t>
   </si>
   <si>
-    <t xml:space="preserve">7af88cb2-bab7-474c-a721-90b29cc868fa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23df0c13-c751-428f-86c9-6e615982aae8</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,85,88</t>
   </si>
   <si>
+    <t xml:space="preserve">6156a4db-89f9-4f8f-b510-37e12793acec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4c43045d-3129-4be2-afc6-e04409e0a98e</t>
+  </si>
+  <si>
     <t xml:space="preserve">Java UML Attribute repräsentieren die Eigenschaften einer Klasse und können mit einer Multiplizität versehen werden, die angibt, wie viele Instanzen eines Attributs existieren dürfen. Diese Multiplizität wird in eckigen Klammern dargestellt, wobei die Untergrenze und Obergrenze durch zwei Punkte getrennt sind, und ein Stern (*) steht für eine unbestimmte Anzahl von Instanzen.</t>
   </si>
   <si>
-    <t xml:space="preserve">6156a4db-89f9-4f8f-b510-37e12793acec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4c43045d-3129-4be2-afc6-e04409e0a98e</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,85,89</t>
   </si>
   <si>
+    <t xml:space="preserve">9ce7ca44-357a-4395-9c38-157fb9b2afb2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ef2671f7-8ed4-4b6f-ae89-8a3a7ba115df</t>
+  </si>
+  <si>
     <t xml:space="preserve">In UML werden Operationen (Methoden) einer Klasse durch runde Klammern dargestellt, um sie von Attributen zu unterscheiden, die keine Klammern haben. Die Rückgabetypen und Parameter der Operationen werden in UML spezifiziert, wobei Parameter mit "In" für Eingabeparameter gekennzeichnet werden können und der Typ mit einem Doppelpunkt vom Namen getrennt wird, wobei UML im Gegensatz zu Java nicht sofort Typfehler aufzeigt.</t>
   </si>
   <si>
-    <t xml:space="preserve">9ce7ca44-357a-4395-9c38-157fb9b2afb2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ef2671f7-8ed4-4b6f-ae89-8a3a7ba115df</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,85,90</t>
   </si>
   <si>
+    <t xml:space="preserve">0e0fd849-4f1a-4485-9cdf-f79c487d50a9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7d587b36-db9d-40ab-b5a9-c248dd71001f</t>
+  </si>
+  <si>
     <t xml:space="preserve">Java UML Assoziationen beschreiben die Beziehungen zwischen verschiedenen Klassen in einem Klassendiagramm, wobei Assoziationen die Verbindungen zwischen Objekten darstellen und durch Linien repräsentiert werden. Diese Assoziationen können verschiedene Multiplizitäten aufweisen, die angeben, wie viele Instanzen einer Klasse mit Instanzen einer anderen Klasse in Beziehung stehen können, und können auch Rollennamen enthalten, die die Art der Beziehung näher spezifizieren.</t>
   </si>
   <si>
-    <t xml:space="preserve">0e0fd849-4f1a-4485-9cdf-f79c487d50a9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7d587b36-db9d-40ab-b5a9-c248dd71001f</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,85,90,91</t>
   </si>
   <si>
     <t xml:space="preserve">Navigierbarkeit</t>
   </si>
   <si>
+    <t xml:space="preserve">9f8bca8c-032a-4118-9eb4-96594f14fe3c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ad65fa04-8848-499c-8654-55e3f68d1fbb</t>
+  </si>
+  <si>
     <t xml:space="preserve">In UML-Diagrammen kann die Navigierbarkeit von Assoziationen zwischen Klassen durch Pfeile dargestellt werden, wobei die Richtung des Pfeils die Richtung der Navigierbarkeit angibt. In Java wird diese Navigierbarkeit durch Referenzvariablen als Attribute in den Klassen implementiert, wodurch Objekte einer Klasse auf assoziierte Objekte einer anderen Klasse zugreifen können.</t>
   </si>
   <si>
-    <t xml:space="preserve">9f8bca8c-032a-4118-9eb4-96594f14fe3c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ad65fa04-8848-499c-8654-55e3f68d1fbb</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,85,92</t>
   </si>
   <si>
+    <t xml:space="preserve">98667aa3-81c3-472e-8eda-849c71e4e278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95017bb3-978d-4cdd-917a-ba8de3c73014</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java UML Sichtbarkeit werden Attribute üblicherweise als privat (private) deklariert, um die Prinzipien der Objektorientierung wie Kapselung und klare Schnittstellen zu wahren. UML verwendet spezielle Symbole, um die Sichtbarkeit zu kennzeichnen: ein Plus für öffentlich (public), ein Minus für privat (private) und ein Pfund-Symbol für geschützt (protected), wobei Get- und Set-Methoden definiert werden müssen, um den Zugriff auf private Attribute zu ermöglichen.</t>
   </si>
   <si>
-    <t xml:space="preserve">98667aa3-81c3-472e-8eda-849c71e4e278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95017bb3-978d-4cdd-917a-ba8de3c73014</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vererbung in der objektorientierten Programmierung ermöglicht es, dass eine neue Klasse (Unterklasse) die Eigenschaften und Verhaltensweisen einer bestehenden Klasse (Oberklasse) übernehmen kann, wodurch Code-Wiederverwendung und hierarchische Klassifizierung unterstützt werden. Durch diesen Mechanismus können Unterklasse-Objekte auch als Instanzen ihrer Oberklasse betrachtet werden, was Polymorphismus und eine flexible und erweiterbare Code-Struktur fördert.</t>
   </si>
   <si>
     <t xml:space="preserve">43,93,94</t>
   </si>
   <si>
+    <t xml:space="preserve">15904bb0-804e-4ec1-b8f4-47b06070b23c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">536e041b-9888-4a91-acfa-908959ba9471</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java Vererbung und Generalisierung ermöglichen es, Klassen zu schaffen, die gemeinsame Attribute und Methoden von einer Oberklasse erben, um Redundanz zu vermeiden und eine hierarchische Struktur zu schaffen. Durch die Definition einer allgemeinen Klasse wie "Person" mit grundlegenden Eigenschaften und Methoden können spezifischere Klassen wie "Angestellter", "Student" und "Hilfskraft" diese erben und um zusätzliche, spezifische Merkmale erweitern, wodurch eine klare und effiziente Objekthierarchie entsteht.</t>
   </si>
   <si>
-    <t xml:space="preserve">15904bb0-804e-4ec1-b8f4-47b06070b23c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">536e041b-9888-4a91-acfa-908959ba9471</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,93,95</t>
   </si>
   <si>
+    <t xml:space="preserve">464f6a24-ba4e-44b2-bcea-e066758e1b24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">961e89af-cd16-4ede-ac9b-e16d8ddf9679</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java können Klassen und Operationen als abstrakt definiert werden, wobei abstrakte Klassen als Vorlage dienen, von denen andere Klassen Attribute und Methoden erben, ohne dass von der abstrakten Klasse selbst Objekte instanziiert werden. UML visualisiert abstrakte Klassen und Operationen durch Kursivschrift oder das Schlüsselwort "abstrakt", und in Java wird das Schlüsselwort `abstract` verwendet, um zu kennzeichnen, dass eine Klasse oder Methode abstrakt ist und von abgeleiteten Klassen implementiert werden muss.</t>
   </si>
   <si>
-    <t xml:space="preserve">464f6a24-ba4e-44b2-bcea-e066758e1b24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">961e89af-cd16-4ede-ac9b-e16d8ddf9679</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,85,93,96</t>
   </si>
   <si>
+    <t xml:space="preserve">46fd92aa-34de-4782-bf0c-3e5e4279c427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3f8ffed4-abd2-4c50-9c79-9788810b1ef3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36acc1c6-a4ec-41f1-9868-f597862a0c1a</t>
+  </si>
+  <si>
     <t xml:space="preserve">Java UML Interfaces repräsentieren abstrakte Klassen mit ausschließlich abstrakten Methoden, die als Schnittstellen dienen und die vollständige Abkapselung von Funktionalitäten ermöglichen. Sie legen fest, welche Methoden von implementierenden Klassen definiert werden müssen, ohne selbst Instanzen zu erzeugen, und dienen als Verträge zwischen verschiedenen Entwicklern, um die Interaktion zwischen verschiedenen Teilen eines Programms zu koordinieren.</t>
   </si>
   <si>
-    <t xml:space="preserve">46fd92aa-34de-4782-bf0c-3e5e4279c427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3f8ffed4-abd2-4c50-9c79-9788810b1ef3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36acc1c6-a4ec-41f1-9868-f597862a0c1a</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,85,93,97</t>
   </si>
   <si>
+    <t xml:space="preserve">6aeac450-f0f5-4235-b7df-cafcc9ae555f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4762eccf-5763-48d2-ab0f-21884328780c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ff59f2a4-660f-4f14-9f13-ce969939461a</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java UML Vererbung übernimmt eine Unterklasse alle Attribute, Methoden und Anfangswerte der Oberklasse, wobei Unterklassen nie etwas von der geerbten Funktionalität löschen können. Zusätzlich können Unterklassen das Verhalten von Methoden neu definieren, indem sie diese überschreiben, wobei die überschriebenen Methoden die gleiche Signatur wie die der Oberklasse haben müssen.</t>
   </si>
   <si>
-    <t xml:space="preserve">6aeac450-f0f5-4235-b7df-cafcc9ae555f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4762eccf-5763-48d2-ab0f-21884328780c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ff59f2a4-660f-4f14-9f13-ce969939461a</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,98</t>
   </si>
   <si>
+    <t xml:space="preserve">518e1e49-1530-450d-9935-11e1b558532a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de0b421b-5139-4136-baac-0b787b4753f3</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java ermöglicht Polymorphie, dass Methoden und Operatoren mehrere Formen annehmen können, indem sie mehrmals definiert und implementiert werden. Die Vererbungshierarchie und die Möglichkeit, Methoden zu überladen und zu überschreiben, erlauben es, dass Objekte einer Oberklasse als Objekte einer Unterklasse interpretiert werden können, wodurch zur Laufzeit die passende Methode dynamisch gebunden und ausgeführt wird, was als Polymorphismus bezeichnet wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">518e1e49-1530-450d-9935-11e1b558532a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">de0b421b-5139-4136-baac-0b787b4753f3</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,98,99</t>
   </si>
   <si>
+    <t xml:space="preserve">eaaf62a0-6720-469c-91c0-52b9e68bbbe6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a4d090b7-221c-4932-a309-ffab11522825</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java ist jede Klasse, die definiert wird, implizit eine Unterklasse der zentralen Objektklasse, wenn keine explizite Oberklasse angegeben wird. Diese Objektklasse stellt grundlegende Methoden wie toString und equals zur Verfügung, die von allen abgeleiteten Klassen genutzt und überschrieben werden können, um Polymorphie und andere objektorientierte Konzepte zu unterstützen.</t>
   </si>
   <si>
-    <t xml:space="preserve">eaaf62a0-6720-469c-91c0-52b9e68bbbe6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a4d090b7-221c-4932-a309-ffab11522825</t>
-  </si>
-  <si>
     <t xml:space="preserve">Die Ausnahmebehandlung in der Programmierung ermöglicht es, auf Fehler während der Ausführung eines Programms zu reagieren, indem Ausnahmen (Exceptions) abgefangen und entsprechend behandelt werden. In Java werden Ausnahmen mit try-catch-Blöcken gehandhabt, wobei der Code, der eine Ausnahme auslösen könnte, in den try-Block eingefügt und die Logik zur Fehlerbehandlung im catch-Block implementiert wird.</t>
   </si>
   <si>
     <t xml:space="preserve">43,100,101</t>
   </si>
   <si>
+    <t xml:space="preserve">92fec94f-be2b-4558-bf29-b623ed45131a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">570d6e9a-69cc-4479-abda-431dc9e17355</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java bezeichnet der Begriff "Exceptions" Ausnahmesituationen, die während der Ausführung eines Programms auftreten können, wenn etwas Unerwartetes geschieht, wie beispielsweise eine Division durch Null. Um solche Ausnahmen zu behandeln, bietet Java die Try-Catch-Blöcke an, in denen der Code, der eine Ausnahme auslösen könnte, in einem Try-Block platziert wird und die Behandlung der Ausnahme im zugehörigen Catch-Block erfolgt, wodurch der Code übersichtlicher und robuster gegenüber Fehlern wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">92fec94f-be2b-4558-bf29-b623ed45131a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">570d6e9a-69cc-4479-abda-431dc9e17355</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,100,101,102</t>
   </si>
   <si>
+    <t xml:space="preserve">f22f543e-2cbc-48aa-a268-549bbcdf8e34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c5228462-fbf2-477a-965b-31a18ecef87d</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Java können Entwickler eigene Ausnahmen definieren und mit dem Schlüsselwort `throw` auslösen, wobei oft ein neues Ausnahmeobjekt mit `new` erstellt wird. Die Ausnahmebehandlung erfolgt durch `try`-Blöcke, die gefolgt von `catch`-Blöcken sind, um spezifische Fehler zu fangen und zu behandeln, und optional einem `finally`-Block für Aufräumarbeiten, der unabhängig vom Erfolg der Fehlerbehandlung ausgeführt wird.</t>
   </si>
   <si>
-    <t xml:space="preserve">f22f543e-2cbc-48aa-a268-549bbcdf8e34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c5228462-fbf2-477a-965b-31a18ecef87d</t>
+    <t xml:space="preserve">21699b3f-2e32-45e2-a0a5-f671a0f98694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0c24b88b-ea6b-49f5-b6e2-a2ba29305814</t>
   </si>
   <si>
     <t xml:space="preserve">In Java können Ausnahmen mit Try-Catch-Blöcken behandelt werden, um Fehler während der Laufzeit zu handhaben, wie im Beispiel des WURTLE-Spiels gezeigt, bei dem Wörter aus einer Datei geladen werden. Wenn beim Laden der Datei ein Fehler auftritt, fängt der Catch-Block die Ausnahme ab und ermöglicht es dem Programm, mit einem Fallback-Wörterarray fortzufahren, ohne dass der Benutzer einen Fehler bemerkt.</t>
   </si>
   <si>
-    <t xml:space="preserve">21699b3f-2e32-45e2-a0a5-f671a0f98694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0c24b88b-ea6b-49f5-b6e2-a2ba29305814</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dateien sind digitale Container, die Daten auf Speichermedien wie Festplatten oder SSDs speichern und es ermöglichen, Informationen dauerhaft zu bewahren und zu übertragen. In der objektorientierten Programmierung, wie in Java, werden Dateien mithilfe von Klassen und Methoden gelesen, geschrieben und verwaltet, wobei die Abstraktion und Kapselung von Dateioperationen die Interaktion mit dem Dateisystem vereinfacht und sicherer macht.</t>
   </si>
   <si>
     <t xml:space="preserve">43,103,104</t>
   </si>
   <si>
+    <t xml:space="preserve">28d36645-53cb-48fe-93cc-2dc2b3876c8a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ff472184-baa6-4bd0-92ed-2ca9e91215f9</t>
+  </si>
+  <si>
     <t xml:space="preserve">Java Dateien Streams ermöglichen es, sequenziell Daten zu lesen und zu schreiben, indem sie eine konzeptionelle Darstellung von Datenflüssen als Ströme (Streams) verwenden. In Java gibt es verschiedene Klassen im Paket java.io, wie File-InputStream und File-OutputStream, um Dateien zu lesen bzw. zu schreiben, sowie weitere spezialisierte Streams für bidirektionale Zugriffe oder das Verarbeiten von Objekten und primitiven Datentypen.</t>
   </si>
   <si>
-    <t xml:space="preserve">28d36645-53cb-48fe-93cc-2dc2b3876c8a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ff472184-baa6-4bd0-92ed-2ca9e91215f9</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,103,105</t>
   </si>
   <si>
+    <t xml:space="preserve">1e770da7-7997-4b68-870b-b217491e3b49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e870474f-0b0d-4268-b517-a861b8f795a6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">922d59cb-9209-4533-a6a7-80f0b501a2f0</t>
+  </si>
+  <si>
     <t xml:space="preserve">Java-Dateien-Serialisierung ermöglicht es, komplexe Objektstrukturen, die im Speicher eines Programms existieren, in eine sequenzielle Byte-Reihenfolge umzuwandeln und dauerhaft zu speichern, um sie später wiederherstellen zu können. In Java wird dies durch die Implementierung des Serializable-Interfaces erreicht, wobei die Serialisierung und Deserialisierung von Objekten rekursiv erfolgt, um alle verknüpften Objekte und deren Attribute zu erfassen und in einem Stream zu speichern oder aus diesem zu lesen.</t>
   </si>
   <si>
-    <t xml:space="preserve">1e770da7-7997-4b68-870b-b217491e3b49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e870474f-0b0d-4268-b517-a861b8f795a6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">922d59cb-9209-4533-a6a7-80f0b501a2f0</t>
-  </si>
-  <si>
     <t xml:space="preserve">43,103,106</t>
   </si>
   <si>
+    <t xml:space="preserve">85929eed-e41b-4ad3-8824-fe50066cefdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">755c961e-2b0f-46a7-bcf0-eae69016c103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fab0567f-4eac-4351-a5b1-ea323b1549be</t>
+  </si>
+  <si>
     <t xml:space="preserve">Java bietet mit Reader und Writer Klassen eine Möglichkeit, Text zeichenorientiert statt byte-orientiert zu verarbeiten, was insbesondere für die strukturierte Ausgabe von Daten wie Studenteninformationen in Textdateien nützlich ist. Diese Klassen ermöglichen es, Daten zu lesen und zu schreiben, wobei die Daten als Strings repräsentiert werden, was mehr Speicherplatz beanspruchen kann als die reine Byte-Darstellung.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85929eed-e41b-4ad3-8824-fe50066cefdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">755c961e-2b0f-46a7-bcf0-eae69016c103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fab0567f-4eac-4351-a5b1-ea323b1549be</t>
   </si>
   <si>
     <t xml:space="preserve">43,107</t>
@@ -2140,6 +2140,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF2A6099"/>
       <name val="Calibri"/>
       <family val="0"/>
@@ -2150,13 +2157,6 @@
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
       <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2252,7 +2252,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2357,6 +2357,10 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2405,7 +2409,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2413,11 +2417,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2437,7 +2441,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2462,19 +2466,19 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="9" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="12" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="9" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="12" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -2485,12 +2489,12 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -2517,6 +2521,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2529,7 +2537,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2541,7 +2549,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2624,7 +2632,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I245"/>
-  <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.76953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.15"/>
@@ -6106,8 +6114,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AMJ125"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.41"/>
@@ -6118,13 +6126,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="31.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="11" style="0" width="12.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="63.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="10" style="0" width="12.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="26" width="63.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>186</v>
       </c>
@@ -6137,7 +6145,7 @@
       <c r="D1" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="27" t="s">
         <v>190</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -6153,7 +6161,7 @@
         <v>80</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>81</v>
+        <v>193</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>193</v>
@@ -6168,262 +6176,246 @@
         <v>193</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="P1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="P1" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="R1" s="27"/>
+      <c r="Q1" s="28"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="28" t="n">
+      <c r="A2" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="30" t="n">
+      <c r="B2" s="30"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="G2" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="28" t="n">
+      <c r="G2" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="I2" s="31"/>
+      <c r="I2" s="32"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="S2" s="15"/>
+      <c r="R2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="32" t="n">
+      <c r="A3" s="33" t="n">
         <v>3</v>
       </c>
       <c r="B3" s="24"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="34" t="s">
+      <c r="C3" s="33"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35" t="s">
         <v>197</v>
       </c>
       <c r="F3" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="G3" s="32" t="n">
+      <c r="G3" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="35" t="n">
+      <c r="H3" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="I3" s="36"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="38" t="s">
+      <c r="I3" s="37"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="R3" s="15"/>
+      <c r="Q3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="32" t="n">
+      <c r="A4" s="33" t="n">
         <v>4</v>
       </c>
       <c r="B4" s="24"/>
-      <c r="C4" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="33"/>
+      <c r="C4" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="34"/>
       <c r="E4" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="32" t="n">
+      <c r="G4" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="12"/>
-      <c r="K4" s="40" t="s">
+      <c r="H4" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="41" t="s">
         <v>200</v>
       </c>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="8" t="s">
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="Q4" s="38" t="s">
+      <c r="P4" s="39" t="s">
         <v>202</v>
       </c>
-      <c r="R4" s="41"/>
+      <c r="Q4" s="42"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="32" t="n">
+      <c r="A5" s="33" t="n">
         <v>5</v>
       </c>
       <c r="B5" s="24"/>
-      <c r="C5" s="32" t="n">
+      <c r="C5" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="33"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="F5" s="39" t="s">
+      <c r="F5" s="40" t="s">
         <v>204</v>
       </c>
-      <c r="G5" s="32" t="n">
+      <c r="G5" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="8" t="s">
+      <c r="H5" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="K5" s="40" t="s">
+      <c r="K5" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="L5" s="40" t="s">
+      <c r="L5" s="41"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="M5" s="40"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
       <c r="P5" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="Q5" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="R5" s="41"/>
+      <c r="Q5" s="42"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="42" t="n">
+      <c r="A6" s="43" t="n">
         <v>6</v>
       </c>
       <c r="B6" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="42" t="n">
+      <c r="C6" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43" t="s">
+      <c r="D6" s="44"/>
+      <c r="E6" s="44" t="s">
         <v>209</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G6" s="42" t="n">
+      <c r="G6" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="44" t="n">
+      <c r="H6" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="I6" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="47" t="s">
         <v>210</v>
       </c>
-      <c r="K6" s="46" t="s">
+      <c r="K6" s="47" t="s">
         <v>211</v>
       </c>
-      <c r="L6" s="46" t="s">
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="P6" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="46"/>
-      <c r="P6" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="R6" s="41"/>
+      <c r="Q6" s="42"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42" t="n">
+      <c r="A7" s="43" t="n">
         <v>7</v>
       </c>
       <c r="B7" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="42" t="n">
+      <c r="C7" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43" t="s">
+      <c r="D7" s="44"/>
+      <c r="E7" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="48" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="42" t="n">
+      <c r="G7" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="42" t="n">
+      <c r="H7" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="I7" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="47" t="s">
         <v>214</v>
       </c>
-      <c r="K7" s="46" t="s">
+      <c r="K7" s="47" t="s">
         <v>215</v>
       </c>
-      <c r="L7" s="46" t="s">
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="P7" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="R7" s="48"/>
+      <c r="Q7" s="49"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32" t="n">
+      <c r="A8" s="33" t="n">
         <v>8</v>
       </c>
       <c r="B8" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="32"/>
+      <c r="C8" s="33"/>
       <c r="D8" s="21"/>
       <c r="E8" s="21" t="s">
         <v>217</v>
@@ -6431,425 +6423,399 @@
       <c r="F8" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="G8" s="32" t="n">
+      <c r="G8" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="32" t="n">
+      <c r="H8" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="49"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="40" t="s">
+      <c r="I8" s="50"/>
+      <c r="J8" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="38" t="s">
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="R8" s="41"/>
+      <c r="Q8" s="42"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="32" t="n">
+      <c r="A9" s="33" t="n">
         <v>9</v>
       </c>
       <c r="B9" s="24"/>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="33" t="n">
         <v>5</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="G9" s="32" t="n">
+      <c r="G9" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="H9" s="51" t="n">
+      <c r="H9" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="8" t="s">
+      <c r="I9" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="41" t="s">
         <v>220</v>
       </c>
-      <c r="K9" s="40" t="s">
+      <c r="K9" s="41" t="s">
         <v>221</v>
       </c>
-      <c r="L9" s="40" t="s">
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
       <c r="P9" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="Q9" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="R9" s="48"/>
+      <c r="Q9" s="49"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="32" t="n">
+      <c r="A10" s="33" t="n">
         <v>10</v>
       </c>
       <c r="B10" s="24"/>
-      <c r="C10" s="32"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="24"/>
       <c r="E10" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="32" t="n">
+      <c r="G10" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="H10" s="51" t="n">
+      <c r="H10" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8" t="s">
+      <c r="I10" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="R10" s="41"/>
+      <c r="Q10" s="42"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="32" t="n">
+      <c r="A11" s="33" t="n">
         <v>11</v>
       </c>
       <c r="B11" s="24"/>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="33" t="n">
         <v>7</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="F11" s="52" t="s">
+      <c r="F11" s="53" t="s">
         <v>133</v>
       </c>
-      <c r="G11" s="32" t="n">
+      <c r="G11" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="H11" s="32" t="n">
+      <c r="H11" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="8" t="s">
+      <c r="I11" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="41" t="s">
         <v>227</v>
       </c>
-      <c r="K11" s="40" t="s">
+      <c r="K11" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="L11" s="40" t="s">
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="P11" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="R11" s="41"/>
+      <c r="Q11" s="42"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="32" t="n">
+      <c r="A12" s="33" t="n">
         <v>12</v>
       </c>
       <c r="B12" s="24"/>
-      <c r="C12" s="32" t="n">
+      <c r="C12" s="33" t="n">
         <v>8</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="24" t="s">
         <v>230</v>
       </c>
-      <c r="F12" s="52" t="s">
+      <c r="F12" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="G12" s="32" t="n">
+      <c r="G12" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="H12" s="32" t="n">
+      <c r="H12" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I12" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="8" t="s">
+      <c r="I12" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="41" t="s">
         <v>231</v>
       </c>
-      <c r="K12" s="40" t="s">
+      <c r="K12" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="L12" s="40" t="s">
+      <c r="L12" s="41"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="P12" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="M12" s="40"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="R12" s="41"/>
+      <c r="Q12" s="42"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="32" t="n">
+      <c r="A13" s="33" t="n">
         <v>13</v>
       </c>
       <c r="B13" s="24"/>
-      <c r="C13" s="32" t="n">
+      <c r="C13" s="33" t="n">
         <v>9</v>
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="F13" s="52" t="s">
+      <c r="F13" s="53" t="s">
         <v>235</v>
       </c>
-      <c r="G13" s="32" t="n">
+      <c r="G13" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="H13" s="32" t="n">
+      <c r="H13" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="8" t="s">
+      <c r="I13" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="41" t="s">
         <v>236</v>
       </c>
-      <c r="K13" s="40" t="s">
+      <c r="K13" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="L13" s="40" t="s">
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
       <c r="P13" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="Q13" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="R13" s="41"/>
+      <c r="Q13" s="42"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32" t="n">
+      <c r="A14" s="33" t="n">
         <v>14</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>240</v>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C14" s="33" t="n">
         <v>10</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="24" t="s">
         <v>241</v>
       </c>
-      <c r="F14" s="52" t="s">
+      <c r="F14" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="G14" s="32" t="n">
+      <c r="G14" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="H14" s="32" t="n">
+      <c r="H14" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="8" t="s">
+      <c r="I14" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="K14" s="40" t="s">
+      <c r="K14" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="L14" s="40" t="s">
+      <c r="L14" s="41"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="P14" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="M14" s="40"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="R14" s="41"/>
+      <c r="Q14" s="42"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="32" t="n">
+      <c r="A15" s="33" t="n">
         <v>16</v>
       </c>
       <c r="B15" s="24"/>
-      <c r="C15" s="32" t="n">
+      <c r="C15" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="24" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="G15" s="32" t="n">
+      <c r="G15" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="H15" s="32" t="n">
+      <c r="H15" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="8" t="s">
+      <c r="I15" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="41" t="s">
         <v>246</v>
       </c>
-      <c r="K15" s="40" t="s">
+      <c r="K15" s="41" t="s">
         <v>247</v>
       </c>
-      <c r="L15" s="40" t="s">
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="P15" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="R15" s="41"/>
+      <c r="Q15" s="42"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="32" t="n">
+      <c r="A16" s="33" t="n">
         <v>17</v>
       </c>
       <c r="B16" s="24"/>
-      <c r="C16" s="32" t="n">
+      <c r="C16" s="33" t="n">
         <v>13</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="G16" s="32" t="n">
+      <c r="G16" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="H16" s="32" t="n">
+      <c r="H16" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="8" t="s">
+      <c r="I16" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="K16" s="40" t="s">
+      <c r="K16" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="L16" s="40" t="s">
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="P16" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="R16" s="41"/>
+      <c r="Q16" s="42"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="32" t="n">
+      <c r="A17" s="33" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="C17" s="32" t="n">
+      <c r="C17" s="33" t="n">
         <v>11</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24" t="s">
         <v>254</v>
       </c>
-      <c r="F17" s="52" t="s">
+      <c r="F17" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="G17" s="49" t="n">
+      <c r="G17" s="50" t="n">
         <v>8</v>
       </c>
-      <c r="H17" s="32" t="n">
+      <c r="H17" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I17" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="I17" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="41" t="s">
         <v>255</v>
       </c>
-      <c r="K17" s="40" t="s">
+      <c r="K17" s="41" t="s">
         <v>256</v>
       </c>
-      <c r="L17" s="40" t="s">
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="P17" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q17" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="R17" s="41"/>
+      <c r="Q17" s="42"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="42" t="n">
+      <c r="A18" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="B18" s="53" t="n">
+      <c r="B18" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="42" t="n">
+      <c r="C18" s="43" t="n">
         <v>14</v>
       </c>
       <c r="D18" s="23"/>
@@ -6859,369 +6825,356 @@
       <c r="F18" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="42" t="n">
+      <c r="G18" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="42" t="n">
+      <c r="H18" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="5" t="s">
+      <c r="I18" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47" t="s">
         <v>259</v>
       </c>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46" t="s">
+      <c r="L18" s="47"/>
+      <c r="M18" s="47"/>
+      <c r="N18" s="47"/>
+      <c r="O18" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="M18" s="46"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="46"/>
       <c r="P18" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="Q18" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="R18" s="41"/>
+      <c r="Q18" s="42"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="42" t="n">
+      <c r="A19" s="43" t="n">
         <v>19</v>
       </c>
       <c r="B19" s="23"/>
-      <c r="C19" s="42" t="n">
+      <c r="C19" s="43" t="n">
         <v>15</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="23" t="s">
         <v>262</v>
       </c>
-      <c r="F19" s="47" t="s">
+      <c r="F19" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="G19" s="42" t="n">
+      <c r="G19" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="H19" s="42" t="n">
+      <c r="H19" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="5" t="s">
+      <c r="I19" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="47" t="s">
         <v>263</v>
       </c>
-      <c r="K19" s="46" t="s">
+      <c r="K19" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="L19" s="46" t="s">
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46"/>
-      <c r="O19" s="46"/>
       <c r="P19" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="Q19" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="R19" s="48"/>
+      <c r="Q19" s="49"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="42" t="n">
+      <c r="A20" s="43" t="n">
         <v>20</v>
       </c>
       <c r="B20" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="42"/>
+      <c r="C20" s="43"/>
       <c r="D20" s="23" t="n">
         <v>19</v>
       </c>
       <c r="E20" s="23" t="s">
         <v>267</v>
       </c>
-      <c r="F20" s="47" t="s">
+      <c r="F20" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="G20" s="42" t="n">
+      <c r="G20" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="H20" s="42" t="n">
+      <c r="H20" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="I20" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="20"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="46"/>
-      <c r="O20" s="46"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="54" t="s">
+      <c r="I20" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="47"/>
+      <c r="K20" s="47"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="47"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="55" t="s">
         <v>268</v>
       </c>
-      <c r="R20" s="41"/>
+      <c r="Q20" s="42"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="42" t="n">
+      <c r="A21" s="43" t="n">
         <v>21</v>
       </c>
       <c r="B21" s="23"/>
-      <c r="C21" s="42" t="n">
+      <c r="C21" s="43" t="n">
         <v>17</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="F21" s="55" t="s">
+      <c r="F21" s="56" t="s">
         <v>270</v>
       </c>
-      <c r="G21" s="42" t="n">
+      <c r="G21" s="43" t="n">
         <v>20</v>
       </c>
-      <c r="H21" s="42" t="n">
+      <c r="H21" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="I21" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="5" t="s">
+      <c r="I21" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="47"/>
+      <c r="K21" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46" t="s">
+      <c r="L21" s="47"/>
+      <c r="M21" s="47" t="s">
         <v>272</v>
       </c>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46" t="s">
+      <c r="N21" s="47"/>
+      <c r="O21" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="O21" s="46"/>
       <c r="P21" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="Q21" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="R21" s="41"/>
+      <c r="Q21" s="42"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="42" t="n">
+      <c r="A22" s="43" t="n">
         <v>22</v>
       </c>
       <c r="B22" s="23"/>
-      <c r="C22" s="42" t="n">
+      <c r="C22" s="43" t="n">
         <v>18</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="23" t="s">
         <v>275</v>
       </c>
-      <c r="F22" s="55" t="s">
+      <c r="F22" s="56" t="s">
         <v>276</v>
       </c>
-      <c r="G22" s="42" t="n">
+      <c r="G22" s="43" t="n">
         <v>20</v>
       </c>
-      <c r="H22" s="42" t="n">
+      <c r="H22" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="I22" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="5" t="s">
+      <c r="I22" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="47" t="s">
         <v>277</v>
       </c>
-      <c r="K22" s="46" t="s">
+      <c r="K22" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="L22" s="46" t="s">
+      <c r="L22" s="47"/>
+      <c r="M22" s="47" t="s">
         <v>279</v>
       </c>
-      <c r="M22" s="46"/>
-      <c r="N22" s="46" t="s">
+      <c r="N22" s="47"/>
+      <c r="O22" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="O22" s="46"/>
       <c r="P22" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="Q22" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="R22" s="48"/>
-    </row>
-    <row r="23" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="56" t="n">
+      <c r="Q22" s="49"/>
+    </row>
+    <row r="23" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="57" t="n">
         <v>39</v>
       </c>
-      <c r="B23" s="57" t="n">
+      <c r="B23" s="58" t="n">
         <v>8</v>
       </c>
-      <c r="C23" s="56"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57" t="s">
+      <c r="C23" s="57"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58" t="s">
         <v>282</v>
       </c>
-      <c r="F23" s="57" t="s">
+      <c r="F23" s="58" t="s">
         <v>126</v>
       </c>
-      <c r="G23" s="56" t="n">
+      <c r="G23" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="56" t="n">
+      <c r="H23" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="I23" s="56"/>
-      <c r="J23" s="58"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="59"/>
       <c r="K23" s="59"/>
       <c r="L23" s="59"/>
       <c r="M23" s="59"/>
       <c r="N23" s="59"/>
-      <c r="O23" s="59"/>
-      <c r="P23" s="58"/>
-      <c r="Q23" s="5" t="s">
+      <c r="O23" s="60"/>
+      <c r="P23" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="R23" s="60"/>
-    </row>
-    <row r="24" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="56" t="n">
+      <c r="Q23" s="61"/>
+      <c r="AMJ23" s="0"/>
+    </row>
+    <row r="24" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="57" t="n">
         <v>40</v>
       </c>
-      <c r="B24" s="57"/>
-      <c r="C24" s="56" t="n">
+      <c r="B24" s="58"/>
+      <c r="C24" s="57" t="n">
         <v>42</v>
       </c>
-      <c r="D24" s="57"/>
-      <c r="E24" s="57" t="s">
+      <c r="D24" s="58"/>
+      <c r="E24" s="58" t="s">
         <v>284</v>
       </c>
-      <c r="F24" s="62" t="s">
+      <c r="F24" s="63" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="56" t="n">
+      <c r="G24" s="57" t="n">
         <v>39</v>
       </c>
-      <c r="H24" s="56" t="n">
+      <c r="H24" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="I24" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="58"/>
-      <c r="K24" s="59"/>
-      <c r="L24" s="59" t="s">
+      <c r="I24" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="59"/>
+      <c r="K24" s="59" t="s">
         <v>285</v>
       </c>
-      <c r="M24" s="59"/>
-      <c r="N24" s="59" t="s">
+      <c r="L24" s="59"/>
+      <c r="M24" s="59" t="s">
         <v>286</v>
       </c>
-      <c r="O24" s="59"/>
-      <c r="P24" s="58" t="s">
+      <c r="N24" s="59"/>
+      <c r="O24" s="60" t="s">
         <v>287</v>
       </c>
-      <c r="Q24" s="5" t="s">
+      <c r="P24" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="R24" s="63"/>
-    </row>
-    <row r="25" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="56" t="n">
+      <c r="Q24" s="64"/>
+      <c r="AMJ24" s="0"/>
+    </row>
+    <row r="25" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="57" t="n">
         <v>41</v>
       </c>
-      <c r="B25" s="57"/>
-      <c r="C25" s="56" t="n">
+      <c r="B25" s="58"/>
+      <c r="C25" s="57" t="n">
         <v>43</v>
       </c>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57" t="s">
+      <c r="D25" s="58"/>
+      <c r="E25" s="58" t="s">
         <v>289</v>
       </c>
-      <c r="F25" s="62" t="s">
+      <c r="F25" s="63" t="s">
         <v>128</v>
       </c>
-      <c r="G25" s="56" t="n">
+      <c r="G25" s="57" t="n">
         <v>39</v>
       </c>
-      <c r="H25" s="56" t="n">
+      <c r="H25" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="I25" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="58"/>
+      <c r="I25" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="59"/>
       <c r="K25" s="59"/>
       <c r="L25" s="59"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="59" t="s">
+      <c r="M25" s="59" t="s">
         <v>290</v>
       </c>
-      <c r="O25" s="59"/>
-      <c r="P25" s="58" t="s">
+      <c r="N25" s="59"/>
+      <c r="O25" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="Q25" s="5" t="s">
+      <c r="P25" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="R25" s="63"/>
-    </row>
-    <row r="26" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="56" t="n">
+      <c r="Q25" s="64"/>
+      <c r="AMJ25" s="0"/>
+    </row>
+    <row r="26" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="57" t="n">
         <v>42</v>
       </c>
-      <c r="B26" s="57"/>
-      <c r="C26" s="56" t="n">
+      <c r="B26" s="58"/>
+      <c r="C26" s="57" t="n">
         <v>44</v>
       </c>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57" t="s">
+      <c r="D26" s="58"/>
+      <c r="E26" s="58" t="s">
         <v>292</v>
       </c>
-      <c r="F26" s="62" t="s">
+      <c r="F26" s="63" t="s">
         <v>129</v>
       </c>
-      <c r="G26" s="56" t="n">
+      <c r="G26" s="57" t="n">
         <v>39</v>
       </c>
-      <c r="H26" s="56" t="n">
+      <c r="H26" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="I26" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="58"/>
+      <c r="I26" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="59"/>
       <c r="K26" s="59"/>
       <c r="L26" s="59"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="59" t="s">
+      <c r="M26" s="59" t="s">
         <v>293</v>
       </c>
-      <c r="O26" s="59"/>
-      <c r="P26" s="58" t="s">
+      <c r="N26" s="59"/>
+      <c r="O26" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="Q26" s="5" t="s">
+      <c r="P26" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="R26" s="63"/>
-    </row>
-    <row r="27" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="32" t="n">
+      <c r="Q26" s="64"/>
+      <c r="AMJ26" s="0"/>
+    </row>
+    <row r="27" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="33" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="24" t="n">
         <v>8.39</v>
       </c>
-      <c r="C27" s="32" t="n">
+      <c r="C27" s="33" t="n">
         <v>19</v>
       </c>
       <c r="D27" s="24"/>
@@ -7231,35 +7184,35 @@
       <c r="F27" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="G27" s="32" t="n">
+      <c r="G27" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="32" t="n">
+      <c r="H27" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="I27" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="8"/>
-      <c r="K27" s="40" t="s">
+      <c r="I27" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="41" t="s">
         <v>296</v>
       </c>
-      <c r="L27" s="40"/>
-      <c r="M27" s="40"/>
-      <c r="N27" s="40"/>
-      <c r="O27" s="40"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="8" t="s">
+        <v>108</v>
+      </c>
       <c r="P27" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q27" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="R27" s="60"/>
-    </row>
-    <row r="28" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="32"/>
+      <c r="Q27" s="61"/>
+      <c r="AMJ27" s="0"/>
+    </row>
+    <row r="28" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="33"/>
       <c r="B28" s="24"/>
-      <c r="C28" s="32" t="n">
+      <c r="C28" s="33" t="n">
         <v>20</v>
       </c>
       <c r="D28" s="24"/>
@@ -7267,716 +7220,688 @@
         <v>295</v>
       </c>
       <c r="F28" s="24"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="8" t="s">
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41" t="s">
         <v>298</v>
       </c>
-      <c r="K28" s="40"/>
-      <c r="L28" s="40" t="s">
+      <c r="L28" s="41"/>
+      <c r="M28" s="41" t="s">
         <v>299</v>
       </c>
-      <c r="M28" s="40"/>
-      <c r="N28" s="40" t="s">
+      <c r="N28" s="41"/>
+      <c r="O28" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="O28" s="40"/>
       <c r="P28" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="Q28" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="R28" s="60"/>
-    </row>
-    <row r="29" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="32"/>
+      <c r="Q28" s="61"/>
+      <c r="AMJ28" s="0"/>
+    </row>
+    <row r="29" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="33"/>
       <c r="B29" s="24"/>
-      <c r="C29" s="32" t="n">
+      <c r="C29" s="33" t="n">
         <v>21</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="F29" s="39" t="s">
+      <c r="F29" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="G29" s="32" t="n">
+      <c r="G29" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="8" t="s">
+      <c r="H29" s="33"/>
+      <c r="I29" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="41" t="s">
         <v>302</v>
       </c>
-      <c r="K29" s="40" t="s">
+      <c r="K29" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="L29" s="40" t="s">
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="M29" s="40"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="40"/>
       <c r="P29" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="Q29" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="R29" s="60"/>
-    </row>
-    <row r="30" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32" t="n">
+      <c r="Q29" s="61"/>
+      <c r="AMJ29" s="0"/>
+    </row>
+    <row r="30" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="33" t="n">
         <v>24</v>
       </c>
       <c r="B30" s="24"/>
-      <c r="C30" s="32" t="n">
+      <c r="C30" s="33" t="n">
         <v>22</v>
       </c>
       <c r="D30" s="24"/>
       <c r="E30" s="24" t="s">
         <v>306</v>
       </c>
-      <c r="F30" s="39" t="s">
+      <c r="F30" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="G30" s="32" t="n">
+      <c r="G30" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="H30" s="32" t="n">
+      <c r="H30" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I30" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="8" t="s">
+      <c r="I30" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="41" t="s">
         <v>307</v>
       </c>
-      <c r="K30" s="40" t="s">
+      <c r="K30" s="41" t="s">
         <v>308</v>
       </c>
-      <c r="L30" s="40" t="s">
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="M30" s="40"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="40"/>
       <c r="P30" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="Q30" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="R30" s="60"/>
-    </row>
-    <row r="31" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="32" t="n">
+      <c r="Q30" s="61"/>
+      <c r="AMJ30" s="0"/>
+    </row>
+    <row r="31" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="33" t="n">
         <v>25</v>
       </c>
       <c r="B31" s="24"/>
-      <c r="C31" s="32" t="n">
+      <c r="C31" s="33" t="n">
         <v>23</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24" t="s">
         <v>311</v>
       </c>
-      <c r="F31" s="39" t="s">
+      <c r="F31" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="G31" s="32" t="n">
+      <c r="G31" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="H31" s="32" t="n">
+      <c r="H31" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="I31" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="8" t="s">
+      <c r="I31" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="41" t="s">
         <v>312</v>
       </c>
-      <c r="K31" s="40" t="s">
+      <c r="K31" s="41" t="s">
         <v>313</v>
       </c>
-      <c r="L31" s="40" t="s">
+      <c r="L31" s="41"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="41"/>
+      <c r="O31" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="M31" s="40"/>
-      <c r="N31" s="40"/>
-      <c r="O31" s="40"/>
       <c r="P31" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="Q31" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="R31" s="60"/>
-    </row>
-    <row r="32" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="32" t="n">
+      <c r="Q31" s="61"/>
+      <c r="AMJ31" s="0"/>
+    </row>
+    <row r="32" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="33" t="n">
         <v>26</v>
       </c>
       <c r="B32" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="C32" s="32" t="n">
+      <c r="C32" s="33" t="n">
         <v>24</v>
       </c>
       <c r="D32" s="24"/>
       <c r="E32" s="24" t="s">
         <v>316</v>
       </c>
-      <c r="F32" s="64" t="s">
+      <c r="F32" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="G32" s="49" t="n">
+      <c r="G32" s="50" t="n">
         <v>23</v>
       </c>
-      <c r="H32" s="49" t="n">
+      <c r="H32" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="I32" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="8" t="s">
+      <c r="I32" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="41" t="s">
         <v>317</v>
       </c>
-      <c r="K32" s="40" t="s">
+      <c r="K32" s="41" t="s">
         <v>318</v>
       </c>
-      <c r="L32" s="40" t="s">
+      <c r="L32" s="41" t="s">
         <v>319</v>
       </c>
-      <c r="M32" s="40" t="s">
+      <c r="M32" s="41"/>
+      <c r="N32" s="41"/>
+      <c r="O32" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="P32" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="N32" s="40"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q32" s="8" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="33" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="32"/>
+      <c r="AMJ32" s="0"/>
+    </row>
+    <row r="33" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="33"/>
       <c r="B33" s="24"/>
-      <c r="C33" s="32" t="n">
+      <c r="C33" s="33" t="n">
         <v>25</v>
       </c>
       <c r="D33" s="24"/>
       <c r="E33" s="24" t="s">
         <v>316</v>
       </c>
-      <c r="F33" s="39" t="s">
+      <c r="F33" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="G33" s="32" t="n">
+      <c r="G33" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="8"/>
-      <c r="K33" s="40" t="s">
+      <c r="H33" s="33"/>
+      <c r="I33" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="41" t="s">
         <v>321</v>
       </c>
-      <c r="L33" s="40"/>
-      <c r="M33" s="40"/>
-      <c r="N33" s="40"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="8" t="s">
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41"/>
+      <c r="O33" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="60"/>
-    </row>
-    <row r="34" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="32" t="n">
+      <c r="P33" s="8"/>
+      <c r="Q33" s="61"/>
+      <c r="AMJ33" s="0"/>
+    </row>
+    <row r="34" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="33" t="n">
         <v>27</v>
       </c>
       <c r="B34" s="24" t="s">
         <v>323</v>
       </c>
-      <c r="C34" s="32" t="n">
+      <c r="C34" s="33" t="n">
         <v>26</v>
       </c>
       <c r="D34" s="24"/>
       <c r="E34" s="24" t="s">
         <v>324</v>
       </c>
-      <c r="F34" s="39" t="s">
+      <c r="F34" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="G34" s="32" t="n">
+      <c r="G34" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="32" t="n">
+      <c r="H34" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I34" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="8" t="s">
+      <c r="I34" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="41" t="s">
         <v>325</v>
       </c>
-      <c r="K34" s="40" t="s">
+      <c r="K34" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="L34" s="40" t="s">
+      <c r="L34" s="41"/>
+      <c r="M34" s="41"/>
+      <c r="N34" s="41"/>
+      <c r="O34" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P34" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="M34" s="40"/>
-      <c r="N34" s="40"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q34" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="R34" s="60"/>
-    </row>
-    <row r="35" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="32" t="n">
+      <c r="Q34" s="61"/>
+      <c r="AMJ34" s="0"/>
+    </row>
+    <row r="35" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="33" t="n">
         <v>28</v>
       </c>
       <c r="B35" s="24" t="n">
         <v>26</v>
       </c>
-      <c r="C35" s="32" t="n">
+      <c r="C35" s="33" t="n">
         <v>27</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="24" t="s">
         <v>328</v>
       </c>
-      <c r="F35" s="39" t="s">
+      <c r="F35" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="G35" s="32" t="n">
+      <c r="G35" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="H35" s="32" t="n">
+      <c r="H35" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="I35" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="8" t="s">
+      <c r="I35" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="41" t="s">
         <v>329</v>
       </c>
-      <c r="K35" s="40" t="s">
+      <c r="K35" s="41" t="s">
         <v>330</v>
       </c>
-      <c r="L35" s="40" t="s">
+      <c r="L35" s="41"/>
+      <c r="M35" s="41"/>
+      <c r="N35" s="41"/>
+      <c r="O35" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="P35" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="M35" s="40"/>
-      <c r="N35" s="40"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q35" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="R35" s="60"/>
-    </row>
-    <row r="36" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="42" t="n">
+      <c r="Q35" s="61"/>
+      <c r="AMJ35" s="0"/>
+    </row>
+    <row r="36" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="43" t="n">
         <v>29</v>
       </c>
       <c r="B36" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="C36" s="42" t="n">
+      <c r="C36" s="43" t="n">
         <v>28</v>
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="23" t="s">
         <v>332</v>
       </c>
-      <c r="F36" s="43" t="s">
+      <c r="F36" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="G36" s="45" t="n">
+      <c r="G36" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="45" t="n">
+      <c r="H36" s="46" t="n">
         <v>6</v>
       </c>
-      <c r="I36" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="5" t="s">
+      <c r="I36" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="47" t="s">
         <v>333</v>
       </c>
-      <c r="K36" s="46" t="s">
+      <c r="K36" s="47" t="s">
         <v>334</v>
       </c>
-      <c r="L36" s="46" t="s">
+      <c r="L36" s="47"/>
+      <c r="M36" s="47"/>
+      <c r="N36" s="47"/>
+      <c r="O36" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="P36" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="M36" s="46"/>
-      <c r="N36" s="46"/>
-      <c r="O36" s="46"/>
-      <c r="P36" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q36" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="R36" s="60"/>
-    </row>
-    <row r="37" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="42" t="n">
+      <c r="Q36" s="61"/>
+      <c r="AMJ36" s="0"/>
+    </row>
+    <row r="37" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="43" t="n">
         <v>30</v>
       </c>
       <c r="B37" s="23"/>
-      <c r="C37" s="42" t="n">
+      <c r="C37" s="43" t="n">
         <v>29</v>
       </c>
       <c r="D37" s="23"/>
       <c r="E37" s="23" t="s">
         <v>336</v>
       </c>
-      <c r="F37" s="65" t="s">
+      <c r="F37" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="G37" s="45" t="n">
+      <c r="G37" s="46" t="n">
         <v>29</v>
       </c>
-      <c r="H37" s="45" t="n">
+      <c r="H37" s="46" t="n">
         <v>6</v>
       </c>
-      <c r="I37" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="5" t="s">
+      <c r="I37" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="47" t="s">
         <v>337</v>
       </c>
-      <c r="K37" s="46" t="s">
+      <c r="K37" s="47" t="s">
         <v>338</v>
       </c>
-      <c r="L37" s="46" t="s">
+      <c r="L37" s="47"/>
+      <c r="M37" s="47"/>
+      <c r="N37" s="47"/>
+      <c r="O37" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="M37" s="46"/>
-      <c r="N37" s="46"/>
-      <c r="O37" s="46"/>
       <c r="P37" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="Q37" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="R37" s="63"/>
-    </row>
-    <row r="38" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="56" t="n">
+      <c r="Q37" s="64"/>
+      <c r="AMJ37" s="0"/>
+    </row>
+    <row r="38" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="57" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="57" t="n">
+      <c r="B38" s="58" t="n">
         <v>23</v>
       </c>
-      <c r="C38" s="56" t="n">
+      <c r="C38" s="57" t="n">
         <v>33</v>
       </c>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57" t="s">
+      <c r="D38" s="58"/>
+      <c r="E38" s="58" t="s">
         <v>341</v>
       </c>
-      <c r="F38" s="57" t="s">
+      <c r="F38" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="G38" s="56" t="n">
+      <c r="G38" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="56" t="n">
+      <c r="H38" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="I38" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="58" t="s">
+      <c r="I38" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="59" t="s">
         <v>342</v>
       </c>
       <c r="K38" s="59" t="s">
         <v>343</v>
       </c>
-      <c r="L38" s="59" t="s">
+      <c r="L38" s="59"/>
+      <c r="M38" s="59" t="s">
         <v>344</v>
       </c>
-      <c r="M38" s="59"/>
       <c r="N38" s="59" t="s">
         <v>345</v>
       </c>
-      <c r="O38" s="59" t="s">
+      <c r="O38" s="60" t="s">
+        <v>121</v>
+      </c>
+      <c r="P38" s="67" t="s">
         <v>346</v>
       </c>
-      <c r="P38" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q38" s="58" t="s">
-        <v>342</v>
-      </c>
-      <c r="R38" s="60"/>
-    </row>
-    <row r="39" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="56"/>
-      <c r="B39" s="57"/>
-      <c r="C39" s="56" t="n">
+      <c r="Q38" s="61"/>
+      <c r="AMJ38" s="0"/>
+    </row>
+    <row r="39" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="57"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="57" t="n">
         <v>34</v>
       </c>
-      <c r="D39" s="57"/>
-      <c r="E39" s="57" t="s">
+      <c r="D39" s="58"/>
+      <c r="E39" s="58" t="s">
         <v>341</v>
       </c>
-      <c r="F39" s="57"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="58" t="s">
+      <c r="F39" s="58"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="59"/>
+      <c r="K39" s="59" t="s">
         <v>347</v>
       </c>
-      <c r="K39" s="59"/>
-      <c r="L39" s="59" t="s">
+      <c r="L39" s="59"/>
+      <c r="M39" s="59" t="s">
         <v>348</v>
       </c>
-      <c r="M39" s="59"/>
-      <c r="N39" s="59" t="s">
+      <c r="N39" s="59"/>
+      <c r="O39" s="60" t="s">
         <v>349</v>
       </c>
-      <c r="O39" s="59"/>
-      <c r="P39" s="58" t="s">
+      <c r="P39" s="67" t="s">
         <v>350</v>
       </c>
-      <c r="Q39" s="58" t="s">
-        <v>347</v>
-      </c>
-      <c r="R39" s="60"/>
-    </row>
-    <row r="40" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="56"/>
-      <c r="B40" s="57"/>
-      <c r="C40" s="56" t="n">
+      <c r="Q39" s="61"/>
+      <c r="AMJ39" s="0"/>
+    </row>
+    <row r="40" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="57"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="57" t="n">
         <v>35</v>
       </c>
-      <c r="D40" s="57"/>
-      <c r="E40" s="57" t="s">
+      <c r="D40" s="58"/>
+      <c r="E40" s="58" t="s">
         <v>341</v>
       </c>
-      <c r="F40" s="62" t="s">
+      <c r="F40" s="63" t="s">
         <v>109</v>
       </c>
-      <c r="G40" s="56" t="n">
+      <c r="G40" s="57" t="n">
         <v>34</v>
       </c>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="58" t="s">
+      <c r="H40" s="57"/>
+      <c r="I40" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="59" t="s">
         <v>351</v>
       </c>
       <c r="K40" s="59" t="s">
         <v>352</v>
       </c>
-      <c r="L40" s="59" t="s">
-        <v>353</v>
-      </c>
+      <c r="L40" s="59"/>
       <c r="M40" s="59"/>
       <c r="N40" s="59"/>
-      <c r="O40" s="59"/>
-      <c r="P40" s="58" t="s">
+      <c r="O40" s="60" t="s">
+        <v>353</v>
+      </c>
+      <c r="P40" s="67" t="s">
         <v>354</v>
       </c>
-      <c r="Q40" s="58" t="s">
-        <v>351</v>
-      </c>
-      <c r="R40" s="63"/>
-    </row>
-    <row r="41" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="32" t="n">
+      <c r="Q40" s="64"/>
+      <c r="AMJ40" s="0"/>
+    </row>
+    <row r="41" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="33" t="n">
         <v>31</v>
       </c>
       <c r="B41" s="24" t="s">
         <v>355</v>
       </c>
-      <c r="C41" s="32"/>
+      <c r="C41" s="33"/>
       <c r="D41" s="24"/>
-      <c r="E41" s="66" t="s">
+      <c r="E41" s="68" t="s">
         <v>356</v>
       </c>
       <c r="F41" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="G41" s="49" t="n">
+      <c r="G41" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="49" t="n">
+      <c r="H41" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="I41" s="32"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="40"/>
-      <c r="L41" s="40"/>
-      <c r="M41" s="40"/>
-      <c r="N41" s="40"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="8"/>
-      <c r="Q41" s="8" t="s">
+      <c r="I41" s="33"/>
+      <c r="J41" s="41"/>
+      <c r="K41" s="41"/>
+      <c r="L41" s="41"/>
+      <c r="M41" s="41"/>
+      <c r="N41" s="41"/>
+      <c r="O41" s="8"/>
+      <c r="P41" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="R41" s="60"/>
-    </row>
-    <row r="42" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="32" t="n">
+      <c r="Q41" s="61"/>
+      <c r="AMJ41" s="0"/>
+    </row>
+    <row r="42" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="33" t="n">
         <v>32</v>
       </c>
       <c r="B42" s="24"/>
-      <c r="C42" s="32" t="n">
+      <c r="C42" s="33" t="n">
         <v>30</v>
       </c>
       <c r="D42" s="24"/>
       <c r="E42" s="24" t="s">
         <v>358</v>
       </c>
-      <c r="F42" s="39" t="s">
+      <c r="F42" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="G42" s="32" t="n">
+      <c r="G42" s="33" t="n">
         <v>31</v>
       </c>
-      <c r="H42" s="32" t="n">
+      <c r="H42" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="I42" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="8" t="s">
+      <c r="I42" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="41" t="s">
         <v>359</v>
       </c>
-      <c r="K42" s="40" t="s">
+      <c r="K42" s="41" t="s">
         <v>360</v>
       </c>
-      <c r="L42" s="40" t="s">
+      <c r="L42" s="41"/>
+      <c r="M42" s="41"/>
+      <c r="N42" s="41"/>
+      <c r="O42" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="P42" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="M42" s="40"/>
-      <c r="N42" s="40"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q42" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="R42" s="60"/>
-    </row>
-    <row r="43" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="32"/>
+      <c r="Q42" s="61"/>
+      <c r="AMJ42" s="0"/>
+    </row>
+    <row r="43" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="33"/>
       <c r="B43" s="24"/>
-      <c r="C43" s="32" t="n">
+      <c r="C43" s="33" t="n">
         <v>31</v>
       </c>
       <c r="D43" s="24"/>
-      <c r="E43" s="66" t="s">
+      <c r="E43" s="68" t="s">
         <v>356</v>
       </c>
-      <c r="F43" s="39" t="s">
+      <c r="F43" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="G43" s="32" t="n">
+      <c r="G43" s="33" t="n">
         <v>31</v>
       </c>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="8" t="s">
+      <c r="H43" s="33"/>
+      <c r="I43" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="41" t="s">
         <v>362</v>
       </c>
-      <c r="K43" s="40" t="s">
+      <c r="K43" s="41" t="s">
         <v>363</v>
       </c>
-      <c r="L43" s="40" t="s">
+      <c r="L43" s="41"/>
+      <c r="M43" s="41"/>
+      <c r="N43" s="41"/>
+      <c r="O43" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="M43" s="40"/>
-      <c r="N43" s="40"/>
-      <c r="O43" s="40"/>
       <c r="P43" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="Q43" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="R43" s="63"/>
-    </row>
-    <row r="44" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="32" t="n">
+      <c r="Q43" s="64"/>
+      <c r="AMJ43" s="0"/>
+    </row>
+    <row r="44" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="33" t="n">
         <v>33</v>
       </c>
       <c r="B44" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="C44" s="32" t="n">
+      <c r="C44" s="33" t="n">
         <v>32</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="24" t="s">
         <v>366</v>
       </c>
-      <c r="F44" s="39" t="s">
+      <c r="F44" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="G44" s="32" t="n">
+      <c r="G44" s="33" t="n">
         <v>31</v>
       </c>
-      <c r="H44" s="32" t="n">
+      <c r="H44" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="I44" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="8"/>
-      <c r="K44" s="40" t="s">
+      <c r="I44" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="L44" s="40"/>
-      <c r="M44" s="40"/>
-      <c r="N44" s="40"/>
-      <c r="O44" s="40"/>
+      <c r="K44" s="41"/>
+      <c r="L44" s="41"/>
+      <c r="M44" s="41"/>
+      <c r="N44" s="41"/>
+      <c r="O44" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="P44" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q44" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="R44" s="60"/>
-    </row>
-    <row r="45" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="42" t="n">
+      <c r="Q44" s="61"/>
+      <c r="AMJ44" s="0"/>
+    </row>
+    <row r="45" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="43" t="n">
         <v>35</v>
       </c>
       <c r="B45" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="C45" s="42"/>
+      <c r="C45" s="43"/>
       <c r="D45" s="23"/>
       <c r="E45" s="23" t="s">
         <v>369</v>
@@ -7984,288 +7909,284 @@
       <c r="F45" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="G45" s="42" t="n">
+      <c r="G45" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="H45" s="42" t="n">
+      <c r="H45" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="I45" s="42"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="46"/>
-      <c r="L45" s="46"/>
-      <c r="M45" s="46"/>
-      <c r="N45" s="46"/>
-      <c r="O45" s="46"/>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="8" t="s">
+      <c r="I45" s="43"/>
+      <c r="J45" s="47"/>
+      <c r="K45" s="47"/>
+      <c r="L45" s="47"/>
+      <c r="M45" s="47"/>
+      <c r="N45" s="47"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="R45" s="60"/>
-    </row>
-    <row r="46" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="42" t="n">
+      <c r="Q45" s="61"/>
+      <c r="AMJ45" s="0"/>
+    </row>
+    <row r="46" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="43" t="n">
         <v>36</v>
       </c>
       <c r="B46" s="23"/>
-      <c r="C46" s="42" t="n">
+      <c r="C46" s="43" t="n">
         <v>36</v>
       </c>
       <c r="D46" s="23"/>
       <c r="E46" s="23" t="s">
         <v>371</v>
       </c>
-      <c r="F46" s="47" t="s">
+      <c r="F46" s="48" t="s">
         <v>123</v>
       </c>
-      <c r="G46" s="42" t="n">
+      <c r="G46" s="43" t="n">
         <v>35</v>
       </c>
-      <c r="H46" s="42" t="n">
+      <c r="H46" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="I46" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="5" t="s">
+      <c r="I46" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="47" t="s">
         <v>372</v>
       </c>
-      <c r="K46" s="46" t="s">
+      <c r="K46" s="47" t="s">
         <v>373</v>
       </c>
-      <c r="L46" s="46" t="s">
+      <c r="L46" s="47"/>
+      <c r="M46" s="47" t="s">
         <v>374</v>
       </c>
-      <c r="M46" s="46"/>
-      <c r="N46" s="46" t="s">
+      <c r="N46" s="47"/>
+      <c r="O46" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="P46" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="O46" s="46"/>
-      <c r="P46" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q46" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="R46" s="63"/>
-    </row>
-    <row r="47" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="42" t="n">
+      <c r="Q46" s="64"/>
+      <c r="AMJ46" s="0"/>
+    </row>
+    <row r="47" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="43" t="n">
         <v>37</v>
       </c>
       <c r="B47" s="23"/>
-      <c r="C47" s="42" t="n">
+      <c r="C47" s="43" t="n">
         <v>37</v>
       </c>
       <c r="D47" s="23"/>
       <c r="E47" s="23" t="s">
         <v>371</v>
       </c>
-      <c r="F47" s="47" t="s">
+      <c r="F47" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="G47" s="42" t="n">
+      <c r="G47" s="43" t="n">
         <v>35</v>
       </c>
-      <c r="H47" s="42" t="n">
+      <c r="H47" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="I47" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="5"/>
-      <c r="K47" s="46" t="s">
+      <c r="I47" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="47" t="s">
         <v>376</v>
       </c>
-      <c r="L47" s="46"/>
-      <c r="M47" s="46"/>
-      <c r="N47" s="46"/>
-      <c r="O47" s="46"/>
-      <c r="P47" s="5" t="s">
+      <c r="K47" s="47"/>
+      <c r="L47" s="47"/>
+      <c r="M47" s="47"/>
+      <c r="N47" s="47"/>
+      <c r="O47" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="Q47" s="8" t="s">
+      <c r="P47" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="R47" s="63"/>
-    </row>
-    <row r="48" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="42"/>
+      <c r="Q47" s="64"/>
+      <c r="AMJ47" s="0"/>
+    </row>
+    <row r="48" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="43"/>
       <c r="B48" s="23"/>
-      <c r="C48" s="42" t="n">
+      <c r="C48" s="43" t="n">
         <v>38</v>
       </c>
       <c r="D48" s="23"/>
       <c r="E48" s="23" t="s">
         <v>378</v>
       </c>
-      <c r="F48" s="47"/>
-      <c r="G48" s="42"/>
-      <c r="H48" s="42"/>
-      <c r="I48" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="5"/>
-      <c r="K48" s="46" t="s">
+      <c r="F48" s="48"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="47" t="s">
         <v>379</v>
       </c>
-      <c r="L48" s="46"/>
-      <c r="M48" s="46"/>
-      <c r="N48" s="46"/>
-      <c r="O48" s="46"/>
-      <c r="P48" s="5" t="s">
+      <c r="K48" s="47"/>
+      <c r="L48" s="47"/>
+      <c r="M48" s="47"/>
+      <c r="N48" s="47"/>
+      <c r="O48" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="Q48" s="8" t="s">
+      <c r="P48" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="R48" s="63"/>
-    </row>
-    <row r="49" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="42"/>
+      <c r="Q48" s="64"/>
+      <c r="AMJ48" s="0"/>
+    </row>
+    <row r="49" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="43"/>
       <c r="B49" s="23"/>
-      <c r="C49" s="42" t="n">
+      <c r="C49" s="43" t="n">
         <v>39</v>
       </c>
       <c r="D49" s="23"/>
       <c r="E49" s="23" t="s">
         <v>381</v>
       </c>
-      <c r="F49" s="47"/>
-      <c r="G49" s="42"/>
-      <c r="H49" s="42"/>
-      <c r="I49" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="5"/>
-      <c r="K49" s="46" t="s">
+      <c r="F49" s="48"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="47" t="s">
         <v>382</v>
       </c>
-      <c r="L49" s="46"/>
-      <c r="M49" s="46"/>
-      <c r="N49" s="46"/>
-      <c r="O49" s="46"/>
-      <c r="P49" s="5" t="s">
+      <c r="K49" s="47"/>
+      <c r="L49" s="47"/>
+      <c r="M49" s="47"/>
+      <c r="N49" s="47"/>
+      <c r="O49" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="Q49" s="8" t="s">
+      <c r="P49" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="R49" s="63"/>
-    </row>
-    <row r="50" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="42"/>
+      <c r="Q49" s="64"/>
+      <c r="AMJ49" s="0"/>
+    </row>
+    <row r="50" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="43"/>
       <c r="B50" s="23"/>
-      <c r="C50" s="42" t="n">
+      <c r="C50" s="43" t="n">
         <v>40</v>
       </c>
       <c r="D50" s="23"/>
       <c r="E50" s="23" t="s">
         <v>378</v>
       </c>
-      <c r="F50" s="47"/>
-      <c r="G50" s="42"/>
-      <c r="H50" s="42"/>
-      <c r="I50" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="5"/>
-      <c r="K50" s="46" t="s">
+      <c r="F50" s="48"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="47" t="s">
         <v>384</v>
       </c>
-      <c r="L50" s="46"/>
-      <c r="M50" s="46"/>
-      <c r="N50" s="46"/>
-      <c r="O50" s="46"/>
-      <c r="P50" s="5" t="s">
+      <c r="K50" s="47"/>
+      <c r="L50" s="47"/>
+      <c r="M50" s="47"/>
+      <c r="N50" s="47"/>
+      <c r="O50" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="Q50" s="8" t="s">
+      <c r="P50" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="R50" s="60"/>
-    </row>
-    <row r="51" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="42" t="n">
+      <c r="Q50" s="61"/>
+      <c r="AMJ50" s="0"/>
+    </row>
+    <row r="51" s="62" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="43" t="n">
         <v>38</v>
       </c>
       <c r="B51" s="23"/>
-      <c r="C51" s="42" t="n">
+      <c r="C51" s="43" t="n">
         <v>41</v>
       </c>
       <c r="D51" s="23"/>
       <c r="E51" s="23" t="s">
         <v>386</v>
       </c>
-      <c r="F51" s="47" t="s">
+      <c r="F51" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="G51" s="42" t="n">
+      <c r="G51" s="43" t="n">
         <v>35</v>
       </c>
-      <c r="H51" s="42" t="n">
+      <c r="H51" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="I51" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="5" t="s">
+      <c r="I51" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="K51" s="46" t="s">
+      <c r="K51" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="L51" s="46" t="s">
+      <c r="L51" s="47"/>
+      <c r="M51" s="47" t="s">
         <v>389</v>
       </c>
-      <c r="M51" s="46"/>
-      <c r="N51" s="46" t="s">
+      <c r="N51" s="47"/>
+      <c r="O51" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="O51" s="46"/>
       <c r="P51" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="Q51" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="R51" s="63"/>
+      <c r="Q51" s="64"/>
+      <c r="AMJ51" s="0"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="67" t="n">
+      <c r="A52" s="69" t="n">
         <v>43</v>
       </c>
-      <c r="B52" s="68" t="n">
+      <c r="B52" s="70" t="n">
         <v>2</v>
       </c>
-      <c r="C52" s="67"/>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68" t="n">
+      <c r="C52" s="69"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70" t="n">
         <v>43</v>
       </c>
-      <c r="F52" s="29" t="s">
+      <c r="F52" s="30" t="s">
         <v>392</v>
       </c>
-      <c r="G52" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" s="67" t="n">
+      <c r="G52" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="I52" s="67"/>
-      <c r="K52" s="69"/>
-      <c r="L52" s="69"/>
-      <c r="M52" s="69"/>
-      <c r="N52" s="69"/>
-      <c r="O52" s="69"/>
-      <c r="R52" s="48"/>
+      <c r="I52" s="69"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="71"/>
+      <c r="L52" s="71"/>
+      <c r="M52" s="71"/>
+      <c r="N52" s="71"/>
+      <c r="Q52" s="49"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="32" t="n">
+      <c r="A53" s="33" t="n">
         <v>44</v>
       </c>
       <c r="B53" s="24"/>
-      <c r="C53" s="32" t="n">
+      <c r="C53" s="33" t="n">
         <v>45</v>
       </c>
       <c r="D53" s="24"/>
@@ -8275,35 +8196,34 @@
       <c r="F53" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="G53" s="49" t="n">
+      <c r="G53" s="50" t="n">
         <v>43</v>
       </c>
-      <c r="H53" s="49" t="n">
+      <c r="H53" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="I53" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="8"/>
-      <c r="K53" s="40" t="s">
+      <c r="I53" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="41" t="s">
         <v>394</v>
       </c>
-      <c r="L53" s="40"/>
-      <c r="M53" s="40"/>
-      <c r="N53" s="40"/>
-      <c r="O53" s="40"/>
-      <c r="P53" s="8"/>
-      <c r="Q53" s="8" t="s">
+      <c r="K53" s="41"/>
+      <c r="L53" s="41"/>
+      <c r="M53" s="41"/>
+      <c r="N53" s="41"/>
+      <c r="O53" s="8"/>
+      <c r="P53" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="R53" s="48"/>
+      <c r="Q53" s="49"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="42" t="n">
+      <c r="A54" s="43" t="n">
         <v>45</v>
       </c>
       <c r="B54" s="23"/>
-      <c r="C54" s="42" t="n">
+      <c r="C54" s="43" t="n">
         <v>46</v>
       </c>
       <c r="D54" s="23"/>
@@ -8313,35 +8233,34 @@
       <c r="F54" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="G54" s="42" t="n">
+      <c r="G54" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H54" s="42" t="n">
+      <c r="H54" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I54" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="5"/>
-      <c r="K54" s="46" t="s">
+      <c r="I54" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="47" t="s">
         <v>397</v>
       </c>
-      <c r="L54" s="46"/>
-      <c r="M54" s="46"/>
-      <c r="N54" s="46"/>
-      <c r="O54" s="46"/>
-      <c r="P54" s="5"/>
-      <c r="Q54" s="5" t="s">
+      <c r="K54" s="47"/>
+      <c r="L54" s="47"/>
+      <c r="M54" s="47"/>
+      <c r="N54" s="47"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="R54" s="48"/>
+      <c r="Q54" s="49"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="32" t="n">
+      <c r="A55" s="33" t="n">
         <v>46</v>
       </c>
       <c r="B55" s="24"/>
-      <c r="C55" s="32" t="n">
+      <c r="C55" s="33" t="n">
         <v>47</v>
       </c>
       <c r="D55" s="24"/>
@@ -8351,391 +8270,377 @@
       <c r="F55" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="G55" s="32" t="n">
+      <c r="G55" s="33" t="n">
         <v>43</v>
       </c>
-      <c r="H55" s="32" t="n">
+      <c r="H55" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I55" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="8"/>
-      <c r="K55" s="40" t="s">
+      <c r="I55" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="41" t="s">
         <v>400</v>
       </c>
-      <c r="L55" s="40"/>
-      <c r="M55" s="40"/>
-      <c r="N55" s="40"/>
-      <c r="O55" s="40"/>
-      <c r="P55" s="8"/>
-      <c r="Q55" s="8" t="s">
+      <c r="K55" s="41"/>
+      <c r="L55" s="41"/>
+      <c r="M55" s="41"/>
+      <c r="N55" s="41"/>
+      <c r="O55" s="8"/>
+      <c r="P55" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="R55" s="48"/>
+      <c r="Q55" s="49"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="32" t="n">
+      <c r="A56" s="33" t="n">
         <v>47</v>
       </c>
       <c r="B56" s="24"/>
-      <c r="C56" s="32" t="n">
+      <c r="C56" s="33" t="n">
         <v>48</v>
       </c>
       <c r="D56" s="24"/>
       <c r="E56" s="24" t="s">
         <v>402</v>
       </c>
-      <c r="F56" s="39" t="s">
+      <c r="F56" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="G56" s="32" t="n">
+      <c r="G56" s="33" t="n">
         <v>46</v>
       </c>
-      <c r="H56" s="32" t="n">
+      <c r="H56" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="8"/>
-      <c r="K56" s="40" t="s">
+      <c r="I56" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="41" t="s">
         <v>403</v>
       </c>
-      <c r="L56" s="40"/>
-      <c r="M56" s="40"/>
-      <c r="N56" s="40"/>
-      <c r="O56" s="40"/>
-      <c r="P56" s="8"/>
-      <c r="Q56" s="8" t="s">
+      <c r="K56" s="41"/>
+      <c r="L56" s="41"/>
+      <c r="M56" s="41"/>
+      <c r="N56" s="41"/>
+      <c r="O56" s="8"/>
+      <c r="P56" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="R56" s="48"/>
+      <c r="Q56" s="49"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="32" t="n">
+      <c r="A57" s="33" t="n">
         <v>48</v>
       </c>
       <c r="B57" s="24" t="n">
         <v>47</v>
       </c>
-      <c r="C57" s="32" t="n">
+      <c r="C57" s="33" t="n">
         <v>49</v>
       </c>
       <c r="D57" s="24"/>
       <c r="E57" s="24" t="s">
         <v>405</v>
       </c>
-      <c r="F57" s="39" t="s">
+      <c r="F57" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="G57" s="32" t="n">
+      <c r="G57" s="33" t="n">
         <v>46</v>
       </c>
-      <c r="H57" s="32" t="n">
+      <c r="H57" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I57" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="8"/>
-      <c r="K57" s="40" t="s">
+      <c r="I57" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="41" t="s">
         <v>406</v>
       </c>
-      <c r="L57" s="40"/>
-      <c r="M57" s="40"/>
-      <c r="N57" s="40"/>
-      <c r="O57" s="40"/>
-      <c r="P57" s="8"/>
-      <c r="Q57" s="8" t="s">
+      <c r="K57" s="41"/>
+      <c r="L57" s="41"/>
+      <c r="M57" s="41"/>
+      <c r="N57" s="41"/>
+      <c r="O57" s="8"/>
+      <c r="P57" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="R57" s="48"/>
+      <c r="Q57" s="49"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="32" t="n">
+      <c r="A58" s="33" t="n">
         <v>49</v>
       </c>
       <c r="B58" s="24"/>
-      <c r="C58" s="32" t="n">
+      <c r="C58" s="33" t="n">
         <v>50</v>
       </c>
       <c r="D58" s="24"/>
       <c r="E58" s="24" t="s">
         <v>408</v>
       </c>
-      <c r="F58" s="39" t="s">
+      <c r="F58" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="G58" s="32" t="n">
+      <c r="G58" s="33" t="n">
         <v>46</v>
       </c>
-      <c r="H58" s="32" t="n">
+      <c r="H58" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="8"/>
-      <c r="K58" s="40" t="s">
+      <c r="I58" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="41" t="s">
         <v>409</v>
       </c>
-      <c r="L58" s="40"/>
-      <c r="M58" s="40"/>
-      <c r="N58" s="40"/>
-      <c r="O58" s="40"/>
-      <c r="P58" s="8"/>
-      <c r="Q58" s="8" t="s">
+      <c r="K58" s="41"/>
+      <c r="L58" s="41"/>
+      <c r="M58" s="41"/>
+      <c r="N58" s="41"/>
+      <c r="O58" s="8"/>
+      <c r="P58" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="R58" s="48"/>
+      <c r="Q58" s="49"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="32" t="n">
+      <c r="A59" s="33" t="n">
         <v>50</v>
       </c>
       <c r="B59" s="24"/>
-      <c r="C59" s="32" t="n">
+      <c r="C59" s="33" t="n">
         <v>51</v>
       </c>
       <c r="D59" s="24"/>
       <c r="E59" s="24" t="s">
         <v>411</v>
       </c>
-      <c r="F59" s="39" t="s">
+      <c r="F59" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="G59" s="32" t="n">
+      <c r="G59" s="33" t="n">
         <v>46</v>
       </c>
-      <c r="H59" s="32" t="n">
+      <c r="H59" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I59" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="8"/>
-      <c r="K59" s="40" t="s">
+      <c r="I59" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="41" t="s">
         <v>412</v>
       </c>
-      <c r="L59" s="40"/>
-      <c r="M59" s="40"/>
-      <c r="N59" s="40"/>
-      <c r="O59" s="40"/>
-      <c r="P59" s="8"/>
-      <c r="Q59" s="8" t="s">
+      <c r="K59" s="41"/>
+      <c r="L59" s="41"/>
+      <c r="M59" s="41"/>
+      <c r="N59" s="41"/>
+      <c r="O59" s="8"/>
+      <c r="P59" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="R59" s="48"/>
+      <c r="Q59" s="49"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="32" t="n">
+      <c r="A60" s="33" t="n">
         <v>51</v>
       </c>
       <c r="B60" s="24" t="n">
         <v>49</v>
       </c>
-      <c r="C60" s="32" t="n">
+      <c r="C60" s="33" t="n">
         <v>52</v>
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="24" t="s">
         <v>414</v>
       </c>
-      <c r="F60" s="39" t="s">
+      <c r="F60" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="G60" s="32" t="n">
+      <c r="G60" s="33" t="n">
         <v>46</v>
       </c>
-      <c r="H60" s="32" t="n">
+      <c r="H60" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I60" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="8"/>
-      <c r="K60" s="40" t="s">
+      <c r="I60" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="41" t="s">
         <v>415</v>
       </c>
-      <c r="L60" s="40"/>
-      <c r="M60" s="40"/>
-      <c r="N60" s="40" t="s">
+      <c r="K60" s="41"/>
+      <c r="L60" s="41"/>
+      <c r="M60" s="41" t="s">
         <v>416</v>
       </c>
-      <c r="O60" s="40"/>
-      <c r="P60" s="8"/>
-      <c r="Q60" s="8" t="s">
+      <c r="N60" s="41"/>
+      <c r="O60" s="8"/>
+      <c r="P60" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="R60" s="48"/>
+      <c r="Q60" s="49"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="32" t="n">
+      <c r="A61" s="33" t="n">
         <v>52</v>
       </c>
       <c r="B61" s="24"/>
-      <c r="C61" s="32" t="n">
+      <c r="C61" s="33" t="n">
         <v>53</v>
       </c>
       <c r="D61" s="24"/>
       <c r="E61" s="24" t="s">
         <v>418</v>
       </c>
-      <c r="F61" s="52" t="s">
+      <c r="F61" s="53" t="s">
         <v>419</v>
       </c>
-      <c r="G61" s="32" t="n">
+      <c r="G61" s="33" t="n">
         <v>51</v>
       </c>
-      <c r="H61" s="32" t="n">
+      <c r="H61" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I61" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="8"/>
-      <c r="K61" s="40" t="s">
+      <c r="I61" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="41" t="s">
         <v>420</v>
       </c>
-      <c r="L61" s="40"/>
-      <c r="M61" s="40"/>
-      <c r="N61" s="40"/>
-      <c r="O61" s="40"/>
-      <c r="P61" s="8"/>
-      <c r="Q61" s="8" t="s">
+      <c r="K61" s="41"/>
+      <c r="L61" s="41"/>
+      <c r="M61" s="41"/>
+      <c r="N61" s="41"/>
+      <c r="O61" s="8"/>
+      <c r="P61" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="R61" s="48"/>
+      <c r="Q61" s="49"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="32" t="n">
+      <c r="A62" s="33" t="n">
         <v>53</v>
       </c>
       <c r="B62" s="24"/>
-      <c r="C62" s="32" t="n">
+      <c r="C62" s="33" t="n">
         <v>54</v>
       </c>
       <c r="D62" s="24"/>
       <c r="E62" s="24" t="s">
         <v>422</v>
       </c>
-      <c r="F62" s="52" t="s">
+      <c r="F62" s="53" t="s">
         <v>160</v>
       </c>
-      <c r="G62" s="32" t="n">
+      <c r="G62" s="33" t="n">
         <v>51</v>
       </c>
-      <c r="H62" s="32" t="n">
+      <c r="H62" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I62" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="8"/>
-      <c r="K62" s="40" t="s">
+      <c r="I62" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="41" t="s">
         <v>423</v>
       </c>
-      <c r="L62" s="40"/>
-      <c r="M62" s="40"/>
-      <c r="N62" s="40"/>
-      <c r="O62" s="40"/>
-      <c r="P62" s="8"/>
-      <c r="Q62" s="8" t="s">
+      <c r="K62" s="41"/>
+      <c r="L62" s="41"/>
+      <c r="M62" s="41"/>
+      <c r="N62" s="41"/>
+      <c r="O62" s="8"/>
+      <c r="P62" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="R62" s="41"/>
+      <c r="Q62" s="42"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="32" t="n">
+      <c r="A63" s="33" t="n">
         <v>54</v>
       </c>
       <c r="B63" s="24"/>
-      <c r="C63" s="32" t="n">
+      <c r="C63" s="33" t="n">
         <v>55</v>
       </c>
       <c r="D63" s="24"/>
       <c r="E63" s="24" t="s">
         <v>425</v>
       </c>
-      <c r="F63" s="39" t="s">
+      <c r="F63" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="G63" s="32" t="n">
+      <c r="G63" s="33" t="n">
         <v>46</v>
       </c>
-      <c r="H63" s="32" t="n">
+      <c r="H63" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I63" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="8" t="s">
+      <c r="I63" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="41" t="s">
         <v>426</v>
       </c>
-      <c r="K63" s="40" t="s">
+      <c r="K63" s="41" t="s">
         <v>427</v>
       </c>
-      <c r="L63" s="40" t="s">
+      <c r="L63" s="41"/>
+      <c r="M63" s="41"/>
+      <c r="N63" s="41"/>
+      <c r="O63" s="8"/>
+      <c r="P63" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="M63" s="40"/>
-      <c r="N63" s="40"/>
-      <c r="O63" s="40"/>
-      <c r="P63" s="8"/>
-      <c r="Q63" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="R63" s="41"/>
+      <c r="Q63" s="42"/>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="32" t="n">
+      <c r="A64" s="33" t="n">
         <v>55</v>
       </c>
       <c r="B64" s="24"/>
-      <c r="C64" s="32" t="n">
+      <c r="C64" s="33" t="n">
         <v>56</v>
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="24" t="s">
         <v>429</v>
       </c>
-      <c r="F64" s="39" t="s">
+      <c r="F64" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="G64" s="32" t="n">
+      <c r="G64" s="33" t="n">
         <v>46</v>
       </c>
-      <c r="H64" s="32" t="n">
+      <c r="H64" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I64" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="8" t="s">
+      <c r="I64" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="41" t="s">
         <v>430</v>
       </c>
-      <c r="K64" s="40" t="s">
+      <c r="K64" s="41" t="s">
         <v>431</v>
       </c>
-      <c r="L64" s="40" t="s">
+      <c r="L64" s="41"/>
+      <c r="M64" s="41"/>
+      <c r="N64" s="41"/>
+      <c r="O64" s="8"/>
+      <c r="P64" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="M64" s="40"/>
-      <c r="N64" s="40"/>
-      <c r="O64" s="40"/>
-      <c r="P64" s="8"/>
-      <c r="Q64" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="R64" s="41"/>
+      <c r="Q64" s="42"/>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="42" t="n">
+      <c r="A65" s="43" t="n">
         <v>56</v>
       </c>
       <c r="B65" s="23"/>
-      <c r="C65" s="42" t="n">
+      <c r="C65" s="43" t="n">
         <v>57</v>
       </c>
       <c r="D65" s="23"/>
@@ -8745,39 +8650,36 @@
       <c r="F65" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G65" s="42" t="n">
+      <c r="G65" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H65" s="70" t="n">
+      <c r="H65" s="72" t="n">
         <v>2</v>
       </c>
-      <c r="I65" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="5" t="s">
+      <c r="I65" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="47" t="s">
         <v>434</v>
       </c>
-      <c r="K65" s="46" t="s">
+      <c r="K65" s="47" t="s">
         <v>435</v>
       </c>
-      <c r="L65" s="46" t="s">
+      <c r="L65" s="47"/>
+      <c r="M65" s="47"/>
+      <c r="N65" s="47"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="M65" s="46"/>
-      <c r="N65" s="46"/>
-      <c r="O65" s="46"/>
-      <c r="P65" s="5"/>
-      <c r="Q65" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="R65" s="48"/>
+      <c r="Q65" s="49"/>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="32" t="n">
+      <c r="A66" s="33" t="n">
         <v>57</v>
       </c>
       <c r="B66" s="24"/>
-      <c r="C66" s="32"/>
+      <c r="C66" s="33"/>
       <c r="D66" s="24"/>
       <c r="E66" s="24" t="s">
         <v>437</v>
@@ -8785,233 +8687,219 @@
       <c r="F66" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G66" s="32" t="n">
+      <c r="G66" s="33" t="n">
         <v>43</v>
       </c>
-      <c r="H66" s="32" t="n">
+      <c r="H66" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I66" s="32"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="40"/>
-      <c r="L66" s="40"/>
-      <c r="M66" s="40"/>
-      <c r="N66" s="40"/>
-      <c r="O66" s="40"/>
-      <c r="P66" s="8"/>
-      <c r="Q66" s="8" t="s">
+      <c r="I66" s="33"/>
+      <c r="J66" s="41"/>
+      <c r="K66" s="41"/>
+      <c r="L66" s="41"/>
+      <c r="M66" s="41"/>
+      <c r="N66" s="41"/>
+      <c r="O66" s="8"/>
+      <c r="P66" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="R66" s="41"/>
+      <c r="Q66" s="42"/>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="32" t="n">
+      <c r="A67" s="33" t="n">
         <v>58</v>
       </c>
       <c r="B67" s="24"/>
-      <c r="C67" s="32" t="n">
+      <c r="C67" s="33" t="n">
         <v>58</v>
       </c>
       <c r="D67" s="24"/>
       <c r="E67" s="24" t="s">
         <v>439</v>
       </c>
-      <c r="F67" s="39" t="s">
+      <c r="F67" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="G67" s="32" t="n">
+      <c r="G67" s="33" t="n">
         <v>57</v>
       </c>
-      <c r="H67" s="32" t="n">
+      <c r="H67" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I67" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="8" t="s">
+      <c r="I67" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="41" t="s">
         <v>440</v>
       </c>
-      <c r="K67" s="40" t="s">
+      <c r="K67" s="41" t="s">
         <v>441</v>
       </c>
-      <c r="L67" s="40" t="s">
+      <c r="L67" s="41"/>
+      <c r="M67" s="41"/>
+      <c r="N67" s="41"/>
+      <c r="O67" s="8"/>
+      <c r="P67" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="M67" s="40"/>
-      <c r="N67" s="40"/>
-      <c r="O67" s="40"/>
-      <c r="P67" s="8"/>
-      <c r="Q67" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="R67" s="41"/>
+      <c r="Q67" s="42"/>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="32" t="n">
+      <c r="A68" s="33" t="n">
         <v>59</v>
       </c>
       <c r="B68" s="24"/>
-      <c r="C68" s="32" t="n">
+      <c r="C68" s="33" t="n">
         <v>59</v>
       </c>
       <c r="D68" s="24"/>
       <c r="E68" s="24" t="s">
         <v>443</v>
       </c>
-      <c r="F68" s="39" t="s">
+      <c r="F68" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="G68" s="32" t="n">
+      <c r="G68" s="33" t="n">
         <v>57</v>
       </c>
-      <c r="H68" s="32" t="n">
+      <c r="H68" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I68" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="8" t="s">
+      <c r="I68" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="41" t="s">
         <v>444</v>
       </c>
-      <c r="K68" s="40" t="s">
+      <c r="K68" s="41" t="s">
         <v>445</v>
       </c>
-      <c r="L68" s="40" t="s">
+      <c r="L68" s="41"/>
+      <c r="M68" s="41"/>
+      <c r="N68" s="41"/>
+      <c r="O68" s="8"/>
+      <c r="P68" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="M68" s="40"/>
-      <c r="N68" s="40"/>
-      <c r="O68" s="40"/>
-      <c r="P68" s="8"/>
-      <c r="Q68" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="R68" s="41"/>
+      <c r="Q68" s="42"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="32" t="n">
+      <c r="A69" s="33" t="n">
         <v>60</v>
       </c>
       <c r="B69" s="24"/>
-      <c r="C69" s="32" t="n">
+      <c r="C69" s="33" t="n">
         <v>60</v>
       </c>
       <c r="D69" s="24"/>
       <c r="E69" s="24" t="s">
         <v>447</v>
       </c>
-      <c r="F69" s="39" t="s">
+      <c r="F69" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="G69" s="32" t="n">
+      <c r="G69" s="33" t="n">
         <v>57</v>
       </c>
-      <c r="H69" s="32" t="n">
+      <c r="H69" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I69" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="8" t="s">
+      <c r="I69" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="41" t="s">
         <v>448</v>
       </c>
-      <c r="K69" s="40" t="s">
+      <c r="K69" s="41" t="s">
         <v>449</v>
       </c>
-      <c r="L69" s="40" t="s">
+      <c r="L69" s="41"/>
+      <c r="M69" s="41"/>
+      <c r="N69" s="41"/>
+      <c r="O69" s="8"/>
+      <c r="P69" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="M69" s="40"/>
-      <c r="N69" s="40"/>
-      <c r="O69" s="40"/>
-      <c r="P69" s="8"/>
-      <c r="Q69" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="R69" s="41"/>
+      <c r="Q69" s="42"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="32" t="n">
+      <c r="A70" s="33" t="n">
         <v>61</v>
       </c>
       <c r="B70" s="24"/>
-      <c r="C70" s="32" t="n">
+      <c r="C70" s="33" t="n">
         <v>61</v>
       </c>
       <c r="D70" s="24"/>
       <c r="E70" s="24" t="s">
         <v>451</v>
       </c>
-      <c r="F70" s="39" t="s">
+      <c r="F70" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="G70" s="32" t="n">
+      <c r="G70" s="33" t="n">
         <v>57</v>
       </c>
-      <c r="H70" s="32" t="n">
+      <c r="H70" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I70" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="8" t="s">
+      <c r="I70" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="41" t="s">
         <v>452</v>
       </c>
-      <c r="K70" s="40" t="s">
+      <c r="K70" s="41" t="s">
         <v>453</v>
       </c>
-      <c r="L70" s="40" t="s">
+      <c r="L70" s="41"/>
+      <c r="M70" s="41"/>
+      <c r="N70" s="41"/>
+      <c r="O70" s="8"/>
+      <c r="P70" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="M70" s="40"/>
-      <c r="N70" s="40"/>
-      <c r="O70" s="40"/>
-      <c r="P70" s="8"/>
-      <c r="Q70" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="R70" s="48"/>
+      <c r="Q70" s="49"/>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="32"/>
+      <c r="A71" s="33"/>
       <c r="B71" s="24"/>
-      <c r="C71" s="32" t="n">
+      <c r="C71" s="33" t="n">
         <v>62</v>
       </c>
       <c r="D71" s="24"/>
       <c r="E71" s="24" t="s">
         <v>437</v>
       </c>
-      <c r="F71" s="39" t="s">
+      <c r="F71" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="G71" s="32" t="n">
+      <c r="G71" s="33" t="n">
         <v>57</v>
       </c>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="8"/>
-      <c r="K71" s="40" t="s">
+      <c r="H71" s="33"/>
+      <c r="I71" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="41" t="s">
         <v>455</v>
       </c>
-      <c r="L71" s="40"/>
-      <c r="M71" s="40"/>
-      <c r="N71" s="40"/>
-      <c r="O71" s="40"/>
-      <c r="P71" s="8"/>
-      <c r="Q71" s="8" t="s">
+      <c r="K71" s="41"/>
+      <c r="L71" s="41"/>
+      <c r="M71" s="41"/>
+      <c r="N71" s="41"/>
+      <c r="O71" s="8"/>
+      <c r="P71" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="R71" s="48"/>
+      <c r="Q71" s="49"/>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="42" t="n">
+      <c r="A72" s="43" t="n">
         <v>62</v>
       </c>
       <c r="B72" s="23"/>
-      <c r="C72" s="42"/>
+      <c r="C72" s="43"/>
       <c r="D72" s="23"/>
       <c r="E72" s="23" t="s">
         <v>457</v>
@@ -9019,119 +8907,112 @@
       <c r="F72" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="G72" s="42" t="n">
+      <c r="G72" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H72" s="42" t="n">
+      <c r="H72" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I72" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="5"/>
-      <c r="K72" s="46"/>
-      <c r="L72" s="46"/>
-      <c r="M72" s="46"/>
-      <c r="N72" s="46"/>
-      <c r="O72" s="46"/>
-      <c r="P72" s="5"/>
-      <c r="Q72" s="5" t="s">
+      <c r="I72" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="47"/>
+      <c r="K72" s="47"/>
+      <c r="L72" s="47"/>
+      <c r="M72" s="47"/>
+      <c r="N72" s="47"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="R72" s="41"/>
+      <c r="Q72" s="42"/>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="42" t="n">
+      <c r="A73" s="43" t="n">
         <v>63</v>
       </c>
       <c r="B73" s="23"/>
-      <c r="C73" s="42" t="n">
+      <c r="C73" s="43" t="n">
         <v>63</v>
       </c>
       <c r="D73" s="23"/>
       <c r="E73" s="23" t="s">
         <v>459</v>
       </c>
-      <c r="F73" s="47" t="s">
+      <c r="F73" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="G73" s="42" t="n">
+      <c r="G73" s="43" t="n">
         <v>62</v>
       </c>
-      <c r="H73" s="42" t="n">
+      <c r="H73" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I73" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="5" t="s">
+      <c r="I73" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="47" t="s">
         <v>460</v>
       </c>
-      <c r="K73" s="46" t="s">
+      <c r="K73" s="47" t="s">
         <v>461</v>
       </c>
-      <c r="L73" s="46" t="s">
+      <c r="L73" s="47"/>
+      <c r="M73" s="47"/>
+      <c r="N73" s="47"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="M73" s="46"/>
-      <c r="N73" s="46"/>
-      <c r="O73" s="46"/>
-      <c r="P73" s="5"/>
-      <c r="Q73" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="R73" s="41"/>
+      <c r="Q73" s="42"/>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="42" t="n">
+      <c r="A74" s="43" t="n">
         <v>64</v>
       </c>
       <c r="B74" s="23"/>
-      <c r="C74" s="42" t="n">
+      <c r="C74" s="43" t="n">
         <v>64</v>
       </c>
       <c r="D74" s="23"/>
       <c r="E74" s="23" t="s">
         <v>463</v>
       </c>
-      <c r="F74" s="47" t="s">
+      <c r="F74" s="48" t="s">
         <v>147</v>
       </c>
-      <c r="G74" s="42" t="n">
+      <c r="G74" s="43" t="n">
         <v>62</v>
       </c>
-      <c r="H74" s="42" t="n">
+      <c r="H74" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I74" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="5" t="s">
+      <c r="I74" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="47" t="s">
         <v>464</v>
       </c>
-      <c r="K74" s="46" t="s">
+      <c r="K74" s="47" t="s">
         <v>465</v>
       </c>
-      <c r="L74" s="46" t="s">
+      <c r="L74" s="47"/>
+      <c r="M74" s="47"/>
+      <c r="N74" s="47"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="M74" s="46"/>
-      <c r="N74" s="46"/>
-      <c r="O74" s="46"/>
-      <c r="P74" s="5"/>
-      <c r="Q74" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="R74" s="41"/>
+      <c r="Q74" s="42"/>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="42" t="n">
+      <c r="A75" s="43" t="n">
         <v>65</v>
       </c>
       <c r="B75" s="23" t="n">
         <v>63</v>
       </c>
-      <c r="C75" s="42" t="n">
+      <c r="C75" s="43" t="n">
         <v>65</v>
       </c>
       <c r="D75" s="23" t="n">
@@ -9140,313 +9021,295 @@
       <c r="E75" s="23" t="s">
         <v>467</v>
       </c>
-      <c r="F75" s="47" t="s">
+      <c r="F75" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="G75" s="42" t="n">
+      <c r="G75" s="43" t="n">
         <v>62</v>
       </c>
-      <c r="H75" s="42" t="n">
+      <c r="H75" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I75" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="5" t="s">
+      <c r="I75" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="47" t="s">
         <v>468</v>
       </c>
-      <c r="K75" s="46" t="s">
+      <c r="K75" s="47" t="s">
         <v>469</v>
       </c>
-      <c r="L75" s="46" t="s">
+      <c r="L75" s="47"/>
+      <c r="M75" s="47"/>
+      <c r="N75" s="47"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="M75" s="46"/>
-      <c r="N75" s="46"/>
-      <c r="O75" s="46"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="R75" s="41"/>
+      <c r="Q75" s="42"/>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="42" t="n">
+      <c r="A76" s="43" t="n">
         <v>66</v>
       </c>
       <c r="B76" s="23"/>
-      <c r="C76" s="42" t="n">
+      <c r="C76" s="43" t="n">
         <v>66</v>
       </c>
       <c r="D76" s="23"/>
       <c r="E76" s="23" t="s">
         <v>471</v>
       </c>
-      <c r="F76" s="55" t="s">
+      <c r="F76" s="56" t="s">
         <v>270</v>
       </c>
-      <c r="G76" s="42" t="n">
+      <c r="G76" s="43" t="n">
         <v>65</v>
       </c>
-      <c r="H76" s="42" t="n">
+      <c r="H76" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I76" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="5" t="s">
+      <c r="I76" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" s="47" t="s">
         <v>472</v>
       </c>
-      <c r="K76" s="46" t="s">
+      <c r="K76" s="47" t="s">
         <v>473</v>
       </c>
-      <c r="L76" s="46" t="s">
+      <c r="L76" s="47"/>
+      <c r="M76" s="47"/>
+      <c r="N76" s="47"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="M76" s="46"/>
-      <c r="N76" s="46"/>
-      <c r="O76" s="46"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="R76" s="41"/>
+      <c r="Q76" s="42"/>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="42" t="n">
+      <c r="A77" s="43" t="n">
         <v>67</v>
       </c>
       <c r="B77" s="23"/>
-      <c r="C77" s="42" t="n">
+      <c r="C77" s="43" t="n">
         <v>67</v>
       </c>
       <c r="D77" s="23"/>
       <c r="E77" s="23" t="s">
         <v>475</v>
       </c>
-      <c r="F77" s="55" t="s">
+      <c r="F77" s="56" t="s">
         <v>276</v>
       </c>
-      <c r="G77" s="42" t="n">
+      <c r="G77" s="43" t="n">
         <v>65</v>
       </c>
-      <c r="H77" s="42" t="n">
+      <c r="H77" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I77" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="5" t="s">
+      <c r="I77" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="47" t="s">
         <v>476</v>
       </c>
-      <c r="K77" s="46" t="s">
+      <c r="K77" s="47" t="s">
         <v>477</v>
       </c>
-      <c r="L77" s="46" t="s">
+      <c r="L77" s="47"/>
+      <c r="M77" s="47"/>
+      <c r="N77" s="47"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="M77" s="46"/>
-      <c r="N77" s="46"/>
-      <c r="O77" s="46"/>
-      <c r="P77" s="5"/>
-      <c r="Q77" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="R77" s="41"/>
+      <c r="Q77" s="42"/>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="42"/>
+      <c r="A78" s="43"/>
       <c r="B78" s="23"/>
-      <c r="C78" s="42" t="n">
+      <c r="C78" s="43" t="n">
         <v>68</v>
       </c>
       <c r="D78" s="23"/>
       <c r="E78" s="23" t="s">
         <v>479</v>
       </c>
-      <c r="F78" s="55" t="s">
+      <c r="F78" s="56" t="s">
         <v>480</v>
       </c>
-      <c r="G78" s="42" t="n">
+      <c r="G78" s="43" t="n">
         <v>65</v>
       </c>
-      <c r="H78" s="42"/>
-      <c r="I78" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="5" t="s">
+      <c r="H78" s="43"/>
+      <c r="I78" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="47"/>
+      <c r="K78" s="47" t="s">
         <v>481</v>
       </c>
-      <c r="K78" s="46"/>
-      <c r="L78" s="46" t="s">
+      <c r="L78" s="47" t="s">
         <v>482</v>
       </c>
-      <c r="M78" s="46" t="s">
+      <c r="M78" s="47"/>
+      <c r="N78" s="47"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="N78" s="46"/>
-      <c r="O78" s="46"/>
-      <c r="P78" s="5"/>
-      <c r="Q78" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="R78" s="48"/>
+      <c r="Q78" s="49"/>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="32" t="n">
+      <c r="A79" s="33" t="n">
         <v>68</v>
       </c>
       <c r="B79" s="24"/>
-      <c r="C79" s="32"/>
+      <c r="C79" s="33"/>
       <c r="D79" s="24"/>
       <c r="E79" s="24" t="s">
         <v>484</v>
       </c>
-      <c r="F79" s="71" t="s">
+      <c r="F79" s="73" t="s">
         <v>126</v>
       </c>
-      <c r="G79" s="51" t="n">
+      <c r="G79" s="52" t="n">
         <v>43</v>
       </c>
-      <c r="H79" s="32" t="n">
+      <c r="H79" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I79" s="32"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="40"/>
-      <c r="L79" s="40"/>
-      <c r="M79" s="40"/>
-      <c r="N79" s="40"/>
-      <c r="O79" s="40"/>
-      <c r="P79" s="8"/>
-      <c r="Q79" s="8" t="s">
+      <c r="I79" s="33"/>
+      <c r="J79" s="41"/>
+      <c r="K79" s="41"/>
+      <c r="L79" s="41"/>
+      <c r="M79" s="41"/>
+      <c r="N79" s="41"/>
+      <c r="O79" s="8"/>
+      <c r="P79" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="R79" s="48"/>
+      <c r="Q79" s="49"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="32" t="n">
+      <c r="A80" s="33" t="n">
         <v>69</v>
       </c>
       <c r="B80" s="24"/>
-      <c r="C80" s="32" t="n">
+      <c r="C80" s="33" t="n">
         <v>69</v>
       </c>
       <c r="D80" s="24"/>
       <c r="E80" s="24" t="s">
         <v>486</v>
       </c>
-      <c r="F80" s="39" t="s">
+      <c r="F80" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="G80" s="32" t="n">
+      <c r="G80" s="33" t="n">
         <v>68</v>
       </c>
-      <c r="H80" s="32" t="n">
+      <c r="H80" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I80" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="8"/>
-      <c r="K80" s="40" t="s">
+      <c r="I80" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="41" t="s">
         <v>487</v>
       </c>
-      <c r="L80" s="40"/>
-      <c r="M80" s="40"/>
-      <c r="N80" s="40"/>
-      <c r="O80" s="40"/>
-      <c r="P80" s="8"/>
-      <c r="Q80" s="8" t="s">
+      <c r="K80" s="41"/>
+      <c r="L80" s="41"/>
+      <c r="M80" s="41"/>
+      <c r="N80" s="41"/>
+      <c r="O80" s="8"/>
+      <c r="P80" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="R80" s="48"/>
+      <c r="Q80" s="49"/>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="32" t="n">
+      <c r="A81" s="33" t="n">
         <v>70</v>
       </c>
       <c r="B81" s="24"/>
-      <c r="C81" s="32" t="n">
+      <c r="C81" s="33" t="n">
         <v>70</v>
       </c>
       <c r="D81" s="24"/>
       <c r="E81" s="24" t="s">
         <v>489</v>
       </c>
-      <c r="F81" s="52" t="s">
+      <c r="F81" s="53" t="s">
         <v>490</v>
       </c>
-      <c r="G81" s="32" t="n">
+      <c r="G81" s="33" t="n">
         <v>69</v>
       </c>
-      <c r="H81" s="32" t="n">
+      <c r="H81" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I81" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="8"/>
-      <c r="K81" s="40" t="s">
+      <c r="I81" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="41" t="s">
         <v>491</v>
       </c>
-      <c r="L81" s="40"/>
-      <c r="M81" s="40"/>
-      <c r="N81" s="40"/>
-      <c r="O81" s="40"/>
-      <c r="P81" s="8"/>
-      <c r="Q81" s="8" t="s">
+      <c r="K81" s="41"/>
+      <c r="L81" s="41"/>
+      <c r="M81" s="41"/>
+      <c r="N81" s="41"/>
+      <c r="O81" s="8"/>
+      <c r="P81" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="R81" s="41"/>
+      <c r="Q81" s="42"/>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="32" t="n">
+      <c r="A82" s="33" t="n">
         <v>71</v>
       </c>
       <c r="B82" s="24"/>
-      <c r="C82" s="32" t="n">
+      <c r="C82" s="33" t="n">
         <v>71</v>
       </c>
       <c r="D82" s="24"/>
       <c r="E82" s="24" t="s">
         <v>493</v>
       </c>
-      <c r="F82" s="39" t="s">
+      <c r="F82" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="G82" s="32" t="n">
+      <c r="G82" s="33" t="n">
         <v>68</v>
       </c>
-      <c r="H82" s="32" t="n">
+      <c r="H82" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I82" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="8" t="s">
+      <c r="I82" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="41" t="s">
         <v>494</v>
       </c>
-      <c r="K82" s="40" t="s">
+      <c r="K82" s="41" t="s">
         <v>495</v>
       </c>
-      <c r="L82" s="40" t="s">
+      <c r="L82" s="41"/>
+      <c r="M82" s="41"/>
+      <c r="N82" s="41"/>
+      <c r="O82" s="8"/>
+      <c r="P82" s="8" t="s">
         <v>496</v>
       </c>
-      <c r="M82" s="40"/>
-      <c r="N82" s="40"/>
-      <c r="O82" s="40"/>
-      <c r="P82" s="8"/>
-      <c r="Q82" s="8" t="s">
-        <v>494</v>
-      </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="42" t="n">
+      <c r="A83" s="43" t="n">
         <v>72</v>
       </c>
       <c r="B83" s="23"/>
-      <c r="C83" s="42"/>
+      <c r="C83" s="43"/>
       <c r="D83" s="23"/>
       <c r="E83" s="23" t="s">
         <v>497</v>
@@ -9454,139 +9317,135 @@
       <c r="F83" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="G83" s="42" t="n">
+      <c r="G83" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H83" s="42" t="n">
+      <c r="H83" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I83" s="42"/>
-      <c r="J83" s="5"/>
-      <c r="K83" s="46"/>
-      <c r="L83" s="46"/>
-      <c r="M83" s="46"/>
-      <c r="N83" s="46"/>
-      <c r="O83" s="46"/>
-      <c r="P83" s="5"/>
-      <c r="Q83" s="5" t="s">
+      <c r="I83" s="43"/>
+      <c r="J83" s="47"/>
+      <c r="K83" s="47"/>
+      <c r="L83" s="47"/>
+      <c r="M83" s="47"/>
+      <c r="N83" s="47"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="5" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="42" t="n">
+      <c r="A84" s="43" t="n">
         <v>73</v>
       </c>
       <c r="B84" s="23"/>
-      <c r="C84" s="42" t="n">
+      <c r="C84" s="43" t="n">
         <v>72</v>
       </c>
       <c r="D84" s="23"/>
       <c r="E84" s="23" t="s">
         <v>499</v>
       </c>
-      <c r="F84" s="47" t="s">
+      <c r="F84" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="G84" s="42" t="n">
+      <c r="G84" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H84" s="42" t="n">
+      <c r="H84" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I84" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="5"/>
-      <c r="K84" s="46" t="s">
+      <c r="I84" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="47" t="s">
         <v>500</v>
       </c>
-      <c r="L84" s="46"/>
-      <c r="M84" s="46"/>
-      <c r="N84" s="46"/>
-      <c r="O84" s="46"/>
-      <c r="P84" s="5"/>
-      <c r="Q84" s="5" t="s">
+      <c r="K84" s="47"/>
+      <c r="L84" s="47"/>
+      <c r="M84" s="47"/>
+      <c r="N84" s="47"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="5" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="42" t="n">
+      <c r="A85" s="43" t="n">
         <v>74</v>
       </c>
       <c r="B85" s="23"/>
-      <c r="C85" s="42" t="n">
+      <c r="C85" s="43" t="n">
         <v>73</v>
       </c>
       <c r="D85" s="23"/>
       <c r="E85" s="23"/>
-      <c r="F85" s="47" t="s">
+      <c r="F85" s="48" t="s">
         <v>155</v>
       </c>
-      <c r="G85" s="42" t="n">
+      <c r="G85" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H85" s="42" t="n">
+      <c r="H85" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I85" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="5"/>
-      <c r="K85" s="72"/>
-      <c r="L85" s="46"/>
-      <c r="M85" s="46"/>
-      <c r="N85" s="46"/>
-      <c r="O85" s="46"/>
-      <c r="P85" s="5"/>
-      <c r="Q85" s="5" t="s">
+      <c r="I85" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="74"/>
+      <c r="K85" s="47"/>
+      <c r="L85" s="47"/>
+      <c r="M85" s="47"/>
+      <c r="N85" s="47"/>
+      <c r="O85" s="5"/>
+      <c r="P85" s="5" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="42" t="n">
+      <c r="A86" s="43" t="n">
         <v>75</v>
       </c>
       <c r="B86" s="23"/>
-      <c r="C86" s="42" t="n">
+      <c r="C86" s="43" t="n">
         <v>74</v>
       </c>
       <c r="D86" s="23"/>
       <c r="E86" s="23" t="s">
         <v>503</v>
       </c>
-      <c r="F86" s="47" t="s">
+      <c r="F86" s="48" t="s">
         <v>156</v>
       </c>
-      <c r="G86" s="42" t="n">
+      <c r="G86" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H86" s="42" t="n">
+      <c r="H86" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I86" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="5"/>
-      <c r="K86" s="46" t="s">
+      <c r="I86" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" s="47" t="s">
         <v>504</v>
       </c>
-      <c r="L86" s="46"/>
-      <c r="M86" s="46"/>
-      <c r="N86" s="46"/>
-      <c r="O86" s="46"/>
-      <c r="P86" s="5"/>
-      <c r="Q86" s="5" t="s">
+      <c r="K86" s="47"/>
+      <c r="L86" s="47"/>
+      <c r="M86" s="47"/>
+      <c r="N86" s="47"/>
+      <c r="O86" s="5"/>
+      <c r="P86" s="5" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="42" t="n">
+      <c r="A87" s="43" t="n">
         <v>76</v>
       </c>
       <c r="B87" s="23" t="n">
         <v>75</v>
       </c>
-      <c r="C87" s="42" t="n">
+      <c r="C87" s="43" t="n">
         <v>75</v>
       </c>
       <c r="D87" s="23" t="n">
@@ -9595,152 +9454,146 @@
       <c r="E87" s="23" t="s">
         <v>506</v>
       </c>
-      <c r="F87" s="47" t="s">
+      <c r="F87" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="G87" s="42" t="n">
+      <c r="G87" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H87" s="42" t="n">
+      <c r="H87" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I87" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="5"/>
-      <c r="K87" s="46" t="s">
+      <c r="I87" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="47" t="s">
         <v>507</v>
       </c>
-      <c r="L87" s="46"/>
-      <c r="M87" s="46"/>
-      <c r="N87" s="46"/>
-      <c r="O87" s="46"/>
-      <c r="P87" s="5"/>
-      <c r="Q87" s="5" t="s">
+      <c r="K87" s="47"/>
+      <c r="L87" s="47"/>
+      <c r="M87" s="47"/>
+      <c r="N87" s="47"/>
+      <c r="O87" s="5"/>
+      <c r="P87" s="5" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="42" t="n">
+      <c r="A88" s="43" t="n">
         <v>77</v>
       </c>
       <c r="B88" s="23" t="n">
         <v>75</v>
       </c>
-      <c r="C88" s="42"/>
+      <c r="C88" s="43"/>
       <c r="D88" s="23" t="n">
         <v>75</v>
       </c>
       <c r="E88" s="23"/>
-      <c r="F88" s="47" t="s">
+      <c r="F88" s="48" t="s">
         <v>509</v>
       </c>
-      <c r="G88" s="42" t="n">
+      <c r="G88" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H88" s="42" t="n">
+      <c r="H88" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I88" s="42"/>
-      <c r="J88" s="5"/>
-      <c r="K88" s="46"/>
-      <c r="L88" s="46"/>
-      <c r="M88" s="46"/>
-      <c r="N88" s="46"/>
-      <c r="O88" s="46"/>
-      <c r="P88" s="5"/>
-      <c r="Q88" s="5" t="s">
+      <c r="I88" s="43"/>
+      <c r="J88" s="47"/>
+      <c r="K88" s="47"/>
+      <c r="L88" s="47"/>
+      <c r="M88" s="47"/>
+      <c r="N88" s="47"/>
+      <c r="O88" s="5"/>
+      <c r="P88" s="5" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="42" t="n">
+      <c r="A89" s="43" t="n">
         <v>78</v>
       </c>
       <c r="B89" s="23"/>
-      <c r="C89" s="42" t="n">
+      <c r="C89" s="43" t="n">
         <v>76</v>
       </c>
       <c r="D89" s="23"/>
       <c r="E89" s="23" t="s">
         <v>511</v>
       </c>
-      <c r="F89" s="55" t="s">
+      <c r="F89" s="56" t="s">
         <v>512</v>
       </c>
-      <c r="G89" s="42" t="n">
+      <c r="G89" s="43" t="n">
         <v>77</v>
       </c>
-      <c r="H89" s="42" t="n">
+      <c r="H89" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I89" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="5"/>
-      <c r="K89" s="46" t="s">
+      <c r="I89" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="47" t="s">
         <v>513</v>
       </c>
-      <c r="L89" s="46"/>
-      <c r="M89" s="46"/>
-      <c r="N89" s="46"/>
-      <c r="O89" s="46"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="5" t="s">
+      <c r="K89" s="47"/>
+      <c r="L89" s="47"/>
+      <c r="M89" s="47"/>
+      <c r="N89" s="47"/>
+      <c r="O89" s="5"/>
+      <c r="P89" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="R89" s="41"/>
+      <c r="Q89" s="42"/>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="42" t="n">
+      <c r="A90" s="43" t="n">
         <v>79</v>
       </c>
       <c r="B90" s="23"/>
-      <c r="C90" s="42" t="n">
+      <c r="C90" s="43" t="n">
         <v>77</v>
       </c>
       <c r="D90" s="23"/>
       <c r="E90" s="23" t="s">
         <v>515</v>
       </c>
-      <c r="F90" s="55" t="s">
+      <c r="F90" s="56" t="s">
         <v>516</v>
       </c>
-      <c r="G90" s="42" t="n">
+      <c r="G90" s="43" t="n">
         <v>77</v>
       </c>
-      <c r="H90" s="42" t="n">
+      <c r="H90" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I90" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="5" t="s">
+      <c r="I90" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="47" t="s">
         <v>517</v>
       </c>
-      <c r="K90" s="46" t="s">
+      <c r="K90" s="47" t="s">
         <v>518</v>
       </c>
-      <c r="L90" s="46" t="s">
+      <c r="L90" s="47"/>
+      <c r="M90" s="47" t="s">
         <v>519</v>
       </c>
-      <c r="M90" s="46"/>
-      <c r="N90" s="46" t="s">
+      <c r="N90" s="47"/>
+      <c r="O90" s="5"/>
+      <c r="P90" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="O90" s="46"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="R90" s="48"/>
+      <c r="Q90" s="49"/>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="32" t="n">
+      <c r="A91" s="33" t="n">
         <v>80</v>
       </c>
       <c r="B91" s="24"/>
-      <c r="C91" s="32"/>
+      <c r="C91" s="33"/>
       <c r="D91" s="24"/>
       <c r="E91" s="24" t="s">
         <v>521</v>
@@ -9748,797 +9601,745 @@
       <c r="F91" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="G91" s="32" t="n">
+      <c r="G91" s="33" t="n">
         <v>43</v>
       </c>
-      <c r="H91" s="32" t="n">
+      <c r="H91" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I91" s="32"/>
-      <c r="J91" s="8"/>
-      <c r="K91" s="40"/>
-      <c r="L91" s="40"/>
-      <c r="M91" s="40"/>
-      <c r="N91" s="40"/>
-      <c r="O91" s="40"/>
-      <c r="P91" s="8"/>
-      <c r="Q91" s="8" t="s">
+      <c r="I91" s="33"/>
+      <c r="J91" s="41"/>
+      <c r="K91" s="41"/>
+      <c r="L91" s="41"/>
+      <c r="M91" s="41"/>
+      <c r="N91" s="41"/>
+      <c r="O91" s="8"/>
+      <c r="P91" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="R91" s="41"/>
+      <c r="Q91" s="42"/>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="32" t="n">
+      <c r="A92" s="33" t="n">
         <v>81</v>
       </c>
       <c r="B92" s="24"/>
-      <c r="C92" s="32" t="n">
+      <c r="C92" s="33" t="n">
         <v>78</v>
       </c>
       <c r="D92" s="24"/>
       <c r="E92" s="24" t="s">
         <v>523</v>
       </c>
-      <c r="F92" s="39" t="s">
+      <c r="F92" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="G92" s="32" t="n">
+      <c r="G92" s="33" t="n">
         <v>80</v>
       </c>
-      <c r="H92" s="32" t="n">
+      <c r="H92" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I92" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="8" t="s">
+      <c r="I92" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="41" t="s">
         <v>524</v>
       </c>
-      <c r="K92" s="40" t="s">
+      <c r="K92" s="41" t="s">
         <v>525</v>
       </c>
-      <c r="L92" s="40" t="s">
+      <c r="L92" s="41"/>
+      <c r="M92" s="41"/>
+      <c r="N92" s="41"/>
+      <c r="O92" s="8"/>
+      <c r="P92" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="M92" s="40"/>
-      <c r="N92" s="40"/>
-      <c r="O92" s="40"/>
-      <c r="P92" s="8"/>
-      <c r="Q92" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="R92" s="41"/>
+      <c r="Q92" s="42"/>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="32" t="n">
+      <c r="A93" s="33" t="n">
         <v>82</v>
       </c>
       <c r="B93" s="24"/>
-      <c r="C93" s="32" t="n">
+      <c r="C93" s="33" t="n">
         <v>79</v>
       </c>
       <c r="D93" s="24"/>
       <c r="E93" s="24" t="s">
         <v>527</v>
       </c>
-      <c r="F93" s="39" t="s">
+      <c r="F93" s="40" t="s">
         <v>162</v>
       </c>
-      <c r="G93" s="32" t="n">
+      <c r="G93" s="33" t="n">
         <v>80</v>
       </c>
-      <c r="H93" s="32" t="n">
+      <c r="H93" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I93" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="8" t="s">
+      <c r="I93" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" s="41" t="s">
         <v>528</v>
       </c>
-      <c r="K93" s="40" t="s">
+      <c r="K93" s="41" t="s">
         <v>529</v>
       </c>
-      <c r="L93" s="40" t="s">
+      <c r="L93" s="41"/>
+      <c r="M93" s="41"/>
+      <c r="N93" s="41"/>
+      <c r="O93" s="8"/>
+      <c r="P93" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="M93" s="40"/>
-      <c r="N93" s="40"/>
-      <c r="O93" s="40"/>
-      <c r="P93" s="8"/>
-      <c r="Q93" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="R93" s="41"/>
+      <c r="Q93" s="42"/>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="32" t="n">
+      <c r="A94" s="33" t="n">
         <v>83</v>
       </c>
       <c r="B94" s="24"/>
-      <c r="C94" s="32" t="n">
+      <c r="C94" s="33" t="n">
         <v>80</v>
       </c>
       <c r="D94" s="24"/>
       <c r="E94" s="24" t="s">
         <v>531</v>
       </c>
-      <c r="F94" s="39" t="s">
+      <c r="F94" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="G94" s="32" t="n">
+      <c r="G94" s="33" t="n">
         <v>80</v>
       </c>
-      <c r="H94" s="32" t="n">
+      <c r="H94" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I94" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="8" t="s">
+      <c r="I94" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" s="41" t="s">
         <v>532</v>
       </c>
-      <c r="K94" s="40" t="s">
+      <c r="K94" s="41" t="s">
         <v>533</v>
       </c>
-      <c r="L94" s="40" t="s">
+      <c r="L94" s="41"/>
+      <c r="M94" s="41"/>
+      <c r="N94" s="41"/>
+      <c r="O94" s="8"/>
+      <c r="P94" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="M94" s="40"/>
-      <c r="N94" s="40"/>
-      <c r="O94" s="40"/>
-      <c r="P94" s="8"/>
-      <c r="Q94" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="R94" s="41"/>
+      <c r="Q94" s="42"/>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="32" t="n">
+      <c r="A95" s="33" t="n">
         <v>84</v>
       </c>
       <c r="B95" s="24"/>
-      <c r="C95" s="32" t="n">
+      <c r="C95" s="33" t="n">
         <v>81</v>
       </c>
       <c r="D95" s="24"/>
       <c r="E95" s="24" t="s">
         <v>535</v>
       </c>
-      <c r="F95" s="39" t="s">
+      <c r="F95" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="G95" s="32" t="n">
+      <c r="G95" s="33" t="n">
         <v>80</v>
       </c>
-      <c r="H95" s="32" t="n">
+      <c r="H95" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I95" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="8" t="s">
+      <c r="I95" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" s="41" t="s">
         <v>536</v>
       </c>
-      <c r="K95" s="40" t="s">
+      <c r="K95" s="41" t="s">
         <v>537</v>
       </c>
-      <c r="L95" s="40" t="s">
+      <c r="L95" s="41"/>
+      <c r="M95" s="41"/>
+      <c r="N95" s="41"/>
+      <c r="O95" s="8"/>
+      <c r="P95" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="M95" s="40"/>
-      <c r="N95" s="40"/>
-      <c r="O95" s="40"/>
-      <c r="P95" s="8"/>
-      <c r="Q95" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="R95" s="48"/>
+      <c r="Q95" s="49"/>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="42" t="n">
+      <c r="A96" s="43" t="n">
         <v>85</v>
       </c>
       <c r="B96" s="23"/>
-      <c r="C96" s="42"/>
+      <c r="C96" s="43"/>
       <c r="D96" s="23"/>
       <c r="E96" s="23"/>
       <c r="F96" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="G96" s="42" t="n">
+      <c r="G96" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H96" s="42" t="n">
+      <c r="H96" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I96" s="42"/>
-      <c r="J96" s="5"/>
-      <c r="K96" s="46"/>
-      <c r="L96" s="46"/>
-      <c r="M96" s="46"/>
-      <c r="N96" s="46"/>
-      <c r="O96" s="46"/>
-      <c r="P96" s="5"/>
-      <c r="Q96" s="5" t="s">
+      <c r="I96" s="43"/>
+      <c r="J96" s="47"/>
+      <c r="K96" s="47"/>
+      <c r="L96" s="47"/>
+      <c r="M96" s="47"/>
+      <c r="N96" s="47"/>
+      <c r="O96" s="5"/>
+      <c r="P96" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="R96" s="41"/>
+      <c r="Q96" s="42"/>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="42"/>
+      <c r="A97" s="43"/>
       <c r="B97" s="23"/>
-      <c r="C97" s="42" t="n">
+      <c r="C97" s="43" t="n">
         <v>82</v>
       </c>
       <c r="D97" s="23"/>
       <c r="E97" s="23" t="s">
         <v>540</v>
       </c>
-      <c r="F97" s="47" t="s">
+      <c r="F97" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="G97" s="42" t="n">
+      <c r="G97" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H97" s="42"/>
-      <c r="I97" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" s="5" t="s">
+      <c r="H97" s="43"/>
+      <c r="I97" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="47" t="s">
         <v>541</v>
       </c>
-      <c r="K97" s="46" t="s">
+      <c r="K97" s="47" t="s">
         <v>542</v>
       </c>
-      <c r="L97" s="46" t="s">
+      <c r="L97" s="47"/>
+      <c r="M97" s="47"/>
+      <c r="N97" s="47"/>
+      <c r="O97" s="5"/>
+      <c r="P97" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="M97" s="46"/>
-      <c r="N97" s="46"/>
-      <c r="O97" s="46"/>
-      <c r="P97" s="5"/>
-      <c r="Q97" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="R97" s="48"/>
+      <c r="Q97" s="49"/>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="42"/>
+      <c r="A98" s="43"/>
       <c r="B98" s="23"/>
-      <c r="C98" s="42" t="n">
+      <c r="C98" s="43" t="n">
         <v>83</v>
       </c>
       <c r="D98" s="23"/>
       <c r="E98" s="23" t="s">
         <v>540</v>
       </c>
-      <c r="F98" s="47" t="s">
+      <c r="F98" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="G98" s="42" t="n">
+      <c r="G98" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H98" s="42"/>
-      <c r="I98" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="5"/>
-      <c r="K98" s="46" t="s">
+      <c r="H98" s="43"/>
+      <c r="I98" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="47" t="s">
         <v>544</v>
       </c>
-      <c r="L98" s="46"/>
-      <c r="M98" s="46"/>
-      <c r="N98" s="46"/>
-      <c r="O98" s="46"/>
-      <c r="P98" s="5"/>
-      <c r="Q98" s="5" t="s">
+      <c r="K98" s="47"/>
+      <c r="L98" s="47"/>
+      <c r="M98" s="47"/>
+      <c r="N98" s="47"/>
+      <c r="O98" s="5"/>
+      <c r="P98" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="R98" s="41"/>
+      <c r="Q98" s="42"/>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="42" t="n">
+      <c r="A99" s="43" t="n">
         <v>86</v>
       </c>
       <c r="B99" s="23"/>
-      <c r="C99" s="42" t="n">
+      <c r="C99" s="43" t="n">
         <v>84</v>
       </c>
       <c r="D99" s="23"/>
       <c r="E99" s="23" t="s">
         <v>546</v>
       </c>
-      <c r="F99" s="47" t="s">
+      <c r="F99" s="48" t="s">
         <v>155</v>
       </c>
-      <c r="G99" s="42" t="n">
+      <c r="G99" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H99" s="42" t="n">
+      <c r="H99" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I99" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J99" s="5" t="s">
+      <c r="I99" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="47" t="s">
         <v>547</v>
       </c>
-      <c r="K99" s="46" t="s">
+      <c r="K99" s="47" t="s">
         <v>548</v>
       </c>
-      <c r="L99" s="46" t="s">
+      <c r="L99" s="47"/>
+      <c r="M99" s="47"/>
+      <c r="N99" s="47"/>
+      <c r="O99" s="5"/>
+      <c r="P99" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="M99" s="46"/>
-      <c r="N99" s="46"/>
-      <c r="O99" s="46"/>
-      <c r="P99" s="5"/>
-      <c r="Q99" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="R99" s="41"/>
+      <c r="Q99" s="42"/>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="42" t="n">
+      <c r="A100" s="43" t="n">
         <v>87</v>
       </c>
       <c r="B100" s="23"/>
-      <c r="C100" s="42" t="n">
+      <c r="C100" s="43" t="n">
         <v>85</v>
       </c>
       <c r="D100" s="23"/>
       <c r="E100" s="23" t="s">
         <v>550</v>
       </c>
-      <c r="F100" s="47" t="s">
+      <c r="F100" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="G100" s="42" t="n">
+      <c r="G100" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H100" s="42" t="n">
+      <c r="H100" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I100" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" s="5" t="s">
+      <c r="I100" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" s="47" t="s">
         <v>551</v>
       </c>
-      <c r="K100" s="46" t="s">
+      <c r="K100" s="47" t="s">
         <v>552</v>
       </c>
-      <c r="L100" s="46" t="s">
+      <c r="L100" s="47"/>
+      <c r="M100" s="47"/>
+      <c r="N100" s="47"/>
+      <c r="O100" s="5"/>
+      <c r="P100" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="M100" s="46"/>
-      <c r="N100" s="46"/>
-      <c r="O100" s="46"/>
-      <c r="P100" s="5"/>
-      <c r="Q100" s="5" t="s">
-        <v>551</v>
-      </c>
-      <c r="R100" s="41"/>
+      <c r="Q100" s="42"/>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="42" t="n">
+      <c r="A101" s="43" t="n">
         <v>88</v>
       </c>
       <c r="B101" s="23"/>
-      <c r="C101" s="42" t="n">
+      <c r="C101" s="43" t="n">
         <v>86</v>
       </c>
       <c r="D101" s="23"/>
       <c r="E101" s="23" t="s">
         <v>554</v>
       </c>
-      <c r="F101" s="47" t="s">
+      <c r="F101" s="48" t="s">
         <v>166</v>
       </c>
-      <c r="G101" s="42" t="n">
+      <c r="G101" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H101" s="42" t="n">
+      <c r="H101" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I101" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J101" s="5" t="s">
+      <c r="I101" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" s="47" t="s">
         <v>555</v>
       </c>
-      <c r="K101" s="46" t="s">
+      <c r="K101" s="47" t="s">
         <v>556</v>
       </c>
-      <c r="L101" s="46" t="s">
+      <c r="L101" s="47"/>
+      <c r="M101" s="47"/>
+      <c r="N101" s="47"/>
+      <c r="O101" s="5"/>
+      <c r="P101" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="M101" s="46"/>
-      <c r="N101" s="46"/>
-      <c r="O101" s="46"/>
-      <c r="P101" s="5"/>
-      <c r="Q101" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="R101" s="41"/>
+      <c r="Q101" s="42"/>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="42" t="n">
+      <c r="A102" s="43" t="n">
         <v>89</v>
       </c>
       <c r="B102" s="23"/>
-      <c r="C102" s="42" t="n">
+      <c r="C102" s="43" t="n">
         <v>87</v>
       </c>
       <c r="D102" s="23"/>
       <c r="E102" s="23" t="s">
         <v>558</v>
       </c>
-      <c r="F102" s="47" t="s">
+      <c r="F102" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="G102" s="42" t="n">
+      <c r="G102" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H102" s="42" t="n">
+      <c r="H102" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I102" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="5" t="s">
+      <c r="I102" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" s="47" t="s">
         <v>559</v>
       </c>
-      <c r="K102" s="46" t="s">
+      <c r="K102" s="47" t="s">
         <v>560</v>
       </c>
-      <c r="L102" s="46" t="s">
+      <c r="L102" s="47"/>
+      <c r="M102" s="47"/>
+      <c r="N102" s="47"/>
+      <c r="O102" s="5"/>
+      <c r="P102" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="M102" s="46"/>
-      <c r="N102" s="46"/>
-      <c r="O102" s="46"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="R102" s="41"/>
+      <c r="Q102" s="42"/>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="42" t="n">
+      <c r="A103" s="43" t="n">
         <v>90</v>
       </c>
       <c r="B103" s="23"/>
-      <c r="C103" s="42" t="n">
+      <c r="C103" s="43" t="n">
         <v>88</v>
       </c>
       <c r="D103" s="23"/>
       <c r="E103" s="23" t="s">
         <v>562</v>
       </c>
-      <c r="F103" s="47" t="s">
+      <c r="F103" s="48" t="s">
         <v>168</v>
       </c>
-      <c r="G103" s="42" t="n">
+      <c r="G103" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H103" s="42" t="n">
+      <c r="H103" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I103" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J103" s="5" t="s">
+      <c r="I103" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="47" t="s">
         <v>563</v>
       </c>
-      <c r="K103" s="46" t="s">
+      <c r="K103" s="47" t="s">
         <v>564</v>
       </c>
-      <c r="L103" s="46" t="s">
+      <c r="L103" s="47"/>
+      <c r="M103" s="47"/>
+      <c r="N103" s="47"/>
+      <c r="O103" s="5"/>
+      <c r="P103" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="M103" s="46"/>
-      <c r="N103" s="46"/>
-      <c r="O103" s="46"/>
-      <c r="P103" s="5"/>
-      <c r="Q103" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="R103" s="41"/>
+      <c r="Q103" s="42"/>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="42" t="n">
+      <c r="A104" s="43" t="n">
         <v>91</v>
       </c>
       <c r="B104" s="23"/>
-      <c r="C104" s="42" t="n">
+      <c r="C104" s="43" t="n">
         <v>89</v>
       </c>
       <c r="D104" s="23"/>
       <c r="E104" s="23" t="s">
         <v>566</v>
       </c>
-      <c r="F104" s="55" t="s">
+      <c r="F104" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="G104" s="42" t="n">
+      <c r="G104" s="43" t="n">
         <v>90</v>
       </c>
-      <c r="H104" s="42" t="n">
+      <c r="H104" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I104" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J104" s="5" t="s">
+      <c r="I104" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" s="47" t="s">
         <v>568</v>
       </c>
-      <c r="K104" s="46" t="s">
+      <c r="K104" s="47" t="s">
         <v>569</v>
       </c>
-      <c r="L104" s="46" t="s">
+      <c r="L104" s="47"/>
+      <c r="M104" s="47"/>
+      <c r="N104" s="47"/>
+      <c r="O104" s="5"/>
+      <c r="P104" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="M104" s="46"/>
-      <c r="N104" s="46"/>
-      <c r="O104" s="46"/>
-      <c r="P104" s="5"/>
-      <c r="Q104" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="R104" s="41"/>
+      <c r="Q104" s="42"/>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="42" t="n">
+      <c r="A105" s="43" t="n">
         <v>92</v>
       </c>
       <c r="B105" s="23"/>
-      <c r="C105" s="42" t="n">
+      <c r="C105" s="43" t="n">
         <v>90</v>
       </c>
       <c r="D105" s="23"/>
       <c r="E105" s="23" t="s">
         <v>571</v>
       </c>
-      <c r="F105" s="47" t="s">
+      <c r="F105" s="48" t="s">
         <v>170</v>
       </c>
-      <c r="G105" s="42" t="n">
+      <c r="G105" s="43" t="n">
         <v>85</v>
       </c>
-      <c r="H105" s="42" t="n">
+      <c r="H105" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I105" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" s="5" t="s">
+      <c r="I105" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="47" t="s">
         <v>572</v>
       </c>
-      <c r="K105" s="46" t="s">
+      <c r="K105" s="47" t="s">
         <v>573</v>
       </c>
-      <c r="L105" s="46" t="s">
+      <c r="L105" s="47"/>
+      <c r="M105" s="47"/>
+      <c r="N105" s="47"/>
+      <c r="O105" s="5"/>
+      <c r="P105" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="M105" s="46"/>
-      <c r="N105" s="46"/>
-      <c r="O105" s="46"/>
-      <c r="P105" s="5"/>
-      <c r="Q105" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="R105" s="48"/>
+      <c r="Q105" s="49"/>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="32" t="n">
+      <c r="A106" s="33" t="n">
         <v>93</v>
       </c>
       <c r="B106" s="24"/>
-      <c r="C106" s="32"/>
+      <c r="C106" s="33"/>
       <c r="D106" s="24"/>
       <c r="E106" s="24"/>
       <c r="F106" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="G106" s="32" t="n">
+      <c r="G106" s="33" t="n">
         <v>43</v>
       </c>
-      <c r="H106" s="32" t="n">
+      <c r="H106" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I106" s="32"/>
-      <c r="J106" s="8"/>
-      <c r="K106" s="40"/>
-      <c r="L106" s="40"/>
-      <c r="M106" s="40"/>
-      <c r="N106" s="40"/>
-      <c r="O106" s="40"/>
-      <c r="P106" s="8"/>
-      <c r="Q106" s="8" t="s">
+      <c r="I106" s="33"/>
+      <c r="J106" s="41"/>
+      <c r="K106" s="41"/>
+      <c r="L106" s="41"/>
+      <c r="M106" s="41"/>
+      <c r="N106" s="41"/>
+      <c r="O106" s="8"/>
+      <c r="P106" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="R106" s="41"/>
+      <c r="Q106" s="42"/>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="32" t="n">
+      <c r="A107" s="33" t="n">
         <v>94</v>
       </c>
       <c r="B107" s="24"/>
-      <c r="C107" s="32" t="n">
+      <c r="C107" s="33" t="n">
         <v>91</v>
       </c>
       <c r="D107" s="24"/>
       <c r="E107" s="24" t="s">
         <v>576</v>
       </c>
-      <c r="F107" s="39" t="s">
+      <c r="F107" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="G107" s="32" t="n">
+      <c r="G107" s="33" t="n">
         <v>93</v>
       </c>
-      <c r="H107" s="32" t="n">
+      <c r="H107" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I107" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" s="8" t="s">
+      <c r="I107" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="41" t="s">
         <v>577</v>
       </c>
-      <c r="K107" s="40" t="s">
+      <c r="K107" s="41" t="s">
         <v>578</v>
       </c>
-      <c r="L107" s="40" t="s">
+      <c r="L107" s="41"/>
+      <c r="M107" s="41"/>
+      <c r="N107" s="41"/>
+      <c r="O107" s="8"/>
+      <c r="P107" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="M107" s="40"/>
-      <c r="N107" s="40"/>
-      <c r="O107" s="40"/>
-      <c r="P107" s="8"/>
-      <c r="Q107" s="8" t="s">
-        <v>577</v>
-      </c>
-      <c r="R107" s="41"/>
+      <c r="Q107" s="42"/>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="32" t="n">
+      <c r="A108" s="33" t="n">
         <v>95</v>
       </c>
       <c r="B108" s="24"/>
-      <c r="C108" s="32" t="n">
+      <c r="C108" s="33" t="n">
         <v>92</v>
       </c>
       <c r="D108" s="24"/>
       <c r="E108" s="24" t="s">
         <v>580</v>
       </c>
-      <c r="F108" s="39" t="s">
+      <c r="F108" s="40" t="s">
         <v>173</v>
       </c>
-      <c r="G108" s="32" t="n">
+      <c r="G108" s="33" t="n">
         <v>93</v>
       </c>
-      <c r="H108" s="32" t="n">
+      <c r="H108" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I108" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" s="8" t="s">
+      <c r="I108" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="41" t="s">
         <v>581</v>
       </c>
-      <c r="K108" s="40" t="s">
+      <c r="K108" s="41" t="s">
         <v>582</v>
       </c>
-      <c r="L108" s="40" t="s">
+      <c r="L108" s="41"/>
+      <c r="M108" s="41"/>
+      <c r="N108" s="41"/>
+      <c r="O108" s="8"/>
+      <c r="P108" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="M108" s="40"/>
-      <c r="N108" s="40"/>
-      <c r="O108" s="40"/>
-      <c r="P108" s="8"/>
-      <c r="Q108" s="8" t="s">
-        <v>581</v>
-      </c>
-      <c r="R108" s="41"/>
+      <c r="Q108" s="42"/>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="32" t="n">
+      <c r="A109" s="33" t="n">
         <v>96</v>
       </c>
       <c r="B109" s="24"/>
-      <c r="C109" s="32" t="n">
+      <c r="C109" s="33" t="n">
         <v>93</v>
       </c>
       <c r="D109" s="24"/>
       <c r="E109" s="24" t="s">
         <v>584</v>
       </c>
-      <c r="F109" s="39" t="s">
+      <c r="F109" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="G109" s="32" t="n">
+      <c r="G109" s="33" t="n">
         <v>93</v>
       </c>
-      <c r="H109" s="32" t="n">
+      <c r="H109" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I109" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="8" t="s">
+      <c r="I109" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="41" t="s">
         <v>585</v>
       </c>
-      <c r="K109" s="40" t="s">
+      <c r="K109" s="41" t="s">
         <v>586</v>
       </c>
-      <c r="L109" s="40" t="s">
+      <c r="L109" s="41"/>
+      <c r="M109" s="41" t="s">
         <v>587</v>
       </c>
-      <c r="M109" s="40"/>
-      <c r="N109" s="40" t="s">
+      <c r="N109" s="41"/>
+      <c r="O109" s="8"/>
+      <c r="P109" s="8" t="s">
         <v>588</v>
       </c>
-      <c r="O109" s="40"/>
-      <c r="P109" s="8"/>
-      <c r="Q109" s="8" t="s">
-        <v>585</v>
-      </c>
-      <c r="R109" s="41"/>
+      <c r="Q109" s="42"/>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="32" t="n">
+      <c r="A110" s="33" t="n">
         <v>97</v>
       </c>
       <c r="B110" s="24"/>
-      <c r="C110" s="32" t="n">
+      <c r="C110" s="33" t="n">
         <v>94</v>
       </c>
       <c r="D110" s="24"/>
       <c r="E110" s="24" t="s">
         <v>589</v>
       </c>
-      <c r="F110" s="39" t="s">
+      <c r="F110" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="G110" s="32" t="n">
+      <c r="G110" s="33" t="n">
         <v>93</v>
       </c>
-      <c r="H110" s="32" t="n">
+      <c r="H110" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I110" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J110" s="8" t="s">
+      <c r="I110" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" s="41" t="s">
         <v>590</v>
       </c>
-      <c r="K110" s="40" t="s">
+      <c r="K110" s="41" t="s">
         <v>591</v>
       </c>
-      <c r="L110" s="40" t="s">
+      <c r="L110" s="41"/>
+      <c r="M110" s="41" t="s">
         <v>592</v>
       </c>
-      <c r="M110" s="40"/>
-      <c r="N110" s="40" t="s">
+      <c r="N110" s="41"/>
+      <c r="O110" s="8"/>
+      <c r="P110" s="8" t="s">
         <v>593</v>
       </c>
-      <c r="O110" s="40"/>
-      <c r="P110" s="8"/>
-      <c r="Q110" s="8" t="s">
-        <v>590</v>
-      </c>
-      <c r="R110" s="41"/>
+      <c r="Q110" s="42"/>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="42" t="n">
+      <c r="A111" s="43" t="n">
         <v>98</v>
       </c>
       <c r="B111" s="23"/>
-      <c r="C111" s="42" t="n">
+      <c r="C111" s="43" t="n">
         <v>95</v>
       </c>
       <c r="D111" s="23"/>
@@ -10548,192 +10349,179 @@
       <c r="F111" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="G111" s="42" t="n">
+      <c r="G111" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H111" s="42" t="n">
+      <c r="H111" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I111" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J111" s="5" t="s">
+      <c r="I111" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="47" t="s">
         <v>595</v>
       </c>
-      <c r="K111" s="46" t="s">
+      <c r="K111" s="47" t="s">
         <v>596</v>
       </c>
-      <c r="L111" s="46" t="s">
+      <c r="L111" s="47"/>
+      <c r="M111" s="47"/>
+      <c r="N111" s="47"/>
+      <c r="O111" s="5"/>
+      <c r="P111" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="M111" s="46"/>
-      <c r="N111" s="46"/>
-      <c r="O111" s="46"/>
-      <c r="P111" s="5"/>
-      <c r="Q111" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="R111" s="41"/>
+      <c r="Q111" s="42"/>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="42" t="n">
+      <c r="A112" s="43" t="n">
         <v>99</v>
       </c>
       <c r="B112" s="23"/>
-      <c r="C112" s="42" t="n">
+      <c r="C112" s="43" t="n">
         <v>96</v>
       </c>
       <c r="D112" s="23"/>
       <c r="E112" s="23" t="s">
         <v>598</v>
       </c>
-      <c r="F112" s="47" t="s">
+      <c r="F112" s="48" t="s">
         <v>176</v>
       </c>
-      <c r="G112" s="42" t="n">
+      <c r="G112" s="43" t="n">
         <v>98</v>
       </c>
-      <c r="H112" s="42" t="n">
+      <c r="H112" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I112" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J112" s="5" t="s">
+      <c r="I112" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" s="47" t="s">
         <v>599</v>
       </c>
-      <c r="K112" s="46" t="s">
+      <c r="K112" s="47" t="s">
         <v>600</v>
       </c>
-      <c r="L112" s="46" t="s">
+      <c r="L112" s="47"/>
+      <c r="M112" s="47"/>
+      <c r="N112" s="47"/>
+      <c r="O112" s="5"/>
+      <c r="P112" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="M112" s="46"/>
-      <c r="N112" s="46"/>
-      <c r="O112" s="46"/>
-      <c r="P112" s="5"/>
-      <c r="Q112" s="5" t="s">
-        <v>599</v>
-      </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="32" t="n">
+      <c r="A113" s="33" t="n">
         <v>100</v>
       </c>
       <c r="B113" s="24"/>
-      <c r="C113" s="32"/>
+      <c r="C113" s="33"/>
       <c r="D113" s="24"/>
       <c r="E113" s="24"/>
       <c r="F113" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="G113" s="32" t="n">
+      <c r="G113" s="33" t="n">
         <v>43</v>
       </c>
-      <c r="H113" s="32" t="n">
+      <c r="H113" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I113" s="32"/>
-      <c r="J113" s="8"/>
-      <c r="K113" s="40"/>
-      <c r="L113" s="40"/>
-      <c r="M113" s="40"/>
-      <c r="N113" s="40"/>
-      <c r="O113" s="40"/>
-      <c r="P113" s="8"/>
-      <c r="Q113" s="8" t="s">
+      <c r="I113" s="33"/>
+      <c r="J113" s="41"/>
+      <c r="K113" s="41"/>
+      <c r="L113" s="41"/>
+      <c r="M113" s="41"/>
+      <c r="N113" s="41"/>
+      <c r="O113" s="8"/>
+      <c r="P113" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="R113" s="41"/>
+      <c r="Q113" s="42"/>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="32" t="n">
+      <c r="A114" s="33" t="n">
         <v>101</v>
       </c>
       <c r="B114" s="24"/>
-      <c r="C114" s="32" t="n">
+      <c r="C114" s="33" t="n">
         <v>97</v>
       </c>
       <c r="D114" s="24"/>
       <c r="E114" s="24" t="s">
         <v>603</v>
       </c>
-      <c r="F114" s="39" t="s">
+      <c r="F114" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="G114" s="32" t="n">
+      <c r="G114" s="33" t="n">
         <v>100</v>
       </c>
-      <c r="H114" s="32" t="n">
+      <c r="H114" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I114" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J114" s="8" t="s">
+      <c r="I114" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" s="41" t="s">
         <v>604</v>
       </c>
-      <c r="K114" s="40" t="s">
+      <c r="K114" s="41" t="s">
         <v>605</v>
       </c>
-      <c r="L114" s="40" t="s">
+      <c r="L114" s="41"/>
+      <c r="M114" s="41"/>
+      <c r="N114" s="41"/>
+      <c r="O114" s="8"/>
+      <c r="P114" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="M114" s="40"/>
-      <c r="N114" s="40"/>
-      <c r="O114" s="40"/>
-      <c r="P114" s="8"/>
-      <c r="Q114" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="R114" s="41"/>
+      <c r="Q114" s="42"/>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="32" t="n">
+      <c r="A115" s="33" t="n">
         <v>102</v>
       </c>
       <c r="B115" s="24"/>
-      <c r="C115" s="32" t="n">
+      <c r="C115" s="33" t="n">
         <v>98</v>
       </c>
       <c r="D115" s="24"/>
       <c r="E115" s="24" t="s">
         <v>607</v>
       </c>
-      <c r="F115" s="39" t="s">
+      <c r="F115" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="G115" s="32" t="n">
+      <c r="G115" s="33" t="n">
         <v>100</v>
       </c>
-      <c r="H115" s="32" t="n">
+      <c r="H115" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I115" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J115" s="8" t="s">
+      <c r="I115" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" s="41" t="s">
         <v>608</v>
       </c>
-      <c r="K115" s="40" t="s">
+      <c r="K115" s="41" t="s">
         <v>609</v>
       </c>
-      <c r="L115" s="40" t="s">
+      <c r="L115" s="41"/>
+      <c r="M115" s="41"/>
+      <c r="N115" s="41"/>
+      <c r="O115" s="8"/>
+      <c r="P115" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="M115" s="40"/>
-      <c r="N115" s="40"/>
-      <c r="O115" s="40"/>
-      <c r="P115" s="8"/>
-      <c r="Q115" s="8" t="s">
-        <v>608</v>
-      </c>
-      <c r="R115" s="41"/>
+      <c r="Q115" s="42"/>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="32"/>
+      <c r="A116" s="33"/>
       <c r="B116" s="24"/>
-      <c r="C116" s="32" t="n">
+      <c r="C116" s="33" t="n">
         <v>99</v>
       </c>
       <c r="D116" s="24"/>
@@ -10741,35 +10529,32 @@
         <v>607</v>
       </c>
       <c r="F116" s="24"/>
-      <c r="G116" s="32"/>
-      <c r="H116" s="32"/>
-      <c r="I116" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J116" s="8" t="s">
+      <c r="G116" s="33"/>
+      <c r="H116" s="33"/>
+      <c r="I116" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" s="41"/>
+      <c r="K116" s="41" t="s">
         <v>611</v>
       </c>
-      <c r="K116" s="40"/>
-      <c r="L116" s="40" t="s">
+      <c r="L116" s="41"/>
+      <c r="M116" s="41" t="s">
         <v>612</v>
       </c>
-      <c r="M116" s="40"/>
-      <c r="N116" s="40" t="s">
+      <c r="N116" s="41"/>
+      <c r="O116" s="8"/>
+      <c r="P116" s="8" t="s">
         <v>613</v>
       </c>
-      <c r="O116" s="40"/>
-      <c r="P116" s="8"/>
-      <c r="Q116" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="R116" s="48"/>
+      <c r="Q116" s="49"/>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="42" t="n">
+      <c r="A117" s="43" t="n">
         <v>103</v>
       </c>
       <c r="B117" s="23"/>
-      <c r="C117" s="42"/>
+      <c r="C117" s="43"/>
       <c r="D117" s="23"/>
       <c r="E117" s="23" t="n">
         <v>43</v>
@@ -10777,160 +10562,150 @@
       <c r="F117" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="G117" s="42" t="n">
+      <c r="G117" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H117" s="42" t="n">
+      <c r="H117" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I117" s="42"/>
-      <c r="J117" s="5"/>
-      <c r="K117" s="46"/>
-      <c r="L117" s="46"/>
-      <c r="M117" s="46"/>
-      <c r="N117" s="46"/>
-      <c r="O117" s="46"/>
-      <c r="P117" s="5"/>
-      <c r="Q117" s="5" t="s">
+      <c r="I117" s="43"/>
+      <c r="J117" s="47"/>
+      <c r="K117" s="47"/>
+      <c r="L117" s="47"/>
+      <c r="M117" s="47"/>
+      <c r="N117" s="47"/>
+      <c r="O117" s="5"/>
+      <c r="P117" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="R117" s="41"/>
+      <c r="Q117" s="42"/>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="42" t="n">
+      <c r="A118" s="43" t="n">
         <v>104</v>
       </c>
       <c r="B118" s="23"/>
-      <c r="C118" s="42" t="n">
+      <c r="C118" s="43" t="n">
         <v>100</v>
       </c>
       <c r="D118" s="23"/>
       <c r="E118" s="23" t="s">
         <v>615</v>
       </c>
-      <c r="F118" s="47" t="s">
+      <c r="F118" s="48" t="s">
         <v>181</v>
       </c>
-      <c r="G118" s="42" t="n">
+      <c r="G118" s="43" t="n">
         <v>103</v>
       </c>
-      <c r="H118" s="42" t="n">
+      <c r="H118" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I118" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" s="5" t="s">
+      <c r="I118" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" s="47" t="s">
         <v>616</v>
       </c>
-      <c r="K118" s="46" t="s">
+      <c r="K118" s="47" t="s">
         <v>617</v>
       </c>
-      <c r="L118" s="46" t="s">
+      <c r="L118" s="47"/>
+      <c r="M118" s="47"/>
+      <c r="N118" s="47"/>
+      <c r="O118" s="5"/>
+      <c r="P118" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="M118" s="46"/>
-      <c r="N118" s="46"/>
-      <c r="O118" s="46"/>
-      <c r="P118" s="5"/>
-      <c r="Q118" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="R118" s="41"/>
+      <c r="Q118" s="42"/>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="42" t="n">
+      <c r="A119" s="43" t="n">
         <v>105</v>
       </c>
       <c r="B119" s="23"/>
-      <c r="C119" s="42" t="n">
+      <c r="C119" s="43" t="n">
         <v>101</v>
       </c>
       <c r="D119" s="23"/>
       <c r="E119" s="23" t="s">
         <v>619</v>
       </c>
-      <c r="F119" s="47" t="s">
+      <c r="F119" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="G119" s="42" t="n">
+      <c r="G119" s="43" t="n">
         <v>103</v>
       </c>
-      <c r="H119" s="42" t="n">
+      <c r="H119" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I119" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J119" s="5" t="s">
+      <c r="I119" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" s="47" t="s">
         <v>620</v>
       </c>
-      <c r="K119" s="46" t="s">
+      <c r="K119" s="47" t="s">
         <v>621</v>
       </c>
-      <c r="L119" s="46" t="s">
+      <c r="L119" s="47"/>
+      <c r="M119" s="47" t="s">
         <v>622</v>
       </c>
-      <c r="M119" s="46"/>
-      <c r="N119" s="46" t="s">
+      <c r="N119" s="47"/>
+      <c r="O119" s="5"/>
+      <c r="P119" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="O119" s="46"/>
-      <c r="P119" s="5"/>
-      <c r="Q119" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="R119" s="41"/>
+      <c r="Q119" s="42"/>
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="42" t="n">
+      <c r="A120" s="43" t="n">
         <v>106</v>
       </c>
       <c r="B120" s="23"/>
-      <c r="C120" s="42" t="n">
+      <c r="C120" s="43" t="n">
         <v>102</v>
       </c>
       <c r="D120" s="23"/>
       <c r="E120" s="23" t="s">
         <v>624</v>
       </c>
-      <c r="F120" s="47" t="s">
+      <c r="F120" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="G120" s="42" t="n">
+      <c r="G120" s="43" t="n">
         <v>103</v>
       </c>
-      <c r="H120" s="42" t="n">
+      <c r="H120" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I120" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J120" s="5" t="s">
+      <c r="I120" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" s="47" t="s">
         <v>625</v>
       </c>
-      <c r="K120" s="46" t="s">
+      <c r="K120" s="47" t="s">
         <v>626</v>
       </c>
-      <c r="L120" s="46" t="s">
+      <c r="L120" s="47"/>
+      <c r="M120" s="47" t="s">
         <v>627</v>
       </c>
-      <c r="M120" s="46"/>
-      <c r="N120" s="46" t="s">
+      <c r="N120" s="47"/>
+      <c r="O120" s="5"/>
+      <c r="P120" s="5" t="s">
         <v>628</v>
       </c>
-      <c r="O120" s="46"/>
-      <c r="P120" s="5"/>
-      <c r="Q120" s="5" t="s">
-        <v>625</v>
-      </c>
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="32" t="n">
+      <c r="A121" s="33" t="n">
         <v>107</v>
       </c>
       <c r="B121" s="24"/>
-      <c r="C121" s="32" t="n">
+      <c r="C121" s="33" t="n">
         <v>103</v>
       </c>
       <c r="D121" s="24"/>
@@ -10940,34 +10715,33 @@
       <c r="F121" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G121" s="32" t="n">
+      <c r="G121" s="33" t="n">
         <v>43</v>
       </c>
-      <c r="H121" s="32" t="n">
+      <c r="H121" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I121" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J121" s="8"/>
-      <c r="K121" s="40" t="s">
+      <c r="I121" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="L121" s="40"/>
-      <c r="M121" s="40"/>
-      <c r="N121" s="40"/>
-      <c r="O121" s="40"/>
-      <c r="P121" s="8"/>
-      <c r="Q121" s="8" t="s">
+      <c r="K121" s="41"/>
+      <c r="L121" s="41"/>
+      <c r="M121" s="41"/>
+      <c r="N121" s="41"/>
+      <c r="O121" s="8"/>
+      <c r="P121" s="8" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="42" t="n">
+      <c r="A122" s="43" t="n">
         <v>108</v>
       </c>
       <c r="B122" s="23"/>
-      <c r="C122" s="42" t="n">
+      <c r="C122" s="43" t="n">
         <v>104</v>
       </c>
       <c r="D122" s="23"/>
@@ -10977,79 +10751,71 @@
       <c r="F122" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="G122" s="42" t="n">
+      <c r="G122" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="H122" s="42" t="n">
+      <c r="H122" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I122" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J122" s="5"/>
-      <c r="K122" s="46" t="s">
+      <c r="I122" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" s="47" t="s">
         <v>633</v>
       </c>
-      <c r="L122" s="46"/>
-      <c r="M122" s="46"/>
-      <c r="N122" s="46"/>
-      <c r="O122" s="46"/>
-      <c r="P122" s="5"/>
-      <c r="Q122" s="5" t="s">
+      <c r="K122" s="47"/>
+      <c r="L122" s="47"/>
+      <c r="M122" s="47"/>
+      <c r="N122" s="47"/>
+      <c r="O122" s="5"/>
+      <c r="P122" s="5" t="s">
         <v>634</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="42" t="n">
+      <c r="A123" s="43" t="n">
         <v>109</v>
       </c>
       <c r="B123" s="23"/>
-      <c r="C123" s="42" t="n">
+      <c r="C123" s="43" t="n">
         <v>105</v>
       </c>
       <c r="D123" s="23"/>
       <c r="E123" s="23" t="s">
         <v>635</v>
       </c>
-      <c r="F123" s="47" t="s">
+      <c r="F123" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="G123" s="42" t="n">
+      <c r="G123" s="43" t="n">
         <v>108</v>
       </c>
-      <c r="H123" s="42" t="n">
+      <c r="H123" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="I123" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J123" s="5"/>
-      <c r="K123" s="46" t="s">
+      <c r="I123" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" s="47" t="s">
         <v>636</v>
       </c>
-      <c r="L123" s="46"/>
-      <c r="M123" s="46"/>
-      <c r="N123" s="46"/>
-      <c r="O123" s="46"/>
-      <c r="P123" s="5"/>
-      <c r="Q123" s="5" t="s">
+      <c r="K123" s="47"/>
+      <c r="L123" s="47"/>
+      <c r="M123" s="47"/>
+      <c r="N123" s="47"/>
+      <c r="O123" s="5"/>
+      <c r="P123" s="5" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="67"/>
-      <c r="C124" s="67"/>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="67"/>
-      <c r="C125" s="67"/>
-    </row>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="69"/>
+      <c r="C124" s="69"/>
+    </row>
+    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="69"/>
+      <c r="C125" s="69"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.700694444444444" right="0.700694444444444" top="0.7875" bottom="0.7875" header="0.511805555555555" footer="0.511805555555555"/>
@@ -11067,7 +10833,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.76953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.15"/>
@@ -11331,8 +11097,8 @@
       <c r="J17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="68"/>
-      <c r="B18" s="68"/>
+      <c r="A18" s="70"/>
+      <c r="B18" s="70"/>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
